--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>14.08.2026 09:27:20</t>
+    <t>14.08.2026 10:14:56</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -4303,7 +4303,7 @@
     <t>HFA</t>
   </si>
   <si>
-    <t>HSBC PORTFÖY ALLİANZ SERBEST ÖZEL FON</t>
+    <t>HSBC PORTFÖY ALLİANZ DEĞİŞKEN ÖZEL FON</t>
   </si>
   <si>
     <t>HFI</t>
@@ -16347,7 +16347,7 @@
         <v>46248</v>
       </c>
       <c r="D162" s="7">
-        <v>1.343533</v>
+        <v>1.343881</v>
       </c>
       <c r="E162" s="8">
         <v>101770246</v>
@@ -16356,7 +16356,7 @@
         <v>39</v>
       </c>
       <c r="G162" s="8">
-        <v>136731670.48</v>
+        <v>136767118.38</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -16669,7 +16669,7 @@
         <v>46248</v>
       </c>
       <c r="D176" s="7">
-        <v>1.743667</v>
+        <v>1.743659</v>
       </c>
       <c r="E176" s="8">
         <v>1327738269</v>
@@ -16678,7 +16678,7 @@
         <v>2892</v>
       </c>
       <c r="G176" s="8">
-        <v>2315134037.43</v>
+        <v>2315122238.37</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -16899,7 +16899,7 @@
         <v>46248</v>
       </c>
       <c r="D186" s="7">
-        <v>0.792622</v>
+        <v>0.793305</v>
       </c>
       <c r="E186" s="8">
         <v>207068257</v>
@@ -16908,7 +16908,7 @@
         <v>24</v>
       </c>
       <c r="G186" s="8">
-        <v>164126904.14</v>
+        <v>164268213.8</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -19267,17 +19267,17 @@
       <c r="C289" s="6">
         <v>46248</v>
       </c>
-      <c r="D289" s="8">
-        <v>0</v>
+      <c r="D289" s="7">
+        <v>1.468378</v>
       </c>
       <c r="E289" s="8">
-        <v>0</v>
+        <v>2186721220</v>
       </c>
       <c r="F289" s="9">
         <v>61</v>
       </c>
       <c r="G289" s="8">
-        <v>0</v>
+        <v>3210932782.98</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -20119,7 +20119,7 @@
         <v>46248</v>
       </c>
       <c r="D326" s="7">
-        <v>73.937052</v>
+        <v>73.948974</v>
       </c>
       <c r="E326" s="8">
         <v>7358618</v>
@@ -20128,7 +20128,7 @@
         <v>3</v>
       </c>
       <c r="G326" s="8">
-        <v>544074520.04</v>
+        <v>544162249.73</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
@@ -20395,7 +20395,7 @@
         <v>46248</v>
       </c>
       <c r="D338" s="7">
-        <v>101.460335</v>
+        <v>101.462029</v>
       </c>
       <c r="E338" s="8">
         <v>22490084</v>
@@ -20404,7 +20404,7 @@
         <v>1</v>
       </c>
       <c r="G338" s="8">
-        <v>2281851460.05</v>
+        <v>2281889559.74</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
@@ -21866,17 +21866,17 @@
       <c r="C402" s="6">
         <v>46248</v>
       </c>
-      <c r="D402" s="8">
-        <v>0</v>
+      <c r="D402" s="7">
+        <v>1.810198</v>
       </c>
       <c r="E402" s="8">
-        <v>0</v>
+        <v>1458819918</v>
       </c>
       <c r="F402" s="9">
         <v>1365</v>
       </c>
       <c r="G402" s="8">
-        <v>0</v>
+        <v>2640753209.72</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
@@ -22395,17 +22395,17 @@
       <c r="C425" s="6">
         <v>46248</v>
       </c>
-      <c r="D425" s="8">
-        <v>0</v>
+      <c r="D425" s="7">
+        <v>44.359577</v>
       </c>
       <c r="E425" s="8">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F425" s="9">
         <v>1</v>
       </c>
       <c r="G425" s="8">
-        <v>0</v>
+        <v>4435957.68</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
@@ -22856,7 +22856,7 @@
         <v>46248</v>
       </c>
       <c r="D445" s="7">
-        <v>7.653979</v>
+        <v>7.665967</v>
       </c>
       <c r="E445" s="8">
         <v>257723151</v>
@@ -22865,7 +22865,7 @@
         <v>2342</v>
       </c>
       <c r="G445" s="8">
-        <v>1972607578.74</v>
+        <v>1975697139.73</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
@@ -24557,17 +24557,17 @@
       <c r="C519" s="6">
         <v>46248</v>
       </c>
-      <c r="D519" s="8">
-        <v>0</v>
+      <c r="D519" s="7">
+        <v>76.829227</v>
       </c>
       <c r="E519" s="8">
-        <v>0</v>
+        <v>5527677</v>
       </c>
       <c r="F519" s="9">
         <v>1</v>
       </c>
       <c r="G519" s="8">
-        <v>0</v>
+        <v>424687151.09</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
@@ -24787,17 +24787,17 @@
       <c r="C529" s="6">
         <v>46248</v>
       </c>
-      <c r="D529" s="8">
-        <v>0</v>
+      <c r="D529" s="7">
+        <v>62.454857</v>
       </c>
       <c r="E529" s="8">
-        <v>0</v>
+        <v>3941000</v>
       </c>
       <c r="F529" s="9">
         <v>1</v>
       </c>
       <c r="G529" s="8">
-        <v>0</v>
+        <v>246134590.13</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
@@ -24948,17 +24948,17 @@
       <c r="C536" s="6">
         <v>46248</v>
       </c>
-      <c r="D536" s="8">
-        <v>0</v>
+      <c r="D536" s="7">
+        <v>70.370022</v>
       </c>
       <c r="E536" s="8">
-        <v>0</v>
+        <v>53983981</v>
       </c>
       <c r="F536" s="9">
         <v>2</v>
       </c>
       <c r="G536" s="8">
-        <v>0</v>
+        <v>3798853917.57</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.25">
@@ -25109,17 +25109,17 @@
       <c r="C543" s="6">
         <v>46248</v>
       </c>
-      <c r="D543" s="8">
-        <v>0</v>
+      <c r="D543" s="7">
+        <v>60.737761</v>
       </c>
       <c r="E543" s="8">
-        <v>0</v>
+        <v>194715</v>
       </c>
       <c r="F543" s="9">
         <v>1</v>
       </c>
       <c r="G543" s="8">
-        <v>0</v>
+        <v>11826553.15</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -25132,17 +25132,17 @@
       <c r="C544" s="6">
         <v>46248</v>
       </c>
-      <c r="D544" s="8">
-        <v>0</v>
+      <c r="D544" s="7">
+        <v>61.487886</v>
       </c>
       <c r="E544" s="8">
-        <v>0</v>
+        <v>8101428</v>
       </c>
       <c r="F544" s="9">
         <v>4</v>
       </c>
       <c r="G544" s="8">
-        <v>0</v>
+        <v>498139681.63</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
@@ -25178,17 +25178,17 @@
       <c r="C546" s="6">
         <v>46248</v>
       </c>
-      <c r="D546" s="8">
-        <v>0</v>
+      <c r="D546" s="7">
+        <v>76.101797</v>
       </c>
       <c r="E546" s="8">
-        <v>0</v>
+        <v>2099501</v>
       </c>
       <c r="F546" s="9">
         <v>2</v>
       </c>
       <c r="G546" s="8">
-        <v>0</v>
+        <v>159775798.67</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
@@ -25247,17 +25247,17 @@
       <c r="C549" s="6">
         <v>46248</v>
       </c>
-      <c r="D549" s="8">
-        <v>0</v>
+      <c r="D549" s="7">
+        <v>69.965845</v>
       </c>
       <c r="E549" s="8">
-        <v>0</v>
+        <v>5961167</v>
       </c>
       <c r="F549" s="9">
         <v>4</v>
       </c>
       <c r="G549" s="8">
-        <v>0</v>
+        <v>417078087.67</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -25293,17 +25293,17 @@
       <c r="C551" s="6">
         <v>46248</v>
       </c>
-      <c r="D551" s="8">
-        <v>0</v>
+      <c r="D551" s="7">
+        <v>53.549853</v>
       </c>
       <c r="E551" s="8">
-        <v>0</v>
+        <v>30698413</v>
       </c>
       <c r="F551" s="9">
         <v>3</v>
       </c>
       <c r="G551" s="8">
-        <v>0</v>
+        <v>1643895490.71</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -25316,17 +25316,17 @@
       <c r="C552" s="6">
         <v>46248</v>
       </c>
-      <c r="D552" s="8">
-        <v>0</v>
+      <c r="D552" s="10">
+        <v>11.79357</v>
       </c>
       <c r="E552" s="8">
-        <v>0</v>
+        <v>29486927</v>
       </c>
       <c r="F552" s="9">
         <v>1</v>
       </c>
       <c r="G552" s="8">
-        <v>0</v>
+        <v>347756131.23</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
@@ -25362,17 +25362,17 @@
       <c r="C554" s="6">
         <v>46248</v>
       </c>
-      <c r="D554" s="8">
-        <v>0</v>
+      <c r="D554" s="7">
+        <v>70.259437</v>
       </c>
       <c r="E554" s="8">
-        <v>0</v>
+        <v>5822807</v>
       </c>
       <c r="F554" s="9">
         <v>3</v>
       </c>
       <c r="G554" s="8">
-        <v>0</v>
+        <v>409107143.84</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
@@ -25385,17 +25385,17 @@
       <c r="C555" s="6">
         <v>46248</v>
       </c>
-      <c r="D555" s="8">
-        <v>0</v>
+      <c r="D555" s="7">
+        <v>66.984754</v>
       </c>
       <c r="E555" s="8">
-        <v>0</v>
+        <v>123364230</v>
       </c>
       <c r="F555" s="9">
         <v>3</v>
       </c>
       <c r="G555" s="8">
-        <v>0</v>
+        <v>8263522579.84</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -25431,17 +25431,17 @@
       <c r="C557" s="6">
         <v>46248</v>
       </c>
-      <c r="D557" s="8">
-        <v>0</v>
+      <c r="D557" s="7">
+        <v>65.620039</v>
       </c>
       <c r="E557" s="8">
-        <v>0</v>
+        <v>90240169</v>
       </c>
       <c r="F557" s="9">
         <v>2</v>
       </c>
       <c r="G557" s="8">
-        <v>0</v>
+        <v>5921563369.55</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
@@ -25477,17 +25477,17 @@
       <c r="C559" s="6">
         <v>46248</v>
       </c>
-      <c r="D559" s="8">
-        <v>0</v>
+      <c r="D559" s="7">
+        <v>8.415003</v>
       </c>
       <c r="E559" s="8">
-        <v>0</v>
+        <v>342290935</v>
       </c>
       <c r="F559" s="9">
         <v>1</v>
       </c>
       <c r="G559" s="8">
-        <v>0</v>
+        <v>2880379094.42</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.25">
@@ -25523,17 +25523,17 @@
       <c r="C561" s="6">
         <v>46248</v>
       </c>
-      <c r="D561" s="8">
-        <v>0</v>
+      <c r="D561" s="7">
+        <v>11.241304</v>
       </c>
       <c r="E561" s="8">
-        <v>0</v>
+        <v>6927</v>
       </c>
       <c r="F561" s="9">
         <v>1</v>
       </c>
       <c r="G561" s="8">
-        <v>0</v>
+        <v>77868.51</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
@@ -25546,17 +25546,17 @@
       <c r="C562" s="6">
         <v>46248</v>
       </c>
-      <c r="D562" s="8">
-        <v>0</v>
+      <c r="D562" s="7">
+        <v>67.967874</v>
       </c>
       <c r="E562" s="8">
-        <v>0</v>
+        <v>23597904</v>
       </c>
       <c r="F562" s="9">
         <v>3</v>
       </c>
       <c r="G562" s="8">
-        <v>0</v>
+        <v>1603899371.78</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
@@ -25661,17 +25661,17 @@
       <c r="C567" s="6">
         <v>46248</v>
       </c>
-      <c r="D567" s="8">
-        <v>0</v>
+      <c r="D567" s="7">
+        <v>66.548538</v>
       </c>
       <c r="E567" s="8">
-        <v>0</v>
+        <v>14263356</v>
       </c>
       <c r="F567" s="9">
         <v>3</v>
       </c>
       <c r="G567" s="8">
-        <v>0</v>
+        <v>949205495.81</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
@@ -25730,17 +25730,17 @@
       <c r="C570" s="6">
         <v>46248</v>
       </c>
-      <c r="D570" s="8">
-        <v>0</v>
+      <c r="D570" s="7">
+        <v>63.801383</v>
       </c>
       <c r="E570" s="8">
-        <v>0</v>
+        <v>2316713</v>
       </c>
       <c r="F570" s="9">
         <v>2</v>
       </c>
       <c r="G570" s="8">
-        <v>0</v>
+        <v>147809494.22</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -25753,17 +25753,17 @@
       <c r="C571" s="6">
         <v>46248</v>
       </c>
-      <c r="D571" s="8">
-        <v>0</v>
+      <c r="D571" s="7">
+        <v>63.971473</v>
       </c>
       <c r="E571" s="8">
-        <v>0</v>
+        <v>3663843</v>
       </c>
       <c r="F571" s="9">
         <v>2</v>
       </c>
       <c r="G571" s="8">
-        <v>0</v>
+        <v>234381434.9</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
@@ -25822,17 +25822,17 @@
       <c r="C574" s="6">
         <v>46248</v>
       </c>
-      <c r="D574" s="8">
-        <v>0</v>
+      <c r="D574" s="7">
+        <v>59.734197</v>
       </c>
       <c r="E574" s="8">
-        <v>0</v>
+        <v>9779449</v>
       </c>
       <c r="F574" s="9">
         <v>1</v>
       </c>
       <c r="G574" s="8">
-        <v>0</v>
+        <v>584167534.81</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
@@ -26144,17 +26144,17 @@
       <c r="C588" s="6">
         <v>46248</v>
       </c>
-      <c r="D588" s="8">
-        <v>0</v>
+      <c r="D588" s="10">
+        <v>68.25815</v>
       </c>
       <c r="E588" s="8">
-        <v>0</v>
+        <v>8202021</v>
       </c>
       <c r="F588" s="9">
         <v>4</v>
       </c>
       <c r="G588" s="8">
-        <v>0</v>
+        <v>559854780.19</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -26260,7 +26260,7 @@
         <v>46248</v>
       </c>
       <c r="D593" s="7">
-        <v>2.730035</v>
+        <v>2.730134</v>
       </c>
       <c r="E593" s="8">
         <v>1181608</v>
@@ -26269,7 +26269,7 @@
         <v>107</v>
       </c>
       <c r="G593" s="8">
-        <v>3225831.13</v>
+        <v>3225947.72</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
@@ -26535,17 +26535,17 @@
       <c r="C605" s="6">
         <v>46248</v>
       </c>
-      <c r="D605" s="8">
-        <v>0</v>
+      <c r="D605" s="7">
+        <v>60.905951</v>
       </c>
       <c r="E605" s="8">
-        <v>0</v>
+        <v>29495736</v>
       </c>
       <c r="F605" s="9">
         <v>4</v>
       </c>
       <c r="G605" s="8">
-        <v>0</v>
+        <v>1796465849.08</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
@@ -26880,17 +26880,17 @@
       <c r="C620" s="6">
         <v>46248</v>
       </c>
-      <c r="D620" s="8">
-        <v>0</v>
+      <c r="D620" s="7">
+        <v>64.495398</v>
       </c>
       <c r="E620" s="8">
-        <v>0</v>
+        <v>11319859</v>
       </c>
       <c r="F620" s="9">
         <v>445</v>
       </c>
       <c r="G620" s="8">
-        <v>0</v>
+        <v>730078815.04</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
@@ -27018,17 +27018,17 @@
       <c r="C626" s="6">
         <v>46248</v>
       </c>
-      <c r="D626" s="8">
-        <v>0</v>
+      <c r="D626" s="7">
+        <v>45.124482</v>
       </c>
       <c r="E626" s="8">
-        <v>0</v>
+        <v>58637</v>
       </c>
       <c r="F626" s="9">
         <v>1</v>
       </c>
       <c r="G626" s="8">
-        <v>0</v>
+        <v>2645964.23</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
@@ -27179,17 +27179,17 @@
       <c r="C633" s="6">
         <v>46248</v>
       </c>
-      <c r="D633" s="8">
-        <v>0</v>
+      <c r="D633" s="7">
+        <v>21.100684</v>
       </c>
       <c r="E633" s="8">
-        <v>0</v>
+        <v>16788159</v>
       </c>
       <c r="F633" s="9">
         <v>2459</v>
       </c>
       <c r="G633" s="8">
-        <v>0</v>
+        <v>354241634.03</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
@@ -27386,17 +27386,17 @@
       <c r="C642" s="6">
         <v>46248</v>
       </c>
-      <c r="D642" s="8">
-        <v>0</v>
+      <c r="D642" s="7">
+        <v>15.193458</v>
       </c>
       <c r="E642" s="8">
-        <v>0</v>
+        <v>22904394</v>
       </c>
       <c r="F642" s="9">
         <v>5</v>
       </c>
       <c r="G642" s="8">
-        <v>0</v>
+        <v>347996951.93</v>
       </c>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.25">
@@ -27432,17 +27432,17 @@
       <c r="C644" s="6">
         <v>46248</v>
       </c>
-      <c r="D644" s="8">
-        <v>0</v>
+      <c r="D644" s="7">
+        <v>56.975412</v>
       </c>
       <c r="E644" s="8">
-        <v>0</v>
+        <v>4643160</v>
       </c>
       <c r="F644" s="9">
         <v>2</v>
       </c>
       <c r="G644" s="8">
-        <v>0</v>
+        <v>264545954.78</v>
       </c>
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.25">
@@ -27547,17 +27547,17 @@
       <c r="C649" s="6">
         <v>46248</v>
       </c>
-      <c r="D649" s="8">
-        <v>0</v>
+      <c r="D649" s="7">
+        <v>6.967315</v>
       </c>
       <c r="E649" s="8">
-        <v>0</v>
+        <v>4029467144</v>
       </c>
       <c r="F649" s="9">
         <v>1</v>
       </c>
       <c r="G649" s="8">
-        <v>0</v>
+        <v>28074568464.14</v>
       </c>
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.25">
@@ -27616,17 +27616,17 @@
       <c r="C652" s="6">
         <v>46248</v>
       </c>
-      <c r="D652" s="8">
-        <v>0</v>
+      <c r="D652" s="7">
+        <v>52.134162</v>
       </c>
       <c r="E652" s="8">
-        <v>0</v>
+        <v>28012535</v>
       </c>
       <c r="F652" s="9">
         <v>2</v>
       </c>
       <c r="G652" s="8">
-        <v>0</v>
+        <v>1460410029.73</v>
       </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
@@ -27639,17 +27639,17 @@
       <c r="C653" s="6">
         <v>46248</v>
       </c>
-      <c r="D653" s="8">
-        <v>0</v>
+      <c r="D653" s="7">
+        <v>6.423783</v>
       </c>
       <c r="E653" s="8">
-        <v>0</v>
+        <v>64816259</v>
       </c>
       <c r="F653" s="9">
         <v>540</v>
       </c>
       <c r="G653" s="8">
-        <v>0</v>
+        <v>416365587.53</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
@@ -27685,17 +27685,17 @@
       <c r="C655" s="6">
         <v>46248</v>
       </c>
-      <c r="D655" s="8">
-        <v>0</v>
+      <c r="D655" s="7">
+        <v>5.946518</v>
       </c>
       <c r="E655" s="8">
-        <v>0</v>
+        <v>341860798</v>
       </c>
       <c r="F655" s="9">
         <v>1</v>
       </c>
       <c r="G655" s="8">
-        <v>0</v>
+        <v>2032881258.81</v>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
@@ -27777,17 +27777,17 @@
       <c r="C659" s="6">
         <v>46248</v>
       </c>
-      <c r="D659" s="8">
-        <v>0</v>
+      <c r="D659" s="7">
+        <v>0.466344</v>
       </c>
       <c r="E659" s="8">
-        <v>0</v>
+        <v>10235761127</v>
       </c>
       <c r="F659" s="9">
         <v>38252</v>
       </c>
       <c r="G659" s="8">
-        <v>0</v>
+        <v>4773389092.84</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
@@ -27800,17 +27800,17 @@
       <c r="C660" s="6">
         <v>46248</v>
       </c>
-      <c r="D660" s="8">
-        <v>0</v>
+      <c r="D660" s="7">
+        <v>1.406746</v>
       </c>
       <c r="E660" s="8">
-        <v>0</v>
+        <v>802553655</v>
       </c>
       <c r="F660" s="9">
         <v>2718</v>
       </c>
       <c r="G660" s="8">
-        <v>0</v>
+        <v>1128988775.78</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.25">
@@ -27869,17 +27869,17 @@
       <c r="C663" s="6">
         <v>46248</v>
       </c>
-      <c r="D663" s="8">
-        <v>0</v>
+      <c r="D663" s="7">
+        <v>4.193664</v>
       </c>
       <c r="E663" s="8">
-        <v>0</v>
+        <v>23661906</v>
       </c>
       <c r="F663" s="9">
         <v>3478</v>
       </c>
       <c r="G663" s="8">
-        <v>0</v>
+        <v>99230073.23</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -27892,17 +27892,17 @@
       <c r="C664" s="6">
         <v>46248</v>
       </c>
-      <c r="D664" s="8">
-        <v>0</v>
+      <c r="D664" s="7">
+        <v>67.567048</v>
       </c>
       <c r="E664" s="8">
-        <v>0</v>
+        <v>52499640</v>
       </c>
       <c r="F664" s="9">
         <v>3</v>
       </c>
       <c r="G664" s="8">
-        <v>0</v>
+        <v>3547245681.52</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
@@ -27938,17 +27938,17 @@
       <c r="C666" s="6">
         <v>46248</v>
       </c>
-      <c r="D666" s="8">
-        <v>0</v>
+      <c r="D666" s="7">
+        <v>18.495687</v>
       </c>
       <c r="E666" s="8">
-        <v>0</v>
+        <v>22115</v>
       </c>
       <c r="F666" s="9">
         <v>1</v>
       </c>
       <c r="G666" s="8">
-        <v>0</v>
+        <v>409032.11</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
@@ -27961,17 +27961,17 @@
       <c r="C667" s="6">
         <v>46248</v>
       </c>
-      <c r="D667" s="8">
-        <v>0</v>
+      <c r="D667" s="7">
+        <v>5.621169</v>
       </c>
       <c r="E667" s="8">
-        <v>0</v>
+        <v>212150834</v>
       </c>
       <c r="F667" s="9">
         <v>4636</v>
       </c>
       <c r="G667" s="8">
-        <v>0</v>
+        <v>1192535737.13</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -27984,17 +27984,17 @@
       <c r="C668" s="6">
         <v>46248</v>
       </c>
-      <c r="D668" s="8">
-        <v>0</v>
+      <c r="D668" s="7">
+        <v>66.365139</v>
       </c>
       <c r="E668" s="8">
-        <v>0</v>
+        <v>7872114</v>
       </c>
       <c r="F668" s="9">
         <v>3</v>
       </c>
       <c r="G668" s="8">
-        <v>0</v>
+        <v>522433936.51</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -28030,17 +28030,17 @@
       <c r="C670" s="6">
         <v>46248</v>
       </c>
-      <c r="D670" s="8">
-        <v>0</v>
+      <c r="D670" s="7">
+        <v>4.059404</v>
       </c>
       <c r="E670" s="8">
-        <v>0</v>
+        <v>5020082762</v>
       </c>
       <c r="F670" s="9">
         <v>1</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>20378542678.4</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -28053,17 +28053,17 @@
       <c r="C671" s="6">
         <v>46248</v>
       </c>
-      <c r="D671" s="8">
-        <v>0</v>
+      <c r="D671" s="7">
+        <v>70.895645</v>
       </c>
       <c r="E671" s="8">
-        <v>0</v>
+        <v>7093936</v>
       </c>
       <c r="F671" s="9">
         <v>4</v>
       </c>
       <c r="G671" s="8">
-        <v>0</v>
+        <v>502929169.33</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
@@ -28122,17 +28122,17 @@
       <c r="C674" s="6">
         <v>46248</v>
       </c>
-      <c r="D674" s="8">
-        <v>0</v>
+      <c r="D674" s="7">
+        <v>68.602701</v>
       </c>
       <c r="E674" s="8">
-        <v>0</v>
+        <v>20613565</v>
       </c>
       <c r="F674" s="9">
         <v>1</v>
       </c>
       <c r="G674" s="8">
-        <v>0</v>
+        <v>1414146240.74</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -28214,17 +28214,17 @@
       <c r="C678" s="6">
         <v>46248</v>
       </c>
-      <c r="D678" s="8">
-        <v>0</v>
+      <c r="D678" s="7">
+        <v>7.578166</v>
       </c>
       <c r="E678" s="8">
-        <v>0</v>
+        <v>187251058</v>
       </c>
       <c r="F678" s="9">
         <v>4185</v>
       </c>
       <c r="G678" s="8">
-        <v>0</v>
+        <v>1419019569.96</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
@@ -28260,17 +28260,17 @@
       <c r="C680" s="6">
         <v>46248</v>
       </c>
-      <c r="D680" s="8">
-        <v>0</v>
+      <c r="D680" s="7">
+        <v>4.994661</v>
       </c>
       <c r="E680" s="8">
-        <v>0</v>
+        <v>80349276</v>
       </c>
       <c r="F680" s="9">
         <v>5855</v>
       </c>
       <c r="G680" s="8">
-        <v>0</v>
+        <v>401317397.71</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -28283,17 +28283,17 @@
       <c r="C681" s="6">
         <v>46248</v>
       </c>
-      <c r="D681" s="8">
-        <v>0</v>
+      <c r="D681" s="7">
+        <v>8.675061</v>
       </c>
       <c r="E681" s="8">
-        <v>0</v>
+        <v>202591047</v>
       </c>
       <c r="F681" s="9">
         <v>5234</v>
       </c>
       <c r="G681" s="8">
-        <v>0</v>
+        <v>1757489605.34</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
@@ -28306,17 +28306,17 @@
       <c r="C682" s="6">
         <v>46248</v>
       </c>
-      <c r="D682" s="8">
-        <v>0</v>
+      <c r="D682" s="7">
+        <v>5.582807</v>
       </c>
       <c r="E682" s="8">
-        <v>0</v>
+        <v>65232945</v>
       </c>
       <c r="F682" s="9">
         <v>6077</v>
       </c>
       <c r="G682" s="8">
-        <v>0</v>
+        <v>364182937.23</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
@@ -28375,17 +28375,17 @@
       <c r="C685" s="6">
         <v>46248</v>
       </c>
-      <c r="D685" s="8">
-        <v>0</v>
+      <c r="D685" s="7">
+        <v>69.261313</v>
       </c>
       <c r="E685" s="8">
-        <v>0</v>
+        <v>1210798</v>
       </c>
       <c r="F685" s="9">
         <v>1</v>
       </c>
       <c r="G685" s="8">
-        <v>0</v>
+        <v>83861459.13</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
@@ -28444,17 +28444,17 @@
       <c r="C688" s="6">
         <v>46248</v>
       </c>
-      <c r="D688" s="8">
-        <v>0</v>
+      <c r="D688" s="7">
+        <v>67.418965</v>
       </c>
       <c r="E688" s="8">
-        <v>0</v>
+        <v>6829649</v>
       </c>
       <c r="F688" s="9">
         <v>2</v>
       </c>
       <c r="G688" s="8">
-        <v>0</v>
+        <v>460447864.69</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
@@ -28467,17 +28467,17 @@
       <c r="C689" s="6">
         <v>46248</v>
       </c>
-      <c r="D689" s="8">
-        <v>0</v>
+      <c r="D689" s="7">
+        <v>8.775841</v>
       </c>
       <c r="E689" s="8">
-        <v>0</v>
+        <v>11399360</v>
       </c>
       <c r="F689" s="9">
         <v>1376</v>
       </c>
       <c r="G689" s="8">
-        <v>0</v>
+        <v>100038975.12</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
@@ -28513,17 +28513,17 @@
       <c r="C691" s="6">
         <v>46248</v>
       </c>
-      <c r="D691" s="8">
-        <v>0</v>
+      <c r="D691" s="7">
+        <v>7.004404</v>
       </c>
       <c r="E691" s="8">
-        <v>0</v>
+        <v>9208708</v>
       </c>
       <c r="F691" s="9">
         <v>1214</v>
       </c>
       <c r="G691" s="8">
-        <v>0</v>
+        <v>64501509.89</v>
       </c>
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.25">
@@ -28766,17 +28766,17 @@
       <c r="C702" s="6">
         <v>46248</v>
       </c>
-      <c r="D702" s="8">
-        <v>0</v>
+      <c r="D702" s="7">
+        <v>4.319623</v>
       </c>
       <c r="E702" s="8">
-        <v>0</v>
+        <v>128091840</v>
       </c>
       <c r="F702" s="9">
         <v>1096</v>
       </c>
       <c r="G702" s="8">
-        <v>0</v>
+        <v>553308506.48</v>
       </c>
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.25">
@@ -28859,7 +28859,7 @@
         <v>46248</v>
       </c>
       <c r="D706" s="7">
-        <v>3.115462</v>
+        <v>3.115539</v>
       </c>
       <c r="E706" s="8">
         <v>31165055</v>
@@ -28868,7 +28868,7 @@
         <v>547</v>
       </c>
       <c r="G706" s="8">
-        <v>97093560.02</v>
+        <v>97095933.31</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.25">
@@ -30101,7 +30101,7 @@
         <v>46248</v>
       </c>
       <c r="D760" s="7">
-        <v>0.368194</v>
+        <v>0.368463</v>
       </c>
       <c r="E760" s="8">
         <v>3759335989</v>
@@ -30110,7 +30110,7 @@
         <v>2554</v>
       </c>
       <c r="G760" s="8">
-        <v>1384165075.76</v>
+        <v>1385176881.45</v>
       </c>
     </row>
     <row r="761" spans="1:7" x14ac:dyDescent="0.25">
@@ -33435,17 +33435,17 @@
       <c r="C905" s="6">
         <v>46248</v>
       </c>
-      <c r="D905" s="8">
-        <v>0</v>
+      <c r="D905" s="7">
+        <v>14.793818</v>
       </c>
       <c r="E905" s="8">
-        <v>0</v>
+        <v>16015197</v>
       </c>
       <c r="F905" s="9">
         <v>376</v>
       </c>
       <c r="G905" s="8">
-        <v>0</v>
+        <v>236925916</v>
       </c>
     </row>
     <row r="906" spans="1:7" x14ac:dyDescent="0.25">
@@ -35229,17 +35229,17 @@
       <c r="C983" s="6">
         <v>46248</v>
       </c>
-      <c r="D983" s="8">
-        <v>0</v>
+      <c r="D983" s="7">
+        <v>6825.509569</v>
       </c>
       <c r="E983" s="8">
-        <v>0</v>
+        <v>784807</v>
       </c>
       <c r="F983" s="9">
         <v>37</v>
       </c>
       <c r="G983" s="8">
-        <v>0</v>
+        <v>5356707688.33</v>
       </c>
     </row>
     <row r="984" spans="1:7" x14ac:dyDescent="0.25">
@@ -35252,17 +35252,17 @@
       <c r="C984" s="6">
         <v>46248</v>
       </c>
-      <c r="D984" s="8">
-        <v>0</v>
+      <c r="D984" s="7">
+        <v>57.037376</v>
       </c>
       <c r="E984" s="8">
-        <v>0</v>
+        <v>317318808</v>
       </c>
       <c r="F984" s="9">
         <v>5721</v>
       </c>
       <c r="G984" s="8">
-        <v>0</v>
+        <v>18099032228.17</v>
       </c>
     </row>
     <row r="985" spans="1:7" x14ac:dyDescent="0.25">
@@ -35298,17 +35298,17 @@
       <c r="C986" s="6">
         <v>46248</v>
       </c>
-      <c r="D986" s="8">
-        <v>0</v>
+      <c r="D986" s="7">
+        <v>1.701788</v>
       </c>
       <c r="E986" s="8">
-        <v>0</v>
+        <v>189321082</v>
       </c>
       <c r="F986" s="9">
         <v>5</v>
       </c>
       <c r="G986" s="8">
-        <v>0</v>
+        <v>322184437.44</v>
       </c>
     </row>
     <row r="987" spans="1:7" x14ac:dyDescent="0.25">
@@ -35321,17 +35321,17 @@
       <c r="C987" s="6">
         <v>46248</v>
       </c>
-      <c r="D987" s="8">
-        <v>0</v>
+      <c r="D987" s="10">
+        <v>51.84816</v>
       </c>
       <c r="E987" s="8">
-        <v>0</v>
+        <v>3094492</v>
       </c>
       <c r="F987" s="9">
         <v>1</v>
       </c>
       <c r="G987" s="8">
-        <v>0</v>
+        <v>160443715.77</v>
       </c>
     </row>
     <row r="988" spans="1:7" x14ac:dyDescent="0.25">
@@ -35344,17 +35344,17 @@
       <c r="C988" s="6">
         <v>46248</v>
       </c>
-      <c r="D988" s="8">
-        <v>0</v>
+      <c r="D988" s="7">
+        <v>1.770788</v>
       </c>
       <c r="E988" s="8">
-        <v>0</v>
+        <v>6198814</v>
       </c>
       <c r="F988" s="9">
         <v>168</v>
       </c>
       <c r="G988" s="8">
-        <v>0</v>
+        <v>10976782.57</v>
       </c>
     </row>
     <row r="989" spans="1:7" x14ac:dyDescent="0.25">
@@ -35390,17 +35390,17 @@
       <c r="C990" s="6">
         <v>46248</v>
       </c>
-      <c r="D990" s="8">
-        <v>0</v>
+      <c r="D990" s="10">
+        <v>5.16462</v>
       </c>
       <c r="E990" s="8">
-        <v>0</v>
+        <v>486804530</v>
       </c>
       <c r="F990" s="9">
         <v>12773</v>
       </c>
       <c r="G990" s="8">
-        <v>0</v>
+        <v>2514160468.54</v>
       </c>
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.25">
@@ -35413,17 +35413,17 @@
       <c r="C991" s="6">
         <v>46248</v>
       </c>
-      <c r="D991" s="8">
-        <v>0</v>
+      <c r="D991" s="10">
+        <v>1.75938</v>
       </c>
       <c r="E991" s="8">
-        <v>0</v>
+        <v>338980289</v>
       </c>
       <c r="F991" s="9">
         <v>3400</v>
       </c>
       <c r="G991" s="8">
-        <v>0</v>
+        <v>596394972.5</v>
       </c>
     </row>
     <row r="992" spans="1:7" x14ac:dyDescent="0.25">
@@ -35436,17 +35436,17 @@
       <c r="C992" s="6">
         <v>46248</v>
       </c>
-      <c r="D992" s="8">
-        <v>0</v>
+      <c r="D992" s="10">
+        <v>57.58521</v>
       </c>
       <c r="E992" s="8">
-        <v>0</v>
+        <v>5926148</v>
       </c>
       <c r="F992" s="9">
         <v>12</v>
       </c>
       <c r="G992" s="8">
-        <v>0</v>
+        <v>341258474.8</v>
       </c>
     </row>
     <row r="993" spans="1:7" x14ac:dyDescent="0.25">
@@ -35459,17 +35459,17 @@
       <c r="C993" s="6">
         <v>46248</v>
       </c>
-      <c r="D993" s="8">
-        <v>0</v>
+      <c r="D993" s="7">
+        <v>15.474648</v>
       </c>
       <c r="E993" s="8">
-        <v>0</v>
+        <v>3147787</v>
       </c>
       <c r="F993" s="9">
         <v>1</v>
       </c>
       <c r="G993" s="8">
-        <v>0</v>
+        <v>48710895.01</v>
       </c>
     </row>
     <row r="994" spans="1:7" x14ac:dyDescent="0.25">
@@ -35482,17 +35482,17 @@
       <c r="C994" s="6">
         <v>46248</v>
       </c>
-      <c r="D994" s="8">
-        <v>0</v>
+      <c r="D994" s="7">
+        <v>52.376069</v>
       </c>
       <c r="E994" s="8">
-        <v>0</v>
+        <v>487431278</v>
       </c>
       <c r="F994" s="9">
         <v>7053</v>
       </c>
       <c r="G994" s="8">
-        <v>0</v>
+        <v>25529734312.07</v>
       </c>
     </row>
     <row r="995" spans="1:7" x14ac:dyDescent="0.25">
@@ -35528,17 +35528,17 @@
       <c r="C996" s="6">
         <v>46248</v>
       </c>
-      <c r="D996" s="8">
-        <v>0</v>
+      <c r="D996" s="7">
+        <v>54.382865</v>
       </c>
       <c r="E996" s="8">
-        <v>0</v>
+        <v>522293133</v>
       </c>
       <c r="F996" s="9">
         <v>1381</v>
       </c>
       <c r="G996" s="8">
-        <v>0</v>
+        <v>28403796909.43</v>
       </c>
     </row>
     <row r="997" spans="1:7" x14ac:dyDescent="0.25">
@@ -35574,17 +35574,17 @@
       <c r="C998" s="6">
         <v>46248</v>
       </c>
-      <c r="D998" s="8">
-        <v>0</v>
+      <c r="D998" s="7">
+        <v>48.599717</v>
       </c>
       <c r="E998" s="8">
-        <v>0</v>
+        <v>467461515</v>
       </c>
       <c r="F998" s="9">
         <v>201</v>
       </c>
       <c r="G998" s="8">
-        <v>0</v>
+        <v>22718497349.51</v>
       </c>
     </row>
     <row r="999" spans="1:7" x14ac:dyDescent="0.25">
@@ -35597,17 +35597,17 @@
       <c r="C999" s="6">
         <v>46248</v>
       </c>
-      <c r="D999" s="8">
-        <v>0</v>
+      <c r="D999" s="7">
+        <v>48.806744</v>
       </c>
       <c r="E999" s="8">
-        <v>0</v>
+        <v>89667114</v>
       </c>
       <c r="F999" s="9">
         <v>826</v>
       </c>
       <c r="G999" s="8">
-        <v>0</v>
+        <v>4376359850.2</v>
       </c>
     </row>
     <row r="1000" spans="1:7" x14ac:dyDescent="0.25">
@@ -35620,17 +35620,17 @@
       <c r="C1000" s="6">
         <v>46248</v>
       </c>
-      <c r="D1000" s="8">
-        <v>0</v>
+      <c r="D1000" s="7">
+        <v>1.839923</v>
       </c>
       <c r="E1000" s="8">
-        <v>0</v>
+        <v>179618321</v>
       </c>
       <c r="F1000" s="9">
         <v>1</v>
       </c>
       <c r="G1000" s="8">
-        <v>0</v>
+        <v>330483936.24</v>
       </c>
     </row>
     <row r="1001" spans="1:7" x14ac:dyDescent="0.25">
@@ -35643,17 +35643,17 @@
       <c r="C1001" s="6">
         <v>46248</v>
       </c>
-      <c r="D1001" s="8">
-        <v>0</v>
+      <c r="D1001" s="10">
+        <v>1.79167</v>
       </c>
       <c r="E1001" s="8">
-        <v>0</v>
+        <v>39442409</v>
       </c>
       <c r="F1001" s="9">
         <v>1</v>
       </c>
       <c r="G1001" s="8">
-        <v>0</v>
+        <v>70667763.29</v>
       </c>
     </row>
     <row r="1002" spans="1:7" x14ac:dyDescent="0.25">
@@ -35666,17 +35666,17 @@
       <c r="C1002" s="6">
         <v>46248</v>
       </c>
-      <c r="D1002" s="8">
-        <v>0</v>
+      <c r="D1002" s="7">
+        <v>52.662275</v>
       </c>
       <c r="E1002" s="8">
-        <v>0</v>
+        <v>79449195</v>
       </c>
       <c r="F1002" s="9">
         <v>54</v>
       </c>
       <c r="G1002" s="8">
-        <v>0</v>
+        <v>4183975316.16</v>
       </c>
     </row>
     <row r="1003" spans="1:7" x14ac:dyDescent="0.25">
@@ -35689,17 +35689,17 @@
       <c r="C1003" s="6">
         <v>46248</v>
       </c>
-      <c r="D1003" s="8">
-        <v>0</v>
+      <c r="D1003" s="7">
+        <v>4.439397</v>
       </c>
       <c r="E1003" s="8">
-        <v>0</v>
+        <v>82683881</v>
       </c>
       <c r="F1003" s="9">
         <v>1</v>
       </c>
       <c r="G1003" s="8">
-        <v>0</v>
+        <v>367066584.43</v>
       </c>
     </row>
     <row r="1004" spans="1:7" x14ac:dyDescent="0.25">
@@ -35712,17 +35712,17 @@
       <c r="C1004" s="6">
         <v>46248</v>
       </c>
-      <c r="D1004" s="8">
-        <v>0</v>
+      <c r="D1004" s="7">
+        <v>2.935165</v>
       </c>
       <c r="E1004" s="8">
-        <v>0</v>
+        <v>1023681366</v>
       </c>
       <c r="F1004" s="9">
         <v>29177</v>
       </c>
       <c r="G1004" s="8">
-        <v>0</v>
+        <v>3004673799.75</v>
       </c>
     </row>
     <row r="1005" spans="1:7" x14ac:dyDescent="0.25">
@@ -35781,17 +35781,17 @@
       <c r="C1007" s="6">
         <v>46248</v>
       </c>
-      <c r="D1007" s="8">
-        <v>0</v>
+      <c r="D1007" s="10">
+        <v>1.64944</v>
       </c>
       <c r="E1007" s="8">
-        <v>0</v>
+        <v>10718389</v>
       </c>
       <c r="F1007" s="9">
         <v>282</v>
       </c>
       <c r="G1007" s="8">
-        <v>0</v>
+        <v>17679336.72</v>
       </c>
     </row>
     <row r="1008" spans="1:7" x14ac:dyDescent="0.25">
@@ -35896,17 +35896,17 @@
       <c r="C1012" s="6">
         <v>46248</v>
       </c>
-      <c r="D1012" s="8">
-        <v>0</v>
+      <c r="D1012" s="7">
+        <v>1.186282</v>
       </c>
       <c r="E1012" s="8">
-        <v>0</v>
+        <v>27398056345</v>
       </c>
       <c r="F1012" s="9">
         <v>1840</v>
       </c>
       <c r="G1012" s="8">
-        <v>0</v>
+        <v>32501818035.02</v>
       </c>
     </row>
     <row r="1013" spans="1:7" x14ac:dyDescent="0.25">
@@ -35942,17 +35942,17 @@
       <c r="C1014" s="6">
         <v>46248</v>
       </c>
-      <c r="D1014" s="8">
-        <v>0</v>
+      <c r="D1014" s="7">
+        <v>36.339763</v>
       </c>
       <c r="E1014" s="8">
-        <v>0</v>
+        <v>95518</v>
       </c>
       <c r="F1014" s="9">
         <v>1</v>
       </c>
       <c r="G1014" s="8">
-        <v>0</v>
+        <v>3471101.51</v>
       </c>
     </row>
     <row r="1015" spans="1:7" x14ac:dyDescent="0.25">
@@ -36034,17 +36034,17 @@
       <c r="C1018" s="6">
         <v>46248</v>
       </c>
-      <c r="D1018" s="8">
-        <v>0</v>
+      <c r="D1018" s="7">
+        <v>1.528839</v>
       </c>
       <c r="E1018" s="8">
-        <v>0</v>
+        <v>38712906</v>
       </c>
       <c r="F1018" s="9">
         <v>27</v>
       </c>
       <c r="G1018" s="8">
-        <v>0</v>
+        <v>59185784.16</v>
       </c>
     </row>
     <row r="1019" spans="1:7" x14ac:dyDescent="0.25">
@@ -36057,17 +36057,17 @@
       <c r="C1019" s="6">
         <v>46248</v>
       </c>
-      <c r="D1019" s="8">
-        <v>0</v>
+      <c r="D1019" s="7">
+        <v>1.478864</v>
       </c>
       <c r="E1019" s="8">
-        <v>0</v>
+        <v>116604442</v>
       </c>
       <c r="F1019" s="9">
         <v>1405</v>
       </c>
       <c r="G1019" s="8">
-        <v>0</v>
+        <v>172442082.64</v>
       </c>
     </row>
     <row r="1020" spans="1:7" x14ac:dyDescent="0.25">
@@ -36103,17 +36103,17 @@
       <c r="C1021" s="6">
         <v>46248</v>
       </c>
-      <c r="D1021" s="8">
-        <v>0</v>
+      <c r="D1021" s="7">
+        <v>0.002257</v>
       </c>
       <c r="E1021" s="8">
-        <v>0</v>
+        <v>21405755952</v>
       </c>
       <c r="F1021" s="9">
         <v>1</v>
       </c>
       <c r="G1021" s="8">
-        <v>0</v>
+        <v>48313167.07</v>
       </c>
     </row>
     <row r="1022" spans="1:7" x14ac:dyDescent="0.25">
@@ -36126,17 +36126,17 @@
       <c r="C1022" s="6">
         <v>46248</v>
       </c>
-      <c r="D1022" s="8">
-        <v>0</v>
+      <c r="D1022" s="7">
+        <v>62.043842</v>
       </c>
       <c r="E1022" s="8">
-        <v>0</v>
+        <v>41940</v>
       </c>
       <c r="F1022" s="9">
         <v>1</v>
       </c>
       <c r="G1022" s="8">
-        <v>0</v>
+        <v>2602118.75</v>
       </c>
     </row>
     <row r="1023" spans="1:7" x14ac:dyDescent="0.25">
@@ -36149,17 +36149,17 @@
       <c r="C1023" s="6">
         <v>46248</v>
       </c>
-      <c r="D1023" s="8">
-        <v>0</v>
+      <c r="D1023" s="10">
+        <v>56.98284</v>
       </c>
       <c r="E1023" s="8">
-        <v>0</v>
+        <v>2046792</v>
       </c>
       <c r="F1023" s="9">
         <v>56</v>
       </c>
       <c r="G1023" s="8">
-        <v>0</v>
+        <v>116632020.67</v>
       </c>
     </row>
     <row r="1024" spans="1:7" x14ac:dyDescent="0.25">
@@ -36172,17 +36172,17 @@
       <c r="C1024" s="6">
         <v>46248</v>
       </c>
-      <c r="D1024" s="8">
-        <v>0</v>
+      <c r="D1024" s="7">
+        <v>51.779668</v>
       </c>
       <c r="E1024" s="8">
-        <v>0</v>
+        <v>1726780</v>
       </c>
       <c r="F1024" s="9">
         <v>2</v>
       </c>
       <c r="G1024" s="8">
-        <v>0</v>
+        <v>89412095.81</v>
       </c>
     </row>
     <row r="1025" spans="1:7" x14ac:dyDescent="0.25">
@@ -36287,17 +36287,17 @@
       <c r="C1029" s="6">
         <v>46248</v>
       </c>
-      <c r="D1029" s="8">
-        <v>0</v>
+      <c r="D1029" s="7">
+        <v>3.101583</v>
       </c>
       <c r="E1029" s="8">
-        <v>0</v>
+        <v>2941745961</v>
       </c>
       <c r="F1029" s="9">
         <v>46</v>
       </c>
       <c r="G1029" s="8">
-        <v>0</v>
+        <v>9124070699.99</v>
       </c>
     </row>
     <row r="1030" spans="1:7" x14ac:dyDescent="0.25">
@@ -36356,17 +36356,17 @@
       <c r="C1032" s="6">
         <v>46248</v>
       </c>
-      <c r="D1032" s="8">
-        <v>0</v>
+      <c r="D1032" s="7">
+        <v>57.625726</v>
       </c>
       <c r="E1032" s="8">
-        <v>0</v>
+        <v>196370</v>
       </c>
       <c r="F1032" s="9">
         <v>1</v>
       </c>
       <c r="G1032" s="8">
-        <v>0</v>
+        <v>11315963.88</v>
       </c>
     </row>
     <row r="1033" spans="1:7" x14ac:dyDescent="0.25">
@@ -36425,17 +36425,17 @@
       <c r="C1035" s="6">
         <v>46248</v>
       </c>
-      <c r="D1035" s="8">
-        <v>0</v>
+      <c r="D1035" s="7">
+        <v>4.803391</v>
       </c>
       <c r="E1035" s="8">
-        <v>0</v>
+        <v>19863036480</v>
       </c>
       <c r="F1035" s="9">
         <v>105035</v>
       </c>
       <c r="G1035" s="8">
-        <v>0</v>
+        <v>95409924046.66</v>
       </c>
     </row>
     <row r="1036" spans="1:7" x14ac:dyDescent="0.25">
@@ -36448,17 +36448,17 @@
       <c r="C1036" s="6">
         <v>46248</v>
       </c>
-      <c r="D1036" s="8">
-        <v>0</v>
+      <c r="D1036" s="7">
+        <v>168.279387</v>
       </c>
       <c r="E1036" s="8">
-        <v>0</v>
+        <v>74818</v>
       </c>
       <c r="F1036" s="9">
         <v>1</v>
       </c>
       <c r="G1036" s="8">
-        <v>0</v>
+        <v>12590327.14</v>
       </c>
     </row>
     <row r="1037" spans="1:7" x14ac:dyDescent="0.25">
@@ -36471,17 +36471,17 @@
       <c r="C1037" s="6">
         <v>46248</v>
       </c>
-      <c r="D1037" s="8">
-        <v>0</v>
+      <c r="D1037" s="7">
+        <v>1.579106</v>
       </c>
       <c r="E1037" s="8">
-        <v>0</v>
+        <v>79488359</v>
       </c>
       <c r="F1037" s="9">
         <v>1194</v>
       </c>
       <c r="G1037" s="8">
-        <v>0</v>
+        <v>125520569.88</v>
       </c>
     </row>
     <row r="1038" spans="1:7" x14ac:dyDescent="0.25">
@@ -36540,17 +36540,17 @@
       <c r="C1040" s="6">
         <v>46248</v>
       </c>
-      <c r="D1040" s="8">
-        <v>0</v>
+      <c r="D1040" s="7">
+        <v>2.749798</v>
       </c>
       <c r="E1040" s="8">
-        <v>0</v>
+        <v>24785369</v>
       </c>
       <c r="F1040" s="9">
         <v>1</v>
       </c>
       <c r="G1040" s="8">
-        <v>0</v>
+        <v>68154763.26</v>
       </c>
     </row>
     <row r="1041" spans="1:7" x14ac:dyDescent="0.25">
@@ -36609,17 +36609,17 @@
       <c r="C1043" s="6">
         <v>46248</v>
       </c>
-      <c r="D1043" s="8">
-        <v>0</v>
+      <c r="D1043" s="7">
+        <v>1.999022</v>
       </c>
       <c r="E1043" s="8">
-        <v>0</v>
+        <v>343019054</v>
       </c>
       <c r="F1043" s="9">
         <v>13518</v>
       </c>
       <c r="G1043" s="8">
-        <v>0</v>
+        <v>685702561.19</v>
       </c>
     </row>
     <row r="1044" spans="1:7" x14ac:dyDescent="0.25">
@@ -36678,17 +36678,17 @@
       <c r="C1046" s="6">
         <v>46248</v>
       </c>
-      <c r="D1046" s="8">
-        <v>0</v>
+      <c r="D1046" s="7">
+        <v>4.448248</v>
       </c>
       <c r="E1046" s="8">
-        <v>0</v>
+        <v>1127191620</v>
       </c>
       <c r="F1046" s="9">
         <v>1</v>
       </c>
       <c r="G1046" s="8">
-        <v>0</v>
+        <v>5014027765.99</v>
       </c>
     </row>
     <row r="1047" spans="1:7" x14ac:dyDescent="0.25">
@@ -36793,17 +36793,17 @@
       <c r="C1051" s="6">
         <v>46248</v>
       </c>
-      <c r="D1051" s="8">
-        <v>0</v>
+      <c r="D1051" s="10">
+        <v>1.40805</v>
       </c>
       <c r="E1051" s="8">
-        <v>0</v>
+        <v>1938109494</v>
       </c>
       <c r="F1051" s="9">
         <v>73</v>
       </c>
       <c r="G1051" s="8">
-        <v>0</v>
+        <v>2728954292.54</v>
       </c>
     </row>
     <row r="1052" spans="1:7" x14ac:dyDescent="0.25">
@@ -36908,17 +36908,17 @@
       <c r="C1056" s="6">
         <v>46248</v>
       </c>
-      <c r="D1056" s="8">
-        <v>0</v>
+      <c r="D1056" s="7">
+        <v>52.620525</v>
       </c>
       <c r="E1056" s="8">
-        <v>0</v>
+        <v>267344</v>
       </c>
       <c r="F1056" s="9">
         <v>12</v>
       </c>
       <c r="G1056" s="8">
-        <v>0</v>
+        <v>14067781.67</v>
       </c>
     </row>
     <row r="1057" spans="1:7" x14ac:dyDescent="0.25">
@@ -36931,17 +36931,17 @@
       <c r="C1057" s="6">
         <v>46248</v>
       </c>
-      <c r="D1057" s="8">
-        <v>0</v>
+      <c r="D1057" s="7">
+        <v>1.684812</v>
       </c>
       <c r="E1057" s="8">
-        <v>0</v>
+        <v>301350586</v>
       </c>
       <c r="F1057" s="9">
         <v>13756</v>
       </c>
       <c r="G1057" s="8">
-        <v>0</v>
+        <v>507718935.47</v>
       </c>
     </row>
     <row r="1058" spans="1:7" x14ac:dyDescent="0.25">
@@ -36977,17 +36977,17 @@
       <c r="C1059" s="6">
         <v>46248</v>
       </c>
-      <c r="D1059" s="8">
-        <v>0</v>
+      <c r="D1059" s="7">
+        <v>20.844891</v>
       </c>
       <c r="E1059" s="8">
-        <v>0</v>
+        <v>213531482</v>
       </c>
       <c r="F1059" s="9">
         <v>22967</v>
       </c>
       <c r="G1059" s="8">
-        <v>0</v>
+        <v>4451040363.99</v>
       </c>
     </row>
     <row r="1060" spans="1:7" x14ac:dyDescent="0.25">
@@ -37000,17 +37000,17 @@
       <c r="C1060" s="6">
         <v>46248</v>
       </c>
-      <c r="D1060" s="8">
-        <v>0</v>
+      <c r="D1060" s="7">
+        <v>48.641217</v>
       </c>
       <c r="E1060" s="8">
-        <v>0</v>
+        <v>6383206</v>
       </c>
       <c r="F1060" s="9">
         <v>548</v>
       </c>
       <c r="G1060" s="8">
-        <v>0</v>
+        <v>310486910.83</v>
       </c>
     </row>
     <row r="1061" spans="1:7" x14ac:dyDescent="0.25">
@@ -37115,17 +37115,17 @@
       <c r="C1065" s="6">
         <v>46248</v>
       </c>
-      <c r="D1065" s="8">
-        <v>0</v>
+      <c r="D1065" s="7">
+        <v>1.036023</v>
       </c>
       <c r="E1065" s="8">
-        <v>0</v>
+        <v>1508400</v>
       </c>
       <c r="F1065" s="9">
         <v>16</v>
       </c>
       <c r="G1065" s="8">
-        <v>0</v>
+        <v>1562737.65</v>
       </c>
     </row>
     <row r="1066" spans="1:7" x14ac:dyDescent="0.25">
@@ -37161,17 +37161,17 @@
       <c r="C1067" s="6">
         <v>46248</v>
       </c>
-      <c r="D1067" s="8">
-        <v>0</v>
+      <c r="D1067" s="10">
+        <v>1.86091</v>
       </c>
       <c r="E1067" s="8">
-        <v>0</v>
+        <v>40504916394</v>
       </c>
       <c r="F1067" s="9">
         <v>1326</v>
       </c>
       <c r="G1067" s="8">
-        <v>0</v>
+        <v>75375990128.13</v>
       </c>
     </row>
     <row r="1068" spans="1:7" x14ac:dyDescent="0.25">
@@ -37184,17 +37184,17 @@
       <c r="C1068" s="6">
         <v>46248</v>
       </c>
-      <c r="D1068" s="8">
-        <v>0</v>
+      <c r="D1068" s="7">
+        <v>3.948908</v>
       </c>
       <c r="E1068" s="8">
-        <v>0</v>
+        <v>149035087</v>
       </c>
       <c r="F1068" s="9">
         <v>6208</v>
       </c>
       <c r="G1068" s="8">
-        <v>0</v>
+        <v>588525815.29</v>
       </c>
     </row>
     <row r="1069" spans="1:7" x14ac:dyDescent="0.25">
@@ -37230,17 +37230,17 @@
       <c r="C1070" s="6">
         <v>46248</v>
       </c>
-      <c r="D1070" s="8">
-        <v>0</v>
+      <c r="D1070" s="7">
+        <v>21.162645</v>
       </c>
       <c r="E1070" s="8">
-        <v>0</v>
+        <v>2137304</v>
       </c>
       <c r="F1070" s="9">
         <v>607</v>
       </c>
       <c r="G1070" s="8">
-        <v>0</v>
+        <v>45231005.25</v>
       </c>
     </row>
     <row r="1071" spans="1:7" x14ac:dyDescent="0.25">
@@ -37322,17 +37322,17 @@
       <c r="C1074" s="6">
         <v>46248</v>
       </c>
-      <c r="D1074" s="8">
-        <v>0</v>
+      <c r="D1074" s="10">
+        <v>0.52047</v>
       </c>
       <c r="E1074" s="8">
-        <v>0</v>
+        <v>2900805400</v>
       </c>
       <c r="F1074" s="9">
         <v>1136</v>
       </c>
       <c r="G1074" s="8">
-        <v>0</v>
+        <v>1509783112.29</v>
       </c>
     </row>
     <row r="1075" spans="1:7" x14ac:dyDescent="0.25">
@@ -37345,17 +37345,17 @@
       <c r="C1075" s="6">
         <v>46248</v>
       </c>
-      <c r="D1075" s="8">
-        <v>0</v>
+      <c r="D1075" s="7">
+        <v>74.440112</v>
       </c>
       <c r="E1075" s="8">
-        <v>0</v>
+        <v>9829248</v>
       </c>
       <c r="F1075" s="9">
         <v>165</v>
       </c>
       <c r="G1075" s="8">
-        <v>0</v>
+        <v>731690319.59</v>
       </c>
     </row>
     <row r="1076" spans="1:7" x14ac:dyDescent="0.25">
@@ -37414,17 +37414,17 @@
       <c r="C1078" s="6">
         <v>46248</v>
       </c>
-      <c r="D1078" s="8">
-        <v>0</v>
+      <c r="D1078" s="7">
+        <v>49.321491</v>
       </c>
       <c r="E1078" s="8">
-        <v>0</v>
+        <v>495470</v>
       </c>
       <c r="F1078" s="9">
         <v>1</v>
       </c>
       <c r="G1078" s="8">
-        <v>0</v>
+        <v>24437319.14</v>
       </c>
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.25">
@@ -37529,17 +37529,17 @@
       <c r="C1083" s="6">
         <v>46248</v>
       </c>
-      <c r="D1083" s="8">
-        <v>0</v>
+      <c r="D1083" s="7">
+        <v>5.202843</v>
       </c>
       <c r="E1083" s="8">
-        <v>0</v>
+        <v>38986701</v>
       </c>
       <c r="F1083" s="9">
         <v>3782</v>
       </c>
       <c r="G1083" s="8">
-        <v>0</v>
+        <v>202841680.11</v>
       </c>
     </row>
     <row r="1084" spans="1:7" x14ac:dyDescent="0.25">
@@ -37575,17 +37575,17 @@
       <c r="C1085" s="6">
         <v>46248</v>
       </c>
-      <c r="D1085" s="8">
-        <v>0</v>
+      <c r="D1085" s="7">
+        <v>5.693814</v>
       </c>
       <c r="E1085" s="8">
-        <v>0</v>
+        <v>5662272972</v>
       </c>
       <c r="F1085" s="9">
         <v>9925</v>
       </c>
       <c r="G1085" s="8">
-        <v>0</v>
+        <v>32239929878.57</v>
       </c>
     </row>
     <row r="1086" spans="1:7" x14ac:dyDescent="0.25">
@@ -37621,17 +37621,17 @@
       <c r="C1087" s="6">
         <v>46248</v>
       </c>
-      <c r="D1087" s="8">
-        <v>0</v>
+      <c r="D1087" s="7">
+        <v>45.363668</v>
       </c>
       <c r="E1087" s="8">
-        <v>0</v>
+        <v>2415590</v>
       </c>
       <c r="F1087" s="9">
         <v>1</v>
       </c>
       <c r="G1087" s="8">
-        <v>0</v>
+        <v>109580021.95</v>
       </c>
     </row>
     <row r="1088" spans="1:7" x14ac:dyDescent="0.25">
@@ -37667,17 +37667,17 @@
       <c r="C1089" s="6">
         <v>46248</v>
       </c>
-      <c r="D1089" s="8">
-        <v>0</v>
+      <c r="D1089" s="10">
+        <v>2.70165</v>
       </c>
       <c r="E1089" s="8">
-        <v>0</v>
+        <v>643546216</v>
       </c>
       <c r="F1089" s="9">
         <v>19609</v>
       </c>
       <c r="G1089" s="8">
-        <v>0</v>
+        <v>1738636890.8</v>
       </c>
     </row>
     <row r="1090" spans="1:7" x14ac:dyDescent="0.25">
@@ -37690,17 +37690,17 @@
       <c r="C1090" s="6">
         <v>46248</v>
       </c>
-      <c r="D1090" s="8">
-        <v>0</v>
+      <c r="D1090" s="7">
+        <v>22.220428</v>
       </c>
       <c r="E1090" s="8">
-        <v>0</v>
+        <v>29940204</v>
       </c>
       <c r="F1090" s="9">
         <v>5703</v>
       </c>
       <c r="G1090" s="8">
-        <v>0</v>
+        <v>665284140.54</v>
       </c>
     </row>
     <row r="1091" spans="1:7" x14ac:dyDescent="0.25">
@@ -37713,17 +37713,17 @@
       <c r="C1091" s="6">
         <v>46248</v>
       </c>
-      <c r="D1091" s="8">
-        <v>0</v>
+      <c r="D1091" s="7">
+        <v>8.006197</v>
       </c>
       <c r="E1091" s="8">
-        <v>0</v>
+        <v>56055627</v>
       </c>
       <c r="F1091" s="9">
         <v>4209</v>
       </c>
       <c r="G1091" s="8">
-        <v>0</v>
+        <v>448792379.56</v>
       </c>
     </row>
     <row r="1092" spans="1:7" x14ac:dyDescent="0.25">
@@ -37736,17 +37736,17 @@
       <c r="C1092" s="6">
         <v>46248</v>
       </c>
-      <c r="D1092" s="8">
-        <v>0</v>
+      <c r="D1092" s="7">
+        <v>10.543491</v>
       </c>
       <c r="E1092" s="8">
-        <v>0</v>
+        <v>2301609547</v>
       </c>
       <c r="F1092" s="9">
         <v>645</v>
       </c>
       <c r="G1092" s="8">
-        <v>0</v>
+        <v>24267000063.68</v>
       </c>
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.25">
@@ -37759,17 +37759,17 @@
       <c r="C1093" s="6">
         <v>46248</v>
       </c>
-      <c r="D1093" s="8">
-        <v>0</v>
+      <c r="D1093" s="7">
+        <v>14.740041</v>
       </c>
       <c r="E1093" s="8">
-        <v>0</v>
+        <v>8542172</v>
       </c>
       <c r="F1093" s="9">
         <v>717</v>
       </c>
       <c r="G1093" s="8">
-        <v>0</v>
+        <v>125911969.61</v>
       </c>
     </row>
     <row r="1094" spans="1:7" x14ac:dyDescent="0.25">
@@ -37782,17 +37782,17 @@
       <c r="C1094" s="6">
         <v>46248</v>
       </c>
-      <c r="D1094" s="8">
-        <v>0</v>
+      <c r="D1094" s="7">
+        <v>70.377554</v>
       </c>
       <c r="E1094" s="8">
-        <v>0</v>
+        <v>71912127</v>
       </c>
       <c r="F1094" s="9">
         <v>1437</v>
       </c>
       <c r="G1094" s="8">
-        <v>0</v>
+        <v>5060999602.41</v>
       </c>
     </row>
     <row r="1095" spans="1:7" x14ac:dyDescent="0.25">
@@ -37805,17 +37805,17 @@
       <c r="C1095" s="6">
         <v>46248</v>
       </c>
-      <c r="D1095" s="8">
-        <v>0</v>
+      <c r="D1095" s="7">
+        <v>29.161137</v>
       </c>
       <c r="E1095" s="8">
-        <v>0</v>
+        <v>32515349</v>
       </c>
       <c r="F1095" s="9">
         <v>1</v>
       </c>
       <c r="G1095" s="8">
-        <v>0</v>
+        <v>948184562.98</v>
       </c>
     </row>
     <row r="1096" spans="1:7" x14ac:dyDescent="0.25">
@@ -37828,17 +37828,17 @@
       <c r="C1096" s="6">
         <v>46248</v>
       </c>
-      <c r="D1096" s="8">
-        <v>0</v>
+      <c r="D1096" s="7">
+        <v>7.635792</v>
       </c>
       <c r="E1096" s="8">
-        <v>0</v>
+        <v>3459404757</v>
       </c>
       <c r="F1096" s="9">
         <v>44770</v>
       </c>
       <c r="G1096" s="8">
-        <v>0</v>
+        <v>26415296862.75</v>
       </c>
     </row>
     <row r="1097" spans="1:7" x14ac:dyDescent="0.25">
@@ -37851,17 +37851,17 @@
       <c r="C1097" s="6">
         <v>46248</v>
       </c>
-      <c r="D1097" s="8">
-        <v>0</v>
+      <c r="D1097" s="7">
+        <v>1.149987</v>
       </c>
       <c r="E1097" s="8">
-        <v>0</v>
+        <v>224210662</v>
       </c>
       <c r="F1097" s="9">
         <v>2528</v>
       </c>
       <c r="G1097" s="8">
-        <v>0</v>
+        <v>257839456.63</v>
       </c>
     </row>
     <row r="1098" spans="1:7" x14ac:dyDescent="0.25">
@@ -37874,17 +37874,17 @@
       <c r="C1098" s="6">
         <v>46248</v>
       </c>
-      <c r="D1098" s="8">
-        <v>0</v>
+      <c r="D1098" s="7">
+        <v>1.421441</v>
       </c>
       <c r="E1098" s="8">
-        <v>0</v>
+        <v>73014981</v>
       </c>
       <c r="F1098" s="9">
         <v>2079</v>
       </c>
       <c r="G1098" s="8">
-        <v>0</v>
+        <v>103786509.82</v>
       </c>
     </row>
     <row r="1099" spans="1:7" x14ac:dyDescent="0.25">
@@ -37897,17 +37897,17 @@
       <c r="C1099" s="6">
         <v>46248</v>
       </c>
-      <c r="D1099" s="8">
-        <v>0</v>
+      <c r="D1099" s="7">
+        <v>0.748373</v>
       </c>
       <c r="E1099" s="8">
-        <v>0</v>
+        <v>814109867</v>
       </c>
       <c r="F1099" s="9">
         <v>3681</v>
       </c>
       <c r="G1099" s="8">
-        <v>0</v>
+        <v>609257930.27</v>
       </c>
     </row>
     <row r="1100" spans="1:7" x14ac:dyDescent="0.25">
@@ -37920,17 +37920,17 @@
       <c r="C1100" s="6">
         <v>46248</v>
       </c>
-      <c r="D1100" s="8">
-        <v>0</v>
+      <c r="D1100" s="7">
+        <v>1.723814</v>
       </c>
       <c r="E1100" s="8">
-        <v>0</v>
+        <v>105066192</v>
       </c>
       <c r="F1100" s="9">
         <v>2126</v>
       </c>
       <c r="G1100" s="8">
-        <v>0</v>
+        <v>181114551.09</v>
       </c>
     </row>
     <row r="1101" spans="1:7" x14ac:dyDescent="0.25">
@@ -37966,17 +37966,17 @@
       <c r="C1102" s="6">
         <v>46248</v>
       </c>
-      <c r="D1102" s="8">
-        <v>0</v>
+      <c r="D1102" s="7">
+        <v>12.030428</v>
       </c>
       <c r="E1102" s="8">
-        <v>0</v>
+        <v>675981723</v>
       </c>
       <c r="F1102" s="9">
         <v>40847</v>
       </c>
       <c r="G1102" s="8">
-        <v>0</v>
+        <v>8132349325.45</v>
       </c>
     </row>
     <row r="1103" spans="1:7" x14ac:dyDescent="0.25">
@@ -37989,17 +37989,17 @@
       <c r="C1103" s="6">
         <v>46248</v>
       </c>
-      <c r="D1103" s="8">
-        <v>0</v>
+      <c r="D1103" s="7">
+        <v>1.761887</v>
       </c>
       <c r="E1103" s="8">
-        <v>0</v>
+        <v>392570970</v>
       </c>
       <c r="F1103" s="9">
         <v>1</v>
       </c>
       <c r="G1103" s="8">
-        <v>0</v>
+        <v>691665524.02</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.25">
@@ -38104,17 +38104,17 @@
       <c r="C1108" s="6">
         <v>46248</v>
       </c>
-      <c r="D1108" s="8">
-        <v>0</v>
+      <c r="D1108" s="7">
+        <v>1.203146</v>
       </c>
       <c r="E1108" s="8">
-        <v>0</v>
+        <v>57493451</v>
       </c>
       <c r="F1108" s="9">
         <v>1600</v>
       </c>
       <c r="G1108" s="8">
-        <v>0</v>
+        <v>69172992.64</v>
       </c>
     </row>
     <row r="1109" spans="1:7" x14ac:dyDescent="0.25">
@@ -38150,17 +38150,17 @@
       <c r="C1110" s="6">
         <v>46248</v>
       </c>
-      <c r="D1110" s="8">
-        <v>0</v>
+      <c r="D1110" s="7">
+        <v>53.734828</v>
       </c>
       <c r="E1110" s="8">
-        <v>0</v>
+        <v>207100</v>
       </c>
       <c r="F1110" s="9">
         <v>18</v>
       </c>
       <c r="G1110" s="8">
-        <v>0</v>
+        <v>11128482.85</v>
       </c>
     </row>
     <row r="1111" spans="1:7" x14ac:dyDescent="0.25">
@@ -38173,17 +38173,17 @@
       <c r="C1111" s="6">
         <v>46248</v>
       </c>
-      <c r="D1111" s="8">
-        <v>0</v>
+      <c r="D1111" s="7">
+        <v>28.013859</v>
       </c>
       <c r="E1111" s="8">
-        <v>0</v>
+        <v>3206812881</v>
       </c>
       <c r="F1111" s="9">
         <v>65079</v>
       </c>
       <c r="G1111" s="8">
-        <v>0</v>
+        <v>89835203072.53</v>
       </c>
     </row>
     <row r="1112" spans="1:7" x14ac:dyDescent="0.25">
@@ -38219,17 +38219,17 @@
       <c r="C1113" s="6">
         <v>46248</v>
       </c>
-      <c r="D1113" s="8">
-        <v>0</v>
+      <c r="D1113" s="7">
+        <v>2.383983</v>
       </c>
       <c r="E1113" s="8">
-        <v>0</v>
+        <v>199895915</v>
       </c>
       <c r="F1113" s="9">
         <v>5862</v>
       </c>
       <c r="G1113" s="8">
-        <v>0</v>
+        <v>476548519.09</v>
       </c>
     </row>
     <row r="1114" spans="1:7" x14ac:dyDescent="0.25">
@@ -39301,7 +39301,7 @@
         <v>46248</v>
       </c>
       <c r="D1160" s="7">
-        <v>1.291584</v>
+        <v>1.291963</v>
       </c>
       <c r="E1160" s="8">
         <v>255836822</v>
@@ -39310,7 +39310,7 @@
         <v>123</v>
       </c>
       <c r="G1160" s="8">
-        <v>330434696.16</v>
+        <v>330531649.14</v>
       </c>
     </row>
     <row r="1161" spans="1:7" x14ac:dyDescent="0.25">
@@ -39323,17 +39323,17 @@
       <c r="C1161" s="6">
         <v>46248</v>
       </c>
-      <c r="D1161" s="8">
-        <v>0</v>
+      <c r="D1161" s="7">
+        <v>1.601787</v>
       </c>
       <c r="E1161" s="8">
-        <v>0</v>
+        <v>2651303752</v>
       </c>
       <c r="F1161" s="9">
         <v>13</v>
       </c>
       <c r="G1161" s="8">
-        <v>0</v>
+        <v>4246823641.16</v>
       </c>
     </row>
     <row r="1162" spans="1:7" x14ac:dyDescent="0.25">
@@ -39346,17 +39346,17 @@
       <c r="C1162" s="6">
         <v>46248</v>
       </c>
-      <c r="D1162" s="8">
-        <v>0</v>
+      <c r="D1162" s="7">
+        <v>1.966296</v>
       </c>
       <c r="E1162" s="8">
-        <v>0</v>
+        <v>1800673679</v>
       </c>
       <c r="F1162" s="9">
         <v>15</v>
       </c>
       <c r="G1162" s="8">
-        <v>0</v>
+        <v>3540658180.18</v>
       </c>
     </row>
     <row r="1163" spans="1:7" x14ac:dyDescent="0.25">
@@ -40036,17 +40036,17 @@
       <c r="C1192" s="6">
         <v>46248</v>
       </c>
-      <c r="D1192" s="8">
-        <v>0</v>
+      <c r="D1192" s="7">
+        <v>0.783189</v>
       </c>
       <c r="E1192" s="8">
-        <v>0</v>
+        <v>1033653600</v>
       </c>
       <c r="F1192" s="9">
         <v>19</v>
       </c>
       <c r="G1192" s="8">
-        <v>0</v>
+        <v>809545704.51</v>
       </c>
     </row>
     <row r="1193" spans="1:7" x14ac:dyDescent="0.25">
@@ -40083,7 +40083,7 @@
         <v>46248</v>
       </c>
       <c r="D1194" s="7">
-        <v>5.402601</v>
+        <v>5.402761</v>
       </c>
       <c r="E1194" s="8">
         <v>15870144</v>
@@ -40092,7 +40092,7 @@
         <v>2131</v>
       </c>
       <c r="G1194" s="8">
-        <v>85740054.44</v>
+        <v>85742588.71</v>
       </c>
     </row>
     <row r="1195" spans="1:7" x14ac:dyDescent="0.25">
@@ -40910,8 +40910,8 @@
       <c r="C1230" s="6">
         <v>46248</v>
       </c>
-      <c r="D1230" s="10">
-        <v>1.16324</v>
+      <c r="D1230" s="7">
+        <v>1.163023</v>
       </c>
       <c r="E1230" s="8">
         <v>161317904</v>
@@ -40920,7 +40920,7 @@
         <v>3387</v>
       </c>
       <c r="G1230" s="8">
-        <v>187651486.15</v>
+        <v>187616437.58</v>
       </c>
     </row>
     <row r="1231" spans="1:7" x14ac:dyDescent="0.25">
@@ -40979,17 +40979,17 @@
       <c r="C1233" s="6">
         <v>46248</v>
       </c>
-      <c r="D1233" s="8">
-        <v>0</v>
+      <c r="D1233" s="10">
+        <v>2.29741</v>
       </c>
       <c r="E1233" s="8">
-        <v>0</v>
+        <v>6866499553</v>
       </c>
       <c r="F1233" s="9">
         <v>1</v>
       </c>
       <c r="G1233" s="8">
-        <v>0</v>
+        <v>15775166923.5</v>
       </c>
     </row>
     <row r="1234" spans="1:7" x14ac:dyDescent="0.25">
@@ -41347,17 +41347,17 @@
       <c r="C1249" s="6">
         <v>46248</v>
       </c>
-      <c r="D1249" s="8">
-        <v>0</v>
+      <c r="D1249" s="7">
+        <v>1.578229</v>
       </c>
       <c r="E1249" s="8">
-        <v>0</v>
+        <v>592973692</v>
       </c>
       <c r="F1249" s="9">
         <v>1</v>
       </c>
       <c r="G1249" s="8">
-        <v>0</v>
+        <v>935848224.87</v>
       </c>
     </row>
     <row r="1250" spans="1:7" x14ac:dyDescent="0.25">
@@ -41693,7 +41693,7 @@
         <v>46248</v>
       </c>
       <c r="D1264" s="7">
-        <v>1.634426</v>
+        <v>1.632554</v>
       </c>
       <c r="E1264" s="8">
         <v>225217639</v>
@@ -41702,7 +41702,7 @@
         <v>1711</v>
       </c>
       <c r="G1264" s="8">
-        <v>368101531.82</v>
+        <v>367679922.66</v>
       </c>
     </row>
     <row r="1265" spans="1:7" x14ac:dyDescent="0.25">
@@ -42083,17 +42083,17 @@
       <c r="C1281" s="6">
         <v>46248</v>
       </c>
-      <c r="D1281" s="8">
-        <v>0</v>
+      <c r="D1281" s="7">
+        <v>1.002633</v>
       </c>
       <c r="E1281" s="8">
-        <v>0</v>
+        <v>24973451</v>
       </c>
       <c r="F1281" s="9">
         <v>38</v>
       </c>
       <c r="G1281" s="8">
-        <v>0</v>
+        <v>25039207.42</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.25">
@@ -42474,17 +42474,17 @@
       <c r="C1298" s="6">
         <v>46248</v>
       </c>
-      <c r="D1298" s="8">
-        <v>0</v>
+      <c r="D1298" s="7">
+        <v>51.770424</v>
       </c>
       <c r="E1298" s="8">
-        <v>0</v>
+        <v>20128718</v>
       </c>
       <c r="F1298" s="9">
         <v>265</v>
       </c>
       <c r="G1298" s="8">
-        <v>0</v>
+        <v>1042072259.15</v>
       </c>
     </row>
     <row r="1299" spans="1:7" x14ac:dyDescent="0.25">
@@ -43533,7 +43533,7 @@
         <v>46248</v>
       </c>
       <c r="D1344" s="7">
-        <v>1.516013</v>
+        <v>1.515913</v>
       </c>
       <c r="E1344" s="8">
         <v>807855222</v>
@@ -43542,7 +43542,7 @@
         <v>51</v>
       </c>
       <c r="G1344" s="8">
-        <v>1224718861.09</v>
+        <v>1224638038.81</v>
       </c>
     </row>
     <row r="1345" spans="1:7" x14ac:dyDescent="0.25">
@@ -45579,17 +45579,17 @@
       <c r="C1433" s="6">
         <v>46248</v>
       </c>
-      <c r="D1433" s="8">
-        <v>0</v>
+      <c r="D1433" s="7">
+        <v>1.265661</v>
       </c>
       <c r="E1433" s="8">
-        <v>0</v>
+        <v>664630</v>
       </c>
       <c r="F1433" s="9">
         <v>113</v>
       </c>
       <c r="G1433" s="8">
-        <v>0</v>
+        <v>841196.14</v>
       </c>
     </row>
     <row r="1434" spans="1:7" x14ac:dyDescent="0.25">
@@ -48087,7 +48087,7 @@
         <v>46248</v>
       </c>
       <c r="D1542" s="7">
-        <v>1.118005</v>
+        <v>1.118249</v>
       </c>
       <c r="E1542" s="8">
         <v>24849072</v>
@@ -48096,7 +48096,7 @@
         <v>121</v>
       </c>
       <c r="G1542" s="8">
-        <v>27781376.47</v>
+        <v>27787442.36</v>
       </c>
     </row>
     <row r="1543" spans="1:7" x14ac:dyDescent="0.25">
@@ -48110,7 +48110,7 @@
         <v>46248</v>
       </c>
       <c r="D1543" s="7">
-        <v>1.143113</v>
+        <v>1.143301</v>
       </c>
       <c r="E1543" s="8">
         <v>34407131</v>
@@ -48119,7 +48119,7 @@
         <v>24</v>
       </c>
       <c r="G1543" s="8">
-        <v>39331254.9</v>
+        <v>39337715.02</v>
       </c>
     </row>
     <row r="1544" spans="1:7" x14ac:dyDescent="0.25">
@@ -48224,8 +48224,8 @@
       <c r="C1548" s="6">
         <v>46248</v>
       </c>
-      <c r="D1548" s="7">
-        <v>11.747245</v>
+      <c r="D1548" s="10">
+        <v>11.74743</v>
       </c>
       <c r="E1548" s="8">
         <v>17835737</v>
@@ -48234,7 +48234,7 @@
         <v>1617</v>
       </c>
       <c r="G1548" s="8">
-        <v>209520778.45</v>
+        <v>209524074</v>
       </c>
     </row>
     <row r="1549" spans="1:7" x14ac:dyDescent="0.25">
@@ -48247,8 +48247,8 @@
       <c r="C1549" s="6">
         <v>46248</v>
       </c>
-      <c r="D1549" s="10">
-        <v>5.52178</v>
+      <c r="D1549" s="7">
+        <v>5.521808</v>
       </c>
       <c r="E1549" s="8">
         <v>125596067</v>
@@ -48257,7 +48257,7 @@
         <v>4292</v>
       </c>
       <c r="G1549" s="8">
-        <v>693513833.1</v>
+        <v>693517377.08</v>
       </c>
     </row>
     <row r="1550" spans="1:7" x14ac:dyDescent="0.25">
@@ -48547,7 +48547,7 @@
         <v>46248</v>
       </c>
       <c r="D1562" s="7">
-        <v>14.685686</v>
+        <v>14.686265</v>
       </c>
       <c r="E1562" s="8">
         <v>19134476</v>
@@ -48556,7 +48556,7 @@
         <v>1917</v>
       </c>
       <c r="G1562" s="8">
-        <v>281002904.72</v>
+        <v>281013978.95</v>
       </c>
     </row>
     <row r="1563" spans="1:7" x14ac:dyDescent="0.25">
@@ -48662,7 +48662,7 @@
         <v>46248</v>
       </c>
       <c r="D1567" s="7">
-        <v>1.734476</v>
+        <v>1.736227</v>
       </c>
       <c r="E1567" s="8">
         <v>71905303</v>
@@ -48671,7 +48671,7 @@
         <v>23</v>
       </c>
       <c r="G1567" s="8">
-        <v>124718027.36</v>
+        <v>124843954.38</v>
       </c>
     </row>
     <row r="1568" spans="1:7" x14ac:dyDescent="0.25">
@@ -49282,17 +49282,17 @@
       <c r="C1594" s="6">
         <v>46248</v>
       </c>
-      <c r="D1594" s="8">
-        <v>0</v>
+      <c r="D1594" s="7">
+        <v>1.203399</v>
       </c>
       <c r="E1594" s="8">
-        <v>0</v>
+        <v>300626629</v>
       </c>
       <c r="F1594" s="9">
         <v>1</v>
       </c>
       <c r="G1594" s="8">
-        <v>0</v>
+        <v>361773930.38</v>
       </c>
     </row>
     <row r="1595" spans="1:7" x14ac:dyDescent="0.25">
@@ -49512,17 +49512,17 @@
       <c r="C1604" s="6">
         <v>46248</v>
       </c>
-      <c r="D1604" s="8">
-        <v>0</v>
+      <c r="D1604" s="7">
+        <v>1.855801</v>
       </c>
       <c r="E1604" s="8">
-        <v>0</v>
+        <v>249193999</v>
       </c>
       <c r="F1604" s="9">
         <v>834</v>
       </c>
       <c r="G1604" s="8">
-        <v>0</v>
+        <v>462454499.77</v>
       </c>
     </row>
     <row r="1605" spans="1:7" x14ac:dyDescent="0.25">
@@ -49627,17 +49627,17 @@
       <c r="C1609" s="6">
         <v>46248</v>
       </c>
-      <c r="D1609" s="8">
-        <v>0</v>
+      <c r="D1609" s="7">
+        <v>1.008097</v>
       </c>
       <c r="E1609" s="8">
-        <v>0</v>
+        <v>31672521</v>
       </c>
       <c r="F1609" s="9">
         <v>127</v>
       </c>
       <c r="G1609" s="8">
-        <v>0</v>
+        <v>31928989.22</v>
       </c>
     </row>
     <row r="1610" spans="1:7" x14ac:dyDescent="0.25">
@@ -49857,17 +49857,17 @@
       <c r="C1619" s="6">
         <v>46248</v>
       </c>
-      <c r="D1619" s="8">
-        <v>0</v>
+      <c r="D1619" s="7">
+        <v>1.368751</v>
       </c>
       <c r="E1619" s="8">
-        <v>0</v>
+        <v>114353466</v>
       </c>
       <c r="F1619" s="9">
         <v>19</v>
       </c>
       <c r="G1619" s="8">
-        <v>0</v>
+        <v>156521375.61</v>
       </c>
     </row>
     <row r="1620" spans="1:7" x14ac:dyDescent="0.25">
@@ -49880,17 +49880,17 @@
       <c r="C1620" s="6">
         <v>46248</v>
       </c>
-      <c r="D1620" s="8">
-        <v>0</v>
+      <c r="D1620" s="7">
+        <v>0.947627</v>
       </c>
       <c r="E1620" s="8">
-        <v>0</v>
+        <v>113804986</v>
       </c>
       <c r="F1620" s="9">
         <v>11</v>
       </c>
       <c r="G1620" s="8">
-        <v>0</v>
+        <v>107844693.61</v>
       </c>
     </row>
     <row r="1621" spans="1:7" x14ac:dyDescent="0.25">
@@ -50686,7 +50686,7 @@
         <v>46248</v>
       </c>
       <c r="D1655" s="7">
-        <v>1.289811</v>
+        <v>1.290647</v>
       </c>
       <c r="E1655" s="8">
         <v>145147711</v>
@@ -50695,7 +50695,7 @@
         <v>69</v>
       </c>
       <c r="G1655" s="8">
-        <v>187213077.78</v>
+        <v>187334412.23</v>
       </c>
     </row>
     <row r="1656" spans="1:7" x14ac:dyDescent="0.25">
@@ -50777,8 +50777,8 @@
       <c r="C1659" s="6">
         <v>46248</v>
       </c>
-      <c r="D1659" s="7">
-        <v>0.591348</v>
+      <c r="D1659" s="10">
+        <v>0.59135</v>
       </c>
       <c r="E1659" s="8">
         <v>3789185216</v>
@@ -50787,7 +50787,7 @@
         <v>1170</v>
       </c>
       <c r="G1659" s="8">
-        <v>2240726253.98</v>
+        <v>2240736099.92</v>
       </c>
     </row>
     <row r="1660" spans="1:7" x14ac:dyDescent="0.25">
@@ -51192,7 +51192,7 @@
         <v>46248</v>
       </c>
       <c r="D1677" s="7">
-        <v>0.279437</v>
+        <v>0.279439</v>
       </c>
       <c r="E1677" s="8">
         <v>1663080294</v>
@@ -51201,7 +51201,7 @@
         <v>199</v>
       </c>
       <c r="G1677" s="8">
-        <v>464725917.12</v>
+        <v>464729124.09</v>
       </c>
     </row>
     <row r="1678" spans="1:7" x14ac:dyDescent="0.25">
@@ -52388,7 +52388,7 @@
         <v>46248</v>
       </c>
       <c r="D1729" s="7">
-        <v>1.757288</v>
+        <v>1.757301</v>
       </c>
       <c r="E1729" s="8">
         <v>1031667850</v>
@@ -52397,7 +52397,7 @@
         <v>113302</v>
       </c>
       <c r="G1729" s="8">
-        <v>1812937741.01</v>
+        <v>1812951135.89</v>
       </c>
     </row>
     <row r="1730" spans="1:7" x14ac:dyDescent="0.25">
@@ -54504,7 +54504,7 @@
         <v>46248</v>
       </c>
       <c r="D1821" s="7">
-        <v>0.259511</v>
+        <v>0.259513</v>
       </c>
       <c r="E1821" s="8">
         <v>5185403572</v>
@@ -54513,7 +54513,7 @@
         <v>396</v>
       </c>
       <c r="G1821" s="8">
-        <v>1345667433.26</v>
+        <v>1345677278.92</v>
       </c>
     </row>
     <row r="1822" spans="1:7" x14ac:dyDescent="0.25">
@@ -54549,8 +54549,8 @@
       <c r="C1823" s="6">
         <v>46248</v>
       </c>
-      <c r="D1823" s="10">
-        <v>9.14435</v>
+      <c r="D1823" s="7">
+        <v>9.144656</v>
       </c>
       <c r="E1823" s="8">
         <v>29874741</v>
@@ -54559,7 +54559,7 @@
         <v>39</v>
       </c>
       <c r="G1823" s="8">
-        <v>273185098.49</v>
+        <v>273194227.65</v>
       </c>
     </row>
     <row r="1824" spans="1:7" x14ac:dyDescent="0.25">
@@ -54687,17 +54687,17 @@
       <c r="C1829" s="6">
         <v>46248</v>
       </c>
-      <c r="D1829" s="8">
-        <v>0</v>
+      <c r="D1829" s="7">
+        <v>1.002073</v>
       </c>
       <c r="E1829" s="8">
-        <v>0</v>
+        <v>105425274</v>
       </c>
       <c r="F1829" s="9">
         <v>2754</v>
       </c>
       <c r="G1829" s="8">
-        <v>0</v>
+        <v>105643835</v>
       </c>
     </row>
     <row r="1830" spans="1:7" x14ac:dyDescent="0.25">
@@ -55101,17 +55101,17 @@
       <c r="C1847" s="6">
         <v>46248</v>
       </c>
-      <c r="D1847" s="8">
-        <v>0</v>
+      <c r="D1847" s="7">
+        <v>14.556637</v>
       </c>
       <c r="E1847" s="8">
-        <v>0</v>
+        <v>374375562</v>
       </c>
       <c r="F1847" s="9">
         <v>9848</v>
       </c>
       <c r="G1847" s="8">
-        <v>0</v>
+        <v>5449649049.79</v>
       </c>
     </row>
     <row r="1848" spans="1:7" x14ac:dyDescent="0.25">
@@ -55170,17 +55170,17 @@
       <c r="C1850" s="6">
         <v>46248</v>
       </c>
-      <c r="D1850" s="8">
-        <v>0</v>
+      <c r="D1850" s="7">
+        <v>14.425207</v>
       </c>
       <c r="E1850" s="8">
-        <v>0</v>
+        <v>128663497</v>
       </c>
       <c r="F1850" s="9">
         <v>3582</v>
       </c>
       <c r="G1850" s="8">
-        <v>0</v>
+        <v>1855997573.58</v>
       </c>
     </row>
     <row r="1851" spans="1:7" x14ac:dyDescent="0.25">
@@ -55423,17 +55423,17 @@
       <c r="C1861" s="6">
         <v>46248</v>
       </c>
-      <c r="D1861" s="8">
-        <v>0</v>
+      <c r="D1861" s="7">
+        <v>2.673934</v>
       </c>
       <c r="E1861" s="8">
-        <v>0</v>
+        <v>40693972</v>
       </c>
       <c r="F1861" s="9">
         <v>116</v>
       </c>
       <c r="G1861" s="8">
-        <v>0</v>
+        <v>108813010.98</v>
       </c>
     </row>
     <row r="1862" spans="1:7" x14ac:dyDescent="0.25">
@@ -55998,17 +55998,17 @@
       <c r="C1886" s="6">
         <v>46248</v>
       </c>
-      <c r="D1886" s="8">
-        <v>0</v>
+      <c r="D1886" s="7">
+        <v>2.781889</v>
       </c>
       <c r="E1886" s="8">
-        <v>0</v>
+        <v>910323641</v>
       </c>
       <c r="F1886" s="9">
         <v>17109</v>
       </c>
       <c r="G1886" s="8">
-        <v>0</v>
+        <v>2532419661.82</v>
       </c>
     </row>
     <row r="1887" spans="1:7" x14ac:dyDescent="0.25">
@@ -56090,17 +56090,17 @@
       <c r="C1890" s="6">
         <v>46248</v>
       </c>
-      <c r="D1890" s="8">
-        <v>0</v>
+      <c r="D1890" s="7">
+        <v>5.926197</v>
       </c>
       <c r="E1890" s="8">
-        <v>0</v>
+        <v>181073436</v>
       </c>
       <c r="F1890" s="9">
         <v>13889</v>
       </c>
       <c r="G1890" s="8">
-        <v>0</v>
+        <v>1073076893.49</v>
       </c>
     </row>
     <row r="1891" spans="1:7" x14ac:dyDescent="0.25">
@@ -56918,17 +56918,17 @@
       <c r="C1926" s="6">
         <v>46248</v>
       </c>
-      <c r="D1926" s="8">
-        <v>0</v>
+      <c r="D1926" s="7">
+        <v>7.823178</v>
       </c>
       <c r="E1926" s="8">
-        <v>0</v>
+        <v>706428467</v>
       </c>
       <c r="F1926" s="9">
         <v>3367</v>
       </c>
       <c r="G1926" s="8">
-        <v>0</v>
+        <v>5526515853.02</v>
       </c>
     </row>
     <row r="1927" spans="1:7" x14ac:dyDescent="0.25">
@@ -57079,17 +57079,17 @@
       <c r="C1933" s="6">
         <v>46248</v>
       </c>
-      <c r="D1933" s="8">
-        <v>0</v>
+      <c r="D1933" s="7">
+        <v>0.959863</v>
       </c>
       <c r="E1933" s="8">
-        <v>0</v>
+        <v>1832005848</v>
       </c>
       <c r="F1933" s="9">
         <v>14875</v>
       </c>
       <c r="G1933" s="8">
-        <v>0</v>
+        <v>1758475277.2</v>
       </c>
     </row>
     <row r="1934" spans="1:7" x14ac:dyDescent="0.25">
@@ -57539,17 +57539,17 @@
       <c r="C1953" s="6">
         <v>46248</v>
       </c>
-      <c r="D1953" s="8">
-        <v>0</v>
+      <c r="D1953" s="7">
+        <v>13.013224</v>
       </c>
       <c r="E1953" s="8">
-        <v>0</v>
+        <v>844022842</v>
       </c>
       <c r="F1953" s="9">
         <v>61313</v>
       </c>
       <c r="G1953" s="8">
-        <v>0</v>
+        <v>10983457901.83</v>
       </c>
     </row>
     <row r="1954" spans="1:7" x14ac:dyDescent="0.25">
@@ -57654,17 +57654,17 @@
       <c r="C1958" s="6">
         <v>46248</v>
       </c>
-      <c r="D1958" s="8">
-        <v>0</v>
+      <c r="D1958" s="7">
+        <v>2.033045</v>
       </c>
       <c r="E1958" s="8">
-        <v>0</v>
+        <v>2113757623</v>
       </c>
       <c r="F1958" s="9">
         <v>613</v>
       </c>
       <c r="G1958" s="8">
-        <v>0</v>
+        <v>4297363361.16</v>
       </c>
     </row>
     <row r="1959" spans="1:7" x14ac:dyDescent="0.25">
@@ -57677,17 +57677,17 @@
       <c r="C1959" s="6">
         <v>46248</v>
       </c>
-      <c r="D1959" s="8">
-        <v>0</v>
+      <c r="D1959" s="7">
+        <v>46.148308</v>
       </c>
       <c r="E1959" s="8">
-        <v>0</v>
+        <v>331891</v>
       </c>
       <c r="F1959" s="9">
         <v>46</v>
       </c>
       <c r="G1959" s="8">
-        <v>0</v>
+        <v>15316208.17</v>
       </c>
     </row>
     <row r="1960" spans="1:7" x14ac:dyDescent="0.25">
@@ -57723,17 +57723,17 @@
       <c r="C1961" s="6">
         <v>46248</v>
       </c>
-      <c r="D1961" s="8">
-        <v>0</v>
+      <c r="D1961" s="7">
+        <v>6.363207</v>
       </c>
       <c r="E1961" s="8">
-        <v>0</v>
+        <v>242465615</v>
       </c>
       <c r="F1961" s="9">
         <v>3352</v>
       </c>
       <c r="G1961" s="8">
-        <v>0</v>
+        <v>1542858939.61</v>
       </c>
     </row>
     <row r="1962" spans="1:7" x14ac:dyDescent="0.25">
@@ -58091,8 +58091,8 @@
       <c r="C1977" s="6">
         <v>46248</v>
       </c>
-      <c r="D1977" s="7">
-        <v>3.959046</v>
+      <c r="D1977" s="11">
+        <v>3.9606</v>
       </c>
       <c r="E1977" s="8">
         <v>144094200</v>
@@ -58101,7 +58101,7 @@
         <v>6597</v>
       </c>
       <c r="G1977" s="8">
-        <v>570475517.14</v>
+        <v>570699485.56</v>
       </c>
     </row>
     <row r="1978" spans="1:7" x14ac:dyDescent="0.25">
@@ -58667,7 +58667,7 @@
         <v>46248</v>
       </c>
       <c r="D2002" s="7">
-        <v>1.888959</v>
+        <v>1.882629</v>
       </c>
       <c r="E2002" s="8">
         <v>306521428</v>
@@ -58676,7 +58676,7 @@
         <v>11</v>
       </c>
       <c r="G2002" s="8">
-        <v>579006278.34</v>
+        <v>577066127.32</v>
       </c>
     </row>
     <row r="2003" spans="1:7" x14ac:dyDescent="0.25">
@@ -58713,7 +58713,7 @@
         <v>46248</v>
       </c>
       <c r="D2004" s="7">
-        <v>5.744083</v>
+        <v>5.743522</v>
       </c>
       <c r="E2004" s="8">
         <v>106786382</v>
@@ -58722,7 +58722,7 @@
         <v>1</v>
       </c>
       <c r="G2004" s="8">
-        <v>613389857.09</v>
+        <v>613329881.04</v>
       </c>
     </row>
     <row r="2005" spans="1:7" x14ac:dyDescent="0.25">
@@ -58874,7 +58874,7 @@
         <v>46248</v>
       </c>
       <c r="D2011" s="7">
-        <v>19.200053</v>
+        <v>19.200501</v>
       </c>
       <c r="E2011" s="8">
         <v>165117629</v>
@@ -58883,7 +58883,7 @@
         <v>2772</v>
       </c>
       <c r="G2011" s="8">
-        <v>3170267288.33</v>
+        <v>3170341186.31</v>
       </c>
     </row>
     <row r="2012" spans="1:7" x14ac:dyDescent="0.25">
@@ -59150,7 +59150,7 @@
         <v>46248</v>
       </c>
       <c r="D2023" s="7">
-        <v>11.876349</v>
+        <v>11.874013</v>
       </c>
       <c r="E2023" s="8">
         <v>299315692</v>
@@ -59159,7 +59159,7 @@
         <v>24</v>
       </c>
       <c r="G2023" s="8">
-        <v>3554777765.53</v>
+        <v>3554078378.01</v>
       </c>
     </row>
     <row r="2024" spans="1:7" x14ac:dyDescent="0.25">
@@ -59196,7 +59196,7 @@
         <v>46248</v>
       </c>
       <c r="D2025" s="7">
-        <v>4.340538</v>
+        <v>4.339582</v>
       </c>
       <c r="E2025" s="8">
         <v>11391000</v>
@@ -59205,7 +59205,7 @@
         <v>933</v>
       </c>
       <c r="G2025" s="8">
-        <v>49443073.51</v>
+        <v>49432174.88</v>
       </c>
     </row>
     <row r="2026" spans="1:7" x14ac:dyDescent="0.25">
@@ -59265,7 +59265,7 @@
         <v>46248</v>
       </c>
       <c r="D2028" s="7">
-        <v>7.507256</v>
+        <v>7.505689</v>
       </c>
       <c r="E2028" s="8">
         <v>274862095</v>
@@ -59274,7 +59274,7 @@
         <v>1</v>
       </c>
       <c r="G2028" s="8">
-        <v>2063460059.8</v>
+        <v>2063029341.11</v>
       </c>
     </row>
     <row r="2029" spans="1:7" x14ac:dyDescent="0.25">
@@ -59288,7 +59288,7 @@
         <v>46248</v>
       </c>
       <c r="D2029" s="7">
-        <v>1.294639</v>
+        <v>1.296348</v>
       </c>
       <c r="E2029" s="8">
         <v>31041816</v>
@@ -59297,7 +59297,7 @@
         <v>1008</v>
       </c>
       <c r="G2029" s="8">
-        <v>40187937.46</v>
+        <v>40241005.41</v>
       </c>
     </row>
     <row r="2030" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>17.08.2026 09:28:05</t>
+    <t>17.08.2026 10:08:48</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -13523,8 +13523,8 @@
       <c r="C39" s="6">
         <v>46251</v>
       </c>
-      <c r="D39" s="7">
-        <v>21.432931</v>
+      <c r="D39" s="10">
+        <v>21.49891</v>
       </c>
       <c r="E39" s="8">
         <v>6008791</v>
@@ -13533,7 +13533,7 @@
         <v>183</v>
       </c>
       <c r="G39" s="8">
-        <v>128786000.7</v>
+        <v>129182455.47</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -13547,7 +13547,7 @@
         <v>46251</v>
       </c>
       <c r="D40" s="7">
-        <v>31.062728</v>
+        <v>31.161993</v>
       </c>
       <c r="E40" s="8">
         <v>1749021</v>
@@ -13556,7 +13556,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="8">
-        <v>54329363.02</v>
+        <v>54502980.17</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -13694,7 +13694,7 @@
         <v>21180</v>
       </c>
       <c r="G46" s="8">
-        <v>14632446005.59</v>
+        <v>14632452311.64</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -14559,7 +14559,7 @@
         <v>46251</v>
       </c>
       <c r="D84" s="7">
-        <v>1.187586</v>
+        <v>1.187745</v>
       </c>
       <c r="E84" s="8">
         <v>41643777</v>
@@ -14568,7 +14568,7 @@
         <v>814</v>
       </c>
       <c r="G84" s="8">
-        <v>49455558.4</v>
+        <v>49462192.44</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -14720,7 +14720,7 @@
         <v>46251</v>
       </c>
       <c r="D91" s="7">
-        <v>18.831658</v>
+        <v>18.823679</v>
       </c>
       <c r="E91" s="8">
         <v>58703314</v>
@@ -14729,7 +14729,7 @@
         <v>9765</v>
       </c>
       <c r="G91" s="8">
-        <v>1105480745.26</v>
+        <v>1105012360.14</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -15295,16 +15295,16 @@
         <v>46251</v>
       </c>
       <c r="D116" s="7">
-        <v>2.937893</v>
+        <v>2.934949</v>
       </c>
       <c r="E116" s="8">
-        <v>1196356226</v>
+        <v>1152244773</v>
       </c>
       <c r="F116" s="9">
         <v>11</v>
       </c>
       <c r="G116" s="8">
-        <v>3514766300.21</v>
+        <v>3381779943.78</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -16891,7 +16891,7 @@
         <v>2872</v>
       </c>
       <c r="G185" s="8">
-        <v>126668189.79</v>
+        <v>126668188.81</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -18133,7 +18133,7 @@
         <v>403</v>
       </c>
       <c r="G239" s="8">
-        <v>1378193489.48</v>
+        <v>1378193490.58</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -18883,7 +18883,7 @@
         <v>46251</v>
       </c>
       <c r="D272" s="7">
-        <v>3.119389</v>
+        <v>3.119336</v>
       </c>
       <c r="E272" s="8">
         <v>39944095</v>
@@ -18892,7 +18892,7 @@
         <v>1540</v>
       </c>
       <c r="G272" s="8">
-        <v>124601161.97</v>
+        <v>124599051.44</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -19136,7 +19136,7 @@
         <v>46251</v>
       </c>
       <c r="D283" s="7">
-        <v>1.224382</v>
+        <v>1.224353</v>
       </c>
       <c r="E283" s="8">
         <v>63929695</v>
@@ -19145,7 +19145,7 @@
         <v>695</v>
       </c>
       <c r="G283" s="8">
-        <v>78274349.67</v>
+        <v>78272514.41</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -19273,17 +19273,17 @@
       <c r="C289" s="6">
         <v>46251</v>
       </c>
-      <c r="D289" s="8">
-        <v>0</v>
+      <c r="D289" s="7">
+        <v>1.472753</v>
       </c>
       <c r="E289" s="8">
-        <v>0</v>
+        <v>2188814721</v>
       </c>
       <c r="F289" s="9">
         <v>61</v>
       </c>
       <c r="G289" s="8">
-        <v>0</v>
+        <v>3223582476.68</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -19457,8 +19457,8 @@
       <c r="C297" s="6">
         <v>46251</v>
       </c>
-      <c r="D297" s="10">
-        <v>47.92448</v>
+      <c r="D297" s="11">
+        <v>47.7527</v>
       </c>
       <c r="E297" s="8">
         <v>56318233</v>
@@ -19467,7 +19467,7 @@
         <v>228</v>
       </c>
       <c r="G297" s="8">
-        <v>2699022039.28</v>
+        <v>2689347690.92</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -20769,7 +20769,7 @@
         <v>46251</v>
       </c>
       <c r="D354" s="7">
-        <v>1.431769</v>
+        <v>1.431579</v>
       </c>
       <c r="E354" s="8">
         <v>42898955</v>
@@ -20778,7 +20778,7 @@
         <v>2723</v>
       </c>
       <c r="G354" s="8">
-        <v>61421388.31</v>
+        <v>61413252.32</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -21550,8 +21550,8 @@
       <c r="C388" s="6">
         <v>46251</v>
       </c>
-      <c r="D388" s="7">
-        <v>1.131616</v>
+      <c r="D388" s="10">
+        <v>1.13162</v>
       </c>
       <c r="E388" s="8">
         <v>18867606</v>
@@ -21560,7 +21560,7 @@
         <v>773</v>
       </c>
       <c r="G388" s="8">
-        <v>21350878.31</v>
+        <v>21350962.98</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -21872,17 +21872,17 @@
       <c r="C402" s="6">
         <v>46251</v>
       </c>
-      <c r="D402" s="8">
-        <v>0</v>
+      <c r="D402" s="7">
+        <v>1.815616</v>
       </c>
       <c r="E402" s="8">
-        <v>0</v>
+        <v>1455596770</v>
       </c>
       <c r="F402" s="9">
         <v>1367</v>
       </c>
       <c r="G402" s="8">
-        <v>0</v>
+        <v>2642804999.2</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
@@ -21965,7 +21965,7 @@
         <v>46251</v>
       </c>
       <c r="D406" s="7">
-        <v>1.127101</v>
+        <v>1.127131</v>
       </c>
       <c r="E406" s="8">
         <v>25174562</v>
@@ -21974,7 +21974,7 @@
         <v>1457</v>
       </c>
       <c r="G406" s="8">
-        <v>28374269.14</v>
+        <v>28375035.31</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
@@ -22057,7 +22057,7 @@
         <v>46251</v>
       </c>
       <c r="D410" s="7">
-        <v>1.211899</v>
+        <v>1.211891</v>
       </c>
       <c r="E410" s="8">
         <v>34345710</v>
@@ -22066,7 +22066,7 @@
         <v>1742</v>
       </c>
       <c r="G410" s="8">
-        <v>41623543.98</v>
+        <v>41623242.35</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
@@ -22401,17 +22401,17 @@
       <c r="C425" s="6">
         <v>46251</v>
       </c>
-      <c r="D425" s="8">
-        <v>0</v>
+      <c r="D425" s="7">
+        <v>44.382808</v>
       </c>
       <c r="E425" s="8">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F425" s="9">
         <v>1</v>
       </c>
       <c r="G425" s="8">
-        <v>0</v>
+        <v>4438280.78</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
@@ -23207,7 +23207,7 @@
         <v>46251</v>
       </c>
       <c r="D460" s="7">
-        <v>58.941076</v>
+        <v>58.956286</v>
       </c>
       <c r="E460" s="8">
         <v>838296051</v>
@@ -23216,7 +23216,7 @@
         <v>12189</v>
       </c>
       <c r="G460" s="8">
-        <v>49410071255.84</v>
+        <v>49422821491.3</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.25">
@@ -23897,7 +23897,7 @@
         <v>46251</v>
       </c>
       <c r="D490" s="7">
-        <v>4.888427</v>
+        <v>4.898603</v>
       </c>
       <c r="E490" s="8">
         <v>78362491</v>
@@ -23906,7 +23906,7 @@
         <v>550</v>
       </c>
       <c r="G490" s="8">
-        <v>383069312.27</v>
+        <v>383866715.93</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
@@ -24495,7 +24495,7 @@
         <v>46251</v>
       </c>
       <c r="D516" s="7">
-        <v>5.630262</v>
+        <v>5.639421</v>
       </c>
       <c r="E516" s="8">
         <v>206558521.63</v>
@@ -24504,7 +24504,7 @@
         <v>2140</v>
       </c>
       <c r="G516" s="8">
-        <v>1162978586.92</v>
+        <v>1164870481.42</v>
       </c>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.25">
@@ -24563,17 +24563,17 @@
       <c r="C519" s="6">
         <v>46251</v>
       </c>
-      <c r="D519" s="8">
-        <v>0</v>
+      <c r="D519" s="7">
+        <v>77.080644</v>
       </c>
       <c r="E519" s="8">
-        <v>0</v>
+        <v>5527677</v>
       </c>
       <c r="F519" s="9">
         <v>1</v>
       </c>
       <c r="G519" s="8">
-        <v>0</v>
+        <v>426076902.26</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
@@ -24655,17 +24655,17 @@
       <c r="C523" s="6">
         <v>46251</v>
       </c>
-      <c r="D523" s="8">
-        <v>0</v>
+      <c r="D523" s="10">
+        <v>12.64654</v>
       </c>
       <c r="E523" s="8">
-        <v>0</v>
+        <v>29702642</v>
       </c>
       <c r="F523" s="9">
         <v>2708</v>
       </c>
       <c r="G523" s="8">
-        <v>0</v>
+        <v>375635637.51</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.25">
@@ -24678,17 +24678,17 @@
       <c r="C524" s="6">
         <v>46251</v>
       </c>
-      <c r="D524" s="8">
-        <v>0</v>
+      <c r="D524" s="7">
+        <v>63.417309</v>
       </c>
       <c r="E524" s="8">
-        <v>0</v>
+        <v>7935068</v>
       </c>
       <c r="F524" s="9">
         <v>1</v>
       </c>
       <c r="G524" s="8">
-        <v>0</v>
+        <v>503220661.33</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.25">
@@ -24770,17 +24770,17 @@
       <c r="C528" s="6">
         <v>46251</v>
       </c>
-      <c r="D528" s="8">
-        <v>0</v>
+      <c r="D528" s="10">
+        <v>66.62542</v>
       </c>
       <c r="E528" s="8">
-        <v>0</v>
+        <v>32360328</v>
       </c>
       <c r="F528" s="9">
         <v>5</v>
       </c>
       <c r="G528" s="8">
-        <v>0</v>
+        <v>2156020456.08</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.25">
@@ -24793,17 +24793,17 @@
       <c r="C529" s="6">
         <v>46251</v>
       </c>
-      <c r="D529" s="8">
-        <v>0</v>
+      <c r="D529" s="7">
+        <v>62.549909</v>
       </c>
       <c r="E529" s="8">
-        <v>0</v>
+        <v>3941000</v>
       </c>
       <c r="F529" s="9">
         <v>1</v>
       </c>
       <c r="G529" s="8">
-        <v>0</v>
+        <v>246509190.75</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
@@ -24954,17 +24954,17 @@
       <c r="C536" s="6">
         <v>46251</v>
       </c>
-      <c r="D536" s="8">
-        <v>0</v>
+      <c r="D536" s="7">
+        <v>70.595378</v>
       </c>
       <c r="E536" s="8">
-        <v>0</v>
+        <v>53983981</v>
       </c>
       <c r="F536" s="9">
         <v>2</v>
       </c>
       <c r="G536" s="8">
-        <v>0</v>
+        <v>3811019569.21</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.25">
@@ -24977,17 +24977,17 @@
       <c r="C537" s="6">
         <v>46251</v>
       </c>
-      <c r="D537" s="8">
-        <v>0</v>
+      <c r="D537" s="7">
+        <v>13.192115</v>
       </c>
       <c r="E537" s="8">
-        <v>0</v>
+        <v>188573335</v>
       </c>
       <c r="F537" s="9">
         <v>22633</v>
       </c>
       <c r="G537" s="8">
-        <v>0</v>
+        <v>2487681142.67</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
@@ -25001,7 +25001,7 @@
         <v>46251</v>
       </c>
       <c r="D538" s="7">
-        <v>3.451349</v>
+        <v>3.452149</v>
       </c>
       <c r="E538" s="8">
         <v>321394919</v>
@@ -25010,7 +25010,7 @@
         <v>3268</v>
       </c>
       <c r="G538" s="8">
-        <v>1109245905.6</v>
+        <v>1109503031.98</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
@@ -25023,17 +25023,17 @@
       <c r="C539" s="6">
         <v>46251</v>
       </c>
-      <c r="D539" s="8">
-        <v>0</v>
+      <c r="D539" s="10">
+        <v>70.79417</v>
       </c>
       <c r="E539" s="8">
-        <v>0</v>
+        <v>11533344</v>
       </c>
       <c r="F539" s="9">
         <v>2</v>
       </c>
       <c r="G539" s="8">
-        <v>0</v>
+        <v>816493517.91</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
@@ -25092,17 +25092,17 @@
       <c r="C542" s="6">
         <v>46251</v>
       </c>
-      <c r="D542" s="8">
-        <v>0</v>
+      <c r="D542" s="7">
+        <v>64.360211</v>
       </c>
       <c r="E542" s="8">
-        <v>0</v>
+        <v>3425896</v>
       </c>
       <c r="F542" s="9">
         <v>3</v>
       </c>
       <c r="G542" s="8">
-        <v>0</v>
+        <v>220491389.9</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
@@ -25115,17 +25115,17 @@
       <c r="C543" s="6">
         <v>46251</v>
       </c>
-      <c r="D543" s="8">
-        <v>0</v>
+      <c r="D543" s="7">
+        <v>60.777299</v>
       </c>
       <c r="E543" s="8">
-        <v>0</v>
+        <v>194715</v>
       </c>
       <c r="F543" s="9">
         <v>1</v>
       </c>
       <c r="G543" s="8">
-        <v>0</v>
+        <v>11834251.76</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -25138,17 +25138,17 @@
       <c r="C544" s="6">
         <v>46251</v>
       </c>
-      <c r="D544" s="8">
-        <v>0</v>
+      <c r="D544" s="7">
+        <v>61.592866</v>
       </c>
       <c r="E544" s="8">
-        <v>0</v>
+        <v>8101428</v>
       </c>
       <c r="F544" s="9">
         <v>4</v>
       </c>
       <c r="G544" s="8">
-        <v>0</v>
+        <v>498990167.59</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
@@ -25161,17 +25161,17 @@
       <c r="C545" s="6">
         <v>46251</v>
       </c>
-      <c r="D545" s="8">
-        <v>0</v>
+      <c r="D545" s="7">
+        <v>66.484984</v>
       </c>
       <c r="E545" s="8">
-        <v>0</v>
+        <v>23236050</v>
       </c>
       <c r="F545" s="9">
         <v>1</v>
       </c>
       <c r="G545" s="8">
-        <v>0</v>
+        <v>1544848401.06</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -25184,17 +25184,17 @@
       <c r="C546" s="6">
         <v>46251</v>
       </c>
-      <c r="D546" s="8">
-        <v>0</v>
+      <c r="D546" s="7">
+        <v>76.211431</v>
       </c>
       <c r="E546" s="8">
-        <v>0</v>
+        <v>2099501</v>
       </c>
       <c r="F546" s="9">
         <v>2</v>
       </c>
       <c r="G546" s="8">
-        <v>0</v>
+        <v>160005976.28</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
@@ -25230,17 +25230,17 @@
       <c r="C548" s="6">
         <v>46251</v>
       </c>
-      <c r="D548" s="8">
-        <v>0</v>
+      <c r="D548" s="7">
+        <v>61.082824</v>
       </c>
       <c r="E548" s="8">
-        <v>0</v>
+        <v>6634456</v>
       </c>
       <c r="F548" s="9">
         <v>1</v>
       </c>
       <c r="G548" s="8">
-        <v>0</v>
+        <v>405251308.35</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
@@ -25253,17 +25253,17 @@
       <c r="C549" s="6">
         <v>46251</v>
       </c>
-      <c r="D549" s="8">
-        <v>0</v>
+      <c r="D549" s="7">
+        <v>70.151146</v>
       </c>
       <c r="E549" s="8">
-        <v>0</v>
+        <v>5961167</v>
       </c>
       <c r="F549" s="9">
         <v>4</v>
       </c>
       <c r="G549" s="8">
-        <v>0</v>
+        <v>418182693.86</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -25276,17 +25276,17 @@
       <c r="C550" s="6">
         <v>46251</v>
       </c>
-      <c r="D550" s="8">
-        <v>0</v>
+      <c r="D550" s="7">
+        <v>70.320168</v>
       </c>
       <c r="E550" s="8">
-        <v>0</v>
+        <v>1555160</v>
       </c>
       <c r="F550" s="9">
         <v>2</v>
       </c>
       <c r="G550" s="8">
-        <v>0</v>
+        <v>109359112.45</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
@@ -25299,17 +25299,17 @@
       <c r="C551" s="6">
         <v>46251</v>
       </c>
-      <c r="D551" s="8">
-        <v>0</v>
+      <c r="D551" s="7">
+        <v>53.628568</v>
       </c>
       <c r="E551" s="8">
-        <v>0</v>
+        <v>30698413</v>
       </c>
       <c r="F551" s="9">
         <v>3</v>
       </c>
       <c r="G551" s="8">
-        <v>0</v>
+        <v>1646311924.02</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -25322,17 +25322,17 @@
       <c r="C552" s="6">
         <v>46251</v>
       </c>
-      <c r="D552" s="8">
-        <v>0</v>
+      <c r="D552" s="7">
+        <v>11.888817</v>
       </c>
       <c r="E552" s="8">
-        <v>0</v>
+        <v>29486927</v>
       </c>
       <c r="F552" s="9">
         <v>1</v>
       </c>
       <c r="G552" s="8">
-        <v>0</v>
+        <v>350564668.85</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
@@ -25345,17 +25345,17 @@
       <c r="C553" s="6">
         <v>46251</v>
       </c>
-      <c r="D553" s="8">
-        <v>0</v>
+      <c r="D553" s="7">
+        <v>80.379295</v>
       </c>
       <c r="E553" s="8">
-        <v>0</v>
+        <v>11573436</v>
       </c>
       <c r="F553" s="9">
         <v>3</v>
       </c>
       <c r="G553" s="8">
-        <v>0</v>
+        <v>930264626.02</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
@@ -25368,17 +25368,17 @@
       <c r="C554" s="6">
         <v>46251</v>
       </c>
-      <c r="D554" s="8">
-        <v>0</v>
+      <c r="D554" s="7">
+        <v>70.365549</v>
       </c>
       <c r="E554" s="8">
-        <v>0</v>
+        <v>5822807</v>
       </c>
       <c r="F554" s="9">
         <v>3</v>
       </c>
       <c r="G554" s="8">
-        <v>0</v>
+        <v>409725010.26</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
@@ -25437,17 +25437,17 @@
       <c r="C557" s="6">
         <v>46251</v>
       </c>
-      <c r="D557" s="8">
-        <v>0</v>
+      <c r="D557" s="7">
+        <v>65.705331</v>
       </c>
       <c r="E557" s="8">
-        <v>0</v>
+        <v>90240169</v>
       </c>
       <c r="F557" s="9">
         <v>2</v>
       </c>
       <c r="G557" s="8">
-        <v>0</v>
+        <v>5929260153.71</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
@@ -25483,17 +25483,17 @@
       <c r="C559" s="6">
         <v>46251</v>
       </c>
-      <c r="D559" s="8">
-        <v>0</v>
+      <c r="D559" s="7">
+        <v>8.442281</v>
       </c>
       <c r="E559" s="8">
-        <v>0</v>
+        <v>342290935</v>
       </c>
       <c r="F559" s="9">
         <v>1</v>
       </c>
       <c r="G559" s="8">
-        <v>0</v>
+        <v>2889716427.18</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.25">
@@ -25506,17 +25506,17 @@
       <c r="C560" s="6">
         <v>46251</v>
       </c>
-      <c r="D560" s="8">
-        <v>0</v>
+      <c r="D560" s="7">
+        <v>69.167705</v>
       </c>
       <c r="E560" s="8">
-        <v>0</v>
+        <v>6963426</v>
       </c>
       <c r="F560" s="9">
         <v>4</v>
       </c>
       <c r="G560" s="8">
-        <v>0</v>
+        <v>481644196.54</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
@@ -25529,17 +25529,17 @@
       <c r="C561" s="6">
         <v>46251</v>
       </c>
-      <c r="D561" s="8">
-        <v>0</v>
+      <c r="D561" s="7">
+        <v>11.152056</v>
       </c>
       <c r="E561" s="8">
-        <v>0</v>
+        <v>6927</v>
       </c>
       <c r="F561" s="9">
         <v>1</v>
       </c>
       <c r="G561" s="8">
-        <v>0</v>
+        <v>77250.29</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
@@ -25552,17 +25552,17 @@
       <c r="C562" s="6">
         <v>46251</v>
       </c>
-      <c r="D562" s="8">
-        <v>0</v>
+      <c r="D562" s="10">
+        <v>68.06085</v>
       </c>
       <c r="E562" s="8">
-        <v>0</v>
+        <v>23597904</v>
       </c>
       <c r="F562" s="9">
         <v>3</v>
       </c>
       <c r="G562" s="8">
-        <v>0</v>
+        <v>1606093404.65</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
@@ -25598,17 +25598,17 @@
       <c r="C564" s="6">
         <v>46251</v>
       </c>
-      <c r="D564" s="8">
-        <v>0</v>
+      <c r="D564" s="7">
+        <v>1.670254</v>
       </c>
       <c r="E564" s="8">
-        <v>0</v>
+        <v>27146583</v>
       </c>
       <c r="F564" s="9">
         <v>1954</v>
       </c>
       <c r="G564" s="8">
-        <v>0</v>
+        <v>45341676.07</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
@@ -25667,17 +25667,17 @@
       <c r="C567" s="6">
         <v>46251</v>
       </c>
-      <c r="D567" s="8">
-        <v>0</v>
+      <c r="D567" s="7">
+        <v>66.644876</v>
       </c>
       <c r="E567" s="8">
-        <v>0</v>
+        <v>14263356</v>
       </c>
       <c r="F567" s="9">
         <v>3</v>
       </c>
       <c r="G567" s="8">
-        <v>0</v>
+        <v>950579594.97</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
@@ -25713,17 +25713,17 @@
       <c r="C569" s="6">
         <v>46251</v>
       </c>
-      <c r="D569" s="8">
-        <v>0</v>
+      <c r="D569" s="7">
+        <v>64.059136</v>
       </c>
       <c r="E569" s="8">
-        <v>0</v>
+        <v>6334853</v>
       </c>
       <c r="F569" s="9">
         <v>3</v>
       </c>
       <c r="G569" s="8">
-        <v>0</v>
+        <v>405805207.2</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.25">
@@ -25736,17 +25736,17 @@
       <c r="C570" s="6">
         <v>46251</v>
       </c>
-      <c r="D570" s="8">
-        <v>0</v>
+      <c r="D570" s="7">
+        <v>63.895793</v>
       </c>
       <c r="E570" s="8">
-        <v>0</v>
+        <v>2316713</v>
       </c>
       <c r="F570" s="9">
         <v>2</v>
       </c>
       <c r="G570" s="8">
-        <v>0</v>
+        <v>148028213.66</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -25759,17 +25759,17 @@
       <c r="C571" s="6">
         <v>46251</v>
       </c>
-      <c r="D571" s="8">
-        <v>0</v>
+      <c r="D571" s="7">
+        <v>64.075762</v>
       </c>
       <c r="E571" s="8">
-        <v>0</v>
+        <v>3663843</v>
       </c>
       <c r="F571" s="9">
         <v>2</v>
       </c>
       <c r="G571" s="8">
-        <v>0</v>
+        <v>234763530.48</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
@@ -25828,17 +25828,17 @@
       <c r="C574" s="6">
         <v>46251</v>
       </c>
-      <c r="D574" s="8">
-        <v>0</v>
+      <c r="D574" s="7">
+        <v>59.810717</v>
       </c>
       <c r="E574" s="8">
-        <v>0</v>
+        <v>9779449</v>
       </c>
       <c r="F574" s="9">
         <v>1</v>
       </c>
       <c r="G574" s="8">
-        <v>0</v>
+        <v>584915859.2</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
@@ -25943,17 +25943,17 @@
       <c r="C579" s="6">
         <v>46251</v>
       </c>
-      <c r="D579" s="8">
-        <v>0</v>
+      <c r="D579" s="7">
+        <v>65.953482</v>
       </c>
       <c r="E579" s="8">
-        <v>0</v>
+        <v>30617607</v>
       </c>
       <c r="F579" s="9">
         <v>2</v>
       </c>
       <c r="G579" s="8">
-        <v>0</v>
+        <v>2019337801.52</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.25">
@@ -26059,7 +26059,7 @@
         <v>46251</v>
       </c>
       <c r="D584" s="7">
-        <v>1489.079526</v>
+        <v>1490.010294</v>
       </c>
       <c r="E584" s="8">
         <v>931444</v>
@@ -26068,7 +26068,7 @@
         <v>926</v>
       </c>
       <c r="G584" s="8">
-        <v>1386994189.73</v>
+        <v>1387861148.36</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.25">
@@ -26150,17 +26150,17 @@
       <c r="C588" s="6">
         <v>46251</v>
       </c>
-      <c r="D588" s="8">
-        <v>0</v>
+      <c r="D588" s="7">
+        <v>68.368979</v>
       </c>
       <c r="E588" s="8">
-        <v>0</v>
+        <v>8202021</v>
       </c>
       <c r="F588" s="9">
         <v>4</v>
       </c>
       <c r="G588" s="8">
-        <v>0</v>
+        <v>560763797.52</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -26403,17 +26403,17 @@
       <c r="C599" s="6">
         <v>46251</v>
       </c>
-      <c r="D599" s="8">
-        <v>0</v>
+      <c r="D599" s="7">
+        <v>62.974642</v>
       </c>
       <c r="E599" s="8">
-        <v>0</v>
+        <v>25599906</v>
       </c>
       <c r="F599" s="9">
         <v>1</v>
       </c>
       <c r="G599" s="8">
-        <v>0</v>
+        <v>1612144908.59</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.25">
@@ -26541,17 +26541,17 @@
       <c r="C605" s="6">
         <v>46251</v>
       </c>
-      <c r="D605" s="8">
-        <v>0</v>
+      <c r="D605" s="7">
+        <v>61.014003</v>
       </c>
       <c r="E605" s="8">
-        <v>0</v>
+        <v>29495736</v>
       </c>
       <c r="F605" s="9">
         <v>4</v>
       </c>
       <c r="G605" s="8">
-        <v>0</v>
+        <v>1799652916.16</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
@@ -26771,17 +26771,17 @@
       <c r="C615" s="6">
         <v>46251</v>
       </c>
-      <c r="D615" s="8">
-        <v>0</v>
+      <c r="D615" s="7">
+        <v>53.982841</v>
       </c>
       <c r="E615" s="8">
-        <v>0</v>
+        <v>7213686</v>
       </c>
       <c r="F615" s="9">
         <v>301</v>
       </c>
       <c r="G615" s="8">
-        <v>0</v>
+        <v>389415267.53</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
@@ -26886,17 +26886,17 @@
       <c r="C620" s="6">
         <v>46251</v>
       </c>
-      <c r="D620" s="8">
-        <v>0</v>
+      <c r="D620" s="7">
+        <v>64.579054</v>
       </c>
       <c r="E620" s="8">
-        <v>0</v>
+        <v>10671178</v>
       </c>
       <c r="F620" s="9">
         <v>453</v>
       </c>
       <c r="G620" s="8">
-        <v>0</v>
+        <v>689134576.43</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
@@ -26932,17 +26932,17 @@
       <c r="C622" s="6">
         <v>46251</v>
       </c>
-      <c r="D622" s="8">
-        <v>0</v>
+      <c r="D622" s="7">
+        <v>12.082482</v>
       </c>
       <c r="E622" s="8">
-        <v>0</v>
+        <v>102639691</v>
       </c>
       <c r="F622" s="9">
         <v>9520</v>
       </c>
       <c r="G622" s="8">
-        <v>0</v>
+        <v>1240142231.44</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
@@ -26955,17 +26955,17 @@
       <c r="C623" s="6">
         <v>46251</v>
       </c>
-      <c r="D623" s="8">
-        <v>0</v>
+      <c r="D623" s="7">
+        <v>72.139688</v>
       </c>
       <c r="E623" s="8">
-        <v>0</v>
+        <v>94192380</v>
       </c>
       <c r="F623" s="9">
         <v>3580</v>
       </c>
       <c r="G623" s="8">
-        <v>0</v>
+        <v>6795008945.43</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
@@ -27024,17 +27024,17 @@
       <c r="C626" s="6">
         <v>46251</v>
       </c>
-      <c r="D626" s="8">
-        <v>0</v>
+      <c r="D626" s="7">
+        <v>45.151531</v>
       </c>
       <c r="E626" s="8">
-        <v>0</v>
+        <v>58637</v>
       </c>
       <c r="F626" s="9">
         <v>1</v>
       </c>
       <c r="G626" s="8">
-        <v>0</v>
+        <v>2647550.3</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
@@ -27047,17 +27047,17 @@
       <c r="C627" s="6">
         <v>46251</v>
       </c>
-      <c r="D627" s="8">
-        <v>0</v>
+      <c r="D627" s="7">
+        <v>18.494726</v>
       </c>
       <c r="E627" s="8">
-        <v>0</v>
+        <v>40163278</v>
       </c>
       <c r="F627" s="9">
         <v>2813</v>
       </c>
       <c r="G627" s="8">
-        <v>0</v>
+        <v>742808827.07</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
@@ -27070,17 +27070,17 @@
       <c r="C628" s="6">
         <v>46251</v>
       </c>
-      <c r="D628" s="8">
-        <v>0</v>
+      <c r="D628" s="7">
+        <v>57.915022</v>
       </c>
       <c r="E628" s="8">
-        <v>0</v>
+        <v>14772170</v>
       </c>
       <c r="F628" s="9">
         <v>2</v>
       </c>
       <c r="G628" s="8">
-        <v>0</v>
+        <v>855530551.81</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
@@ -27116,17 +27116,17 @@
       <c r="C630" s="6">
         <v>46251</v>
       </c>
-      <c r="D630" s="8">
-        <v>0</v>
+      <c r="D630" s="7">
+        <v>62.002445</v>
       </c>
       <c r="E630" s="8">
-        <v>0</v>
+        <v>20837078</v>
       </c>
       <c r="F630" s="9">
         <v>2</v>
       </c>
       <c r="G630" s="8">
-        <v>0</v>
+        <v>1291949783.54</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -27185,17 +27185,17 @@
       <c r="C633" s="6">
         <v>46251</v>
       </c>
-      <c r="D633" s="8">
-        <v>0</v>
+      <c r="D633" s="7">
+        <v>21.139272</v>
       </c>
       <c r="E633" s="8">
-        <v>0</v>
+        <v>16787250</v>
       </c>
       <c r="F633" s="9">
         <v>2453</v>
       </c>
       <c r="G633" s="8">
-        <v>0</v>
+        <v>354870236.09</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
@@ -27392,17 +27392,17 @@
       <c r="C642" s="6">
         <v>46251</v>
       </c>
-      <c r="D642" s="8">
-        <v>0</v>
+      <c r="D642" s="10">
+        <v>15.24241</v>
       </c>
       <c r="E642" s="8">
-        <v>0</v>
+        <v>22904394</v>
       </c>
       <c r="F642" s="9">
         <v>5</v>
       </c>
       <c r="G642" s="8">
-        <v>0</v>
+        <v>349118161.32</v>
       </c>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.25">
@@ -27438,17 +27438,17 @@
       <c r="C644" s="6">
         <v>46251</v>
       </c>
-      <c r="D644" s="8">
-        <v>0</v>
+      <c r="D644" s="7">
+        <v>57.067411</v>
       </c>
       <c r="E644" s="8">
-        <v>0</v>
+        <v>4643160</v>
       </c>
       <c r="F644" s="9">
         <v>2</v>
       </c>
       <c r="G644" s="8">
-        <v>0</v>
+        <v>264973122.26</v>
       </c>
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.25">
@@ -27553,17 +27553,17 @@
       <c r="C649" s="6">
         <v>46251</v>
       </c>
-      <c r="D649" s="8">
-        <v>0</v>
+      <c r="D649" s="7">
+        <v>6.983099</v>
       </c>
       <c r="E649" s="8">
-        <v>0</v>
+        <v>4029467144</v>
       </c>
       <c r="F649" s="9">
         <v>1</v>
       </c>
       <c r="G649" s="8">
-        <v>0</v>
+        <v>28138169927.83</v>
       </c>
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.25">
@@ -27622,17 +27622,17 @@
       <c r="C652" s="6">
         <v>46251</v>
       </c>
-      <c r="D652" s="8">
-        <v>0</v>
+      <c r="D652" s="7">
+        <v>52.202957</v>
       </c>
       <c r="E652" s="8">
-        <v>0</v>
+        <v>28012535</v>
       </c>
       <c r="F652" s="9">
         <v>2</v>
       </c>
       <c r="G652" s="8">
-        <v>0</v>
+        <v>1462337166.18</v>
       </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
@@ -27645,17 +27645,17 @@
       <c r="C653" s="6">
         <v>46251</v>
       </c>
-      <c r="D653" s="8">
-        <v>0</v>
+      <c r="D653" s="7">
+        <v>6.440643</v>
       </c>
       <c r="E653" s="8">
-        <v>0</v>
+        <v>64668747</v>
       </c>
       <c r="F653" s="9">
         <v>537</v>
       </c>
       <c r="G653" s="8">
-        <v>0</v>
+        <v>416508310.63</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
@@ -27668,17 +27668,17 @@
       <c r="C654" s="6">
         <v>46251</v>
       </c>
-      <c r="D654" s="8">
-        <v>0</v>
+      <c r="D654" s="7">
+        <v>11.712433</v>
       </c>
       <c r="E654" s="8">
-        <v>0</v>
+        <v>1085763583</v>
       </c>
       <c r="F654" s="9">
         <v>62367</v>
       </c>
       <c r="G654" s="8">
-        <v>0</v>
+        <v>12716933741.45</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
@@ -27691,17 +27691,17 @@
       <c r="C655" s="6">
         <v>46251</v>
       </c>
-      <c r="D655" s="8">
-        <v>0</v>
+      <c r="D655" s="7">
+        <v>5.961691</v>
       </c>
       <c r="E655" s="8">
-        <v>0</v>
+        <v>341860798</v>
       </c>
       <c r="F655" s="9">
         <v>1</v>
       </c>
       <c r="G655" s="8">
-        <v>0</v>
+        <v>2038068507.74</v>
       </c>
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.25">
@@ -27783,17 +27783,17 @@
       <c r="C659" s="6">
         <v>46251</v>
       </c>
-      <c r="D659" s="8">
-        <v>0</v>
+      <c r="D659" s="7">
+        <v>0.468103</v>
       </c>
       <c r="E659" s="8">
-        <v>0</v>
+        <v>10251819576</v>
       </c>
       <c r="F659" s="9">
         <v>38231</v>
       </c>
       <c r="G659" s="8">
-        <v>0</v>
+        <v>4798911948.04</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
@@ -27806,17 +27806,17 @@
       <c r="C660" s="6">
         <v>46251</v>
       </c>
-      <c r="D660" s="8">
-        <v>0</v>
+      <c r="D660" s="7">
+        <v>1.410547</v>
       </c>
       <c r="E660" s="8">
-        <v>0</v>
+        <v>803261909</v>
       </c>
       <c r="F660" s="9">
         <v>2716</v>
       </c>
       <c r="G660" s="8">
-        <v>0</v>
+        <v>1133038871.18</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.25">
@@ -27875,17 +27875,17 @@
       <c r="C663" s="6">
         <v>46251</v>
       </c>
-      <c r="D663" s="8">
-        <v>0</v>
+      <c r="D663" s="7">
+        <v>4.209894</v>
       </c>
       <c r="E663" s="8">
-        <v>0</v>
+        <v>23677414</v>
       </c>
       <c r="F663" s="9">
         <v>3471</v>
       </c>
       <c r="G663" s="8">
-        <v>0</v>
+        <v>99679401.69</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -27898,17 +27898,17 @@
       <c r="C664" s="6">
         <v>46251</v>
       </c>
-      <c r="D664" s="8">
-        <v>0</v>
+      <c r="D664" s="7">
+        <v>67.657525</v>
       </c>
       <c r="E664" s="8">
-        <v>0</v>
+        <v>52499640</v>
       </c>
       <c r="F664" s="9">
         <v>3</v>
       </c>
       <c r="G664" s="8">
-        <v>0</v>
+        <v>3551995698.14</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
@@ -27921,17 +27921,17 @@
       <c r="C665" s="6">
         <v>46251</v>
       </c>
-      <c r="D665" s="8">
-        <v>0</v>
+      <c r="D665" s="7">
+        <v>64.290888</v>
       </c>
       <c r="E665" s="8">
-        <v>0</v>
+        <v>4739268</v>
       </c>
       <c r="F665" s="9">
         <v>1</v>
       </c>
       <c r="G665" s="8">
-        <v>0</v>
+        <v>304691746.98</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
@@ -27944,17 +27944,17 @@
       <c r="C666" s="6">
         <v>46251</v>
       </c>
-      <c r="D666" s="8">
-        <v>0</v>
+      <c r="D666" s="10">
+        <v>18.48054</v>
       </c>
       <c r="E666" s="8">
-        <v>0</v>
+        <v>22115</v>
       </c>
       <c r="F666" s="9">
         <v>1</v>
       </c>
       <c r="G666" s="8">
-        <v>0</v>
+        <v>408697.15</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
@@ -27967,17 +27967,17 @@
       <c r="C667" s="6">
         <v>46251</v>
       </c>
-      <c r="D667" s="8">
-        <v>0</v>
+      <c r="D667" s="10">
+        <v>5.62272</v>
       </c>
       <c r="E667" s="8">
-        <v>0</v>
+        <v>211914620</v>
       </c>
       <c r="F667" s="9">
         <v>4627</v>
       </c>
       <c r="G667" s="8">
-        <v>0</v>
+        <v>1191536480.29</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -27990,17 +27990,17 @@
       <c r="C668" s="6">
         <v>46251</v>
       </c>
-      <c r="D668" s="8">
-        <v>0</v>
+      <c r="D668" s="7">
+        <v>66.451667</v>
       </c>
       <c r="E668" s="8">
-        <v>0</v>
+        <v>7872114</v>
       </c>
       <c r="F668" s="9">
         <v>3</v>
       </c>
       <c r="G668" s="8">
-        <v>0</v>
+        <v>523115101.61</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -28013,17 +28013,17 @@
       <c r="C669" s="6">
         <v>46251</v>
       </c>
-      <c r="D669" s="8">
-        <v>0</v>
+      <c r="D669" s="7">
+        <v>72.978728</v>
       </c>
       <c r="E669" s="8">
-        <v>0</v>
+        <v>5533354</v>
       </c>
       <c r="F669" s="9">
         <v>2</v>
       </c>
       <c r="G669" s="8">
-        <v>0</v>
+        <v>403817134.57</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
@@ -28036,17 +28036,17 @@
       <c r="C670" s="6">
         <v>46251</v>
       </c>
-      <c r="D670" s="8">
-        <v>0</v>
+      <c r="D670" s="7">
+        <v>4.069835</v>
       </c>
       <c r="E670" s="8">
-        <v>0</v>
+        <v>5020082762</v>
       </c>
       <c r="F670" s="9">
         <v>1</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>20430907513.8</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -28059,17 +28059,17 @@
       <c r="C671" s="6">
         <v>46251</v>
       </c>
-      <c r="D671" s="8">
-        <v>0</v>
+      <c r="D671" s="7">
+        <v>71.121612</v>
       </c>
       <c r="E671" s="8">
-        <v>0</v>
+        <v>7093936</v>
       </c>
       <c r="F671" s="9">
         <v>4</v>
       </c>
       <c r="G671" s="8">
-        <v>0</v>
+        <v>504532167.08</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
@@ -28128,17 +28128,17 @@
       <c r="C674" s="6">
         <v>46251</v>
       </c>
-      <c r="D674" s="8">
-        <v>0</v>
+      <c r="D674" s="10">
+        <v>68.69537</v>
       </c>
       <c r="E674" s="8">
-        <v>0</v>
+        <v>20613565</v>
       </c>
       <c r="F674" s="9">
         <v>1</v>
       </c>
       <c r="G674" s="8">
-        <v>0</v>
+        <v>1416056467.16</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -28151,17 +28151,17 @@
       <c r="C675" s="6">
         <v>46251</v>
       </c>
-      <c r="D675" s="8">
-        <v>0</v>
+      <c r="D675" s="7">
+        <v>63.220653</v>
       </c>
       <c r="E675" s="8">
-        <v>0</v>
+        <v>9491810</v>
       </c>
       <c r="F675" s="9">
         <v>5</v>
       </c>
       <c r="G675" s="8">
-        <v>0</v>
+        <v>600078428.44</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
@@ -28174,17 +28174,17 @@
       <c r="C676" s="6">
         <v>46251</v>
       </c>
-      <c r="D676" s="8">
-        <v>0</v>
+      <c r="D676" s="7">
+        <v>7.426892</v>
       </c>
       <c r="E676" s="8">
-        <v>0</v>
+        <v>190000000</v>
       </c>
       <c r="F676" s="9">
         <v>1</v>
       </c>
       <c r="G676" s="8">
-        <v>0</v>
+        <v>1411109569.68</v>
       </c>
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.25">
@@ -28197,17 +28197,17 @@
       <c r="C677" s="6">
         <v>46251</v>
       </c>
-      <c r="D677" s="8">
-        <v>0</v>
+      <c r="D677" s="7">
+        <v>61.710002</v>
       </c>
       <c r="E677" s="8">
-        <v>0</v>
+        <v>876698</v>
       </c>
       <c r="F677" s="9">
         <v>3</v>
       </c>
       <c r="G677" s="8">
-        <v>0</v>
+        <v>54101035.71</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
@@ -28220,17 +28220,17 @@
       <c r="C678" s="6">
         <v>46251</v>
       </c>
-      <c r="D678" s="8">
-        <v>0</v>
+      <c r="D678" s="7">
+        <v>7.565891</v>
       </c>
       <c r="E678" s="8">
-        <v>0</v>
+        <v>187192844</v>
       </c>
       <c r="F678" s="9">
         <v>4165</v>
       </c>
       <c r="G678" s="8">
-        <v>0</v>
+        <v>1416280637.05</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
@@ -28243,17 +28243,17 @@
       <c r="C679" s="6">
         <v>46251</v>
       </c>
-      <c r="D679" s="8">
-        <v>0</v>
+      <c r="D679" s="7">
+        <v>7.318717</v>
       </c>
       <c r="E679" s="8">
-        <v>0</v>
+        <v>61129370</v>
       </c>
       <c r="F679" s="9">
         <v>4101</v>
       </c>
       <c r="G679" s="8">
-        <v>0</v>
+        <v>447388584.43</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
@@ -28266,17 +28266,17 @@
       <c r="C680" s="6">
         <v>46251</v>
       </c>
-      <c r="D680" s="8">
-        <v>0</v>
+      <c r="D680" s="7">
+        <v>5.005118</v>
       </c>
       <c r="E680" s="8">
-        <v>0</v>
+        <v>80179659</v>
       </c>
       <c r="F680" s="9">
         <v>5824</v>
       </c>
       <c r="G680" s="8">
-        <v>0</v>
+        <v>401308659.49</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -28312,17 +28312,17 @@
       <c r="C682" s="6">
         <v>46251</v>
       </c>
-      <c r="D682" s="8">
-        <v>0</v>
+      <c r="D682" s="7">
+        <v>5.589052</v>
       </c>
       <c r="E682" s="8">
-        <v>0</v>
+        <v>64948334</v>
       </c>
       <c r="F682" s="9">
         <v>6080</v>
       </c>
       <c r="G682" s="8">
-        <v>0</v>
+        <v>362999589.87</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
@@ -28381,17 +28381,17 @@
       <c r="C685" s="6">
         <v>46251</v>
       </c>
-      <c r="D685" s="8">
-        <v>0</v>
+      <c r="D685" s="7">
+        <v>69.496607</v>
       </c>
       <c r="E685" s="8">
-        <v>0</v>
+        <v>1210798</v>
       </c>
       <c r="F685" s="9">
         <v>1</v>
       </c>
       <c r="G685" s="8">
-        <v>0</v>
+        <v>84146353.14</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
@@ -28404,17 +28404,17 @@
       <c r="C686" s="6">
         <v>46251</v>
       </c>
-      <c r="D686" s="8">
-        <v>0</v>
+      <c r="D686" s="7">
+        <v>7.667841</v>
       </c>
       <c r="E686" s="8">
-        <v>0</v>
+        <v>495954942</v>
       </c>
       <c r="F686" s="9">
         <v>9890</v>
       </c>
       <c r="G686" s="8">
-        <v>0</v>
+        <v>3802903712.1</v>
       </c>
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.25">
@@ -28450,17 +28450,17 @@
       <c r="C688" s="6">
         <v>46251</v>
       </c>
-      <c r="D688" s="8">
-        <v>0</v>
+      <c r="D688" s="7">
+        <v>67.531475</v>
       </c>
       <c r="E688" s="8">
-        <v>0</v>
+        <v>6829649</v>
       </c>
       <c r="F688" s="9">
         <v>2</v>
       </c>
       <c r="G688" s="8">
-        <v>0</v>
+        <v>461216272.18</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
@@ -28473,17 +28473,17 @@
       <c r="C689" s="6">
         <v>46251</v>
       </c>
-      <c r="D689" s="8">
-        <v>0</v>
+      <c r="D689" s="7">
+        <v>8.801652</v>
       </c>
       <c r="E689" s="8">
-        <v>0</v>
+        <v>11390666</v>
       </c>
       <c r="F689" s="9">
         <v>1377</v>
       </c>
       <c r="G689" s="8">
-        <v>0</v>
+        <v>100256677.41</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
@@ -28496,17 +28496,17 @@
       <c r="C690" s="6">
         <v>46251</v>
       </c>
-      <c r="D690" s="8">
-        <v>0</v>
+      <c r="D690" s="7">
+        <v>8.018364</v>
       </c>
       <c r="E690" s="8">
-        <v>0</v>
+        <v>9291870</v>
       </c>
       <c r="F690" s="9">
         <v>2413</v>
       </c>
       <c r="G690" s="8">
-        <v>0</v>
+        <v>74505591.43</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.25">
@@ -28635,7 +28635,7 @@
         <v>46251</v>
       </c>
       <c r="D696" s="7">
-        <v>1.106777</v>
+        <v>1.100035</v>
       </c>
       <c r="E696" s="8">
         <v>36682987</v>
@@ -28644,7 +28644,7 @@
         <v>67</v>
       </c>
       <c r="G696" s="8">
-        <v>40599882.82</v>
+        <v>40352567.56</v>
       </c>
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.25">
@@ -28772,17 +28772,17 @@
       <c r="C702" s="6">
         <v>46251</v>
       </c>
-      <c r="D702" s="8">
-        <v>0</v>
+      <c r="D702" s="7">
+        <v>4.325004</v>
       </c>
       <c r="E702" s="8">
-        <v>0</v>
+        <v>127536848</v>
       </c>
       <c r="F702" s="9">
         <v>1091</v>
       </c>
       <c r="G702" s="8">
-        <v>0</v>
+        <v>551597404.96</v>
       </c>
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.25">
@@ -30107,7 +30107,7 @@
         <v>46251</v>
       </c>
       <c r="D760" s="7">
-        <v>0.368899</v>
+        <v>0.368864</v>
       </c>
       <c r="E760" s="8">
         <v>3758844322</v>
@@ -30116,7 +30116,7 @@
         <v>2555</v>
       </c>
       <c r="G760" s="8">
-        <v>1386634979.72</v>
+        <v>1386503240.83</v>
       </c>
     </row>
     <row r="761" spans="1:7" x14ac:dyDescent="0.25">
@@ -30567,7 +30567,7 @@
         <v>46251</v>
       </c>
       <c r="D780" s="7">
-        <v>1.102689</v>
+        <v>1.104515</v>
       </c>
       <c r="E780" s="8">
         <v>123150867</v>
@@ -30576,7 +30576,7 @@
         <v>829</v>
       </c>
       <c r="G780" s="8">
-        <v>135797098.07</v>
+        <v>136021964.33</v>
       </c>
     </row>
     <row r="781" spans="1:7" x14ac:dyDescent="0.25">
@@ -31279,8 +31279,8 @@
       <c r="C811" s="6">
         <v>46251</v>
       </c>
-      <c r="D811" s="7">
-        <v>2.623834</v>
+      <c r="D811" s="12">
+        <v>2.642</v>
       </c>
       <c r="E811" s="8">
         <v>12868452</v>
@@ -31289,7 +31289,7 @@
         <v>224</v>
       </c>
       <c r="G811" s="8">
-        <v>33764677.8</v>
+        <v>33998447.98</v>
       </c>
     </row>
     <row r="812" spans="1:7" x14ac:dyDescent="0.25">
@@ -33441,17 +33441,17 @@
       <c r="C905" s="6">
         <v>46251</v>
       </c>
-      <c r="D905" s="8">
-        <v>0</v>
+      <c r="D905" s="7">
+        <v>14.820358</v>
       </c>
       <c r="E905" s="8">
-        <v>0</v>
+        <v>15453482</v>
       </c>
       <c r="F905" s="9">
         <v>375</v>
       </c>
       <c r="G905" s="8">
-        <v>0</v>
+        <v>229026135.02</v>
       </c>
     </row>
     <row r="906" spans="1:7" x14ac:dyDescent="0.25">
@@ -33833,7 +33833,7 @@
         <v>46251</v>
       </c>
       <c r="D922" s="7">
-        <v>0.122558</v>
+        <v>0.122569</v>
       </c>
       <c r="E922" s="8">
         <v>1105011730</v>
@@ -33842,7 +33842,7 @@
         <v>22</v>
       </c>
       <c r="G922" s="8">
-        <v>135427747.21</v>
+        <v>135440185.86</v>
       </c>
     </row>
     <row r="923" spans="1:7" x14ac:dyDescent="0.25">
@@ -33948,7 +33948,7 @@
         <v>46251</v>
       </c>
       <c r="D927" s="7">
-        <v>0.180254</v>
+        <v>0.180261</v>
       </c>
       <c r="E927" s="8">
         <v>40206676514</v>
@@ -33957,7 +33957,7 @@
         <v>166</v>
       </c>
       <c r="G927" s="8">
-        <v>7247410363.45</v>
+        <v>7247684266.53</v>
       </c>
     </row>
     <row r="928" spans="1:7" x14ac:dyDescent="0.25">
@@ -34039,17 +34039,17 @@
       <c r="C931" s="6">
         <v>46251</v>
       </c>
-      <c r="D931" s="8">
-        <v>0</v>
+      <c r="D931" s="7">
+        <v>1.310796</v>
       </c>
       <c r="E931" s="8">
-        <v>0</v>
+        <v>892900152</v>
       </c>
       <c r="F931" s="9">
         <v>788</v>
       </c>
       <c r="G931" s="8">
-        <v>0</v>
+        <v>1170409769.08</v>
       </c>
     </row>
     <row r="932" spans="1:7" x14ac:dyDescent="0.25">
@@ -35235,17 +35235,17 @@
       <c r="C983" s="6">
         <v>46251</v>
       </c>
-      <c r="D983" s="8">
-        <v>0</v>
+      <c r="D983" s="7">
+        <v>6797.511458</v>
       </c>
       <c r="E983" s="8">
-        <v>0</v>
+        <v>784807</v>
       </c>
       <c r="F983" s="9">
         <v>37</v>
       </c>
       <c r="G983" s="8">
-        <v>0</v>
+        <v>5334734574.63</v>
       </c>
     </row>
     <row r="984" spans="1:7" x14ac:dyDescent="0.25">
@@ -35258,17 +35258,17 @@
       <c r="C984" s="6">
         <v>46251</v>
       </c>
-      <c r="D984" s="8">
-        <v>0</v>
+      <c r="D984" s="7">
+        <v>57.211475</v>
       </c>
       <c r="E984" s="8">
-        <v>0</v>
+        <v>317829329</v>
       </c>
       <c r="F984" s="9">
         <v>5726</v>
       </c>
       <c r="G984" s="8">
-        <v>0</v>
+        <v>18183484751.76</v>
       </c>
     </row>
     <row r="985" spans="1:7" x14ac:dyDescent="0.25">
@@ -35304,17 +35304,17 @@
       <c r="C986" s="6">
         <v>46251</v>
       </c>
-      <c r="D986" s="8">
-        <v>0</v>
+      <c r="D986" s="7">
+        <v>1.715066</v>
       </c>
       <c r="E986" s="8">
-        <v>0</v>
+        <v>189321082</v>
       </c>
       <c r="F986" s="9">
         <v>5</v>
       </c>
       <c r="G986" s="8">
-        <v>0</v>
+        <v>324698207.52</v>
       </c>
     </row>
     <row r="987" spans="1:7" x14ac:dyDescent="0.25">
@@ -35327,17 +35327,17 @@
       <c r="C987" s="6">
         <v>46251</v>
       </c>
-      <c r="D987" s="8">
-        <v>0</v>
+      <c r="D987" s="7">
+        <v>51.861609</v>
       </c>
       <c r="E987" s="8">
-        <v>0</v>
+        <v>3094492</v>
       </c>
       <c r="F987" s="9">
         <v>1</v>
       </c>
       <c r="G987" s="8">
-        <v>0</v>
+        <v>160485334.22</v>
       </c>
     </row>
     <row r="988" spans="1:7" x14ac:dyDescent="0.25">
@@ -35396,17 +35396,17 @@
       <c r="C990" s="6">
         <v>46251</v>
       </c>
-      <c r="D990" s="8">
-        <v>0</v>
+      <c r="D990" s="7">
+        <v>5.185393</v>
       </c>
       <c r="E990" s="8">
-        <v>0</v>
+        <v>480359962</v>
       </c>
       <c r="F990" s="9">
         <v>12774</v>
       </c>
       <c r="G990" s="8">
-        <v>0</v>
+        <v>2490854957.49</v>
       </c>
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.25">
@@ -35419,17 +35419,17 @@
       <c r="C991" s="6">
         <v>46251</v>
       </c>
-      <c r="D991" s="8">
-        <v>0</v>
+      <c r="D991" s="7">
+        <v>1.763941</v>
       </c>
       <c r="E991" s="8">
-        <v>0</v>
+        <v>341642605</v>
       </c>
       <c r="F991" s="9">
         <v>3400</v>
       </c>
       <c r="G991" s="8">
-        <v>0</v>
+        <v>602637385.09</v>
       </c>
     </row>
     <row r="992" spans="1:7" x14ac:dyDescent="0.25">
@@ -35465,17 +35465,17 @@
       <c r="C993" s="6">
         <v>46251</v>
       </c>
-      <c r="D993" s="8">
-        <v>0</v>
+      <c r="D993" s="7">
+        <v>15.489338</v>
       </c>
       <c r="E993" s="8">
-        <v>0</v>
+        <v>3147787</v>
       </c>
       <c r="F993" s="9">
         <v>1</v>
       </c>
       <c r="G993" s="8">
-        <v>0</v>
+        <v>48757136.04</v>
       </c>
     </row>
     <row r="994" spans="1:7" x14ac:dyDescent="0.25">
@@ -35488,17 +35488,17 @@
       <c r="C994" s="6">
         <v>46251</v>
       </c>
-      <c r="D994" s="8">
-        <v>0</v>
+      <c r="D994" s="7">
+        <v>52.422828</v>
       </c>
       <c r="E994" s="8">
-        <v>0</v>
+        <v>487820842</v>
       </c>
       <c r="F994" s="9">
         <v>7061</v>
       </c>
       <c r="G994" s="8">
-        <v>0</v>
+        <v>25572947883.3</v>
       </c>
     </row>
     <row r="995" spans="1:7" x14ac:dyDescent="0.25">
@@ -35534,17 +35534,17 @@
       <c r="C996" s="6">
         <v>46251</v>
       </c>
-      <c r="D996" s="8">
-        <v>0</v>
+      <c r="D996" s="7">
+        <v>54.437843</v>
       </c>
       <c r="E996" s="8">
-        <v>0</v>
+        <v>521385066</v>
       </c>
       <c r="F996" s="9">
         <v>1379</v>
       </c>
       <c r="G996" s="8">
-        <v>0</v>
+        <v>28383078485.79</v>
       </c>
     </row>
     <row r="997" spans="1:7" x14ac:dyDescent="0.25">
@@ -35580,17 +35580,17 @@
       <c r="C998" s="6">
         <v>46251</v>
       </c>
-      <c r="D998" s="8">
-        <v>0</v>
+      <c r="D998" s="7">
+        <v>48.651446</v>
       </c>
       <c r="E998" s="8">
-        <v>0</v>
+        <v>469986316</v>
       </c>
       <c r="F998" s="9">
         <v>203</v>
       </c>
       <c r="G998" s="8">
-        <v>0</v>
+        <v>22865514103</v>
       </c>
     </row>
     <row r="999" spans="1:7" x14ac:dyDescent="0.25">
@@ -35603,17 +35603,17 @@
       <c r="C999" s="6">
         <v>46251</v>
       </c>
-      <c r="D999" s="8">
-        <v>0</v>
+      <c r="D999" s="7">
+        <v>48.846138</v>
       </c>
       <c r="E999" s="8">
-        <v>0</v>
+        <v>89738206</v>
       </c>
       <c r="F999" s="9">
         <v>826</v>
       </c>
       <c r="G999" s="8">
-        <v>0</v>
+        <v>4383364829.66</v>
       </c>
     </row>
     <row r="1000" spans="1:7" x14ac:dyDescent="0.25">
@@ -35626,17 +35626,17 @@
       <c r="C1000" s="6">
         <v>46251</v>
       </c>
-      <c r="D1000" s="8">
-        <v>0</v>
+      <c r="D1000" s="7">
+        <v>1.853146</v>
       </c>
       <c r="E1000" s="8">
-        <v>0</v>
+        <v>179618321</v>
       </c>
       <c r="F1000" s="9">
         <v>1</v>
       </c>
       <c r="G1000" s="8">
-        <v>0</v>
+        <v>332859034.64</v>
       </c>
     </row>
     <row r="1001" spans="1:7" x14ac:dyDescent="0.25">
@@ -35649,17 +35649,17 @@
       <c r="C1001" s="6">
         <v>46251</v>
       </c>
-      <c r="D1001" s="8">
-        <v>0</v>
+      <c r="D1001" s="7">
+        <v>1.796656</v>
       </c>
       <c r="E1001" s="8">
-        <v>0</v>
+        <v>39442409</v>
       </c>
       <c r="F1001" s="9">
         <v>1</v>
       </c>
       <c r="G1001" s="8">
-        <v>0</v>
+        <v>70864440.71</v>
       </c>
     </row>
     <row r="1002" spans="1:7" x14ac:dyDescent="0.25">
@@ -35672,17 +35672,17 @@
       <c r="C1002" s="6">
         <v>46251</v>
       </c>
-      <c r="D1002" s="8">
-        <v>0</v>
+      <c r="D1002" s="10">
+        <v>52.83114</v>
       </c>
       <c r="E1002" s="8">
-        <v>0</v>
+        <v>80232138</v>
       </c>
       <c r="F1002" s="9">
         <v>55</v>
       </c>
       <c r="G1002" s="8">
-        <v>0</v>
+        <v>4238755331.9</v>
       </c>
     </row>
     <row r="1003" spans="1:7" x14ac:dyDescent="0.25">
@@ -35695,17 +35695,17 @@
       <c r="C1003" s="6">
         <v>46251</v>
       </c>
-      <c r="D1003" s="8">
-        <v>0</v>
+      <c r="D1003" s="7">
+        <v>4.453191</v>
       </c>
       <c r="E1003" s="8">
-        <v>0</v>
+        <v>82683881</v>
       </c>
       <c r="F1003" s="9">
         <v>1</v>
       </c>
       <c r="G1003" s="8">
-        <v>0</v>
+        <v>368207095.63</v>
       </c>
     </row>
     <row r="1004" spans="1:7" x14ac:dyDescent="0.25">
@@ -35718,17 +35718,17 @@
       <c r="C1004" s="6">
         <v>46251</v>
       </c>
-      <c r="D1004" s="8">
-        <v>0</v>
+      <c r="D1004" s="7">
+        <v>2.940153</v>
       </c>
       <c r="E1004" s="8">
-        <v>0</v>
+        <v>1021488048</v>
       </c>
       <c r="F1004" s="9">
         <v>29399</v>
       </c>
       <c r="G1004" s="8">
-        <v>0</v>
+        <v>3003330770.59</v>
       </c>
     </row>
     <row r="1005" spans="1:7" x14ac:dyDescent="0.25">
@@ -35902,17 +35902,17 @@
       <c r="C1012" s="6">
         <v>46251</v>
       </c>
-      <c r="D1012" s="8">
-        <v>0</v>
+      <c r="D1012" s="7">
+        <v>1.191368</v>
       </c>
       <c r="E1012" s="8">
-        <v>0</v>
+        <v>24534316374</v>
       </c>
       <c r="F1012" s="9">
         <v>1553</v>
       </c>
       <c r="G1012" s="8">
-        <v>0</v>
+        <v>29229408717.17</v>
       </c>
     </row>
     <row r="1013" spans="1:7" x14ac:dyDescent="0.25">
@@ -35948,17 +35948,17 @@
       <c r="C1014" s="6">
         <v>46251</v>
       </c>
-      <c r="D1014" s="8">
-        <v>0</v>
+      <c r="D1014" s="7">
+        <v>36.441448</v>
       </c>
       <c r="E1014" s="8">
-        <v>0</v>
+        <v>95518</v>
       </c>
       <c r="F1014" s="9">
         <v>1</v>
       </c>
       <c r="G1014" s="8">
-        <v>0</v>
+        <v>3480814.26</v>
       </c>
     </row>
     <row r="1015" spans="1:7" x14ac:dyDescent="0.25">
@@ -36063,17 +36063,17 @@
       <c r="C1019" s="6">
         <v>46251</v>
       </c>
-      <c r="D1019" s="8">
-        <v>0</v>
+      <c r="D1019" s="7">
+        <v>1.476053</v>
       </c>
       <c r="E1019" s="8">
-        <v>0</v>
+        <v>116593110</v>
       </c>
       <c r="F1019" s="9">
         <v>1403</v>
       </c>
       <c r="G1019" s="8">
-        <v>0</v>
+        <v>172097632.27</v>
       </c>
     </row>
     <row r="1020" spans="1:7" x14ac:dyDescent="0.25">
@@ -36109,17 +36109,17 @@
       <c r="C1021" s="6">
         <v>46251</v>
       </c>
-      <c r="D1021" s="8">
-        <v>0</v>
+      <c r="D1021" s="7">
+        <v>0.002259</v>
       </c>
       <c r="E1021" s="8">
-        <v>0</v>
+        <v>21405755952</v>
       </c>
       <c r="F1021" s="9">
         <v>1</v>
       </c>
       <c r="G1021" s="8">
-        <v>0</v>
+        <v>48359323.79</v>
       </c>
     </row>
     <row r="1022" spans="1:7" x14ac:dyDescent="0.25">
@@ -36132,17 +36132,17 @@
       <c r="C1022" s="6">
         <v>46251</v>
       </c>
-      <c r="D1022" s="8">
-        <v>0</v>
+      <c r="D1022" s="7">
+        <v>62.070441</v>
       </c>
       <c r="E1022" s="8">
-        <v>0</v>
+        <v>41940</v>
       </c>
       <c r="F1022" s="9">
         <v>1</v>
       </c>
       <c r="G1022" s="8">
-        <v>0</v>
+        <v>2603234.28</v>
       </c>
     </row>
     <row r="1023" spans="1:7" x14ac:dyDescent="0.25">
@@ -36178,17 +36178,17 @@
       <c r="C1024" s="6">
         <v>46251</v>
       </c>
-      <c r="D1024" s="8">
-        <v>0</v>
+      <c r="D1024" s="7">
+        <v>51.820994</v>
       </c>
       <c r="E1024" s="8">
-        <v>0</v>
+        <v>1726780</v>
       </c>
       <c r="F1024" s="9">
         <v>2</v>
       </c>
       <c r="G1024" s="8">
-        <v>0</v>
+        <v>89483455.95</v>
       </c>
     </row>
     <row r="1025" spans="1:7" x14ac:dyDescent="0.25">
@@ -36224,8 +36224,8 @@
       <c r="C1026" s="6">
         <v>46251</v>
       </c>
-      <c r="D1026" s="10">
-        <v>2.47825</v>
+      <c r="D1026" s="7">
+        <v>2.478255</v>
       </c>
       <c r="E1026" s="8">
         <v>1424253757</v>
@@ -36234,7 +36234,7 @@
         <v>1660</v>
       </c>
       <c r="G1026" s="8">
-        <v>3529656177.23</v>
+        <v>3529663731.45</v>
       </c>
     </row>
     <row r="1027" spans="1:7" x14ac:dyDescent="0.25">
@@ -36293,17 +36293,17 @@
       <c r="C1029" s="6">
         <v>46251</v>
       </c>
-      <c r="D1029" s="8">
-        <v>0</v>
+      <c r="D1029" s="7">
+        <v>3.111463</v>
       </c>
       <c r="E1029" s="8">
-        <v>0</v>
+        <v>2941745961</v>
       </c>
       <c r="F1029" s="9">
         <v>46</v>
       </c>
       <c r="G1029" s="8">
-        <v>0</v>
+        <v>9153134009.6</v>
       </c>
     </row>
     <row r="1030" spans="1:7" x14ac:dyDescent="0.25">
@@ -36362,17 +36362,17 @@
       <c r="C1032" s="6">
         <v>46251</v>
       </c>
-      <c r="D1032" s="8">
-        <v>0</v>
+      <c r="D1032" s="7">
+        <v>57.704279</v>
       </c>
       <c r="E1032" s="8">
-        <v>0</v>
+        <v>196370</v>
       </c>
       <c r="F1032" s="9">
         <v>1</v>
       </c>
       <c r="G1032" s="8">
-        <v>0</v>
+        <v>11331389.34</v>
       </c>
     </row>
     <row r="1033" spans="1:7" x14ac:dyDescent="0.25">
@@ -36431,17 +36431,17 @@
       <c r="C1035" s="6">
         <v>46251</v>
       </c>
-      <c r="D1035" s="8">
-        <v>0</v>
+      <c r="D1035" s="7">
+        <v>4.818191</v>
       </c>
       <c r="E1035" s="8">
-        <v>0</v>
+        <v>19966858952</v>
       </c>
       <c r="F1035" s="9">
         <v>105192</v>
       </c>
       <c r="G1035" s="8">
-        <v>0</v>
+        <v>96204139826.11</v>
       </c>
     </row>
     <row r="1036" spans="1:7" x14ac:dyDescent="0.25">
@@ -36454,17 +36454,17 @@
       <c r="C1036" s="6">
         <v>46251</v>
       </c>
-      <c r="D1036" s="8">
-        <v>0</v>
+      <c r="D1036" s="7">
+        <v>168.428568</v>
       </c>
       <c r="E1036" s="8">
-        <v>0</v>
+        <v>74818</v>
       </c>
       <c r="F1036" s="9">
         <v>1</v>
       </c>
       <c r="G1036" s="8">
-        <v>0</v>
+        <v>12601488.62</v>
       </c>
     </row>
     <row r="1037" spans="1:7" x14ac:dyDescent="0.25">
@@ -36477,17 +36477,17 @@
       <c r="C1037" s="6">
         <v>46251</v>
       </c>
-      <c r="D1037" s="8">
-        <v>0</v>
+      <c r="D1037" s="7">
+        <v>1.582626</v>
       </c>
       <c r="E1037" s="8">
-        <v>0</v>
+        <v>79048851</v>
       </c>
       <c r="F1037" s="9">
         <v>1190</v>
       </c>
       <c r="G1037" s="8">
-        <v>0</v>
+        <v>125104790.51</v>
       </c>
     </row>
     <row r="1038" spans="1:7" x14ac:dyDescent="0.25">
@@ -36546,17 +36546,17 @@
       <c r="C1040" s="6">
         <v>46251</v>
       </c>
-      <c r="D1040" s="8">
-        <v>0</v>
+      <c r="D1040" s="7">
+        <v>2.813579</v>
       </c>
       <c r="E1040" s="8">
-        <v>0</v>
+        <v>24785369</v>
       </c>
       <c r="F1040" s="9">
         <v>1</v>
       </c>
       <c r="G1040" s="8">
-        <v>0</v>
+        <v>69735595.35</v>
       </c>
     </row>
     <row r="1041" spans="1:7" x14ac:dyDescent="0.25">
@@ -36615,17 +36615,17 @@
       <c r="C1043" s="6">
         <v>46251</v>
       </c>
-      <c r="D1043" s="8">
-        <v>0</v>
+      <c r="D1043" s="7">
+        <v>2.035582</v>
       </c>
       <c r="E1043" s="8">
-        <v>0</v>
+        <v>351871809</v>
       </c>
       <c r="F1043" s="9">
         <v>13627</v>
       </c>
       <c r="G1043" s="8">
-        <v>0</v>
+        <v>716263746.77</v>
       </c>
     </row>
     <row r="1044" spans="1:7" x14ac:dyDescent="0.25">
@@ -36684,17 +36684,17 @@
       <c r="C1046" s="6">
         <v>46251</v>
       </c>
-      <c r="D1046" s="8">
-        <v>0</v>
+      <c r="D1046" s="7">
+        <v>4.462051</v>
       </c>
       <c r="E1046" s="8">
-        <v>0</v>
+        <v>1127191620</v>
       </c>
       <c r="F1046" s="9">
         <v>1</v>
       </c>
       <c r="G1046" s="8">
-        <v>0</v>
+        <v>5029586768.01</v>
       </c>
     </row>
     <row r="1047" spans="1:7" x14ac:dyDescent="0.25">
@@ -36799,17 +36799,17 @@
       <c r="C1051" s="6">
         <v>46251</v>
       </c>
-      <c r="D1051" s="8">
-        <v>0</v>
+      <c r="D1051" s="7">
+        <v>1.412543</v>
       </c>
       <c r="E1051" s="8">
-        <v>0</v>
+        <v>1933417141</v>
       </c>
       <c r="F1051" s="9">
         <v>73</v>
       </c>
       <c r="G1051" s="8">
-        <v>0</v>
+        <v>2731034941.06</v>
       </c>
     </row>
     <row r="1052" spans="1:7" x14ac:dyDescent="0.25">
@@ -36937,17 +36937,17 @@
       <c r="C1057" s="6">
         <v>46251</v>
       </c>
-      <c r="D1057" s="8">
-        <v>0</v>
+      <c r="D1057" s="7">
+        <v>1.706918</v>
       </c>
       <c r="E1057" s="8">
-        <v>0</v>
+        <v>301571758</v>
       </c>
       <c r="F1057" s="9">
         <v>13736</v>
       </c>
       <c r="G1057" s="8">
-        <v>0</v>
+        <v>514758304.18</v>
       </c>
     </row>
     <row r="1058" spans="1:7" x14ac:dyDescent="0.25">
@@ -36983,17 +36983,17 @@
       <c r="C1059" s="6">
         <v>46251</v>
       </c>
-      <c r="D1059" s="8">
-        <v>0</v>
+      <c r="D1059" s="7">
+        <v>21.035054</v>
       </c>
       <c r="E1059" s="8">
-        <v>0</v>
+        <v>213103165</v>
       </c>
       <c r="F1059" s="9">
         <v>22967</v>
       </c>
       <c r="G1059" s="8">
-        <v>0</v>
+        <v>4482636683.81</v>
       </c>
     </row>
     <row r="1060" spans="1:7" x14ac:dyDescent="0.25">
@@ -37006,17 +37006,17 @@
       <c r="C1060" s="6">
         <v>46251</v>
       </c>
-      <c r="D1060" s="8">
-        <v>0</v>
+      <c r="D1060" s="10">
+        <v>48.67056</v>
       </c>
       <c r="E1060" s="8">
-        <v>0</v>
+        <v>6265892</v>
       </c>
       <c r="F1060" s="9">
         <v>548</v>
       </c>
       <c r="G1060" s="8">
-        <v>0</v>
+        <v>304964472.23</v>
       </c>
     </row>
     <row r="1061" spans="1:7" x14ac:dyDescent="0.25">
@@ -37167,17 +37167,17 @@
       <c r="C1067" s="6">
         <v>46251</v>
       </c>
-      <c r="D1067" s="8">
-        <v>0</v>
+      <c r="D1067" s="7">
+        <v>1.866653</v>
       </c>
       <c r="E1067" s="8">
-        <v>0</v>
+        <v>39707417640</v>
       </c>
       <c r="F1067" s="9">
         <v>1320</v>
       </c>
       <c r="G1067" s="8">
-        <v>0</v>
+        <v>74119968480.45</v>
       </c>
     </row>
     <row r="1068" spans="1:7" x14ac:dyDescent="0.25">
@@ -37213,17 +37213,17 @@
       <c r="C1069" s="6">
         <v>46251</v>
       </c>
-      <c r="D1069" s="8">
-        <v>0</v>
+      <c r="D1069" s="7">
+        <v>3.974992</v>
       </c>
       <c r="E1069" s="8">
-        <v>0</v>
+        <v>149445776</v>
       </c>
       <c r="F1069" s="9">
         <v>6202</v>
       </c>
       <c r="G1069" s="8">
-        <v>0</v>
+        <v>594045744.07</v>
       </c>
     </row>
     <row r="1070" spans="1:7" x14ac:dyDescent="0.25">
@@ -37443,17 +37443,17 @@
       <c r="C1079" s="6">
         <v>46251</v>
       </c>
-      <c r="D1079" s="8">
-        <v>0</v>
+      <c r="D1079" s="7">
+        <v>49.358801</v>
       </c>
       <c r="E1079" s="8">
-        <v>0</v>
+        <v>495470</v>
       </c>
       <c r="F1079" s="9">
         <v>1</v>
       </c>
       <c r="G1079" s="8">
-        <v>0</v>
+        <v>24455805.08</v>
       </c>
     </row>
     <row r="1080" spans="1:7" x14ac:dyDescent="0.25">
@@ -37558,17 +37558,17 @@
       <c r="C1084" s="6">
         <v>46251</v>
       </c>
-      <c r="D1084" s="8">
-        <v>0</v>
+      <c r="D1084" s="7">
+        <v>5.195447</v>
       </c>
       <c r="E1084" s="8">
-        <v>0</v>
+        <v>39052054</v>
       </c>
       <c r="F1084" s="9">
         <v>3786</v>
       </c>
       <c r="G1084" s="8">
-        <v>0</v>
+        <v>202892863.21</v>
       </c>
     </row>
     <row r="1085" spans="1:7" x14ac:dyDescent="0.25">
@@ -37604,17 +37604,17 @@
       <c r="C1086" s="6">
         <v>46251</v>
       </c>
-      <c r="D1086" s="8">
-        <v>0</v>
+      <c r="D1086" s="7">
+        <v>5.710726</v>
       </c>
       <c r="E1086" s="8">
-        <v>0</v>
+        <v>5647281127</v>
       </c>
       <c r="F1086" s="9">
         <v>9897</v>
       </c>
       <c r="G1086" s="8">
-        <v>0</v>
+        <v>32250076882.33</v>
       </c>
     </row>
     <row r="1087" spans="1:7" x14ac:dyDescent="0.25">
@@ -37650,17 +37650,17 @@
       <c r="C1088" s="6">
         <v>46251</v>
       </c>
-      <c r="D1088" s="8">
-        <v>0</v>
+      <c r="D1088" s="7">
+        <v>45.431635</v>
       </c>
       <c r="E1088" s="8">
-        <v>0</v>
+        <v>2415590</v>
       </c>
       <c r="F1088" s="9">
         <v>1</v>
       </c>
       <c r="G1088" s="8">
-        <v>0</v>
+        <v>109744204.18</v>
       </c>
     </row>
     <row r="1089" spans="1:7" x14ac:dyDescent="0.25">
@@ -37696,17 +37696,17 @@
       <c r="C1090" s="6">
         <v>46251</v>
       </c>
-      <c r="D1090" s="8">
-        <v>0</v>
+      <c r="D1090" s="7">
+        <v>2.685326</v>
       </c>
       <c r="E1090" s="8">
-        <v>0</v>
+        <v>651838019</v>
       </c>
       <c r="F1090" s="9">
         <v>19730</v>
       </c>
       <c r="G1090" s="8">
-        <v>0</v>
+        <v>1750397268.07</v>
       </c>
     </row>
     <row r="1091" spans="1:7" x14ac:dyDescent="0.25">
@@ -37719,17 +37719,17 @@
       <c r="C1091" s="6">
         <v>46251</v>
       </c>
-      <c r="D1091" s="8">
-        <v>0</v>
+      <c r="D1091" s="7">
+        <v>22.329694</v>
       </c>
       <c r="E1091" s="8">
-        <v>0</v>
+        <v>30071033</v>
       </c>
       <c r="F1091" s="9">
         <v>5696</v>
       </c>
       <c r="G1091" s="8">
-        <v>0</v>
+        <v>671476954.65</v>
       </c>
     </row>
     <row r="1092" spans="1:7" x14ac:dyDescent="0.25">
@@ -37742,17 +37742,17 @@
       <c r="C1092" s="6">
         <v>46251</v>
       </c>
-      <c r="D1092" s="8">
-        <v>0</v>
+      <c r="D1092" s="7">
+        <v>8.026453</v>
       </c>
       <c r="E1092" s="8">
-        <v>0</v>
+        <v>55256093</v>
       </c>
       <c r="F1092" s="9">
         <v>4204</v>
       </c>
       <c r="G1092" s="8">
-        <v>0</v>
+        <v>443510438.52</v>
       </c>
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.25">
@@ -37765,17 +37765,17 @@
       <c r="C1093" s="6">
         <v>46251</v>
       </c>
-      <c r="D1093" s="8">
-        <v>0</v>
+      <c r="D1093" s="7">
+        <v>10.565084</v>
       </c>
       <c r="E1093" s="8">
-        <v>0</v>
+        <v>2301921570</v>
       </c>
       <c r="F1093" s="9">
         <v>646</v>
       </c>
       <c r="G1093" s="8">
-        <v>0</v>
+        <v>24319995700.23</v>
       </c>
     </row>
     <row r="1094" spans="1:7" x14ac:dyDescent="0.25">
@@ -37788,17 +37788,17 @@
       <c r="C1094" s="6">
         <v>46251</v>
       </c>
-      <c r="D1094" s="8">
-        <v>0</v>
+      <c r="D1094" s="7">
+        <v>14.894168</v>
       </c>
       <c r="E1094" s="8">
-        <v>0</v>
+        <v>8543633</v>
       </c>
       <c r="F1094" s="9">
         <v>715</v>
       </c>
       <c r="G1094" s="8">
-        <v>0</v>
+        <v>127250304.1</v>
       </c>
     </row>
     <row r="1095" spans="1:7" x14ac:dyDescent="0.25">
@@ -37811,17 +37811,17 @@
       <c r="C1095" s="6">
         <v>46251</v>
       </c>
-      <c r="D1095" s="8">
-        <v>0</v>
+      <c r="D1095" s="7">
+        <v>70.428834</v>
       </c>
       <c r="E1095" s="8">
-        <v>0</v>
+        <v>71406624</v>
       </c>
       <c r="F1095" s="9">
         <v>1437</v>
       </c>
       <c r="G1095" s="8">
-        <v>0</v>
+        <v>5029085272.85</v>
       </c>
     </row>
     <row r="1096" spans="1:7" x14ac:dyDescent="0.25">
@@ -37834,17 +37834,17 @@
       <c r="C1096" s="6">
         <v>46251</v>
       </c>
-      <c r="D1096" s="8">
-        <v>0</v>
+      <c r="D1096" s="7">
+        <v>29.352841</v>
       </c>
       <c r="E1096" s="8">
-        <v>0</v>
+        <v>32515349</v>
       </c>
       <c r="F1096" s="9">
         <v>1</v>
       </c>
       <c r="G1096" s="8">
-        <v>0</v>
+        <v>954417876.81</v>
       </c>
     </row>
     <row r="1097" spans="1:7" x14ac:dyDescent="0.25">
@@ -37857,17 +37857,17 @@
       <c r="C1097" s="6">
         <v>46251</v>
       </c>
-      <c r="D1097" s="8">
-        <v>0</v>
+      <c r="D1097" s="7">
+        <v>7.658363</v>
       </c>
       <c r="E1097" s="8">
-        <v>0</v>
+        <v>3475634453</v>
       </c>
       <c r="F1097" s="9">
         <v>44830</v>
       </c>
       <c r="G1097" s="8">
-        <v>0</v>
+        <v>26617671502.61</v>
       </c>
     </row>
     <row r="1098" spans="1:7" x14ac:dyDescent="0.25">
@@ -37880,17 +37880,17 @@
       <c r="C1098" s="6">
         <v>46251</v>
       </c>
-      <c r="D1098" s="8">
-        <v>0</v>
+      <c r="D1098" s="10">
+        <v>1.16008</v>
       </c>
       <c r="E1098" s="8">
-        <v>0</v>
+        <v>226165185</v>
       </c>
       <c r="F1098" s="9">
         <v>2528</v>
       </c>
       <c r="G1098" s="8">
-        <v>0</v>
+        <v>262369782.83</v>
       </c>
     </row>
     <row r="1099" spans="1:7" x14ac:dyDescent="0.25">
@@ -37903,17 +37903,17 @@
       <c r="C1099" s="6">
         <v>46251</v>
       </c>
-      <c r="D1099" s="8">
-        <v>0</v>
+      <c r="D1099" s="10">
+        <v>1.42313</v>
       </c>
       <c r="E1099" s="8">
-        <v>0</v>
+        <v>71915951</v>
       </c>
       <c r="F1099" s="9">
         <v>2074</v>
       </c>
       <c r="G1099" s="8">
-        <v>0</v>
+        <v>102345718.52</v>
       </c>
     </row>
     <row r="1100" spans="1:7" x14ac:dyDescent="0.25">
@@ -37949,17 +37949,17 @@
       <c r="C1101" s="6">
         <v>46251</v>
       </c>
-      <c r="D1101" s="8">
-        <v>0</v>
+      <c r="D1101" s="7">
+        <v>1.733528</v>
       </c>
       <c r="E1101" s="8">
-        <v>0</v>
+        <v>103587921</v>
       </c>
       <c r="F1101" s="9">
         <v>2134</v>
       </c>
       <c r="G1101" s="8">
-        <v>0</v>
+        <v>179572510.14</v>
       </c>
     </row>
     <row r="1102" spans="1:7" x14ac:dyDescent="0.25">
@@ -37995,17 +37995,17 @@
       <c r="C1103" s="6">
         <v>46251</v>
       </c>
-      <c r="D1103" s="8">
-        <v>0</v>
+      <c r="D1103" s="7">
+        <v>11.957428</v>
       </c>
       <c r="E1103" s="8">
-        <v>0</v>
+        <v>676228418</v>
       </c>
       <c r="F1103" s="9">
         <v>40889</v>
       </c>
       <c r="G1103" s="8">
-        <v>0</v>
+        <v>8085952661.75</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.25">
@@ -38018,17 +38018,17 @@
       <c r="C1104" s="6">
         <v>46251</v>
       </c>
-      <c r="D1104" s="8">
-        <v>0</v>
+      <c r="D1104" s="7">
+        <v>1.767634</v>
       </c>
       <c r="E1104" s="8">
-        <v>0</v>
+        <v>392570970</v>
       </c>
       <c r="F1104" s="9">
         <v>1</v>
       </c>
       <c r="G1104" s="8">
-        <v>0</v>
+        <v>693921761.91</v>
       </c>
     </row>
     <row r="1105" spans="1:7" x14ac:dyDescent="0.25">
@@ -38202,17 +38202,17 @@
       <c r="C1112" s="6">
         <v>46251</v>
       </c>
-      <c r="D1112" s="8">
-        <v>0</v>
+      <c r="D1112" s="7">
+        <v>27.895218</v>
       </c>
       <c r="E1112" s="8">
-        <v>0</v>
+        <v>3201461306</v>
       </c>
       <c r="F1112" s="9">
         <v>65128</v>
       </c>
       <c r="G1112" s="8">
-        <v>0</v>
+        <v>89305461037.64</v>
       </c>
     </row>
     <row r="1113" spans="1:7" x14ac:dyDescent="0.25">
@@ -38248,17 +38248,17 @@
       <c r="C1114" s="6">
         <v>46251</v>
       </c>
-      <c r="D1114" s="8">
-        <v>0</v>
+      <c r="D1114" s="10">
+        <v>2.37411</v>
       </c>
       <c r="E1114" s="8">
-        <v>0</v>
+        <v>199978811</v>
       </c>
       <c r="F1114" s="9">
         <v>5863</v>
       </c>
       <c r="G1114" s="8">
-        <v>0</v>
+        <v>474771737.9</v>
       </c>
     </row>
     <row r="1115" spans="1:7" x14ac:dyDescent="0.25">
@@ -38525,7 +38525,7 @@
         <v>46251</v>
       </c>
       <c r="D1126" s="7">
-        <v>3.652857</v>
+        <v>3.652027</v>
       </c>
       <c r="E1126" s="8">
         <v>245457201</v>
@@ -38534,7 +38534,7 @@
         <v>12</v>
       </c>
       <c r="G1126" s="8">
-        <v>896620013.64</v>
+        <v>896416239.1</v>
       </c>
     </row>
     <row r="1127" spans="1:7" x14ac:dyDescent="0.25">
@@ -38846,8 +38846,8 @@
       <c r="C1140" s="6">
         <v>46251</v>
       </c>
-      <c r="D1140" s="7">
-        <v>1.265606</v>
+      <c r="D1140" s="10">
+        <v>1.26308</v>
       </c>
       <c r="E1140" s="8">
         <v>395837739</v>
@@ -38856,7 +38856,7 @@
         <v>963</v>
       </c>
       <c r="G1140" s="8">
-        <v>500974771.51</v>
+        <v>499974706.68</v>
       </c>
     </row>
     <row r="1141" spans="1:7" x14ac:dyDescent="0.25">
@@ -38869,17 +38869,17 @@
       <c r="C1141" s="6">
         <v>46251</v>
       </c>
-      <c r="D1141" s="8">
-        <v>0</v>
+      <c r="D1141" s="7">
+        <v>6.131929</v>
       </c>
       <c r="E1141" s="8">
-        <v>0</v>
+        <v>125123309</v>
       </c>
       <c r="F1141" s="9">
         <v>6711</v>
       </c>
       <c r="G1141" s="8">
-        <v>0</v>
+        <v>767247291.32</v>
       </c>
     </row>
     <row r="1142" spans="1:7" x14ac:dyDescent="0.25">
@@ -39352,17 +39352,17 @@
       <c r="C1162" s="6">
         <v>46251</v>
       </c>
-      <c r="D1162" s="8">
-        <v>0</v>
+      <c r="D1162" s="7">
+        <v>1.602337</v>
       </c>
       <c r="E1162" s="8">
-        <v>0</v>
+        <v>2651303752</v>
       </c>
       <c r="F1162" s="9">
         <v>13</v>
       </c>
       <c r="G1162" s="8">
-        <v>0</v>
+        <v>4248282172.1</v>
       </c>
     </row>
     <row r="1163" spans="1:7" x14ac:dyDescent="0.25">
@@ -39375,17 +39375,17 @@
       <c r="C1163" s="6">
         <v>46251</v>
       </c>
-      <c r="D1163" s="8">
-        <v>0</v>
+      <c r="D1163" s="7">
+        <v>2.115815</v>
       </c>
       <c r="E1163" s="8">
-        <v>0</v>
+        <v>1800673679</v>
       </c>
       <c r="F1163" s="9">
         <v>15</v>
       </c>
       <c r="G1163" s="8">
-        <v>0</v>
+        <v>3809891965.72</v>
       </c>
     </row>
     <row r="1164" spans="1:7" x14ac:dyDescent="0.25">
@@ -39517,7 +39517,7 @@
         <v>2.009163</v>
       </c>
       <c r="E1169" s="8">
-        <v>363164244</v>
+        <v>363164242</v>
       </c>
       <c r="F1169" s="9">
         <v>1056</v>
@@ -39606,7 +39606,7 @@
         <v>46251</v>
       </c>
       <c r="D1173" s="7">
-        <v>1.258593</v>
+        <v>1.227172</v>
       </c>
       <c r="E1173" s="8">
         <v>10755621</v>
@@ -39615,7 +39615,7 @@
         <v>119</v>
       </c>
       <c r="G1173" s="8">
-        <v>13536944.3</v>
+        <v>13198996.78</v>
       </c>
     </row>
     <row r="1174" spans="1:7" x14ac:dyDescent="0.25">
@@ -40065,17 +40065,17 @@
       <c r="C1193" s="6">
         <v>46251</v>
       </c>
-      <c r="D1193" s="8">
-        <v>0</v>
+      <c r="D1193" s="7">
+        <v>0.779878</v>
       </c>
       <c r="E1193" s="8">
-        <v>0</v>
+        <v>1033653600</v>
       </c>
       <c r="F1193" s="9">
         <v>19</v>
       </c>
       <c r="G1193" s="8">
-        <v>0</v>
+        <v>806123826.72</v>
       </c>
     </row>
     <row r="1194" spans="1:7" x14ac:dyDescent="0.25">
@@ -40089,7 +40089,7 @@
         <v>46251</v>
       </c>
       <c r="D1194" s="7">
-        <v>5.686269</v>
+        <v>5.686408</v>
       </c>
       <c r="E1194" s="8">
         <v>27321158</v>
@@ -40098,7 +40098,7 @@
         <v>12840</v>
       </c>
       <c r="G1194" s="8">
-        <v>155355466.16</v>
+        <v>155359253.08</v>
       </c>
     </row>
     <row r="1195" spans="1:7" x14ac:dyDescent="0.25">
@@ -41008,17 +41008,17 @@
       <c r="C1234" s="6">
         <v>46251</v>
       </c>
-      <c r="D1234" s="8">
-        <v>0</v>
+      <c r="D1234" s="7">
+        <v>2.304527</v>
       </c>
       <c r="E1234" s="8">
-        <v>0</v>
+        <v>6866499553</v>
       </c>
       <c r="F1234" s="9">
         <v>1</v>
       </c>
       <c r="G1234" s="8">
-        <v>0</v>
+        <v>15824031509.15</v>
       </c>
     </row>
     <row r="1235" spans="1:7" x14ac:dyDescent="0.25">
@@ -41331,7 +41331,7 @@
         <v>46251</v>
       </c>
       <c r="D1248" s="7">
-        <v>5.266987</v>
+        <v>5.266819</v>
       </c>
       <c r="E1248" s="8">
         <v>291282431</v>
@@ -41340,7 +41340,7 @@
         <v>158</v>
       </c>
       <c r="G1248" s="8">
-        <v>1534180792.24</v>
+        <v>1534131832.3</v>
       </c>
     </row>
     <row r="1249" spans="1:7" x14ac:dyDescent="0.25">
@@ -41376,17 +41376,17 @@
       <c r="C1250" s="6">
         <v>46251</v>
       </c>
-      <c r="D1250" s="8">
-        <v>0</v>
+      <c r="D1250" s="10">
+        <v>1.58018</v>
       </c>
       <c r="E1250" s="8">
-        <v>0</v>
+        <v>592973692</v>
       </c>
       <c r="F1250" s="9">
         <v>1</v>
       </c>
       <c r="G1250" s="8">
-        <v>0</v>
+        <v>937005333.31</v>
       </c>
     </row>
     <row r="1251" spans="1:7" x14ac:dyDescent="0.25">
@@ -42549,17 +42549,17 @@
       <c r="C1301" s="6">
         <v>46251</v>
       </c>
-      <c r="D1301" s="8">
-        <v>0</v>
+      <c r="D1301" s="7">
+        <v>8.167551</v>
       </c>
       <c r="E1301" s="8">
-        <v>0</v>
+        <v>22659462</v>
       </c>
       <c r="F1301" s="9">
         <v>434</v>
       </c>
       <c r="G1301" s="8">
-        <v>0</v>
+        <v>185072308.36</v>
       </c>
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
@@ -42848,8 +42848,8 @@
       <c r="C1314" s="6">
         <v>46251</v>
       </c>
-      <c r="D1314" s="10">
-        <v>13.23175</v>
+      <c r="D1314" s="7">
+        <v>13.234641</v>
       </c>
       <c r="E1314" s="8">
         <v>367449310</v>
@@ -42858,7 +42858,7 @@
         <v>11181</v>
       </c>
       <c r="G1314" s="8">
-        <v>4861997515.91</v>
+        <v>4863059621.8</v>
       </c>
     </row>
     <row r="1315" spans="1:7" x14ac:dyDescent="0.25">
@@ -43447,7 +43447,7 @@
         <v>46251</v>
       </c>
       <c r="D1340" s="7">
-        <v>25.616091</v>
+        <v>25.983062</v>
       </c>
       <c r="E1340" s="8">
         <v>35533191</v>
@@ -43456,7 +43456,7 @@
         <v>2519</v>
       </c>
       <c r="G1340" s="8">
-        <v>910221452.35</v>
+        <v>923261097.36</v>
       </c>
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.25">
@@ -43676,17 +43676,17 @@
       <c r="C1350" s="6">
         <v>46251</v>
       </c>
-      <c r="D1350" s="10">
-        <v>0.15473</v>
+      <c r="D1350" s="7">
+        <v>0.155217</v>
       </c>
       <c r="E1350" s="8">
-        <v>9357402159</v>
+        <v>9266354967</v>
       </c>
       <c r="F1350" s="9">
         <v>4170</v>
       </c>
       <c r="G1350" s="8">
-        <v>1447872238.2</v>
+        <v>1438292045.17</v>
       </c>
     </row>
     <row r="1351" spans="1:7" x14ac:dyDescent="0.25">
@@ -43768,17 +43768,17 @@
       <c r="C1354" s="6">
         <v>46251</v>
       </c>
-      <c r="D1354" s="8">
-        <v>0</v>
+      <c r="D1354" s="7">
+        <v>7.135152</v>
       </c>
       <c r="E1354" s="8">
-        <v>0</v>
+        <v>458436699</v>
       </c>
       <c r="F1354" s="9">
         <v>22649</v>
       </c>
       <c r="G1354" s="8">
-        <v>0</v>
+        <v>3271015418.73</v>
       </c>
     </row>
     <row r="1355" spans="1:7" x14ac:dyDescent="0.25">
@@ -44031,7 +44031,7 @@
         <v>8172</v>
       </c>
       <c r="G1365" s="8">
-        <v>3536464358.42</v>
+        <v>3536458323.36</v>
       </c>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.25">
@@ -44895,8 +44895,8 @@
       <c r="C1403" s="6">
         <v>46251</v>
       </c>
-      <c r="D1403" s="7">
-        <v>25.030285</v>
+      <c r="D1403" s="10">
+        <v>25.03138</v>
       </c>
       <c r="E1403" s="8">
         <v>403828398</v>
@@ -44905,7 +44905,7 @@
         <v>45</v>
       </c>
       <c r="G1403" s="8">
-        <v>10107939862.35</v>
+        <v>10108382239.81</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.25">
@@ -45608,17 +45608,17 @@
       <c r="C1434" s="6">
         <v>46251</v>
       </c>
-      <c r="D1434" s="8">
-        <v>0</v>
+      <c r="D1434" s="7">
+        <v>1.264272</v>
       </c>
       <c r="E1434" s="8">
-        <v>0</v>
+        <v>676585</v>
       </c>
       <c r="F1434" s="9">
         <v>114</v>
       </c>
       <c r="G1434" s="8">
-        <v>0</v>
+        <v>855387.42</v>
       </c>
     </row>
     <row r="1435" spans="1:7" x14ac:dyDescent="0.25">
@@ -45700,17 +45700,17 @@
       <c r="C1438" s="6">
         <v>46251</v>
       </c>
-      <c r="D1438" s="8">
-        <v>0</v>
+      <c r="D1438" s="7">
+        <v>0.008394</v>
       </c>
       <c r="E1438" s="8">
-        <v>0</v>
+        <v>3375437181</v>
       </c>
       <c r="F1438" s="9">
         <v>44</v>
       </c>
       <c r="G1438" s="8">
-        <v>0</v>
+        <v>28333939.47</v>
       </c>
     </row>
     <row r="1439" spans="1:7" x14ac:dyDescent="0.25">
@@ -46299,16 +46299,16 @@
         <v>46251</v>
       </c>
       <c r="D1464" s="7">
-        <v>3.112697</v>
+        <v>3.111176</v>
       </c>
       <c r="E1464" s="8">
-        <v>2634164845</v>
+        <v>2634809757</v>
       </c>
       <c r="F1464" s="9">
         <v>369</v>
       </c>
       <c r="G1464" s="8">
-        <v>8199357698.62</v>
+        <v>8197357883.02</v>
       </c>
     </row>
     <row r="1465" spans="1:7" x14ac:dyDescent="0.25">
@@ -49311,17 +49311,17 @@
       <c r="C1595" s="6">
         <v>46251</v>
       </c>
-      <c r="D1595" s="8">
-        <v>0</v>
+      <c r="D1595" s="7">
+        <v>1.234593</v>
       </c>
       <c r="E1595" s="8">
-        <v>0</v>
+        <v>300626629</v>
       </c>
       <c r="F1595" s="9">
         <v>1</v>
       </c>
       <c r="G1595" s="8">
-        <v>0</v>
+        <v>371151507</v>
       </c>
     </row>
     <row r="1596" spans="1:7" x14ac:dyDescent="0.25">
@@ -49541,17 +49541,17 @@
       <c r="C1605" s="6">
         <v>46251</v>
       </c>
-      <c r="D1605" s="8">
-        <v>0</v>
+      <c r="D1605" s="7">
+        <v>1.868898</v>
       </c>
       <c r="E1605" s="8">
-        <v>0</v>
+        <v>247995861</v>
       </c>
       <c r="F1605" s="9">
         <v>830</v>
       </c>
       <c r="G1605" s="8">
-        <v>0</v>
+        <v>463478848.74</v>
       </c>
     </row>
     <row r="1606" spans="1:7" x14ac:dyDescent="0.25">
@@ -49656,17 +49656,17 @@
       <c r="C1610" s="6">
         <v>46251</v>
       </c>
-      <c r="D1610" s="8">
-        <v>0</v>
+      <c r="D1610" s="7">
+        <v>1.020345</v>
       </c>
       <c r="E1610" s="8">
-        <v>0</v>
+        <v>32951675</v>
       </c>
       <c r="F1610" s="9">
         <v>136</v>
       </c>
       <c r="G1610" s="8">
-        <v>0</v>
+        <v>33622074.56</v>
       </c>
     </row>
     <row r="1611" spans="1:7" x14ac:dyDescent="0.25">
@@ -49772,7 +49772,7 @@
         <v>46251</v>
       </c>
       <c r="D1615" s="7">
-        <v>1.395964</v>
+        <v>1.399802</v>
       </c>
       <c r="E1615" s="8">
         <v>22282527</v>
@@ -49781,7 +49781,7 @@
         <v>76</v>
       </c>
       <c r="G1615" s="8">
-        <v>31105613.36</v>
+        <v>31191128.23</v>
       </c>
     </row>
     <row r="1616" spans="1:7" x14ac:dyDescent="0.25">
@@ -49794,17 +49794,17 @@
       <c r="C1616" s="6">
         <v>46251</v>
       </c>
-      <c r="D1616" s="8">
-        <v>0</v>
+      <c r="D1616" s="7">
+        <v>2.018487</v>
       </c>
       <c r="E1616" s="8">
-        <v>0</v>
+        <v>103989051</v>
       </c>
       <c r="F1616" s="9">
         <v>2494</v>
       </c>
       <c r="G1616" s="8">
-        <v>0</v>
+        <v>209900527.93</v>
       </c>
     </row>
     <row r="1617" spans="1:7" x14ac:dyDescent="0.25">
@@ -49886,17 +49886,17 @@
       <c r="C1620" s="6">
         <v>46251</v>
       </c>
-      <c r="D1620" s="8">
-        <v>0</v>
+      <c r="D1620" s="7">
+        <v>1.400965</v>
       </c>
       <c r="E1620" s="8">
-        <v>0</v>
+        <v>103651131</v>
       </c>
       <c r="F1620" s="9">
         <v>19</v>
       </c>
       <c r="G1620" s="8">
-        <v>0</v>
+        <v>145211557.93</v>
       </c>
     </row>
     <row r="1621" spans="1:7" x14ac:dyDescent="0.25">
@@ -49909,17 +49909,17 @@
       <c r="C1621" s="6">
         <v>46251</v>
       </c>
-      <c r="D1621" s="8">
-        <v>0</v>
+      <c r="D1621" s="7">
+        <v>0.955835</v>
       </c>
       <c r="E1621" s="8">
-        <v>0</v>
+        <v>4011986</v>
       </c>
       <c r="F1621" s="9">
         <v>11</v>
       </c>
       <c r="G1621" s="8">
-        <v>0</v>
+        <v>3834796.09</v>
       </c>
     </row>
     <row r="1622" spans="1:7" x14ac:dyDescent="0.25">
@@ -49932,17 +49932,17 @@
       <c r="C1622" s="6">
         <v>46251</v>
       </c>
-      <c r="D1622" s="8">
-        <v>0</v>
+      <c r="D1622" s="7">
+        <v>0.284256</v>
       </c>
       <c r="E1622" s="8">
-        <v>0</v>
+        <v>194986093</v>
       </c>
       <c r="F1622" s="9">
         <v>12</v>
       </c>
       <c r="G1622" s="8">
-        <v>0</v>
+        <v>55425933.39</v>
       </c>
     </row>
     <row r="1623" spans="1:7" x14ac:dyDescent="0.25">
@@ -50577,7 +50577,7 @@
         <v>46251</v>
       </c>
       <c r="D1650" s="7">
-        <v>1.733146</v>
+        <v>1.733201</v>
       </c>
       <c r="E1650" s="8">
         <v>27474329</v>
@@ -50586,7 +50586,7 @@
         <v>581</v>
       </c>
       <c r="G1650" s="8">
-        <v>47617024.35</v>
+        <v>47618548.05</v>
       </c>
     </row>
     <row r="1651" spans="1:7" x14ac:dyDescent="0.25">
@@ -50715,7 +50715,7 @@
         <v>46251</v>
       </c>
       <c r="D1656" s="7">
-        <v>1.279791</v>
+        <v>1.281101</v>
       </c>
       <c r="E1656" s="8">
         <v>145147711</v>
@@ -50724,7 +50724,7 @@
         <v>69</v>
       </c>
       <c r="G1656" s="8">
-        <v>185758761.07</v>
+        <v>185948848.61</v>
       </c>
     </row>
     <row r="1657" spans="1:7" x14ac:dyDescent="0.25">
@@ -50807,7 +50807,7 @@
         <v>46251</v>
       </c>
       <c r="D1660" s="7">
-        <v>0.592976</v>
+        <v>0.592843</v>
       </c>
       <c r="E1660" s="8">
         <v>3789226767</v>
@@ -50816,7 +50816,7 @@
         <v>1171</v>
       </c>
       <c r="G1660" s="8">
-        <v>2246921210.91</v>
+        <v>2246415286.69</v>
       </c>
     </row>
     <row r="1661" spans="1:7" x14ac:dyDescent="0.25">
@@ -51589,7 +51589,7 @@
         <v>46251</v>
       </c>
       <c r="D1694" s="7">
-        <v>2.818343</v>
+        <v>2.819189</v>
       </c>
       <c r="E1694" s="8">
         <v>265325692</v>
@@ -51598,7 +51598,7 @@
         <v>1321</v>
       </c>
       <c r="G1694" s="8">
-        <v>747778755.61</v>
+        <v>748003311.25</v>
       </c>
     </row>
     <row r="1695" spans="1:7" x14ac:dyDescent="0.25">
@@ -52624,7 +52624,7 @@
         <v>46251</v>
       </c>
       <c r="D1739" s="7">
-        <v>8611.792989</v>
+        <v>8611.792448</v>
       </c>
       <c r="E1739" s="8">
         <v>32781221</v>
@@ -52633,7 +52633,7 @@
         <v>106539</v>
       </c>
       <c r="G1739" s="8">
-        <v>282305089173.99</v>
+        <v>282305071445.73</v>
       </c>
     </row>
     <row r="1740" spans="1:7" x14ac:dyDescent="0.25">
@@ -52807,8 +52807,8 @@
       <c r="C1747" s="6">
         <v>46251</v>
       </c>
-      <c r="D1747" s="10">
-        <v>1.41473</v>
+      <c r="D1747" s="7">
+        <v>1.419209</v>
       </c>
       <c r="E1747" s="8">
         <v>41238160</v>
@@ -52817,7 +52817,7 @@
         <v>89</v>
       </c>
       <c r="G1747" s="8">
-        <v>58340856.01</v>
+        <v>58525553.66</v>
       </c>
     </row>
     <row r="1748" spans="1:7" x14ac:dyDescent="0.25">
@@ -53751,7 +53751,7 @@
         <v>46251</v>
       </c>
       <c r="D1788" s="7">
-        <v>2.908368</v>
+        <v>2.908487</v>
       </c>
       <c r="E1788" s="8">
         <v>3045628</v>
@@ -53760,7 +53760,7 @@
         <v>523</v>
       </c>
       <c r="G1788" s="8">
-        <v>8857806.43</v>
+        <v>8858169</v>
       </c>
     </row>
     <row r="1789" spans="1:7" x14ac:dyDescent="0.25">
@@ -54532,8 +54532,8 @@
       <c r="C1822" s="6">
         <v>46251</v>
       </c>
-      <c r="D1822" s="7">
-        <v>0.259936</v>
+      <c r="D1822" s="10">
+        <v>0.25985</v>
       </c>
       <c r="E1822" s="8">
         <v>5184664242</v>
@@ -54542,7 +54542,7 @@
         <v>393</v>
       </c>
       <c r="G1822" s="8">
-        <v>1347679174.9</v>
+        <v>1347232626.88</v>
       </c>
     </row>
     <row r="1823" spans="1:7" x14ac:dyDescent="0.25">
@@ -54716,17 +54716,17 @@
       <c r="C1830" s="6">
         <v>46251</v>
       </c>
-      <c r="D1830" s="8">
-        <v>0</v>
+      <c r="D1830" s="7">
+        <v>1.000171</v>
       </c>
       <c r="E1830" s="8">
-        <v>0</v>
+        <v>123548631</v>
       </c>
       <c r="F1830" s="9">
         <v>2957</v>
       </c>
       <c r="G1830" s="8">
-        <v>0</v>
+        <v>123569699.19</v>
       </c>
     </row>
     <row r="1831" spans="1:7" x14ac:dyDescent="0.25">
@@ -55130,17 +55130,17 @@
       <c r="C1848" s="6">
         <v>46251</v>
       </c>
-      <c r="D1848" s="8">
-        <v>0</v>
+      <c r="D1848" s="7">
+        <v>14.610334</v>
       </c>
       <c r="E1848" s="8">
-        <v>0</v>
+        <v>374277311</v>
       </c>
       <c r="F1848" s="9">
         <v>9850</v>
       </c>
       <c r="G1848" s="8">
-        <v>0</v>
+        <v>5468316511.18</v>
       </c>
     </row>
     <row r="1849" spans="1:7" x14ac:dyDescent="0.25">
@@ -55199,17 +55199,17 @@
       <c r="C1851" s="6">
         <v>46251</v>
       </c>
-      <c r="D1851" s="8">
-        <v>0</v>
+      <c r="D1851" s="7">
+        <v>14.470464</v>
       </c>
       <c r="E1851" s="8">
-        <v>0</v>
+        <v>128584122</v>
       </c>
       <c r="F1851" s="9">
         <v>3582</v>
       </c>
       <c r="G1851" s="8">
-        <v>0</v>
+        <v>1860671902.29</v>
       </c>
     </row>
     <row r="1852" spans="1:7" x14ac:dyDescent="0.25">
@@ -55452,17 +55452,17 @@
       <c r="C1862" s="6">
         <v>46251</v>
       </c>
-      <c r="D1862" s="8">
-        <v>0</v>
+      <c r="D1862" s="7">
+        <v>2.679876</v>
       </c>
       <c r="E1862" s="8">
-        <v>0</v>
+        <v>40319714</v>
       </c>
       <c r="F1862" s="9">
         <v>116</v>
       </c>
       <c r="G1862" s="8">
-        <v>0</v>
+        <v>108051831.16</v>
       </c>
     </row>
     <row r="1863" spans="1:7" x14ac:dyDescent="0.25">
@@ -56027,17 +56027,17 @@
       <c r="C1887" s="6">
         <v>46251</v>
       </c>
-      <c r="D1887" s="8">
-        <v>0</v>
+      <c r="D1887" s="7">
+        <v>2.769571</v>
       </c>
       <c r="E1887" s="8">
-        <v>0</v>
+        <v>912783704</v>
       </c>
       <c r="F1887" s="9">
         <v>17078</v>
       </c>
       <c r="G1887" s="8">
-        <v>0</v>
+        <v>2528019031</v>
       </c>
     </row>
     <row r="1888" spans="1:7" x14ac:dyDescent="0.25">
@@ -56119,17 +56119,17 @@
       <c r="C1891" s="6">
         <v>46251</v>
       </c>
-      <c r="D1891" s="8">
-        <v>0</v>
+      <c r="D1891" s="7">
+        <v>5.924218</v>
       </c>
       <c r="E1891" s="8">
-        <v>0</v>
+        <v>181241902</v>
       </c>
       <c r="F1891" s="9">
         <v>13902</v>
       </c>
       <c r="G1891" s="8">
-        <v>0</v>
+        <v>1073716540.78</v>
       </c>
     </row>
     <row r="1892" spans="1:7" x14ac:dyDescent="0.25">
@@ -56947,17 +56947,17 @@
       <c r="C1927" s="6">
         <v>46251</v>
       </c>
-      <c r="D1927" s="8">
-        <v>0</v>
+      <c r="D1927" s="7">
+        <v>7.858703</v>
       </c>
       <c r="E1927" s="8">
-        <v>0</v>
+        <v>704489121</v>
       </c>
       <c r="F1927" s="9">
         <v>3364</v>
       </c>
       <c r="G1927" s="8">
-        <v>0</v>
+        <v>5536370592.03</v>
       </c>
     </row>
     <row r="1928" spans="1:7" x14ac:dyDescent="0.25">
@@ -57108,17 +57108,17 @@
       <c r="C1934" s="6">
         <v>46251</v>
       </c>
-      <c r="D1934" s="8">
-        <v>0</v>
+      <c r="D1934" s="7">
+        <v>0.966708</v>
       </c>
       <c r="E1934" s="8">
-        <v>0</v>
+        <v>1832423284</v>
       </c>
       <c r="F1934" s="9">
         <v>14871</v>
       </c>
       <c r="G1934" s="8">
-        <v>0</v>
+        <v>1771418420.61</v>
       </c>
     </row>
     <row r="1935" spans="1:7" x14ac:dyDescent="0.25">
@@ -57568,17 +57568,17 @@
       <c r="C1954" s="6">
         <v>46251</v>
       </c>
-      <c r="D1954" s="8">
-        <v>0</v>
+      <c r="D1954" s="7">
+        <v>13.056489</v>
       </c>
       <c r="E1954" s="8">
-        <v>0</v>
+        <v>843339204</v>
       </c>
       <c r="F1954" s="9">
         <v>61307</v>
       </c>
       <c r="G1954" s="8">
-        <v>0</v>
+        <v>11011048777.9</v>
       </c>
     </row>
     <row r="1955" spans="1:7" x14ac:dyDescent="0.25">
@@ -57683,17 +57683,17 @@
       <c r="C1959" s="6">
         <v>46251</v>
       </c>
-      <c r="D1959" s="8">
-        <v>0</v>
+      <c r="D1959" s="7">
+        <v>2.040075</v>
       </c>
       <c r="E1959" s="8">
-        <v>0</v>
+        <v>2136109070</v>
       </c>
       <c r="F1959" s="9">
         <v>601</v>
       </c>
       <c r="G1959" s="8">
-        <v>0</v>
+        <v>4357822207.51</v>
       </c>
     </row>
     <row r="1960" spans="1:7" x14ac:dyDescent="0.25">
@@ -57706,17 +57706,17 @@
       <c r="C1960" s="6">
         <v>46251</v>
       </c>
-      <c r="D1960" s="8">
-        <v>0</v>
+      <c r="D1960" s="10">
+        <v>46.18171</v>
       </c>
       <c r="E1960" s="8">
-        <v>0</v>
+        <v>333957</v>
       </c>
       <c r="F1960" s="9">
         <v>47</v>
       </c>
       <c r="G1960" s="8">
-        <v>0</v>
+        <v>15422705.4</v>
       </c>
     </row>
     <row r="1961" spans="1:7" x14ac:dyDescent="0.25">
@@ -57752,17 +57752,17 @@
       <c r="C1962" s="6">
         <v>46251</v>
       </c>
-      <c r="D1962" s="8">
-        <v>0</v>
+      <c r="D1962" s="7">
+        <v>6.380814</v>
       </c>
       <c r="E1962" s="8">
-        <v>0</v>
+        <v>241401806</v>
       </c>
       <c r="F1962" s="9">
         <v>3347</v>
       </c>
       <c r="G1962" s="8">
-        <v>0</v>
+        <v>1540339960.3</v>
       </c>
     </row>
     <row r="1963" spans="1:7" x14ac:dyDescent="0.25">
@@ -58696,7 +58696,7 @@
         <v>46251</v>
       </c>
       <c r="D2003" s="7">
-        <v>1.883912</v>
+        <v>1.884202</v>
       </c>
       <c r="E2003" s="8">
         <v>306521428</v>
@@ -58705,7 +58705,7 @@
         <v>11</v>
       </c>
       <c r="G2003" s="8">
-        <v>577459293.72</v>
+        <v>577548418.83</v>
       </c>
     </row>
     <row r="2004" spans="1:7" x14ac:dyDescent="0.25">
@@ -58742,7 +58742,7 @@
         <v>46251</v>
       </c>
       <c r="D2005" s="7">
-        <v>5.755199</v>
+        <v>5.754052</v>
       </c>
       <c r="E2005" s="8">
         <v>106786382</v>
@@ -58751,7 +58751,7 @@
         <v>1</v>
       </c>
       <c r="G2005" s="8">
-        <v>614576844.4</v>
+        <v>614454417.46</v>
       </c>
     </row>
     <row r="2006" spans="1:7" x14ac:dyDescent="0.25">
@@ -59178,8 +59178,8 @@
       <c r="C2024" s="6">
         <v>46251</v>
       </c>
-      <c r="D2024" s="7">
-        <v>11.889285</v>
+      <c r="D2024" s="10">
+        <v>11.88884</v>
       </c>
       <c r="E2024" s="8">
         <v>299315692</v>
@@ -59188,7 +59188,7 @@
         <v>24</v>
       </c>
       <c r="G2024" s="8">
-        <v>3558649530.07</v>
+        <v>3558516498.18</v>
       </c>
     </row>
     <row r="2025" spans="1:7" x14ac:dyDescent="0.25">
@@ -59294,7 +59294,7 @@
         <v>46251</v>
       </c>
       <c r="D2029" s="7">
-        <v>7.513718</v>
+        <v>7.513555</v>
       </c>
       <c r="E2029" s="8">
         <v>274862095</v>
@@ -59303,7 +59303,7 @@
         <v>1</v>
       </c>
       <c r="G2029" s="8">
-        <v>2065236324.23</v>
+        <v>2065191548.17</v>
       </c>
     </row>
     <row r="2030" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>18.08.2026 09:24:10</t>
+    <t>18.08.2026 14:09:41</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -13241,17 +13241,17 @@
       <c r="C27" s="6">
         <v>46252</v>
       </c>
-      <c r="D27" s="8">
-        <v>0</v>
+      <c r="D27" s="7">
+        <v>0.176497</v>
       </c>
       <c r="E27" s="8">
-        <v>0</v>
+        <v>7556686794</v>
       </c>
       <c r="F27" s="9">
         <v>35163</v>
       </c>
       <c r="G27" s="8">
-        <v>0</v>
+        <v>1333734074.49</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -13379,8 +13379,8 @@
       <c r="C33" s="6">
         <v>46252</v>
       </c>
-      <c r="D33" s="10">
-        <v>0.61426</v>
+      <c r="D33" s="7">
+        <v>0.614359</v>
       </c>
       <c r="E33" s="8">
         <v>2223772091</v>
@@ -13389,7 +13389,7 @@
         <v>14956</v>
       </c>
       <c r="G33" s="8">
-        <v>1365975136.29</v>
+        <v>1366194775.52</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -13449,7 +13449,7 @@
         <v>46252</v>
       </c>
       <c r="D36" s="7">
-        <v>36.153264</v>
+        <v>36.152506</v>
       </c>
       <c r="E36" s="8">
         <v>3248439</v>
@@ -13458,7 +13458,7 @@
         <v>2651</v>
       </c>
       <c r="G36" s="8">
-        <v>117441672.21</v>
+        <v>117439211.39</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -13518,7 +13518,7 @@
         <v>46252</v>
       </c>
       <c r="D39" s="7">
-        <v>21.497448</v>
+        <v>21.530336</v>
       </c>
       <c r="E39" s="8">
         <v>6008795</v>
@@ -13527,7 +13527,7 @@
         <v>183</v>
       </c>
       <c r="G39" s="8">
-        <v>129173759.14</v>
+        <v>129371372.97</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -13540,8 +13540,8 @@
       <c r="C40" s="6">
         <v>46252</v>
       </c>
-      <c r="D40" s="7">
-        <v>31.161295</v>
+      <c r="D40" s="10">
+        <v>31.19254</v>
       </c>
       <c r="E40" s="8">
         <v>1749021</v>
@@ -13550,7 +13550,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="8">
-        <v>54501759.44</v>
+        <v>54556408.24</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -14276,17 +14276,17 @@
       <c r="C72" s="6">
         <v>46252</v>
       </c>
-      <c r="D72" s="8">
-        <v>0</v>
+      <c r="D72" s="7">
+        <v>6.751577</v>
       </c>
       <c r="E72" s="8">
-        <v>0</v>
+        <v>12414996</v>
       </c>
       <c r="F72" s="9">
         <v>2910</v>
       </c>
       <c r="G72" s="8">
-        <v>0</v>
+        <v>83820801.13</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -14391,17 +14391,17 @@
       <c r="C77" s="6">
         <v>46252</v>
       </c>
-      <c r="D77" s="8">
-        <v>0</v>
+      <c r="D77" s="7">
+        <v>16.111236</v>
       </c>
       <c r="E77" s="8">
-        <v>0</v>
+        <v>253481321</v>
       </c>
       <c r="F77" s="9">
         <v>7422</v>
       </c>
       <c r="G77" s="8">
-        <v>0</v>
+        <v>4083897290.19</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -14414,17 +14414,17 @@
       <c r="C78" s="6">
         <v>46252</v>
       </c>
-      <c r="D78" s="8">
-        <v>0</v>
+      <c r="D78" s="10">
+        <v>18.58421</v>
       </c>
       <c r="E78" s="8">
-        <v>0</v>
+        <v>173710349</v>
       </c>
       <c r="F78" s="9">
         <v>5116</v>
       </c>
       <c r="G78" s="8">
-        <v>0</v>
+        <v>3228269602.77</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -14829,7 +14829,7 @@
         <v>46252</v>
       </c>
       <c r="D96" s="7">
-        <v>63.681798</v>
+        <v>63.682389</v>
       </c>
       <c r="E96" s="8">
         <v>396560996</v>
@@ -14838,7 +14838,7 @@
         <v>6</v>
       </c>
       <c r="G96" s="8">
-        <v>25253717373.37</v>
+        <v>25253951489.32</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -15358,7 +15358,7 @@
         <v>46252</v>
       </c>
       <c r="D119" s="7">
-        <v>1.793524</v>
+        <v>1.791388</v>
       </c>
       <c r="E119" s="8">
         <v>5346384</v>
@@ -15367,7 +15367,7 @@
         <v>57</v>
       </c>
       <c r="G119" s="8">
-        <v>9588865.61</v>
+        <v>9577448.01</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -15748,8 +15748,8 @@
       <c r="C136" s="6">
         <v>46252</v>
       </c>
-      <c r="D136" s="10">
-        <v>3.24458</v>
+      <c r="D136" s="7">
+        <v>3.244559</v>
       </c>
       <c r="E136" s="8">
         <v>69762716</v>
@@ -15758,7 +15758,7 @@
         <v>2024</v>
       </c>
       <c r="G136" s="8">
-        <v>226350719.27</v>
+        <v>226349219.39</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -16369,8 +16369,8 @@
       <c r="C163" s="6">
         <v>46252</v>
       </c>
-      <c r="D163" s="7">
-        <v>1.604889</v>
+      <c r="D163" s="10">
+        <v>1.60236</v>
       </c>
       <c r="E163" s="8">
         <v>52251334</v>
@@ -16379,7 +16379,7 @@
         <v>1059</v>
       </c>
       <c r="G163" s="8">
-        <v>83857611.54</v>
+        <v>83725436.25</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -16669,7 +16669,7 @@
         <v>46252</v>
       </c>
       <c r="D176" s="7">
-        <v>1.752124</v>
+        <v>1.752129</v>
       </c>
       <c r="E176" s="8">
         <v>1329029362</v>
@@ -16678,7 +16678,7 @@
         <v>2856</v>
       </c>
       <c r="G176" s="8">
-        <v>2328624671.86</v>
+        <v>2328630971.35</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -16875,8 +16875,8 @@
       <c r="C185" s="6">
         <v>46252</v>
       </c>
-      <c r="D185" s="12">
-        <v>1.237</v>
+      <c r="D185" s="7">
+        <v>1.241597</v>
       </c>
       <c r="E185" s="8">
         <v>98819369</v>
@@ -16885,7 +16885,7 @@
         <v>2782</v>
       </c>
       <c r="G185" s="8">
-        <v>122239572</v>
+        <v>122693862.98</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -17128,8 +17128,8 @@
       <c r="C196" s="6">
         <v>46252</v>
       </c>
-      <c r="D196" s="10">
-        <v>2.06514</v>
+      <c r="D196" s="7">
+        <v>2.065215</v>
       </c>
       <c r="E196" s="8">
         <v>67831653</v>
@@ -17138,7 +17138,7 @@
         <v>13</v>
       </c>
       <c r="G196" s="8">
-        <v>140081854.49</v>
+        <v>140086930.86</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -17151,17 +17151,17 @@
       <c r="C197" s="6">
         <v>46252</v>
       </c>
-      <c r="D197" s="8">
-        <v>0</v>
+      <c r="D197" s="7">
+        <v>2.931346</v>
       </c>
       <c r="E197" s="8">
-        <v>0</v>
+        <v>101063959</v>
       </c>
       <c r="F197" s="9">
         <v>28</v>
       </c>
       <c r="G197" s="8">
-        <v>0</v>
+        <v>296253470.59</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -18656,7 +18656,7 @@
         <v>2194</v>
       </c>
       <c r="G262" s="8">
-        <v>551534904.2</v>
+        <v>551534907</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -19061,7 +19061,7 @@
         <v>46252</v>
       </c>
       <c r="D280" s="7">
-        <v>5.326467</v>
+        <v>5.313141</v>
       </c>
       <c r="E280" s="8">
         <v>5053577</v>
@@ -19070,7 +19070,7 @@
         <v>1156</v>
       </c>
       <c r="G280" s="8">
-        <v>26917709.53</v>
+        <v>26850367.29</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -19383,7 +19383,7 @@
         <v>46252</v>
       </c>
       <c r="D294" s="7">
-        <v>48.078969</v>
+        <v>47.968191</v>
       </c>
       <c r="E294" s="8">
         <v>86320000</v>
@@ -19392,7 +19392,7 @@
         <v>629</v>
       </c>
       <c r="G294" s="8">
-        <v>4150176612.24</v>
+        <v>4140614286.1</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -19461,7 +19461,7 @@
         <v>656</v>
       </c>
       <c r="G297" s="8">
-        <v>9139878262.67</v>
+        <v>9139877927.61</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -19553,7 +19553,7 @@
         <v>309544</v>
       </c>
       <c r="G301" s="8">
-        <v>78918598488.52</v>
+        <v>78918598978.87</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -19590,7 +19590,7 @@
         <v>46252</v>
       </c>
       <c r="D303" s="7">
-        <v>6.887193</v>
+        <v>6.889866</v>
       </c>
       <c r="E303" s="8">
         <v>446326380</v>
@@ -19599,7 +19599,7 @@
         <v>15120</v>
       </c>
       <c r="G303" s="8">
-        <v>3073935798.62</v>
+        <v>3075128840.97</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -19705,7 +19705,7 @@
         <v>46252</v>
       </c>
       <c r="D308" s="7">
-        <v>1.290162</v>
+        <v>1.291474</v>
       </c>
       <c r="E308" s="8">
         <v>492012497</v>
@@ -19714,7 +19714,7 @@
         <v>121</v>
       </c>
       <c r="G308" s="8">
-        <v>634775638.89</v>
+        <v>635421331.45</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -20073,7 +20073,7 @@
         <v>46252</v>
       </c>
       <c r="D324" s="7">
-        <v>70.647789</v>
+        <v>70.643127</v>
       </c>
       <c r="E324" s="8">
         <v>4680779</v>
@@ -20082,7 +20082,7 @@
         <v>4</v>
       </c>
       <c r="G324" s="8">
-        <v>330686685.28</v>
+        <v>330664864.32</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
@@ -20096,7 +20096,7 @@
         <v>46252</v>
       </c>
       <c r="D325" s="7">
-        <v>74.292578</v>
+        <v>74.295512</v>
       </c>
       <c r="E325" s="8">
         <v>7358618</v>
@@ -20105,7 +20105,7 @@
         <v>3</v>
       </c>
       <c r="G325" s="8">
-        <v>546690703.27</v>
+        <v>546712294.96</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
@@ -20243,7 +20243,7 @@
         <v>3202</v>
       </c>
       <c r="G331" s="8">
-        <v>12461695793.55</v>
+        <v>12461695803.16</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
@@ -20303,7 +20303,7 @@
         <v>46252</v>
       </c>
       <c r="D334" s="7">
-        <v>101.168529</v>
+        <v>101.163486</v>
       </c>
       <c r="E334" s="8">
         <v>5734193</v>
@@ -20312,7 +20312,7 @@
         <v>2</v>
       </c>
       <c r="G334" s="8">
-        <v>580119868.08</v>
+        <v>580090955.32</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -20371,8 +20371,8 @@
       <c r="C337" s="6">
         <v>46252</v>
       </c>
-      <c r="D337" s="7">
-        <v>101.944768</v>
+      <c r="D337" s="10">
+        <v>101.92686</v>
       </c>
       <c r="E337" s="8">
         <v>22490084</v>
@@ -20381,7 +20381,7 @@
         <v>1</v>
       </c>
       <c r="G337" s="8">
-        <v>2292746405.1</v>
+        <v>2292343633.44</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -20602,7 +20602,7 @@
         <v>46252</v>
       </c>
       <c r="D347" s="7">
-        <v>71.914457</v>
+        <v>71.875562</v>
       </c>
       <c r="E347" s="8">
         <v>49667686</v>
@@ -20611,7 +20611,7 @@
         <v>1428</v>
       </c>
       <c r="G347" s="8">
-        <v>3571824653.94</v>
+        <v>3569892826.82</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
@@ -20648,7 +20648,7 @@
         <v>46252</v>
       </c>
       <c r="D349" s="7">
-        <v>14.783962</v>
+        <v>14.808473</v>
       </c>
       <c r="E349" s="8">
         <v>9541355</v>
@@ -20657,7 +20657,7 @@
         <v>1030</v>
       </c>
       <c r="G349" s="8">
-        <v>141059027.66</v>
+        <v>141292900.17</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
@@ -20740,7 +20740,7 @@
         <v>46252</v>
       </c>
       <c r="D353" s="7">
-        <v>1.427926</v>
+        <v>1.428089</v>
       </c>
       <c r="E353" s="8">
         <v>42885034</v>
@@ -20749,7 +20749,7 @@
         <v>2726</v>
       </c>
       <c r="G353" s="8">
-        <v>61236662.51</v>
+        <v>61243639.53</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -21084,8 +21084,8 @@
       <c r="C368" s="6">
         <v>46252</v>
       </c>
-      <c r="D368" s="10">
-        <v>9.93414</v>
+      <c r="D368" s="7">
+        <v>9.930919</v>
       </c>
       <c r="E368" s="8">
         <v>88833451</v>
@@ -21094,7 +21094,7 @@
         <v>11099</v>
       </c>
       <c r="G368" s="8">
-        <v>882483931.65</v>
+        <v>882197796.28</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -21291,8 +21291,8 @@
       <c r="C377" s="6">
         <v>46252</v>
       </c>
-      <c r="D377" s="7">
-        <v>86.309112</v>
+      <c r="D377" s="10">
+        <v>86.30846</v>
       </c>
       <c r="E377" s="8">
         <v>142488164</v>
@@ -21301,7 +21301,7 @@
         <v>4172</v>
       </c>
       <c r="G377" s="8">
-        <v>12298026853.22</v>
+        <v>12297934009.95</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
@@ -22119,8 +22119,8 @@
       <c r="C413" s="6">
         <v>46252</v>
       </c>
-      <c r="D413" s="10">
-        <v>1.36794</v>
+      <c r="D413" s="7">
+        <v>1.368543</v>
       </c>
       <c r="E413" s="8">
         <v>180871910</v>
@@ -22129,7 +22129,7 @@
         <v>1578</v>
       </c>
       <c r="G413" s="8">
-        <v>247421980.15</v>
+        <v>247530898.48</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.25">
@@ -22350,16 +22350,16 @@
         <v>46252</v>
       </c>
       <c r="D423" s="7">
-        <v>3.036997</v>
+        <v>3.048347</v>
       </c>
       <c r="E423" s="8">
-        <v>14627305</v>
+        <v>14634289</v>
       </c>
       <c r="F423" s="9">
         <v>503</v>
       </c>
       <c r="G423" s="8">
-        <v>44423080.59</v>
+        <v>44610398.09</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
@@ -22488,7 +22488,7 @@
         <v>46252</v>
       </c>
       <c r="D429" s="7">
-        <v>5.421571</v>
+        <v>5.421461</v>
       </c>
       <c r="E429" s="8">
         <v>40408496</v>
@@ -22497,7 +22497,7 @@
         <v>33</v>
       </c>
       <c r="G429" s="8">
-        <v>219077511.19</v>
+        <v>219073072.34</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
@@ -22533,8 +22533,8 @@
       <c r="C431" s="6">
         <v>46252</v>
       </c>
-      <c r="D431" s="10">
-        <v>4.82606</v>
+      <c r="D431" s="7">
+        <v>4.826064</v>
       </c>
       <c r="E431" s="8">
         <v>62327976</v>
@@ -22543,7 +22543,7 @@
         <v>391</v>
       </c>
       <c r="G431" s="8">
-        <v>300798550.09</v>
+        <v>300798804.75</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
@@ -22625,8 +22625,8 @@
       <c r="C435" s="6">
         <v>46252</v>
       </c>
-      <c r="D435" s="11">
-        <v>48.0053</v>
+      <c r="D435" s="10">
+        <v>47.85622</v>
       </c>
       <c r="E435" s="8">
         <v>91460000</v>
@@ -22635,7 +22635,7 @@
         <v>881</v>
       </c>
       <c r="G435" s="8">
-        <v>4390564703.61</v>
+        <v>4376929900.54</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
@@ -23201,7 +23201,7 @@
         <v>46252</v>
       </c>
       <c r="D460" s="7">
-        <v>48.119048</v>
+        <v>47.945513</v>
       </c>
       <c r="E460" s="8">
         <v>47890000.01</v>
@@ -23210,7 +23210,7 @@
         <v>475</v>
       </c>
       <c r="G460" s="8">
-        <v>2304421194.59</v>
+        <v>2296110631.24</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.25">
@@ -23568,8 +23568,8 @@
       <c r="C476" s="6">
         <v>46252</v>
       </c>
-      <c r="D476" s="10">
-        <v>69.00643</v>
+      <c r="D476" s="7">
+        <v>69.026298</v>
       </c>
       <c r="E476" s="8">
         <v>1902186677</v>
@@ -23578,7 +23578,7 @@
         <v>19369</v>
       </c>
       <c r="G476" s="8">
-        <v>131263111210.87</v>
+        <v>131300904381.88</v>
       </c>
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.25">
@@ -23868,7 +23868,7 @@
         <v>46252</v>
       </c>
       <c r="D489" s="7">
-        <v>4.898243</v>
+        <v>4.902523</v>
       </c>
       <c r="E489" s="8">
         <v>78654613</v>
@@ -23877,7 +23877,7 @@
         <v>549</v>
       </c>
       <c r="G489" s="8">
-        <v>385269368.89</v>
+        <v>385606018.88</v>
       </c>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
@@ -23982,17 +23982,17 @@
       <c r="C494" s="6">
         <v>46252</v>
       </c>
-      <c r="D494" s="8">
-        <v>0</v>
+      <c r="D494" s="7">
+        <v>1.320097</v>
       </c>
       <c r="E494" s="8">
-        <v>0</v>
+        <v>596985665</v>
       </c>
       <c r="F494" s="9">
         <v>4152</v>
       </c>
       <c r="G494" s="8">
-        <v>0</v>
+        <v>788078969.97</v>
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
@@ -24005,8 +24005,8 @@
       <c r="C495" s="6">
         <v>46252</v>
       </c>
-      <c r="D495" s="10">
-        <v>55.64702</v>
+      <c r="D495" s="7">
+        <v>55.518803</v>
       </c>
       <c r="E495" s="8">
         <v>184210000.01</v>
@@ -24015,7 +24015,7 @@
         <v>1658</v>
       </c>
       <c r="G495" s="8">
-        <v>10250737502.16</v>
+        <v>10227118777.47</v>
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
@@ -24052,7 +24052,7 @@
         <v>46252</v>
       </c>
       <c r="D497" s="7">
-        <v>47.979976</v>
+        <v>47.826168</v>
       </c>
       <c r="E497" s="8">
         <v>165640000</v>
@@ -24061,7 +24061,7 @@
         <v>1240</v>
       </c>
       <c r="G497" s="8">
-        <v>7947403248.12</v>
+        <v>7921926478.15</v>
       </c>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
@@ -24222,7 +24222,7 @@
         <v>147</v>
       </c>
       <c r="G504" s="8">
-        <v>1506708052.24</v>
+        <v>1506716309.68</v>
       </c>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
@@ -24465,8 +24465,8 @@
       <c r="C515" s="6">
         <v>46252</v>
       </c>
-      <c r="D515" s="7">
-        <v>5.640116</v>
+      <c r="D515" s="10">
+        <v>5.65401</v>
       </c>
       <c r="E515" s="8">
         <v>206504616.63</v>
@@ -24475,7 +24475,7 @@
         <v>2135</v>
       </c>
       <c r="G515" s="8">
-        <v>1164710094.89</v>
+        <v>1167579183.78</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.25">
@@ -24764,17 +24764,17 @@
       <c r="C528" s="6">
         <v>46252</v>
       </c>
-      <c r="D528" s="8">
-        <v>0</v>
+      <c r="D528" s="7">
+        <v>62.590699</v>
       </c>
       <c r="E528" s="8">
-        <v>0</v>
+        <v>3941000</v>
       </c>
       <c r="F528" s="9">
         <v>1</v>
       </c>
       <c r="G528" s="8">
-        <v>0</v>
+        <v>246669943.34</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.25">
@@ -24971,8 +24971,8 @@
       <c r="C537" s="6">
         <v>46252</v>
       </c>
-      <c r="D537" s="7">
-        <v>3.485721</v>
+      <c r="D537" s="10">
+        <v>3.48586</v>
       </c>
       <c r="E537" s="8">
         <v>321296145</v>
@@ -24981,7 +24981,7 @@
         <v>3267</v>
       </c>
       <c r="G537" s="8">
-        <v>1119948687.99</v>
+        <v>1119993245.25</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
@@ -25017,17 +25017,17 @@
       <c r="C539" s="6">
         <v>46252</v>
       </c>
-      <c r="D539" s="8">
-        <v>0</v>
+      <c r="D539" s="7">
+        <v>6.507293</v>
       </c>
       <c r="E539" s="8">
-        <v>0</v>
+        <v>222060386</v>
       </c>
       <c r="F539" s="9">
         <v>2</v>
       </c>
       <c r="G539" s="8">
-        <v>0</v>
+        <v>1445011973.19</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
@@ -25086,17 +25086,17 @@
       <c r="C542" s="6">
         <v>46252</v>
       </c>
-      <c r="D542" s="8">
-        <v>0</v>
+      <c r="D542" s="7">
+        <v>60.884152</v>
       </c>
       <c r="E542" s="8">
-        <v>0</v>
+        <v>194715</v>
       </c>
       <c r="F542" s="9">
         <v>1</v>
       </c>
       <c r="G542" s="8">
-        <v>0</v>
+        <v>11855057.61</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
@@ -25339,17 +25339,17 @@
       <c r="C553" s="6">
         <v>46252</v>
       </c>
-      <c r="D553" s="8">
-        <v>0</v>
+      <c r="D553" s="7">
+        <v>70.418154</v>
       </c>
       <c r="E553" s="8">
-        <v>0</v>
+        <v>5822807</v>
       </c>
       <c r="F553" s="9">
         <v>3</v>
       </c>
       <c r="G553" s="8">
-        <v>0</v>
+        <v>410031322.5</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
@@ -25500,17 +25500,17 @@
       <c r="C560" s="6">
         <v>46252</v>
       </c>
-      <c r="D560" s="8">
-        <v>0</v>
+      <c r="D560" s="7">
+        <v>10.879238</v>
       </c>
       <c r="E560" s="8">
-        <v>0</v>
+        <v>6927</v>
       </c>
       <c r="F560" s="9">
         <v>1</v>
       </c>
       <c r="G560" s="8">
-        <v>0</v>
+        <v>75360.48</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
@@ -25523,17 +25523,17 @@
       <c r="C561" s="6">
         <v>46252</v>
       </c>
-      <c r="D561" s="8">
-        <v>0</v>
+      <c r="D561" s="7">
+        <v>68.174405</v>
       </c>
       <c r="E561" s="8">
-        <v>0</v>
+        <v>23597904</v>
       </c>
       <c r="F561" s="9">
         <v>3</v>
       </c>
       <c r="G561" s="8">
-        <v>0</v>
+        <v>1608773073.71</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
@@ -25662,7 +25662,7 @@
         <v>46252</v>
       </c>
       <c r="D567" s="7">
-        <v>10.599769</v>
+        <v>10.591194</v>
       </c>
       <c r="E567" s="8">
         <v>7328667</v>
@@ -25671,7 +25671,7 @@
         <v>984</v>
       </c>
       <c r="G567" s="8">
-        <v>77682177.84</v>
+        <v>77619334.66</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
@@ -25730,17 +25730,17 @@
       <c r="C570" s="6">
         <v>46252</v>
       </c>
-      <c r="D570" s="8">
-        <v>0</v>
+      <c r="D570" s="7">
+        <v>64.179881</v>
       </c>
       <c r="E570" s="8">
-        <v>0</v>
+        <v>3663843</v>
       </c>
       <c r="F570" s="9">
         <v>2</v>
       </c>
       <c r="G570" s="8">
-        <v>0</v>
+        <v>235145006.12</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -25799,17 +25799,17 @@
       <c r="C573" s="6">
         <v>46252</v>
       </c>
-      <c r="D573" s="8">
-        <v>0</v>
+      <c r="D573" s="7">
+        <v>59.901102</v>
       </c>
       <c r="E573" s="8">
-        <v>0</v>
+        <v>9779449</v>
       </c>
       <c r="F573" s="9">
         <v>1</v>
       </c>
       <c r="G573" s="8">
-        <v>0</v>
+        <v>585799769.04</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
@@ -26053,16 +26053,16 @@
         <v>46252</v>
       </c>
       <c r="D584" s="7">
-        <v>4.300229</v>
+        <v>4.317331</v>
       </c>
       <c r="E584" s="8">
-        <v>3869752</v>
+        <v>3869775</v>
       </c>
       <c r="F584" s="9">
         <v>69</v>
       </c>
       <c r="G584" s="8">
-        <v>16640821.08</v>
+        <v>16707098.92</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.25">
@@ -26213,17 +26213,17 @@
       <c r="C591" s="6">
         <v>46252</v>
       </c>
-      <c r="D591" s="8">
-        <v>0</v>
+      <c r="D591" s="10">
+        <v>7.89062</v>
       </c>
       <c r="E591" s="8">
-        <v>0</v>
+        <v>540321023</v>
       </c>
       <c r="F591" s="9">
         <v>21275</v>
       </c>
       <c r="G591" s="8">
-        <v>0</v>
+        <v>4263467881.42</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.25">
@@ -26237,7 +26237,7 @@
         <v>46252</v>
       </c>
       <c r="D592" s="7">
-        <v>2.745823</v>
+        <v>2.745925</v>
       </c>
       <c r="E592" s="8">
         <v>1181567</v>
@@ -26246,7 +26246,7 @@
         <v>107</v>
       </c>
       <c r="G592" s="8">
-        <v>3244373.86</v>
+        <v>3244493.94</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
@@ -26581,17 +26581,17 @@
       <c r="C607" s="6">
         <v>46252</v>
       </c>
-      <c r="D607" s="8">
-        <v>0</v>
+      <c r="D607" s="7">
+        <v>1.605926</v>
       </c>
       <c r="E607" s="8">
-        <v>0</v>
+        <v>1237739</v>
       </c>
       <c r="F607" s="9">
         <v>477</v>
       </c>
       <c r="G607" s="8">
-        <v>0</v>
+        <v>1987717.73</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.25">
@@ -26604,8 +26604,8 @@
       <c r="C608" s="6">
         <v>46252</v>
       </c>
-      <c r="D608" s="10">
-        <v>4.73869</v>
+      <c r="D608" s="7">
+        <v>4.740517</v>
       </c>
       <c r="E608" s="8">
         <v>17104812</v>
@@ -26614,7 +26614,7 @@
         <v>763</v>
       </c>
       <c r="G608" s="8">
-        <v>81054409.99</v>
+        <v>81085643.54</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.25">
@@ -26627,8 +26627,8 @@
       <c r="C609" s="6">
         <v>46252</v>
       </c>
-      <c r="D609" s="10">
-        <v>4.93032</v>
+      <c r="D609" s="7">
+        <v>4.934398</v>
       </c>
       <c r="E609" s="8">
         <v>5267203</v>
@@ -26637,7 +26637,7 @@
         <v>452</v>
       </c>
       <c r="G609" s="8">
-        <v>25968996.95</v>
+        <v>25990476.1</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
@@ -26650,8 +26650,8 @@
       <c r="C610" s="6">
         <v>46252</v>
       </c>
-      <c r="D610" s="10">
-        <v>4.90226</v>
+      <c r="D610" s="7">
+        <v>4.902146</v>
       </c>
       <c r="E610" s="8">
         <v>7638244</v>
@@ -26660,7 +26660,7 @@
         <v>463</v>
       </c>
       <c r="G610" s="8">
-        <v>37444655.23</v>
+        <v>37443784.74</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.25">
@@ -26674,7 +26674,7 @@
         <v>46252</v>
       </c>
       <c r="D611" s="7">
-        <v>5.308199</v>
+        <v>5.307216</v>
       </c>
       <c r="E611" s="8">
         <v>9398225</v>
@@ -26683,7 +26683,7 @@
         <v>749</v>
       </c>
       <c r="G611" s="8">
-        <v>49887646.44</v>
+        <v>49878408.79</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
@@ -26995,17 +26995,17 @@
       <c r="C625" s="6">
         <v>46252</v>
       </c>
-      <c r="D625" s="8">
-        <v>0</v>
+      <c r="D625" s="7">
+        <v>45.203337</v>
       </c>
       <c r="E625" s="8">
-        <v>0</v>
+        <v>58637</v>
       </c>
       <c r="F625" s="9">
         <v>1</v>
       </c>
       <c r="G625" s="8">
-        <v>0</v>
+        <v>2650588.07</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.25">
@@ -27018,17 +27018,17 @@
       <c r="C626" s="6">
         <v>46252</v>
       </c>
-      <c r="D626" s="8">
-        <v>0</v>
+      <c r="D626" s="7">
+        <v>18.514386</v>
       </c>
       <c r="E626" s="8">
-        <v>0</v>
+        <v>40133042</v>
       </c>
       <c r="F626" s="9">
         <v>2813</v>
       </c>
       <c r="G626" s="8">
-        <v>0</v>
+        <v>743038630.23</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
@@ -27524,17 +27524,17 @@
       <c r="C648" s="6">
         <v>46252</v>
       </c>
-      <c r="D648" s="8">
-        <v>0</v>
+      <c r="D648" s="7">
+        <v>6.990482</v>
       </c>
       <c r="E648" s="8">
-        <v>0</v>
+        <v>4029467144</v>
       </c>
       <c r="F648" s="9">
         <v>1</v>
       </c>
       <c r="G648" s="8">
-        <v>0</v>
+        <v>28167916424.28</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
@@ -27662,17 +27662,17 @@
       <c r="C654" s="6">
         <v>46252</v>
       </c>
-      <c r="D654" s="8">
-        <v>0</v>
+      <c r="D654" s="7">
+        <v>5.967538</v>
       </c>
       <c r="E654" s="8">
-        <v>0</v>
+        <v>341860798</v>
       </c>
       <c r="F654" s="9">
         <v>1</v>
       </c>
       <c r="G654" s="8">
-        <v>0</v>
+        <v>2040067367.66</v>
       </c>
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.25">
@@ -27777,17 +27777,17 @@
       <c r="C659" s="6">
         <v>46252</v>
       </c>
-      <c r="D659" s="8">
-        <v>0</v>
+      <c r="D659" s="7">
+        <v>1.431334</v>
       </c>
       <c r="E659" s="8">
-        <v>0</v>
+        <v>803287799</v>
       </c>
       <c r="F659" s="9">
         <v>2714</v>
       </c>
       <c r="G659" s="8">
-        <v>0</v>
+        <v>1149773509.81</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
@@ -27800,17 +27800,17 @@
       <c r="C660" s="6">
         <v>46252</v>
       </c>
-      <c r="D660" s="8">
-        <v>0</v>
+      <c r="D660" s="7">
+        <v>12.603547</v>
       </c>
       <c r="E660" s="8">
-        <v>0</v>
+        <v>529605190</v>
       </c>
       <c r="F660" s="9">
         <v>52896</v>
       </c>
       <c r="G660" s="8">
-        <v>0</v>
+        <v>6674903918.53</v>
       </c>
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.25">
@@ -27915,17 +27915,17 @@
       <c r="C665" s="6">
         <v>46252</v>
       </c>
-      <c r="D665" s="8">
-        <v>0</v>
+      <c r="D665" s="7">
+        <v>18.423229</v>
       </c>
       <c r="E665" s="8">
-        <v>0</v>
+        <v>22115</v>
       </c>
       <c r="F665" s="9">
         <v>1</v>
       </c>
       <c r="G665" s="8">
-        <v>0</v>
+        <v>407429.71</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
@@ -28007,17 +28007,17 @@
       <c r="C669" s="6">
         <v>46252</v>
       </c>
-      <c r="D669" s="8">
-        <v>0</v>
+      <c r="D669" s="7">
+        <v>4.074285</v>
       </c>
       <c r="E669" s="8">
-        <v>0</v>
+        <v>5020082762</v>
       </c>
       <c r="F669" s="9">
         <v>1</v>
       </c>
       <c r="G669" s="8">
-        <v>0</v>
+        <v>20453250134.53</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
@@ -28191,17 +28191,17 @@
       <c r="C677" s="6">
         <v>46252</v>
       </c>
-      <c r="D677" s="8">
-        <v>0</v>
+      <c r="D677" s="10">
+        <v>7.62998</v>
       </c>
       <c r="E677" s="8">
-        <v>0</v>
+        <v>187192015</v>
       </c>
       <c r="F677" s="9">
         <v>4164</v>
       </c>
       <c r="G677" s="8">
-        <v>0</v>
+        <v>1428271297.48</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
@@ -28237,17 +28237,17 @@
       <c r="C679" s="6">
         <v>46252</v>
       </c>
-      <c r="D679" s="8">
-        <v>0</v>
+      <c r="D679" s="10">
+        <v>5.00425</v>
       </c>
       <c r="E679" s="8">
-        <v>0</v>
+        <v>80112120</v>
       </c>
       <c r="F679" s="9">
         <v>5800</v>
       </c>
       <c r="G679" s="8">
-        <v>0</v>
+        <v>400901049.2</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
@@ -28260,17 +28260,17 @@
       <c r="C680" s="6">
         <v>46252</v>
       </c>
-      <c r="D680" s="8">
-        <v>0</v>
+      <c r="D680" s="7">
+        <v>8.694325</v>
       </c>
       <c r="E680" s="8">
-        <v>0</v>
+        <v>200211346</v>
       </c>
       <c r="F680" s="9">
         <v>5225</v>
       </c>
       <c r="G680" s="8">
-        <v>0</v>
+        <v>1740702424.96</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -28375,17 +28375,17 @@
       <c r="C685" s="6">
         <v>46252</v>
       </c>
-      <c r="D685" s="8">
-        <v>0</v>
+      <c r="D685" s="7">
+        <v>7.681805</v>
       </c>
       <c r="E685" s="8">
-        <v>0</v>
+        <v>496253176</v>
       </c>
       <c r="F685" s="9">
         <v>9911</v>
       </c>
       <c r="G685" s="8">
-        <v>0</v>
+        <v>3812120007.83</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
@@ -28444,17 +28444,17 @@
       <c r="C688" s="6">
         <v>46252</v>
       </c>
-      <c r="D688" s="8">
-        <v>0</v>
+      <c r="D688" s="7">
+        <v>8.798739</v>
       </c>
       <c r="E688" s="8">
-        <v>0</v>
+        <v>11415401</v>
       </c>
       <c r="F688" s="9">
         <v>1378</v>
       </c>
       <c r="G688" s="8">
-        <v>0</v>
+        <v>100441132.39</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
@@ -28467,17 +28467,17 @@
       <c r="C689" s="6">
         <v>46252</v>
       </c>
-      <c r="D689" s="8">
-        <v>0</v>
+      <c r="D689" s="7">
+        <v>7.974857</v>
       </c>
       <c r="E689" s="8">
-        <v>0</v>
+        <v>9207333</v>
       </c>
       <c r="F689" s="9">
         <v>2401</v>
       </c>
       <c r="G689" s="8">
-        <v>0</v>
+        <v>73427159.7</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
@@ -28743,17 +28743,17 @@
       <c r="C701" s="6">
         <v>46252</v>
       </c>
-      <c r="D701" s="8">
-        <v>0</v>
+      <c r="D701" s="7">
+        <v>4.324883</v>
       </c>
       <c r="E701" s="8">
-        <v>0</v>
+        <v>127533146</v>
       </c>
       <c r="F701" s="9">
         <v>1086</v>
       </c>
       <c r="G701" s="8">
-        <v>0</v>
+        <v>551565978.08</v>
       </c>
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.25">
@@ -28905,7 +28905,7 @@
         <v>46252</v>
       </c>
       <c r="D708" s="7">
-        <v>16834.507839</v>
+        <v>16834.485954</v>
       </c>
       <c r="E708" s="8">
         <v>3698337</v>
@@ -28914,7 +28914,7 @@
         <v>18</v>
       </c>
       <c r="G708" s="8">
-        <v>62259683218.88</v>
+        <v>62259602277.9</v>
       </c>
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.25">
@@ -29227,7 +29227,7 @@
         <v>46252</v>
       </c>
       <c r="D722" s="7">
-        <v>26.117043</v>
+        <v>26.117786</v>
       </c>
       <c r="E722" s="8">
         <v>109096943</v>
@@ -29236,7 +29236,7 @@
         <v>12</v>
       </c>
       <c r="G722" s="8">
-        <v>2849289550.46</v>
+        <v>2849370660.03</v>
       </c>
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.25">
@@ -30078,7 +30078,7 @@
         <v>46252</v>
       </c>
       <c r="D759" s="7">
-        <v>0.369679</v>
+        <v>0.369849</v>
       </c>
       <c r="E759" s="8">
         <v>3758848520</v>
@@ -30087,7 +30087,7 @@
         <v>2551</v>
       </c>
       <c r="G759" s="8">
-        <v>1389566213.65</v>
+        <v>1390206766.72</v>
       </c>
     </row>
     <row r="760" spans="1:7" x14ac:dyDescent="0.25">
@@ -30514,8 +30514,8 @@
       <c r="C778" s="6">
         <v>46252</v>
       </c>
-      <c r="D778" s="11">
-        <v>2.0051</v>
+      <c r="D778" s="7">
+        <v>2.006023</v>
       </c>
       <c r="E778" s="8">
         <v>16391656</v>
@@ -30524,7 +30524,7 @@
         <v>223</v>
       </c>
       <c r="G778" s="8">
-        <v>32866904.85</v>
+        <v>32882032.53</v>
       </c>
     </row>
     <row r="779" spans="1:7" x14ac:dyDescent="0.25">
@@ -30538,7 +30538,7 @@
         <v>46252</v>
       </c>
       <c r="D779" s="7">
-        <v>1.108039</v>
+        <v>1.107951</v>
       </c>
       <c r="E779" s="8">
         <v>125132280</v>
@@ -30547,7 +30547,7 @@
         <v>845</v>
       </c>
       <c r="G779" s="8">
-        <v>138651416.22</v>
+        <v>138640474.91</v>
       </c>
     </row>
     <row r="780" spans="1:7" x14ac:dyDescent="0.25">
@@ -31159,7 +31159,7 @@
         <v>46252</v>
       </c>
       <c r="D806" s="7">
-        <v>1.740776</v>
+        <v>1.740787</v>
       </c>
       <c r="E806" s="8">
         <v>45366370</v>
@@ -31168,7 +31168,7 @@
         <v>2814</v>
       </c>
       <c r="G806" s="8">
-        <v>78972700.09</v>
+        <v>78973168.48</v>
       </c>
     </row>
     <row r="807" spans="1:7" x14ac:dyDescent="0.25">
@@ -31435,7 +31435,7 @@
         <v>46252</v>
       </c>
       <c r="D818" s="7">
-        <v>3.880251</v>
+        <v>3.880095</v>
       </c>
       <c r="E818" s="8">
         <v>54301341</v>
@@ -31444,7 +31444,7 @@
         <v>16</v>
       </c>
       <c r="G818" s="8">
-        <v>210702843.28</v>
+        <v>210694337.95</v>
       </c>
     </row>
     <row r="819" spans="1:7" x14ac:dyDescent="0.25">
@@ -32447,7 +32447,7 @@
         <v>46252</v>
       </c>
       <c r="D862" s="7">
-        <v>4.619635</v>
+        <v>4.619645</v>
       </c>
       <c r="E862" s="8">
         <v>382831186</v>
@@ -32456,7 +32456,7 @@
         <v>11</v>
       </c>
       <c r="G862" s="8">
-        <v>1768540454.32</v>
+        <v>1768544280.19</v>
       </c>
     </row>
     <row r="863" spans="1:7" x14ac:dyDescent="0.25">
@@ -32585,7 +32585,7 @@
         <v>46252</v>
       </c>
       <c r="D868" s="7">
-        <v>53.603327</v>
+        <v>53.610863</v>
       </c>
       <c r="E868" s="8">
         <v>31995937.25</v>
@@ -32594,7 +32594,7 @@
         <v>149</v>
       </c>
       <c r="G868" s="8">
-        <v>1715088673.16</v>
+        <v>1715329807.79</v>
       </c>
     </row>
     <row r="869" spans="1:7" x14ac:dyDescent="0.25">
@@ -32722,17 +32722,17 @@
       <c r="C874" s="6">
         <v>46252</v>
       </c>
-      <c r="D874" s="8">
-        <v>0</v>
+      <c r="D874" s="7">
+        <v>7.232006</v>
       </c>
       <c r="E874" s="8">
-        <v>0</v>
+        <v>4673858</v>
       </c>
       <c r="F874" s="9">
         <v>398</v>
       </c>
       <c r="G874" s="8">
-        <v>0</v>
+        <v>33801367.68</v>
       </c>
     </row>
     <row r="875" spans="1:7" x14ac:dyDescent="0.25">
@@ -32769,16 +32769,16 @@
         <v>46252</v>
       </c>
       <c r="D876" s="7">
-        <v>63.890739</v>
+        <v>63.892179</v>
       </c>
       <c r="E876" s="8">
-        <v>4484949</v>
+        <v>4530576</v>
       </c>
       <c r="F876" s="9">
         <v>3</v>
       </c>
       <c r="G876" s="8">
-        <v>286546706.64</v>
+        <v>289468374.64</v>
       </c>
     </row>
     <row r="877" spans="1:7" x14ac:dyDescent="0.25">
@@ -32976,7 +32976,7 @@
         <v>46252</v>
       </c>
       <c r="D885" s="7">
-        <v>1.513944</v>
+        <v>1.513817</v>
       </c>
       <c r="E885" s="8">
         <v>121251595</v>
@@ -32985,7 +32985,7 @@
         <v>1207</v>
       </c>
       <c r="G885" s="8">
-        <v>183568184.28</v>
+        <v>183552767.85</v>
       </c>
     </row>
     <row r="886" spans="1:7" x14ac:dyDescent="0.25">
@@ -33091,7 +33091,7 @@
         <v>46252</v>
       </c>
       <c r="D890" s="7">
-        <v>7.063323</v>
+        <v>7.063254</v>
       </c>
       <c r="E890" s="8">
         <v>43526148</v>
@@ -33100,7 +33100,7 @@
         <v>13</v>
       </c>
       <c r="G890" s="8">
-        <v>307439243.18</v>
+        <v>307436248</v>
       </c>
     </row>
     <row r="891" spans="1:7" x14ac:dyDescent="0.25">
@@ -33160,7 +33160,7 @@
         <v>46252</v>
       </c>
       <c r="D893" s="7">
-        <v>8.172239</v>
+        <v>8.172308</v>
       </c>
       <c r="E893" s="8">
         <v>133150986</v>
@@ -33169,7 +33169,7 @@
         <v>6472</v>
       </c>
       <c r="G893" s="8">
-        <v>1088141686.36</v>
+        <v>1088150881.09</v>
       </c>
     </row>
     <row r="894" spans="1:7" x14ac:dyDescent="0.25">
@@ -33412,17 +33412,17 @@
       <c r="C904" s="6">
         <v>46252</v>
       </c>
-      <c r="D904" s="8">
-        <v>0</v>
+      <c r="D904" s="7">
+        <v>14.835709</v>
       </c>
       <c r="E904" s="8">
-        <v>0</v>
+        <v>15441990</v>
       </c>
       <c r="F904" s="9">
         <v>373</v>
       </c>
       <c r="G904" s="8">
-        <v>0</v>
+        <v>229092871.78</v>
       </c>
     </row>
     <row r="905" spans="1:7" x14ac:dyDescent="0.25">
@@ -33574,7 +33574,7 @@
         <v>46252</v>
       </c>
       <c r="D911" s="7">
-        <v>4.035776</v>
+        <v>4.035787</v>
       </c>
       <c r="E911" s="8">
         <v>147588046</v>
@@ -33583,7 +33583,7 @@
         <v>13</v>
       </c>
       <c r="G911" s="8">
-        <v>595632344.17</v>
+        <v>595633907.1</v>
       </c>
     </row>
     <row r="912" spans="1:7" x14ac:dyDescent="0.25">
@@ -33619,8 +33619,8 @@
       <c r="C913" s="6">
         <v>46252</v>
       </c>
-      <c r="D913" s="7">
-        <v>4.581314</v>
+      <c r="D913" s="10">
+        <v>4.58158</v>
       </c>
       <c r="E913" s="8">
         <v>3865796400</v>
@@ -33629,7 +33629,7 @@
         <v>6048</v>
       </c>
       <c r="G913" s="8">
-        <v>17710427655.73</v>
+        <v>17711455444.28</v>
       </c>
     </row>
     <row r="914" spans="1:7" x14ac:dyDescent="0.25">
@@ -33643,7 +33643,7 @@
         <v>46252</v>
       </c>
       <c r="D914" s="7">
-        <v>6.302933</v>
+        <v>6.302943</v>
       </c>
       <c r="E914" s="8">
         <v>1082393506</v>
@@ -33652,7 +33652,7 @@
         <v>6479</v>
       </c>
       <c r="G914" s="8">
-        <v>6822253795.73</v>
+        <v>6822264073.66</v>
       </c>
     </row>
     <row r="915" spans="1:7" x14ac:dyDescent="0.25">
@@ -33688,8 +33688,8 @@
       <c r="C916" s="6">
         <v>46252</v>
       </c>
-      <c r="D916" s="7">
-        <v>56.858621</v>
+      <c r="D916" s="10">
+        <v>56.86012</v>
       </c>
       <c r="E916" s="8">
         <v>9907429</v>
@@ -33698,7 +33698,7 @@
         <v>1</v>
       </c>
       <c r="G916" s="8">
-        <v>563322752.12</v>
+        <v>563337601.06</v>
       </c>
     </row>
     <row r="917" spans="1:7" x14ac:dyDescent="0.25">
@@ -33712,7 +33712,7 @@
         <v>46252</v>
       </c>
       <c r="D917" s="7">
-        <v>0.734052</v>
+        <v>0.732771</v>
       </c>
       <c r="E917" s="8">
         <v>803906870</v>
@@ -33721,7 +33721,7 @@
         <v>16</v>
       </c>
       <c r="G917" s="8">
-        <v>590109293.69</v>
+        <v>589080017.06</v>
       </c>
     </row>
     <row r="918" spans="1:7" x14ac:dyDescent="0.25">
@@ -33735,7 +33735,7 @@
         <v>46252</v>
       </c>
       <c r="D918" s="7">
-        <v>0.894614</v>
+        <v>0.894635</v>
       </c>
       <c r="E918" s="8">
         <v>1216724709.57</v>
@@ -33744,7 +33744,7 @@
         <v>15265</v>
       </c>
       <c r="G918" s="8">
-        <v>1088498863.69</v>
+        <v>1088524610.06</v>
       </c>
     </row>
     <row r="919" spans="1:7" x14ac:dyDescent="0.25">
@@ -33803,8 +33803,8 @@
       <c r="C921" s="6">
         <v>46252</v>
       </c>
-      <c r="D921" s="7">
-        <v>0.122992</v>
+      <c r="D921" s="12">
+        <v>0.123</v>
       </c>
       <c r="E921" s="8">
         <v>1105011730</v>
@@ -33813,7 +33813,7 @@
         <v>22</v>
       </c>
       <c r="G921" s="8">
-        <v>135908016.99</v>
+        <v>135916438.3</v>
       </c>
     </row>
     <row r="922" spans="1:7" x14ac:dyDescent="0.25">
@@ -33919,7 +33919,7 @@
         <v>46252</v>
       </c>
       <c r="D926" s="7">
-        <v>0.180786</v>
+        <v>0.180911</v>
       </c>
       <c r="E926" s="8">
         <v>40206496514</v>
@@ -33928,7 +33928,7 @@
         <v>165</v>
       </c>
       <c r="G926" s="8">
-        <v>7268783659.36</v>
+        <v>7273777631.11</v>
       </c>
     </row>
     <row r="927" spans="1:7" x14ac:dyDescent="0.25">
@@ -34011,7 +34011,7 @@
         <v>46252</v>
       </c>
       <c r="D930" s="7">
-        <v>1.312371</v>
+        <v>1.312372</v>
       </c>
       <c r="E930" s="8">
         <v>896074324</v>
@@ -34020,7 +34020,7 @@
         <v>786</v>
       </c>
       <c r="G930" s="8">
-        <v>1175982309.96</v>
+        <v>1175982630.71</v>
       </c>
     </row>
     <row r="931" spans="1:7" x14ac:dyDescent="0.25">
@@ -34056,17 +34056,17 @@
       <c r="C932" s="6">
         <v>46252</v>
       </c>
-      <c r="D932" s="8">
-        <v>0</v>
+      <c r="D932" s="7">
+        <v>7.421178</v>
       </c>
       <c r="E932" s="8">
-        <v>0</v>
+        <v>74179379</v>
       </c>
       <c r="F932" s="9">
         <v>2003</v>
       </c>
       <c r="G932" s="8">
-        <v>0</v>
+        <v>550498357.42</v>
       </c>
     </row>
     <row r="933" spans="1:7" x14ac:dyDescent="0.25">
@@ -34148,8 +34148,8 @@
       <c r="C936" s="6">
         <v>46252</v>
       </c>
-      <c r="D936" s="10">
-        <v>6.94029</v>
+      <c r="D936" s="7">
+        <v>6.940157</v>
       </c>
       <c r="E936" s="8">
         <v>42020927</v>
@@ -34158,7 +34158,7 @@
         <v>51</v>
       </c>
       <c r="G936" s="8">
-        <v>291637418.09</v>
+        <v>291631836.93</v>
       </c>
     </row>
     <row r="937" spans="1:7" x14ac:dyDescent="0.25">
@@ -34333,7 +34333,7 @@
         <v>46252</v>
       </c>
       <c r="D944" s="7">
-        <v>10.319915</v>
+        <v>10.319975</v>
       </c>
       <c r="E944" s="8">
         <v>26517213</v>
@@ -34342,7 +34342,7 @@
         <v>12</v>
       </c>
       <c r="G944" s="8">
-        <v>273655392.13</v>
+        <v>273656964.74</v>
       </c>
     </row>
     <row r="945" spans="1:7" x14ac:dyDescent="0.25">
@@ -34471,7 +34471,7 @@
         <v>46252</v>
       </c>
       <c r="D950" s="7">
-        <v>67.661438</v>
+        <v>67.660661</v>
       </c>
       <c r="E950" s="8">
         <v>6408826</v>
@@ -34480,7 +34480,7 @@
         <v>55</v>
       </c>
       <c r="G950" s="8">
-        <v>433630380.81</v>
+        <v>433625405.25</v>
       </c>
     </row>
     <row r="951" spans="1:7" x14ac:dyDescent="0.25">
@@ -34562,8 +34562,8 @@
       <c r="C954" s="6">
         <v>46252</v>
       </c>
-      <c r="D954" s="10">
-        <v>6.41989</v>
+      <c r="D954" s="7">
+        <v>6.428469</v>
       </c>
       <c r="E954" s="8">
         <v>1994370.66</v>
@@ -34572,7 +34572,7 @@
         <v>717</v>
       </c>
       <c r="G954" s="8">
-        <v>12803639.98</v>
+        <v>12820748.98</v>
       </c>
     </row>
     <row r="955" spans="1:7" x14ac:dyDescent="0.25">
@@ -34655,7 +34655,7 @@
         <v>46252</v>
       </c>
       <c r="D958" s="7">
-        <v>4.739985</v>
+        <v>4.739949</v>
       </c>
       <c r="E958" s="8">
         <v>284279113</v>
@@ -34664,7 +34664,7 @@
         <v>1201</v>
       </c>
       <c r="G958" s="8">
-        <v>1347478857.47</v>
+        <v>1347468579.71</v>
       </c>
     </row>
     <row r="959" spans="1:7" x14ac:dyDescent="0.25">
@@ -34793,7 +34793,7 @@
         <v>46252</v>
       </c>
       <c r="D964" s="7">
-        <v>5.983682</v>
+        <v>5.983708</v>
       </c>
       <c r="E964" s="8">
         <v>45771790.29</v>
@@ -34802,7 +34802,7 @@
         <v>26</v>
       </c>
       <c r="G964" s="8">
-        <v>273883832.78</v>
+        <v>273885041.68</v>
       </c>
     </row>
     <row r="965" spans="1:7" x14ac:dyDescent="0.25">
@@ -34848,7 +34848,7 @@
         <v>333</v>
       </c>
       <c r="G966" s="8">
-        <v>93662855.7</v>
+        <v>93662855.54</v>
       </c>
     </row>
     <row r="967" spans="1:7" x14ac:dyDescent="0.25">
@@ -34908,7 +34908,7 @@
         <v>46252</v>
       </c>
       <c r="D969" s="7">
-        <v>1.337175</v>
+        <v>1.337169</v>
       </c>
       <c r="E969" s="8">
         <v>4370883210</v>
@@ -34917,7 +34917,7 @@
         <v>16</v>
       </c>
       <c r="G969" s="8">
-        <v>5844636076.88</v>
+        <v>5844610344.97</v>
       </c>
     </row>
     <row r="970" spans="1:7" x14ac:dyDescent="0.25">
@@ -34977,7 +34977,7 @@
         <v>46252</v>
       </c>
       <c r="D972" s="7">
-        <v>10.877376</v>
+        <v>10.903299</v>
       </c>
       <c r="E972" s="8">
         <v>9188142</v>
@@ -34986,7 +34986,7 @@
         <v>87</v>
       </c>
       <c r="G972" s="8">
-        <v>99942877.13</v>
+        <v>100181057.76</v>
       </c>
     </row>
     <row r="973" spans="1:7" x14ac:dyDescent="0.25">
@@ -35414,7 +35414,7 @@
         <v>46252</v>
       </c>
       <c r="D991" s="7">
-        <v>72.715321</v>
+        <v>57.836873</v>
       </c>
       <c r="E991" s="8">
         <v>5926148</v>
@@ -35423,7 +35423,7 @@
         <v>12</v>
       </c>
       <c r="G991" s="8">
-        <v>430921753.77</v>
+        <v>342749869.93</v>
       </c>
     </row>
     <row r="992" spans="1:7" x14ac:dyDescent="0.25">
@@ -36173,7 +36173,7 @@
         <v>46252</v>
       </c>
       <c r="D1024" s="7">
-        <v>6.811716</v>
+        <v>6.811762</v>
       </c>
       <c r="E1024" s="8">
         <v>78703596</v>
@@ -36182,7 +36182,7 @@
         <v>5094</v>
       </c>
       <c r="G1024" s="8">
-        <v>536106509.67</v>
+        <v>536110133.57</v>
       </c>
     </row>
     <row r="1025" spans="1:7" x14ac:dyDescent="0.25">
@@ -36748,7 +36748,7 @@
         <v>46252</v>
       </c>
       <c r="D1049" s="7">
-        <v>55.705735</v>
+        <v>55.610866</v>
       </c>
       <c r="E1049" s="8">
         <v>82260000</v>
@@ -36757,7 +36757,7 @@
         <v>858</v>
       </c>
       <c r="G1049" s="8">
-        <v>4582353726.17</v>
+        <v>4574549859.05</v>
       </c>
     </row>
     <row r="1050" spans="1:7" x14ac:dyDescent="0.25">
@@ -37115,8 +37115,8 @@
       <c r="C1065" s="6">
         <v>46252</v>
       </c>
-      <c r="D1065" s="7">
-        <v>3.154404</v>
+      <c r="D1065" s="10">
+        <v>3.15443</v>
       </c>
       <c r="E1065" s="8">
         <v>142257981</v>
@@ -37125,7 +37125,7 @@
         <v>700</v>
       </c>
       <c r="G1065" s="8">
-        <v>448739127.04</v>
+        <v>448742796.69</v>
       </c>
     </row>
     <row r="1066" spans="1:7" x14ac:dyDescent="0.25">
@@ -37208,7 +37208,7 @@
         <v>46252</v>
       </c>
       <c r="D1069" s="7">
-        <v>0.145184</v>
+        <v>0.145185</v>
       </c>
       <c r="E1069" s="8">
         <v>203403320</v>
@@ -37217,7 +37217,7 @@
         <v>145</v>
       </c>
       <c r="G1069" s="8">
-        <v>29530816.74</v>
+        <v>29531054.13</v>
       </c>
     </row>
     <row r="1070" spans="1:7" x14ac:dyDescent="0.25">
@@ -37231,7 +37231,7 @@
         <v>46252</v>
       </c>
       <c r="D1070" s="7">
-        <v>21.329431</v>
+        <v>21.329507</v>
       </c>
       <c r="E1070" s="8">
         <v>2133378</v>
@@ -37240,7 +37240,7 @@
         <v>605</v>
       </c>
       <c r="G1070" s="8">
-        <v>45503737.84</v>
+        <v>45503900.27</v>
       </c>
     </row>
     <row r="1071" spans="1:7" x14ac:dyDescent="0.25">
@@ -37322,8 +37322,8 @@
       <c r="C1074" s="6">
         <v>46252</v>
       </c>
-      <c r="D1074" s="10">
-        <v>0.49323</v>
+      <c r="D1074" s="7">
+        <v>0.523738</v>
       </c>
       <c r="E1074" s="8">
         <v>2889914966</v>
@@ -37332,7 +37332,7 @@
         <v>1134</v>
       </c>
       <c r="G1074" s="8">
-        <v>1425392085.11</v>
+        <v>1513557485.63</v>
       </c>
     </row>
     <row r="1075" spans="1:7" x14ac:dyDescent="0.25">
@@ -37369,7 +37369,7 @@
         <v>46252</v>
       </c>
       <c r="D1076" s="7">
-        <v>48.106886</v>
+        <v>47.986407</v>
       </c>
       <c r="E1076" s="8">
         <v>116190000.01</v>
@@ -37378,7 +37378,7 @@
         <v>1025</v>
       </c>
       <c r="G1076" s="8">
-        <v>5589539112.82</v>
+        <v>5575540592.38</v>
       </c>
     </row>
     <row r="1077" spans="1:7" x14ac:dyDescent="0.25">
@@ -37506,8 +37506,8 @@
       <c r="C1082" s="6">
         <v>46252</v>
       </c>
-      <c r="D1082" s="10">
-        <v>64.88147</v>
+      <c r="D1082" s="7">
+        <v>64.718426</v>
       </c>
       <c r="E1082" s="8">
         <v>25335000</v>
@@ -37516,7 +37516,7 @@
         <v>361</v>
       </c>
       <c r="G1082" s="8">
-        <v>1643772032.94</v>
+        <v>1639641321.77</v>
       </c>
     </row>
     <row r="1083" spans="1:7" x14ac:dyDescent="0.25">
@@ -37622,7 +37622,7 @@
         <v>46252</v>
       </c>
       <c r="D1087" s="7">
-        <v>45.528758</v>
+        <v>45.529363</v>
       </c>
       <c r="E1087" s="8">
         <v>2415590</v>
@@ -37631,7 +37631,7 @@
         <v>1</v>
       </c>
       <c r="G1087" s="8">
-        <v>109978813.64</v>
+        <v>109980274.73</v>
       </c>
     </row>
     <row r="1088" spans="1:7" x14ac:dyDescent="0.25">
@@ -37897,8 +37897,8 @@
       <c r="C1099" s="6">
         <v>46252</v>
       </c>
-      <c r="D1099" s="7">
-        <v>0.721879</v>
+      <c r="D1099" s="10">
+        <v>0.75186</v>
       </c>
       <c r="E1099" s="8">
         <v>813649385</v>
@@ -37907,7 +37907,7 @@
         <v>3669</v>
       </c>
       <c r="G1099" s="8">
-        <v>587356177.7</v>
+        <v>611750351.85</v>
       </c>
     </row>
     <row r="1100" spans="1:7" x14ac:dyDescent="0.25">
@@ -38013,7 +38013,7 @@
         <v>46252</v>
       </c>
       <c r="D1104" s="7">
-        <v>1.270987</v>
+        <v>1.270999</v>
       </c>
       <c r="E1104" s="8">
         <v>433373921</v>
@@ -38022,7 +38022,7 @@
         <v>139</v>
       </c>
       <c r="G1104" s="8">
-        <v>550812782.22</v>
+        <v>550817839.75</v>
       </c>
     </row>
     <row r="1105" spans="1:7" x14ac:dyDescent="0.25">
@@ -38818,7 +38818,7 @@
         <v>46252</v>
       </c>
       <c r="D1139" s="7">
-        <v>1.276213</v>
+        <v>1.280045</v>
       </c>
       <c r="E1139" s="8">
         <v>394815941</v>
@@ -38827,7 +38827,7 @@
         <v>959</v>
       </c>
       <c r="G1139" s="8">
-        <v>503869092.4</v>
+        <v>505382111.42</v>
       </c>
     </row>
     <row r="1140" spans="1:7" x14ac:dyDescent="0.25">
@@ -39002,16 +39002,16 @@
         <v>46252</v>
       </c>
       <c r="D1147" s="7">
-        <v>7.794591</v>
+        <v>7.851579</v>
       </c>
       <c r="E1147" s="8">
-        <v>6716219</v>
+        <v>6718193</v>
       </c>
       <c r="F1147" s="9">
         <v>774</v>
       </c>
       <c r="G1147" s="8">
-        <v>52350180.46</v>
+        <v>52748423.38</v>
       </c>
     </row>
     <row r="1148" spans="1:7" x14ac:dyDescent="0.25">
@@ -39048,16 +39048,16 @@
         <v>46252</v>
       </c>
       <c r="D1149" s="7">
-        <v>10.917678</v>
+        <v>11.057051</v>
       </c>
       <c r="E1149" s="8">
-        <v>90811765</v>
+        <v>90696842</v>
       </c>
       <c r="F1149" s="9">
         <v>7602</v>
       </c>
       <c r="G1149" s="8">
-        <v>991453605.5</v>
+        <v>1002839614.58</v>
       </c>
     </row>
     <row r="1150" spans="1:7" x14ac:dyDescent="0.25">
@@ -39071,7 +39071,7 @@
         <v>46252</v>
       </c>
       <c r="D1150" s="7">
-        <v>4.502232</v>
+        <v>4.444027</v>
       </c>
       <c r="E1150" s="8">
         <v>6085154</v>
@@ -39080,7 +39080,7 @@
         <v>29</v>
       </c>
       <c r="G1150" s="8">
-        <v>27396774.51</v>
+        <v>27042587.83</v>
       </c>
     </row>
     <row r="1151" spans="1:7" x14ac:dyDescent="0.25">
@@ -39323,17 +39323,17 @@
       <c r="C1161" s="6">
         <v>46252</v>
       </c>
-      <c r="D1161" s="8">
-        <v>0</v>
+      <c r="D1161" s="7">
+        <v>1.602059</v>
       </c>
       <c r="E1161" s="8">
-        <v>0</v>
+        <v>2651303752</v>
       </c>
       <c r="F1161" s="9">
         <v>13</v>
       </c>
       <c r="G1161" s="8">
-        <v>0</v>
+        <v>4247545031.07</v>
       </c>
     </row>
     <row r="1162" spans="1:7" x14ac:dyDescent="0.25">
@@ -39346,17 +39346,17 @@
       <c r="C1162" s="6">
         <v>46252</v>
       </c>
-      <c r="D1162" s="8">
-        <v>0</v>
+      <c r="D1162" s="7">
+        <v>2.121156</v>
       </c>
       <c r="E1162" s="8">
-        <v>0</v>
+        <v>1808708408</v>
       </c>
       <c r="F1162" s="9">
         <v>15</v>
       </c>
       <c r="G1162" s="8">
-        <v>0</v>
+        <v>3836553471.35</v>
       </c>
     </row>
     <row r="1163" spans="1:7" x14ac:dyDescent="0.25">
@@ -40014,16 +40014,16 @@
         <v>46252</v>
       </c>
       <c r="D1191" s="7">
-        <v>2.746969</v>
+        <v>2.747562</v>
       </c>
       <c r="E1191" s="8">
-        <v>10306304</v>
+        <v>10303774</v>
       </c>
       <c r="F1191" s="9">
         <v>683</v>
       </c>
       <c r="G1191" s="8">
-        <v>28311097.43</v>
+        <v>28310258.85</v>
       </c>
     </row>
     <row r="1192" spans="1:7" x14ac:dyDescent="0.25">
@@ -40036,17 +40036,17 @@
       <c r="C1192" s="6">
         <v>46252</v>
       </c>
-      <c r="D1192" s="8">
-        <v>0</v>
+      <c r="D1192" s="7">
+        <v>0.783918</v>
       </c>
       <c r="E1192" s="8">
-        <v>0</v>
+        <v>1033653600</v>
       </c>
       <c r="F1192" s="9">
         <v>19</v>
       </c>
       <c r="G1192" s="8">
-        <v>0</v>
+        <v>810299960.04</v>
       </c>
     </row>
     <row r="1193" spans="1:7" x14ac:dyDescent="0.25">
@@ -40289,17 +40289,17 @@
       <c r="C1203" s="6">
         <v>46252</v>
       </c>
-      <c r="D1203" s="8">
-        <v>0</v>
+      <c r="D1203" s="7">
+        <v>1.508301</v>
       </c>
       <c r="E1203" s="8">
-        <v>0</v>
+        <v>1348018778</v>
       </c>
       <c r="F1203" s="9">
         <v>411</v>
       </c>
       <c r="G1203" s="8">
-        <v>0</v>
+        <v>2033218733.23</v>
       </c>
     </row>
     <row r="1204" spans="1:7" x14ac:dyDescent="0.25">
@@ -40404,17 +40404,17 @@
       <c r="C1208" s="6">
         <v>46252</v>
       </c>
-      <c r="D1208" s="8">
-        <v>0</v>
+      <c r="D1208" s="7">
+        <v>0.959069</v>
       </c>
       <c r="E1208" s="8">
-        <v>0</v>
+        <v>588672037</v>
       </c>
       <c r="F1208" s="9">
         <v>13</v>
       </c>
       <c r="G1208" s="8">
-        <v>0</v>
+        <v>564576839.83</v>
       </c>
     </row>
     <row r="1209" spans="1:7" x14ac:dyDescent="0.25">
@@ -40450,17 +40450,17 @@
       <c r="C1210" s="6">
         <v>46252</v>
       </c>
-      <c r="D1210" s="8">
-        <v>0</v>
+      <c r="D1210" s="10">
+        <v>1.34726</v>
       </c>
       <c r="E1210" s="8">
-        <v>0</v>
+        <v>1487997647</v>
       </c>
       <c r="F1210" s="9">
         <v>35</v>
       </c>
       <c r="G1210" s="8">
-        <v>0</v>
+        <v>2004719740.26</v>
       </c>
     </row>
     <row r="1211" spans="1:7" x14ac:dyDescent="0.25">
@@ -40519,17 +40519,17 @@
       <c r="C1213" s="6">
         <v>46252</v>
       </c>
-      <c r="D1213" s="8">
-        <v>0</v>
+      <c r="D1213" s="7">
+        <v>5.630026</v>
       </c>
       <c r="E1213" s="8">
-        <v>0</v>
+        <v>2163694</v>
       </c>
       <c r="F1213" s="9">
         <v>155</v>
       </c>
       <c r="G1213" s="8">
-        <v>0</v>
+        <v>12181652.77</v>
       </c>
     </row>
     <row r="1214" spans="1:7" x14ac:dyDescent="0.25">
@@ -41347,17 +41347,17 @@
       <c r="C1249" s="6">
         <v>46252</v>
       </c>
-      <c r="D1249" s="8">
-        <v>0</v>
+      <c r="D1249" s="7">
+        <v>1.585256</v>
       </c>
       <c r="E1249" s="8">
-        <v>0</v>
+        <v>592973692</v>
       </c>
       <c r="F1249" s="9">
         <v>1</v>
       </c>
       <c r="G1249" s="8">
-        <v>0</v>
+        <v>940015208.63</v>
       </c>
     </row>
     <row r="1250" spans="1:7" x14ac:dyDescent="0.25">
@@ -42382,17 +42382,17 @@
       <c r="C1294" s="6">
         <v>46252</v>
       </c>
-      <c r="D1294" s="8">
-        <v>0</v>
+      <c r="D1294" s="7">
+        <v>19.726718</v>
       </c>
       <c r="E1294" s="8">
-        <v>0</v>
+        <v>83954952</v>
       </c>
       <c r="F1294" s="9">
         <v>3865</v>
       </c>
       <c r="G1294" s="8">
-        <v>0</v>
+        <v>1656155690.11</v>
       </c>
     </row>
     <row r="1295" spans="1:7" x14ac:dyDescent="0.25">
@@ -42452,7 +42452,7 @@
         <v>46252</v>
       </c>
       <c r="D1297" s="7">
-        <v>4.046546</v>
+        <v>4.046464</v>
       </c>
       <c r="E1297" s="8">
         <v>38677510</v>
@@ -42461,7 +42461,7 @@
         <v>598</v>
       </c>
       <c r="G1297" s="8">
-        <v>156510342.45</v>
+        <v>156507149.29</v>
       </c>
     </row>
     <row r="1298" spans="1:7" x14ac:dyDescent="0.25">
@@ -42521,7 +42521,7 @@
         <v>46252</v>
       </c>
       <c r="D1300" s="7">
-        <v>8.189268</v>
+        <v>8.189308</v>
       </c>
       <c r="E1300" s="8">
         <v>22659905</v>
@@ -42530,7 +42530,7 @@
         <v>435</v>
       </c>
       <c r="G1300" s="8">
-        <v>185568033.92</v>
+        <v>185568945.99</v>
       </c>
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.25">
@@ -42659,7 +42659,7 @@
         <v>46252</v>
       </c>
       <c r="D1306" s="7">
-        <v>2.853382</v>
+        <v>2.859427</v>
       </c>
       <c r="E1306" s="8">
         <v>9677362</v>
@@ -42668,7 +42668,7 @@
         <v>1184</v>
       </c>
       <c r="G1306" s="8">
-        <v>27613208.8</v>
+        <v>27671705.59</v>
       </c>
     </row>
     <row r="1307" spans="1:7" x14ac:dyDescent="0.25">
@@ -42682,7 +42682,7 @@
         <v>46252</v>
       </c>
       <c r="D1307" s="7">
-        <v>3.880137</v>
+        <v>3.919165</v>
       </c>
       <c r="E1307" s="8">
         <v>11235020</v>
@@ -42691,7 +42691,7 @@
         <v>651</v>
       </c>
       <c r="G1307" s="8">
-        <v>43593419.78</v>
+        <v>44031898.53</v>
       </c>
     </row>
     <row r="1308" spans="1:7" x14ac:dyDescent="0.25">
@@ -42705,7 +42705,7 @@
         <v>46252</v>
       </c>
       <c r="D1308" s="7">
-        <v>5.061152</v>
+        <v>5.071505</v>
       </c>
       <c r="E1308" s="8">
         <v>3750176</v>
@@ -42714,7 +42714,7 @@
         <v>225</v>
       </c>
       <c r="G1308" s="8">
-        <v>18980209.79</v>
+        <v>19019035.31</v>
       </c>
     </row>
     <row r="1309" spans="1:7" x14ac:dyDescent="0.25">
@@ -42820,7 +42820,7 @@
         <v>46252</v>
       </c>
       <c r="D1313" s="7">
-        <v>13.263632</v>
+        <v>13.258458</v>
       </c>
       <c r="E1313" s="8">
         <v>365125063</v>
@@ -42829,7 +42829,7 @@
         <v>11191</v>
       </c>
       <c r="G1313" s="8">
-        <v>4842884544.52</v>
+        <v>4840995440.92</v>
       </c>
     </row>
     <row r="1314" spans="1:7" x14ac:dyDescent="0.25">
@@ -43026,8 +43026,8 @@
       <c r="C1322" s="6">
         <v>46252</v>
       </c>
-      <c r="D1322" s="7">
-        <v>5.049811</v>
+      <c r="D1322" s="10">
+        <v>5.05472</v>
       </c>
       <c r="E1322" s="8">
         <v>64779982</v>
@@ -43036,7 +43036,7 @@
         <v>503</v>
       </c>
       <c r="G1322" s="8">
-        <v>327126655.33</v>
+        <v>327444674.72</v>
       </c>
     </row>
     <row r="1323" spans="1:7" x14ac:dyDescent="0.25">
@@ -43165,7 +43165,7 @@
         <v>46252</v>
       </c>
       <c r="D1328" s="7">
-        <v>48.001715</v>
+        <v>47.891115</v>
       </c>
       <c r="E1328" s="8">
         <v>72620000.01</v>
@@ -43174,7 +43174,7 @@
         <v>627</v>
       </c>
       <c r="G1328" s="8">
-        <v>3485884552.41</v>
+        <v>3477852780.86</v>
       </c>
     </row>
     <row r="1329" spans="1:7" x14ac:dyDescent="0.25">
@@ -43418,7 +43418,7 @@
         <v>46252</v>
       </c>
       <c r="D1339" s="7">
-        <v>26.009154</v>
+        <v>26.009156</v>
       </c>
       <c r="E1339" s="8">
         <v>35529976</v>
@@ -43427,7 +43427,7 @@
         <v>2515</v>
       </c>
       <c r="G1339" s="8">
-        <v>924104617.66</v>
+        <v>924104696.96</v>
       </c>
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.25">
@@ -43441,7 +43441,7 @@
         <v>46252</v>
       </c>
       <c r="D1340" s="7">
-        <v>22.564631</v>
+        <v>22.564765</v>
       </c>
       <c r="E1340" s="8">
         <v>9648166</v>
@@ -43450,7 +43450,7 @@
         <v>1545</v>
       </c>
       <c r="G1340" s="8">
-        <v>217707301.45</v>
+        <v>217708600.06</v>
       </c>
     </row>
     <row r="1341" spans="1:7" x14ac:dyDescent="0.25">
@@ -43740,7 +43740,7 @@
         <v>46252</v>
       </c>
       <c r="D1353" s="7">
-        <v>7.205521</v>
+        <v>7.215745</v>
       </c>
       <c r="E1353" s="8">
         <v>457790734</v>
@@ -43749,7 +43749,7 @@
         <v>22617</v>
       </c>
       <c r="G1353" s="8">
-        <v>3298620790.27</v>
+        <v>3303301054.98</v>
       </c>
     </row>
     <row r="1354" spans="1:7" x14ac:dyDescent="0.25">
@@ -43831,17 +43831,17 @@
       <c r="C1357" s="6">
         <v>46252</v>
       </c>
-      <c r="D1357" s="8">
-        <v>0</v>
+      <c r="D1357" s="7">
+        <v>7.092231</v>
       </c>
       <c r="E1357" s="8">
-        <v>0</v>
+        <v>124960731</v>
       </c>
       <c r="F1357" s="9">
         <v>14</v>
       </c>
       <c r="G1357" s="8">
-        <v>0</v>
+        <v>886250367.36</v>
       </c>
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.25">
@@ -43946,8 +43946,8 @@
       <c r="C1362" s="6">
         <v>46252</v>
       </c>
-      <c r="D1362" s="7">
-        <v>3.386131</v>
+      <c r="D1362" s="10">
+        <v>3.38876</v>
       </c>
       <c r="E1362" s="8">
         <v>211085432</v>
@@ -43956,7 +43956,7 @@
         <v>3019</v>
       </c>
       <c r="G1362" s="8">
-        <v>714762860.16</v>
+        <v>715317919.09</v>
       </c>
     </row>
     <row r="1363" spans="1:7" x14ac:dyDescent="0.25">
@@ -44361,7 +44361,7 @@
         <v>46252</v>
       </c>
       <c r="D1380" s="7">
-        <v>2.308281</v>
+        <v>2.316437</v>
       </c>
       <c r="E1380" s="8">
         <v>47341678</v>
@@ -44370,7 +44370,7 @@
         <v>638</v>
       </c>
       <c r="G1380" s="8">
-        <v>109277919.37</v>
+        <v>109663992.53</v>
       </c>
     </row>
     <row r="1381" spans="1:7" x14ac:dyDescent="0.25">
@@ -44797,8 +44797,8 @@
       <c r="C1399" s="6">
         <v>46252</v>
       </c>
-      <c r="D1399" s="7">
-        <v>2.308703</v>
+      <c r="D1399" s="10">
+        <v>2.30974</v>
       </c>
       <c r="E1399" s="8">
         <v>32134612</v>
@@ -44807,7 +44807,7 @@
         <v>283</v>
       </c>
       <c r="G1399" s="8">
-        <v>74189274.99</v>
+        <v>74222595.24</v>
       </c>
     </row>
     <row r="1400" spans="1:7" x14ac:dyDescent="0.25">
@@ -44821,7 +44821,7 @@
         <v>46252</v>
       </c>
       <c r="D1400" s="7">
-        <v>2.985384</v>
+        <v>2.988547</v>
       </c>
       <c r="E1400" s="8">
         <v>5328137</v>
@@ -44830,7 +44830,7 @@
         <v>91</v>
       </c>
       <c r="G1400" s="8">
-        <v>15906536.88</v>
+        <v>15923388.85</v>
       </c>
     </row>
     <row r="1401" spans="1:7" x14ac:dyDescent="0.25">
@@ -44958,17 +44958,17 @@
       <c r="C1406" s="6">
         <v>46252</v>
       </c>
-      <c r="D1406" s="8">
-        <v>0</v>
+      <c r="D1406" s="10">
+        <v>4.00217</v>
       </c>
       <c r="E1406" s="8">
-        <v>0</v>
+        <v>9861053671</v>
       </c>
       <c r="F1406" s="9">
         <v>128776</v>
       </c>
       <c r="G1406" s="8">
-        <v>0</v>
+        <v>39465615357.2</v>
       </c>
     </row>
     <row r="1407" spans="1:7" x14ac:dyDescent="0.25">
@@ -45143,7 +45143,7 @@
         <v>46252</v>
       </c>
       <c r="D1414" s="7">
-        <v>4.037138</v>
+        <v>4.038678</v>
       </c>
       <c r="E1414" s="8">
         <v>124385537</v>
@@ -45152,7 +45152,7 @@
         <v>7769</v>
       </c>
       <c r="G1414" s="8">
-        <v>502161606.68</v>
+        <v>502353085.53</v>
       </c>
     </row>
     <row r="1415" spans="1:7" x14ac:dyDescent="0.25">
@@ -45579,17 +45579,17 @@
       <c r="C1433" s="6">
         <v>46252</v>
       </c>
-      <c r="D1433" s="8">
-        <v>0</v>
+      <c r="D1433" s="7">
+        <v>1.268073</v>
       </c>
       <c r="E1433" s="8">
-        <v>0</v>
+        <v>627745</v>
       </c>
       <c r="F1433" s="9">
         <v>114</v>
       </c>
       <c r="G1433" s="8">
-        <v>0</v>
+        <v>796026.34</v>
       </c>
     </row>
     <row r="1434" spans="1:7" x14ac:dyDescent="0.25">
@@ -45717,17 +45717,17 @@
       <c r="C1439" s="6">
         <v>46252</v>
       </c>
-      <c r="D1439" s="8">
-        <v>0</v>
+      <c r="D1439" s="7">
+        <v>1.230042</v>
       </c>
       <c r="E1439" s="8">
-        <v>0</v>
+        <v>30603856824</v>
       </c>
       <c r="F1439" s="9">
         <v>23238</v>
       </c>
       <c r="G1439" s="8">
-        <v>0</v>
+        <v>37644026936.69</v>
       </c>
     </row>
     <row r="1440" spans="1:7" x14ac:dyDescent="0.25">
@@ -45764,16 +45764,16 @@
         <v>46252</v>
       </c>
       <c r="D1441" s="7">
-        <v>2.904645</v>
+        <v>2.907274</v>
       </c>
       <c r="E1441" s="8">
-        <v>102990850</v>
+        <v>95029494</v>
       </c>
       <c r="F1441" s="9">
         <v>49</v>
       </c>
       <c r="G1441" s="8">
-        <v>299151812.02</v>
+        <v>276276795.96</v>
       </c>
     </row>
     <row r="1442" spans="1:7" x14ac:dyDescent="0.25">
@@ -46020,13 +46020,13 @@
         <v>34.52567</v>
       </c>
       <c r="E1452" s="8">
-        <v>65862847</v>
+        <v>65865847</v>
       </c>
       <c r="F1452" s="9">
         <v>108</v>
       </c>
       <c r="G1452" s="8">
-        <v>2273958940.6</v>
+        <v>2274062516.55</v>
       </c>
     </row>
     <row r="1453" spans="1:7" x14ac:dyDescent="0.25">
@@ -48064,7 +48064,7 @@
         <v>46252</v>
       </c>
       <c r="D1541" s="7">
-        <v>1.097776</v>
+        <v>1.098096</v>
       </c>
       <c r="E1541" s="8">
         <v>21432304</v>
@@ -48073,7 +48073,7 @@
         <v>340</v>
       </c>
       <c r="G1541" s="8">
-        <v>23527858.69</v>
+        <v>23534725.8</v>
       </c>
     </row>
     <row r="1542" spans="1:7" x14ac:dyDescent="0.25">
@@ -48109,8 +48109,8 @@
       <c r="C1543" s="6">
         <v>46252</v>
       </c>
-      <c r="D1543" s="10">
-        <v>1.14423</v>
+      <c r="D1543" s="7">
+        <v>1.144707</v>
       </c>
       <c r="E1543" s="8">
         <v>34407131</v>
@@ -48119,7 +48119,7 @@
         <v>23</v>
       </c>
       <c r="G1543" s="8">
-        <v>39369671.97</v>
+        <v>39386092.17</v>
       </c>
     </row>
     <row r="1544" spans="1:7" x14ac:dyDescent="0.25">
@@ -49282,17 +49282,17 @@
       <c r="C1594" s="6">
         <v>46252</v>
       </c>
-      <c r="D1594" s="8">
-        <v>0</v>
+      <c r="D1594" s="7">
+        <v>1.237408</v>
       </c>
       <c r="E1594" s="8">
-        <v>0</v>
+        <v>300626629</v>
       </c>
       <c r="F1594" s="9">
         <v>1</v>
       </c>
       <c r="G1594" s="8">
-        <v>0</v>
+        <v>371997881.5</v>
       </c>
     </row>
     <row r="1595" spans="1:7" x14ac:dyDescent="0.25">
@@ -49375,7 +49375,7 @@
         <v>46252</v>
       </c>
       <c r="D1598" s="7">
-        <v>49.208562</v>
+        <v>49.211699</v>
       </c>
       <c r="E1598" s="8">
         <v>10527011</v>
@@ -49384,7 +49384,7 @@
         <v>57</v>
       </c>
       <c r="G1598" s="8">
-        <v>518019074.5</v>
+        <v>518052099.15</v>
       </c>
     </row>
     <row r="1599" spans="1:7" x14ac:dyDescent="0.25">
@@ -49512,17 +49512,17 @@
       <c r="C1604" s="6">
         <v>46252</v>
       </c>
-      <c r="D1604" s="8">
-        <v>0</v>
+      <c r="D1604" s="7">
+        <v>1.890985</v>
       </c>
       <c r="E1604" s="8">
-        <v>0</v>
+        <v>254523245</v>
       </c>
       <c r="F1604" s="9">
         <v>816</v>
       </c>
       <c r="G1604" s="8">
-        <v>0</v>
+        <v>481299631.68</v>
       </c>
     </row>
     <row r="1605" spans="1:7" x14ac:dyDescent="0.25">
@@ -49627,17 +49627,17 @@
       <c r="C1609" s="6">
         <v>46252</v>
       </c>
-      <c r="D1609" s="8">
-        <v>0</v>
+      <c r="D1609" s="7">
+        <v>1.024286</v>
       </c>
       <c r="E1609" s="8">
-        <v>0</v>
+        <v>33483524</v>
       </c>
       <c r="F1609" s="9">
         <v>137</v>
       </c>
       <c r="G1609" s="8">
-        <v>0</v>
+        <v>34296689.44</v>
       </c>
     </row>
     <row r="1610" spans="1:7" x14ac:dyDescent="0.25">
@@ -49743,7 +49743,7 @@
         <v>46252</v>
       </c>
       <c r="D1614" s="7">
-        <v>1.399707</v>
+        <v>1.402033</v>
       </c>
       <c r="E1614" s="8">
         <v>22295412</v>
@@ -49752,7 +49752,7 @@
         <v>78</v>
       </c>
       <c r="G1614" s="8">
-        <v>31207049.78</v>
+        <v>31258902.56</v>
       </c>
     </row>
     <row r="1615" spans="1:7" x14ac:dyDescent="0.25">
@@ -49765,17 +49765,17 @@
       <c r="C1615" s="6">
         <v>46252</v>
       </c>
-      <c r="D1615" s="8">
-        <v>0</v>
+      <c r="D1615" s="7">
+        <v>1.993874</v>
       </c>
       <c r="E1615" s="8">
-        <v>0</v>
+        <v>106053691</v>
       </c>
       <c r="F1615" s="9">
         <v>2517</v>
       </c>
       <c r="G1615" s="8">
-        <v>0</v>
+        <v>211457710.27</v>
       </c>
     </row>
     <row r="1616" spans="1:7" x14ac:dyDescent="0.25">
@@ -49857,17 +49857,17 @@
       <c r="C1619" s="6">
         <v>46252</v>
       </c>
-      <c r="D1619" s="8">
-        <v>0</v>
+      <c r="D1619" s="11">
+        <v>1.4111</v>
       </c>
       <c r="E1619" s="8">
-        <v>0</v>
+        <v>181913164</v>
       </c>
       <c r="F1619" s="9">
         <v>21</v>
       </c>
       <c r="G1619" s="8">
-        <v>0</v>
+        <v>256697655.39</v>
       </c>
     </row>
     <row r="1620" spans="1:7" x14ac:dyDescent="0.25">
@@ -49880,17 +49880,17 @@
       <c r="C1620" s="6">
         <v>46252</v>
       </c>
-      <c r="D1620" s="8">
-        <v>0</v>
+      <c r="D1620" s="7">
+        <v>0.969602</v>
       </c>
       <c r="E1620" s="8">
-        <v>0</v>
+        <v>4011986</v>
       </c>
       <c r="F1620" s="9">
         <v>11</v>
       </c>
       <c r="G1620" s="8">
-        <v>0</v>
+        <v>3890028.95</v>
       </c>
     </row>
     <row r="1621" spans="1:7" x14ac:dyDescent="0.25">
@@ -49903,17 +49903,17 @@
       <c r="C1621" s="6">
         <v>46252</v>
       </c>
-      <c r="D1621" s="8">
-        <v>0</v>
+      <c r="D1621" s="10">
+        <v>0.29337</v>
       </c>
       <c r="E1621" s="8">
-        <v>0</v>
+        <v>194986093</v>
       </c>
       <c r="F1621" s="9">
         <v>12</v>
       </c>
       <c r="G1621" s="8">
-        <v>0</v>
+        <v>57203075.29</v>
       </c>
     </row>
     <row r="1622" spans="1:7" x14ac:dyDescent="0.25">
@@ -50364,16 +50364,16 @@
         <v>46252</v>
       </c>
       <c r="D1641" s="7">
-        <v>2.163525</v>
+        <v>2.177368</v>
       </c>
       <c r="E1641" s="8">
-        <v>43586281</v>
+        <v>43586256</v>
       </c>
       <c r="F1641" s="9">
         <v>797</v>
       </c>
       <c r="G1641" s="8">
-        <v>94300008.88</v>
+        <v>94903306.44</v>
       </c>
     </row>
     <row r="1642" spans="1:7" x14ac:dyDescent="0.25">
@@ -50685,8 +50685,8 @@
       <c r="C1655" s="6">
         <v>46252</v>
       </c>
-      <c r="D1655" s="7">
-        <v>1.291391</v>
+      <c r="D1655" s="10">
+        <v>1.29277</v>
       </c>
       <c r="E1655" s="8">
         <v>145150911</v>
@@ -50695,7 +50695,7 @@
         <v>71</v>
       </c>
       <c r="G1655" s="8">
-        <v>187446586.58</v>
+        <v>187646767.28</v>
       </c>
     </row>
     <row r="1656" spans="1:7" x14ac:dyDescent="0.25">
@@ -51192,7 +51192,7 @@
         <v>46252</v>
       </c>
       <c r="D1677" s="7">
-        <v>0.280459</v>
+        <v>0.280461</v>
       </c>
       <c r="E1677" s="8">
         <v>1663080294</v>
@@ -51201,7 +51201,7 @@
         <v>199</v>
       </c>
       <c r="G1677" s="8">
-        <v>466426480.85</v>
+        <v>466429845.33</v>
       </c>
     </row>
     <row r="1678" spans="1:7" x14ac:dyDescent="0.25">
@@ -51352,17 +51352,17 @@
       <c r="C1684" s="6">
         <v>46252</v>
       </c>
-      <c r="D1684" s="8">
-        <v>0</v>
+      <c r="D1684" s="7">
+        <v>4.530326</v>
       </c>
       <c r="E1684" s="8">
-        <v>0</v>
+        <v>732499746</v>
       </c>
       <c r="F1684" s="9">
         <v>2778</v>
       </c>
       <c r="G1684" s="8">
-        <v>0</v>
+        <v>3318462412.27</v>
       </c>
     </row>
     <row r="1685" spans="1:7" x14ac:dyDescent="0.25">
@@ -51560,7 +51560,7 @@
         <v>46252</v>
       </c>
       <c r="D1693" s="7">
-        <v>2.822189</v>
+        <v>2.821995</v>
       </c>
       <c r="E1693" s="8">
         <v>265379478</v>
@@ -51569,7 +51569,7 @@
         <v>1328</v>
       </c>
       <c r="G1693" s="8">
-        <v>748951003.98</v>
+        <v>748899683</v>
       </c>
     </row>
     <row r="1694" spans="1:7" x14ac:dyDescent="0.25">
@@ -52213,7 +52213,7 @@
         <v>112933</v>
       </c>
       <c r="G1721" s="8">
-        <v>20955327335.56</v>
+        <v>20955327558.48</v>
       </c>
     </row>
     <row r="1722" spans="1:7" x14ac:dyDescent="0.25">
@@ -52249,17 +52249,17 @@
       <c r="C1723" s="6">
         <v>46252</v>
       </c>
-      <c r="D1723" s="8">
-        <v>0</v>
+      <c r="D1723" s="7">
+        <v>5.329793</v>
       </c>
       <c r="E1723" s="8">
-        <v>0</v>
+        <v>10162360</v>
       </c>
       <c r="F1723" s="9">
         <v>545</v>
       </c>
       <c r="G1723" s="8">
-        <v>0</v>
+        <v>54163274.68</v>
       </c>
     </row>
     <row r="1724" spans="1:7" x14ac:dyDescent="0.25">
@@ -52272,17 +52272,17 @@
       <c r="C1724" s="6">
         <v>46252</v>
       </c>
-      <c r="D1724" s="8">
-        <v>0</v>
+      <c r="D1724" s="7">
+        <v>6.441079</v>
       </c>
       <c r="E1724" s="8">
-        <v>0</v>
+        <v>92285808</v>
       </c>
       <c r="F1724" s="9">
         <v>908</v>
       </c>
       <c r="G1724" s="8">
-        <v>0</v>
+        <v>594420176.22</v>
       </c>
     </row>
     <row r="1725" spans="1:7" x14ac:dyDescent="0.25">
@@ -52387,8 +52387,8 @@
       <c r="C1729" s="6">
         <v>46252</v>
       </c>
-      <c r="D1729" s="10">
-        <v>1.75616</v>
+      <c r="D1729" s="7">
+        <v>1.756179</v>
       </c>
       <c r="E1729" s="8">
         <v>1028008850</v>
@@ -52397,7 +52397,7 @@
         <v>113223</v>
       </c>
       <c r="G1729" s="8">
-        <v>1805347669.89</v>
+        <v>1805367938.76</v>
       </c>
     </row>
     <row r="1730" spans="1:7" x14ac:dyDescent="0.25">
@@ -52765,7 +52765,7 @@
         <v>86</v>
       </c>
       <c r="G1745" s="8">
-        <v>401798321.06</v>
+        <v>401798321.05</v>
       </c>
     </row>
     <row r="1746" spans="1:7" x14ac:dyDescent="0.25">
@@ -52779,7 +52779,7 @@
         <v>46252</v>
       </c>
       <c r="D1746" s="7">
-        <v>1.419118</v>
+        <v>1.420688</v>
       </c>
       <c r="E1746" s="8">
         <v>41238300</v>
@@ -52788,7 +52788,7 @@
         <v>89</v>
       </c>
       <c r="G1746" s="8">
-        <v>58522002.98</v>
+        <v>58586769.21</v>
       </c>
     </row>
     <row r="1747" spans="1:7" x14ac:dyDescent="0.25">
@@ -53123,17 +53123,17 @@
       <c r="C1761" s="6">
         <v>46252</v>
       </c>
-      <c r="D1761" s="8">
-        <v>0</v>
+      <c r="D1761" s="7">
+        <v>13.200143</v>
       </c>
       <c r="E1761" s="8">
-        <v>0</v>
+        <v>455027893</v>
       </c>
       <c r="F1761" s="9">
         <v>12725</v>
       </c>
       <c r="G1761" s="8">
-        <v>0</v>
+        <v>6006433345.94</v>
       </c>
     </row>
     <row r="1762" spans="1:7" x14ac:dyDescent="0.25">
@@ -53262,7 +53262,7 @@
         <v>46252</v>
       </c>
       <c r="D1767" s="7">
-        <v>78.311238</v>
+        <v>78.312769</v>
       </c>
       <c r="E1767" s="8">
         <v>23712000</v>
@@ -53271,7 +53271,7 @@
         <v>389</v>
       </c>
       <c r="G1767" s="8">
-        <v>1856916076.81</v>
+        <v>1856952387.66</v>
       </c>
     </row>
     <row r="1768" spans="1:7" x14ac:dyDescent="0.25">
@@ -53607,7 +53607,7 @@
         <v>46252</v>
       </c>
       <c r="D1782" s="7">
-        <v>70.563347</v>
+        <v>70.579718</v>
       </c>
       <c r="E1782" s="8">
         <v>31086506</v>
@@ -53616,7 +53616,7 @@
         <v>1</v>
       </c>
       <c r="G1782" s="8">
-        <v>2193567911.14</v>
+        <v>2194076826.07</v>
       </c>
     </row>
     <row r="1783" spans="1:7" x14ac:dyDescent="0.25">
@@ -54559,7 +54559,7 @@
         <v>39</v>
       </c>
       <c r="G1823" s="8">
-        <v>274950278.26</v>
+        <v>274950278.49</v>
       </c>
     </row>
     <row r="1824" spans="1:7" x14ac:dyDescent="0.25">
@@ -54687,17 +54687,17 @@
       <c r="C1829" s="6">
         <v>46252</v>
       </c>
-      <c r="D1829" s="8">
-        <v>0</v>
+      <c r="D1829" s="7">
+        <v>1.007843</v>
       </c>
       <c r="E1829" s="8">
-        <v>0</v>
+        <v>131581286</v>
       </c>
       <c r="F1829" s="9">
         <v>3111</v>
       </c>
       <c r="G1829" s="8">
-        <v>0</v>
+        <v>132613343.72</v>
       </c>
     </row>
     <row r="1830" spans="1:7" x14ac:dyDescent="0.25">
@@ -55101,17 +55101,17 @@
       <c r="C1847" s="6">
         <v>46252</v>
       </c>
-      <c r="D1847" s="8">
-        <v>0</v>
+      <c r="D1847" s="7">
+        <v>14.688578</v>
       </c>
       <c r="E1847" s="8">
-        <v>0</v>
+        <v>374012663</v>
       </c>
       <c r="F1847" s="9">
         <v>9848</v>
       </c>
       <c r="G1847" s="8">
-        <v>0</v>
+        <v>5493714324.95</v>
       </c>
     </row>
     <row r="1848" spans="1:7" x14ac:dyDescent="0.25">
@@ -55170,17 +55170,17 @@
       <c r="C1850" s="6">
         <v>46252</v>
       </c>
-      <c r="D1850" s="8">
-        <v>0</v>
+      <c r="D1850" s="7">
+        <v>14.485909</v>
       </c>
       <c r="E1850" s="8">
-        <v>0</v>
+        <v>128410302</v>
       </c>
       <c r="F1850" s="9">
         <v>3585</v>
       </c>
       <c r="G1850" s="8">
-        <v>0</v>
+        <v>1860139909.05</v>
       </c>
     </row>
     <row r="1851" spans="1:7" x14ac:dyDescent="0.25">
@@ -55423,17 +55423,17 @@
       <c r="C1861" s="6">
         <v>46252</v>
       </c>
-      <c r="D1861" s="8">
-        <v>0</v>
+      <c r="D1861" s="7">
+        <v>2.691932</v>
       </c>
       <c r="E1861" s="8">
-        <v>0</v>
+        <v>39969656</v>
       </c>
       <c r="F1861" s="9">
         <v>115</v>
       </c>
       <c r="G1861" s="8">
-        <v>0</v>
+        <v>107595613.49</v>
       </c>
     </row>
     <row r="1862" spans="1:7" x14ac:dyDescent="0.25">
@@ -55515,17 +55515,17 @@
       <c r="C1865" s="6">
         <v>46252</v>
       </c>
-      <c r="D1865" s="8">
-        <v>0</v>
+      <c r="D1865" s="7">
+        <v>4.080253</v>
       </c>
       <c r="E1865" s="8">
-        <v>0</v>
+        <v>65930814</v>
       </c>
       <c r="F1865" s="9">
         <v>270</v>
       </c>
       <c r="G1865" s="8">
-        <v>0</v>
+        <v>269014387.97</v>
       </c>
     </row>
     <row r="1866" spans="1:7" x14ac:dyDescent="0.25">
@@ -56090,17 +56090,17 @@
       <c r="C1890" s="6">
         <v>46252</v>
       </c>
-      <c r="D1890" s="8">
-        <v>0</v>
+      <c r="D1890" s="7">
+        <v>5.959518</v>
       </c>
       <c r="E1890" s="8">
-        <v>0</v>
+        <v>182037991</v>
       </c>
       <c r="F1890" s="9">
         <v>13917</v>
       </c>
       <c r="G1890" s="8">
-        <v>0</v>
+        <v>1084858737.87</v>
       </c>
     </row>
     <row r="1891" spans="1:7" x14ac:dyDescent="0.25">
@@ -56435,17 +56435,17 @@
       <c r="C1905" s="6">
         <v>46252</v>
       </c>
-      <c r="D1905" s="8">
-        <v>0</v>
+      <c r="D1905" s="7">
+        <v>1.029201</v>
       </c>
       <c r="E1905" s="8">
-        <v>0</v>
+        <v>127125</v>
       </c>
       <c r="F1905" s="9">
         <v>49</v>
       </c>
       <c r="G1905" s="8">
-        <v>0</v>
+        <v>130837.14</v>
       </c>
     </row>
     <row r="1906" spans="1:7" x14ac:dyDescent="0.25">
@@ -56918,17 +56918,17 @@
       <c r="C1926" s="6">
         <v>46252</v>
       </c>
-      <c r="D1926" s="8">
-        <v>0</v>
+      <c r="D1926" s="7">
+        <v>7.914812</v>
       </c>
       <c r="E1926" s="8">
-        <v>0</v>
+        <v>704131649</v>
       </c>
       <c r="F1926" s="9">
         <v>3362</v>
       </c>
       <c r="G1926" s="8">
-        <v>0</v>
+        <v>5573069720.94</v>
       </c>
     </row>
     <row r="1927" spans="1:7" x14ac:dyDescent="0.25">
@@ -57079,17 +57079,17 @@
       <c r="C1933" s="6">
         <v>46252</v>
       </c>
-      <c r="D1933" s="8">
-        <v>0</v>
+      <c r="D1933" s="7">
+        <v>0.979969</v>
       </c>
       <c r="E1933" s="8">
-        <v>0</v>
+        <v>1833165903</v>
       </c>
       <c r="F1933" s="9">
         <v>14868</v>
       </c>
       <c r="G1933" s="8">
-        <v>0</v>
+        <v>1796445005.2</v>
       </c>
     </row>
     <row r="1934" spans="1:7" x14ac:dyDescent="0.25">
@@ -57539,17 +57539,17 @@
       <c r="C1953" s="6">
         <v>46252</v>
       </c>
-      <c r="D1953" s="8">
-        <v>0</v>
+      <c r="D1953" s="7">
+        <v>13.218794</v>
       </c>
       <c r="E1953" s="8">
-        <v>0</v>
+        <v>842212737</v>
       </c>
       <c r="F1953" s="9">
         <v>61264</v>
       </c>
       <c r="G1953" s="8">
-        <v>0</v>
+        <v>11133036848.58</v>
       </c>
     </row>
     <row r="1954" spans="1:7" x14ac:dyDescent="0.25">
@@ -58092,7 +58092,7 @@
         <v>46252</v>
       </c>
       <c r="D1977" s="7">
-        <v>3.998703</v>
+        <v>3.999215</v>
       </c>
       <c r="E1977" s="8">
         <v>144007400</v>
@@ -58101,7 +58101,7 @@
         <v>6563</v>
       </c>
       <c r="G1977" s="8">
-        <v>575842815.24</v>
+        <v>575916561.04</v>
       </c>
     </row>
     <row r="1978" spans="1:7" x14ac:dyDescent="0.25">
@@ -58666,8 +58666,8 @@
       <c r="C2002" s="6">
         <v>46252</v>
       </c>
-      <c r="D2002" s="7">
-        <v>1.888809</v>
+      <c r="D2002" s="11">
+        <v>1.8888</v>
       </c>
       <c r="E2002" s="8">
         <v>306521428</v>
@@ -58676,7 +58676,7 @@
         <v>11</v>
       </c>
       <c r="G2002" s="8">
-        <v>578960539.16</v>
+        <v>578957721.34</v>
       </c>
     </row>
     <row r="2003" spans="1:7" x14ac:dyDescent="0.25">
@@ -58713,7 +58713,7 @@
         <v>46252</v>
       </c>
       <c r="D2004" s="7">
-        <v>5.772285</v>
+        <v>5.766292</v>
       </c>
       <c r="E2004" s="8">
         <v>106786382</v>
@@ -58722,7 +58722,7 @@
         <v>1</v>
       </c>
       <c r="G2004" s="8">
-        <v>616401465.72</v>
+        <v>615761425.24</v>
       </c>
     </row>
     <row r="2005" spans="1:7" x14ac:dyDescent="0.25">
@@ -58874,7 +58874,7 @@
         <v>46252</v>
       </c>
       <c r="D2011" s="7">
-        <v>19.228682</v>
+        <v>19.228756</v>
       </c>
       <c r="E2011" s="8">
         <v>165095699</v>
@@ -58883,7 +58883,7 @@
         <v>2764</v>
       </c>
       <c r="G2011" s="8">
-        <v>3174572775.87</v>
+        <v>3174584954.03</v>
       </c>
     </row>
     <row r="2012" spans="1:7" x14ac:dyDescent="0.25">
@@ -59150,7 +59150,7 @@
         <v>46252</v>
       </c>
       <c r="D2023" s="7">
-        <v>11.941383</v>
+        <v>11.940456</v>
       </c>
       <c r="E2023" s="8">
         <v>299315692</v>
@@ -59159,7 +59159,7 @@
         <v>24</v>
       </c>
       <c r="G2023" s="8">
-        <v>3574243180.33</v>
+        <v>3573965703.34</v>
       </c>
     </row>
     <row r="2024" spans="1:7" x14ac:dyDescent="0.25">
@@ -59196,7 +59196,7 @@
         <v>46252</v>
       </c>
       <c r="D2025" s="7">
-        <v>4.348636</v>
+        <v>4.348347</v>
       </c>
       <c r="E2025" s="8">
         <v>11387800</v>
@@ -59205,7 +59205,7 @@
         <v>928</v>
       </c>
       <c r="G2025" s="8">
-        <v>49521401.6</v>
+        <v>49518110.43</v>
       </c>
     </row>
     <row r="2026" spans="1:7" x14ac:dyDescent="0.25">
@@ -59265,7 +59265,7 @@
         <v>46252</v>
       </c>
       <c r="D2028" s="7">
-        <v>7.535854</v>
+        <v>7.536391</v>
       </c>
       <c r="E2028" s="8">
         <v>274862095</v>
@@ -59274,7 +59274,7 @@
         <v>1</v>
       </c>
       <c r="G2028" s="8">
-        <v>2071320613.33</v>
+        <v>2071468162.06</v>
       </c>
     </row>
     <row r="2029" spans="1:7" x14ac:dyDescent="0.25">
@@ -59288,7 +59288,7 @@
         <v>46252</v>
       </c>
       <c r="D2029" s="7">
-        <v>1.303251</v>
+        <v>1.303653</v>
       </c>
       <c r="E2029" s="8">
         <v>30260633</v>
@@ -59297,7 +59297,7 @@
         <v>1009</v>
       </c>
       <c r="G2029" s="8">
-        <v>39437195.67</v>
+        <v>39449371.47</v>
       </c>
     </row>
     <row r="2030" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>20.08.2026 10:03:00</t>
+    <t>20.08.2026 10:47:45</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -8647,7 +8647,7 @@
     <t>PMG</t>
   </si>
   <si>
-    <t>İŞ PORTFÖY MG HİSSE SENEDİ SERBEST ÖZEL FON (HİSSE SENEDİ YOĞUN FON)</t>
+    <t>İŞ PORTFÖY MG HİSSE SENEDİ ÖZEL FONU (HİSSE SENEDİ YOĞUN FON)</t>
   </si>
   <si>
     <t>PMH</t>
@@ -13536,7 +13536,7 @@
         <v>46254</v>
       </c>
       <c r="D39" s="10">
-        <v>21.515261</v>
+        <v>21.668706</v>
       </c>
       <c r="E39" s="8">
         <v>6008589</v>
@@ -13545,7 +13545,7 @@
         <v>184</v>
       </c>
       <c r="G39" s="8">
-        <v>129276358.76</v>
+        <v>130198351.26</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -13559,7 +13559,7 @@
         <v>46254</v>
       </c>
       <c r="D40" s="10">
-        <v>31.222674</v>
+        <v>31.257617</v>
       </c>
       <c r="E40" s="8">
         <v>1749021</v>
@@ -13568,7 +13568,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="8">
-        <v>54609111.86</v>
+        <v>54670228.08</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -14732,7 +14732,7 @@
         <v>46254</v>
       </c>
       <c r="D91" s="10">
-        <v>19.132136</v>
+        <v>19.132138</v>
       </c>
       <c r="E91" s="8">
         <v>58638805</v>
@@ -14741,7 +14741,7 @@
         <v>9724</v>
       </c>
       <c r="G91" s="8">
-        <v>1121885596.49</v>
+        <v>1121885702.95</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -15192,7 +15192,7 @@
         <v>46254</v>
       </c>
       <c r="D111" s="10">
-        <v>2.004564</v>
+        <v>2.004761</v>
       </c>
       <c r="E111" s="8">
         <v>56014840</v>
@@ -15201,7 +15201,7 @@
         <v>2274</v>
       </c>
       <c r="G111" s="8">
-        <v>112285343.91</v>
+        <v>112296375.31</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -16388,7 +16388,7 @@
         <v>46254</v>
       </c>
       <c r="D163" s="10">
-        <v>1.584137</v>
+        <v>1.593298</v>
       </c>
       <c r="E163" s="8">
         <v>52243095</v>
@@ -16397,7 +16397,7 @@
         <v>1061</v>
       </c>
       <c r="G163" s="8">
-        <v>82760201.02</v>
+        <v>83238815.2</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -16687,7 +16687,7 @@
         <v>46254</v>
       </c>
       <c r="D176" s="10">
-        <v>1.756617</v>
+        <v>1.756612</v>
       </c>
       <c r="E176" s="8">
         <v>1338188159</v>
@@ -16696,7 +16696,7 @@
         <v>2892</v>
       </c>
       <c r="G176" s="8">
-        <v>2350684238.87</v>
+        <v>2350677339.42</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -19079,7 +19079,7 @@
         <v>46254</v>
       </c>
       <c r="D280" s="10">
-        <v>5.280137</v>
+        <v>5.323317</v>
       </c>
       <c r="E280" s="8">
         <v>4928585</v>
@@ -19088,7 +19088,7 @@
         <v>1156</v>
       </c>
       <c r="G280" s="8">
-        <v>26023601.84</v>
+        <v>26236419.52</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -19148,7 +19148,7 @@
         <v>46254</v>
       </c>
       <c r="D283" s="10">
-        <v>1.207705</v>
+        <v>1.207307</v>
       </c>
       <c r="E283" s="8">
         <v>67070620</v>
@@ -19157,7 +19157,7 @@
         <v>752</v>
       </c>
       <c r="G283" s="8">
-        <v>81001553.58</v>
+        <v>80974829.27</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -19631,7 +19631,7 @@
         <v>46254</v>
       </c>
       <c r="D304" s="10">
-        <v>6.784188</v>
+        <v>6.785036</v>
       </c>
       <c r="E304" s="8">
         <v>445972552</v>
@@ -19640,7 +19640,7 @@
         <v>15200</v>
       </c>
       <c r="G304" s="8">
-        <v>3025561658.47</v>
+        <v>3025939643.08</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -19769,7 +19769,7 @@
         <v>46254</v>
       </c>
       <c r="D310" s="10">
-        <v>1.300457</v>
+        <v>1.301602</v>
       </c>
       <c r="E310" s="8">
         <v>355839776</v>
@@ -19778,7 +19778,7 @@
         <v>132</v>
       </c>
       <c r="G310" s="8">
-        <v>462754345.52</v>
+        <v>463161759.07</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -20160,7 +20160,7 @@
         <v>46254</v>
       </c>
       <c r="D327" s="10">
-        <v>74.366224</v>
+        <v>74.363948</v>
       </c>
       <c r="E327" s="8">
         <v>7358618</v>
@@ -20169,7 +20169,7 @@
         <v>3</v>
       </c>
       <c r="G327" s="8">
-        <v>547232632.05</v>
+        <v>547215886.8</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
@@ -20436,7 +20436,7 @@
         <v>46254</v>
       </c>
       <c r="D339" s="10">
-        <v>101.890862</v>
+        <v>101.896355</v>
       </c>
       <c r="E339" s="8">
         <v>22490084</v>
@@ -20445,7 +20445,7 @@
         <v>1</v>
       </c>
       <c r="G339" s="8">
-        <v>2291534034.02</v>
+        <v>2291657581.34</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
@@ -20712,7 +20712,7 @@
         <v>46254</v>
       </c>
       <c r="D351" s="10">
-        <v>14.793164</v>
+        <v>14.839444</v>
       </c>
       <c r="E351" s="8">
         <v>9513409</v>
@@ -20721,7 +20721,7 @@
         <v>1035</v>
       </c>
       <c r="G351" s="8">
-        <v>140733418.29</v>
+        <v>141173700.47</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -22046,7 +22046,7 @@
         <v>46254</v>
       </c>
       <c r="D409" s="10">
-        <v>48.450616</v>
+        <v>48.450635</v>
       </c>
       <c r="E409" s="8">
         <v>1407619</v>
@@ -22055,7 +22055,7 @@
         <v>106</v>
       </c>
       <c r="G409" s="8">
-        <v>68200007.74</v>
+        <v>68200034.06</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
@@ -22184,7 +22184,7 @@
         <v>46254</v>
       </c>
       <c r="D415" s="10">
-        <v>1.368457</v>
+        <v>1.368067</v>
       </c>
       <c r="E415" s="8">
         <v>180726615</v>
@@ -22193,7 +22193,7 @@
         <v>1576</v>
       </c>
       <c r="G415" s="8">
-        <v>247316649.23</v>
+        <v>247246133.08</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
@@ -22897,7 +22897,7 @@
         <v>46254</v>
       </c>
       <c r="D446" s="7">
-        <v>7.69251</v>
+        <v>7.74415</v>
       </c>
       <c r="E446" s="8">
         <v>257310931</v>
@@ -22906,7 +22906,7 @@
         <v>2346</v>
       </c>
       <c r="G446" s="8">
-        <v>1979366817.17</v>
+        <v>1992654384.62</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
@@ -23932,7 +23932,7 @@
         <v>46254</v>
       </c>
       <c r="D491" s="10">
-        <v>4.821358</v>
+        <v>4.805017</v>
       </c>
       <c r="E491" s="8">
         <v>78492174</v>
@@ -23941,7 +23941,7 @@
         <v>550</v>
       </c>
       <c r="G491" s="8">
-        <v>378438883.26</v>
+        <v>377156258.92</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
@@ -24046,17 +24046,17 @@
       <c r="C496" s="6">
         <v>46254</v>
       </c>
-      <c r="D496" s="8">
-        <v>0</v>
+      <c r="D496" s="10">
+        <v>1.349148</v>
       </c>
       <c r="E496" s="8">
-        <v>0</v>
+        <v>794325765</v>
       </c>
       <c r="F496" s="9">
         <v>4191</v>
       </c>
       <c r="G496" s="8">
-        <v>0</v>
+        <v>1071662936.89</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
@@ -24529,8 +24529,8 @@
       <c r="C517" s="6">
         <v>46254</v>
       </c>
-      <c r="D517" s="7">
-        <v>5.65087</v>
+      <c r="D517" s="10">
+        <v>5.672856</v>
       </c>
       <c r="E517" s="8">
         <v>205955292.63</v>
@@ -24539,7 +24539,7 @@
         <v>2131</v>
       </c>
       <c r="G517" s="8">
-        <v>1163826611.54</v>
+        <v>1168354792.58</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.25">
@@ -24690,17 +24690,17 @@
       <c r="C524" s="6">
         <v>46254</v>
       </c>
-      <c r="D524" s="8">
-        <v>0</v>
+      <c r="D524" s="10">
+        <v>12.695854</v>
       </c>
       <c r="E524" s="8">
-        <v>0</v>
+        <v>29469544</v>
       </c>
       <c r="F524" s="9">
         <v>2714</v>
       </c>
       <c r="G524" s="8">
-        <v>0</v>
+        <v>374141041.29</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.25">
@@ -24989,17 +24989,17 @@
       <c r="C537" s="6">
         <v>46254</v>
       </c>
-      <c r="D537" s="8">
-        <v>0</v>
+      <c r="D537" s="10">
+        <v>70.999263</v>
       </c>
       <c r="E537" s="8">
-        <v>0</v>
+        <v>53983981</v>
       </c>
       <c r="F537" s="9">
         <v>2</v>
       </c>
       <c r="G537" s="8">
-        <v>0</v>
+        <v>3832822886.7</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
@@ -25036,7 +25036,7 @@
         <v>46254</v>
       </c>
       <c r="D539" s="10">
-        <v>3.484621</v>
+        <v>3.482592</v>
       </c>
       <c r="E539" s="8">
         <v>322339559</v>
@@ -25045,7 +25045,7 @@
         <v>3262</v>
       </c>
       <c r="G539" s="8">
-        <v>1123231310.76</v>
+        <v>1122577224.89</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
@@ -25150,17 +25150,17 @@
       <c r="C544" s="6">
         <v>46254</v>
       </c>
-      <c r="D544" s="8">
-        <v>0</v>
+      <c r="D544" s="10">
+        <v>60.932191</v>
       </c>
       <c r="E544" s="8">
-        <v>0</v>
+        <v>194715</v>
       </c>
       <c r="F544" s="9">
         <v>1</v>
       </c>
       <c r="G544" s="8">
-        <v>0</v>
+        <v>11864411.52</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
@@ -25173,17 +25173,17 @@
       <c r="C545" s="6">
         <v>46254</v>
       </c>
-      <c r="D545" s="8">
-        <v>0</v>
+      <c r="D545" s="10">
+        <v>61.772339</v>
       </c>
       <c r="E545" s="8">
-        <v>0</v>
+        <v>8101428</v>
       </c>
       <c r="F545" s="9">
         <v>4</v>
       </c>
       <c r="G545" s="8">
-        <v>0</v>
+        <v>500444156.03</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -25357,17 +25357,17 @@
       <c r="C553" s="6">
         <v>46254</v>
       </c>
-      <c r="D553" s="8">
-        <v>0</v>
+      <c r="D553" s="10">
+        <v>11.387838</v>
       </c>
       <c r="E553" s="8">
-        <v>0</v>
+        <v>29486927</v>
       </c>
       <c r="F553" s="9">
         <v>1</v>
       </c>
       <c r="G553" s="8">
-        <v>0</v>
+        <v>335792345.74</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
@@ -25403,17 +25403,17 @@
       <c r="C555" s="6">
         <v>46254</v>
       </c>
-      <c r="D555" s="8">
-        <v>0</v>
+      <c r="D555" s="10">
+        <v>70.527521</v>
       </c>
       <c r="E555" s="8">
-        <v>0</v>
+        <v>5822807</v>
       </c>
       <c r="F555" s="9">
         <v>3</v>
       </c>
       <c r="G555" s="8">
-        <v>0</v>
+        <v>410668144.47</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -25702,17 +25702,17 @@
       <c r="C568" s="6">
         <v>46254</v>
       </c>
-      <c r="D568" s="8">
-        <v>0</v>
+      <c r="D568" s="10">
+        <v>66.691039</v>
       </c>
       <c r="E568" s="8">
-        <v>0</v>
+        <v>14263356</v>
       </c>
       <c r="F568" s="9">
         <v>3</v>
       </c>
       <c r="G568" s="8">
-        <v>0</v>
+        <v>951238037.61</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.25">
@@ -26323,8 +26323,8 @@
       <c r="C595" s="6">
         <v>46254</v>
       </c>
-      <c r="D595" s="7">
-        <v>2.74679</v>
+      <c r="D595" s="10">
+        <v>2.746822</v>
       </c>
       <c r="E595" s="8">
         <v>1181601</v>
@@ -26333,7 +26333,7 @@
         <v>106</v>
       </c>
       <c r="G595" s="8">
-        <v>3245610.15</v>
+        <v>3245647.71</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.25">
@@ -26692,7 +26692,7 @@
         <v>46254</v>
       </c>
       <c r="D611" s="10">
-        <v>4.760965</v>
+        <v>4.762694</v>
       </c>
       <c r="E611" s="8">
         <v>16606079</v>
@@ -26701,7 +26701,7 @@
         <v>753</v>
       </c>
       <c r="G611" s="8">
-        <v>79060963.82</v>
+        <v>79089678.1</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
@@ -26714,8 +26714,8 @@
       <c r="C612" s="6">
         <v>46254</v>
       </c>
-      <c r="D612" s="10">
-        <v>4.933406</v>
+      <c r="D612" s="11">
+        <v>4.9378</v>
       </c>
       <c r="E612" s="8">
         <v>5230317</v>
@@ -26724,7 +26724,7 @@
         <v>449</v>
       </c>
       <c r="G612" s="8">
-        <v>25803277.3</v>
+        <v>25826259.84</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
@@ -26738,7 +26738,7 @@
         <v>46254</v>
       </c>
       <c r="D613" s="10">
-        <v>4.913776</v>
+        <v>4.913173</v>
       </c>
       <c r="E613" s="8">
         <v>7485764</v>
@@ -26747,7 +26747,7 @@
         <v>465</v>
       </c>
       <c r="G613" s="8">
-        <v>36783365.64</v>
+        <v>36778855.65</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
@@ -26761,7 +26761,7 @@
         <v>46254</v>
       </c>
       <c r="D614" s="10">
-        <v>5.311969</v>
+        <v>5.318821</v>
       </c>
       <c r="E614" s="8">
         <v>9351924</v>
@@ -26770,7 +26770,7 @@
         <v>746</v>
       </c>
       <c r="G614" s="8">
-        <v>49677127.7</v>
+        <v>49741208.34</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
@@ -27496,17 +27496,17 @@
       <c r="C646" s="6">
         <v>46254</v>
       </c>
-      <c r="D646" s="8">
-        <v>0</v>
+      <c r="D646" s="10">
+        <v>57.284951</v>
       </c>
       <c r="E646" s="8">
-        <v>0</v>
+        <v>4643160</v>
       </c>
       <c r="F646" s="9">
         <v>2</v>
       </c>
       <c r="G646" s="8">
-        <v>0</v>
+        <v>265983193.74</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
@@ -27841,17 +27841,17 @@
       <c r="C661" s="6">
         <v>46254</v>
       </c>
-      <c r="D661" s="8">
-        <v>0</v>
+      <c r="D661" s="10">
+        <v>0.449476</v>
       </c>
       <c r="E661" s="8">
-        <v>0</v>
+        <v>10313622592</v>
       </c>
       <c r="F661" s="9">
         <v>38642</v>
       </c>
       <c r="G661" s="8">
-        <v>0</v>
+        <v>4635722960.64</v>
       </c>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.25">
@@ -27933,17 +27933,17 @@
       <c r="C665" s="6">
         <v>46254</v>
       </c>
-      <c r="D665" s="8">
-        <v>0</v>
+      <c r="D665" s="10">
+        <v>4.125471</v>
       </c>
       <c r="E665" s="8">
-        <v>0</v>
+        <v>23611320</v>
       </c>
       <c r="F665" s="9">
         <v>3470</v>
       </c>
       <c r="G665" s="8">
-        <v>0</v>
+        <v>97407819.58</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
@@ -28048,17 +28048,17 @@
       <c r="C670" s="6">
         <v>46254</v>
       </c>
-      <c r="D670" s="8">
-        <v>0</v>
+      <c r="D670" s="10">
+        <v>66.630788</v>
       </c>
       <c r="E670" s="8">
-        <v>0</v>
+        <v>7872114</v>
       </c>
       <c r="F670" s="9">
         <v>3</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>524525162.4</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -28094,17 +28094,17 @@
       <c r="C672" s="6">
         <v>46254</v>
       </c>
-      <c r="D672" s="8">
-        <v>0</v>
+      <c r="D672" s="10">
+        <v>4.081274</v>
       </c>
       <c r="E672" s="8">
-        <v>0</v>
+        <v>5020082762</v>
       </c>
       <c r="F672" s="9">
         <v>1</v>
       </c>
       <c r="G672" s="8">
-        <v>0</v>
+        <v>20488334157.68</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
@@ -28278,17 +28278,17 @@
       <c r="C680" s="6">
         <v>46254</v>
       </c>
-      <c r="D680" s="8">
-        <v>0</v>
+      <c r="D680" s="10">
+        <v>7.682083</v>
       </c>
       <c r="E680" s="8">
-        <v>0</v>
+        <v>186609034</v>
       </c>
       <c r="F680" s="9">
         <v>4163</v>
       </c>
       <c r="G680" s="8">
-        <v>0</v>
+        <v>1433546141.68</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -28301,17 +28301,17 @@
       <c r="C681" s="6">
         <v>46254</v>
       </c>
-      <c r="D681" s="8">
-        <v>0</v>
+      <c r="D681" s="10">
+        <v>7.647826</v>
       </c>
       <c r="E681" s="8">
-        <v>0</v>
+        <v>60335264</v>
       </c>
       <c r="F681" s="9">
         <v>4249</v>
       </c>
       <c r="G681" s="8">
-        <v>0</v>
+        <v>461433593.02</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
@@ -28830,17 +28830,17 @@
       <c r="C704" s="6">
         <v>46254</v>
       </c>
-      <c r="D704" s="8">
-        <v>0</v>
+      <c r="D704" s="11">
+        <v>4.3341</v>
       </c>
       <c r="E704" s="8">
-        <v>0</v>
+        <v>127194369</v>
       </c>
       <c r="F704" s="9">
         <v>1088</v>
       </c>
       <c r="G704" s="8">
-        <v>0</v>
+        <v>551273161.73</v>
       </c>
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.25">
@@ -30164,8 +30164,8 @@
       <c r="C762" s="6">
         <v>46254</v>
       </c>
-      <c r="D762" s="7">
-        <v>0.36595</v>
+      <c r="D762" s="10">
+        <v>0.365905</v>
       </c>
       <c r="E762" s="8">
         <v>3757888796</v>
@@ -30174,7 +30174,7 @@
         <v>2555</v>
       </c>
       <c r="G762" s="8">
-        <v>1375200379.92</v>
+        <v>1375032014.07</v>
       </c>
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.25">
@@ -30625,7 +30625,7 @@
         <v>46254</v>
       </c>
       <c r="D782" s="10">
-        <v>1.094213</v>
+        <v>1.095343</v>
       </c>
       <c r="E782" s="8">
         <v>130163274</v>
@@ -30634,7 +30634,7 @@
         <v>918</v>
       </c>
       <c r="G782" s="8">
-        <v>142426349.28</v>
+        <v>142573399.29</v>
       </c>
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.25">
@@ -32028,7 +32028,7 @@
         <v>46254</v>
       </c>
       <c r="D843" s="10">
-        <v>0.235406</v>
+        <v>0.235411</v>
       </c>
       <c r="E843" s="8">
         <v>3170552313.13</v>
@@ -32037,7 +32037,7 @@
         <v>2529</v>
       </c>
       <c r="G843" s="8">
-        <v>746368351.54</v>
+        <v>746382655.11</v>
       </c>
     </row>
     <row r="844" spans="1:7" x14ac:dyDescent="0.25">
@@ -32626,7 +32626,7 @@
         <v>46254</v>
       </c>
       <c r="D869" s="10">
-        <v>33.600656</v>
+        <v>33.600484</v>
       </c>
       <c r="E869" s="8">
         <v>54671778</v>
@@ -32635,7 +32635,7 @@
         <v>21824</v>
       </c>
       <c r="G869" s="8">
-        <v>1837007624.16</v>
+        <v>1836998228.16</v>
       </c>
     </row>
     <row r="870" spans="1:7" x14ac:dyDescent="0.25">
@@ -32672,7 +32672,7 @@
         <v>46254</v>
       </c>
       <c r="D871" s="10">
-        <v>52.112721</v>
+        <v>52.111553</v>
       </c>
       <c r="E871" s="8">
         <v>31974782.25</v>
@@ -32681,7 +32681,7 @@
         <v>147</v>
       </c>
       <c r="G871" s="8">
-        <v>1666292897.2</v>
+        <v>1666255561.96</v>
       </c>
     </row>
     <row r="872" spans="1:7" x14ac:dyDescent="0.25">
@@ -34098,7 +34098,7 @@
         <v>46254</v>
       </c>
       <c r="D933" s="10">
-        <v>1.314697</v>
+        <v>1.314693</v>
       </c>
       <c r="E933" s="8">
         <v>880379671</v>
@@ -34107,7 +34107,7 @@
         <v>776</v>
       </c>
       <c r="G933" s="8">
-        <v>1157432695.66</v>
+        <v>1157429319.4</v>
       </c>
     </row>
     <row r="934" spans="1:7" x14ac:dyDescent="0.25">
@@ -35408,17 +35408,17 @@
       <c r="C990" s="6">
         <v>46254</v>
       </c>
-      <c r="D990" s="8">
-        <v>0</v>
+      <c r="D990" s="10">
+        <v>1.818387</v>
       </c>
       <c r="E990" s="8">
-        <v>0</v>
+        <v>6366507</v>
       </c>
       <c r="F990" s="9">
         <v>170</v>
       </c>
       <c r="G990" s="8">
-        <v>0</v>
+        <v>11576772.25</v>
       </c>
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.25">
@@ -35500,17 +35500,17 @@
       <c r="C994" s="6">
         <v>46254</v>
       </c>
-      <c r="D994" s="8">
-        <v>0</v>
+      <c r="D994" s="7">
+        <v>57.70908</v>
       </c>
       <c r="E994" s="8">
-        <v>0</v>
+        <v>4238148</v>
       </c>
       <c r="F994" s="9">
         <v>12</v>
       </c>
       <c r="G994" s="8">
-        <v>0</v>
+        <v>244579623.72</v>
       </c>
     </row>
     <row r="995" spans="1:7" x14ac:dyDescent="0.25">
@@ -35845,17 +35845,17 @@
       <c r="C1009" s="6">
         <v>46254</v>
       </c>
-      <c r="D1009" s="8">
-        <v>0</v>
+      <c r="D1009" s="10">
+        <v>1.664007</v>
       </c>
       <c r="E1009" s="8">
-        <v>0</v>
+        <v>10685831</v>
       </c>
       <c r="F1009" s="9">
         <v>262</v>
       </c>
       <c r="G1009" s="8">
-        <v>0</v>
+        <v>17781299.59</v>
       </c>
     </row>
     <row r="1010" spans="1:7" x14ac:dyDescent="0.25">
@@ -36098,17 +36098,17 @@
       <c r="C1020" s="6">
         <v>46254</v>
       </c>
-      <c r="D1020" s="8">
-        <v>0</v>
+      <c r="D1020" s="10">
+        <v>1.537556</v>
       </c>
       <c r="E1020" s="8">
-        <v>0</v>
+        <v>38711206</v>
       </c>
       <c r="F1020" s="9">
         <v>27</v>
       </c>
       <c r="G1020" s="8">
-        <v>0</v>
+        <v>59520629.75</v>
       </c>
     </row>
     <row r="1021" spans="1:7" x14ac:dyDescent="0.25">
@@ -36213,17 +36213,17 @@
       <c r="C1025" s="6">
         <v>46254</v>
       </c>
-      <c r="D1025" s="8">
-        <v>0</v>
+      <c r="D1025" s="10">
+        <v>57.557926</v>
       </c>
       <c r="E1025" s="8">
-        <v>0</v>
+        <v>2186386</v>
       </c>
       <c r="F1025" s="9">
         <v>56</v>
       </c>
       <c r="G1025" s="8">
-        <v>0</v>
+        <v>125843844.61</v>
       </c>
     </row>
     <row r="1026" spans="1:7" x14ac:dyDescent="0.25">
@@ -36972,17 +36972,17 @@
       <c r="C1058" s="6">
         <v>46254</v>
       </c>
-      <c r="D1058" s="8">
-        <v>0</v>
+      <c r="D1058" s="10">
+        <v>53.140925</v>
       </c>
       <c r="E1058" s="8">
-        <v>0</v>
+        <v>266284</v>
       </c>
       <c r="F1058" s="9">
         <v>11</v>
       </c>
       <c r="G1058" s="8">
-        <v>0</v>
+        <v>14150577.98</v>
       </c>
     </row>
     <row r="1059" spans="1:7" x14ac:dyDescent="0.25">
@@ -37179,17 +37179,17 @@
       <c r="C1067" s="6">
         <v>46254</v>
       </c>
-      <c r="D1067" s="8">
-        <v>0</v>
+      <c r="D1067" s="7">
+        <v>1.07251</v>
       </c>
       <c r="E1067" s="8">
-        <v>0</v>
+        <v>1508400</v>
       </c>
       <c r="F1067" s="9">
         <v>16</v>
       </c>
       <c r="G1067" s="8">
-        <v>0</v>
+        <v>1617774.7</v>
       </c>
     </row>
     <row r="1068" spans="1:7" x14ac:dyDescent="0.25">
@@ -37317,17 +37317,17 @@
       <c r="C1073" s="6">
         <v>46254</v>
       </c>
-      <c r="D1073" s="8">
-        <v>0</v>
+      <c r="D1073" s="10">
+        <v>21.586468</v>
       </c>
       <c r="E1073" s="8">
-        <v>0</v>
+        <v>2077265</v>
       </c>
       <c r="F1073" s="9">
         <v>601</v>
       </c>
       <c r="G1073" s="8">
-        <v>0</v>
+        <v>44840814.5</v>
       </c>
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.25">
@@ -37409,17 +37409,17 @@
       <c r="C1077" s="6">
         <v>46254</v>
       </c>
-      <c r="D1077" s="8">
-        <v>0</v>
+      <c r="D1077" s="10">
+        <v>0.522832</v>
       </c>
       <c r="E1077" s="8">
-        <v>0</v>
+        <v>2883126624</v>
       </c>
       <c r="F1077" s="9">
         <v>1131</v>
       </c>
       <c r="G1077" s="8">
-        <v>0</v>
+        <v>1507390303.62</v>
       </c>
     </row>
     <row r="1078" spans="1:7" x14ac:dyDescent="0.25">
@@ -37432,17 +37432,17 @@
       <c r="C1078" s="6">
         <v>46254</v>
       </c>
-      <c r="D1078" s="8">
-        <v>0</v>
+      <c r="D1078" s="10">
+        <v>74.762795</v>
       </c>
       <c r="E1078" s="8">
-        <v>0</v>
+        <v>9823958</v>
       </c>
       <c r="F1078" s="9">
         <v>166</v>
       </c>
       <c r="G1078" s="8">
-        <v>0</v>
+        <v>734466557.96</v>
       </c>
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.25">
@@ -37984,17 +37984,17 @@
       <c r="C1102" s="6">
         <v>46254</v>
       </c>
-      <c r="D1102" s="8">
-        <v>0</v>
+      <c r="D1102" s="10">
+        <v>0.750378</v>
       </c>
       <c r="E1102" s="8">
-        <v>0</v>
+        <v>811188712</v>
       </c>
       <c r="F1102" s="9">
         <v>3664</v>
       </c>
       <c r="G1102" s="8">
-        <v>0</v>
+        <v>608698406.23</v>
       </c>
     </row>
     <row r="1103" spans="1:7" x14ac:dyDescent="0.25">
@@ -38031,7 +38031,7 @@
         <v>46254</v>
       </c>
       <c r="D1104" s="10">
-        <v>49.265874</v>
+        <v>49.267634</v>
       </c>
       <c r="E1104" s="8">
         <v>41444459</v>
@@ -38040,7 +38040,7 @@
         <v>129</v>
       </c>
       <c r="G1104" s="8">
-        <v>2041797494.51</v>
+        <v>2041870454.38</v>
       </c>
     </row>
     <row r="1105" spans="1:7" x14ac:dyDescent="0.25">
@@ -38191,17 +38191,17 @@
       <c r="C1111" s="6">
         <v>46254</v>
       </c>
-      <c r="D1111" s="8">
-        <v>0</v>
+      <c r="D1111" s="10">
+        <v>1.233414</v>
       </c>
       <c r="E1111" s="8">
-        <v>0</v>
+        <v>57338651</v>
       </c>
       <c r="F1111" s="9">
         <v>1576</v>
       </c>
       <c r="G1111" s="8">
-        <v>0</v>
+        <v>70722292.27</v>
       </c>
     </row>
     <row r="1112" spans="1:7" x14ac:dyDescent="0.25">
@@ -38237,17 +38237,17 @@
       <c r="C1113" s="6">
         <v>46254</v>
       </c>
-      <c r="D1113" s="8">
-        <v>0</v>
+      <c r="D1113" s="10">
+        <v>53.932085</v>
       </c>
       <c r="E1113" s="8">
-        <v>0</v>
+        <v>207100</v>
       </c>
       <c r="F1113" s="9">
         <v>18</v>
       </c>
       <c r="G1113" s="8">
-        <v>0</v>
+        <v>11169334.8</v>
       </c>
     </row>
     <row r="1114" spans="1:7" x14ac:dyDescent="0.25">
@@ -39020,7 +39020,7 @@
         <v>46254</v>
       </c>
       <c r="D1147" s="10">
-        <v>2.269067</v>
+        <v>2.269418</v>
       </c>
       <c r="E1147" s="8">
         <v>217075775</v>
@@ -39029,7 +39029,7 @@
         <v>752</v>
       </c>
       <c r="G1147" s="8">
-        <v>492559430.31</v>
+        <v>492635724.66</v>
       </c>
     </row>
     <row r="1148" spans="1:7" x14ac:dyDescent="0.25">
@@ -39158,7 +39158,7 @@
         <v>46254</v>
       </c>
       <c r="D1153" s="10">
-        <v>4.442456</v>
+        <v>4.315193</v>
       </c>
       <c r="E1153" s="8">
         <v>6085154</v>
@@ -39167,7 +39167,7 @@
         <v>29</v>
       </c>
       <c r="G1153" s="8">
-        <v>27033028.94</v>
+        <v>26258611.72</v>
       </c>
     </row>
     <row r="1154" spans="1:7" x14ac:dyDescent="0.25">
@@ -39410,17 +39410,17 @@
       <c r="C1164" s="6">
         <v>46254</v>
       </c>
-      <c r="D1164" s="8">
-        <v>0</v>
+      <c r="D1164" s="10">
+        <v>1.624898</v>
       </c>
       <c r="E1164" s="8">
-        <v>0</v>
+        <v>2651303752</v>
       </c>
       <c r="F1164" s="9">
         <v>13</v>
       </c>
       <c r="G1164" s="8">
-        <v>0</v>
+        <v>4308099411.9</v>
       </c>
     </row>
     <row r="1165" spans="1:7" x14ac:dyDescent="0.25">
@@ -39433,17 +39433,17 @@
       <c r="C1165" s="6">
         <v>46254</v>
       </c>
-      <c r="D1165" s="8">
-        <v>0</v>
+      <c r="D1165" s="10">
+        <v>2.183466</v>
       </c>
       <c r="E1165" s="8">
-        <v>0</v>
+        <v>1833223343</v>
       </c>
       <c r="F1165" s="9">
         <v>15</v>
       </c>
       <c r="G1165" s="8">
-        <v>0</v>
+        <v>4002781416.28</v>
       </c>
     </row>
     <row r="1166" spans="1:7" x14ac:dyDescent="0.25">
@@ -40078,7 +40078,7 @@
         <v>46254</v>
       </c>
       <c r="D1193" s="10">
-        <v>2.330722</v>
+        <v>2.330732</v>
       </c>
       <c r="E1193" s="8">
         <v>2072327500</v>
@@ -40087,7 +40087,7 @@
         <v>16</v>
       </c>
       <c r="G1193" s="8">
-        <v>4830018463.4</v>
+        <v>4830039023.75</v>
       </c>
     </row>
     <row r="1194" spans="1:7" x14ac:dyDescent="0.25">
@@ -40123,17 +40123,17 @@
       <c r="C1195" s="6">
         <v>46254</v>
       </c>
-      <c r="D1195" s="8">
-        <v>0</v>
+      <c r="D1195" s="7">
+        <v>0.79477</v>
       </c>
       <c r="E1195" s="8">
-        <v>0</v>
+        <v>1033653600</v>
       </c>
       <c r="F1195" s="9">
         <v>19</v>
       </c>
       <c r="G1195" s="8">
-        <v>0</v>
+        <v>821516397.12</v>
       </c>
     </row>
     <row r="1196" spans="1:7" x14ac:dyDescent="0.25">
@@ -40261,17 +40261,17 @@
       <c r="C1201" s="6">
         <v>46254</v>
       </c>
-      <c r="D1201" s="8">
-        <v>0</v>
+      <c r="D1201" s="10">
+        <v>0.421382</v>
       </c>
       <c r="E1201" s="8">
-        <v>0</v>
+        <v>1199204513</v>
       </c>
       <c r="F1201" s="9">
         <v>12</v>
       </c>
       <c r="G1201" s="8">
-        <v>0</v>
+        <v>505322782.55</v>
       </c>
     </row>
     <row r="1202" spans="1:7" x14ac:dyDescent="0.25">
@@ -40376,17 +40376,17 @@
       <c r="C1206" s="6">
         <v>46254</v>
       </c>
-      <c r="D1206" s="8">
-        <v>0</v>
+      <c r="D1206" s="10">
+        <v>1.511778</v>
       </c>
       <c r="E1206" s="8">
-        <v>0</v>
+        <v>1340864412</v>
       </c>
       <c r="F1206" s="9">
         <v>397</v>
       </c>
       <c r="G1206" s="8">
-        <v>0</v>
+        <v>2027089976.4</v>
       </c>
     </row>
     <row r="1207" spans="1:7" x14ac:dyDescent="0.25">
@@ -42171,7 +42171,7 @@
         <v>46254</v>
       </c>
       <c r="D1284" s="10">
-        <v>1.009329</v>
+        <v>1.009211</v>
       </c>
       <c r="E1284" s="8">
         <v>244439002</v>
@@ -42180,7 +42180,7 @@
         <v>137</v>
       </c>
       <c r="G1284" s="8">
-        <v>246719335.88</v>
+        <v>246690481.98</v>
       </c>
     </row>
     <row r="1285" spans="1:7" x14ac:dyDescent="0.25">
@@ -44034,7 +44034,7 @@
         <v>46254</v>
       </c>
       <c r="D1365" s="10">
-        <v>3.430754</v>
+        <v>3.430886</v>
       </c>
       <c r="E1365" s="8">
         <v>209967015</v>
@@ -44043,7 +44043,7 @@
         <v>3027</v>
       </c>
       <c r="G1365" s="8">
-        <v>720345250.94</v>
+        <v>720372862.71</v>
       </c>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.25">
@@ -44908,7 +44908,7 @@
         <v>46254</v>
       </c>
       <c r="D1403" s="10">
-        <v>2.956818</v>
+        <v>2.958031</v>
       </c>
       <c r="E1403" s="8">
         <v>5333945</v>
@@ -44917,7 +44917,7 @@
         <v>92</v>
       </c>
       <c r="G1403" s="8">
-        <v>15771503.77</v>
+        <v>15777972.04</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.25">
@@ -49830,7 +49830,7 @@
         <v>46254</v>
       </c>
       <c r="D1617" s="10">
-        <v>1.398976</v>
+        <v>1.412382</v>
       </c>
       <c r="E1617" s="8">
         <v>22286490</v>
@@ -49839,7 +49839,7 @@
         <v>79</v>
       </c>
       <c r="G1617" s="8">
-        <v>31178256.66</v>
+        <v>31477029.36</v>
       </c>
     </row>
     <row r="1618" spans="1:7" x14ac:dyDescent="0.25">
@@ -49922,7 +49922,7 @@
         <v>46254</v>
       </c>
       <c r="D1621" s="10">
-        <v>3.587421</v>
+        <v>3.587501</v>
       </c>
       <c r="E1621" s="8">
         <v>16558307</v>
@@ -49931,7 +49931,7 @@
         <v>644</v>
       </c>
       <c r="G1621" s="8">
-        <v>59401624.64</v>
+        <v>59402935.83</v>
       </c>
     </row>
     <row r="1622" spans="1:7" x14ac:dyDescent="0.25">
@@ -49977,7 +49977,7 @@
         <v>28</v>
       </c>
       <c r="G1623" s="8">
-        <v>317175091.77</v>
+        <v>317175196.84</v>
       </c>
     </row>
     <row r="1624" spans="1:7" x14ac:dyDescent="0.25">
@@ -50313,7 +50313,7 @@
         <v>46254</v>
       </c>
       <c r="D1638" s="10">
-        <v>1.687955</v>
+        <v>1.687434</v>
       </c>
       <c r="E1638" s="8">
         <v>11161001</v>
@@ -50322,7 +50322,7 @@
         <v>307</v>
       </c>
       <c r="G1638" s="8">
-        <v>18839269.34</v>
+        <v>18833449.62</v>
       </c>
     </row>
     <row r="1639" spans="1:7" x14ac:dyDescent="0.25">
@@ -50796,7 +50796,7 @@
         <v>46254</v>
       </c>
       <c r="D1659" s="10">
-        <v>1.276721</v>
+        <v>1.278932</v>
       </c>
       <c r="E1659" s="8">
         <v>144487176</v>
@@ -50805,7 +50805,7 @@
         <v>72</v>
       </c>
       <c r="G1659" s="8">
-        <v>184469822.37</v>
+        <v>184789274.07</v>
       </c>
     </row>
     <row r="1660" spans="1:7" x14ac:dyDescent="0.25">
@@ -51187,7 +51187,7 @@
         <v>46254</v>
       </c>
       <c r="D1676" s="10">
-        <v>21.032225</v>
+        <v>21.035579</v>
       </c>
       <c r="E1676" s="8">
         <v>52856435</v>
@@ -51196,7 +51196,7 @@
         <v>1</v>
       </c>
       <c r="G1676" s="8">
-        <v>1111688444.79</v>
+        <v>1111865737.52</v>
       </c>
     </row>
     <row r="1677" spans="1:7" x14ac:dyDescent="0.25">
@@ -51486,7 +51486,7 @@
         <v>46254</v>
       </c>
       <c r="D1689" s="7">
-        <v>1.33096</v>
+        <v>1.33104</v>
       </c>
       <c r="E1689" s="8">
         <v>141657132</v>
@@ -51495,7 +51495,7 @@
         <v>1</v>
       </c>
       <c r="G1689" s="8">
-        <v>188539964.81</v>
+        <v>188551319.82</v>
       </c>
     </row>
     <row r="1690" spans="1:7" x14ac:dyDescent="0.25">
@@ -51623,8 +51623,8 @@
       <c r="C1695" s="6">
         <v>46254</v>
       </c>
-      <c r="D1695" s="10">
-        <v>40.908344</v>
+      <c r="D1695" s="7">
+        <v>40.91294</v>
       </c>
       <c r="E1695" s="8">
         <v>27809075</v>
@@ -51633,7 +51633,7 @@
         <v>2853</v>
       </c>
       <c r="G1695" s="8">
-        <v>1137623215.71</v>
+        <v>1137751023.72</v>
       </c>
     </row>
     <row r="1696" spans="1:7" x14ac:dyDescent="0.25">
@@ -51647,7 +51647,7 @@
         <v>46254</v>
       </c>
       <c r="D1696" s="10">
-        <v>6.530219</v>
+        <v>6.530495</v>
       </c>
       <c r="E1696" s="8">
         <v>265539976</v>
@@ -51656,7 +51656,7 @@
         <v>1441</v>
       </c>
       <c r="G1696" s="8">
-        <v>1734034310.32</v>
+        <v>1734107406.43</v>
       </c>
     </row>
     <row r="1697" spans="1:7" x14ac:dyDescent="0.25">
@@ -51670,7 +51670,7 @@
         <v>46254</v>
       </c>
       <c r="D1697" s="10">
-        <v>2.755196</v>
+        <v>2.756719</v>
       </c>
       <c r="E1697" s="8">
         <v>268944617</v>
@@ -51679,7 +51679,7 @@
         <v>1348</v>
       </c>
       <c r="G1697" s="8">
-        <v>740995225.35</v>
+        <v>741404849.96</v>
       </c>
     </row>
     <row r="1698" spans="1:7" x14ac:dyDescent="0.25">
@@ -51693,7 +51693,7 @@
         <v>46254</v>
       </c>
       <c r="D1698" s="10">
-        <v>2.826672</v>
+        <v>2.826673</v>
       </c>
       <c r="E1698" s="8">
         <v>12158429</v>
@@ -51702,7 +51702,7 @@
         <v>113</v>
       </c>
       <c r="G1698" s="8">
-        <v>34367895.34</v>
+        <v>34367897.58</v>
       </c>
     </row>
     <row r="1699" spans="1:7" x14ac:dyDescent="0.25">
@@ -52429,7 +52429,7 @@
         <v>46254</v>
       </c>
       <c r="D1730" s="10">
-        <v>68.323064</v>
+        <v>68.323065</v>
       </c>
       <c r="E1730" s="8">
         <v>33019648</v>
@@ -52438,7 +52438,7 @@
         <v>1853</v>
       </c>
       <c r="G1730" s="8">
-        <v>2256003538.39</v>
+        <v>2256003549.98</v>
       </c>
     </row>
     <row r="1731" spans="1:7" x14ac:dyDescent="0.25">
@@ -52544,7 +52544,7 @@
         <v>46254</v>
       </c>
       <c r="D1735" s="10">
-        <v>1.050855</v>
+        <v>1.050898</v>
       </c>
       <c r="E1735" s="8">
         <v>308404466</v>
@@ -52553,7 +52553,7 @@
         <v>259</v>
       </c>
       <c r="G1735" s="8">
-        <v>324088402.6</v>
+        <v>324101708.65</v>
       </c>
     </row>
     <row r="1736" spans="1:7" x14ac:dyDescent="0.25">
@@ -52875,7 +52875,7 @@
         <v>85</v>
       </c>
       <c r="G1749" s="8">
-        <v>403108636.82</v>
+        <v>403108636.81</v>
       </c>
     </row>
     <row r="1750" spans="1:7" x14ac:dyDescent="0.25">
@@ -52889,7 +52889,7 @@
         <v>46254</v>
       </c>
       <c r="D1750" s="10">
-        <v>1.420373</v>
+        <v>1.426192</v>
       </c>
       <c r="E1750" s="8">
         <v>41248224</v>
@@ -52898,7 +52898,7 @@
         <v>91</v>
       </c>
       <c r="G1750" s="8">
-        <v>58587867.59</v>
+        <v>58827903.79</v>
       </c>
     </row>
     <row r="1751" spans="1:7" x14ac:dyDescent="0.25">
@@ -53050,7 +53050,7 @@
         <v>46254</v>
       </c>
       <c r="D1757" s="10">
-        <v>11.312705</v>
+        <v>11.313134</v>
       </c>
       <c r="E1757" s="8">
         <v>673795028</v>
@@ -53059,7 +53059,7 @@
         <v>2620</v>
       </c>
       <c r="G1757" s="8">
-        <v>7622444294.85</v>
+        <v>7622733242.4</v>
       </c>
     </row>
     <row r="1758" spans="1:7" x14ac:dyDescent="0.25">
@@ -53326,7 +53326,7 @@
         <v>46254</v>
       </c>
       <c r="D1769" s="10">
-        <v>21.211526</v>
+        <v>21.212228</v>
       </c>
       <c r="E1769" s="8">
         <v>23851847.01</v>
@@ -53335,7 +53335,7 @@
         <v>1526</v>
       </c>
       <c r="G1769" s="8">
-        <v>505934077.32</v>
+        <v>505950824.59</v>
       </c>
     </row>
     <row r="1770" spans="1:7" x14ac:dyDescent="0.25">
@@ -53372,7 +53372,7 @@
         <v>46254</v>
       </c>
       <c r="D1771" s="10">
-        <v>77.974854</v>
+        <v>77.977613</v>
       </c>
       <c r="E1771" s="8">
         <v>23712000</v>
@@ -53381,7 +53381,7 @@
         <v>386</v>
       </c>
       <c r="G1771" s="8">
-        <v>1848939742.5</v>
+        <v>1849005165.43</v>
       </c>
     </row>
     <row r="1772" spans="1:7" x14ac:dyDescent="0.25">
@@ -53785,8 +53785,8 @@
       <c r="C1789" s="6">
         <v>46254</v>
       </c>
-      <c r="D1789" s="10">
-        <v>1.455626</v>
+      <c r="D1789" s="7">
+        <v>1.45563</v>
       </c>
       <c r="E1789" s="8">
         <v>10507616737.21</v>
@@ -53795,7 +53795,7 @@
         <v>31601</v>
       </c>
       <c r="G1789" s="8">
-        <v>15295156739.52</v>
+        <v>15295201645.74</v>
       </c>
     </row>
     <row r="1790" spans="1:7" x14ac:dyDescent="0.25">
@@ -53832,7 +53832,7 @@
         <v>46254</v>
       </c>
       <c r="D1791" s="10">
-        <v>2.934765</v>
+        <v>2.934781</v>
       </c>
       <c r="E1791" s="8">
         <v>3247896</v>
@@ -53841,7 +53841,7 @@
         <v>531</v>
       </c>
       <c r="G1791" s="8">
-        <v>9531812.13</v>
+        <v>9531862.12</v>
       </c>
     </row>
     <row r="1792" spans="1:7" x14ac:dyDescent="0.25">
@@ -53864,7 +53864,7 @@
         <v>6286</v>
       </c>
       <c r="G1792" s="8">
-        <v>1164772781</v>
+        <v>1164772914.2</v>
       </c>
     </row>
     <row r="1793" spans="1:7" x14ac:dyDescent="0.25">
@@ -57673,7 +57673,7 @@
         <v>46254</v>
       </c>
       <c r="D1958" s="10">
-        <v>10.686765</v>
+        <v>10.686862</v>
       </c>
       <c r="E1958" s="8">
         <v>59166126</v>
@@ -57682,7 +57682,7 @@
         <v>5601</v>
       </c>
       <c r="G1958" s="8">
-        <v>632294502.97</v>
+        <v>632300205.2</v>
       </c>
     </row>
     <row r="1959" spans="1:7" x14ac:dyDescent="0.25">
@@ -58202,7 +58202,7 @@
         <v>46254</v>
       </c>
       <c r="D1981" s="10">
-        <v>3.998859</v>
+        <v>4.002101</v>
       </c>
       <c r="E1981" s="8">
         <v>143654400</v>
@@ -58211,7 +58211,7 @@
         <v>6566</v>
       </c>
       <c r="G1981" s="8">
-        <v>574453627.48</v>
+        <v>574919413.85</v>
       </c>
     </row>
     <row r="1982" spans="1:7" x14ac:dyDescent="0.25">
@@ -58592,8 +58592,8 @@
       <c r="C1998" s="6">
         <v>46254</v>
       </c>
-      <c r="D1998" s="10">
-        <v>50.307429</v>
+      <c r="D1998" s="7">
+        <v>50.30743</v>
       </c>
       <c r="E1998" s="8">
         <v>9467709</v>
@@ -58602,7 +58602,7 @@
         <v>47</v>
       </c>
       <c r="G1998" s="8">
-        <v>476296098.57</v>
+        <v>476296104.6</v>
       </c>
     </row>
     <row r="1999" spans="1:7" x14ac:dyDescent="0.25">
@@ -58753,8 +58753,8 @@
       <c r="C2005" s="6">
         <v>46254</v>
       </c>
-      <c r="D2005" s="10">
-        <v>1.885085</v>
+      <c r="D2005" s="7">
+        <v>1.88743</v>
       </c>
       <c r="E2005" s="8">
         <v>306521428</v>
@@ -58763,7 +58763,7 @@
         <v>11</v>
       </c>
       <c r="G2005" s="8">
-        <v>577819035.71</v>
+        <v>578537671.05</v>
       </c>
     </row>
     <row r="2006" spans="1:7" x14ac:dyDescent="0.25">
@@ -58961,7 +58961,7 @@
         <v>46254</v>
       </c>
       <c r="D2014" s="10">
-        <v>19.469536</v>
+        <v>19.471153</v>
       </c>
       <c r="E2014" s="8">
         <v>165170912</v>
@@ -58970,7 +58970,7 @@
         <v>2775</v>
       </c>
       <c r="G2014" s="8">
-        <v>3215800958.41</v>
+        <v>3216068060.64</v>
       </c>
     </row>
     <row r="2015" spans="1:7" x14ac:dyDescent="0.25">
@@ -59237,7 +59237,7 @@
         <v>46254</v>
       </c>
       <c r="D2026" s="10">
-        <v>11.985823</v>
+        <v>11.981337</v>
       </c>
       <c r="E2026" s="8">
         <v>299315692</v>
@@ -59246,7 +59246,7 @@
         <v>24</v>
       </c>
       <c r="G2026" s="8">
-        <v>3587544767.5</v>
+        <v>3586202262.34</v>
       </c>
     </row>
     <row r="2027" spans="1:7" x14ac:dyDescent="0.25">
@@ -59283,7 +59283,7 @@
         <v>46254</v>
       </c>
       <c r="D2028" s="10">
-        <v>4.315965</v>
+        <v>4.327292</v>
       </c>
       <c r="E2028" s="8">
         <v>11376800</v>
@@ -59292,7 +59292,7 @@
         <v>929</v>
       </c>
       <c r="G2028" s="8">
-        <v>49101869.4</v>
+        <v>49230735.67</v>
       </c>
     </row>
     <row r="2029" spans="1:7" x14ac:dyDescent="0.25">
@@ -59352,7 +59352,7 @@
         <v>46254</v>
       </c>
       <c r="D2031" s="10">
-        <v>7.556314</v>
+        <v>7.554866</v>
       </c>
       <c r="E2031" s="8">
         <v>274862095</v>
@@ -59361,7 +59361,7 @@
         <v>1</v>
       </c>
       <c r="G2031" s="8">
-        <v>2076944224.61</v>
+        <v>2076546361.84</v>
       </c>
     </row>
     <row r="2032" spans="1:7" x14ac:dyDescent="0.25">
@@ -59375,7 +59375,7 @@
         <v>46254</v>
       </c>
       <c r="D2032" s="10">
-        <v>1.316983</v>
+        <v>1.321568</v>
       </c>
       <c r="E2032" s="8">
         <v>29956126</v>
@@ -59384,7 +59384,7 @@
         <v>1029</v>
       </c>
       <c r="G2032" s="8">
-        <v>39451710.45</v>
+        <v>39589043.49</v>
       </c>
     </row>
     <row r="2033" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>20.08.2026 10:47:45</t>
+    <t>20.08.2026 11:28:04</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -13259,17 +13259,17 @@
       <c r="C27" s="6">
         <v>46254</v>
       </c>
-      <c r="D27" s="8">
-        <v>0</v>
+      <c r="D27" s="10">
+        <v>0.181452</v>
       </c>
       <c r="E27" s="8">
-        <v>0</v>
+        <v>7511077903</v>
       </c>
       <c r="F27" s="9">
         <v>35295</v>
       </c>
       <c r="G27" s="8">
-        <v>0</v>
+        <v>1362897070.95</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -14294,17 +14294,17 @@
       <c r="C72" s="6">
         <v>46254</v>
       </c>
-      <c r="D72" s="8">
-        <v>0</v>
+      <c r="D72" s="10">
+        <v>6.915348</v>
       </c>
       <c r="E72" s="8">
-        <v>0</v>
+        <v>12376378</v>
       </c>
       <c r="F72" s="9">
         <v>2911</v>
       </c>
       <c r="G72" s="8">
-        <v>0</v>
+        <v>85586958.18</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -14409,17 +14409,17 @@
       <c r="C77" s="6">
         <v>46254</v>
       </c>
-      <c r="D77" s="8">
-        <v>0</v>
+      <c r="D77" s="10">
+        <v>16.031402</v>
       </c>
       <c r="E77" s="8">
-        <v>0</v>
+        <v>252295654</v>
       </c>
       <c r="F77" s="9">
         <v>7422</v>
       </c>
       <c r="G77" s="8">
-        <v>0</v>
+        <v>4044652978.83</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -14432,17 +14432,17 @@
       <c r="C78" s="6">
         <v>46254</v>
       </c>
-      <c r="D78" s="8">
-        <v>0</v>
+      <c r="D78" s="10">
+        <v>18.457926</v>
       </c>
       <c r="E78" s="8">
-        <v>0</v>
+        <v>173470740</v>
       </c>
       <c r="F78" s="9">
         <v>5111</v>
       </c>
       <c r="G78" s="8">
-        <v>0</v>
+        <v>3201910152.04</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -14479,16 +14479,16 @@
         <v>46254</v>
       </c>
       <c r="D80" s="10">
-        <v>45.482905</v>
+        <v>45.482672</v>
       </c>
       <c r="E80" s="8">
-        <v>150456</v>
+        <v>149967</v>
       </c>
       <c r="F80" s="9">
         <v>40</v>
       </c>
       <c r="G80" s="8">
-        <v>6843176</v>
+        <v>6820899.82</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -16893,8 +16893,8 @@
       <c r="C185" s="6">
         <v>46254</v>
       </c>
-      <c r="D185" s="10">
-        <v>1.235445</v>
+      <c r="D185" s="11">
+        <v>1.2417</v>
       </c>
       <c r="E185" s="8">
         <v>95034594</v>
@@ -16903,7 +16903,7 @@
         <v>2721</v>
       </c>
       <c r="G185" s="8">
-        <v>117409991.09</v>
+        <v>118004484.84</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -18467,7 +18467,7 @@
         <v>1937</v>
       </c>
       <c r="G253" s="8">
-        <v>229516590.4</v>
+        <v>229514577.29</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -18573,7 +18573,7 @@
         <v>46254</v>
       </c>
       <c r="D258" s="10">
-        <v>0.140454</v>
+        <v>0.140446</v>
       </c>
       <c r="E258" s="8">
         <v>5152791000</v>
@@ -18582,7 +18582,7 @@
         <v>2907</v>
       </c>
       <c r="G258" s="8">
-        <v>723729788.86</v>
+        <v>723689526.38</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -20712,7 +20712,7 @@
         <v>46254</v>
       </c>
       <c r="D351" s="10">
-        <v>14.839444</v>
+        <v>14.839456</v>
       </c>
       <c r="E351" s="8">
         <v>9513409</v>
@@ -20721,7 +20721,7 @@
         <v>1035</v>
       </c>
       <c r="G351" s="8">
-        <v>141173700.47</v>
+        <v>141173818.17</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -21135,7 +21135,7 @@
         <v>313</v>
       </c>
       <c r="G369" s="8">
-        <v>306338237.79</v>
+        <v>306338237.9</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -22413,17 +22413,17 @@
       <c r="C425" s="6">
         <v>46254</v>
       </c>
-      <c r="D425" s="10">
-        <v>3.026101</v>
+      <c r="D425" s="7">
+        <v>3.05088</v>
       </c>
       <c r="E425" s="8">
-        <v>14269492</v>
+        <v>14239137</v>
       </c>
       <c r="F425" s="9">
         <v>502</v>
       </c>
       <c r="G425" s="8">
-        <v>43180918.62</v>
+        <v>43441893.49</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
@@ -22552,7 +22552,7 @@
         <v>46254</v>
       </c>
       <c r="D431" s="10">
-        <v>5.437064</v>
+        <v>5.437373</v>
       </c>
       <c r="E431" s="8">
         <v>40408496</v>
@@ -22561,7 +22561,7 @@
         <v>33</v>
       </c>
       <c r="G431" s="8">
-        <v>219703592.34</v>
+        <v>219716048.37</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
@@ -25726,7 +25726,7 @@
         <v>46254</v>
       </c>
       <c r="D569" s="10">
-        <v>10.518957</v>
+        <v>10.588554</v>
       </c>
       <c r="E569" s="8">
         <v>7322495</v>
@@ -25735,7 +25735,7 @@
         <v>977</v>
       </c>
       <c r="G569" s="8">
-        <v>77025009.7</v>
+        <v>77534631.57</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.25">
@@ -26117,16 +26117,16 @@
         <v>46254</v>
       </c>
       <c r="D586" s="10">
-        <v>4.313107</v>
+        <v>4.347511</v>
       </c>
       <c r="E586" s="8">
-        <v>3869773</v>
+        <v>3869911</v>
       </c>
       <c r="F586" s="9">
         <v>69</v>
       </c>
       <c r="G586" s="8">
-        <v>16690745.11</v>
+        <v>16824480.84</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.25">
@@ -26163,7 +26163,7 @@
         <v>46254</v>
       </c>
       <c r="D588" s="10">
-        <v>0.999275</v>
+        <v>0.999276</v>
       </c>
       <c r="E588" s="8">
         <v>48019946</v>
@@ -26172,7 +26172,7 @@
         <v>6</v>
       </c>
       <c r="G588" s="8">
-        <v>47985150.05</v>
+        <v>47985174.25</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -26300,17 +26300,17 @@
       <c r="C594" s="6">
         <v>46254</v>
       </c>
-      <c r="D594" s="8">
-        <v>0</v>
+      <c r="D594" s="10">
+        <v>7.809039</v>
       </c>
       <c r="E594" s="8">
-        <v>0</v>
+        <v>539504332</v>
       </c>
       <c r="F594" s="9">
         <v>21292</v>
       </c>
       <c r="G594" s="8">
-        <v>0</v>
+        <v>4213010593.17</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.25">
@@ -26668,17 +26668,17 @@
       <c r="C610" s="6">
         <v>46254</v>
       </c>
-      <c r="D610" s="8">
-        <v>0</v>
+      <c r="D610" s="10">
+        <v>1.591516</v>
       </c>
       <c r="E610" s="8">
-        <v>0</v>
+        <v>1231677</v>
       </c>
       <c r="F610" s="9">
         <v>476</v>
       </c>
       <c r="G610" s="8">
-        <v>0</v>
+        <v>1960233.47</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.25">
@@ -27887,17 +27887,17 @@
       <c r="C663" s="6">
         <v>46254</v>
       </c>
-      <c r="D663" s="8">
-        <v>0</v>
+      <c r="D663" s="10">
+        <v>12.529864</v>
       </c>
       <c r="E663" s="8">
-        <v>0</v>
+        <v>528713199</v>
       </c>
       <c r="F663" s="9">
         <v>53004</v>
       </c>
       <c r="G663" s="8">
-        <v>0</v>
+        <v>6624704221.89</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -29774,16 +29774,16 @@
         <v>46254</v>
       </c>
       <c r="D745" s="10">
-        <v>5.990842</v>
+        <v>5.990663</v>
       </c>
       <c r="E745" s="8">
-        <v>38122280</v>
+        <v>38240858</v>
       </c>
       <c r="F745" s="9">
         <v>90</v>
       </c>
       <c r="G745" s="8">
-        <v>228384563.59</v>
+        <v>229088102.86</v>
       </c>
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.25">
@@ -32809,17 +32809,17 @@
       <c r="C877" s="6">
         <v>46254</v>
       </c>
-      <c r="D877" s="8">
-        <v>0</v>
+      <c r="D877" s="10">
+        <v>7.247785</v>
       </c>
       <c r="E877" s="8">
-        <v>0</v>
+        <v>4671928</v>
       </c>
       <c r="F877" s="9">
         <v>397</v>
       </c>
       <c r="G877" s="8">
-        <v>0</v>
+        <v>33861128.15</v>
       </c>
     </row>
     <row r="878" spans="1:7" x14ac:dyDescent="0.25">
@@ -33891,7 +33891,7 @@
         <v>46254</v>
       </c>
       <c r="D924" s="10">
-        <v>0.123355</v>
+        <v>0.123343</v>
       </c>
       <c r="E924" s="8">
         <v>1105011730</v>
@@ -33900,7 +33900,7 @@
         <v>22</v>
       </c>
       <c r="G924" s="8">
-        <v>136308481.58</v>
+        <v>136295830.34</v>
       </c>
     </row>
     <row r="925" spans="1:7" x14ac:dyDescent="0.25">
@@ -34006,7 +34006,7 @@
         <v>46254</v>
       </c>
       <c r="D929" s="10">
-        <v>0.180968</v>
+        <v>0.181023</v>
       </c>
       <c r="E929" s="8">
         <v>38662308904</v>
@@ -34015,7 +34015,7 @@
         <v>164</v>
       </c>
       <c r="G929" s="8">
-        <v>6996640230.67</v>
+        <v>6998767651.79</v>
       </c>
     </row>
     <row r="930" spans="1:7" x14ac:dyDescent="0.25">
@@ -34143,17 +34143,17 @@
       <c r="C935" s="6">
         <v>46254</v>
       </c>
-      <c r="D935" s="8">
-        <v>0</v>
+      <c r="D935" s="10">
+        <v>7.424551</v>
       </c>
       <c r="E935" s="8">
-        <v>0</v>
+        <v>71485303</v>
       </c>
       <c r="F935" s="9">
         <v>2000</v>
       </c>
       <c r="G935" s="8">
-        <v>0</v>
+        <v>530746279.61</v>
       </c>
     </row>
     <row r="936" spans="1:7" x14ac:dyDescent="0.25">
@@ -34650,7 +34650,7 @@
         <v>46254</v>
       </c>
       <c r="D957" s="10">
-        <v>6.326777</v>
+        <v>6.314111</v>
       </c>
       <c r="E957" s="8">
         <v>2005409.66</v>
@@ -34659,7 +34659,7 @@
         <v>721</v>
       </c>
       <c r="G957" s="8">
-        <v>12687779.69</v>
+        <v>12662379.7</v>
       </c>
     </row>
     <row r="958" spans="1:7" x14ac:dyDescent="0.25">
@@ -35064,7 +35064,7 @@
         <v>46254</v>
       </c>
       <c r="D975" s="10">
-        <v>10.890753</v>
+        <v>10.920002</v>
       </c>
       <c r="E975" s="8">
         <v>9162411</v>
@@ -35073,7 +35073,7 @@
         <v>87</v>
       </c>
       <c r="G975" s="8">
-        <v>99785558.94</v>
+        <v>100053541.95</v>
       </c>
     </row>
     <row r="976" spans="1:7" x14ac:dyDescent="0.25">
@@ -36467,16 +36467,16 @@
         <v>46254</v>
       </c>
       <c r="D1036" s="10">
-        <v>41.564587</v>
+        <v>41.556299</v>
       </c>
       <c r="E1036" s="8">
-        <v>24981</v>
+        <v>22981</v>
       </c>
       <c r="F1036" s="9">
         <v>2</v>
       </c>
       <c r="G1036" s="8">
-        <v>1038324.94</v>
+        <v>955005.3</v>
       </c>
     </row>
     <row r="1037" spans="1:7" x14ac:dyDescent="0.25">
@@ -39089,16 +39089,16 @@
         <v>46254</v>
       </c>
       <c r="D1150" s="10">
-        <v>7.687721</v>
+        <v>7.736957</v>
       </c>
       <c r="E1150" s="8">
-        <v>6720971</v>
+        <v>6719737</v>
       </c>
       <c r="F1150" s="9">
         <v>780</v>
       </c>
       <c r="G1150" s="8">
-        <v>51668952.7</v>
+        <v>51990317.33</v>
       </c>
     </row>
     <row r="1151" spans="1:7" x14ac:dyDescent="0.25">
@@ -39135,16 +39135,16 @@
         <v>46254</v>
       </c>
       <c r="D1152" s="10">
-        <v>10.907513</v>
+        <v>10.858322</v>
       </c>
       <c r="E1152" s="8">
-        <v>90549652</v>
+        <v>90467642</v>
       </c>
       <c r="F1152" s="9">
         <v>7590</v>
       </c>
       <c r="G1152" s="8">
-        <v>987671520.56</v>
+        <v>982326776.92</v>
       </c>
     </row>
     <row r="1153" spans="1:7" x14ac:dyDescent="0.25">
@@ -40101,16 +40101,16 @@
         <v>46254</v>
       </c>
       <c r="D1194" s="10">
-        <v>2.730356</v>
+        <v>2.737418</v>
       </c>
       <c r="E1194" s="8">
-        <v>10285677</v>
+        <v>10275176</v>
       </c>
       <c r="F1194" s="9">
         <v>680</v>
       </c>
       <c r="G1194" s="8">
-        <v>28083563.35</v>
+        <v>28127452.47</v>
       </c>
     </row>
     <row r="1195" spans="1:7" x14ac:dyDescent="0.25">
@@ -40492,7 +40492,7 @@
         <v>46254</v>
       </c>
       <c r="D1211" s="10">
-        <v>0.961434</v>
+        <v>0.988954</v>
       </c>
       <c r="E1211" s="8">
         <v>588672037</v>
@@ -40501,7 +40501,7 @@
         <v>13</v>
       </c>
       <c r="G1211" s="8">
-        <v>565969506.47</v>
+        <v>582169426.59</v>
       </c>
     </row>
     <row r="1212" spans="1:7" x14ac:dyDescent="0.25">
@@ -40537,17 +40537,17 @@
       <c r="C1213" s="6">
         <v>46254</v>
       </c>
-      <c r="D1213" s="8">
-        <v>0</v>
+      <c r="D1213" s="10">
+        <v>1.348928</v>
       </c>
       <c r="E1213" s="8">
-        <v>0</v>
+        <v>1339716861</v>
       </c>
       <c r="F1213" s="9">
         <v>34</v>
       </c>
       <c r="G1213" s="8">
-        <v>0</v>
+        <v>1807181319.94</v>
       </c>
     </row>
     <row r="1214" spans="1:7" x14ac:dyDescent="0.25">
@@ -40606,17 +40606,17 @@
       <c r="C1216" s="6">
         <v>46254</v>
       </c>
-      <c r="D1216" s="8">
-        <v>0</v>
+      <c r="D1216" s="10">
+        <v>5.629059</v>
       </c>
       <c r="E1216" s="8">
-        <v>0</v>
+        <v>2163301</v>
       </c>
       <c r="F1216" s="9">
         <v>154</v>
       </c>
       <c r="G1216" s="8">
-        <v>0</v>
+        <v>12177348.9</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.25">
@@ -41434,17 +41434,17 @@
       <c r="C1252" s="6">
         <v>46254</v>
       </c>
-      <c r="D1252" s="8">
-        <v>0</v>
+      <c r="D1252" s="10">
+        <v>1.598098</v>
       </c>
       <c r="E1252" s="8">
-        <v>0</v>
+        <v>592973692</v>
       </c>
       <c r="F1252" s="9">
         <v>1</v>
       </c>
       <c r="G1252" s="8">
-        <v>0</v>
+        <v>947630007.9</v>
       </c>
     </row>
     <row r="1253" spans="1:7" x14ac:dyDescent="0.25">
@@ -42469,17 +42469,17 @@
       <c r="C1297" s="6">
         <v>46254</v>
       </c>
-      <c r="D1297" s="8">
-        <v>0</v>
+      <c r="D1297" s="10">
+        <v>19.585015</v>
       </c>
       <c r="E1297" s="8">
-        <v>0</v>
+        <v>83924190</v>
       </c>
       <c r="F1297" s="9">
         <v>3864</v>
       </c>
       <c r="G1297" s="8">
-        <v>0</v>
+        <v>1643656512.07</v>
       </c>
     </row>
     <row r="1298" spans="1:7" x14ac:dyDescent="0.25">
@@ -42769,7 +42769,7 @@
         <v>46254</v>
       </c>
       <c r="D1310" s="10">
-        <v>3.924677</v>
+        <v>3.908664</v>
       </c>
       <c r="E1310" s="8">
         <v>11321464</v>
@@ -42778,7 +42778,7 @@
         <v>653</v>
       </c>
       <c r="G1310" s="8">
-        <v>44433087.45</v>
+        <v>44251794.09</v>
       </c>
     </row>
     <row r="1311" spans="1:7" x14ac:dyDescent="0.25">
@@ -42792,7 +42792,7 @@
         <v>46254</v>
       </c>
       <c r="D1311" s="10">
-        <v>5.066661</v>
+        <v>5.084885</v>
       </c>
       <c r="E1311" s="8">
         <v>3744558</v>
@@ -42801,7 +42801,7 @@
         <v>223</v>
       </c>
       <c r="G1311" s="8">
-        <v>18972406.22</v>
+        <v>19040648.14</v>
       </c>
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
@@ -43114,7 +43114,7 @@
         <v>46254</v>
       </c>
       <c r="D1325" s="10">
-        <v>5.059805</v>
+        <v>5.065267</v>
       </c>
       <c r="E1325" s="8">
         <v>64247071</v>
@@ -43123,7 +43123,7 @@
         <v>503</v>
       </c>
       <c r="G1325" s="8">
-        <v>325077657.71</v>
+        <v>325428578.46</v>
       </c>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.25">
@@ -43505,7 +43505,7 @@
         <v>46254</v>
       </c>
       <c r="D1342" s="10">
-        <v>26.601911</v>
+        <v>26.590451</v>
       </c>
       <c r="E1342" s="8">
         <v>35427283</v>
@@ -43514,7 +43514,7 @@
         <v>2503</v>
       </c>
       <c r="G1342" s="8">
-        <v>942433431.89</v>
+        <v>942027417.12</v>
       </c>
     </row>
     <row r="1343" spans="1:7" x14ac:dyDescent="0.25">
@@ -43527,8 +43527,8 @@
       <c r="C1343" s="6">
         <v>46254</v>
       </c>
-      <c r="D1343" s="7">
-        <v>23.32697</v>
+      <c r="D1343" s="10">
+        <v>23.281594</v>
       </c>
       <c r="E1343" s="8">
         <v>9642818</v>
@@ -43537,7 +43537,7 @@
         <v>1547</v>
       </c>
       <c r="G1343" s="8">
-        <v>224937724.11</v>
+        <v>224500170.63</v>
       </c>
     </row>
     <row r="1344" spans="1:7" x14ac:dyDescent="0.25">
@@ -44448,7 +44448,7 @@
         <v>46254</v>
       </c>
       <c r="D1383" s="10">
-        <v>2.304702</v>
+        <v>2.322812</v>
       </c>
       <c r="E1383" s="8">
         <v>48044668</v>
@@ -44457,7 +44457,7 @@
         <v>638</v>
       </c>
       <c r="G1383" s="8">
-        <v>110728620.71</v>
+        <v>111598737.25</v>
       </c>
     </row>
     <row r="1384" spans="1:7" x14ac:dyDescent="0.25">
@@ -44516,17 +44516,17 @@
       <c r="C1386" s="6">
         <v>46254</v>
       </c>
-      <c r="D1386" s="8">
-        <v>0</v>
+      <c r="D1386" s="10">
+        <v>5.282889</v>
       </c>
       <c r="E1386" s="8">
-        <v>0</v>
+        <v>2576306418</v>
       </c>
       <c r="F1386" s="9">
         <v>54533</v>
       </c>
       <c r="G1386" s="8">
-        <v>0</v>
+        <v>13610340845</v>
       </c>
     </row>
     <row r="1387" spans="1:7" x14ac:dyDescent="0.25">
@@ -45045,17 +45045,17 @@
       <c r="C1409" s="6">
         <v>46254</v>
       </c>
-      <c r="D1409" s="8">
-        <v>0</v>
+      <c r="D1409" s="10">
+        <v>4.046148</v>
       </c>
       <c r="E1409" s="8">
-        <v>0</v>
+        <v>9320367641</v>
       </c>
       <c r="F1409" s="9">
         <v>127029</v>
       </c>
       <c r="G1409" s="8">
-        <v>0</v>
+        <v>37711585943.3</v>
       </c>
     </row>
     <row r="1410" spans="1:7" x14ac:dyDescent="0.25">
@@ -45230,7 +45230,7 @@
         <v>46254</v>
       </c>
       <c r="D1417" s="7">
-        <v>3.95918</v>
+        <v>3.95385</v>
       </c>
       <c r="E1417" s="8">
         <v>123729532</v>
@@ -45239,7 +45239,7 @@
         <v>8075</v>
       </c>
       <c r="G1417" s="8">
-        <v>489867453.69</v>
+        <v>489207995.8</v>
       </c>
     </row>
     <row r="1418" spans="1:7" x14ac:dyDescent="0.25">
@@ -48151,7 +48151,7 @@
         <v>46254</v>
       </c>
       <c r="D1544" s="10">
-        <v>1.112333</v>
+        <v>1.112721</v>
       </c>
       <c r="E1544" s="8">
         <v>22267494</v>
@@ -48160,7 +48160,7 @@
         <v>373</v>
       </c>
       <c r="G1544" s="8">
-        <v>24768857.55</v>
+        <v>24777506.7</v>
       </c>
     </row>
     <row r="1545" spans="1:7" x14ac:dyDescent="0.25">
@@ -49875,17 +49875,17 @@
       <c r="C1619" s="6">
         <v>46254</v>
       </c>
-      <c r="D1619" s="8">
-        <v>0</v>
+      <c r="D1619" s="7">
+        <v>1.95135</v>
       </c>
       <c r="E1619" s="8">
-        <v>0</v>
+        <v>108729534</v>
       </c>
       <c r="F1619" s="9">
         <v>2639</v>
       </c>
       <c r="G1619" s="8">
-        <v>0</v>
+        <v>212169326.98</v>
       </c>
     </row>
     <row r="1620" spans="1:7" x14ac:dyDescent="0.25">
@@ -50474,16 +50474,16 @@
         <v>46254</v>
       </c>
       <c r="D1645" s="10">
-        <v>2.170671</v>
+        <v>2.190734</v>
       </c>
       <c r="E1645" s="8">
-        <v>43448124</v>
+        <v>43265213</v>
       </c>
       <c r="F1645" s="9">
         <v>801</v>
       </c>
       <c r="G1645" s="8">
-        <v>94311570.22</v>
+        <v>94782588.73</v>
       </c>
     </row>
     <row r="1646" spans="1:7" x14ac:dyDescent="0.25">
@@ -51462,17 +51462,17 @@
       <c r="C1688" s="6">
         <v>46254</v>
       </c>
-      <c r="D1688" s="8">
-        <v>0</v>
+      <c r="D1688" s="7">
+        <v>4.53945</v>
       </c>
       <c r="E1688" s="8">
-        <v>0</v>
+        <v>726366212</v>
       </c>
       <c r="F1688" s="9">
         <v>2777</v>
       </c>
       <c r="G1688" s="8">
-        <v>0</v>
+        <v>3297302880.31</v>
       </c>
     </row>
     <row r="1689" spans="1:7" x14ac:dyDescent="0.25">
@@ -52359,17 +52359,17 @@
       <c r="C1727" s="6">
         <v>46254</v>
       </c>
-      <c r="D1727" s="8">
-        <v>0</v>
+      <c r="D1727" s="10">
+        <v>5.334039</v>
       </c>
       <c r="E1727" s="8">
-        <v>0</v>
+        <v>10150451</v>
       </c>
       <c r="F1727" s="9">
         <v>545</v>
       </c>
       <c r="G1727" s="8">
-        <v>0</v>
+        <v>54142899.95</v>
       </c>
     </row>
     <row r="1728" spans="1:7" x14ac:dyDescent="0.25">
@@ -52382,17 +52382,17 @@
       <c r="C1728" s="6">
         <v>46254</v>
       </c>
-      <c r="D1728" s="8">
-        <v>0</v>
+      <c r="D1728" s="10">
+        <v>6.478327</v>
       </c>
       <c r="E1728" s="8">
-        <v>0</v>
+        <v>92159160</v>
       </c>
       <c r="F1728" s="9">
         <v>913</v>
       </c>
       <c r="G1728" s="8">
-        <v>0</v>
+        <v>597037188.36</v>
       </c>
     </row>
     <row r="1729" spans="1:7" x14ac:dyDescent="0.25">
@@ -53233,17 +53233,17 @@
       <c r="C1765" s="6">
         <v>46254</v>
       </c>
-      <c r="D1765" s="8">
-        <v>0</v>
+      <c r="D1765" s="10">
+        <v>13.151678</v>
       </c>
       <c r="E1765" s="8">
-        <v>0</v>
+        <v>455594163</v>
       </c>
       <c r="F1765" s="9">
         <v>12665</v>
       </c>
       <c r="G1765" s="8">
-        <v>0</v>
+        <v>5991827513.32</v>
       </c>
     </row>
     <row r="1766" spans="1:7" x14ac:dyDescent="0.25">
@@ -55625,17 +55625,17 @@
       <c r="C1869" s="6">
         <v>46254</v>
       </c>
-      <c r="D1869" s="8">
-        <v>0</v>
+      <c r="D1869" s="10">
+        <v>4.100606</v>
       </c>
       <c r="E1869" s="8">
-        <v>0</v>
+        <v>65938802</v>
       </c>
       <c r="F1869" s="9">
         <v>272</v>
       </c>
       <c r="G1869" s="8">
-        <v>0</v>
+        <v>270389069.73</v>
       </c>
     </row>
     <row r="1870" spans="1:7" x14ac:dyDescent="0.25">
@@ -56545,17 +56545,17 @@
       <c r="C1909" s="6">
         <v>46254</v>
       </c>
-      <c r="D1909" s="8">
-        <v>0</v>
+      <c r="D1909" s="10">
+        <v>1.024697</v>
       </c>
       <c r="E1909" s="8">
-        <v>0</v>
+        <v>181202</v>
       </c>
       <c r="F1909" s="9">
         <v>71</v>
       </c>
       <c r="G1909" s="8">
-        <v>0</v>
+        <v>185677.19</v>
       </c>
     </row>
     <row r="1910" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>21.08.2026 11:37:02</t>
+    <t>21.08.2026 22:24:50</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -24101,7 +24101,7 @@
         <v>46255</v>
       </c>
       <c r="D498" s="10">
-        <v>1.366277</v>
+        <v>1.366276</v>
       </c>
       <c r="E498" s="8">
         <v>795044240</v>
@@ -24110,7 +24110,7 @@
         <v>4230</v>
       </c>
       <c r="G498" s="8">
-        <v>1086250635.57</v>
+        <v>1086249953.74</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
@@ -32335,7 +32335,7 @@
         <v>46255</v>
       </c>
       <c r="D856" s="10">
-        <v>11.499307</v>
+        <v>11.499874</v>
       </c>
       <c r="E856" s="8">
         <v>201138551</v>
@@ -32344,7 +32344,7 @@
         <v>3</v>
       </c>
       <c r="G856" s="8">
-        <v>2312953860.5</v>
+        <v>2313067934.76</v>
       </c>
     </row>
     <row r="857" spans="1:7" x14ac:dyDescent="0.25">
@@ -35095,7 +35095,7 @@
         <v>46255</v>
       </c>
       <c r="D976" s="10">
-        <v>10.919586</v>
+        <v>10.958575</v>
       </c>
       <c r="E976" s="8">
         <v>9162474</v>
@@ -35104,7 +35104,7 @@
         <v>86</v>
       </c>
       <c r="G976" s="8">
-        <v>100050425.06</v>
+        <v>100407654.94</v>
       </c>
     </row>
     <row r="977" spans="1:7" x14ac:dyDescent="0.25">
@@ -45766,17 +45766,17 @@
       <c r="C1440" s="6">
         <v>46255</v>
       </c>
-      <c r="D1440" s="8">
-        <v>0</v>
+      <c r="D1440" s="10">
+        <v>1.610779</v>
       </c>
       <c r="E1440" s="8">
-        <v>0</v>
+        <v>874681642</v>
       </c>
       <c r="F1440" s="9">
         <v>1</v>
       </c>
       <c r="G1440" s="8">
-        <v>0</v>
+        <v>1408919128.77</v>
       </c>
     </row>
     <row r="1441" spans="1:7" x14ac:dyDescent="0.25">
@@ -52943,7 +52943,7 @@
         <v>46255</v>
       </c>
       <c r="D1752" s="10">
-        <v>9.564453</v>
+        <v>9.563946</v>
       </c>
       <c r="E1752" s="8">
         <v>4068640599</v>
@@ -52952,7 +52952,7 @@
         <v>12738</v>
       </c>
       <c r="G1752" s="8">
-        <v>38914322888.3</v>
+        <v>38912259676.45</v>
       </c>
     </row>
     <row r="1753" spans="1:7" x14ac:dyDescent="0.25">
@@ -54438,7 +54438,7 @@
         <v>46255</v>
       </c>
       <c r="D1817" s="10">
-        <v>1.823335</v>
+        <v>1.896488</v>
       </c>
       <c r="E1817" s="8">
         <v>359323921</v>
@@ -54447,7 +54447,7 @@
         <v>9409</v>
       </c>
       <c r="G1817" s="8">
-        <v>655167909.04</v>
+        <v>681453590.67</v>
       </c>
     </row>
     <row r="1818" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>24.08.2026 09:28:25</t>
+    <t>24.08.2026 11:51:56</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -12728,7 +12728,7 @@
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
@@ -13271,17 +13271,17 @@
       <c r="C27" s="6">
         <v>46258</v>
       </c>
-      <c r="D27" s="8">
-        <v>0</v>
+      <c r="D27" s="7">
+        <v>0.184998</v>
       </c>
       <c r="E27" s="8">
-        <v>0</v>
+        <v>7525790257</v>
       </c>
       <c r="F27" s="9">
         <v>35219</v>
       </c>
       <c r="G27" s="8">
-        <v>0</v>
+        <v>1392256322.97</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -13340,17 +13340,17 @@
       <c r="C30" s="6">
         <v>46258</v>
       </c>
-      <c r="D30" s="8">
-        <v>0</v>
+      <c r="D30" s="10">
+        <v>1.38275</v>
       </c>
       <c r="E30" s="8">
-        <v>0</v>
+        <v>14650949142</v>
       </c>
       <c r="F30" s="9">
         <v>81513</v>
       </c>
       <c r="G30" s="8">
-        <v>0</v>
+        <v>20258600843.88</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -13548,7 +13548,7 @@
         <v>46258</v>
       </c>
       <c r="D39" s="7">
-        <v>21.658203</v>
+        <v>21.806665</v>
       </c>
       <c r="E39" s="8">
         <v>6013512</v>
@@ -13557,7 +13557,7 @@
         <v>186</v>
       </c>
       <c r="G39" s="8">
-        <v>130241860.66</v>
+        <v>131134640.83</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -13571,7 +13571,7 @@
         <v>46258</v>
       </c>
       <c r="D40" s="7">
-        <v>31.291585</v>
+        <v>31.393522</v>
       </c>
       <c r="E40" s="8">
         <v>1749021</v>
@@ -13580,7 +13580,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="8">
-        <v>54729639.73</v>
+        <v>54907928.57</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -14283,8 +14283,8 @@
       <c r="C71" s="6">
         <v>46258</v>
       </c>
-      <c r="D71" s="7">
-        <v>2.669413</v>
+      <c r="D71" s="10">
+        <v>2.66887</v>
       </c>
       <c r="E71" s="8">
         <v>88777184</v>
@@ -14293,7 +14293,7 @@
         <v>465</v>
       </c>
       <c r="G71" s="8">
-        <v>236982962.16</v>
+        <v>236934795.09</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -14306,17 +14306,17 @@
       <c r="C72" s="6">
         <v>46258</v>
       </c>
-      <c r="D72" s="8">
-        <v>0</v>
+      <c r="D72" s="7">
+        <v>6.965833</v>
       </c>
       <c r="E72" s="8">
-        <v>0</v>
+        <v>12355088</v>
       </c>
       <c r="F72" s="9">
         <v>2905</v>
       </c>
       <c r="G72" s="8">
-        <v>0</v>
+        <v>86063484.78</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -14421,17 +14421,17 @@
       <c r="C77" s="6">
         <v>46258</v>
       </c>
-      <c r="D77" s="8">
-        <v>0</v>
+      <c r="D77" s="7">
+        <v>16.118069</v>
       </c>
       <c r="E77" s="8">
-        <v>0</v>
+        <v>252070680</v>
       </c>
       <c r="F77" s="9">
         <v>7417</v>
       </c>
       <c r="G77" s="8">
-        <v>0</v>
+        <v>4062892557.9</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -14444,17 +14444,17 @@
       <c r="C78" s="6">
         <v>46258</v>
       </c>
-      <c r="D78" s="8">
-        <v>0</v>
+      <c r="D78" s="7">
+        <v>18.564549</v>
       </c>
       <c r="E78" s="8">
-        <v>0</v>
+        <v>173477471</v>
       </c>
       <c r="F78" s="9">
         <v>5101</v>
       </c>
       <c r="G78" s="8">
-        <v>0</v>
+        <v>3220530960.06</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -14628,17 +14628,17 @@
       <c r="C86" s="6">
         <v>46258</v>
       </c>
-      <c r="D86" s="8">
-        <v>0</v>
+      <c r="D86" s="7">
+        <v>135.468757</v>
       </c>
       <c r="E86" s="8">
-        <v>0</v>
+        <v>2028702</v>
       </c>
       <c r="F86" s="9">
         <v>12</v>
       </c>
       <c r="G86" s="8">
-        <v>0</v>
+        <v>274825739.15</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -15388,7 +15388,7 @@
         <v>46258</v>
       </c>
       <c r="D119" s="7">
-        <v>1.813332</v>
+        <v>1.821637</v>
       </c>
       <c r="E119" s="8">
         <v>5624315</v>
@@ -15397,7 +15397,7 @@
         <v>58</v>
       </c>
       <c r="G119" s="8">
-        <v>10198748.63</v>
+        <v>10245457.83</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -15825,7 +15825,7 @@
         <v>46258</v>
       </c>
       <c r="D138" s="7">
-        <v>8.903103</v>
+        <v>8.902275</v>
       </c>
       <c r="E138" s="8">
         <v>99742511</v>
@@ -15834,7 +15834,7 @@
         <v>524</v>
       </c>
       <c r="G138" s="8">
-        <v>888017851.21</v>
+        <v>887935307.13</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -16400,7 +16400,7 @@
         <v>46258</v>
       </c>
       <c r="D163" s="7">
-        <v>1.606332</v>
+        <v>1.611012</v>
       </c>
       <c r="E163" s="8">
         <v>52405548</v>
@@ -16409,7 +16409,7 @@
         <v>1060</v>
       </c>
       <c r="G163" s="8">
-        <v>84180734.82</v>
+        <v>84425961.47</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -16514,17 +16514,17 @@
       <c r="C168" s="6">
         <v>46258</v>
       </c>
-      <c r="D168" s="8">
-        <v>0</v>
+      <c r="D168" s="7">
+        <v>55.186611</v>
       </c>
       <c r="E168" s="8">
-        <v>0</v>
+        <v>28212700</v>
       </c>
       <c r="F168" s="9">
         <v>5</v>
       </c>
       <c r="G168" s="8">
-        <v>0</v>
+        <v>1556963288.25</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -16583,17 +16583,17 @@
       <c r="C171" s="6">
         <v>46258</v>
       </c>
-      <c r="D171" s="8">
-        <v>0</v>
+      <c r="D171" s="7">
+        <v>0.135921</v>
       </c>
       <c r="E171" s="8">
-        <v>0</v>
+        <v>957331903</v>
       </c>
       <c r="F171" s="9">
         <v>41</v>
       </c>
       <c r="G171" s="8">
-        <v>0</v>
+        <v>130121921.6</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -16699,7 +16699,7 @@
         <v>46258</v>
       </c>
       <c r="D176" s="7">
-        <v>1.764841</v>
+        <v>1.764834</v>
       </c>
       <c r="E176" s="8">
         <v>1336115021</v>
@@ -16708,7 +16708,7 @@
         <v>2872</v>
       </c>
       <c r="G176" s="8">
-        <v>2358030513.04</v>
+        <v>2358020915.33</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -16905,17 +16905,17 @@
       <c r="C185" s="6">
         <v>46258</v>
       </c>
-      <c r="D185" s="8">
-        <v>0</v>
+      <c r="D185" s="7">
+        <v>1.267311</v>
       </c>
       <c r="E185" s="8">
-        <v>0</v>
+        <v>86800866</v>
       </c>
       <c r="F185" s="9">
         <v>2599</v>
       </c>
       <c r="G185" s="8">
-        <v>0</v>
+        <v>110003707.08</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -17342,17 +17342,17 @@
       <c r="C204" s="6">
         <v>46258</v>
       </c>
-      <c r="D204" s="8">
-        <v>0</v>
+      <c r="D204" s="7">
+        <v>1.306358</v>
       </c>
       <c r="E204" s="8">
-        <v>0</v>
+        <v>24297975</v>
       </c>
       <c r="F204" s="9">
         <v>240</v>
       </c>
       <c r="G204" s="8">
-        <v>0</v>
+        <v>31741842.29</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -18884,7 +18884,7 @@
         <v>46258</v>
       </c>
       <c r="D271" s="7">
-        <v>1.002819</v>
+        <v>0.999531</v>
       </c>
       <c r="E271" s="8">
         <v>10500000</v>
@@ -18893,7 +18893,7 @@
         <v>1</v>
       </c>
       <c r="G271" s="8">
-        <v>10529596.08</v>
+        <v>10495080.22</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -19114,7 +19114,7 @@
         <v>46258</v>
       </c>
       <c r="D281" s="7">
-        <v>5.311865</v>
+        <v>5.333599</v>
       </c>
       <c r="E281" s="8">
         <v>4919094</v>
@@ -19123,7 +19123,7 @@
         <v>1147</v>
       </c>
       <c r="G281" s="8">
-        <v>26129564.9</v>
+        <v>26236475.66</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -19183,7 +19183,7 @@
         <v>46258</v>
       </c>
       <c r="D284" s="7">
-        <v>1.190381</v>
+        <v>1.189935</v>
       </c>
       <c r="E284" s="8">
         <v>71647235</v>
@@ -19192,7 +19192,7 @@
         <v>771</v>
       </c>
       <c r="G284" s="8">
-        <v>85287491.49</v>
+        <v>85255530.46</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -19320,17 +19320,17 @@
       <c r="C290" s="6">
         <v>46258</v>
       </c>
-      <c r="D290" s="8">
-        <v>0</v>
+      <c r="D290" s="7">
+        <v>1.482974</v>
       </c>
       <c r="E290" s="8">
-        <v>0</v>
+        <v>2095528976</v>
       </c>
       <c r="F290" s="9">
         <v>63</v>
       </c>
       <c r="G290" s="8">
-        <v>0</v>
+        <v>3107614284.58</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -19435,17 +19435,17 @@
       <c r="C295" s="6">
         <v>46258</v>
       </c>
-      <c r="D295" s="8">
-        <v>0</v>
+      <c r="D295" s="7">
+        <v>50.677198</v>
       </c>
       <c r="E295" s="8">
-        <v>0</v>
+        <v>7336331</v>
       </c>
       <c r="F295" s="9">
         <v>100</v>
       </c>
       <c r="G295" s="8">
-        <v>0</v>
+        <v>371784697.31</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -19666,7 +19666,7 @@
         <v>46258</v>
       </c>
       <c r="D305" s="7">
-        <v>7.265157</v>
+        <v>7.277553</v>
       </c>
       <c r="E305" s="8">
         <v>444657153</v>
@@ -19675,7 +19675,7 @@
         <v>15199</v>
       </c>
       <c r="G305" s="8">
-        <v>3230504001.16</v>
+        <v>3236016050.29</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -19804,7 +19804,7 @@
         <v>46258</v>
       </c>
       <c r="D311" s="7">
-        <v>1.317265</v>
+        <v>1.321257</v>
       </c>
       <c r="E311" s="8">
         <v>356407166</v>
@@ -19813,7 +19813,7 @@
         <v>143</v>
       </c>
       <c r="G311" s="8">
-        <v>469482577.52</v>
+        <v>470905394.56</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -19896,7 +19896,7 @@
         <v>46258</v>
       </c>
       <c r="D315" s="7">
-        <v>53.035257</v>
+        <v>53.430453</v>
       </c>
       <c r="E315" s="8">
         <v>26667054</v>
@@ -19905,7 +19905,7 @@
         <v>1031</v>
       </c>
       <c r="G315" s="8">
-        <v>1414294057.85</v>
+        <v>1424832787.77</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -20195,7 +20195,7 @@
         <v>46258</v>
       </c>
       <c r="D328" s="7">
-        <v>74.567889</v>
+        <v>74.568445</v>
       </c>
       <c r="E328" s="8">
         <v>7358618</v>
@@ -20204,7 +20204,7 @@
         <v>3</v>
       </c>
       <c r="G328" s="8">
-        <v>548716608.54</v>
+        <v>548720701.69</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -20471,7 +20471,7 @@
         <v>46258</v>
       </c>
       <c r="D340" s="7">
-        <v>102.788762</v>
+        <v>102.787642</v>
       </c>
       <c r="E340" s="8">
         <v>22490084</v>
@@ -20480,7 +20480,7 @@
         <v>1</v>
       </c>
       <c r="G340" s="8">
-        <v>2311727880.62</v>
+        <v>2311702710.29</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -20724,7 +20724,7 @@
         <v>46258</v>
       </c>
       <c r="D351" s="7">
-        <v>2.236718</v>
+        <v>2.236833</v>
       </c>
       <c r="E351" s="8">
         <v>1801179260</v>
@@ -20733,7 +20733,7 @@
         <v>1297</v>
       </c>
       <c r="G351" s="8">
-        <v>4028729513.12</v>
+        <v>4028936642.04</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
@@ -20747,7 +20747,7 @@
         <v>46258</v>
       </c>
       <c r="D352" s="7">
-        <v>14.888117</v>
+        <v>14.949618</v>
       </c>
       <c r="E352" s="8">
         <v>9728078</v>
@@ -20756,7 +20756,7 @@
         <v>1075</v>
       </c>
       <c r="G352" s="8">
-        <v>144832763.75</v>
+        <v>145431052.85</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -20999,17 +20999,17 @@
       <c r="C363" s="6">
         <v>46258</v>
       </c>
-      <c r="D363" s="8">
-        <v>0</v>
+      <c r="D363" s="7">
+        <v>1.457925</v>
       </c>
       <c r="E363" s="8">
-        <v>0</v>
+        <v>350766274</v>
       </c>
       <c r="F363" s="9">
         <v>462</v>
       </c>
       <c r="G363" s="8">
-        <v>0</v>
+        <v>511390981.01</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
@@ -21483,7 +21483,7 @@
         <v>46258</v>
       </c>
       <c r="D384" s="7">
-        <v>57.425144</v>
+        <v>57.430456</v>
       </c>
       <c r="E384" s="8">
         <v>13830072</v>
@@ -21492,7 +21492,7 @@
         <v>23</v>
       </c>
       <c r="G384" s="8">
-        <v>794193872.74</v>
+        <v>794267337.37</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
@@ -21506,7 +21506,7 @@
         <v>46258</v>
       </c>
       <c r="D385" s="7">
-        <v>49.274262</v>
+        <v>49.215298</v>
       </c>
       <c r="E385" s="8">
         <v>90567785</v>
@@ -21515,7 +21515,7 @@
         <v>34</v>
       </c>
       <c r="G385" s="8">
-        <v>4462660810.25</v>
+        <v>4457320489.26</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
@@ -21621,7 +21621,7 @@
         <v>46258</v>
       </c>
       <c r="D390" s="7">
-        <v>1.144927</v>
+        <v>1.144935</v>
       </c>
       <c r="E390" s="8">
         <v>20451673</v>
@@ -21630,7 +21630,7 @@
         <v>829</v>
       </c>
       <c r="G390" s="8">
-        <v>23415672.02</v>
+        <v>23415839.63</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
@@ -21782,7 +21782,7 @@
         <v>46258</v>
       </c>
       <c r="D397" s="7">
-        <v>1.048474</v>
+        <v>1.048481</v>
       </c>
       <c r="E397" s="8">
         <v>258784162</v>
@@ -21791,7 +21791,7 @@
         <v>86</v>
       </c>
       <c r="G397" s="8">
-        <v>271328430.13</v>
+        <v>271330358.18</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
@@ -21942,17 +21942,17 @@
       <c r="C404" s="6">
         <v>46258</v>
       </c>
-      <c r="D404" s="8">
-        <v>0</v>
+      <c r="D404" s="7">
+        <v>1.828803</v>
       </c>
       <c r="E404" s="8">
-        <v>0</v>
+        <v>1787366791</v>
       </c>
       <c r="F404" s="9">
         <v>1352</v>
       </c>
       <c r="G404" s="8">
-        <v>0</v>
+        <v>3268741313.17</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.25">
@@ -22067,7 +22067,7 @@
         <v>691</v>
       </c>
       <c r="G409" s="8">
-        <v>59723896.48</v>
+        <v>59723896.61</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
@@ -22103,17 +22103,17 @@
       <c r="C411" s="6">
         <v>46258</v>
       </c>
-      <c r="D411" s="8">
-        <v>0</v>
+      <c r="D411" s="7">
+        <v>1.208145</v>
       </c>
       <c r="E411" s="8">
-        <v>0</v>
+        <v>1488289123</v>
       </c>
       <c r="F411" s="9">
         <v>12466</v>
       </c>
       <c r="G411" s="8">
-        <v>0</v>
+        <v>1798068401.42</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.25">
@@ -22127,7 +22127,7 @@
         <v>46258</v>
       </c>
       <c r="D412" s="7">
-        <v>1.205299</v>
+        <v>1.205326</v>
       </c>
       <c r="E412" s="8">
         <v>34787658</v>
@@ -22136,7 +22136,7 @@
         <v>1789</v>
       </c>
       <c r="G412" s="8">
-        <v>41929512.68</v>
+        <v>41930462.45</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.25">
@@ -22219,7 +22219,7 @@
         <v>46258</v>
       </c>
       <c r="D416" s="7">
-        <v>1.425669</v>
+        <v>1.426923</v>
       </c>
       <c r="E416" s="8">
         <v>176763134</v>
@@ -22228,7 +22228,7 @@
         <v>1574</v>
       </c>
       <c r="G416" s="8">
-        <v>252005781.64</v>
+        <v>252227365.1</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
@@ -22472,16 +22472,16 @@
         <v>46258</v>
       </c>
       <c r="D427" s="7">
-        <v>3.058743</v>
+        <v>3.082117</v>
       </c>
       <c r="E427" s="8">
-        <v>14245102</v>
+        <v>14248027</v>
       </c>
       <c r="F427" s="9">
         <v>498</v>
       </c>
       <c r="G427" s="8">
-        <v>43572104.52</v>
+        <v>43914092.42</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
@@ -22494,17 +22494,17 @@
       <c r="C428" s="6">
         <v>46258</v>
       </c>
-      <c r="D428" s="8">
-        <v>0</v>
+      <c r="D428" s="7">
+        <v>44.507993</v>
       </c>
       <c r="E428" s="8">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F428" s="9">
         <v>1</v>
       </c>
       <c r="G428" s="8">
-        <v>0</v>
+        <v>4450799.25</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.25">
@@ -22610,7 +22610,7 @@
         <v>46258</v>
       </c>
       <c r="D433" s="7">
-        <v>5.457008</v>
+        <v>5.458627</v>
       </c>
       <c r="E433" s="8">
         <v>40408496</v>
@@ -22619,7 +22619,7 @@
         <v>33</v>
       </c>
       <c r="G433" s="8">
-        <v>220509465.79</v>
+        <v>220574894.59</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
@@ -22656,7 +22656,7 @@
         <v>46258</v>
       </c>
       <c r="D435" s="7">
-        <v>4.730558</v>
+        <v>4.730553</v>
       </c>
       <c r="E435" s="8">
         <v>62474669</v>
@@ -22665,7 +22665,7 @@
         <v>395</v>
       </c>
       <c r="G435" s="8">
-        <v>295540030.75</v>
+        <v>295539742.53</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
@@ -22955,7 +22955,7 @@
         <v>46258</v>
       </c>
       <c r="D448" s="7">
-        <v>7.780255</v>
+        <v>7.844726</v>
       </c>
       <c r="E448" s="8">
         <v>253594436</v>
@@ -22964,7 +22964,7 @@
         <v>2349</v>
       </c>
       <c r="G448" s="8">
-        <v>1973029383.5</v>
+        <v>1989378807.52</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
@@ -23300,7 +23300,7 @@
         <v>46258</v>
       </c>
       <c r="D463" s="7">
-        <v>59.921231</v>
+        <v>59.921232</v>
       </c>
       <c r="E463" s="8">
         <v>827900176</v>
@@ -23309,7 +23309,7 @@
         <v>12177</v>
       </c>
       <c r="G463" s="8">
-        <v>49608797796.35</v>
+        <v>49608798234.33</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.25">
@@ -23484,7 +23484,7 @@
         <v>46258</v>
       </c>
       <c r="D471" s="7">
-        <v>0.208722</v>
+        <v>0.209346</v>
       </c>
       <c r="E471" s="8">
         <v>52452269476.04</v>
@@ -23493,7 +23493,7 @@
         <v>6516</v>
       </c>
       <c r="G471" s="8">
-        <v>10947959046.94</v>
+        <v>10980686498.75</v>
       </c>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
@@ -23506,17 +23506,17 @@
       <c r="C472" s="6">
         <v>46258</v>
       </c>
-      <c r="D472" s="8">
-        <v>0</v>
+      <c r="D472" s="7">
+        <v>2.329677</v>
       </c>
       <c r="E472" s="8">
-        <v>0</v>
+        <v>280061165</v>
       </c>
       <c r="F472" s="9">
         <v>1815</v>
       </c>
       <c r="G472" s="8">
-        <v>0</v>
+        <v>652451997.97</v>
       </c>
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.25">
@@ -23645,16 +23645,16 @@
         <v>46258</v>
       </c>
       <c r="D478" s="7">
-        <v>0.094157</v>
+        <v>0.098573</v>
       </c>
       <c r="E478" s="8">
-        <v>2860944828</v>
+        <v>2731719228</v>
       </c>
       <c r="F478" s="9">
         <v>1203</v>
       </c>
       <c r="G478" s="8">
-        <v>269376851.66</v>
+        <v>269273345.46</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.25">
@@ -23990,7 +23990,7 @@
         <v>46258</v>
       </c>
       <c r="D493" s="7">
-        <v>4.795712</v>
+        <v>4.804183</v>
       </c>
       <c r="E493" s="8">
         <v>78975959</v>
@@ -23999,7 +23999,7 @@
         <v>552</v>
       </c>
       <c r="G493" s="8">
-        <v>378745983.99</v>
+        <v>379414967.2</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
@@ -24104,17 +24104,17 @@
       <c r="C498" s="6">
         <v>46258</v>
       </c>
-      <c r="D498" s="8">
-        <v>0</v>
+      <c r="D498" s="7">
+        <v>1.382869</v>
       </c>
       <c r="E498" s="8">
-        <v>0</v>
+        <v>799896824</v>
       </c>
       <c r="F498" s="9">
         <v>4371</v>
       </c>
       <c r="G498" s="8">
-        <v>0</v>
+        <v>1106152696.35</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
@@ -24588,7 +24588,7 @@
         <v>46258</v>
       </c>
       <c r="D519" s="7">
-        <v>5.685799</v>
+        <v>5.721901</v>
       </c>
       <c r="E519" s="8">
         <v>205532177.63</v>
@@ -24597,7 +24597,7 @@
         <v>2127</v>
       </c>
       <c r="G519" s="8">
-        <v>1168614611.62</v>
+        <v>1176034840.16</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
@@ -24656,17 +24656,17 @@
       <c r="C522" s="6">
         <v>46258</v>
       </c>
-      <c r="D522" s="8">
-        <v>0</v>
+      <c r="D522" s="7">
+        <v>77.417283</v>
       </c>
       <c r="E522" s="8">
-        <v>0</v>
+        <v>5527677</v>
       </c>
       <c r="F522" s="9">
         <v>1</v>
       </c>
       <c r="G522" s="8">
-        <v>0</v>
+        <v>427937735.12</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.25">
@@ -24748,17 +24748,17 @@
       <c r="C526" s="6">
         <v>46258</v>
       </c>
-      <c r="D526" s="8">
-        <v>0</v>
+      <c r="D526" s="7">
+        <v>12.751364</v>
       </c>
       <c r="E526" s="8">
-        <v>0</v>
+        <v>29228654</v>
       </c>
       <c r="F526" s="9">
         <v>2708</v>
       </c>
       <c r="G526" s="8">
-        <v>0</v>
+        <v>372705217.17</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
@@ -24771,17 +24771,17 @@
       <c r="C527" s="6">
         <v>46258</v>
       </c>
-      <c r="D527" s="8">
-        <v>0</v>
+      <c r="D527" s="7">
+        <v>63.552635</v>
       </c>
       <c r="E527" s="8">
-        <v>0</v>
+        <v>7935068</v>
       </c>
       <c r="F527" s="9">
         <v>1</v>
       </c>
       <c r="G527" s="8">
-        <v>0</v>
+        <v>504294482.77</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.25">
@@ -24863,17 +24863,17 @@
       <c r="C531" s="6">
         <v>46258</v>
       </c>
-      <c r="D531" s="8">
-        <v>0</v>
+      <c r="D531" s="7">
+        <v>66.923025</v>
       </c>
       <c r="E531" s="8">
-        <v>0</v>
+        <v>32360328</v>
       </c>
       <c r="F531" s="9">
         <v>5</v>
       </c>
       <c r="G531" s="8">
-        <v>0</v>
+        <v>2165651025.42</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
@@ -24886,17 +24886,17 @@
       <c r="C532" s="6">
         <v>46258</v>
       </c>
-      <c r="D532" s="8">
-        <v>0</v>
+      <c r="D532" s="7">
+        <v>62.582333</v>
       </c>
       <c r="E532" s="8">
-        <v>0</v>
+        <v>3941000</v>
       </c>
       <c r="F532" s="9">
         <v>1</v>
       </c>
       <c r="G532" s="8">
-        <v>0</v>
+        <v>246636975.93</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
@@ -25047,17 +25047,17 @@
       <c r="C539" s="6">
         <v>46258</v>
       </c>
-      <c r="D539" s="8">
-        <v>0</v>
+      <c r="D539" s="7">
+        <v>71.665743</v>
       </c>
       <c r="E539" s="8">
-        <v>0</v>
+        <v>53983981</v>
       </c>
       <c r="F539" s="9">
         <v>2</v>
       </c>
       <c r="G539" s="8">
-        <v>0</v>
+        <v>3868802133.4</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
@@ -25070,17 +25070,17 @@
       <c r="C540" s="6">
         <v>46258</v>
       </c>
-      <c r="D540" s="8">
-        <v>0</v>
+      <c r="D540" s="7">
+        <v>13.216695</v>
       </c>
       <c r="E540" s="8">
-        <v>0</v>
+        <v>173955653</v>
       </c>
       <c r="F540" s="9">
         <v>22476</v>
       </c>
       <c r="G540" s="8">
-        <v>0</v>
+        <v>2299118840.31</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
@@ -25094,7 +25094,7 @@
         <v>46258</v>
       </c>
       <c r="D541" s="7">
-        <v>3.569268</v>
+        <v>3.569887</v>
       </c>
       <c r="E541" s="8">
         <v>320860727</v>
@@ -25103,7 +25103,7 @@
         <v>3244</v>
       </c>
       <c r="G541" s="8">
-        <v>1145238072</v>
+        <v>1145436559.35</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
@@ -25116,17 +25116,17 @@
       <c r="C542" s="6">
         <v>46258</v>
       </c>
-      <c r="D542" s="8">
-        <v>0</v>
+      <c r="D542" s="7">
+        <v>71.953967</v>
       </c>
       <c r="E542" s="8">
-        <v>0</v>
+        <v>11517383</v>
       </c>
       <c r="F542" s="9">
         <v>2</v>
       </c>
       <c r="G542" s="8">
-        <v>0</v>
+        <v>828721396.58</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
@@ -25139,17 +25139,17 @@
       <c r="C543" s="6">
         <v>46258</v>
       </c>
-      <c r="D543" s="8">
-        <v>0</v>
+      <c r="D543" s="7">
+        <v>6.381016</v>
       </c>
       <c r="E543" s="8">
-        <v>0</v>
+        <v>222060386</v>
       </c>
       <c r="F543" s="9">
         <v>2</v>
       </c>
       <c r="G543" s="8">
-        <v>0</v>
+        <v>1416970844.47</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -25185,17 +25185,17 @@
       <c r="C545" s="6">
         <v>46258</v>
       </c>
-      <c r="D545" s="8">
-        <v>0</v>
+      <c r="D545" s="10">
+        <v>64.60244</v>
       </c>
       <c r="E545" s="8">
-        <v>0</v>
+        <v>3425896</v>
       </c>
       <c r="F545" s="9">
         <v>3</v>
       </c>
       <c r="G545" s="8">
-        <v>0</v>
+        <v>221321240</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -25208,17 +25208,17 @@
       <c r="C546" s="6">
         <v>46258</v>
       </c>
-      <c r="D546" s="8">
-        <v>0</v>
+      <c r="D546" s="7">
+        <v>60.979296</v>
       </c>
       <c r="E546" s="8">
-        <v>0</v>
+        <v>194715</v>
       </c>
       <c r="F546" s="9">
         <v>1</v>
       </c>
       <c r="G546" s="8">
-        <v>0</v>
+        <v>11873583.58</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
@@ -25231,17 +25231,17 @@
       <c r="C547" s="6">
         <v>46258</v>
       </c>
-      <c r="D547" s="8">
-        <v>0</v>
+      <c r="D547" s="7">
+        <v>61.891825</v>
       </c>
       <c r="E547" s="8">
-        <v>0</v>
+        <v>8101428</v>
       </c>
       <c r="F547" s="9">
         <v>4</v>
       </c>
       <c r="G547" s="8">
-        <v>0</v>
+        <v>501412161.77</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
@@ -25254,17 +25254,17 @@
       <c r="C548" s="6">
         <v>46258</v>
       </c>
-      <c r="D548" s="8">
-        <v>0</v>
+      <c r="D548" s="10">
+        <v>66.82505</v>
       </c>
       <c r="E548" s="8">
-        <v>0</v>
+        <v>23236050</v>
       </c>
       <c r="F548" s="9">
         <v>1</v>
       </c>
       <c r="G548" s="8">
-        <v>0</v>
+        <v>1552750198.44</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
@@ -25277,17 +25277,17 @@
       <c r="C549" s="6">
         <v>46258</v>
       </c>
-      <c r="D549" s="8">
-        <v>0</v>
+      <c r="D549" s="10">
+        <v>76.43394</v>
       </c>
       <c r="E549" s="8">
-        <v>0</v>
+        <v>2099501</v>
       </c>
       <c r="F549" s="9">
         <v>2</v>
       </c>
       <c r="G549" s="8">
-        <v>0</v>
+        <v>160473133.86</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -25323,17 +25323,17 @@
       <c r="C551" s="6">
         <v>46258</v>
       </c>
-      <c r="D551" s="8">
-        <v>0</v>
+      <c r="D551" s="7">
+        <v>61.369524</v>
       </c>
       <c r="E551" s="8">
-        <v>0</v>
+        <v>6634456</v>
       </c>
       <c r="F551" s="9">
         <v>1</v>
       </c>
       <c r="G551" s="8">
-        <v>0</v>
+        <v>407153403.44</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -25346,17 +25346,17 @@
       <c r="C552" s="6">
         <v>46258</v>
       </c>
-      <c r="D552" s="8">
-        <v>0</v>
+      <c r="D552" s="7">
+        <v>70.444295</v>
       </c>
       <c r="E552" s="8">
-        <v>0</v>
+        <v>5961167</v>
       </c>
       <c r="F552" s="9">
         <v>4</v>
       </c>
       <c r="G552" s="8">
-        <v>0</v>
+        <v>419930207.9</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
@@ -25369,17 +25369,17 @@
       <c r="C553" s="6">
         <v>46258</v>
       </c>
-      <c r="D553" s="8">
-        <v>0</v>
+      <c r="D553" s="10">
+        <v>70.50975</v>
       </c>
       <c r="E553" s="8">
-        <v>0</v>
+        <v>1555160</v>
       </c>
       <c r="F553" s="9">
         <v>2</v>
       </c>
       <c r="G553" s="8">
-        <v>0</v>
+        <v>109653942.3</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
@@ -25392,17 +25392,17 @@
       <c r="C554" s="6">
         <v>46258</v>
       </c>
-      <c r="D554" s="8">
-        <v>0</v>
+      <c r="D554" s="10">
+        <v>53.92835</v>
       </c>
       <c r="E554" s="8">
-        <v>0</v>
+        <v>30698413</v>
       </c>
       <c r="F554" s="9">
         <v>3</v>
       </c>
       <c r="G554" s="8">
-        <v>0</v>
+        <v>1655514745.68</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
@@ -25415,17 +25415,17 @@
       <c r="C555" s="6">
         <v>46258</v>
       </c>
-      <c r="D555" s="8">
-        <v>0</v>
+      <c r="D555" s="7">
+        <v>11.381405</v>
       </c>
       <c r="E555" s="8">
-        <v>0</v>
+        <v>29486927</v>
       </c>
       <c r="F555" s="9">
         <v>1</v>
       </c>
       <c r="G555" s="8">
-        <v>0</v>
+        <v>335602659.36</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -25438,17 +25438,17 @@
       <c r="C556" s="6">
         <v>46258</v>
       </c>
-      <c r="D556" s="8">
-        <v>0</v>
+      <c r="D556" s="7">
+        <v>80.344537</v>
       </c>
       <c r="E556" s="8">
-        <v>0</v>
+        <v>11573436</v>
       </c>
       <c r="F556" s="9">
         <v>3</v>
       </c>
       <c r="G556" s="8">
-        <v>0</v>
+        <v>929862353.88</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
@@ -25461,17 +25461,17 @@
       <c r="C557" s="6">
         <v>46258</v>
       </c>
-      <c r="D557" s="8">
-        <v>0</v>
+      <c r="D557" s="7">
+        <v>70.462671</v>
       </c>
       <c r="E557" s="8">
-        <v>0</v>
+        <v>5822807</v>
       </c>
       <c r="F557" s="9">
         <v>3</v>
       </c>
       <c r="G557" s="8">
-        <v>0</v>
+        <v>410290531.34</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
@@ -25484,17 +25484,17 @@
       <c r="C558" s="6">
         <v>46258</v>
       </c>
-      <c r="D558" s="8">
-        <v>0</v>
+      <c r="D558" s="7">
+        <v>67.305152</v>
       </c>
       <c r="E558" s="8">
-        <v>0</v>
+        <v>123364230</v>
       </c>
       <c r="F558" s="9">
         <v>3</v>
       </c>
       <c r="G558" s="8">
-        <v>0</v>
+        <v>8303048292.74</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
@@ -25530,17 +25530,17 @@
       <c r="C560" s="6">
         <v>46258</v>
       </c>
-      <c r="D560" s="8">
-        <v>0</v>
+      <c r="D560" s="7">
+        <v>65.981348</v>
       </c>
       <c r="E560" s="8">
-        <v>0</v>
+        <v>90240169</v>
       </c>
       <c r="F560" s="9">
         <v>2</v>
       </c>
       <c r="G560" s="8">
-        <v>0</v>
+        <v>5954167986.64</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
@@ -25576,17 +25576,17 @@
       <c r="C562" s="6">
         <v>46258</v>
       </c>
-      <c r="D562" s="8">
-        <v>0</v>
+      <c r="D562" s="7">
+        <v>8.506368</v>
       </c>
       <c r="E562" s="8">
-        <v>0</v>
+        <v>342290935</v>
       </c>
       <c r="F562" s="9">
         <v>1</v>
       </c>
       <c r="G562" s="8">
-        <v>0</v>
+        <v>2911652744.45</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
@@ -25599,17 +25599,17 @@
       <c r="C563" s="6">
         <v>46258</v>
       </c>
-      <c r="D563" s="8">
-        <v>0</v>
+      <c r="D563" s="7">
+        <v>69.496524</v>
       </c>
       <c r="E563" s="8">
-        <v>0</v>
+        <v>6963426</v>
       </c>
       <c r="F563" s="9">
         <v>4</v>
       </c>
       <c r="G563" s="8">
-        <v>0</v>
+        <v>483933900.09</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.25">
@@ -25622,17 +25622,17 @@
       <c r="C564" s="6">
         <v>46258</v>
       </c>
-      <c r="D564" s="8">
-        <v>0</v>
+      <c r="D564" s="7">
+        <v>10.704145</v>
       </c>
       <c r="E564" s="8">
-        <v>0</v>
+        <v>6927</v>
       </c>
       <c r="F564" s="9">
         <v>1</v>
       </c>
       <c r="G564" s="8">
-        <v>0</v>
+        <v>74147.61</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
@@ -25645,17 +25645,17 @@
       <c r="C565" s="6">
         <v>46258</v>
       </c>
-      <c r="D565" s="8">
-        <v>0</v>
+      <c r="D565" s="7">
+        <v>68.311075</v>
       </c>
       <c r="E565" s="8">
-        <v>0</v>
+        <v>23597904</v>
       </c>
       <c r="F565" s="9">
         <v>3</v>
       </c>
       <c r="G565" s="8">
-        <v>0</v>
+        <v>1611998193.02</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
@@ -25691,17 +25691,17 @@
       <c r="C567" s="6">
         <v>46258</v>
       </c>
-      <c r="D567" s="8">
-        <v>0</v>
+      <c r="D567" s="7">
+        <v>1.720808</v>
       </c>
       <c r="E567" s="8">
-        <v>0</v>
+        <v>25236288</v>
       </c>
       <c r="F567" s="9">
         <v>1943</v>
       </c>
       <c r="G567" s="8">
-        <v>0</v>
+        <v>43426803.68</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
@@ -25760,17 +25760,17 @@
       <c r="C570" s="6">
         <v>46258</v>
       </c>
-      <c r="D570" s="8">
-        <v>0</v>
+      <c r="D570" s="7">
+        <v>66.744307</v>
       </c>
       <c r="E570" s="8">
-        <v>0</v>
+        <v>14263356</v>
       </c>
       <c r="F570" s="9">
         <v>3</v>
       </c>
       <c r="G570" s="8">
-        <v>0</v>
+        <v>951997816.05</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -25784,7 +25784,7 @@
         <v>46258</v>
       </c>
       <c r="D571" s="7">
-        <v>10.604299</v>
+        <v>10.681999</v>
       </c>
       <c r="E571" s="8">
         <v>7290615</v>
@@ -25793,7 +25793,7 @@
         <v>977</v>
       </c>
       <c r="G571" s="8">
-        <v>77311860.06</v>
+        <v>77878340.32</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
@@ -25806,17 +25806,17 @@
       <c r="C572" s="6">
         <v>46258</v>
       </c>
-      <c r="D572" s="8">
-        <v>0</v>
+      <c r="D572" s="7">
+        <v>64.338367</v>
       </c>
       <c r="E572" s="8">
-        <v>0</v>
+        <v>6334853</v>
       </c>
       <c r="F572" s="9">
         <v>3</v>
       </c>
       <c r="G572" s="8">
-        <v>0</v>
+        <v>407574095.35</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
@@ -25829,17 +25829,17 @@
       <c r="C573" s="6">
         <v>46258</v>
       </c>
-      <c r="D573" s="8">
-        <v>0</v>
+      <c r="D573" s="7">
+        <v>63.980219</v>
       </c>
       <c r="E573" s="8">
-        <v>0</v>
+        <v>2316713</v>
       </c>
       <c r="F573" s="9">
         <v>2</v>
       </c>
       <c r="G573" s="8">
-        <v>0</v>
+        <v>148223805.79</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
@@ -25852,17 +25852,17 @@
       <c r="C574" s="6">
         <v>46258</v>
       </c>
-      <c r="D574" s="8">
-        <v>0</v>
+      <c r="D574" s="7">
+        <v>64.355524</v>
       </c>
       <c r="E574" s="8">
-        <v>0</v>
+        <v>3663843</v>
       </c>
       <c r="F574" s="9">
         <v>2</v>
       </c>
       <c r="G574" s="8">
-        <v>0</v>
+        <v>235788535.75</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
@@ -25921,17 +25921,17 @@
       <c r="C577" s="6">
         <v>46258</v>
       </c>
-      <c r="D577" s="8">
-        <v>0</v>
+      <c r="D577" s="7">
+        <v>59.946168</v>
       </c>
       <c r="E577" s="8">
-        <v>0</v>
+        <v>9779449</v>
       </c>
       <c r="F577" s="9">
         <v>1</v>
       </c>
       <c r="G577" s="8">
-        <v>0</v>
+        <v>586240488.93</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
@@ -26036,17 +26036,17 @@
       <c r="C582" s="6">
         <v>46258</v>
       </c>
-      <c r="D582" s="8">
-        <v>0</v>
+      <c r="D582" s="7">
+        <v>66.153064</v>
       </c>
       <c r="E582" s="8">
-        <v>0</v>
+        <v>30617607</v>
       </c>
       <c r="F582" s="9">
         <v>2</v>
       </c>
       <c r="G582" s="8">
-        <v>0</v>
+        <v>2025448510.08</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
@@ -26175,7 +26175,7 @@
         <v>46258</v>
       </c>
       <c r="D588" s="7">
-        <v>4.370446</v>
+        <v>4.410972</v>
       </c>
       <c r="E588" s="8">
         <v>3870523</v>
@@ -26184,7 +26184,7 @@
         <v>70</v>
       </c>
       <c r="G588" s="8">
-        <v>16915911.73</v>
+        <v>17072768.85</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -26220,17 +26220,17 @@
       <c r="C590" s="6">
         <v>46258</v>
       </c>
-      <c r="D590" s="8">
-        <v>0</v>
+      <c r="D590" s="7">
+        <v>1.040877</v>
       </c>
       <c r="E590" s="8">
-        <v>0</v>
+        <v>48331465</v>
       </c>
       <c r="F590" s="9">
         <v>16</v>
       </c>
       <c r="G590" s="8">
-        <v>0</v>
+        <v>50307093.12</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.25">
@@ -26266,17 +26266,17 @@
       <c r="C592" s="6">
         <v>46258</v>
       </c>
-      <c r="D592" s="8">
-        <v>0</v>
+      <c r="D592" s="7">
+        <v>68.696652</v>
       </c>
       <c r="E592" s="8">
-        <v>0</v>
+        <v>8202021</v>
       </c>
       <c r="F592" s="9">
         <v>4</v>
       </c>
       <c r="G592" s="8">
-        <v>0</v>
+        <v>563451382.21</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
@@ -26358,17 +26358,17 @@
       <c r="C596" s="6">
         <v>46258</v>
       </c>
-      <c r="D596" s="8">
-        <v>0</v>
+      <c r="D596" s="7">
+        <v>8.369461</v>
       </c>
       <c r="E596" s="8">
-        <v>0</v>
+        <v>538044561</v>
       </c>
       <c r="F596" s="9">
         <v>21221</v>
       </c>
       <c r="G596" s="8">
-        <v>0</v>
+        <v>4503142973.29</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
@@ -26382,7 +26382,7 @@
         <v>46258</v>
       </c>
       <c r="D597" s="7">
-        <v>2.761127</v>
+        <v>2.761238</v>
       </c>
       <c r="E597" s="8">
         <v>1181601</v>
@@ -26391,7 +26391,7 @@
         <v>106</v>
       </c>
       <c r="G597" s="8">
-        <v>3262550.94</v>
+        <v>3262681.1</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
@@ -26519,17 +26519,17 @@
       <c r="C603" s="6">
         <v>46258</v>
       </c>
-      <c r="D603" s="8">
-        <v>0</v>
+      <c r="D603" s="7">
+        <v>63.207155</v>
       </c>
       <c r="E603" s="8">
-        <v>0</v>
+        <v>25599906</v>
       </c>
       <c r="F603" s="9">
         <v>1</v>
       </c>
       <c r="G603" s="8">
-        <v>0</v>
+        <v>1618097225.38</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.25">
@@ -26657,17 +26657,17 @@
       <c r="C609" s="6">
         <v>46258</v>
       </c>
-      <c r="D609" s="8">
-        <v>0</v>
+      <c r="D609" s="7">
+        <v>61.296718</v>
       </c>
       <c r="E609" s="8">
-        <v>0</v>
+        <v>28454944</v>
       </c>
       <c r="F609" s="9">
         <v>3</v>
       </c>
       <c r="G609" s="8">
-        <v>0</v>
+        <v>1744194691.47</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
@@ -26726,17 +26726,17 @@
       <c r="C612" s="6">
         <v>46258</v>
       </c>
-      <c r="D612" s="8">
-        <v>0</v>
+      <c r="D612" s="7">
+        <v>1.595703</v>
       </c>
       <c r="E612" s="8">
-        <v>0</v>
+        <v>1232313</v>
       </c>
       <c r="F612" s="9">
         <v>472</v>
       </c>
       <c r="G612" s="8">
-        <v>0</v>
+        <v>1966405.43</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
@@ -26749,8 +26749,8 @@
       <c r="C613" s="6">
         <v>46258</v>
       </c>
-      <c r="D613" s="10">
-        <v>4.82712</v>
+      <c r="D613" s="7">
+        <v>4.833166</v>
       </c>
       <c r="E613" s="8">
         <v>16695924</v>
@@ -26759,7 +26759,7 @@
         <v>745</v>
       </c>
       <c r="G613" s="8">
-        <v>80593233.14</v>
+        <v>80694166.68</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
@@ -26773,7 +26773,7 @@
         <v>46258</v>
       </c>
       <c r="D614" s="7">
-        <v>4.944303</v>
+        <v>4.956505</v>
       </c>
       <c r="E614" s="8">
         <v>5228565</v>
@@ -26782,7 +26782,7 @@
         <v>444</v>
       </c>
       <c r="G614" s="8">
-        <v>25851607.93</v>
+        <v>25915410.45</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
@@ -26796,7 +26796,7 @@
         <v>46258</v>
       </c>
       <c r="D615" s="7">
-        <v>4.982066</v>
+        <v>4.981164</v>
       </c>
       <c r="E615" s="8">
         <v>7535533</v>
@@ -26805,7 +26805,7 @@
         <v>460</v>
       </c>
       <c r="G615" s="8">
-        <v>37542524.73</v>
+        <v>37535727.19</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
@@ -26819,7 +26819,7 @@
         <v>46258</v>
       </c>
       <c r="D616" s="7">
-        <v>5.400879</v>
+        <v>5.401763</v>
       </c>
       <c r="E616" s="8">
         <v>9301257</v>
@@ -26828,7 +26828,7 @@
         <v>741</v>
       </c>
       <c r="G616" s="8">
-        <v>50234959.72</v>
+        <v>50243182.73</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
@@ -26887,17 +26887,17 @@
       <c r="C619" s="6">
         <v>46258</v>
       </c>
-      <c r="D619" s="8">
-        <v>0</v>
+      <c r="D619" s="10">
+        <v>52.80823</v>
       </c>
       <c r="E619" s="8">
-        <v>0</v>
+        <v>7364081</v>
       </c>
       <c r="F619" s="9">
         <v>317</v>
       </c>
       <c r="G619" s="8">
-        <v>0</v>
+        <v>388884085.03</v>
       </c>
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.25">
@@ -26956,17 +26956,17 @@
       <c r="C622" s="6">
         <v>46258</v>
       </c>
-      <c r="D622" s="8">
-        <v>0</v>
+      <c r="D622" s="7">
+        <v>1.221417</v>
       </c>
       <c r="E622" s="8">
-        <v>0</v>
+        <v>1688355520</v>
       </c>
       <c r="F622" s="9">
         <v>1764</v>
       </c>
       <c r="G622" s="8">
-        <v>0</v>
+        <v>2062186834.67</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
@@ -27002,17 +27002,17 @@
       <c r="C624" s="6">
         <v>46258</v>
       </c>
-      <c r="D624" s="8">
-        <v>0</v>
+      <c r="D624" s="10">
+        <v>65.17724</v>
       </c>
       <c r="E624" s="8">
-        <v>0</v>
+        <v>11074719</v>
       </c>
       <c r="F624" s="9">
         <v>466</v>
       </c>
       <c r="G624" s="8">
-        <v>0</v>
+        <v>721819618.6</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
@@ -27048,17 +27048,17 @@
       <c r="C626" s="6">
         <v>46258</v>
       </c>
-      <c r="D626" s="8">
-        <v>0</v>
+      <c r="D626" s="10">
+        <v>12.21996</v>
       </c>
       <c r="E626" s="8">
-        <v>0</v>
+        <v>102551400</v>
       </c>
       <c r="F626" s="9">
         <v>9506</v>
       </c>
       <c r="G626" s="8">
-        <v>0</v>
+        <v>1253174020.9</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
@@ -27071,17 +27071,17 @@
       <c r="C627" s="6">
         <v>46258</v>
       </c>
-      <c r="D627" s="8">
-        <v>0</v>
+      <c r="D627" s="10">
+        <v>72.30769</v>
       </c>
       <c r="E627" s="8">
-        <v>0</v>
+        <v>94525960</v>
       </c>
       <c r="F627" s="9">
         <v>3590</v>
       </c>
       <c r="G627" s="8">
-        <v>0</v>
+        <v>6834953827.64</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
@@ -27140,17 +27140,17 @@
       <c r="C630" s="6">
         <v>46258</v>
       </c>
-      <c r="D630" s="8">
-        <v>0</v>
+      <c r="D630" s="7">
+        <v>45.256832</v>
       </c>
       <c r="E630" s="8">
-        <v>0</v>
+        <v>58637</v>
       </c>
       <c r="F630" s="9">
         <v>1</v>
       </c>
       <c r="G630" s="8">
-        <v>0</v>
+        <v>2653724.83</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -27163,17 +27163,17 @@
       <c r="C631" s="6">
         <v>46258</v>
       </c>
-      <c r="D631" s="8">
-        <v>0</v>
+      <c r="D631" s="7">
+        <v>18.656688</v>
       </c>
       <c r="E631" s="8">
-        <v>0</v>
+        <v>39658011</v>
       </c>
       <c r="F631" s="9">
         <v>2812</v>
       </c>
       <c r="G631" s="8">
-        <v>0</v>
+        <v>739887118.59</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
@@ -27186,17 +27186,17 @@
       <c r="C632" s="6">
         <v>46258</v>
       </c>
-      <c r="D632" s="8">
-        <v>0</v>
+      <c r="D632" s="7">
+        <v>58.152821</v>
       </c>
       <c r="E632" s="8">
-        <v>0</v>
+        <v>14772170</v>
       </c>
       <c r="F632" s="9">
         <v>2</v>
       </c>
       <c r="G632" s="8">
-        <v>0</v>
+        <v>859043363.64</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
@@ -27232,17 +27232,17 @@
       <c r="C634" s="6">
         <v>46258</v>
       </c>
-      <c r="D634" s="8">
-        <v>0</v>
+      <c r="D634" s="7">
+        <v>62.382017</v>
       </c>
       <c r="E634" s="8">
-        <v>0</v>
+        <v>20837078</v>
       </c>
       <c r="F634" s="9">
         <v>2</v>
       </c>
       <c r="G634" s="8">
-        <v>0</v>
+        <v>1299858946.28</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
@@ -27301,17 +27301,17 @@
       <c r="C637" s="6">
         <v>46258</v>
       </c>
-      <c r="D637" s="8">
-        <v>0</v>
+      <c r="D637" s="7">
+        <v>21.364025</v>
       </c>
       <c r="E637" s="8">
-        <v>0</v>
+        <v>16728304</v>
       </c>
       <c r="F637" s="9">
         <v>2453</v>
       </c>
       <c r="G637" s="8">
-        <v>0</v>
+        <v>357383911.67</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.25">
@@ -27371,7 +27371,7 @@
         <v>46258</v>
       </c>
       <c r="D640" s="7">
-        <v>1.840143</v>
+        <v>1.856106</v>
       </c>
       <c r="E640" s="8">
         <v>276438087</v>
@@ -27380,7 +27380,7 @@
         <v>282</v>
       </c>
       <c r="G640" s="8">
-        <v>508685504.42</v>
+        <v>513098422.42</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.25">
@@ -27508,17 +27508,17 @@
       <c r="C646" s="6">
         <v>46258</v>
       </c>
-      <c r="D646" s="8">
-        <v>0</v>
+      <c r="D646" s="7">
+        <v>15.357324</v>
       </c>
       <c r="E646" s="8">
-        <v>0</v>
+        <v>321073008</v>
       </c>
       <c r="F646" s="9">
         <v>7</v>
       </c>
       <c r="G646" s="8">
-        <v>0</v>
+        <v>4930822357.93</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
@@ -27554,17 +27554,17 @@
       <c r="C648" s="6">
         <v>46258</v>
       </c>
-      <c r="D648" s="8">
-        <v>0</v>
+      <c r="D648" s="7">
+        <v>57.451083</v>
       </c>
       <c r="E648" s="8">
-        <v>0</v>
+        <v>4643160</v>
       </c>
       <c r="F648" s="9">
         <v>2</v>
       </c>
       <c r="G648" s="8">
-        <v>0</v>
+        <v>266754568.67</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
@@ -27669,17 +27669,17 @@
       <c r="C653" s="6">
         <v>46258</v>
       </c>
-      <c r="D653" s="8">
-        <v>0</v>
+      <c r="D653" s="7">
+        <v>7.028438</v>
       </c>
       <c r="E653" s="8">
-        <v>0</v>
+        <v>4029467144</v>
       </c>
       <c r="F653" s="9">
         <v>1</v>
       </c>
       <c r="G653" s="8">
-        <v>0</v>
+        <v>28320861523.71</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
@@ -27738,17 +27738,17 @@
       <c r="C656" s="6">
         <v>46258</v>
       </c>
-      <c r="D656" s="8">
-        <v>0</v>
+      <c r="D656" s="7">
+        <v>52.384578</v>
       </c>
       <c r="E656" s="8">
-        <v>0</v>
+        <v>28012535</v>
       </c>
       <c r="F656" s="9">
         <v>2</v>
       </c>
       <c r="G656" s="8">
-        <v>0</v>
+        <v>1467424836.07</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
@@ -27761,17 +27761,17 @@
       <c r="C657" s="6">
         <v>46258</v>
       </c>
-      <c r="D657" s="8">
-        <v>0</v>
+      <c r="D657" s="7">
+        <v>6.448373</v>
       </c>
       <c r="E657" s="8">
-        <v>0</v>
+        <v>64486454</v>
       </c>
       <c r="F657" s="9">
         <v>529</v>
       </c>
       <c r="G657" s="8">
-        <v>0</v>
+        <v>415832725.05</v>
       </c>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.25">
@@ -27784,17 +27784,17 @@
       <c r="C658" s="6">
         <v>46258</v>
       </c>
-      <c r="D658" s="8">
-        <v>0</v>
+      <c r="D658" s="7">
+        <v>12.538508</v>
       </c>
       <c r="E658" s="8">
-        <v>0</v>
+        <v>1076291687</v>
       </c>
       <c r="F658" s="9">
         <v>62390</v>
       </c>
       <c r="G658" s="8">
-        <v>0</v>
+        <v>13495092071.55</v>
       </c>
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.25">
@@ -27807,17 +27807,17 @@
       <c r="C659" s="6">
         <v>46258</v>
       </c>
-      <c r="D659" s="8">
-        <v>0</v>
+      <c r="D659" s="7">
+        <v>6.001756</v>
       </c>
       <c r="E659" s="8">
-        <v>0</v>
+        <v>341860798</v>
       </c>
       <c r="F659" s="9">
         <v>1</v>
       </c>
       <c r="G659" s="8">
-        <v>0</v>
+        <v>2051765153.55</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
@@ -27876,8 +27876,8 @@
       <c r="C662" s="6">
         <v>46258</v>
       </c>
-      <c r="D662" s="7">
-        <v>0.959256</v>
+      <c r="D662" s="10">
+        <v>0.96244</v>
       </c>
       <c r="E662" s="8">
         <v>631484047</v>
@@ -27886,7 +27886,7 @@
         <v>3155</v>
       </c>
       <c r="G662" s="8">
-        <v>605754564.15</v>
+        <v>607765518</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.25">
@@ -27899,17 +27899,17 @@
       <c r="C663" s="6">
         <v>46258</v>
       </c>
-      <c r="D663" s="8">
-        <v>0</v>
+      <c r="D663" s="10">
+        <v>0.45222</v>
       </c>
       <c r="E663" s="8">
-        <v>0</v>
+        <v>10306682812</v>
       </c>
       <c r="F663" s="9">
         <v>38732</v>
       </c>
       <c r="G663" s="8">
-        <v>0</v>
+        <v>4660883294.03</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -27922,17 +27922,17 @@
       <c r="C664" s="6">
         <v>46258</v>
       </c>
-      <c r="D664" s="8">
-        <v>0</v>
+      <c r="D664" s="7">
+        <v>1.507788</v>
       </c>
       <c r="E664" s="8">
-        <v>0</v>
+        <v>802079652</v>
       </c>
       <c r="F664" s="9">
         <v>2706</v>
       </c>
       <c r="G664" s="8">
-        <v>0</v>
+        <v>1209365762.53</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
@@ -27945,17 +27945,17 @@
       <c r="C665" s="6">
         <v>46258</v>
       </c>
-      <c r="D665" s="8">
-        <v>0</v>
+      <c r="D665" s="7">
+        <v>13.403286</v>
       </c>
       <c r="E665" s="8">
-        <v>0</v>
+        <v>527296526</v>
       </c>
       <c r="F665" s="9">
         <v>52873</v>
       </c>
       <c r="G665" s="8">
-        <v>0</v>
+        <v>7067506236.23</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
@@ -27991,17 +27991,17 @@
       <c r="C667" s="6">
         <v>46258</v>
       </c>
-      <c r="D667" s="8">
-        <v>0</v>
+      <c r="D667" s="7">
+        <v>4.176233</v>
       </c>
       <c r="E667" s="8">
-        <v>0</v>
+        <v>23572610</v>
       </c>
       <c r="F667" s="9">
         <v>3459</v>
       </c>
       <c r="G667" s="8">
-        <v>0</v>
+        <v>98444710.24</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -28014,17 +28014,17 @@
       <c r="C668" s="6">
         <v>46258</v>
       </c>
-      <c r="D668" s="8">
-        <v>0</v>
+      <c r="D668" s="7">
+        <v>68.100187</v>
       </c>
       <c r="E668" s="8">
-        <v>0</v>
+        <v>52499640</v>
       </c>
       <c r="F668" s="9">
         <v>3</v>
       </c>
       <c r="G668" s="8">
-        <v>0</v>
+        <v>3575235324.06</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -28037,17 +28037,17 @@
       <c r="C669" s="6">
         <v>46258</v>
       </c>
-      <c r="D669" s="8">
-        <v>0</v>
+      <c r="D669" s="7">
+        <v>64.515629</v>
       </c>
       <c r="E669" s="8">
-        <v>0</v>
+        <v>4739268</v>
       </c>
       <c r="F669" s="9">
         <v>1</v>
       </c>
       <c r="G669" s="8">
-        <v>0</v>
+        <v>305756853.83</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
@@ -28060,17 +28060,17 @@
       <c r="C670" s="6">
         <v>46258</v>
       </c>
-      <c r="D670" s="8">
-        <v>0</v>
+      <c r="D670" s="10">
+        <v>18.39272</v>
       </c>
       <c r="E670" s="8">
-        <v>0</v>
+        <v>22115</v>
       </c>
       <c r="F670" s="9">
         <v>1</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>406755.01</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -28083,17 +28083,17 @@
       <c r="C671" s="6">
         <v>46258</v>
       </c>
-      <c r="D671" s="8">
-        <v>0</v>
+      <c r="D671" s="7">
+        <v>5.684398</v>
       </c>
       <c r="E671" s="8">
-        <v>0</v>
+        <v>210158773</v>
       </c>
       <c r="F671" s="9">
         <v>4590</v>
       </c>
       <c r="G671" s="8">
-        <v>0</v>
+        <v>1194626146.16</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
@@ -28106,17 +28106,17 @@
       <c r="C672" s="6">
         <v>46258</v>
       </c>
-      <c r="D672" s="8">
-        <v>0</v>
+      <c r="D672" s="7">
+        <v>66.703693</v>
       </c>
       <c r="E672" s="8">
-        <v>0</v>
+        <v>7872114</v>
       </c>
       <c r="F672" s="9">
         <v>3</v>
       </c>
       <c r="G672" s="8">
-        <v>0</v>
+        <v>525099078.62</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
@@ -28129,17 +28129,17 @@
       <c r="C673" s="6">
         <v>46258</v>
       </c>
-      <c r="D673" s="8">
-        <v>0</v>
+      <c r="D673" s="7">
+        <v>74.074485</v>
       </c>
       <c r="E673" s="8">
-        <v>0</v>
+        <v>5533354</v>
       </c>
       <c r="F673" s="9">
         <v>2</v>
       </c>
       <c r="G673" s="8">
-        <v>0</v>
+        <v>409880346.51</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
@@ -28152,17 +28152,17 @@
       <c r="C674" s="6">
         <v>46258</v>
       </c>
-      <c r="D674" s="8">
-        <v>0</v>
+      <c r="D674" s="7">
+        <v>4.095107</v>
       </c>
       <c r="E674" s="8">
-        <v>0</v>
+        <v>5020082762</v>
       </c>
       <c r="F674" s="9">
         <v>1</v>
       </c>
       <c r="G674" s="8">
-        <v>0</v>
+        <v>20557774164.37</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -28175,17 +28175,17 @@
       <c r="C675" s="6">
         <v>46258</v>
       </c>
-      <c r="D675" s="8">
-        <v>0</v>
+      <c r="D675" s="7">
+        <v>72.267476</v>
       </c>
       <c r="E675" s="8">
-        <v>0</v>
+        <v>7036272</v>
       </c>
       <c r="F675" s="9">
         <v>4</v>
       </c>
       <c r="G675" s="8">
-        <v>0</v>
+        <v>508493618.08</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
@@ -28244,17 +28244,17 @@
       <c r="C678" s="6">
         <v>46258</v>
       </c>
-      <c r="D678" s="8">
-        <v>0</v>
+      <c r="D678" s="7">
+        <v>68.635536</v>
       </c>
       <c r="E678" s="8">
-        <v>0</v>
+        <v>20613565</v>
       </c>
       <c r="F678" s="9">
         <v>1</v>
       </c>
       <c r="G678" s="8">
-        <v>0</v>
+        <v>1414823087.7</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
@@ -28267,17 +28267,17 @@
       <c r="C679" s="6">
         <v>46258</v>
       </c>
-      <c r="D679" s="8">
-        <v>0</v>
+      <c r="D679" s="7">
+        <v>63.449951</v>
       </c>
       <c r="E679" s="8">
-        <v>0</v>
+        <v>9307247</v>
       </c>
       <c r="F679" s="9">
         <v>5</v>
       </c>
       <c r="G679" s="8">
-        <v>0</v>
+        <v>590544368.22</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
@@ -28290,17 +28290,17 @@
       <c r="C680" s="6">
         <v>46258</v>
       </c>
-      <c r="D680" s="8">
-        <v>0</v>
+      <c r="D680" s="10">
+        <v>7.51567</v>
       </c>
       <c r="E680" s="8">
-        <v>0</v>
+        <v>190000000</v>
       </c>
       <c r="F680" s="9">
         <v>1</v>
       </c>
       <c r="G680" s="8">
-        <v>0</v>
+        <v>1427977361.25</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -28313,17 +28313,17 @@
       <c r="C681" s="6">
         <v>46258</v>
       </c>
-      <c r="D681" s="8">
-        <v>0</v>
+      <c r="D681" s="10">
+        <v>62.05337</v>
       </c>
       <c r="E681" s="8">
-        <v>0</v>
+        <v>876698</v>
       </c>
       <c r="F681" s="9">
         <v>3</v>
       </c>
       <c r="G681" s="8">
-        <v>0</v>
+        <v>54402065.3</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
@@ -28336,17 +28336,17 @@
       <c r="C682" s="6">
         <v>46258</v>
       </c>
-      <c r="D682" s="8">
-        <v>0</v>
+      <c r="D682" s="7">
+        <v>7.836644</v>
       </c>
       <c r="E682" s="8">
-        <v>0</v>
+        <v>186210280</v>
       </c>
       <c r="F682" s="9">
         <v>4146</v>
       </c>
       <c r="G682" s="8">
-        <v>0</v>
+        <v>1459263743.06</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
@@ -28359,17 +28359,17 @@
       <c r="C683" s="6">
         <v>46258</v>
       </c>
-      <c r="D683" s="8">
-        <v>0</v>
+      <c r="D683" s="10">
+        <v>7.65047</v>
       </c>
       <c r="E683" s="8">
-        <v>0</v>
+        <v>61136777</v>
       </c>
       <c r="F683" s="9">
         <v>4285</v>
       </c>
       <c r="G683" s="8">
-        <v>0</v>
+        <v>467725073.95</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
@@ -28382,17 +28382,17 @@
       <c r="C684" s="6">
         <v>46258</v>
       </c>
-      <c r="D684" s="8">
-        <v>0</v>
+      <c r="D684" s="10">
+        <v>4.90984</v>
       </c>
       <c r="E684" s="8">
-        <v>0</v>
+        <v>78244056</v>
       </c>
       <c r="F684" s="9">
         <v>5739</v>
       </c>
       <c r="G684" s="8">
-        <v>0</v>
+        <v>384165760.95</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
@@ -28405,17 +28405,17 @@
       <c r="C685" s="6">
         <v>46258</v>
       </c>
-      <c r="D685" s="8">
-        <v>0</v>
+      <c r="D685" s="7">
+        <v>8.775309</v>
       </c>
       <c r="E685" s="8">
-        <v>0</v>
+        <v>199620758</v>
       </c>
       <c r="F685" s="9">
         <v>5208</v>
       </c>
       <c r="G685" s="8">
-        <v>0</v>
+        <v>1751733813.32</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
@@ -28428,17 +28428,17 @@
       <c r="C686" s="6">
         <v>46258</v>
       </c>
-      <c r="D686" s="8">
-        <v>0</v>
+      <c r="D686" s="7">
+        <v>5.711444</v>
       </c>
       <c r="E686" s="8">
-        <v>0</v>
+        <v>64531549</v>
       </c>
       <c r="F686" s="9">
         <v>6036</v>
       </c>
       <c r="G686" s="8">
-        <v>0</v>
+        <v>368568311.46</v>
       </c>
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.25">
@@ -28497,17 +28497,17 @@
       <c r="C689" s="6">
         <v>46258</v>
       </c>
-      <c r="D689" s="8">
-        <v>0</v>
+      <c r="D689" s="7">
+        <v>70.587756</v>
       </c>
       <c r="E689" s="8">
-        <v>0</v>
+        <v>1210798</v>
       </c>
       <c r="F689" s="9">
         <v>1</v>
       </c>
       <c r="G689" s="8">
-        <v>0</v>
+        <v>85467513.79</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
@@ -28520,17 +28520,17 @@
       <c r="C690" s="6">
         <v>46258</v>
       </c>
-      <c r="D690" s="8">
-        <v>0</v>
+      <c r="D690" s="7">
+        <v>7.735223</v>
       </c>
       <c r="E690" s="8">
-        <v>0</v>
+        <v>498377141</v>
       </c>
       <c r="F690" s="9">
         <v>10085</v>
       </c>
       <c r="G690" s="8">
-        <v>0</v>
+        <v>3855058565.8</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.25">
@@ -28566,17 +28566,17 @@
       <c r="C692" s="6">
         <v>46258</v>
       </c>
-      <c r="D692" s="8">
-        <v>0</v>
+      <c r="D692" s="7">
+        <v>67.748842</v>
       </c>
       <c r="E692" s="8">
-        <v>0</v>
+        <v>6829649</v>
       </c>
       <c r="F692" s="9">
         <v>2</v>
       </c>
       <c r="G692" s="8">
-        <v>0</v>
+        <v>462700811.26</v>
       </c>
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.25">
@@ -28589,17 +28589,17 @@
       <c r="C693" s="6">
         <v>46258</v>
       </c>
-      <c r="D693" s="8">
-        <v>0</v>
+      <c r="D693" s="7">
+        <v>8.737106</v>
       </c>
       <c r="E693" s="8">
-        <v>0</v>
+        <v>11470333</v>
       </c>
       <c r="F693" s="9">
         <v>1381</v>
       </c>
       <c r="G693" s="8">
-        <v>0</v>
+        <v>100217516.93</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.25">
@@ -28612,17 +28612,17 @@
       <c r="C694" s="6">
         <v>46258</v>
       </c>
-      <c r="D694" s="8">
-        <v>0</v>
+      <c r="D694" s="11">
+        <v>7.8277</v>
       </c>
       <c r="E694" s="8">
-        <v>0</v>
+        <v>9089550</v>
       </c>
       <c r="F694" s="9">
         <v>2356</v>
       </c>
       <c r="G694" s="8">
-        <v>0</v>
+        <v>71150266.84</v>
       </c>
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.25">
@@ -28635,17 +28635,17 @@
       <c r="C695" s="6">
         <v>46258</v>
       </c>
-      <c r="D695" s="8">
-        <v>0</v>
+      <c r="D695" s="7">
+        <v>7.087264</v>
       </c>
       <c r="E695" s="8">
-        <v>0</v>
+        <v>9159050</v>
       </c>
       <c r="F695" s="9">
         <v>1215</v>
       </c>
       <c r="G695" s="8">
-        <v>0</v>
+        <v>64912606.2</v>
       </c>
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.25">
@@ -28727,17 +28727,17 @@
       <c r="C699" s="6">
         <v>46258</v>
       </c>
-      <c r="D699" s="8">
-        <v>0</v>
+      <c r="D699" s="7">
+        <v>3.225084</v>
       </c>
       <c r="E699" s="8">
-        <v>0</v>
+        <v>498380319</v>
       </c>
       <c r="F699" s="9">
         <v>7506</v>
       </c>
       <c r="G699" s="8">
-        <v>0</v>
+        <v>1607318551.64</v>
       </c>
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.25">
@@ -28773,17 +28773,17 @@
       <c r="C701" s="6">
         <v>46258</v>
       </c>
-      <c r="D701" s="8">
-        <v>0</v>
+      <c r="D701" s="7">
+        <v>1.877895</v>
       </c>
       <c r="E701" s="8">
-        <v>0</v>
+        <v>1887415</v>
       </c>
       <c r="F701" s="9">
         <v>83</v>
       </c>
       <c r="G701" s="8">
-        <v>0</v>
+        <v>3544366.32</v>
       </c>
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.25">
@@ -28888,17 +28888,17 @@
       <c r="C706" s="6">
         <v>46258</v>
       </c>
-      <c r="D706" s="8">
-        <v>0</v>
+      <c r="D706" s="7">
+        <v>4.362676</v>
       </c>
       <c r="E706" s="8">
-        <v>0</v>
+        <v>126137110</v>
       </c>
       <c r="F706" s="9">
         <v>1082</v>
       </c>
       <c r="G706" s="8">
-        <v>0</v>
+        <v>550295364.51</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.25">
@@ -28934,17 +28934,17 @@
       <c r="C708" s="6">
         <v>46258</v>
       </c>
-      <c r="D708" s="8">
-        <v>0</v>
+      <c r="D708" s="7">
+        <v>19.726212</v>
       </c>
       <c r="E708" s="8">
-        <v>0</v>
+        <v>57539929</v>
       </c>
       <c r="F708" s="9">
         <v>17</v>
       </c>
       <c r="G708" s="8">
-        <v>0</v>
+        <v>1135044850.55</v>
       </c>
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.25">
@@ -28957,17 +28957,17 @@
       <c r="C709" s="6">
         <v>46258</v>
       </c>
-      <c r="D709" s="8">
-        <v>0</v>
+      <c r="D709" s="7">
+        <v>1.071201</v>
       </c>
       <c r="E709" s="8">
-        <v>0</v>
+        <v>161731078</v>
       </c>
       <c r="F709" s="9">
         <v>583</v>
       </c>
       <c r="G709" s="8">
-        <v>0</v>
+        <v>173246527.33</v>
       </c>
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.25">
@@ -28980,17 +28980,17 @@
       <c r="C710" s="6">
         <v>46258</v>
       </c>
-      <c r="D710" s="8">
-        <v>0</v>
+      <c r="D710" s="7">
+        <v>3.131029</v>
       </c>
       <c r="E710" s="8">
-        <v>0</v>
+        <v>30601403</v>
       </c>
       <c r="F710" s="9">
         <v>531</v>
       </c>
       <c r="G710" s="8">
-        <v>0</v>
+        <v>95813890.53</v>
       </c>
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.25">
@@ -29049,17 +29049,17 @@
       <c r="C713" s="6">
         <v>46258</v>
       </c>
-      <c r="D713" s="8">
-        <v>0</v>
+      <c r="D713" s="7">
+        <v>13923.557109</v>
       </c>
       <c r="E713" s="8">
-        <v>0</v>
+        <v>3698336</v>
       </c>
       <c r="F713" s="9">
         <v>17</v>
       </c>
       <c r="G713" s="8">
-        <v>0</v>
+        <v>51493992502.88</v>
       </c>
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.25">
@@ -29072,17 +29072,17 @@
       <c r="C714" s="6">
         <v>46258</v>
       </c>
-      <c r="D714" s="8">
-        <v>0</v>
+      <c r="D714" s="7">
+        <v>6.621691</v>
       </c>
       <c r="E714" s="8">
-        <v>0</v>
+        <v>2479606</v>
       </c>
       <c r="F714" s="9">
         <v>11</v>
       </c>
       <c r="G714" s="8">
-        <v>0</v>
+        <v>16419184.72</v>
       </c>
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.25">
@@ -29095,17 +29095,17 @@
       <c r="C715" s="6">
         <v>46258</v>
       </c>
-      <c r="D715" s="8">
-        <v>0</v>
+      <c r="D715" s="7">
+        <v>3.004927</v>
       </c>
       <c r="E715" s="8">
-        <v>0</v>
+        <v>4036816</v>
       </c>
       <c r="F715" s="9">
         <v>128</v>
       </c>
       <c r="G715" s="8">
-        <v>0</v>
+        <v>12130339.13</v>
       </c>
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.25">
@@ -29118,17 +29118,17 @@
       <c r="C716" s="6">
         <v>46258</v>
       </c>
-      <c r="D716" s="8">
-        <v>0</v>
+      <c r="D716" s="7">
+        <v>16.996052</v>
       </c>
       <c r="E716" s="8">
-        <v>0</v>
+        <v>91221799</v>
       </c>
       <c r="F716" s="9">
         <v>13</v>
       </c>
       <c r="G716" s="8">
-        <v>0</v>
+        <v>1550410444.3</v>
       </c>
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.25">
@@ -29164,17 +29164,17 @@
       <c r="C718" s="6">
         <v>46258</v>
       </c>
-      <c r="D718" s="8">
-        <v>0</v>
+      <c r="D718" s="7">
+        <v>3.293543</v>
       </c>
       <c r="E718" s="8">
-        <v>0</v>
+        <v>194667165</v>
       </c>
       <c r="F718" s="9">
         <v>1481</v>
       </c>
       <c r="G718" s="8">
-        <v>0</v>
+        <v>641144643.98</v>
       </c>
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.25">
@@ -29210,17 +29210,17 @@
       <c r="C720" s="6">
         <v>46258</v>
       </c>
-      <c r="D720" s="8">
-        <v>0</v>
+      <c r="D720" s="7">
+        <v>1.831169</v>
       </c>
       <c r="E720" s="8">
-        <v>0</v>
+        <v>33791579</v>
       </c>
       <c r="F720" s="9">
         <v>129</v>
       </c>
       <c r="G720" s="8">
-        <v>0</v>
+        <v>61878100.22</v>
       </c>
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.25">
@@ -29348,17 +29348,17 @@
       <c r="C726" s="6">
         <v>46258</v>
       </c>
-      <c r="D726" s="8">
-        <v>0</v>
+      <c r="D726" s="7">
+        <v>1.797147</v>
       </c>
       <c r="E726" s="8">
-        <v>0</v>
+        <v>31346783</v>
       </c>
       <c r="F726" s="9">
         <v>19</v>
       </c>
       <c r="G726" s="8">
-        <v>0</v>
+        <v>56334776.35</v>
       </c>
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.25">
@@ -29371,17 +29371,17 @@
       <c r="C727" s="6">
         <v>46258</v>
       </c>
-      <c r="D727" s="8">
-        <v>0</v>
+      <c r="D727" s="7">
+        <v>30.955109</v>
       </c>
       <c r="E727" s="8">
-        <v>0</v>
+        <v>109096943</v>
       </c>
       <c r="F727" s="9">
         <v>12</v>
       </c>
       <c r="G727" s="8">
-        <v>0</v>
+        <v>3377107769.62</v>
       </c>
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.25">
@@ -29394,17 +29394,17 @@
       <c r="C728" s="6">
         <v>46258</v>
       </c>
-      <c r="D728" s="8">
-        <v>0</v>
+      <c r="D728" s="7">
+        <v>4.177634</v>
       </c>
       <c r="E728" s="8">
-        <v>0</v>
+        <v>39256306.36</v>
       </c>
       <c r="F728" s="9">
         <v>1815</v>
       </c>
       <c r="G728" s="8">
-        <v>0</v>
+        <v>163998482.56</v>
       </c>
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.25">
@@ -29417,17 +29417,17 @@
       <c r="C729" s="6">
         <v>46258</v>
       </c>
-      <c r="D729" s="8">
-        <v>0</v>
+      <c r="D729" s="7">
+        <v>1.338687</v>
       </c>
       <c r="E729" s="8">
-        <v>0</v>
+        <v>28980489</v>
       </c>
       <c r="F729" s="9">
         <v>155</v>
       </c>
       <c r="G729" s="8">
-        <v>0</v>
+        <v>38795810.68</v>
       </c>
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.25">
@@ -29464,7 +29464,7 @@
         <v>46258</v>
       </c>
       <c r="D731" s="7">
-        <v>5.059459</v>
+        <v>5.060492</v>
       </c>
       <c r="E731" s="8">
         <v>561018563</v>
@@ -29473,7 +29473,7 @@
         <v>2</v>
       </c>
       <c r="G731" s="8">
-        <v>2838450284.64</v>
+        <v>2839030058.66</v>
       </c>
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.25">
@@ -29486,17 +29486,17 @@
       <c r="C732" s="6">
         <v>46258</v>
       </c>
-      <c r="D732" s="8">
-        <v>0</v>
+      <c r="D732" s="10">
+        <v>4.97654</v>
       </c>
       <c r="E732" s="8">
-        <v>0</v>
+        <v>4951108</v>
       </c>
       <c r="F732" s="9">
         <v>383</v>
       </c>
       <c r="G732" s="8">
-        <v>0</v>
+        <v>24639389.4</v>
       </c>
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.25">
@@ -29509,17 +29509,17 @@
       <c r="C733" s="6">
         <v>46258</v>
       </c>
-      <c r="D733" s="8">
-        <v>0</v>
+      <c r="D733" s="7">
+        <v>1.552672</v>
       </c>
       <c r="E733" s="8">
-        <v>0</v>
+        <v>882241872</v>
       </c>
       <c r="F733" s="9">
         <v>267</v>
       </c>
       <c r="G733" s="8">
-        <v>0</v>
+        <v>1369832160.86</v>
       </c>
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.25">
@@ -29532,17 +29532,17 @@
       <c r="C734" s="6">
         <v>46258</v>
       </c>
-      <c r="D734" s="8">
-        <v>0</v>
+      <c r="D734" s="7">
+        <v>0.536955</v>
       </c>
       <c r="E734" s="8">
-        <v>0</v>
+        <v>21237477</v>
       </c>
       <c r="F734" s="9">
         <v>55</v>
       </c>
       <c r="G734" s="8">
-        <v>0</v>
+        <v>11403579.05</v>
       </c>
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.25">
@@ -29601,17 +29601,17 @@
       <c r="C737" s="6">
         <v>46258</v>
       </c>
-      <c r="D737" s="8">
-        <v>0</v>
+      <c r="D737" s="7">
+        <v>3.996367</v>
       </c>
       <c r="E737" s="8">
-        <v>0</v>
+        <v>70383935</v>
       </c>
       <c r="F737" s="9">
         <v>208</v>
       </c>
       <c r="G737" s="8">
-        <v>0</v>
+        <v>281280023.04</v>
       </c>
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.25">
@@ -29647,17 +29647,17 @@
       <c r="C739" s="6">
         <v>46258</v>
       </c>
-      <c r="D739" s="8">
-        <v>0</v>
+      <c r="D739" s="7">
+        <v>3.106328</v>
       </c>
       <c r="E739" s="8">
-        <v>0</v>
+        <v>407241</v>
       </c>
       <c r="F739" s="9">
         <v>12</v>
       </c>
       <c r="G739" s="8">
-        <v>0</v>
+        <v>1265024.19</v>
       </c>
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.25">
@@ -29716,17 +29716,17 @@
       <c r="C742" s="6">
         <v>46258</v>
       </c>
-      <c r="D742" s="8">
-        <v>0</v>
+      <c r="D742" s="7">
+        <v>4.579124</v>
       </c>
       <c r="E742" s="8">
-        <v>0</v>
+        <v>23835511</v>
       </c>
       <c r="F742" s="9">
         <v>1548</v>
       </c>
       <c r="G742" s="8">
-        <v>0</v>
+        <v>109145761.02</v>
       </c>
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.25">
@@ -29762,17 +29762,17 @@
       <c r="C744" s="6">
         <v>46258</v>
       </c>
-      <c r="D744" s="8">
-        <v>0</v>
+      <c r="D744" s="7">
+        <v>8.765045</v>
       </c>
       <c r="E744" s="8">
-        <v>0</v>
+        <v>93724960</v>
       </c>
       <c r="F744" s="9">
         <v>13549</v>
       </c>
       <c r="G744" s="8">
-        <v>0</v>
+        <v>821503459.5</v>
       </c>
     </row>
     <row r="745" spans="1:7" x14ac:dyDescent="0.25">
@@ -29785,17 +29785,17 @@
       <c r="C745" s="6">
         <v>46258</v>
       </c>
-      <c r="D745" s="8">
-        <v>0</v>
+      <c r="D745" s="7">
+        <v>1.408753</v>
       </c>
       <c r="E745" s="8">
-        <v>0</v>
+        <v>10715936090</v>
       </c>
       <c r="F745" s="9">
         <v>2331</v>
       </c>
       <c r="G745" s="8">
-        <v>0</v>
+        <v>15096106835.74</v>
       </c>
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.25">
@@ -29808,17 +29808,17 @@
       <c r="C746" s="6">
         <v>46258</v>
       </c>
-      <c r="D746" s="8">
-        <v>0</v>
+      <c r="D746" s="10">
+        <v>4.14532</v>
       </c>
       <c r="E746" s="8">
-        <v>0</v>
+        <v>12489730</v>
       </c>
       <c r="F746" s="9">
         <v>914</v>
       </c>
       <c r="G746" s="8">
-        <v>0</v>
+        <v>51773932.25</v>
       </c>
     </row>
     <row r="747" spans="1:7" x14ac:dyDescent="0.25">
@@ -29831,17 +29831,17 @@
       <c r="C747" s="6">
         <v>46258</v>
       </c>
-      <c r="D747" s="8">
-        <v>0</v>
+      <c r="D747" s="7">
+        <v>6.051849</v>
       </c>
       <c r="E747" s="8">
-        <v>0</v>
+        <v>36000502</v>
       </c>
       <c r="F747" s="9">
         <v>84</v>
       </c>
       <c r="G747" s="8">
-        <v>0</v>
+        <v>217869595.73</v>
       </c>
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.25">
@@ -29946,17 +29946,17 @@
       <c r="C752" s="6">
         <v>46258</v>
       </c>
-      <c r="D752" s="8">
-        <v>0</v>
+      <c r="D752" s="7">
+        <v>111.663553</v>
       </c>
       <c r="E752" s="8">
-        <v>0</v>
+        <v>30359916</v>
       </c>
       <c r="F752" s="9">
         <v>13</v>
       </c>
       <c r="G752" s="8">
-        <v>0</v>
+        <v>3390096079.88</v>
       </c>
     </row>
     <row r="753" spans="1:7" x14ac:dyDescent="0.25">
@@ -29969,17 +29969,17 @@
       <c r="C753" s="6">
         <v>46258</v>
       </c>
-      <c r="D753" s="8">
-        <v>0</v>
+      <c r="D753" s="7">
+        <v>7.949866</v>
       </c>
       <c r="E753" s="8">
-        <v>0</v>
+        <v>59714381</v>
       </c>
       <c r="F753" s="9">
         <v>112</v>
       </c>
       <c r="G753" s="8">
-        <v>0</v>
+        <v>474721307.42</v>
       </c>
     </row>
     <row r="754" spans="1:7" x14ac:dyDescent="0.25">
@@ -30038,17 +30038,17 @@
       <c r="C756" s="6">
         <v>46258</v>
       </c>
-      <c r="D756" s="8">
-        <v>0</v>
+      <c r="D756" s="7">
+        <v>324.043697</v>
       </c>
       <c r="E756" s="8">
-        <v>0</v>
+        <v>377361</v>
       </c>
       <c r="F756" s="9">
         <v>51</v>
       </c>
       <c r="G756" s="8">
-        <v>0</v>
+        <v>122281453.69</v>
       </c>
     </row>
     <row r="757" spans="1:7" x14ac:dyDescent="0.25">
@@ -30061,17 +30061,17 @@
       <c r="C757" s="6">
         <v>46258</v>
       </c>
-      <c r="D757" s="8">
-        <v>0</v>
+      <c r="D757" s="10">
+        <v>47.01604</v>
       </c>
       <c r="E757" s="8">
-        <v>0</v>
+        <v>324452</v>
       </c>
       <c r="F757" s="9">
         <v>37</v>
       </c>
       <c r="G757" s="8">
-        <v>0</v>
+        <v>15254448.29</v>
       </c>
     </row>
     <row r="758" spans="1:7" x14ac:dyDescent="0.25">
@@ -30130,17 +30130,17 @@
       <c r="C760" s="6">
         <v>46258</v>
       </c>
-      <c r="D760" s="8">
-        <v>0</v>
+      <c r="D760" s="7">
+        <v>17.319614</v>
       </c>
       <c r="E760" s="8">
-        <v>0</v>
+        <v>887234531</v>
       </c>
       <c r="F760" s="9">
         <v>13</v>
       </c>
       <c r="G760" s="8">
-        <v>0</v>
+        <v>15366559518.42</v>
       </c>
     </row>
     <row r="761" spans="1:7" x14ac:dyDescent="0.25">
@@ -30177,7 +30177,7 @@
         <v>46258</v>
       </c>
       <c r="D762" s="7">
-        <v>0.243568</v>
+        <v>0.243666</v>
       </c>
       <c r="E762" s="8">
         <v>8567225782</v>
@@ -30186,7 +30186,7 @@
         <v>3361</v>
       </c>
       <c r="G762" s="8">
-        <v>2086705518.82</v>
+        <v>2087538490.77</v>
       </c>
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.25">
@@ -30200,7 +30200,7 @@
         <v>46258</v>
       </c>
       <c r="D763" s="7">
-        <v>0.366139</v>
+        <v>0.366237</v>
       </c>
       <c r="E763" s="8">
         <v>3748599016</v>
@@ -30209,7 +30209,7 @@
         <v>2548</v>
       </c>
       <c r="G763" s="8">
-        <v>1372509873.32</v>
+        <v>1372876393.33</v>
       </c>
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.25">
@@ -30222,17 +30222,17 @@
       <c r="C764" s="6">
         <v>46258</v>
       </c>
-      <c r="D764" s="8">
-        <v>0</v>
+      <c r="D764" s="7">
+        <v>58.652759</v>
       </c>
       <c r="E764" s="8">
-        <v>0</v>
+        <v>12464352</v>
       </c>
       <c r="F764" s="9">
         <v>190</v>
       </c>
       <c r="G764" s="8">
-        <v>0</v>
+        <v>731068631.26</v>
       </c>
     </row>
     <row r="765" spans="1:7" x14ac:dyDescent="0.25">
@@ -30291,17 +30291,17 @@
       <c r="C767" s="6">
         <v>46258</v>
       </c>
-      <c r="D767" s="8">
-        <v>0</v>
+      <c r="D767" s="7">
+        <v>40.865767</v>
       </c>
       <c r="E767" s="8">
-        <v>0</v>
+        <v>43149120</v>
       </c>
       <c r="F767" s="9">
         <v>12</v>
       </c>
       <c r="G767" s="8">
-        <v>0</v>
+        <v>1763321904.48</v>
       </c>
     </row>
     <row r="768" spans="1:7" x14ac:dyDescent="0.25">
@@ -30314,17 +30314,17 @@
       <c r="C768" s="6">
         <v>46258</v>
       </c>
-      <c r="D768" s="8">
-        <v>0</v>
+      <c r="D768" s="7">
+        <v>2.385638</v>
       </c>
       <c r="E768" s="8">
-        <v>0</v>
+        <v>2939697537</v>
       </c>
       <c r="F768" s="9">
         <v>9519</v>
       </c>
       <c r="G768" s="8">
-        <v>0</v>
+        <v>7013055467.13</v>
       </c>
     </row>
     <row r="769" spans="1:7" x14ac:dyDescent="0.25">
@@ -30337,17 +30337,17 @@
       <c r="C769" s="6">
         <v>46258</v>
       </c>
-      <c r="D769" s="8">
-        <v>0</v>
+      <c r="D769" s="7">
+        <v>7.249286</v>
       </c>
       <c r="E769" s="8">
-        <v>0</v>
+        <v>34414080</v>
       </c>
       <c r="F769" s="9">
         <v>14</v>
       </c>
       <c r="G769" s="8">
-        <v>0</v>
+        <v>249477512.08</v>
       </c>
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.25">
@@ -30383,17 +30383,17 @@
       <c r="C771" s="6">
         <v>46258</v>
       </c>
-      <c r="D771" s="8">
-        <v>0</v>
+      <c r="D771" s="7">
+        <v>1.353709</v>
       </c>
       <c r="E771" s="8">
-        <v>0</v>
+        <v>291815213</v>
       </c>
       <c r="F771" s="9">
         <v>24</v>
       </c>
       <c r="G771" s="8">
-        <v>0</v>
+        <v>395032781.31</v>
       </c>
     </row>
     <row r="772" spans="1:7" x14ac:dyDescent="0.25">
@@ -30416,7 +30416,7 @@
         <v>2875</v>
       </c>
       <c r="G772" s="8">
-        <v>1126940968.79</v>
+        <v>1126941441.35</v>
       </c>
     </row>
     <row r="773" spans="1:7" x14ac:dyDescent="0.25">
@@ -30475,17 +30475,17 @@
       <c r="C775" s="6">
         <v>46258</v>
       </c>
-      <c r="D775" s="8">
-        <v>0</v>
+      <c r="D775" s="7">
+        <v>546.236145</v>
       </c>
       <c r="E775" s="8">
-        <v>0</v>
+        <v>9741</v>
       </c>
       <c r="F775" s="9">
         <v>17</v>
       </c>
       <c r="G775" s="8">
-        <v>0</v>
+        <v>5320886.29</v>
       </c>
     </row>
     <row r="776" spans="1:7" x14ac:dyDescent="0.25">
@@ -30508,7 +30508,7 @@
         <v>6779</v>
       </c>
       <c r="G776" s="8">
-        <v>313871945.27</v>
+        <v>313871946.96</v>
       </c>
     </row>
     <row r="777" spans="1:7" x14ac:dyDescent="0.25">
@@ -30522,7 +30522,7 @@
         <v>46258</v>
       </c>
       <c r="D777" s="7">
-        <v>1660.923373</v>
+        <v>1660.926004</v>
       </c>
       <c r="E777" s="8">
         <v>2489541</v>
@@ -30531,7 +30531,7 @@
         <v>2393</v>
       </c>
       <c r="G777" s="8">
-        <v>4134936834.42</v>
+        <v>4134943385.78</v>
       </c>
     </row>
     <row r="778" spans="1:7" x14ac:dyDescent="0.25">
@@ -30636,17 +30636,17 @@
       <c r="C782" s="6">
         <v>46258</v>
       </c>
-      <c r="D782" s="8">
-        <v>0</v>
+      <c r="D782" s="7">
+        <v>1.966429</v>
       </c>
       <c r="E782" s="8">
-        <v>0</v>
+        <v>20178562</v>
       </c>
       <c r="F782" s="9">
         <v>233</v>
       </c>
       <c r="G782" s="8">
-        <v>0</v>
+        <v>39679717.31</v>
       </c>
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.25">
@@ -30660,7 +30660,7 @@
         <v>46258</v>
       </c>
       <c r="D783" s="7">
-        <v>1.067691</v>
+        <v>1.066477</v>
       </c>
       <c r="E783" s="8">
         <v>125713628</v>
@@ -30669,7 +30669,7 @@
         <v>951</v>
       </c>
       <c r="G783" s="8">
-        <v>134223355.62</v>
+        <v>134070734.51</v>
       </c>
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.25">
@@ -30682,17 +30682,17 @@
       <c r="C784" s="6">
         <v>46258</v>
       </c>
-      <c r="D784" s="8">
-        <v>0</v>
+      <c r="D784" s="7">
+        <v>59.285534</v>
       </c>
       <c r="E784" s="8">
-        <v>0</v>
+        <v>76999056</v>
       </c>
       <c r="F784" s="9">
         <v>2594</v>
       </c>
       <c r="G784" s="8">
-        <v>0</v>
+        <v>4564930160.1</v>
       </c>
     </row>
     <row r="785" spans="1:7" x14ac:dyDescent="0.25">
@@ -30705,17 +30705,17 @@
       <c r="C785" s="6">
         <v>46258</v>
       </c>
-      <c r="D785" s="8">
-        <v>0</v>
+      <c r="D785" s="7">
+        <v>12.987864</v>
       </c>
       <c r="E785" s="8">
-        <v>0</v>
+        <v>6936066</v>
       </c>
       <c r="F785" s="9">
         <v>13</v>
       </c>
       <c r="G785" s="8">
-        <v>0</v>
+        <v>90084681.76</v>
       </c>
     </row>
     <row r="786" spans="1:7" x14ac:dyDescent="0.25">
@@ -30751,17 +30751,17 @@
       <c r="C787" s="6">
         <v>46258</v>
       </c>
-      <c r="D787" s="8">
-        <v>0</v>
+      <c r="D787" s="10">
+        <v>0.00354</v>
       </c>
       <c r="E787" s="8">
-        <v>0</v>
+        <v>568993837</v>
       </c>
       <c r="F787" s="9">
         <v>12</v>
       </c>
       <c r="G787" s="8">
-        <v>0</v>
+        <v>2014055</v>
       </c>
     </row>
     <row r="788" spans="1:7" x14ac:dyDescent="0.25">
@@ -30774,17 +30774,17 @@
       <c r="C788" s="6">
         <v>46258</v>
       </c>
-      <c r="D788" s="8">
-        <v>0</v>
+      <c r="D788" s="7">
+        <v>411.039946</v>
       </c>
       <c r="E788" s="8">
-        <v>0</v>
+        <v>551203</v>
       </c>
       <c r="F788" s="9">
         <v>16</v>
       </c>
       <c r="G788" s="8">
-        <v>0</v>
+        <v>226566451.15</v>
       </c>
     </row>
     <row r="789" spans="1:7" x14ac:dyDescent="0.25">
@@ -30797,17 +30797,17 @@
       <c r="C789" s="6">
         <v>46258</v>
       </c>
-      <c r="D789" s="8">
-        <v>0</v>
+      <c r="D789" s="7">
+        <v>1.970404</v>
       </c>
       <c r="E789" s="8">
-        <v>0</v>
+        <v>1151128347</v>
       </c>
       <c r="F789" s="9">
         <v>13</v>
       </c>
       <c r="G789" s="8">
-        <v>0</v>
+        <v>2268188102.79</v>
       </c>
     </row>
     <row r="790" spans="1:7" x14ac:dyDescent="0.25">
@@ -30820,17 +30820,17 @@
       <c r="C790" s="6">
         <v>46258</v>
       </c>
-      <c r="D790" s="8">
-        <v>0</v>
+      <c r="D790" s="7">
+        <v>27.909915</v>
       </c>
       <c r="E790" s="8">
-        <v>0</v>
+        <v>2727730</v>
       </c>
       <c r="F790" s="9">
         <v>16</v>
       </c>
       <c r="G790" s="8">
-        <v>0</v>
+        <v>76130711.56</v>
       </c>
     </row>
     <row r="791" spans="1:7" x14ac:dyDescent="0.25">
@@ -30866,17 +30866,17 @@
       <c r="C792" s="6">
         <v>46258</v>
       </c>
-      <c r="D792" s="8">
-        <v>0</v>
+      <c r="D792" s="7">
+        <v>5.314542</v>
       </c>
       <c r="E792" s="8">
-        <v>0</v>
+        <v>108720021</v>
       </c>
       <c r="F792" s="9">
         <v>1491</v>
       </c>
       <c r="G792" s="8">
-        <v>0</v>
+        <v>577797070.17</v>
       </c>
     </row>
     <row r="793" spans="1:7" x14ac:dyDescent="0.25">
@@ -30889,17 +30889,17 @@
       <c r="C793" s="6">
         <v>46258</v>
       </c>
-      <c r="D793" s="8">
-        <v>0</v>
+      <c r="D793" s="7">
+        <v>20.551391</v>
       </c>
       <c r="E793" s="8">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="F793" s="9">
         <v>11</v>
       </c>
       <c r="G793" s="8">
-        <v>0</v>
+        <v>2885415.35</v>
       </c>
     </row>
     <row r="794" spans="1:7" x14ac:dyDescent="0.25">
@@ -30912,17 +30912,17 @@
       <c r="C794" s="6">
         <v>46258</v>
       </c>
-      <c r="D794" s="8">
-        <v>0</v>
+      <c r="D794" s="7">
+        <v>5.892505</v>
       </c>
       <c r="E794" s="8">
-        <v>0</v>
+        <v>997109</v>
       </c>
       <c r="F794" s="9">
         <v>12</v>
       </c>
       <c r="G794" s="8">
-        <v>0</v>
+        <v>5875470.16</v>
       </c>
     </row>
     <row r="795" spans="1:7" x14ac:dyDescent="0.25">
@@ -31050,17 +31050,17 @@
       <c r="C800" s="6">
         <v>46258</v>
       </c>
-      <c r="D800" s="8">
-        <v>0</v>
+      <c r="D800" s="7">
+        <v>11.558966</v>
       </c>
       <c r="E800" s="8">
-        <v>0</v>
+        <v>18379256</v>
       </c>
       <c r="F800" s="9">
         <v>23</v>
       </c>
       <c r="G800" s="8">
-        <v>0</v>
+        <v>212445193.22</v>
       </c>
     </row>
     <row r="801" spans="1:7" x14ac:dyDescent="0.25">
@@ -31119,17 +31119,17 @@
       <c r="C803" s="6">
         <v>46258</v>
       </c>
-      <c r="D803" s="8">
-        <v>0</v>
+      <c r="D803" s="7">
+        <v>6.356928</v>
       </c>
       <c r="E803" s="8">
-        <v>0</v>
+        <v>982591960</v>
       </c>
       <c r="F803" s="9">
         <v>6659</v>
       </c>
       <c r="G803" s="8">
-        <v>0</v>
+        <v>6246266422.87</v>
       </c>
     </row>
     <row r="804" spans="1:7" x14ac:dyDescent="0.25">
@@ -31281,7 +31281,7 @@
         <v>46258</v>
       </c>
       <c r="D810" s="7">
-        <v>1.750796</v>
+        <v>1.753749</v>
       </c>
       <c r="E810" s="8">
         <v>44529671</v>
@@ -31290,7 +31290,7 @@
         <v>2812</v>
       </c>
       <c r="G810" s="8">
-        <v>77962348.32</v>
+        <v>78093855.98</v>
       </c>
     </row>
     <row r="811" spans="1:7" x14ac:dyDescent="0.25">
@@ -32062,17 +32062,17 @@
       <c r="C844" s="6">
         <v>46258</v>
       </c>
-      <c r="D844" s="8">
-        <v>0</v>
+      <c r="D844" s="10">
+        <v>0.23831</v>
       </c>
       <c r="E844" s="8">
-        <v>0</v>
+        <v>3167281687.13</v>
       </c>
       <c r="F844" s="9">
         <v>2520</v>
       </c>
       <c r="G844" s="8">
-        <v>0</v>
+        <v>754796000.73</v>
       </c>
     </row>
     <row r="845" spans="1:7" x14ac:dyDescent="0.25">
@@ -32844,17 +32844,17 @@
       <c r="C878" s="6">
         <v>46258</v>
       </c>
-      <c r="D878" s="8">
-        <v>0</v>
+      <c r="D878" s="7">
+        <v>7.292694</v>
       </c>
       <c r="E878" s="8">
-        <v>0</v>
+        <v>4632104</v>
       </c>
       <c r="F878" s="9">
         <v>395</v>
       </c>
       <c r="G878" s="8">
-        <v>0</v>
+        <v>33780516.1</v>
       </c>
     </row>
     <row r="879" spans="1:7" x14ac:dyDescent="0.25">
@@ -33282,7 +33282,7 @@
         <v>46258</v>
       </c>
       <c r="D897" s="7">
-        <v>8.196689</v>
+        <v>8.221885</v>
       </c>
       <c r="E897" s="8">
         <v>132291047</v>
@@ -33291,7 +33291,7 @@
         <v>6498</v>
       </c>
       <c r="G897" s="8">
-        <v>1084348584.22</v>
+        <v>1087681792.08</v>
       </c>
     </row>
     <row r="898" spans="1:7" x14ac:dyDescent="0.25">
@@ -33534,17 +33534,17 @@
       <c r="C908" s="6">
         <v>46258</v>
       </c>
-      <c r="D908" s="8">
-        <v>0</v>
+      <c r="D908" s="7">
+        <v>14.988553</v>
       </c>
       <c r="E908" s="8">
-        <v>0</v>
+        <v>15404799</v>
       </c>
       <c r="F908" s="9">
         <v>371</v>
       </c>
       <c r="G908" s="8">
-        <v>0</v>
+        <v>230895638.79</v>
       </c>
     </row>
     <row r="909" spans="1:7" x14ac:dyDescent="0.25">
@@ -33926,7 +33926,7 @@
         <v>46258</v>
       </c>
       <c r="D925" s="7">
-        <v>0.123393</v>
+        <v>0.123533</v>
       </c>
       <c r="E925" s="8">
         <v>1105011730</v>
@@ -33935,7 +33935,7 @@
         <v>22</v>
       </c>
       <c r="G925" s="8">
-        <v>136350689.9</v>
+        <v>136505747.15</v>
       </c>
     </row>
     <row r="926" spans="1:7" x14ac:dyDescent="0.25">
@@ -33949,7 +33949,7 @@
         <v>46258</v>
       </c>
       <c r="D926" s="7">
-        <v>9.613964</v>
+        <v>9.649227</v>
       </c>
       <c r="E926" s="8">
         <v>36642196</v>
@@ -33958,7 +33958,7 @@
         <v>1750</v>
       </c>
       <c r="G926" s="8">
-        <v>352276743.75</v>
+        <v>353568859.9</v>
       </c>
     </row>
     <row r="927" spans="1:7" x14ac:dyDescent="0.25">
@@ -34041,7 +34041,7 @@
         <v>46258</v>
       </c>
       <c r="D930" s="7">
-        <v>0.181441</v>
+        <v>0.181953</v>
       </c>
       <c r="E930" s="8">
         <v>38636593007</v>
@@ -34050,7 +34050,7 @@
         <v>164</v>
       </c>
       <c r="G930" s="8">
-        <v>7010264007.2</v>
+        <v>7030033143.38</v>
       </c>
     </row>
     <row r="931" spans="1:7" x14ac:dyDescent="0.25">
@@ -34178,17 +34178,17 @@
       <c r="C936" s="6">
         <v>46258</v>
       </c>
-      <c r="D936" s="8">
-        <v>0</v>
+      <c r="D936" s="7">
+        <v>7.475438</v>
       </c>
       <c r="E936" s="8">
-        <v>0</v>
+        <v>71006734</v>
       </c>
       <c r="F936" s="9">
         <v>1993</v>
       </c>
       <c r="G936" s="8">
-        <v>0</v>
+        <v>530806408.68</v>
       </c>
     </row>
     <row r="937" spans="1:7" x14ac:dyDescent="0.25">
@@ -34685,7 +34685,7 @@
         <v>46258</v>
       </c>
       <c r="D958" s="7">
-        <v>6.308304</v>
+        <v>6.324153</v>
       </c>
       <c r="E958" s="8">
         <v>2027532.66</v>
@@ -34694,7 +34694,7 @@
         <v>718</v>
       </c>
       <c r="G958" s="8">
-        <v>12790291.58</v>
+        <v>12822426.98</v>
       </c>
     </row>
     <row r="959" spans="1:7" x14ac:dyDescent="0.25">
@@ -34753,17 +34753,17 @@
       <c r="C961" s="6">
         <v>46258</v>
       </c>
-      <c r="D961" s="8">
-        <v>0</v>
+      <c r="D961" s="7">
+        <v>67.414774</v>
       </c>
       <c r="E961" s="8">
-        <v>0</v>
+        <v>315131629</v>
       </c>
       <c r="F961" s="9">
         <v>6407</v>
       </c>
       <c r="G961" s="8">
-        <v>0</v>
+        <v>21244527545.01</v>
       </c>
     </row>
     <row r="962" spans="1:7" x14ac:dyDescent="0.25">
@@ -34961,7 +34961,7 @@
         <v>46258</v>
       </c>
       <c r="D970" s="7">
-        <v>5.983067</v>
+        <v>5.983088</v>
       </c>
       <c r="E970" s="8">
         <v>15827873</v>
@@ -34970,7 +34970,7 @@
         <v>326</v>
       </c>
       <c r="G970" s="8">
-        <v>94699220.26</v>
+        <v>94699550.26</v>
       </c>
     </row>
     <row r="971" spans="1:7" x14ac:dyDescent="0.25">
@@ -35328,17 +35328,17 @@
       <c r="C986" s="6">
         <v>46258</v>
       </c>
-      <c r="D986" s="8">
-        <v>0</v>
+      <c r="D986" s="7">
+        <v>7163.844425</v>
       </c>
       <c r="E986" s="8">
-        <v>0</v>
+        <v>783207</v>
       </c>
       <c r="F986" s="9">
         <v>37</v>
       </c>
       <c r="G986" s="8">
-        <v>0</v>
+        <v>5610773100.33</v>
       </c>
     </row>
     <row r="987" spans="1:7" x14ac:dyDescent="0.25">
@@ -35351,17 +35351,17 @@
       <c r="C987" s="6">
         <v>46258</v>
       </c>
-      <c r="D987" s="8">
-        <v>0</v>
+      <c r="D987" s="7">
+        <v>58.130981</v>
       </c>
       <c r="E987" s="8">
-        <v>0</v>
+        <v>309834135</v>
       </c>
       <c r="F987" s="9">
         <v>5721</v>
       </c>
       <c r="G987" s="8">
-        <v>0</v>
+        <v>18010962345.57</v>
       </c>
     </row>
     <row r="988" spans="1:7" x14ac:dyDescent="0.25">
@@ -35397,17 +35397,17 @@
       <c r="C989" s="6">
         <v>46258</v>
       </c>
-      <c r="D989" s="8">
-        <v>0</v>
+      <c r="D989" s="7">
+        <v>1.789485</v>
       </c>
       <c r="E989" s="8">
-        <v>0</v>
+        <v>189321082</v>
       </c>
       <c r="F989" s="9">
         <v>5</v>
       </c>
       <c r="G989" s="8">
-        <v>0</v>
+        <v>338787187.36</v>
       </c>
     </row>
     <row r="990" spans="1:7" x14ac:dyDescent="0.25">
@@ -35420,17 +35420,17 @@
       <c r="C990" s="6">
         <v>46258</v>
       </c>
-      <c r="D990" s="8">
-        <v>0</v>
+      <c r="D990" s="7">
+        <v>52.026848</v>
       </c>
       <c r="E990" s="8">
-        <v>0</v>
+        <v>3094492</v>
       </c>
       <c r="F990" s="9">
         <v>1</v>
       </c>
       <c r="G990" s="8">
-        <v>0</v>
+        <v>160996666.36</v>
       </c>
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.25">
@@ -35443,17 +35443,17 @@
       <c r="C991" s="6">
         <v>46258</v>
       </c>
-      <c r="D991" s="8">
-        <v>0</v>
+      <c r="D991" s="7">
+        <v>1.815986</v>
       </c>
       <c r="E991" s="8">
-        <v>0</v>
+        <v>6388269</v>
       </c>
       <c r="F991" s="9">
         <v>172</v>
       </c>
       <c r="G991" s="8">
-        <v>0</v>
+        <v>11601004.27</v>
       </c>
     </row>
     <row r="992" spans="1:7" x14ac:dyDescent="0.25">
@@ -35489,17 +35489,17 @@
       <c r="C993" s="6">
         <v>46258</v>
       </c>
-      <c r="D993" s="8">
-        <v>0</v>
+      <c r="D993" s="7">
+        <v>5.266607</v>
       </c>
       <c r="E993" s="8">
-        <v>0</v>
+        <v>478713318</v>
       </c>
       <c r="F993" s="9">
         <v>12916</v>
       </c>
       <c r="G993" s="8">
-        <v>0</v>
+        <v>2521195022.64</v>
       </c>
     </row>
     <row r="994" spans="1:7" x14ac:dyDescent="0.25">
@@ -35512,17 +35512,17 @@
       <c r="C994" s="6">
         <v>46258</v>
       </c>
-      <c r="D994" s="8">
-        <v>0</v>
+      <c r="D994" s="7">
+        <v>1.790582</v>
       </c>
       <c r="E994" s="8">
-        <v>0</v>
+        <v>358200626</v>
       </c>
       <c r="F994" s="9">
         <v>3586</v>
       </c>
       <c r="G994" s="8">
-        <v>0</v>
+        <v>641387622.2</v>
       </c>
     </row>
     <row r="995" spans="1:7" x14ac:dyDescent="0.25">
@@ -35535,17 +35535,17 @@
       <c r="C995" s="6">
         <v>46258</v>
       </c>
-      <c r="D995" s="8">
-        <v>0</v>
+      <c r="D995" s="7">
+        <v>57.960804</v>
       </c>
       <c r="E995" s="8">
-        <v>0</v>
+        <v>4238148</v>
       </c>
       <c r="F995" s="9">
         <v>12</v>
       </c>
       <c r="G995" s="8">
-        <v>0</v>
+        <v>245646465.01</v>
       </c>
     </row>
     <row r="996" spans="1:7" x14ac:dyDescent="0.25">
@@ -35558,17 +35558,17 @@
       <c r="C996" s="6">
         <v>46258</v>
       </c>
-      <c r="D996" s="8">
-        <v>0</v>
+      <c r="D996" s="7">
+        <v>15.548339</v>
       </c>
       <c r="E996" s="8">
-        <v>0</v>
+        <v>3147787</v>
       </c>
       <c r="F996" s="9">
         <v>1</v>
       </c>
       <c r="G996" s="8">
-        <v>0</v>
+        <v>48942859.34</v>
       </c>
     </row>
     <row r="997" spans="1:7" x14ac:dyDescent="0.25">
@@ -35581,17 +35581,17 @@
       <c r="C997" s="6">
         <v>46258</v>
       </c>
-      <c r="D997" s="8">
-        <v>0</v>
+      <c r="D997" s="7">
+        <v>52.617728</v>
       </c>
       <c r="E997" s="8">
-        <v>0</v>
+        <v>485559541</v>
       </c>
       <c r="F997" s="9">
         <v>7058</v>
       </c>
       <c r="G997" s="8">
-        <v>0</v>
+        <v>25549039897.6</v>
       </c>
     </row>
     <row r="998" spans="1:7" x14ac:dyDescent="0.25">
@@ -35627,17 +35627,17 @@
       <c r="C999" s="6">
         <v>46258</v>
       </c>
-      <c r="D999" s="8">
-        <v>0</v>
+      <c r="D999" s="7">
+        <v>54.655221</v>
       </c>
       <c r="E999" s="8">
-        <v>0</v>
+        <v>514444484</v>
       </c>
       <c r="F999" s="9">
         <v>1380</v>
       </c>
       <c r="G999" s="8">
-        <v>0</v>
+        <v>28117076725.07</v>
       </c>
     </row>
     <row r="1000" spans="1:7" x14ac:dyDescent="0.25">
@@ -35673,17 +35673,17 @@
       <c r="C1001" s="6">
         <v>46258</v>
       </c>
-      <c r="D1001" s="8">
-        <v>0</v>
+      <c r="D1001" s="7">
+        <v>48.851988</v>
       </c>
       <c r="E1001" s="8">
-        <v>0</v>
+        <v>496530374</v>
       </c>
       <c r="F1001" s="9">
         <v>212</v>
       </c>
       <c r="G1001" s="8">
-        <v>0</v>
+        <v>24256495829.5</v>
       </c>
     </row>
     <row r="1002" spans="1:7" x14ac:dyDescent="0.25">
@@ -35696,17 +35696,17 @@
       <c r="C1002" s="6">
         <v>46258</v>
       </c>
-      <c r="D1002" s="8">
-        <v>0</v>
+      <c r="D1002" s="7">
+        <v>49.018039</v>
       </c>
       <c r="E1002" s="8">
-        <v>0</v>
+        <v>92844834</v>
       </c>
       <c r="F1002" s="9">
         <v>826</v>
       </c>
       <c r="G1002" s="8">
-        <v>0</v>
+        <v>4551071681.79</v>
       </c>
     </row>
     <row r="1003" spans="1:7" x14ac:dyDescent="0.25">
@@ -35719,17 +35719,17 @@
       <c r="C1003" s="6">
         <v>46258</v>
       </c>
-      <c r="D1003" s="8">
-        <v>0</v>
+      <c r="D1003" s="7">
+        <v>1.929665</v>
       </c>
       <c r="E1003" s="8">
-        <v>0</v>
+        <v>179618321</v>
       </c>
       <c r="F1003" s="9">
         <v>1</v>
       </c>
       <c r="G1003" s="8">
-        <v>0</v>
+        <v>346603100.06</v>
       </c>
     </row>
     <row r="1004" spans="1:7" x14ac:dyDescent="0.25">
@@ -35742,17 +35742,17 @@
       <c r="C1004" s="6">
         <v>46258</v>
       </c>
-      <c r="D1004" s="8">
-        <v>0</v>
+      <c r="D1004" s="7">
+        <v>1.809288</v>
       </c>
       <c r="E1004" s="8">
-        <v>0</v>
+        <v>39442409</v>
       </c>
       <c r="F1004" s="9">
         <v>1</v>
       </c>
       <c r="G1004" s="8">
-        <v>0</v>
+        <v>71362676.09</v>
       </c>
     </row>
     <row r="1005" spans="1:7" x14ac:dyDescent="0.25">
@@ -35765,17 +35765,17 @@
       <c r="C1005" s="6">
         <v>46258</v>
       </c>
-      <c r="D1005" s="8">
-        <v>0</v>
+      <c r="D1005" s="7">
+        <v>53.699868</v>
       </c>
       <c r="E1005" s="8">
-        <v>0</v>
+        <v>73061184</v>
       </c>
       <c r="F1005" s="9">
         <v>54</v>
       </c>
       <c r="G1005" s="8">
-        <v>0</v>
+        <v>3923375936.49</v>
       </c>
     </row>
     <row r="1006" spans="1:7" x14ac:dyDescent="0.25">
@@ -35788,17 +35788,17 @@
       <c r="C1006" s="6">
         <v>46258</v>
       </c>
-      <c r="D1006" s="8">
-        <v>0</v>
+      <c r="D1006" s="7">
+        <v>4.486253</v>
       </c>
       <c r="E1006" s="8">
-        <v>0</v>
+        <v>82683881</v>
       </c>
       <c r="F1006" s="9">
         <v>1</v>
       </c>
       <c r="G1006" s="8">
-        <v>0</v>
+        <v>370940849.42</v>
       </c>
     </row>
     <row r="1007" spans="1:7" x14ac:dyDescent="0.25">
@@ -35811,17 +35811,17 @@
       <c r="C1007" s="6">
         <v>46258</v>
       </c>
-      <c r="D1007" s="8">
-        <v>0</v>
+      <c r="D1007" s="11">
+        <v>3.1496</v>
       </c>
       <c r="E1007" s="8">
-        <v>0</v>
+        <v>1018594714</v>
       </c>
       <c r="F1007" s="9">
         <v>30022</v>
       </c>
       <c r="G1007" s="8">
-        <v>0</v>
+        <v>3208165519.38</v>
       </c>
     </row>
     <row r="1008" spans="1:7" x14ac:dyDescent="0.25">
@@ -35880,17 +35880,17 @@
       <c r="C1010" s="6">
         <v>46258</v>
       </c>
-      <c r="D1010" s="8">
-        <v>0</v>
+      <c r="D1010" s="10">
+        <v>1.66469</v>
       </c>
       <c r="E1010" s="8">
-        <v>0</v>
+        <v>10669810</v>
       </c>
       <c r="F1010" s="9">
         <v>261</v>
       </c>
       <c r="G1010" s="8">
-        <v>0</v>
+        <v>17761931.26</v>
       </c>
     </row>
     <row r="1011" spans="1:7" x14ac:dyDescent="0.25">
@@ -35995,17 +35995,17 @@
       <c r="C1015" s="6">
         <v>46258</v>
       </c>
-      <c r="D1015" s="8">
-        <v>0</v>
+      <c r="D1015" s="7">
+        <v>1.203241</v>
       </c>
       <c r="E1015" s="8">
-        <v>0</v>
+        <v>31070756535</v>
       </c>
       <c r="F1015" s="9">
         <v>2082</v>
       </c>
       <c r="G1015" s="8">
-        <v>0</v>
+        <v>37385594445.28</v>
       </c>
     </row>
     <row r="1016" spans="1:7" x14ac:dyDescent="0.25">
@@ -36041,17 +36041,17 @@
       <c r="C1017" s="6">
         <v>46258</v>
       </c>
-      <c r="D1017" s="8">
-        <v>0</v>
+      <c r="D1017" s="7">
+        <v>36.996381</v>
       </c>
       <c r="E1017" s="8">
-        <v>0</v>
+        <v>95518</v>
       </c>
       <c r="F1017" s="9">
         <v>1</v>
       </c>
       <c r="G1017" s="8">
-        <v>0</v>
+        <v>3533820.29</v>
       </c>
     </row>
     <row r="1018" spans="1:7" x14ac:dyDescent="0.25">
@@ -36088,7 +36088,7 @@
         <v>46258</v>
       </c>
       <c r="D1019" s="7">
-        <v>4.331636</v>
+        <v>4.335307</v>
       </c>
       <c r="E1019" s="8">
         <v>2504694</v>
@@ -36097,7 +36097,7 @@
         <v>1056</v>
       </c>
       <c r="G1019" s="8">
-        <v>10849422.5</v>
+        <v>10858616.23</v>
       </c>
     </row>
     <row r="1020" spans="1:7" x14ac:dyDescent="0.25">
@@ -36111,7 +36111,7 @@
         <v>46258</v>
       </c>
       <c r="D1020" s="7">
-        <v>4.665249</v>
+        <v>4.665282</v>
       </c>
       <c r="E1020" s="8">
         <v>45958569</v>
@@ -36120,7 +36120,7 @@
         <v>932</v>
       </c>
       <c r="G1020" s="8">
-        <v>214408155.7</v>
+        <v>214409706.1</v>
       </c>
     </row>
     <row r="1021" spans="1:7" x14ac:dyDescent="0.25">
@@ -36133,17 +36133,17 @@
       <c r="C1021" s="6">
         <v>46258</v>
       </c>
-      <c r="D1021" s="8">
-        <v>0</v>
+      <c r="D1021" s="7">
+        <v>1.542887</v>
       </c>
       <c r="E1021" s="8">
-        <v>0</v>
+        <v>38712606</v>
       </c>
       <c r="F1021" s="9">
         <v>27</v>
       </c>
       <c r="G1021" s="8">
-        <v>0</v>
+        <v>59729168.68</v>
       </c>
     </row>
     <row r="1022" spans="1:7" x14ac:dyDescent="0.25">
@@ -36156,17 +36156,17 @@
       <c r="C1022" s="6">
         <v>46258</v>
       </c>
-      <c r="D1022" s="8">
-        <v>0</v>
+      <c r="D1022" s="7">
+        <v>1.455404</v>
       </c>
       <c r="E1022" s="8">
-        <v>0</v>
+        <v>121551615</v>
       </c>
       <c r="F1022" s="9">
         <v>1419</v>
       </c>
       <c r="G1022" s="8">
-        <v>0</v>
+        <v>176906729.44</v>
       </c>
     </row>
     <row r="1023" spans="1:7" x14ac:dyDescent="0.25">
@@ -36202,17 +36202,17 @@
       <c r="C1024" s="6">
         <v>46258</v>
       </c>
-      <c r="D1024" s="8">
-        <v>0</v>
+      <c r="D1024" s="7">
+        <v>0.002268</v>
       </c>
       <c r="E1024" s="8">
-        <v>0</v>
+        <v>21405755952</v>
       </c>
       <c r="F1024" s="9">
         <v>1</v>
       </c>
       <c r="G1024" s="8">
-        <v>0</v>
+        <v>48542994.12</v>
       </c>
     </row>
     <row r="1025" spans="1:7" x14ac:dyDescent="0.25">
@@ -36225,17 +36225,17 @@
       <c r="C1025" s="6">
         <v>46258</v>
       </c>
-      <c r="D1025" s="8">
-        <v>0</v>
+      <c r="D1025" s="7">
+        <v>62.214789</v>
       </c>
       <c r="E1025" s="8">
-        <v>0</v>
+        <v>41940</v>
       </c>
       <c r="F1025" s="9">
         <v>1</v>
       </c>
       <c r="G1025" s="8">
-        <v>0</v>
+        <v>2609288.23</v>
       </c>
     </row>
     <row r="1026" spans="1:7" x14ac:dyDescent="0.25">
@@ -36248,17 +36248,17 @@
       <c r="C1026" s="6">
         <v>46258</v>
       </c>
-      <c r="D1026" s="8">
-        <v>0</v>
+      <c r="D1026" s="7">
+        <v>58.102418</v>
       </c>
       <c r="E1026" s="8">
-        <v>0</v>
+        <v>2183294</v>
       </c>
       <c r="F1026" s="9">
         <v>55</v>
       </c>
       <c r="G1026" s="8">
-        <v>0</v>
+        <v>126854661.18</v>
       </c>
     </row>
     <row r="1027" spans="1:7" x14ac:dyDescent="0.25">
@@ -36271,17 +36271,17 @@
       <c r="C1027" s="6">
         <v>46258</v>
       </c>
-      <c r="D1027" s="8">
-        <v>0</v>
+      <c r="D1027" s="7">
+        <v>52.031829</v>
       </c>
       <c r="E1027" s="8">
-        <v>0</v>
+        <v>1726780</v>
       </c>
       <c r="F1027" s="9">
         <v>2</v>
       </c>
       <c r="G1027" s="8">
-        <v>0</v>
+        <v>89847521.51</v>
       </c>
     </row>
     <row r="1028" spans="1:7" x14ac:dyDescent="0.25">
@@ -36295,7 +36295,7 @@
         <v>46258</v>
       </c>
       <c r="D1028" s="7">
-        <v>6.821911</v>
+        <v>6.838159</v>
       </c>
       <c r="E1028" s="8">
         <v>78038381</v>
@@ -36304,7 +36304,7 @@
         <v>5061</v>
       </c>
       <c r="G1028" s="8">
-        <v>532370865.88</v>
+        <v>533638863.93</v>
       </c>
     </row>
     <row r="1029" spans="1:7" x14ac:dyDescent="0.25">
@@ -36386,17 +36386,17 @@
       <c r="C1032" s="6">
         <v>46258</v>
       </c>
-      <c r="D1032" s="8">
-        <v>0</v>
+      <c r="D1032" s="7">
+        <v>3.134032</v>
       </c>
       <c r="E1032" s="8">
-        <v>0</v>
+        <v>2940278577</v>
       </c>
       <c r="F1032" s="9">
         <v>46</v>
       </c>
       <c r="G1032" s="8">
-        <v>0</v>
+        <v>9214926478.94</v>
       </c>
     </row>
     <row r="1033" spans="1:7" x14ac:dyDescent="0.25">
@@ -36455,17 +36455,17 @@
       <c r="C1035" s="6">
         <v>46258</v>
       </c>
-      <c r="D1035" s="8">
-        <v>0</v>
+      <c r="D1035" s="7">
+        <v>57.895725</v>
       </c>
       <c r="E1035" s="8">
-        <v>0</v>
+        <v>196370</v>
       </c>
       <c r="F1035" s="9">
         <v>1</v>
       </c>
       <c r="G1035" s="8">
-        <v>0</v>
+        <v>11368983.52</v>
       </c>
     </row>
     <row r="1036" spans="1:7" x14ac:dyDescent="0.25">
@@ -36524,17 +36524,17 @@
       <c r="C1038" s="6">
         <v>46258</v>
       </c>
-      <c r="D1038" s="8">
-        <v>0</v>
+      <c r="D1038" s="7">
+        <v>4.852835</v>
       </c>
       <c r="E1038" s="8">
-        <v>0</v>
+        <v>20126922286</v>
       </c>
       <c r="F1038" s="9">
         <v>107297</v>
       </c>
       <c r="G1038" s="8">
-        <v>0</v>
+        <v>97672633177.43</v>
       </c>
     </row>
     <row r="1039" spans="1:7" x14ac:dyDescent="0.25">
@@ -36547,17 +36547,17 @@
       <c r="C1039" s="6">
         <v>46258</v>
       </c>
-      <c r="D1039" s="8">
-        <v>0</v>
+      <c r="D1039" s="7">
+        <v>169.028781</v>
       </c>
       <c r="E1039" s="8">
-        <v>0</v>
+        <v>74818</v>
       </c>
       <c r="F1039" s="9">
         <v>1</v>
       </c>
       <c r="G1039" s="8">
-        <v>0</v>
+        <v>12646395.3</v>
       </c>
     </row>
     <row r="1040" spans="1:7" x14ac:dyDescent="0.25">
@@ -36570,17 +36570,17 @@
       <c r="C1040" s="6">
         <v>46258</v>
       </c>
-      <c r="D1040" s="8">
-        <v>0</v>
+      <c r="D1040" s="7">
+        <v>1.612454</v>
       </c>
       <c r="E1040" s="8">
-        <v>0</v>
+        <v>75307772</v>
       </c>
       <c r="F1040" s="9">
         <v>1178</v>
       </c>
       <c r="G1040" s="8">
-        <v>0</v>
+        <v>121430323.39</v>
       </c>
     </row>
     <row r="1041" spans="1:7" x14ac:dyDescent="0.25">
@@ -36639,17 +36639,17 @@
       <c r="C1043" s="6">
         <v>46258</v>
       </c>
-      <c r="D1043" s="8">
-        <v>0</v>
+      <c r="D1043" s="7">
+        <v>2.942264</v>
       </c>
       <c r="E1043" s="8">
-        <v>0</v>
+        <v>24785369</v>
       </c>
       <c r="F1043" s="9">
         <v>1</v>
       </c>
       <c r="G1043" s="8">
-        <v>0</v>
+        <v>72925096.93</v>
       </c>
     </row>
     <row r="1044" spans="1:7" x14ac:dyDescent="0.25">
@@ -36708,17 +36708,17 @@
       <c r="C1046" s="6">
         <v>46258</v>
       </c>
-      <c r="D1046" s="8">
-        <v>0</v>
+      <c r="D1046" s="7">
+        <v>2.104186</v>
       </c>
       <c r="E1046" s="8">
-        <v>0</v>
+        <v>382921936</v>
       </c>
       <c r="F1046" s="9">
         <v>14337</v>
       </c>
       <c r="G1046" s="8">
-        <v>0</v>
+        <v>805738976.01</v>
       </c>
     </row>
     <row r="1047" spans="1:7" x14ac:dyDescent="0.25">
@@ -36777,17 +36777,17 @@
       <c r="C1049" s="6">
         <v>46258</v>
       </c>
-      <c r="D1049" s="8">
-        <v>0</v>
+      <c r="D1049" s="7">
+        <v>4.495925</v>
       </c>
       <c r="E1049" s="8">
-        <v>0</v>
+        <v>1127191620</v>
       </c>
       <c r="F1049" s="9">
         <v>1</v>
       </c>
       <c r="G1049" s="8">
-        <v>0</v>
+        <v>5067769241.78</v>
       </c>
     </row>
     <row r="1050" spans="1:7" x14ac:dyDescent="0.25">
@@ -36892,17 +36892,17 @@
       <c r="C1054" s="6">
         <v>46258</v>
       </c>
-      <c r="D1054" s="8">
-        <v>0</v>
+      <c r="D1054" s="7">
+        <v>1.423176</v>
       </c>
       <c r="E1054" s="8">
-        <v>0</v>
+        <v>1897736422</v>
       </c>
       <c r="F1054" s="9">
         <v>71</v>
       </c>
       <c r="G1054" s="8">
-        <v>0</v>
+        <v>2700812274.98</v>
       </c>
     </row>
     <row r="1055" spans="1:7" x14ac:dyDescent="0.25">
@@ -37007,17 +37007,17 @@
       <c r="C1059" s="6">
         <v>46258</v>
       </c>
-      <c r="D1059" s="8">
-        <v>0</v>
+      <c r="D1059" s="7">
+        <v>53.634686</v>
       </c>
       <c r="E1059" s="8">
-        <v>0</v>
+        <v>265284</v>
       </c>
       <c r="F1059" s="9">
         <v>10</v>
       </c>
       <c r="G1059" s="8">
-        <v>0</v>
+        <v>14228423.99</v>
       </c>
     </row>
     <row r="1060" spans="1:7" x14ac:dyDescent="0.25">
@@ -37030,17 +37030,17 @@
       <c r="C1060" s="6">
         <v>46258</v>
       </c>
-      <c r="D1060" s="8">
-        <v>0</v>
+      <c r="D1060" s="7">
+        <v>1.786415</v>
       </c>
       <c r="E1060" s="8">
-        <v>0</v>
+        <v>307483131</v>
       </c>
       <c r="F1060" s="9">
         <v>13875</v>
       </c>
       <c r="G1060" s="8">
-        <v>0</v>
+        <v>549292383.04</v>
       </c>
     </row>
     <row r="1061" spans="1:7" x14ac:dyDescent="0.25">
@@ -37076,17 +37076,17 @@
       <c r="C1062" s="6">
         <v>46258</v>
       </c>
-      <c r="D1062" s="8">
-        <v>0</v>
+      <c r="D1062" s="7">
+        <v>21.869053</v>
       </c>
       <c r="E1062" s="8">
-        <v>0</v>
+        <v>213645740</v>
       </c>
       <c r="F1062" s="9">
         <v>23226</v>
       </c>
       <c r="G1062" s="8">
-        <v>0</v>
+        <v>4672229909.5</v>
       </c>
     </row>
     <row r="1063" spans="1:7" x14ac:dyDescent="0.25">
@@ -37099,17 +37099,17 @@
       <c r="C1063" s="6">
         <v>46258</v>
       </c>
-      <c r="D1063" s="8">
-        <v>0</v>
+      <c r="D1063" s="10">
+        <v>48.79219</v>
       </c>
       <c r="E1063" s="8">
-        <v>0</v>
+        <v>6292642</v>
       </c>
       <c r="F1063" s="9">
         <v>548</v>
       </c>
       <c r="G1063" s="8">
-        <v>0</v>
+        <v>307031784.65</v>
       </c>
     </row>
     <row r="1064" spans="1:7" x14ac:dyDescent="0.25">
@@ -37214,17 +37214,17 @@
       <c r="C1068" s="6">
         <v>46258</v>
       </c>
-      <c r="D1068" s="8">
-        <v>0</v>
+      <c r="D1068" s="7">
+        <v>1.084875</v>
       </c>
       <c r="E1068" s="8">
-        <v>0</v>
+        <v>1508400</v>
       </c>
       <c r="F1068" s="9">
         <v>16</v>
       </c>
       <c r="G1068" s="8">
-        <v>0</v>
+        <v>1636424.91</v>
       </c>
     </row>
     <row r="1069" spans="1:7" x14ac:dyDescent="0.25">
@@ -37237,17 +37237,17 @@
       <c r="C1069" s="6">
         <v>46258</v>
       </c>
-      <c r="D1069" s="8">
-        <v>0</v>
+      <c r="D1069" s="7">
+        <v>3.175411</v>
       </c>
       <c r="E1069" s="8">
-        <v>0</v>
+        <v>139738312</v>
       </c>
       <c r="F1069" s="9">
         <v>693</v>
       </c>
       <c r="G1069" s="8">
-        <v>0</v>
+        <v>443726627.97</v>
       </c>
     </row>
     <row r="1070" spans="1:7" x14ac:dyDescent="0.25">
@@ -37260,17 +37260,17 @@
       <c r="C1070" s="6">
         <v>46258</v>
       </c>
-      <c r="D1070" s="8">
-        <v>0</v>
+      <c r="D1070" s="7">
+        <v>1.880185</v>
       </c>
       <c r="E1070" s="8">
-        <v>0</v>
+        <v>38872370648</v>
       </c>
       <c r="F1070" s="9">
         <v>1344</v>
       </c>
       <c r="G1070" s="8">
-        <v>0</v>
+        <v>73087235875.81</v>
       </c>
     </row>
     <row r="1071" spans="1:7" x14ac:dyDescent="0.25">
@@ -37283,17 +37283,17 @@
       <c r="C1071" s="6">
         <v>46258</v>
       </c>
-      <c r="D1071" s="8">
-        <v>0</v>
+      <c r="D1071" s="7">
+        <v>47.937137</v>
       </c>
       <c r="E1071" s="8">
-        <v>0</v>
+        <v>485020000</v>
       </c>
       <c r="F1071" s="9">
         <v>3270</v>
       </c>
       <c r="G1071" s="8">
-        <v>0</v>
+        <v>23250470303.59</v>
       </c>
     </row>
     <row r="1072" spans="1:7" x14ac:dyDescent="0.25">
@@ -37306,17 +37306,17 @@
       <c r="C1072" s="6">
         <v>46258</v>
       </c>
-      <c r="D1072" s="8">
-        <v>0</v>
+      <c r="D1072" s="10">
+        <v>4.11107</v>
       </c>
       <c r="E1072" s="8">
-        <v>0</v>
+        <v>149168897</v>
       </c>
       <c r="F1072" s="9">
         <v>6157</v>
       </c>
       <c r="G1072" s="8">
-        <v>0</v>
+        <v>613243738.37</v>
       </c>
     </row>
     <row r="1073" spans="1:7" x14ac:dyDescent="0.25">
@@ -37329,17 +37329,17 @@
       <c r="C1073" s="6">
         <v>46258</v>
       </c>
-      <c r="D1073" s="8">
-        <v>0</v>
+      <c r="D1073" s="7">
+        <v>0.146567</v>
       </c>
       <c r="E1073" s="8">
-        <v>0</v>
+        <v>203418320</v>
       </c>
       <c r="F1073" s="9">
         <v>149</v>
       </c>
       <c r="G1073" s="8">
-        <v>0</v>
+        <v>29814402.56</v>
       </c>
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.25">
@@ -37352,17 +37352,17 @@
       <c r="C1074" s="6">
         <v>46258</v>
       </c>
-      <c r="D1074" s="8">
-        <v>0</v>
+      <c r="D1074" s="7">
+        <v>21.736512</v>
       </c>
       <c r="E1074" s="8">
-        <v>0</v>
+        <v>2077409</v>
       </c>
       <c r="F1074" s="9">
         <v>601</v>
       </c>
       <c r="G1074" s="8">
-        <v>0</v>
+        <v>45155625.18</v>
       </c>
     </row>
     <row r="1075" spans="1:7" x14ac:dyDescent="0.25">
@@ -37444,17 +37444,17 @@
       <c r="C1078" s="6">
         <v>46258</v>
       </c>
-      <c r="D1078" s="8">
-        <v>0</v>
+      <c r="D1078" s="7">
+        <v>0.524743</v>
       </c>
       <c r="E1078" s="8">
-        <v>0</v>
+        <v>2879223536</v>
       </c>
       <c r="F1078" s="9">
         <v>1123</v>
       </c>
       <c r="G1078" s="8">
-        <v>0</v>
+        <v>1510852936.38</v>
       </c>
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.25">
@@ -37467,17 +37467,17 @@
       <c r="C1079" s="6">
         <v>46258</v>
       </c>
-      <c r="D1079" s="8">
-        <v>0</v>
+      <c r="D1079" s="7">
+        <v>74.859775</v>
       </c>
       <c r="E1079" s="8">
-        <v>0</v>
+        <v>9822358</v>
       </c>
       <c r="F1079" s="9">
         <v>166</v>
       </c>
       <c r="G1079" s="8">
-        <v>0</v>
+        <v>735299508.39</v>
       </c>
     </row>
     <row r="1080" spans="1:7" x14ac:dyDescent="0.25">
@@ -37513,17 +37513,17 @@
       <c r="C1081" s="6">
         <v>46258</v>
       </c>
-      <c r="D1081" s="8">
-        <v>0</v>
+      <c r="D1081" s="7">
+        <v>4.127671</v>
       </c>
       <c r="E1081" s="8">
-        <v>0</v>
+        <v>3561461588</v>
       </c>
       <c r="F1081" s="9">
         <v>3664</v>
       </c>
       <c r="G1081" s="8">
-        <v>0</v>
+        <v>14700541187.3</v>
       </c>
     </row>
     <row r="1082" spans="1:7" x14ac:dyDescent="0.25">
@@ -37536,17 +37536,17 @@
       <c r="C1082" s="6">
         <v>46258</v>
       </c>
-      <c r="D1082" s="8">
-        <v>0</v>
+      <c r="D1082" s="7">
+        <v>49.546739</v>
       </c>
       <c r="E1082" s="8">
-        <v>0</v>
+        <v>495470</v>
       </c>
       <c r="F1082" s="9">
         <v>1</v>
       </c>
       <c r="G1082" s="8">
-        <v>0</v>
+        <v>24548922.53</v>
       </c>
     </row>
     <row r="1083" spans="1:7" x14ac:dyDescent="0.25">
@@ -37651,17 +37651,17 @@
       <c r="C1087" s="6">
         <v>46258</v>
       </c>
-      <c r="D1087" s="8">
-        <v>0</v>
+      <c r="D1087" s="10">
+        <v>5.21156</v>
       </c>
       <c r="E1087" s="8">
-        <v>0</v>
+        <v>39340281</v>
       </c>
       <c r="F1087" s="9">
         <v>3809</v>
       </c>
       <c r="G1087" s="8">
-        <v>0</v>
+        <v>205024250.29</v>
       </c>
     </row>
     <row r="1088" spans="1:7" x14ac:dyDescent="0.25">
@@ -37697,17 +37697,17 @@
       <c r="C1089" s="6">
         <v>46258</v>
       </c>
-      <c r="D1089" s="8">
-        <v>0</v>
+      <c r="D1089" s="10">
+        <v>5.74961</v>
       </c>
       <c r="E1089" s="8">
-        <v>0</v>
+        <v>5815684045</v>
       </c>
       <c r="F1089" s="9">
         <v>9850</v>
       </c>
       <c r="G1089" s="8">
-        <v>0</v>
+        <v>33437917976.94</v>
       </c>
     </row>
     <row r="1090" spans="1:7" x14ac:dyDescent="0.25">
@@ -37743,17 +37743,17 @@
       <c r="C1091" s="6">
         <v>46258</v>
       </c>
-      <c r="D1091" s="8">
-        <v>0</v>
+      <c r="D1091" s="7">
+        <v>45.663913</v>
       </c>
       <c r="E1091" s="8">
-        <v>0</v>
+        <v>2415590</v>
       </c>
       <c r="F1091" s="9">
         <v>1</v>
       </c>
       <c r="G1091" s="8">
-        <v>0</v>
+        <v>110305292.03</v>
       </c>
     </row>
     <row r="1092" spans="1:7" x14ac:dyDescent="0.25">
@@ -37789,17 +37789,17 @@
       <c r="C1093" s="6">
         <v>46258</v>
       </c>
-      <c r="D1093" s="8">
-        <v>0</v>
+      <c r="D1093" s="10">
+        <v>2.61932</v>
       </c>
       <c r="E1093" s="8">
-        <v>0</v>
+        <v>671046711</v>
       </c>
       <c r="F1093" s="9">
         <v>20863</v>
       </c>
       <c r="G1093" s="8">
-        <v>0</v>
+        <v>1757686019.81</v>
       </c>
     </row>
     <row r="1094" spans="1:7" x14ac:dyDescent="0.25">
@@ -37812,17 +37812,17 @@
       <c r="C1094" s="6">
         <v>46258</v>
       </c>
-      <c r="D1094" s="8">
-        <v>0</v>
+      <c r="D1094" s="12">
+        <v>22.781</v>
       </c>
       <c r="E1094" s="8">
-        <v>0</v>
+        <v>30312427</v>
       </c>
       <c r="F1094" s="9">
         <v>5721</v>
       </c>
       <c r="G1094" s="8">
-        <v>0</v>
+        <v>690547395.58</v>
       </c>
     </row>
     <row r="1095" spans="1:7" x14ac:dyDescent="0.25">
@@ -37835,17 +37835,17 @@
       <c r="C1095" s="6">
         <v>46258</v>
       </c>
-      <c r="D1095" s="8">
-        <v>0</v>
+      <c r="D1095" s="7">
+        <v>8.074577</v>
       </c>
       <c r="E1095" s="8">
-        <v>0</v>
+        <v>54696292</v>
       </c>
       <c r="F1095" s="9">
         <v>4241</v>
       </c>
       <c r="G1095" s="8">
-        <v>0</v>
+        <v>441649424.09</v>
       </c>
     </row>
     <row r="1096" spans="1:7" x14ac:dyDescent="0.25">
@@ -37858,17 +37858,17 @@
       <c r="C1096" s="6">
         <v>46258</v>
       </c>
-      <c r="D1096" s="8">
-        <v>0</v>
+      <c r="D1096" s="7">
+        <v>10.636667</v>
       </c>
       <c r="E1096" s="8">
-        <v>0</v>
+        <v>2299816245</v>
       </c>
       <c r="F1096" s="9">
         <v>635</v>
       </c>
       <c r="G1096" s="8">
-        <v>0</v>
+        <v>24462379889.31</v>
       </c>
     </row>
     <row r="1097" spans="1:7" x14ac:dyDescent="0.25">
@@ -37881,17 +37881,17 @@
       <c r="C1097" s="6">
         <v>46258</v>
       </c>
-      <c r="D1097" s="8">
-        <v>0</v>
+      <c r="D1097" s="7">
+        <v>15.597019</v>
       </c>
       <c r="E1097" s="8">
-        <v>0</v>
+        <v>8616794</v>
       </c>
       <c r="F1097" s="9">
         <v>725</v>
       </c>
       <c r="G1097" s="8">
-        <v>0</v>
+        <v>134396299.87</v>
       </c>
     </row>
     <row r="1098" spans="1:7" x14ac:dyDescent="0.25">
@@ -37904,17 +37904,17 @@
       <c r="C1098" s="6">
         <v>46258</v>
       </c>
-      <c r="D1098" s="8">
-        <v>0</v>
+      <c r="D1098" s="7">
+        <v>70.698656</v>
       </c>
       <c r="E1098" s="8">
-        <v>0</v>
+        <v>72233613</v>
       </c>
       <c r="F1098" s="9">
         <v>1437</v>
       </c>
       <c r="G1098" s="8">
-        <v>0</v>
+        <v>5106819373.56</v>
       </c>
     </row>
     <row r="1099" spans="1:7" x14ac:dyDescent="0.25">
@@ -37927,17 +37927,17 @@
       <c r="C1099" s="6">
         <v>46258</v>
       </c>
-      <c r="D1099" s="8">
-        <v>0</v>
+      <c r="D1099" s="7">
+        <v>30.270897</v>
       </c>
       <c r="E1099" s="8">
-        <v>0</v>
+        <v>32515349</v>
       </c>
       <c r="F1099" s="9">
         <v>1</v>
       </c>
       <c r="G1099" s="8">
-        <v>0</v>
+        <v>984268771.03</v>
       </c>
     </row>
     <row r="1100" spans="1:7" x14ac:dyDescent="0.25">
@@ -37950,17 +37950,17 @@
       <c r="C1100" s="6">
         <v>46258</v>
       </c>
-      <c r="D1100" s="8">
-        <v>0</v>
+      <c r="D1100" s="7">
+        <v>7.712053</v>
       </c>
       <c r="E1100" s="8">
-        <v>0</v>
+        <v>3555618821</v>
       </c>
       <c r="F1100" s="9">
         <v>45522</v>
       </c>
       <c r="G1100" s="8">
-        <v>0</v>
+        <v>27421121781.23</v>
       </c>
     </row>
     <row r="1101" spans="1:7" x14ac:dyDescent="0.25">
@@ -37973,17 +37973,17 @@
       <c r="C1101" s="6">
         <v>46258</v>
       </c>
-      <c r="D1101" s="8">
-        <v>0</v>
+      <c r="D1101" s="10">
+        <v>1.16996</v>
       </c>
       <c r="E1101" s="8">
-        <v>0</v>
+        <v>219480244</v>
       </c>
       <c r="F1101" s="9">
         <v>2572</v>
       </c>
       <c r="G1101" s="8">
-        <v>0</v>
+        <v>256783155.74</v>
       </c>
     </row>
     <row r="1102" spans="1:7" x14ac:dyDescent="0.25">
@@ -37996,17 +37996,17 @@
       <c r="C1102" s="6">
         <v>46258</v>
       </c>
-      <c r="D1102" s="8">
-        <v>0</v>
+      <c r="D1102" s="7">
+        <v>1.448091</v>
       </c>
       <c r="E1102" s="8">
-        <v>0</v>
+        <v>71026534</v>
       </c>
       <c r="F1102" s="9">
         <v>2075</v>
       </c>
       <c r="G1102" s="8">
-        <v>0</v>
+        <v>102852918.67</v>
       </c>
     </row>
     <row r="1103" spans="1:7" x14ac:dyDescent="0.25">
@@ -38019,17 +38019,17 @@
       <c r="C1103" s="6">
         <v>46258</v>
       </c>
-      <c r="D1103" s="8">
-        <v>0</v>
+      <c r="D1103" s="7">
+        <v>0.752901</v>
       </c>
       <c r="E1103" s="8">
-        <v>0</v>
+        <v>809896031</v>
       </c>
       <c r="F1103" s="9">
         <v>3648</v>
       </c>
       <c r="G1103" s="8">
-        <v>0</v>
+        <v>609771660.12</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.25">
@@ -38042,17 +38042,17 @@
       <c r="C1104" s="6">
         <v>46258</v>
       </c>
-      <c r="D1104" s="8">
-        <v>0</v>
+      <c r="D1104" s="7">
+        <v>1.767707</v>
       </c>
       <c r="E1104" s="8">
-        <v>0</v>
+        <v>115885201</v>
       </c>
       <c r="F1104" s="9">
         <v>2282</v>
       </c>
       <c r="G1104" s="8">
-        <v>0</v>
+        <v>204851107.54</v>
       </c>
     </row>
     <row r="1105" spans="1:7" x14ac:dyDescent="0.25">
@@ -38088,17 +38088,17 @@
       <c r="C1106" s="6">
         <v>46258</v>
       </c>
-      <c r="D1106" s="8">
-        <v>0</v>
+      <c r="D1106" s="7">
+        <v>12.683885</v>
       </c>
       <c r="E1106" s="8">
-        <v>0</v>
+        <v>671280828</v>
       </c>
       <c r="F1106" s="9">
         <v>41317</v>
       </c>
       <c r="G1106" s="8">
-        <v>0</v>
+        <v>8514449093.2</v>
       </c>
     </row>
     <row r="1107" spans="1:7" x14ac:dyDescent="0.25">
@@ -38111,17 +38111,17 @@
       <c r="C1107" s="6">
         <v>46258</v>
       </c>
-      <c r="D1107" s="8">
-        <v>0</v>
+      <c r="D1107" s="7">
+        <v>1.781203</v>
       </c>
       <c r="E1107" s="8">
-        <v>0</v>
+        <v>392570970</v>
       </c>
       <c r="F1107" s="9">
         <v>1</v>
       </c>
       <c r="G1107" s="8">
-        <v>0</v>
+        <v>699248517.93</v>
       </c>
     </row>
     <row r="1108" spans="1:7" x14ac:dyDescent="0.25">
@@ -38134,17 +38134,17 @@
       <c r="C1108" s="6">
         <v>46258</v>
       </c>
-      <c r="D1108" s="8">
-        <v>0</v>
+      <c r="D1108" s="7">
+        <v>1.277848</v>
       </c>
       <c r="E1108" s="8">
-        <v>0</v>
+        <v>668727970</v>
       </c>
       <c r="F1108" s="9">
         <v>137</v>
       </c>
       <c r="G1108" s="8">
-        <v>0</v>
+        <v>854532789.52</v>
       </c>
     </row>
     <row r="1109" spans="1:7" x14ac:dyDescent="0.25">
@@ -38226,17 +38226,17 @@
       <c r="C1112" s="6">
         <v>46258</v>
       </c>
-      <c r="D1112" s="8">
-        <v>0</v>
+      <c r="D1112" s="7">
+        <v>1.236476</v>
       </c>
       <c r="E1112" s="8">
-        <v>0</v>
+        <v>57213651</v>
       </c>
       <c r="F1112" s="9">
         <v>1565</v>
       </c>
       <c r="G1112" s="8">
-        <v>0</v>
+        <v>70743287.23</v>
       </c>
     </row>
     <row r="1113" spans="1:7" x14ac:dyDescent="0.25">
@@ -38272,17 +38272,17 @@
       <c r="C1114" s="6">
         <v>46258</v>
       </c>
-      <c r="D1114" s="8">
-        <v>0</v>
+      <c r="D1114" s="7">
+        <v>53.979554</v>
       </c>
       <c r="E1114" s="8">
-        <v>0</v>
+        <v>207100</v>
       </c>
       <c r="F1114" s="9">
         <v>18</v>
       </c>
       <c r="G1114" s="8">
-        <v>0</v>
+        <v>11179165.73</v>
       </c>
     </row>
     <row r="1115" spans="1:7" x14ac:dyDescent="0.25">
@@ -38295,17 +38295,17 @@
       <c r="C1115" s="6">
         <v>46258</v>
       </c>
-      <c r="D1115" s="8">
-        <v>0</v>
+      <c r="D1115" s="7">
+        <v>29.390159</v>
       </c>
       <c r="E1115" s="8">
-        <v>0</v>
+        <v>3187375790</v>
       </c>
       <c r="F1115" s="9">
         <v>65290</v>
       </c>
       <c r="G1115" s="8">
-        <v>0</v>
+        <v>93677480581.26</v>
       </c>
     </row>
     <row r="1116" spans="1:7" x14ac:dyDescent="0.25">
@@ -38341,17 +38341,17 @@
       <c r="C1117" s="6">
         <v>46258</v>
       </c>
-      <c r="D1117" s="8">
-        <v>0</v>
+      <c r="D1117" s="7">
+        <v>2.493898</v>
       </c>
       <c r="E1117" s="8">
-        <v>0</v>
+        <v>198104888</v>
       </c>
       <c r="F1117" s="9">
         <v>5863</v>
       </c>
       <c r="G1117" s="8">
-        <v>0</v>
+        <v>494053383.64</v>
       </c>
     </row>
     <row r="1118" spans="1:7" x14ac:dyDescent="0.25">
@@ -38618,7 +38618,7 @@
         <v>46258</v>
       </c>
       <c r="D1129" s="7">
-        <v>3.682196</v>
+        <v>3.681474</v>
       </c>
       <c r="E1129" s="8">
         <v>245457201</v>
@@ -38627,7 +38627,7 @@
         <v>12</v>
       </c>
       <c r="G1129" s="8">
-        <v>903821460.82</v>
+        <v>903644324.96</v>
       </c>
     </row>
     <row r="1130" spans="1:7" x14ac:dyDescent="0.25">
@@ -38686,17 +38686,17 @@
       <c r="C1132" s="6">
         <v>46258</v>
       </c>
-      <c r="D1132" s="8">
-        <v>0</v>
+      <c r="D1132" s="7">
+        <v>4.637592</v>
       </c>
       <c r="E1132" s="8">
-        <v>0</v>
+        <v>552407333</v>
       </c>
       <c r="F1132" s="9">
         <v>13</v>
       </c>
       <c r="G1132" s="8">
-        <v>0</v>
+        <v>2561839729.75</v>
       </c>
     </row>
     <row r="1133" spans="1:7" x14ac:dyDescent="0.25">
@@ -38940,7 +38940,7 @@
         <v>46258</v>
       </c>
       <c r="D1143" s="7">
-        <v>1.319535</v>
+        <v>1.323739</v>
       </c>
       <c r="E1143" s="8">
         <v>383692080</v>
@@ -38949,7 +38949,7 @@
         <v>940</v>
       </c>
       <c r="G1143" s="8">
-        <v>506295117.73</v>
+        <v>507908335.77</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.25">
@@ -38962,17 +38962,17 @@
       <c r="C1144" s="6">
         <v>46258</v>
       </c>
-      <c r="D1144" s="8">
-        <v>0</v>
+      <c r="D1144" s="7">
+        <v>5.964036</v>
       </c>
       <c r="E1144" s="8">
-        <v>0</v>
+        <v>124884945</v>
       </c>
       <c r="F1144" s="9">
         <v>6673</v>
       </c>
       <c r="G1144" s="8">
-        <v>0</v>
+        <v>744818352.34</v>
       </c>
     </row>
     <row r="1145" spans="1:7" x14ac:dyDescent="0.25">
@@ -39054,17 +39054,17 @@
       <c r="C1148" s="6">
         <v>46258</v>
       </c>
-      <c r="D1148" s="8">
-        <v>0</v>
+      <c r="D1148" s="7">
+        <v>2.279447</v>
       </c>
       <c r="E1148" s="8">
-        <v>0</v>
+        <v>218283096</v>
       </c>
       <c r="F1148" s="9">
         <v>754</v>
       </c>
       <c r="G1148" s="8">
-        <v>0</v>
+        <v>497564667.69</v>
       </c>
     </row>
     <row r="1149" spans="1:7" x14ac:dyDescent="0.25">
@@ -39124,16 +39124,16 @@
         <v>46258</v>
       </c>
       <c r="D1151" s="7">
-        <v>7.747508</v>
+        <v>7.852845</v>
       </c>
       <c r="E1151" s="8">
-        <v>6719435</v>
+        <v>6717556</v>
       </c>
       <c r="F1151" s="9">
         <v>776</v>
       </c>
       <c r="G1151" s="8">
-        <v>52058876.07</v>
+        <v>52751928.66</v>
       </c>
     </row>
     <row r="1152" spans="1:7" x14ac:dyDescent="0.25">
@@ -39169,17 +39169,17 @@
       <c r="C1153" s="6">
         <v>46258</v>
       </c>
-      <c r="D1153" s="10">
-        <v>11.24797</v>
+      <c r="D1153" s="7">
+        <v>11.636369</v>
       </c>
       <c r="E1153" s="8">
-        <v>90417526</v>
+        <v>90282513</v>
       </c>
       <c r="F1153" s="9">
         <v>7558</v>
       </c>
       <c r="G1153" s="8">
-        <v>1017013644.2</v>
+        <v>1050560645.84</v>
       </c>
     </row>
     <row r="1154" spans="1:7" x14ac:dyDescent="0.25">
@@ -39193,7 +39193,7 @@
         <v>46258</v>
       </c>
       <c r="D1154" s="7">
-        <v>4.351412</v>
+        <v>4.322457</v>
       </c>
       <c r="E1154" s="8">
         <v>6087863</v>
@@ -39202,7 +39202,7 @@
         <v>29</v>
       </c>
       <c r="G1154" s="8">
-        <v>26490802.08</v>
+        <v>26314524.59</v>
       </c>
     </row>
     <row r="1155" spans="1:7" x14ac:dyDescent="0.25">
@@ -39377,7 +39377,7 @@
         <v>46258</v>
       </c>
       <c r="D1162" s="7">
-        <v>17.007948</v>
+        <v>17.007949</v>
       </c>
       <c r="E1162" s="8">
         <v>9181755</v>
@@ -39386,7 +39386,7 @@
         <v>1355</v>
       </c>
       <c r="G1162" s="8">
-        <v>156162810.66</v>
+        <v>156162816.65</v>
       </c>
     </row>
     <row r="1163" spans="1:7" x14ac:dyDescent="0.25">
@@ -39445,17 +39445,17 @@
       <c r="C1165" s="6">
         <v>46258</v>
       </c>
-      <c r="D1165" s="8">
-        <v>0</v>
+      <c r="D1165" s="7">
+        <v>1.618561</v>
       </c>
       <c r="E1165" s="8">
-        <v>0</v>
+        <v>2651303752</v>
       </c>
       <c r="F1165" s="9">
         <v>13</v>
       </c>
       <c r="G1165" s="8">
-        <v>0</v>
+        <v>4291298011.69</v>
       </c>
     </row>
     <row r="1166" spans="1:7" x14ac:dyDescent="0.25">
@@ -39468,17 +39468,17 @@
       <c r="C1166" s="6">
         <v>46258</v>
       </c>
-      <c r="D1166" s="8">
-        <v>0</v>
+      <c r="D1166" s="7">
+        <v>2.141952</v>
       </c>
       <c r="E1166" s="8">
-        <v>0</v>
+        <v>1833223343</v>
       </c>
       <c r="F1166" s="9">
         <v>15</v>
       </c>
       <c r="G1166" s="8">
-        <v>0</v>
+        <v>3926675539.92</v>
       </c>
     </row>
     <row r="1167" spans="1:7" x14ac:dyDescent="0.25">
@@ -39698,17 +39698,17 @@
       <c r="C1176" s="6">
         <v>46258</v>
       </c>
-      <c r="D1176" s="8">
-        <v>0</v>
+      <c r="D1176" s="7">
+        <v>1.245236</v>
       </c>
       <c r="E1176" s="8">
-        <v>0</v>
+        <v>10801755</v>
       </c>
       <c r="F1176" s="9">
         <v>115</v>
       </c>
       <c r="G1176" s="8">
-        <v>0</v>
+        <v>13450738.06</v>
       </c>
     </row>
     <row r="1177" spans="1:7" x14ac:dyDescent="0.25">
@@ -39951,8 +39951,8 @@
       <c r="C1187" s="6">
         <v>46258</v>
       </c>
-      <c r="D1187" s="10">
-        <v>1.34745</v>
+      <c r="D1187" s="7">
+        <v>1.347767</v>
       </c>
       <c r="E1187" s="8">
         <v>110112373</v>
@@ -39961,7 +39961,7 @@
         <v>1503</v>
       </c>
       <c r="G1187" s="8">
-        <v>148370922.88</v>
+        <v>148405857.77</v>
       </c>
     </row>
     <row r="1188" spans="1:7" x14ac:dyDescent="0.25">
@@ -39998,7 +39998,7 @@
         <v>46258</v>
       </c>
       <c r="D1189" s="7">
-        <v>1.415962</v>
+        <v>1.415958</v>
       </c>
       <c r="E1189" s="8">
         <v>53692250</v>
@@ -40007,7 +40007,7 @@
         <v>45</v>
       </c>
       <c r="G1189" s="8">
-        <v>76026170.33</v>
+        <v>76025994.46</v>
       </c>
     </row>
     <row r="1190" spans="1:7" x14ac:dyDescent="0.25">
@@ -40136,16 +40136,16 @@
         <v>46258</v>
       </c>
       <c r="D1195" s="7">
-        <v>2.750935</v>
+        <v>2.772669</v>
       </c>
       <c r="E1195" s="8">
-        <v>10268772</v>
+        <v>10268716</v>
       </c>
       <c r="F1195" s="9">
         <v>675</v>
       </c>
       <c r="G1195" s="8">
-        <v>28248723.18</v>
+        <v>28471755.32</v>
       </c>
     </row>
     <row r="1196" spans="1:7" x14ac:dyDescent="0.25">
@@ -40158,17 +40158,17 @@
       <c r="C1196" s="6">
         <v>46258</v>
       </c>
-      <c r="D1196" s="8">
-        <v>0</v>
+      <c r="D1196" s="7">
+        <v>0.802064</v>
       </c>
       <c r="E1196" s="8">
-        <v>0</v>
+        <v>1033653600</v>
       </c>
       <c r="F1196" s="9">
         <v>19</v>
       </c>
       <c r="G1196" s="8">
-        <v>0</v>
+        <v>829056613.81</v>
       </c>
     </row>
     <row r="1197" spans="1:7" x14ac:dyDescent="0.25">
@@ -40204,17 +40204,17 @@
       <c r="C1198" s="6">
         <v>46258</v>
       </c>
-      <c r="D1198" s="8">
-        <v>0</v>
+      <c r="D1198" s="7">
+        <v>5.300821</v>
       </c>
       <c r="E1198" s="8">
-        <v>0</v>
+        <v>15766207</v>
       </c>
       <c r="F1198" s="9">
         <v>2110</v>
       </c>
       <c r="G1198" s="8">
-        <v>0</v>
+        <v>83573834.43</v>
       </c>
     </row>
     <row r="1199" spans="1:7" x14ac:dyDescent="0.25">
@@ -40411,17 +40411,17 @@
       <c r="C1207" s="6">
         <v>46258</v>
       </c>
-      <c r="D1207" s="8">
-        <v>0</v>
+      <c r="D1207" s="7">
+        <v>1.519658</v>
       </c>
       <c r="E1207" s="8">
-        <v>0</v>
+        <v>1341691934</v>
       </c>
       <c r="F1207" s="9">
         <v>394</v>
       </c>
       <c r="G1207" s="8">
-        <v>0</v>
+        <v>2038913378.13</v>
       </c>
     </row>
     <row r="1208" spans="1:7" x14ac:dyDescent="0.25">
@@ -40435,7 +40435,7 @@
         <v>46258</v>
       </c>
       <c r="D1208" s="7">
-        <v>72.504351</v>
+        <v>72.500113</v>
       </c>
       <c r="E1208" s="8">
         <v>19233520</v>
@@ -40444,7 +40444,7 @@
         <v>278</v>
       </c>
       <c r="G1208" s="8">
-        <v>1394513884.25</v>
+        <v>1394432377.58</v>
       </c>
     </row>
     <row r="1209" spans="1:7" x14ac:dyDescent="0.25">
@@ -40458,7 +40458,7 @@
         <v>46258</v>
       </c>
       <c r="D1209" s="7">
-        <v>57.735819</v>
+        <v>57.739031</v>
       </c>
       <c r="E1209" s="8">
         <v>145913440</v>
@@ -40467,7 +40467,7 @@
         <v>1780</v>
       </c>
       <c r="G1209" s="8">
-        <v>8424431900.1</v>
+        <v>8424900672.42</v>
       </c>
     </row>
     <row r="1210" spans="1:7" x14ac:dyDescent="0.25">
@@ -40527,7 +40527,7 @@
         <v>46258</v>
       </c>
       <c r="D1212" s="7">
-        <v>1.034791</v>
+        <v>1.035137</v>
       </c>
       <c r="E1212" s="8">
         <v>588672037</v>
@@ -40536,7 +40536,7 @@
         <v>13</v>
       </c>
       <c r="G1212" s="8">
-        <v>609152631.96</v>
+        <v>609356102.91</v>
       </c>
     </row>
     <row r="1213" spans="1:7" x14ac:dyDescent="0.25">
@@ -40572,17 +40572,17 @@
       <c r="C1214" s="6">
         <v>46258</v>
       </c>
-      <c r="D1214" s="8">
-        <v>0</v>
+      <c r="D1214" s="7">
+        <v>1.355629</v>
       </c>
       <c r="E1214" s="8">
-        <v>0</v>
+        <v>1339279649</v>
       </c>
       <c r="F1214" s="9">
         <v>34</v>
       </c>
       <c r="G1214" s="8">
-        <v>0</v>
+        <v>1815566455</v>
       </c>
     </row>
     <row r="1215" spans="1:7" x14ac:dyDescent="0.25">
@@ -40618,17 +40618,17 @@
       <c r="C1216" s="6">
         <v>46258</v>
       </c>
-      <c r="D1216" s="8">
-        <v>0</v>
+      <c r="D1216" s="7">
+        <v>5.281352</v>
       </c>
       <c r="E1216" s="8">
-        <v>0</v>
+        <v>286944997</v>
       </c>
       <c r="F1216" s="9">
         <v>80</v>
       </c>
       <c r="G1216" s="8">
-        <v>0</v>
+        <v>1515457460.63</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.25">
@@ -40641,17 +40641,17 @@
       <c r="C1217" s="6">
         <v>46258</v>
       </c>
-      <c r="D1217" s="8">
-        <v>0</v>
+      <c r="D1217" s="7">
+        <v>5.663741</v>
       </c>
       <c r="E1217" s="8">
-        <v>0</v>
+        <v>2163299</v>
       </c>
       <c r="F1217" s="9">
         <v>153</v>
       </c>
       <c r="G1217" s="8">
-        <v>0</v>
+        <v>12252364.46</v>
       </c>
     </row>
     <row r="1218" spans="1:7" x14ac:dyDescent="0.25">
@@ -40802,8 +40802,8 @@
       <c r="C1224" s="6">
         <v>46258</v>
       </c>
-      <c r="D1224" s="7">
-        <v>3.079181</v>
+      <c r="D1224" s="11">
+        <v>3.0794</v>
       </c>
       <c r="E1224" s="8">
         <v>1064914900</v>
@@ -40812,7 +40812,7 @@
         <v>15</v>
       </c>
       <c r="G1224" s="8">
-        <v>3279065411.92</v>
+        <v>3279298801.33</v>
       </c>
     </row>
     <row r="1225" spans="1:7" x14ac:dyDescent="0.25">
@@ -40964,7 +40964,7 @@
         <v>46258</v>
       </c>
       <c r="D1231" s="7">
-        <v>8.054063</v>
+        <v>8.058797</v>
       </c>
       <c r="E1231" s="8">
         <v>188312373</v>
@@ -40973,7 +40973,7 @@
         <v>12</v>
       </c>
       <c r="G1231" s="8">
-        <v>1516679686.67</v>
+        <v>1517571238.05</v>
       </c>
     </row>
     <row r="1232" spans="1:7" x14ac:dyDescent="0.25">
@@ -41101,17 +41101,17 @@
       <c r="C1237" s="6">
         <v>46258</v>
       </c>
-      <c r="D1237" s="8">
-        <v>0</v>
+      <c r="D1237" s="7">
+        <v>2.322083</v>
       </c>
       <c r="E1237" s="8">
-        <v>0</v>
+        <v>6866499553</v>
       </c>
       <c r="F1237" s="9">
         <v>1</v>
       </c>
       <c r="G1237" s="8">
-        <v>0</v>
+        <v>15944585183.33</v>
       </c>
     </row>
     <row r="1238" spans="1:7" x14ac:dyDescent="0.25">
@@ -41124,17 +41124,17 @@
       <c r="C1238" s="6">
         <v>46258</v>
       </c>
-      <c r="D1238" s="8">
-        <v>0</v>
+      <c r="D1238" s="7">
+        <v>50.938197</v>
       </c>
       <c r="E1238" s="8">
-        <v>0</v>
+        <v>3559908</v>
       </c>
       <c r="F1238" s="9">
         <v>19</v>
       </c>
       <c r="G1238" s="8">
-        <v>0</v>
+        <v>181335295.62</v>
       </c>
     </row>
     <row r="1239" spans="1:7" x14ac:dyDescent="0.25">
@@ -41331,17 +41331,17 @@
       <c r="C1247" s="6">
         <v>46258</v>
       </c>
-      <c r="D1247" s="8">
-        <v>0</v>
+      <c r="D1247" s="7">
+        <v>23.477498</v>
       </c>
       <c r="E1247" s="8">
-        <v>0</v>
+        <v>91880589</v>
       </c>
       <c r="F1247" s="9">
         <v>18324</v>
       </c>
       <c r="G1247" s="8">
-        <v>0</v>
+        <v>2157126321.83</v>
       </c>
     </row>
     <row r="1248" spans="1:7" x14ac:dyDescent="0.25">
@@ -41469,17 +41469,17 @@
       <c r="C1253" s="6">
         <v>46258</v>
       </c>
-      <c r="D1253" s="8">
-        <v>0</v>
+      <c r="D1253" s="7">
+        <v>1.610982</v>
       </c>
       <c r="E1253" s="8">
-        <v>0</v>
+        <v>592973692</v>
       </c>
       <c r="F1253" s="9">
         <v>1</v>
       </c>
       <c r="G1253" s="8">
-        <v>0</v>
+        <v>955270120.4</v>
       </c>
     </row>
     <row r="1254" spans="1:7" x14ac:dyDescent="0.25">
@@ -41539,7 +41539,7 @@
         <v>46258</v>
       </c>
       <c r="D1256" s="7">
-        <v>9401.327202</v>
+        <v>156.562872</v>
       </c>
       <c r="E1256" s="8">
         <v>2588867</v>
@@ -41548,7 +41548,7 @@
         <v>11</v>
       </c>
       <c r="G1256" s="8">
-        <v>24338785748.61</v>
+        <v>405320453.82</v>
       </c>
     </row>
     <row r="1257" spans="1:7" x14ac:dyDescent="0.25">
@@ -41838,7 +41838,7 @@
         <v>46258</v>
       </c>
       <c r="D1269" s="7">
-        <v>66.512737</v>
+        <v>66.527626</v>
       </c>
       <c r="E1269" s="8">
         <v>54144466</v>
@@ -41847,7 +41847,7 @@
         <v>1</v>
       </c>
       <c r="G1269" s="8">
-        <v>3601296603.29</v>
+        <v>3602102770.35</v>
       </c>
     </row>
     <row r="1270" spans="1:7" x14ac:dyDescent="0.25">
@@ -41975,8 +41975,8 @@
       <c r="C1275" s="6">
         <v>46258</v>
       </c>
-      <c r="D1275" s="10">
-        <v>3.87466</v>
+      <c r="D1275" s="7">
+        <v>3.870807</v>
       </c>
       <c r="E1275" s="8">
         <v>35851273</v>
@@ -41985,7 +41985,7 @@
         <v>93</v>
       </c>
       <c r="G1275" s="8">
-        <v>138911511.16</v>
+        <v>138773344.43</v>
       </c>
     </row>
     <row r="1276" spans="1:7" x14ac:dyDescent="0.25">
@@ -42022,7 +42022,7 @@
         <v>46258</v>
       </c>
       <c r="D1277" s="7">
-        <v>68.495268</v>
+        <v>68.511185</v>
       </c>
       <c r="E1277" s="8">
         <v>896094</v>
@@ -42031,7 +42031,7 @@
         <v>1</v>
       </c>
       <c r="G1277" s="8">
-        <v>61378198.51</v>
+        <v>61392461.45</v>
       </c>
     </row>
     <row r="1278" spans="1:7" x14ac:dyDescent="0.25">
@@ -42091,7 +42091,7 @@
         <v>46258</v>
       </c>
       <c r="D1280" s="7">
-        <v>62.539247</v>
+        <v>62.465433</v>
       </c>
       <c r="E1280" s="8">
         <v>17189834</v>
@@ -42100,7 +42100,7 @@
         <v>1</v>
       </c>
       <c r="G1280" s="8">
-        <v>1075039279.68</v>
+        <v>1073770419.44</v>
       </c>
     </row>
     <row r="1281" spans="1:7" x14ac:dyDescent="0.25">
@@ -42206,7 +42206,7 @@
         <v>46258</v>
       </c>
       <c r="D1285" s="7">
-        <v>1.014028</v>
+        <v>1.014265</v>
       </c>
       <c r="E1285" s="8">
         <v>292393185</v>
@@ -42215,7 +42215,7 @@
         <v>160</v>
       </c>
       <c r="G1285" s="8">
-        <v>296494937.27</v>
+        <v>296564280.73</v>
       </c>
     </row>
     <row r="1286" spans="1:7" x14ac:dyDescent="0.25">
@@ -42504,17 +42504,17 @@
       <c r="C1298" s="6">
         <v>46258</v>
       </c>
-      <c r="D1298" s="8">
-        <v>0</v>
+      <c r="D1298" s="7">
+        <v>19.692121</v>
       </c>
       <c r="E1298" s="8">
-        <v>0</v>
+        <v>83482513</v>
       </c>
       <c r="F1298" s="9">
         <v>3847</v>
       </c>
       <c r="G1298" s="8">
-        <v>0</v>
+        <v>1643947762.72</v>
       </c>
     </row>
     <row r="1299" spans="1:7" x14ac:dyDescent="0.25">
@@ -42574,7 +42574,7 @@
         <v>46258</v>
       </c>
       <c r="D1301" s="7">
-        <v>4.086601</v>
+        <v>4.086765</v>
       </c>
       <c r="E1301" s="8">
         <v>38725290</v>
@@ -42583,7 +42583,7 @@
         <v>599</v>
       </c>
       <c r="G1301" s="8">
-        <v>158254814.28</v>
+        <v>158261149.73</v>
       </c>
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
@@ -42642,17 +42642,17 @@
       <c r="C1304" s="6">
         <v>46258</v>
       </c>
-      <c r="D1304" s="8">
-        <v>0</v>
+      <c r="D1304" s="7">
+        <v>8.301321</v>
       </c>
       <c r="E1304" s="8">
-        <v>0</v>
+        <v>22627249</v>
       </c>
       <c r="F1304" s="9">
         <v>430</v>
       </c>
       <c r="G1304" s="8">
-        <v>0</v>
+        <v>187836050.44</v>
       </c>
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
@@ -42804,7 +42804,7 @@
         <v>46258</v>
       </c>
       <c r="D1311" s="7">
-        <v>4.008094</v>
+        <v>4.074116</v>
       </c>
       <c r="E1311" s="8">
         <v>11325391</v>
@@ -42813,7 +42813,7 @@
         <v>652</v>
       </c>
       <c r="G1311" s="8">
-        <v>45393226.15</v>
+        <v>46140955.54</v>
       </c>
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
@@ -42827,7 +42827,7 @@
         <v>46258</v>
       </c>
       <c r="D1312" s="7">
-        <v>5.095696</v>
+        <v>5.131556</v>
       </c>
       <c r="E1312" s="8">
         <v>3753438</v>
@@ -42836,7 +42836,7 @@
         <v>225</v>
       </c>
       <c r="G1312" s="8">
-        <v>19126377.34</v>
+        <v>19260978.61</v>
       </c>
     </row>
     <row r="1313" spans="1:7" x14ac:dyDescent="0.25">
@@ -42928,7 +42928,7 @@
         <v>27748</v>
       </c>
       <c r="G1316" s="8">
-        <v>48384699248.85</v>
+        <v>48384699271.83</v>
       </c>
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
@@ -42942,7 +42942,7 @@
         <v>46258</v>
       </c>
       <c r="D1317" s="7">
-        <v>12.900537</v>
+        <v>12.893489</v>
       </c>
       <c r="E1317" s="8">
         <v>362936554</v>
@@ -42951,7 +42951,7 @@
         <v>11222</v>
       </c>
       <c r="G1317" s="8">
-        <v>4682076479.23</v>
+        <v>4679518328.51</v>
       </c>
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
@@ -43149,7 +43149,7 @@
         <v>46258</v>
       </c>
       <c r="D1326" s="7">
-        <v>5.071604</v>
+        <v>5.088404</v>
       </c>
       <c r="E1326" s="8">
         <v>64298243</v>
@@ -43158,7 +43158,7 @@
         <v>504</v>
       </c>
       <c r="G1326" s="8">
-        <v>326095246.09</v>
+        <v>327175451.62</v>
       </c>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
@@ -43263,17 +43263,17 @@
       <c r="C1331" s="6">
         <v>46258</v>
       </c>
-      <c r="D1331" s="8">
-        <v>0</v>
+      <c r="D1331" s="7">
+        <v>52.506431</v>
       </c>
       <c r="E1331" s="8">
-        <v>0</v>
+        <v>107758829</v>
       </c>
       <c r="F1331" s="9">
         <v>579</v>
       </c>
       <c r="G1331" s="8">
-        <v>0</v>
+        <v>5658031570.3</v>
       </c>
     </row>
     <row r="1332" spans="1:7" x14ac:dyDescent="0.25">
@@ -43319,7 +43319,7 @@
         <v>694</v>
       </c>
       <c r="G1333" s="8">
-        <v>34192424.52</v>
+        <v>34192427.2</v>
       </c>
     </row>
     <row r="1334" spans="1:7" x14ac:dyDescent="0.25">
@@ -43356,7 +43356,7 @@
         <v>46258</v>
       </c>
       <c r="D1335" s="7">
-        <v>60.852651</v>
+        <v>60.852668</v>
       </c>
       <c r="E1335" s="8">
         <v>1663915438</v>
@@ -43365,7 +43365,7 @@
         <v>21767</v>
       </c>
       <c r="G1335" s="8">
-        <v>101253665354.53</v>
+        <v>101253693673.47</v>
       </c>
     </row>
     <row r="1336" spans="1:7" x14ac:dyDescent="0.25">
@@ -43401,17 +43401,17 @@
       <c r="C1337" s="6">
         <v>46258</v>
       </c>
-      <c r="D1337" s="8">
-        <v>0</v>
+      <c r="D1337" s="7">
+        <v>54.209964</v>
       </c>
       <c r="E1337" s="8">
-        <v>0</v>
+        <v>2941947877</v>
       </c>
       <c r="F1337" s="9">
         <v>23502</v>
       </c>
       <c r="G1337" s="8">
-        <v>0</v>
+        <v>159482887756.92</v>
       </c>
     </row>
     <row r="1338" spans="1:7" x14ac:dyDescent="0.25">
@@ -43424,17 +43424,17 @@
       <c r="C1338" s="6">
         <v>46258</v>
       </c>
-      <c r="D1338" s="8">
-        <v>0</v>
+      <c r="D1338" s="7">
+        <v>52.899836</v>
       </c>
       <c r="E1338" s="8">
-        <v>0</v>
+        <v>91411125</v>
       </c>
       <c r="F1338" s="9">
         <v>374</v>
       </c>
       <c r="G1338" s="8">
-        <v>0</v>
+        <v>4835633521.44</v>
       </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
@@ -43447,17 +43447,17 @@
       <c r="C1339" s="6">
         <v>46258</v>
       </c>
-      <c r="D1339" s="8">
-        <v>0</v>
+      <c r="D1339" s="7">
+        <v>67.235353</v>
       </c>
       <c r="E1339" s="8">
-        <v>0</v>
+        <v>35455823</v>
       </c>
       <c r="F1339" s="9">
         <v>744</v>
       </c>
       <c r="G1339" s="8">
-        <v>0</v>
+        <v>2383884765.95</v>
       </c>
     </row>
     <row r="1340" spans="1:7" x14ac:dyDescent="0.25">
@@ -43664,7 +43664,7 @@
         <v>53</v>
       </c>
       <c r="G1348" s="8">
-        <v>1259079227.87</v>
+        <v>1259079295.76</v>
       </c>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
@@ -43861,17 +43861,17 @@
       <c r="C1357" s="6">
         <v>46258</v>
       </c>
-      <c r="D1357" s="8">
-        <v>0</v>
+      <c r="D1357" s="7">
+        <v>7.485208</v>
       </c>
       <c r="E1357" s="8">
-        <v>0</v>
+        <v>454123622</v>
       </c>
       <c r="F1357" s="9">
         <v>22447</v>
       </c>
       <c r="G1357" s="8">
-        <v>0</v>
+        <v>3399209691.41</v>
       </c>
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.25">
@@ -44069,7 +44069,7 @@
         <v>46258</v>
       </c>
       <c r="D1366" s="7">
-        <v>3.487453</v>
+        <v>3.489923</v>
       </c>
       <c r="E1366" s="8">
         <v>212409687</v>
@@ -44078,7 +44078,7 @@
         <v>3035</v>
       </c>
       <c r="G1366" s="8">
-        <v>740768837.39</v>
+        <v>741293450.17</v>
       </c>
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.25">
@@ -44114,17 +44114,17 @@
       <c r="C1368" s="6">
         <v>46258</v>
       </c>
-      <c r="D1368" s="8">
-        <v>0</v>
+      <c r="D1368" s="7">
+        <v>0.162312</v>
       </c>
       <c r="E1368" s="8">
-        <v>0</v>
+        <v>20420067445</v>
       </c>
       <c r="F1368" s="9">
         <v>8202</v>
       </c>
       <c r="G1368" s="8">
-        <v>0</v>
+        <v>3314422617.1</v>
       </c>
     </row>
     <row r="1369" spans="1:7" x14ac:dyDescent="0.25">
@@ -44229,17 +44229,17 @@
       <c r="C1373" s="6">
         <v>46258</v>
       </c>
-      <c r="D1373" s="8">
-        <v>0</v>
+      <c r="D1373" s="7">
+        <v>1.136046</v>
       </c>
       <c r="E1373" s="8">
-        <v>0</v>
+        <v>39397688</v>
       </c>
       <c r="F1373" s="9">
         <v>442</v>
       </c>
       <c r="G1373" s="8">
-        <v>0</v>
+        <v>44757593.55</v>
       </c>
     </row>
     <row r="1374" spans="1:7" x14ac:dyDescent="0.25">
@@ -44413,17 +44413,17 @@
       <c r="C1381" s="6">
         <v>46258</v>
       </c>
-      <c r="D1381" s="8">
-        <v>0</v>
+      <c r="D1381" s="7">
+        <v>6.175143</v>
       </c>
       <c r="E1381" s="8">
-        <v>0</v>
+        <v>13509448</v>
       </c>
       <c r="F1381" s="9">
         <v>11</v>
       </c>
       <c r="G1381" s="8">
-        <v>0</v>
+        <v>83422767.46</v>
       </c>
     </row>
     <row r="1382" spans="1:7" x14ac:dyDescent="0.25">
@@ -44459,17 +44459,17 @@
       <c r="C1383" s="6">
         <v>46258</v>
       </c>
-      <c r="D1383" s="8">
-        <v>0</v>
+      <c r="D1383" s="10">
+        <v>1.34174</v>
       </c>
       <c r="E1383" s="8">
-        <v>0</v>
+        <v>2398364628</v>
       </c>
       <c r="F1383" s="9">
         <v>12</v>
       </c>
       <c r="G1383" s="8">
-        <v>0</v>
+        <v>3217981928.01</v>
       </c>
     </row>
     <row r="1384" spans="1:7" x14ac:dyDescent="0.25">
@@ -44483,7 +44483,7 @@
         <v>46258</v>
       </c>
       <c r="D1384" s="7">
-        <v>2.332865</v>
+        <v>2.348659</v>
       </c>
       <c r="E1384" s="8">
         <v>48652016</v>
@@ -44492,7 +44492,7 @@
         <v>651</v>
       </c>
       <c r="G1384" s="8">
-        <v>113498568.97</v>
+        <v>114266998.46</v>
       </c>
     </row>
     <row r="1385" spans="1:7" x14ac:dyDescent="0.25">
@@ -44551,17 +44551,17 @@
       <c r="C1387" s="6">
         <v>46258</v>
       </c>
-      <c r="D1387" s="8">
-        <v>0</v>
+      <c r="D1387" s="7">
+        <v>5.137777</v>
       </c>
       <c r="E1387" s="8">
-        <v>0</v>
+        <v>1905572233</v>
       </c>
       <c r="F1387" s="9">
         <v>49680</v>
       </c>
       <c r="G1387" s="8">
-        <v>0</v>
+        <v>9790405133.06</v>
       </c>
     </row>
     <row r="1388" spans="1:7" x14ac:dyDescent="0.25">
@@ -44689,17 +44689,17 @@
       <c r="C1393" s="6">
         <v>46258</v>
       </c>
-      <c r="D1393" s="8">
-        <v>0</v>
+      <c r="D1393" s="7">
+        <v>9.447514</v>
       </c>
       <c r="E1393" s="8">
-        <v>0</v>
+        <v>11389382485</v>
       </c>
       <c r="F1393" s="9">
         <v>34</v>
       </c>
       <c r="G1393" s="8">
-        <v>0</v>
+        <v>107601351009.46</v>
       </c>
     </row>
     <row r="1394" spans="1:7" x14ac:dyDescent="0.25">
@@ -44712,17 +44712,17 @@
       <c r="C1394" s="6">
         <v>46258</v>
       </c>
-      <c r="D1394" s="8">
-        <v>0</v>
+      <c r="D1394" s="7">
+        <v>0.247654</v>
       </c>
       <c r="E1394" s="8">
-        <v>0</v>
+        <v>1083898739</v>
       </c>
       <c r="F1394" s="9">
         <v>13</v>
       </c>
       <c r="G1394" s="8">
-        <v>0</v>
+        <v>268431957.67</v>
       </c>
     </row>
     <row r="1395" spans="1:7" x14ac:dyDescent="0.25">
@@ -44758,17 +44758,17 @@
       <c r="C1396" s="6">
         <v>46258</v>
       </c>
-      <c r="D1396" s="8">
-        <v>0</v>
+      <c r="D1396" s="7">
+        <v>1.750308</v>
       </c>
       <c r="E1396" s="8">
-        <v>0</v>
+        <v>9776185516</v>
       </c>
       <c r="F1396" s="9">
         <v>14</v>
       </c>
       <c r="G1396" s="8">
-        <v>0</v>
+        <v>17111335665.99</v>
       </c>
     </row>
     <row r="1397" spans="1:7" x14ac:dyDescent="0.25">
@@ -44804,17 +44804,17 @@
       <c r="C1398" s="6">
         <v>46258</v>
       </c>
-      <c r="D1398" s="8">
-        <v>0</v>
+      <c r="D1398" s="7">
+        <v>0.604008</v>
       </c>
       <c r="E1398" s="8">
-        <v>0</v>
+        <v>1086338077</v>
       </c>
       <c r="F1398" s="9">
         <v>11</v>
       </c>
       <c r="G1398" s="8">
-        <v>0</v>
+        <v>656157423.77</v>
       </c>
     </row>
     <row r="1399" spans="1:7" x14ac:dyDescent="0.25">
@@ -44920,7 +44920,7 @@
         <v>46258</v>
       </c>
       <c r="D1403" s="7">
-        <v>2.354304</v>
+        <v>2.367793</v>
       </c>
       <c r="E1403" s="8">
         <v>32110173</v>
@@ -44929,7 +44929,7 @@
         <v>282</v>
       </c>
       <c r="G1403" s="8">
-        <v>75597120.06</v>
+        <v>76030253.89</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.25">
@@ -44943,7 +44943,7 @@
         <v>46258</v>
       </c>
       <c r="D1404" s="7">
-        <v>2.972451</v>
+        <v>2.981881</v>
       </c>
       <c r="E1404" s="8">
         <v>5390532</v>
@@ -44952,7 +44952,7 @@
         <v>94</v>
       </c>
       <c r="G1404" s="8">
-        <v>16023090</v>
+        <v>16073925.93</v>
       </c>
     </row>
     <row r="1405" spans="1:7" x14ac:dyDescent="0.25">
@@ -45011,17 +45011,17 @@
       <c r="C1407" s="6">
         <v>46258</v>
       </c>
-      <c r="D1407" s="8">
-        <v>0</v>
+      <c r="D1407" s="7">
+        <v>10.717299</v>
       </c>
       <c r="E1407" s="8">
-        <v>0</v>
+        <v>1328323884</v>
       </c>
       <c r="F1407" s="9">
         <v>12</v>
       </c>
       <c r="G1407" s="8">
-        <v>0</v>
+        <v>14236044795.83</v>
       </c>
     </row>
     <row r="1408" spans="1:7" x14ac:dyDescent="0.25">
@@ -45057,17 +45057,17 @@
       <c r="C1409" s="6">
         <v>46258</v>
       </c>
-      <c r="D1409" s="8">
-        <v>0</v>
+      <c r="D1409" s="10">
+        <v>2.33758</v>
       </c>
       <c r="E1409" s="8">
-        <v>0</v>
+        <v>5452599548</v>
       </c>
       <c r="F1409" s="9">
         <v>14</v>
       </c>
       <c r="G1409" s="8">
-        <v>0</v>
+        <v>12745887149.25</v>
       </c>
     </row>
     <row r="1410" spans="1:7" x14ac:dyDescent="0.25">
@@ -45080,17 +45080,17 @@
       <c r="C1410" s="6">
         <v>46258</v>
       </c>
-      <c r="D1410" s="8">
-        <v>0</v>
+      <c r="D1410" s="7">
+        <v>4.058165</v>
       </c>
       <c r="E1410" s="8">
-        <v>0</v>
+        <v>8715674112</v>
       </c>
       <c r="F1410" s="9">
         <v>123216</v>
       </c>
       <c r="G1410" s="8">
-        <v>0</v>
+        <v>35369642712.51</v>
       </c>
     </row>
     <row r="1411" spans="1:7" x14ac:dyDescent="0.25">
@@ -45172,17 +45172,17 @@
       <c r="C1414" s="6">
         <v>46258</v>
       </c>
-      <c r="D1414" s="8">
-        <v>0</v>
+      <c r="D1414" s="7">
+        <v>1059.356879</v>
       </c>
       <c r="E1414" s="8">
-        <v>0</v>
+        <v>9465870</v>
       </c>
       <c r="F1414" s="9">
         <v>17</v>
       </c>
       <c r="G1414" s="8">
-        <v>0</v>
+        <v>10027734504.32</v>
       </c>
     </row>
     <row r="1415" spans="1:7" x14ac:dyDescent="0.25">
@@ -45265,7 +45265,7 @@
         <v>46258</v>
       </c>
       <c r="D1418" s="7">
-        <v>3.990294</v>
+        <v>3.993119</v>
       </c>
       <c r="E1418" s="8">
         <v>123057961</v>
@@ -45274,7 +45274,7 @@
         <v>8096</v>
       </c>
       <c r="G1418" s="8">
-        <v>491037425.95</v>
+        <v>491385063.8</v>
       </c>
     </row>
     <row r="1419" spans="1:7" x14ac:dyDescent="0.25">
@@ -45425,17 +45425,17 @@
       <c r="C1425" s="6">
         <v>46258</v>
       </c>
-      <c r="D1425" s="8">
-        <v>0</v>
+      <c r="D1425" s="7">
+        <v>0.988042</v>
       </c>
       <c r="E1425" s="8">
-        <v>0</v>
+        <v>27391409</v>
       </c>
       <c r="F1425" s="9">
         <v>131</v>
       </c>
       <c r="G1425" s="8">
-        <v>0</v>
+        <v>27063872.21</v>
       </c>
     </row>
     <row r="1426" spans="1:7" x14ac:dyDescent="0.25">
@@ -45494,17 +45494,17 @@
       <c r="C1428" s="6">
         <v>46258</v>
       </c>
-      <c r="D1428" s="8">
-        <v>0</v>
+      <c r="D1428" s="7">
+        <v>2.501757</v>
       </c>
       <c r="E1428" s="8">
-        <v>0</v>
+        <v>1355278480</v>
       </c>
       <c r="F1428" s="9">
         <v>13</v>
       </c>
       <c r="G1428" s="8">
-        <v>0</v>
+        <v>3390577143.52</v>
       </c>
     </row>
     <row r="1429" spans="1:7" x14ac:dyDescent="0.25">
@@ -45517,17 +45517,17 @@
       <c r="C1429" s="6">
         <v>46258</v>
       </c>
-      <c r="D1429" s="8">
-        <v>0</v>
+      <c r="D1429" s="7">
+        <v>1.072612</v>
       </c>
       <c r="E1429" s="8">
-        <v>0</v>
+        <v>457773766</v>
       </c>
       <c r="F1429" s="9">
         <v>536</v>
       </c>
       <c r="G1429" s="8">
-        <v>0</v>
+        <v>491013855.45</v>
       </c>
     </row>
     <row r="1430" spans="1:7" x14ac:dyDescent="0.25">
@@ -45678,17 +45678,17 @@
       <c r="C1436" s="6">
         <v>46258</v>
       </c>
-      <c r="D1436" s="8">
-        <v>0</v>
+      <c r="D1436" s="7">
+        <v>16.077005</v>
       </c>
       <c r="E1436" s="8">
-        <v>0</v>
+        <v>4069112830</v>
       </c>
       <c r="F1436" s="9">
         <v>16</v>
       </c>
       <c r="G1436" s="8">
-        <v>0</v>
+        <v>65419147224.74</v>
       </c>
     </row>
     <row r="1437" spans="1:7" x14ac:dyDescent="0.25">
@@ -45701,17 +45701,17 @@
       <c r="C1437" s="6">
         <v>46258</v>
       </c>
-      <c r="D1437" s="8">
-        <v>0</v>
+      <c r="D1437" s="7">
+        <v>1.274124</v>
       </c>
       <c r="E1437" s="8">
-        <v>0</v>
+        <v>628268</v>
       </c>
       <c r="F1437" s="9">
         <v>118</v>
       </c>
       <c r="G1437" s="8">
-        <v>0</v>
+        <v>800491.17</v>
       </c>
     </row>
     <row r="1438" spans="1:7" x14ac:dyDescent="0.25">
@@ -45839,17 +45839,17 @@
       <c r="C1443" s="6">
         <v>46258</v>
       </c>
-      <c r="D1443" s="8">
-        <v>0</v>
+      <c r="D1443" s="7">
+        <v>1.239854</v>
       </c>
       <c r="E1443" s="8">
-        <v>0</v>
+        <v>29233310738</v>
       </c>
       <c r="F1443" s="9">
         <v>24220</v>
       </c>
       <c r="G1443" s="8">
-        <v>0</v>
+        <v>36245051207</v>
       </c>
     </row>
     <row r="1444" spans="1:7" x14ac:dyDescent="0.25">
@@ -46667,17 +46667,17 @@
       <c r="C1479" s="6">
         <v>46258</v>
       </c>
-      <c r="D1479" s="8">
-        <v>0</v>
+      <c r="D1479" s="10">
+        <v>3.18259</v>
       </c>
       <c r="E1479" s="8">
-        <v>0</v>
+        <v>35118450838</v>
       </c>
       <c r="F1479" s="9">
         <v>54288</v>
       </c>
       <c r="G1479" s="8">
-        <v>0</v>
+        <v>111767632795.37</v>
       </c>
     </row>
     <row r="1480" spans="1:7" x14ac:dyDescent="0.25">
@@ -47173,17 +47173,17 @@
       <c r="C1501" s="6">
         <v>46258</v>
       </c>
-      <c r="D1501" s="8">
-        <v>0</v>
+      <c r="D1501" s="7">
+        <v>1.275405</v>
       </c>
       <c r="E1501" s="8">
-        <v>0</v>
+        <v>972225810</v>
       </c>
       <c r="F1501" s="9">
         <v>8550</v>
       </c>
       <c r="G1501" s="8">
-        <v>0</v>
+        <v>1239981941.93</v>
       </c>
     </row>
     <row r="1502" spans="1:7" x14ac:dyDescent="0.25">
@@ -48048,7 +48048,7 @@
         <v>46258</v>
       </c>
       <c r="D1539" s="7">
-        <v>22.414828</v>
+        <v>22.407642</v>
       </c>
       <c r="E1539" s="8">
         <v>42798417</v>
@@ -48057,7 +48057,7 @@
         <v>11</v>
       </c>
       <c r="G1539" s="8">
-        <v>959319155.61</v>
+        <v>959011596.12</v>
       </c>
     </row>
     <row r="1540" spans="1:7" x14ac:dyDescent="0.25">
@@ -48186,7 +48186,7 @@
         <v>46258</v>
       </c>
       <c r="D1545" s="7">
-        <v>1.132699</v>
+        <v>1.133623</v>
       </c>
       <c r="E1545" s="8">
         <v>23389132</v>
@@ -48195,7 +48195,7 @@
         <v>401</v>
       </c>
       <c r="G1545" s="8">
-        <v>26492840.37</v>
+        <v>26514460.98</v>
       </c>
     </row>
     <row r="1546" spans="1:7" x14ac:dyDescent="0.25">
@@ -49404,17 +49404,17 @@
       <c r="C1598" s="6">
         <v>46258</v>
       </c>
-      <c r="D1598" s="8">
-        <v>0</v>
+      <c r="D1598" s="7">
+        <v>1.261418</v>
       </c>
       <c r="E1598" s="8">
-        <v>0</v>
+        <v>300626629</v>
       </c>
       <c r="F1598" s="9">
         <v>1</v>
       </c>
       <c r="G1598" s="8">
-        <v>0</v>
+        <v>379215709.45</v>
       </c>
     </row>
     <row r="1599" spans="1:7" x14ac:dyDescent="0.25">
@@ -49634,17 +49634,17 @@
       <c r="C1608" s="6">
         <v>46258</v>
       </c>
-      <c r="D1608" s="8">
-        <v>0</v>
+      <c r="D1608" s="7">
+        <v>1.875832</v>
       </c>
       <c r="E1608" s="8">
-        <v>0</v>
+        <v>229161609</v>
       </c>
       <c r="F1608" s="9">
         <v>784</v>
       </c>
       <c r="G1608" s="8">
-        <v>0</v>
+        <v>429868620.26</v>
       </c>
     </row>
     <row r="1609" spans="1:7" x14ac:dyDescent="0.25">
@@ -49749,17 +49749,17 @@
       <c r="C1613" s="6">
         <v>46258</v>
       </c>
-      <c r="D1613" s="8">
-        <v>0</v>
+      <c r="D1613" s="7">
+        <v>1.042366</v>
       </c>
       <c r="E1613" s="8">
-        <v>0</v>
+        <v>40283215</v>
       </c>
       <c r="F1613" s="9">
         <v>193</v>
       </c>
       <c r="G1613" s="8">
-        <v>0</v>
+        <v>41989868.97</v>
       </c>
     </row>
     <row r="1614" spans="1:7" x14ac:dyDescent="0.25">
@@ -49864,8 +49864,8 @@
       <c r="C1618" s="6">
         <v>46258</v>
       </c>
-      <c r="D1618" s="10">
-        <v>1.41124</v>
+      <c r="D1618" s="7">
+        <v>1.423472</v>
       </c>
       <c r="E1618" s="8">
         <v>22214442</v>
@@ -49874,7 +49874,7 @@
         <v>77</v>
       </c>
       <c r="G1618" s="8">
-        <v>31349910.15</v>
+        <v>31621643.05</v>
       </c>
     </row>
     <row r="1619" spans="1:7" x14ac:dyDescent="0.25">
@@ -49888,7 +49888,7 @@
         <v>46258</v>
       </c>
       <c r="D1619" s="7">
-        <v>1.034581</v>
+        <v>1.002888</v>
       </c>
       <c r="E1619" s="8">
         <v>200402645</v>
@@ -49897,7 +49897,7 @@
         <v>47</v>
       </c>
       <c r="G1619" s="8">
-        <v>207332712.99</v>
+        <v>200981446.33</v>
       </c>
     </row>
     <row r="1620" spans="1:7" x14ac:dyDescent="0.25">
@@ -49910,17 +49910,17 @@
       <c r="C1620" s="6">
         <v>46258</v>
       </c>
-      <c r="D1620" s="8">
-        <v>0</v>
+      <c r="D1620" s="7">
+        <v>1.927576</v>
       </c>
       <c r="E1620" s="8">
-        <v>0</v>
+        <v>106854310</v>
       </c>
       <c r="F1620" s="9">
         <v>2643</v>
       </c>
       <c r="G1620" s="8">
-        <v>0</v>
+        <v>205969783.65</v>
       </c>
     </row>
     <row r="1621" spans="1:7" x14ac:dyDescent="0.25">
@@ -49956,17 +49956,17 @@
       <c r="C1622" s="6">
         <v>46258</v>
       </c>
-      <c r="D1622" s="8">
-        <v>0</v>
+      <c r="D1622" s="7">
+        <v>3.605157</v>
       </c>
       <c r="E1622" s="8">
-        <v>0</v>
+        <v>16548302</v>
       </c>
       <c r="F1622" s="9">
         <v>643</v>
       </c>
       <c r="G1622" s="8">
-        <v>0</v>
+        <v>59659223.74</v>
       </c>
     </row>
     <row r="1623" spans="1:7" x14ac:dyDescent="0.25">
@@ -50002,17 +50002,17 @@
       <c r="C1624" s="6">
         <v>46258</v>
       </c>
-      <c r="D1624" s="8">
-        <v>0</v>
+      <c r="D1624" s="10">
+        <v>1.43608</v>
       </c>
       <c r="E1624" s="8">
-        <v>0</v>
+        <v>247082756</v>
       </c>
       <c r="F1624" s="9">
         <v>31</v>
       </c>
       <c r="G1624" s="8">
-        <v>0</v>
+        <v>354830591.45</v>
       </c>
     </row>
     <row r="1625" spans="1:7" x14ac:dyDescent="0.25">
@@ -50025,17 +50025,17 @@
       <c r="C1625" s="6">
         <v>46258</v>
       </c>
-      <c r="D1625" s="8">
-        <v>0</v>
+      <c r="D1625" s="7">
+        <v>0.960766</v>
       </c>
       <c r="E1625" s="8">
-        <v>0</v>
+        <v>924536</v>
       </c>
       <c r="F1625" s="9">
         <v>11</v>
       </c>
       <c r="G1625" s="8">
-        <v>0</v>
+        <v>888262.32</v>
       </c>
     </row>
     <row r="1626" spans="1:7" x14ac:dyDescent="0.25">
@@ -50048,17 +50048,17 @@
       <c r="C1626" s="6">
         <v>46258</v>
       </c>
-      <c r="D1626" s="8">
-        <v>0</v>
+      <c r="D1626" s="10">
+        <v>0.28794</v>
       </c>
       <c r="E1626" s="8">
-        <v>0</v>
+        <v>194986093</v>
       </c>
       <c r="F1626" s="9">
         <v>12</v>
       </c>
       <c r="G1626" s="8">
-        <v>0</v>
+        <v>56144220.13</v>
       </c>
     </row>
     <row r="1627" spans="1:7" x14ac:dyDescent="0.25">
@@ -50347,17 +50347,17 @@
       <c r="C1639" s="6">
         <v>46258</v>
       </c>
-      <c r="D1639" s="8">
-        <v>0</v>
+      <c r="D1639" s="7">
+        <v>1.720697</v>
       </c>
       <c r="E1639" s="8">
-        <v>0</v>
+        <v>13785826</v>
       </c>
       <c r="F1639" s="9">
         <v>323</v>
       </c>
       <c r="G1639" s="8">
-        <v>0</v>
+        <v>23721234.23</v>
       </c>
     </row>
     <row r="1640" spans="1:7" x14ac:dyDescent="0.25">
@@ -50508,17 +50508,17 @@
       <c r="C1646" s="6">
         <v>46258</v>
       </c>
-      <c r="D1646" s="7">
-        <v>2.196631</v>
+      <c r="D1646" s="10">
+        <v>2.21376</v>
       </c>
       <c r="E1646" s="8">
-        <v>43275645</v>
+        <v>43292339</v>
       </c>
       <c r="F1646" s="9">
         <v>802</v>
       </c>
       <c r="G1646" s="8">
-        <v>95060631.61</v>
+        <v>95838833.23</v>
       </c>
     </row>
     <row r="1647" spans="1:7" x14ac:dyDescent="0.25">
@@ -50693,7 +50693,7 @@
         <v>46258</v>
       </c>
       <c r="D1654" s="7">
-        <v>1.783265</v>
+        <v>1.783345</v>
       </c>
       <c r="E1654" s="8">
         <v>27973985</v>
@@ -50702,7 +50702,7 @@
         <v>582</v>
       </c>
       <c r="G1654" s="8">
-        <v>49885030.18</v>
+        <v>49887274.89</v>
       </c>
     </row>
     <row r="1655" spans="1:7" x14ac:dyDescent="0.25">
@@ -50830,8 +50830,8 @@
       <c r="C1660" s="6">
         <v>46258</v>
       </c>
-      <c r="D1660" s="7">
-        <v>1.282158</v>
+      <c r="D1660" s="10">
+        <v>1.28313</v>
       </c>
       <c r="E1660" s="8">
         <v>144493010</v>
@@ -50840,7 +50840,7 @@
         <v>70</v>
       </c>
       <c r="G1660" s="8">
-        <v>185262822.41</v>
+        <v>185403270.07</v>
       </c>
     </row>
     <row r="1661" spans="1:7" x14ac:dyDescent="0.25">
@@ -51221,17 +51221,17 @@
       <c r="C1677" s="6">
         <v>46258</v>
       </c>
-      <c r="D1677" s="8">
-        <v>0</v>
+      <c r="D1677" s="7">
+        <v>21.149373</v>
       </c>
       <c r="E1677" s="8">
-        <v>0</v>
+        <v>52856435</v>
       </c>
       <c r="F1677" s="9">
         <v>1</v>
       </c>
       <c r="G1677" s="8">
-        <v>0</v>
+        <v>1117880475.66</v>
       </c>
     </row>
     <row r="1678" spans="1:7" x14ac:dyDescent="0.25">
@@ -51313,17 +51313,17 @@
       <c r="C1681" s="6">
         <v>46258</v>
       </c>
-      <c r="D1681" s="8">
-        <v>0</v>
+      <c r="D1681" s="7">
+        <v>53.365127</v>
       </c>
       <c r="E1681" s="8">
-        <v>0</v>
+        <v>755447903</v>
       </c>
       <c r="F1681" s="9">
         <v>10705</v>
       </c>
       <c r="G1681" s="8">
-        <v>0</v>
+        <v>40314572907.79</v>
       </c>
     </row>
     <row r="1682" spans="1:7" x14ac:dyDescent="0.25">
@@ -51337,7 +51337,7 @@
         <v>46258</v>
       </c>
       <c r="D1682" s="7">
-        <v>0.281012</v>
+        <v>0.281676</v>
       </c>
       <c r="E1682" s="8">
         <v>1658549609</v>
@@ -51346,7 +51346,7 @@
         <v>198</v>
       </c>
       <c r="G1682" s="8">
-        <v>466071614.46</v>
+        <v>467174001.47</v>
       </c>
     </row>
     <row r="1683" spans="1:7" x14ac:dyDescent="0.25">
@@ -51497,17 +51497,17 @@
       <c r="C1689" s="6">
         <v>46258</v>
       </c>
-      <c r="D1689" s="8">
-        <v>0</v>
+      <c r="D1689" s="7">
+        <v>4.564288</v>
       </c>
       <c r="E1689" s="8">
-        <v>0</v>
+        <v>723761913</v>
       </c>
       <c r="F1689" s="9">
         <v>2774</v>
       </c>
       <c r="G1689" s="8">
-        <v>0</v>
+        <v>3303458085.76</v>
       </c>
     </row>
     <row r="1690" spans="1:7" x14ac:dyDescent="0.25">
@@ -51520,17 +51520,17 @@
       <c r="C1690" s="6">
         <v>46258</v>
       </c>
-      <c r="D1690" s="8">
-        <v>0</v>
+      <c r="D1690" s="7">
+        <v>1.337956</v>
       </c>
       <c r="E1690" s="8">
-        <v>0</v>
+        <v>141657132</v>
       </c>
       <c r="F1690" s="9">
         <v>1</v>
       </c>
       <c r="G1690" s="8">
-        <v>0</v>
+        <v>189531026.44</v>
       </c>
     </row>
     <row r="1691" spans="1:7" x14ac:dyDescent="0.25">
@@ -51635,17 +51635,17 @@
       <c r="C1695" s="6">
         <v>46258</v>
       </c>
-      <c r="D1695" s="8">
-        <v>0</v>
+      <c r="D1695" s="7">
+        <v>59.881286</v>
       </c>
       <c r="E1695" s="8">
-        <v>0</v>
+        <v>5459727</v>
       </c>
       <c r="F1695" s="9">
         <v>44</v>
       </c>
       <c r="G1695" s="8">
-        <v>0</v>
+        <v>326935475</v>
       </c>
     </row>
     <row r="1696" spans="1:7" x14ac:dyDescent="0.25">
@@ -51658,17 +51658,17 @@
       <c r="C1696" s="6">
         <v>46258</v>
       </c>
-      <c r="D1696" s="8">
-        <v>0</v>
+      <c r="D1696" s="7">
+        <v>41.297721</v>
       </c>
       <c r="E1696" s="8">
-        <v>0</v>
+        <v>27808316</v>
       </c>
       <c r="F1696" s="9">
         <v>2870</v>
       </c>
       <c r="G1696" s="8">
-        <v>0</v>
+        <v>1148420074</v>
       </c>
     </row>
     <row r="1697" spans="1:7" x14ac:dyDescent="0.25">
@@ -51681,17 +51681,17 @@
       <c r="C1697" s="6">
         <v>46258</v>
       </c>
-      <c r="D1697" s="8">
-        <v>0</v>
+      <c r="D1697" s="7">
+        <v>6.566208</v>
       </c>
       <c r="E1697" s="8">
-        <v>0</v>
+        <v>265835527</v>
       </c>
       <c r="F1697" s="9">
         <v>1437</v>
       </c>
       <c r="G1697" s="8">
-        <v>0</v>
+        <v>1745531321.75</v>
       </c>
     </row>
     <row r="1698" spans="1:7" x14ac:dyDescent="0.25">
@@ -51705,7 +51705,7 @@
         <v>46258</v>
       </c>
       <c r="D1698" s="7">
-        <v>2.752144</v>
+        <v>2.752406</v>
       </c>
       <c r="E1698" s="8">
         <v>267733782</v>
@@ -51714,7 +51714,7 @@
         <v>1349</v>
       </c>
       <c r="G1698" s="8">
-        <v>736841824.37</v>
+        <v>736912186.35</v>
       </c>
     </row>
     <row r="1699" spans="1:7" x14ac:dyDescent="0.25">
@@ -51750,17 +51750,17 @@
       <c r="C1700" s="6">
         <v>46258</v>
       </c>
-      <c r="D1700" s="8">
-        <v>0</v>
+      <c r="D1700" s="10">
+        <v>42.98361</v>
       </c>
       <c r="E1700" s="8">
-        <v>0</v>
+        <v>31135008</v>
       </c>
       <c r="F1700" s="9">
         <v>9006</v>
       </c>
       <c r="G1700" s="8">
-        <v>0</v>
+        <v>1338295054.56</v>
       </c>
     </row>
     <row r="1701" spans="1:7" x14ac:dyDescent="0.25">
@@ -52118,17 +52118,17 @@
       <c r="C1716" s="6">
         <v>46258</v>
       </c>
-      <c r="D1716" s="8">
-        <v>0</v>
+      <c r="D1716" s="7">
+        <v>50.007432</v>
       </c>
       <c r="E1716" s="8">
-        <v>0</v>
+        <v>45101206</v>
       </c>
       <c r="F1716" s="9">
         <v>17</v>
       </c>
       <c r="G1716" s="8">
-        <v>0</v>
+        <v>2255395491.76</v>
       </c>
     </row>
     <row r="1717" spans="1:7" x14ac:dyDescent="0.25">
@@ -52325,17 +52325,17 @@
       <c r="C1725" s="6">
         <v>46258</v>
       </c>
-      <c r="D1725" s="8">
-        <v>0</v>
+      <c r="D1725" s="7">
+        <v>49.938351</v>
       </c>
       <c r="E1725" s="8">
-        <v>0</v>
+        <v>15067521</v>
       </c>
       <c r="F1725" s="9">
         <v>66</v>
       </c>
       <c r="G1725" s="8">
-        <v>0</v>
+        <v>752447153.51</v>
       </c>
     </row>
     <row r="1726" spans="1:7" x14ac:dyDescent="0.25">
@@ -52394,17 +52394,17 @@
       <c r="C1728" s="6">
         <v>46258</v>
       </c>
-      <c r="D1728" s="8">
-        <v>0</v>
+      <c r="D1728" s="7">
+        <v>5.355472</v>
       </c>
       <c r="E1728" s="8">
-        <v>0</v>
+        <v>10149573</v>
       </c>
       <c r="F1728" s="9">
         <v>543</v>
       </c>
       <c r="G1728" s="8">
-        <v>0</v>
+        <v>54355749.41</v>
       </c>
     </row>
     <row r="1729" spans="1:7" x14ac:dyDescent="0.25">
@@ -52417,17 +52417,17 @@
       <c r="C1729" s="6">
         <v>46258</v>
       </c>
-      <c r="D1729" s="8">
-        <v>0</v>
+      <c r="D1729" s="7">
+        <v>6.562911</v>
       </c>
       <c r="E1729" s="8">
-        <v>0</v>
+        <v>91845905</v>
       </c>
       <c r="F1729" s="9">
         <v>913</v>
       </c>
       <c r="G1729" s="8">
-        <v>0</v>
+        <v>602776485.47</v>
       </c>
     </row>
     <row r="1730" spans="1:7" x14ac:dyDescent="0.25">
@@ -52463,17 +52463,17 @@
       <c r="C1731" s="6">
         <v>46258</v>
       </c>
-      <c r="D1731" s="8">
-        <v>0</v>
+      <c r="D1731" s="7">
+        <v>68.881698</v>
       </c>
       <c r="E1731" s="8">
-        <v>0</v>
+        <v>33140278</v>
       </c>
       <c r="F1731" s="9">
         <v>1844</v>
       </c>
       <c r="G1731" s="8">
-        <v>0</v>
+        <v>2282758609.98</v>
       </c>
     </row>
     <row r="1732" spans="1:7" x14ac:dyDescent="0.25">
@@ -52533,7 +52533,7 @@
         <v>46258</v>
       </c>
       <c r="D1734" s="7">
-        <v>1.762815</v>
+        <v>1.770352</v>
       </c>
       <c r="E1734" s="8">
         <v>1024042350</v>
@@ -52542,7 +52542,7 @@
         <v>113073</v>
       </c>
       <c r="G1734" s="8">
-        <v>1805197557.15</v>
+        <v>1812915581.32</v>
       </c>
     </row>
     <row r="1735" spans="1:7" x14ac:dyDescent="0.25">
@@ -52579,7 +52579,7 @@
         <v>46258</v>
       </c>
       <c r="D1736" s="7">
-        <v>1.056965</v>
+        <v>1.057158</v>
       </c>
       <c r="E1736" s="8">
         <v>318183272</v>
@@ -52588,7 +52588,7 @@
         <v>264</v>
       </c>
       <c r="G1736" s="8">
-        <v>336308583.22</v>
+        <v>336369888.19</v>
       </c>
     </row>
     <row r="1737" spans="1:7" x14ac:dyDescent="0.25">
@@ -52670,17 +52670,17 @@
       <c r="C1740" s="6">
         <v>46258</v>
       </c>
-      <c r="D1740" s="8">
-        <v>0</v>
+      <c r="D1740" s="7">
+        <v>71.094552</v>
       </c>
       <c r="E1740" s="8">
-        <v>0</v>
+        <v>5663669</v>
       </c>
       <c r="F1740" s="9">
         <v>1</v>
       </c>
       <c r="G1740" s="8">
-        <v>0</v>
+        <v>402656012.21</v>
       </c>
     </row>
     <row r="1741" spans="1:7" x14ac:dyDescent="0.25">
@@ -52693,17 +52693,17 @@
       <c r="C1741" s="6">
         <v>46258</v>
       </c>
-      <c r="D1741" s="8">
-        <v>0</v>
+      <c r="D1741" s="7">
+        <v>53.543429</v>
       </c>
       <c r="E1741" s="8">
-        <v>0</v>
+        <v>166311216</v>
       </c>
       <c r="F1741" s="9">
         <v>518</v>
       </c>
       <c r="G1741" s="8">
-        <v>0</v>
+        <v>8904872865.69</v>
       </c>
     </row>
     <row r="1742" spans="1:7" x14ac:dyDescent="0.25">
@@ -52717,7 +52717,7 @@
         <v>46258</v>
       </c>
       <c r="D1742" s="7">
-        <v>1.369437</v>
+        <v>1.369435</v>
       </c>
       <c r="E1742" s="8">
         <v>2917723624</v>
@@ -52726,7 +52726,7 @@
         <v>10487</v>
       </c>
       <c r="G1742" s="8">
-        <v>3995637688.62</v>
+        <v>3995632638.2</v>
       </c>
     </row>
     <row r="1743" spans="1:7" x14ac:dyDescent="0.25">
@@ -52763,7 +52763,7 @@
         <v>46258</v>
       </c>
       <c r="D1744" s="7">
-        <v>20.292565</v>
+        <v>20.292556</v>
       </c>
       <c r="E1744" s="8">
         <v>3709778</v>
@@ -52772,7 +52772,7 @@
         <v>869</v>
       </c>
       <c r="G1744" s="8">
-        <v>75280910.58</v>
+        <v>75280879.06</v>
       </c>
     </row>
     <row r="1745" spans="1:7" x14ac:dyDescent="0.25">
@@ -52877,17 +52877,17 @@
       <c r="C1749" s="6">
         <v>46258</v>
       </c>
-      <c r="D1749" s="8">
-        <v>0</v>
+      <c r="D1749" s="7">
+        <v>7.712278</v>
       </c>
       <c r="E1749" s="8">
-        <v>0</v>
+        <v>1200475000</v>
       </c>
       <c r="F1749" s="9">
         <v>1</v>
       </c>
       <c r="G1749" s="8">
-        <v>0</v>
+        <v>9258396924</v>
       </c>
     </row>
     <row r="1750" spans="1:7" x14ac:dyDescent="0.25">
@@ -52910,7 +52910,7 @@
         <v>85</v>
       </c>
       <c r="G1750" s="8">
-        <v>408522781.07</v>
+        <v>408522781.05</v>
       </c>
     </row>
     <row r="1751" spans="1:7" x14ac:dyDescent="0.25">
@@ -52924,7 +52924,7 @@
         <v>46258</v>
       </c>
       <c r="D1751" s="7">
-        <v>1.426229</v>
+        <v>1.432037</v>
       </c>
       <c r="E1751" s="8">
         <v>41251542</v>
@@ -52933,7 +52933,7 @@
         <v>92</v>
       </c>
       <c r="G1751" s="8">
-        <v>58834151.81</v>
+        <v>59073741.69</v>
       </c>
     </row>
     <row r="1752" spans="1:7" x14ac:dyDescent="0.25">
@@ -52970,7 +52970,7 @@
         <v>46258</v>
       </c>
       <c r="D1753" s="7">
-        <v>1.985252</v>
+        <v>1.992298</v>
       </c>
       <c r="E1753" s="8">
         <v>25967299</v>
@@ -52979,7 +52979,7 @@
         <v>2551</v>
       </c>
       <c r="G1753" s="8">
-        <v>51551626.92</v>
+        <v>51734590.76</v>
       </c>
     </row>
     <row r="1754" spans="1:7" x14ac:dyDescent="0.25">
@@ -52992,17 +52992,17 @@
       <c r="C1754" s="6">
         <v>46258</v>
       </c>
-      <c r="D1754" s="8">
-        <v>0</v>
+      <c r="D1754" s="7">
+        <v>50.212177</v>
       </c>
       <c r="E1754" s="8">
-        <v>0</v>
+        <v>14230233</v>
       </c>
       <c r="F1754" s="9">
         <v>82</v>
       </c>
       <c r="G1754" s="8">
-        <v>0</v>
+        <v>714530971.12</v>
       </c>
     </row>
     <row r="1755" spans="1:7" x14ac:dyDescent="0.25">
@@ -53038,17 +53038,17 @@
       <c r="C1756" s="6">
         <v>46258</v>
       </c>
-      <c r="D1756" s="8">
-        <v>0</v>
+      <c r="D1756" s="7">
+        <v>4.267324</v>
       </c>
       <c r="E1756" s="8">
-        <v>0</v>
+        <v>1216123947</v>
       </c>
       <c r="F1756" s="9">
         <v>3</v>
       </c>
       <c r="G1756" s="8">
-        <v>0</v>
+        <v>5189595140.18</v>
       </c>
     </row>
     <row r="1757" spans="1:7" x14ac:dyDescent="0.25">
@@ -53084,17 +53084,17 @@
       <c r="C1758" s="6">
         <v>46258</v>
       </c>
-      <c r="D1758" s="8">
-        <v>0</v>
+      <c r="D1758" s="10">
+        <v>11.38232</v>
       </c>
       <c r="E1758" s="8">
-        <v>0</v>
+        <v>672077275</v>
       </c>
       <c r="F1758" s="9">
         <v>2604</v>
       </c>
       <c r="G1758" s="8">
-        <v>0</v>
+        <v>7649798590.28</v>
       </c>
     </row>
     <row r="1759" spans="1:7" x14ac:dyDescent="0.25">
@@ -53153,17 +53153,17 @@
       <c r="C1761" s="6">
         <v>46258</v>
       </c>
-      <c r="D1761" s="8">
-        <v>0</v>
+      <c r="D1761" s="7">
+        <v>57.144527</v>
       </c>
       <c r="E1761" s="8">
-        <v>0</v>
+        <v>12799131</v>
       </c>
       <c r="F1761" s="9">
         <v>101</v>
       </c>
       <c r="G1761" s="8">
-        <v>0</v>
+        <v>731400288.34</v>
       </c>
     </row>
     <row r="1762" spans="1:7" x14ac:dyDescent="0.25">
@@ -53176,17 +53176,17 @@
       <c r="C1762" s="6">
         <v>46258</v>
       </c>
-      <c r="D1762" s="8">
-        <v>0</v>
+      <c r="D1762" s="7">
+        <v>59.657216</v>
       </c>
       <c r="E1762" s="8">
-        <v>0</v>
+        <v>418063786</v>
       </c>
       <c r="F1762" s="9">
         <v>6985</v>
       </c>
       <c r="G1762" s="8">
-        <v>0</v>
+        <v>24940521654.98</v>
       </c>
     </row>
     <row r="1763" spans="1:7" x14ac:dyDescent="0.25">
@@ -53222,17 +53222,17 @@
       <c r="C1764" s="6">
         <v>46258</v>
       </c>
-      <c r="D1764" s="8">
-        <v>0</v>
+      <c r="D1764" s="7">
+        <v>68.127872</v>
       </c>
       <c r="E1764" s="8">
-        <v>0</v>
+        <v>5611179</v>
       </c>
       <c r="F1764" s="9">
         <v>1</v>
       </c>
       <c r="G1764" s="8">
-        <v>0</v>
+        <v>382277683.87</v>
       </c>
     </row>
     <row r="1765" spans="1:7" x14ac:dyDescent="0.25">
@@ -53245,17 +53245,17 @@
       <c r="C1765" s="6">
         <v>46258</v>
       </c>
-      <c r="D1765" s="8">
-        <v>0</v>
+      <c r="D1765" s="7">
+        <v>2.178974</v>
       </c>
       <c r="E1765" s="8">
-        <v>0</v>
+        <v>94754772340</v>
       </c>
       <c r="F1765" s="9">
         <v>158280</v>
       </c>
       <c r="G1765" s="8">
-        <v>0</v>
+        <v>206468154538.22</v>
       </c>
     </row>
     <row r="1766" spans="1:7" x14ac:dyDescent="0.25">
@@ -53268,17 +53268,17 @@
       <c r="C1766" s="6">
         <v>46258</v>
       </c>
-      <c r="D1766" s="8">
-        <v>0</v>
+      <c r="D1766" s="7">
+        <v>13.769033</v>
       </c>
       <c r="E1766" s="8">
-        <v>0</v>
+        <v>454590186</v>
       </c>
       <c r="F1766" s="9">
         <v>12565</v>
       </c>
       <c r="G1766" s="8">
-        <v>0</v>
+        <v>6259267362.68</v>
       </c>
     </row>
     <row r="1767" spans="1:7" x14ac:dyDescent="0.25">
@@ -53337,17 +53337,17 @@
       <c r="C1769" s="6">
         <v>46258</v>
       </c>
-      <c r="D1769" s="8">
-        <v>0</v>
+      <c r="D1769" s="7">
+        <v>78.505216</v>
       </c>
       <c r="E1769" s="8">
-        <v>0</v>
+        <v>28800887</v>
       </c>
       <c r="F1769" s="9">
         <v>1463</v>
       </c>
       <c r="G1769" s="8">
-        <v>0</v>
+        <v>2261019866.29</v>
       </c>
     </row>
     <row r="1770" spans="1:7" x14ac:dyDescent="0.25">
@@ -53360,17 +53360,17 @@
       <c r="C1770" s="6">
         <v>46258</v>
       </c>
-      <c r="D1770" s="8">
-        <v>0</v>
+      <c r="D1770" s="10">
+        <v>21.19174</v>
       </c>
       <c r="E1770" s="8">
-        <v>0</v>
+        <v>23556292.01</v>
       </c>
       <c r="F1770" s="9">
         <v>1524</v>
       </c>
       <c r="G1770" s="8">
-        <v>0</v>
+        <v>499198824.36</v>
       </c>
     </row>
     <row r="1771" spans="1:7" x14ac:dyDescent="0.25">
@@ -53406,17 +53406,17 @@
       <c r="C1772" s="6">
         <v>46258</v>
       </c>
-      <c r="D1772" s="8">
-        <v>0</v>
+      <c r="D1772" s="7">
+        <v>79.359231</v>
       </c>
       <c r="E1772" s="8">
-        <v>0</v>
+        <v>23712000</v>
       </c>
       <c r="F1772" s="9">
         <v>386</v>
       </c>
       <c r="G1772" s="8">
-        <v>0</v>
+        <v>1881766090.34</v>
       </c>
     </row>
     <row r="1773" spans="1:7" x14ac:dyDescent="0.25">
@@ -53475,17 +53475,17 @@
       <c r="C1775" s="6">
         <v>46258</v>
       </c>
-      <c r="D1775" s="8">
-        <v>0</v>
+      <c r="D1775" s="7">
+        <v>28.488016</v>
       </c>
       <c r="E1775" s="8">
-        <v>0</v>
+        <v>4925625</v>
       </c>
       <c r="F1775" s="9">
         <v>1514</v>
       </c>
       <c r="G1775" s="8">
-        <v>0</v>
+        <v>140321285.69</v>
       </c>
     </row>
     <row r="1776" spans="1:7" x14ac:dyDescent="0.25">
@@ -53728,17 +53728,17 @@
       <c r="C1786" s="6">
         <v>46258</v>
       </c>
-      <c r="D1786" s="8">
-        <v>0</v>
+      <c r="D1786" s="7">
+        <v>51.498919</v>
       </c>
       <c r="E1786" s="8">
-        <v>0</v>
+        <v>17213905</v>
       </c>
       <c r="F1786" s="9">
         <v>105</v>
       </c>
       <c r="G1786" s="8">
-        <v>0</v>
+        <v>886497499.16</v>
       </c>
     </row>
     <row r="1787" spans="1:7" x14ac:dyDescent="0.25">
@@ -53751,17 +53751,17 @@
       <c r="C1787" s="6">
         <v>46258</v>
       </c>
-      <c r="D1787" s="8">
-        <v>0</v>
+      <c r="D1787" s="7">
+        <v>70.425042</v>
       </c>
       <c r="E1787" s="8">
-        <v>0</v>
+        <v>31086506</v>
       </c>
       <c r="F1787" s="9">
         <v>1</v>
       </c>
       <c r="G1787" s="8">
-        <v>0</v>
+        <v>2189268499.9</v>
       </c>
     </row>
     <row r="1788" spans="1:7" x14ac:dyDescent="0.25">
@@ -53821,7 +53821,7 @@
         <v>46258</v>
       </c>
       <c r="D1790" s="7">
-        <v>1.519827</v>
+        <v>1.520705</v>
       </c>
       <c r="E1790" s="8">
         <v>10491499893.21</v>
@@ -53830,7 +53830,7 @@
         <v>31535</v>
       </c>
       <c r="G1790" s="8">
-        <v>15945269600.24</v>
+        <v>15954479028.07</v>
       </c>
     </row>
     <row r="1791" spans="1:7" x14ac:dyDescent="0.25">
@@ -53847,7 +53847,7 @@
         <v>1.14858</v>
       </c>
       <c r="E1791" s="8">
-        <v>190240966</v>
+        <v>190240964</v>
       </c>
       <c r="F1791" s="9">
         <v>348</v>
@@ -53867,7 +53867,7 @@
         <v>46258</v>
       </c>
       <c r="D1792" s="7">
-        <v>2.955077</v>
+        <v>2.974548</v>
       </c>
       <c r="E1792" s="8">
         <v>3911562</v>
@@ -53876,7 +53876,7 @@
         <v>529</v>
       </c>
       <c r="G1792" s="8">
-        <v>11558965.85</v>
+        <v>11635128.14</v>
       </c>
     </row>
     <row r="1793" spans="1:7" x14ac:dyDescent="0.25">
@@ -54359,7 +54359,7 @@
         <v>256</v>
       </c>
       <c r="G1813" s="8">
-        <v>2475585291.71</v>
+        <v>2475585293.31</v>
       </c>
     </row>
     <row r="1814" spans="1:7" x14ac:dyDescent="0.25">
@@ -54442,7 +54442,7 @@
         <v>46258</v>
       </c>
       <c r="D1817" s="7">
-        <v>1.947039</v>
+        <v>1.950291</v>
       </c>
       <c r="E1817" s="8">
         <v>354535726</v>
@@ -54451,7 +54451,7 @@
         <v>9373</v>
       </c>
       <c r="G1817" s="8">
-        <v>690294940.95</v>
+        <v>691447871.51</v>
       </c>
     </row>
     <row r="1818" spans="1:7" x14ac:dyDescent="0.25">
@@ -54832,17 +54832,17 @@
       <c r="C1834" s="6">
         <v>46258</v>
       </c>
-      <c r="D1834" s="8">
-        <v>0</v>
+      <c r="D1834" s="7">
+        <v>1.049093</v>
       </c>
       <c r="E1834" s="8">
-        <v>0</v>
+        <v>183737420</v>
       </c>
       <c r="F1834" s="9">
         <v>4485</v>
       </c>
       <c r="G1834" s="8">
-        <v>0</v>
+        <v>192757576.53</v>
       </c>
     </row>
     <row r="1835" spans="1:7" x14ac:dyDescent="0.25">
@@ -55039,17 +55039,17 @@
       <c r="C1843" s="6">
         <v>46258</v>
       </c>
-      <c r="D1843" s="8">
-        <v>0</v>
+      <c r="D1843" s="7">
+        <v>2.791847</v>
       </c>
       <c r="E1843" s="8">
-        <v>0</v>
+        <v>2639601019</v>
       </c>
       <c r="F1843" s="9">
         <v>151</v>
       </c>
       <c r="G1843" s="8">
-        <v>0</v>
+        <v>7369363446.92</v>
       </c>
     </row>
     <row r="1844" spans="1:7" x14ac:dyDescent="0.25">
@@ -55062,17 +55062,17 @@
       <c r="C1844" s="6">
         <v>46258</v>
       </c>
-      <c r="D1844" s="8">
-        <v>0</v>
+      <c r="D1844" s="7">
+        <v>2.446152</v>
       </c>
       <c r="E1844" s="8">
-        <v>0</v>
+        <v>1598347444</v>
       </c>
       <c r="F1844" s="9">
         <v>244</v>
       </c>
       <c r="G1844" s="8">
-        <v>0</v>
+        <v>3909800092.23</v>
       </c>
     </row>
     <row r="1845" spans="1:7" x14ac:dyDescent="0.25">
@@ -55108,17 +55108,17 @@
       <c r="C1846" s="6">
         <v>46258</v>
       </c>
-      <c r="D1846" s="8">
-        <v>0</v>
+      <c r="D1846" s="7">
+        <v>53.930677</v>
       </c>
       <c r="E1846" s="8">
-        <v>0</v>
+        <v>28378082</v>
       </c>
       <c r="F1846" s="9">
         <v>564</v>
       </c>
       <c r="G1846" s="8">
-        <v>0</v>
+        <v>1530449188.41</v>
       </c>
     </row>
     <row r="1847" spans="1:7" x14ac:dyDescent="0.25">
@@ -55131,17 +55131,17 @@
       <c r="C1847" s="6">
         <v>46258</v>
       </c>
-      <c r="D1847" s="8">
-        <v>0</v>
+      <c r="D1847" s="7">
+        <v>0.902029</v>
       </c>
       <c r="E1847" s="8">
-        <v>0</v>
+        <v>1468794629</v>
       </c>
       <c r="F1847" s="9">
         <v>5994</v>
       </c>
       <c r="G1847" s="8">
-        <v>0</v>
+        <v>1324895020.52</v>
       </c>
     </row>
     <row r="1848" spans="1:7" x14ac:dyDescent="0.25">
@@ -55246,17 +55246,17 @@
       <c r="C1852" s="6">
         <v>46258</v>
       </c>
-      <c r="D1852" s="8">
-        <v>0</v>
+      <c r="D1852" s="7">
+        <v>14.848034</v>
       </c>
       <c r="E1852" s="8">
-        <v>0</v>
+        <v>372154793</v>
       </c>
       <c r="F1852" s="9">
         <v>9832</v>
       </c>
       <c r="G1852" s="8">
-        <v>0</v>
+        <v>5525767064.37</v>
       </c>
     </row>
     <row r="1853" spans="1:7" x14ac:dyDescent="0.25">
@@ -55315,17 +55315,17 @@
       <c r="C1855" s="6">
         <v>46258</v>
       </c>
-      <c r="D1855" s="8">
-        <v>0</v>
+      <c r="D1855" s="7">
+        <v>14.600076</v>
       </c>
       <c r="E1855" s="8">
-        <v>0</v>
+        <v>127442666</v>
       </c>
       <c r="F1855" s="9">
         <v>3580</v>
       </c>
       <c r="G1855" s="8">
-        <v>0</v>
+        <v>1860672604.24</v>
       </c>
     </row>
     <row r="1856" spans="1:7" x14ac:dyDescent="0.25">
@@ -55499,17 +55499,17 @@
       <c r="C1863" s="6">
         <v>46258</v>
       </c>
-      <c r="D1863" s="8">
-        <v>0</v>
+      <c r="D1863" s="7">
+        <v>55.668494</v>
       </c>
       <c r="E1863" s="8">
-        <v>0</v>
+        <v>111505977</v>
       </c>
       <c r="F1863" s="9">
         <v>2548</v>
       </c>
       <c r="G1863" s="8">
-        <v>0</v>
+        <v>6207369850.87</v>
       </c>
     </row>
     <row r="1864" spans="1:7" x14ac:dyDescent="0.25">
@@ -55568,17 +55568,17 @@
       <c r="C1866" s="6">
         <v>46258</v>
       </c>
-      <c r="D1866" s="8">
-        <v>0</v>
+      <c r="D1866" s="7">
+        <v>2.720813</v>
       </c>
       <c r="E1866" s="8">
-        <v>0</v>
+        <v>39969656</v>
       </c>
       <c r="F1866" s="9">
         <v>114</v>
       </c>
       <c r="G1866" s="8">
-        <v>0</v>
+        <v>108749973.39</v>
       </c>
     </row>
     <row r="1867" spans="1:7" x14ac:dyDescent="0.25">
@@ -55660,17 +55660,17 @@
       <c r="C1870" s="6">
         <v>46258</v>
       </c>
-      <c r="D1870" s="8">
-        <v>0</v>
+      <c r="D1870" s="7">
+        <v>4.120426</v>
       </c>
       <c r="E1870" s="8">
-        <v>0</v>
+        <v>65938891</v>
       </c>
       <c r="F1870" s="9">
         <v>273</v>
       </c>
       <c r="G1870" s="8">
-        <v>0</v>
+        <v>271696339.52</v>
       </c>
     </row>
     <row r="1871" spans="1:7" x14ac:dyDescent="0.25">
@@ -56143,17 +56143,17 @@
       <c r="C1891" s="6">
         <v>46258</v>
       </c>
-      <c r="D1891" s="8">
-        <v>0</v>
+      <c r="D1891" s="7">
+        <v>2.684422</v>
       </c>
       <c r="E1891" s="8">
-        <v>0</v>
+        <v>908838572</v>
       </c>
       <c r="F1891" s="9">
         <v>17150</v>
       </c>
       <c r="G1891" s="8">
-        <v>0</v>
+        <v>2439705954.49</v>
       </c>
     </row>
     <row r="1892" spans="1:7" x14ac:dyDescent="0.25">
@@ -56235,17 +56235,17 @@
       <c r="C1895" s="6">
         <v>46258</v>
       </c>
-      <c r="D1895" s="8">
-        <v>0</v>
+      <c r="D1895" s="10">
+        <v>5.73766</v>
       </c>
       <c r="E1895" s="8">
-        <v>0</v>
+        <v>182620070</v>
       </c>
       <c r="F1895" s="9">
         <v>14192</v>
       </c>
       <c r="G1895" s="8">
-        <v>0</v>
+        <v>1047811878.99</v>
       </c>
     </row>
     <row r="1896" spans="1:7" x14ac:dyDescent="0.25">
@@ -56580,17 +56580,17 @@
       <c r="C1910" s="6">
         <v>46258</v>
       </c>
-      <c r="D1910" s="8">
-        <v>0</v>
+      <c r="D1910" s="7">
+        <v>1.027624</v>
       </c>
       <c r="E1910" s="8">
-        <v>0</v>
+        <v>178767</v>
       </c>
       <c r="F1910" s="9">
         <v>78</v>
       </c>
       <c r="G1910" s="8">
-        <v>0</v>
+        <v>183705.21</v>
       </c>
     </row>
     <row r="1911" spans="1:7" x14ac:dyDescent="0.25">
@@ -57063,17 +57063,17 @@
       <c r="C1931" s="6">
         <v>46258</v>
       </c>
-      <c r="D1931" s="8">
-        <v>0</v>
+      <c r="D1931" s="7">
+        <v>8.013723</v>
       </c>
       <c r="E1931" s="8">
-        <v>0</v>
+        <v>701478544</v>
       </c>
       <c r="F1931" s="9">
         <v>3351</v>
       </c>
       <c r="G1931" s="8">
-        <v>0</v>
+        <v>5621454578.34</v>
       </c>
     </row>
     <row r="1932" spans="1:7" x14ac:dyDescent="0.25">
@@ -57224,17 +57224,17 @@
       <c r="C1938" s="6">
         <v>46258</v>
       </c>
-      <c r="D1938" s="8">
-        <v>0</v>
+      <c r="D1938" s="7">
+        <v>0.956351</v>
       </c>
       <c r="E1938" s="8">
-        <v>0</v>
+        <v>1833350612</v>
       </c>
       <c r="F1938" s="9">
         <v>14923</v>
       </c>
       <c r="G1938" s="8">
-        <v>0</v>
+        <v>1753326296.14</v>
       </c>
     </row>
     <row r="1939" spans="1:7" x14ac:dyDescent="0.25">
@@ -57684,17 +57684,17 @@
       <c r="C1958" s="6">
         <v>46258</v>
       </c>
-      <c r="D1958" s="8">
-        <v>0</v>
+      <c r="D1958" s="7">
+        <v>13.977146</v>
       </c>
       <c r="E1958" s="8">
-        <v>0</v>
+        <v>835759824</v>
       </c>
       <c r="F1958" s="9">
         <v>60951</v>
       </c>
       <c r="G1958" s="8">
-        <v>0</v>
+        <v>11681536889.36</v>
       </c>
     </row>
     <row r="1959" spans="1:7" x14ac:dyDescent="0.25">
@@ -57799,17 +57799,17 @@
       <c r="C1963" s="6">
         <v>46258</v>
       </c>
-      <c r="D1963" s="8">
-        <v>0</v>
+      <c r="D1963" s="7">
+        <v>2.056519</v>
       </c>
       <c r="E1963" s="8">
-        <v>0</v>
+        <v>1958858212</v>
       </c>
       <c r="F1963" s="9">
         <v>574</v>
       </c>
       <c r="G1963" s="8">
-        <v>0</v>
+        <v>4028429064.22</v>
       </c>
     </row>
     <row r="1964" spans="1:7" x14ac:dyDescent="0.25">
@@ -57822,17 +57822,17 @@
       <c r="C1964" s="6">
         <v>46258</v>
       </c>
-      <c r="D1964" s="8">
-        <v>0</v>
+      <c r="D1964" s="7">
+        <v>46.350139</v>
       </c>
       <c r="E1964" s="8">
-        <v>0</v>
+        <v>336212</v>
       </c>
       <c r="F1964" s="9">
         <v>48</v>
       </c>
       <c r="G1964" s="8">
-        <v>0</v>
+        <v>15583472.98</v>
       </c>
     </row>
     <row r="1965" spans="1:7" x14ac:dyDescent="0.25">
@@ -57868,17 +57868,17 @@
       <c r="C1966" s="6">
         <v>46258</v>
       </c>
-      <c r="D1966" s="8">
-        <v>0</v>
+      <c r="D1966" s="7">
+        <v>6.421992</v>
       </c>
       <c r="E1966" s="8">
-        <v>0</v>
+        <v>233149168</v>
       </c>
       <c r="F1966" s="9">
         <v>3319</v>
       </c>
       <c r="G1966" s="8">
-        <v>0</v>
+        <v>1497281991.23</v>
       </c>
     </row>
     <row r="1967" spans="1:7" x14ac:dyDescent="0.25">
@@ -58236,8 +58236,8 @@
       <c r="C1982" s="6">
         <v>46258</v>
       </c>
-      <c r="D1982" s="7">
-        <v>4.085715</v>
+      <c r="D1982" s="10">
+        <v>4.09932</v>
       </c>
       <c r="E1982" s="8">
         <v>144062700</v>
@@ -58246,7 +58246,7 @@
         <v>6562</v>
       </c>
       <c r="G1982" s="8">
-        <v>588599085.91</v>
+        <v>590559041.64</v>
       </c>
     </row>
     <row r="1983" spans="1:7" x14ac:dyDescent="0.25">
@@ -58627,17 +58627,17 @@
       <c r="C1999" s="6">
         <v>46258</v>
       </c>
-      <c r="D1999" s="8">
-        <v>0</v>
+      <c r="D1999" s="10">
+        <v>50.38671</v>
       </c>
       <c r="E1999" s="8">
-        <v>0</v>
+        <v>9467709</v>
       </c>
       <c r="F1999" s="9">
         <v>45</v>
       </c>
       <c r="G1999" s="8">
-        <v>0</v>
+        <v>477046704.4</v>
       </c>
     </row>
     <row r="2000" spans="1:7" x14ac:dyDescent="0.25">
@@ -58789,7 +58789,7 @@
         <v>46258</v>
       </c>
       <c r="D2006" s="7">
-        <v>1.908212</v>
+        <v>1.898861</v>
       </c>
       <c r="E2006" s="8">
         <v>306521428</v>
@@ -58798,7 +58798,7 @@
         <v>11</v>
       </c>
       <c r="G2006" s="8">
-        <v>584907823.99</v>
+        <v>582041669.48</v>
       </c>
     </row>
     <row r="2007" spans="1:7" x14ac:dyDescent="0.25">
@@ -58835,7 +58835,7 @@
         <v>46258</v>
       </c>
       <c r="D2008" s="7">
-        <v>5.795892</v>
+        <v>5.798118</v>
       </c>
       <c r="E2008" s="8">
         <v>106786382</v>
@@ -58844,7 +58844,7 @@
         <v>1</v>
       </c>
       <c r="G2008" s="8">
-        <v>618922352.73</v>
+        <v>619160082.34</v>
       </c>
     </row>
     <row r="2009" spans="1:7" x14ac:dyDescent="0.25">
@@ -58996,7 +58996,7 @@
         <v>46258</v>
       </c>
       <c r="D2015" s="7">
-        <v>19.662165</v>
+        <v>19.663427</v>
       </c>
       <c r="E2015" s="8">
         <v>165070258</v>
@@ -59005,7 +59005,7 @@
         <v>2777</v>
       </c>
       <c r="G2015" s="8">
-        <v>3245638678.11</v>
+        <v>3245847022.38</v>
       </c>
     </row>
     <row r="2016" spans="1:7" x14ac:dyDescent="0.25">
@@ -59272,7 +59272,7 @@
         <v>46258</v>
       </c>
       <c r="D2027" s="7">
-        <v>12.017949</v>
+        <v>12.014189</v>
       </c>
       <c r="E2027" s="8">
         <v>299315692</v>
@@ -59281,7 +59281,7 @@
         <v>24</v>
       </c>
       <c r="G2027" s="8">
-        <v>3597160773.16</v>
+        <v>3596035154.46</v>
       </c>
     </row>
     <row r="2028" spans="1:7" x14ac:dyDescent="0.25">
@@ -59318,7 +59318,7 @@
         <v>46258</v>
       </c>
       <c r="D2029" s="7">
-        <v>4.340743</v>
+        <v>4.347448</v>
       </c>
       <c r="E2029" s="8">
         <v>11346800</v>
@@ -59327,7 +59327,7 @@
         <v>927</v>
       </c>
       <c r="G2029" s="8">
-        <v>49253546.87</v>
+        <v>49329620.81</v>
       </c>
     </row>
     <row r="2030" spans="1:7" x14ac:dyDescent="0.25">
@@ -59386,8 +59386,8 @@
       <c r="C2032" s="6">
         <v>46258</v>
       </c>
-      <c r="D2032" s="7">
-        <v>7.570582</v>
+      <c r="D2032" s="10">
+        <v>7.56732</v>
       </c>
       <c r="E2032" s="8">
         <v>274862095</v>
@@ -59396,7 +59396,7 @@
         <v>1</v>
       </c>
       <c r="G2032" s="8">
-        <v>2080866036.2</v>
+        <v>2079969349.69</v>
       </c>
     </row>
     <row r="2033" spans="1:7" x14ac:dyDescent="0.25">
@@ -59409,8 +59409,8 @@
       <c r="C2033" s="6">
         <v>46258</v>
       </c>
-      <c r="D2033" s="10">
-        <v>1.33019</v>
+      <c r="D2033" s="7">
+        <v>1.334715</v>
       </c>
       <c r="E2033" s="8">
         <v>29040984</v>
@@ -59419,7 +59419,7 @@
         <v>1020</v>
       </c>
       <c r="G2033" s="8">
-        <v>38630026.41</v>
+        <v>38761440.31</v>
       </c>
     </row>
     <row r="2034" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>28.08.2026 09:29:06</t>
+    <t>28.08.2026 13:12:35</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -13186,7 +13186,7 @@
         <v>46262</v>
       </c>
       <c r="D23" s="7">
-        <v>57.224553</v>
+        <v>57.207401</v>
       </c>
       <c r="E23" s="8">
         <v>25255042</v>
@@ -13195,7 +13195,7 @@
         <v>159</v>
       </c>
       <c r="G23" s="8">
-        <v>1445208488.22</v>
+        <v>1444775303.22</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -13277,17 +13277,17 @@
       <c r="C27" s="6">
         <v>46262</v>
       </c>
-      <c r="D27" s="8">
-        <v>0</v>
+      <c r="D27" s="7">
+        <v>0.178161</v>
       </c>
       <c r="E27" s="8">
-        <v>0</v>
+        <v>7255718527</v>
       </c>
       <c r="F27" s="9">
         <v>35205</v>
       </c>
       <c r="G27" s="8">
-        <v>0</v>
+        <v>1292684144.86</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -13554,7 +13554,7 @@
         <v>46262</v>
       </c>
       <c r="D39" s="7">
-        <v>21.865398</v>
+        <v>21.884282</v>
       </c>
       <c r="E39" s="8">
         <v>6108462</v>
@@ -13563,7 +13563,7 @@
         <v>195</v>
       </c>
       <c r="G39" s="8">
-        <v>133563950.91</v>
+        <v>133679303.27</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -13577,7 +13577,7 @@
         <v>46262</v>
       </c>
       <c r="D40" s="7">
-        <v>31.488469</v>
+        <v>31.524244</v>
       </c>
       <c r="E40" s="8">
         <v>1749021</v>
@@ -13586,7 +13586,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="8">
-        <v>55073993.06</v>
+        <v>55136564.02</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -14132,13 +14132,13 @@
         <v>21.926039</v>
       </c>
       <c r="E64" s="8">
-        <v>11835759</v>
+        <v>11835745</v>
       </c>
       <c r="F64" s="9">
         <v>158</v>
       </c>
       <c r="G64" s="8">
-        <v>259511315.46</v>
+        <v>259511012.28</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -14312,17 +14312,17 @@
       <c r="C72" s="6">
         <v>46262</v>
       </c>
-      <c r="D72" s="8">
-        <v>0</v>
+      <c r="D72" s="7">
+        <v>6.986698</v>
       </c>
       <c r="E72" s="8">
-        <v>0</v>
+        <v>12214662</v>
       </c>
       <c r="F72" s="9">
         <v>2891</v>
       </c>
       <c r="G72" s="8">
-        <v>0</v>
+        <v>85340155.48</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -14427,17 +14427,17 @@
       <c r="C77" s="6">
         <v>46262</v>
       </c>
-      <c r="D77" s="8">
-        <v>0</v>
+      <c r="D77" s="7">
+        <v>16.166986</v>
       </c>
       <c r="E77" s="8">
-        <v>0</v>
+        <v>251324435</v>
       </c>
       <c r="F77" s="9">
         <v>7388</v>
       </c>
       <c r="G77" s="8">
-        <v>0</v>
+        <v>4063158558.04</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -14450,17 +14450,17 @@
       <c r="C78" s="6">
         <v>46262</v>
       </c>
-      <c r="D78" s="8">
-        <v>0</v>
+      <c r="D78" s="7">
+        <v>18.612253</v>
       </c>
       <c r="E78" s="8">
-        <v>0</v>
+        <v>165686692</v>
       </c>
       <c r="F78" s="9">
         <v>5087</v>
       </c>
       <c r="G78" s="8">
-        <v>0</v>
+        <v>3083802692.48</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -15209,8 +15209,8 @@
       <c r="C111" s="6">
         <v>46262</v>
       </c>
-      <c r="D111" s="7">
-        <v>2.100614</v>
+      <c r="D111" s="10">
+        <v>2.10053</v>
       </c>
       <c r="E111" s="8">
         <v>54144893</v>
@@ -15219,7 +15219,7 @@
         <v>2281</v>
       </c>
       <c r="G111" s="8">
-        <v>113737493.61</v>
+        <v>113732967.23</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -15393,8 +15393,8 @@
       <c r="C119" s="6">
         <v>46262</v>
       </c>
-      <c r="D119" s="10">
-        <v>1.84026</v>
+      <c r="D119" s="7">
+        <v>1.837939</v>
       </c>
       <c r="E119" s="8">
         <v>5558493</v>
@@ -15403,7 +15403,7 @@
         <v>57</v>
       </c>
       <c r="G119" s="8">
-        <v>10229074.52</v>
+        <v>10216171.38</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -15831,7 +15831,7 @@
         <v>46262</v>
       </c>
       <c r="D138" s="7">
-        <v>9.121343</v>
+        <v>9.121335</v>
       </c>
       <c r="E138" s="8">
         <v>99748769</v>
@@ -15840,7 +15840,7 @@
         <v>519</v>
       </c>
       <c r="G138" s="8">
-        <v>909842745.05</v>
+        <v>909841889.03</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -16198,8 +16198,8 @@
       <c r="C154" s="6">
         <v>46262</v>
       </c>
-      <c r="D154" s="11">
-        <v>1.7168</v>
+      <c r="D154" s="7">
+        <v>1.716799</v>
       </c>
       <c r="E154" s="8">
         <v>72093716</v>
@@ -16208,7 +16208,7 @@
         <v>261</v>
       </c>
       <c r="G154" s="8">
-        <v>123770455.64</v>
+        <v>123770455.49</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -16406,7 +16406,7 @@
         <v>46262</v>
       </c>
       <c r="D163" s="7">
-        <v>1.629623</v>
+        <v>1.628561</v>
       </c>
       <c r="E163" s="8">
         <v>53018825</v>
@@ -16415,7 +16415,7 @@
         <v>1084</v>
       </c>
       <c r="G163" s="8">
-        <v>86400714.16</v>
+        <v>86344369.79</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -16613,7 +16613,7 @@
         <v>46262</v>
       </c>
       <c r="D172" s="7">
-        <v>1.199277</v>
+        <v>1.199276</v>
       </c>
       <c r="E172" s="8">
         <v>301047795</v>
@@ -16622,7 +16622,7 @@
         <v>90</v>
       </c>
       <c r="G172" s="8">
-        <v>361039706.38</v>
+        <v>361039404.18</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -16705,7 +16705,7 @@
         <v>46262</v>
       </c>
       <c r="D176" s="7">
-        <v>1.784599</v>
+        <v>1.784594</v>
       </c>
       <c r="E176" s="8">
         <v>1331597809</v>
@@ -16714,7 +16714,7 @@
         <v>2795</v>
       </c>
       <c r="G176" s="8">
-        <v>2376368764.82</v>
+        <v>2376361565.39</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -16820,7 +16820,7 @@
         <v>46262</v>
       </c>
       <c r="D181" s="7">
-        <v>1.713691</v>
+        <v>1.713293</v>
       </c>
       <c r="E181" s="8">
         <v>185129213</v>
@@ -16829,7 +16829,7 @@
         <v>2081</v>
       </c>
       <c r="G181" s="8">
-        <v>317254220.8</v>
+        <v>317180623.79</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -16912,7 +16912,7 @@
         <v>46262</v>
       </c>
       <c r="D185" s="7">
-        <v>1.322477</v>
+        <v>1.326798</v>
       </c>
       <c r="E185" s="8">
         <v>91886471</v>
@@ -16921,7 +16921,7 @@
         <v>2536</v>
       </c>
       <c r="G185" s="8">
-        <v>121517743.4</v>
+        <v>121914768.65</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -17717,7 +17717,7 @@
         <v>46262</v>
       </c>
       <c r="D220" s="7">
-        <v>59.904887</v>
+        <v>59.905158</v>
       </c>
       <c r="E220" s="8">
         <v>9289973</v>
@@ -17726,7 +17726,7 @@
         <v>195</v>
       </c>
       <c r="G220" s="8">
-        <v>556514780.48</v>
+        <v>556517300.18</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -17763,16 +17763,16 @@
         <v>46262</v>
       </c>
       <c r="D222" s="7">
-        <v>3.873052</v>
+        <v>3.949715</v>
       </c>
       <c r="E222" s="8">
-        <v>428980658</v>
+        <v>429175764</v>
       </c>
       <c r="F222" s="9">
         <v>17605</v>
       </c>
       <c r="G222" s="8">
-        <v>1661464537.34</v>
+        <v>1695121860.28</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -18936,7 +18936,7 @@
         <v>46262</v>
       </c>
       <c r="D273" s="7">
-        <v>3.191723</v>
+        <v>3.192308</v>
       </c>
       <c r="E273" s="8">
         <v>32354886</v>
@@ -18945,7 +18945,7 @@
         <v>1529</v>
       </c>
       <c r="G273" s="8">
-        <v>103267841.56</v>
+        <v>103286764.42</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -19120,7 +19120,7 @@
         <v>46262</v>
       </c>
       <c r="D281" s="7">
-        <v>5.369521</v>
+        <v>5.369532</v>
       </c>
       <c r="E281" s="8">
         <v>4815299</v>
@@ -19129,7 +19129,7 @@
         <v>1139</v>
       </c>
       <c r="G281" s="8">
-        <v>25855849.55</v>
+        <v>25855900.36</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -19672,7 +19672,7 @@
         <v>46262</v>
       </c>
       <c r="D305" s="7">
-        <v>7.180796</v>
+        <v>7.180244</v>
       </c>
       <c r="E305" s="8">
         <v>445758403</v>
@@ -19681,7 +19681,7 @@
         <v>15279</v>
       </c>
       <c r="G305" s="8">
-        <v>3200900060.51</v>
+        <v>3200654094.22</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -19809,8 +19809,8 @@
       <c r="C311" s="6">
         <v>46262</v>
       </c>
-      <c r="D311" s="10">
-        <v>1.36364</v>
+      <c r="D311" s="7">
+        <v>1.365083</v>
       </c>
       <c r="E311" s="8">
         <v>338577785</v>
@@ -19819,7 +19819,7 @@
         <v>147</v>
       </c>
       <c r="G311" s="8">
-        <v>461698200.04</v>
+        <v>462186699.19</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -19902,7 +19902,7 @@
         <v>46262</v>
       </c>
       <c r="D315" s="7">
-        <v>53.480818</v>
+        <v>53.625401</v>
       </c>
       <c r="E315" s="8">
         <v>26493124</v>
@@ -19911,7 +19911,7 @@
         <v>1055</v>
       </c>
       <c r="G315" s="8">
-        <v>1416873948.32</v>
+        <v>1420704388.24</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -20201,7 +20201,7 @@
         <v>46262</v>
       </c>
       <c r="D328" s="7">
-        <v>74.921585</v>
+        <v>74.928917</v>
       </c>
       <c r="E328" s="8">
         <v>7294243</v>
@@ -20210,7 +20210,7 @@
         <v>3</v>
       </c>
       <c r="G328" s="8">
-        <v>546496247.62</v>
+        <v>546549725.42</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -20477,7 +20477,7 @@
         <v>46262</v>
       </c>
       <c r="D340" s="7">
-        <v>103.225242</v>
+        <v>103.226799</v>
       </c>
       <c r="E340" s="8">
         <v>22490084</v>
@@ -20486,7 +20486,7 @@
         <v>1</v>
       </c>
       <c r="G340" s="8">
-        <v>2321544368.42</v>
+        <v>2321579381.16</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -20753,7 +20753,7 @@
         <v>46262</v>
       </c>
       <c r="D352" s="7">
-        <v>15.029313</v>
+        <v>15.029969</v>
       </c>
       <c r="E352" s="8">
         <v>9772784</v>
@@ -20762,7 +20762,7 @@
         <v>1159</v>
       </c>
       <c r="G352" s="8">
-        <v>146878233.35</v>
+        <v>146884639.36</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -20808,7 +20808,7 @@
         <v>225</v>
       </c>
       <c r="G354" s="8">
-        <v>244019265.28</v>
+        <v>244019264.45</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -22211,7 +22211,7 @@
         <v>339</v>
       </c>
       <c r="G415" s="8">
-        <v>290522202.79</v>
+        <v>290522201.96</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
@@ -22225,7 +22225,7 @@
         <v>46262</v>
       </c>
       <c r="D416" s="7">
-        <v>1.416537</v>
+        <v>1.416191</v>
       </c>
       <c r="E416" s="8">
         <v>174809316</v>
@@ -22234,7 +22234,7 @@
         <v>1558</v>
       </c>
       <c r="G416" s="8">
-        <v>247623822.82</v>
+        <v>247563385.18</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
@@ -22478,16 +22478,16 @@
         <v>46262</v>
       </c>
       <c r="D427" s="7">
-        <v>3.081492</v>
+        <v>3.099406</v>
       </c>
       <c r="E427" s="8">
-        <v>14218420</v>
+        <v>14226296</v>
       </c>
       <c r="F427" s="9">
         <v>497</v>
       </c>
       <c r="G427" s="8">
-        <v>43813950.66</v>
+        <v>44093070.01</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
@@ -22961,7 +22961,7 @@
         <v>46262</v>
       </c>
       <c r="D448" s="7">
-        <v>7.896199</v>
+        <v>7.896286</v>
       </c>
       <c r="E448" s="8">
         <v>254461618</v>
@@ -22970,7 +22970,7 @@
         <v>2379</v>
       </c>
       <c r="G448" s="8">
-        <v>2009279526.4</v>
+        <v>2009301639.41</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
@@ -23490,7 +23490,7 @@
         <v>46262</v>
       </c>
       <c r="D471" s="7">
-        <v>0.209726</v>
+        <v>0.210088</v>
       </c>
       <c r="E471" s="8">
         <v>52456228508.04</v>
@@ -23499,7 +23499,7 @@
         <v>6534</v>
       </c>
       <c r="G471" s="8">
-        <v>11001434771.44</v>
+        <v>11020418915.13</v>
       </c>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
@@ -23996,7 +23996,7 @@
         <v>46262</v>
       </c>
       <c r="D493" s="7">
-        <v>4.823888</v>
+        <v>4.862602</v>
       </c>
       <c r="E493" s="8">
         <v>78487557</v>
@@ -24005,7 +24005,7 @@
         <v>545</v>
       </c>
       <c r="G493" s="8">
-        <v>378615221.15</v>
+        <v>381653742.02</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
@@ -24065,7 +24065,7 @@
         <v>46262</v>
       </c>
       <c r="D496" s="7">
-        <v>20.669588</v>
+        <v>20.653651</v>
       </c>
       <c r="E496" s="8">
         <v>6511</v>
@@ -24074,7 +24074,7 @@
         <v>21</v>
       </c>
       <c r="G496" s="8">
-        <v>134579.69</v>
+        <v>134475.92</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
@@ -24110,17 +24110,17 @@
       <c r="C498" s="6">
         <v>46262</v>
       </c>
-      <c r="D498" s="8">
-        <v>0</v>
+      <c r="D498" s="7">
+        <v>1.422097</v>
       </c>
       <c r="E498" s="8">
-        <v>0</v>
+        <v>854654081</v>
       </c>
       <c r="F498" s="9">
         <v>5095</v>
       </c>
       <c r="G498" s="8">
-        <v>0</v>
+        <v>1215400953.28</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
@@ -24350,7 +24350,7 @@
         <v>146</v>
       </c>
       <c r="G508" s="8">
-        <v>1530940233.25</v>
+        <v>1530940683.21</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
@@ -24525,7 +24525,7 @@
         <v>46262</v>
       </c>
       <c r="D516" s="7">
-        <v>1.195766</v>
+        <v>1.195696</v>
       </c>
       <c r="E516" s="8">
         <v>1653879287.01</v>
@@ -24534,7 +24534,7 @@
         <v>1548</v>
       </c>
       <c r="G516" s="8">
-        <v>1977652566.42</v>
+        <v>1977537331.16</v>
       </c>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.25">
@@ -24594,7 +24594,7 @@
         <v>46262</v>
       </c>
       <c r="D519" s="7">
-        <v>5.761397</v>
+        <v>5.766797</v>
       </c>
       <c r="E519" s="8">
         <v>204436476.63</v>
@@ -24603,7 +24603,7 @@
         <v>2119</v>
       </c>
       <c r="G519" s="8">
-        <v>1177839674.18</v>
+        <v>1178943677.75</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
@@ -24754,17 +24754,17 @@
       <c r="C526" s="6">
         <v>46262</v>
       </c>
-      <c r="D526" s="8">
-        <v>0</v>
+      <c r="D526" s="7">
+        <v>12.830364</v>
       </c>
       <c r="E526" s="8">
-        <v>0</v>
+        <v>29202285</v>
       </c>
       <c r="F526" s="9">
         <v>2703</v>
       </c>
       <c r="G526" s="8">
-        <v>0</v>
+        <v>374675948.8</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
@@ -24892,17 +24892,17 @@
       <c r="C532" s="6">
         <v>46262</v>
       </c>
-      <c r="D532" s="8">
-        <v>0</v>
+      <c r="D532" s="7">
+        <v>62.986773</v>
       </c>
       <c r="E532" s="8">
-        <v>0</v>
+        <v>3941000</v>
       </c>
       <c r="F532" s="9">
         <v>1</v>
       </c>
       <c r="G532" s="8">
-        <v>0</v>
+        <v>248230872.23</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
@@ -25053,17 +25053,17 @@
       <c r="C539" s="6">
         <v>46262</v>
       </c>
-      <c r="D539" s="8">
-        <v>0</v>
+      <c r="D539" s="7">
+        <v>71.633825</v>
       </c>
       <c r="E539" s="8">
-        <v>0</v>
+        <v>53983981</v>
       </c>
       <c r="F539" s="9">
         <v>2</v>
       </c>
       <c r="G539" s="8">
-        <v>0</v>
+        <v>3867079061.49</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
@@ -25076,17 +25076,17 @@
       <c r="C540" s="6">
         <v>46262</v>
       </c>
-      <c r="D540" s="8">
-        <v>0</v>
+      <c r="D540" s="11">
+        <v>13.4032</v>
       </c>
       <c r="E540" s="8">
-        <v>0</v>
+        <v>173195178</v>
       </c>
       <c r="F540" s="9">
         <v>22319</v>
       </c>
       <c r="G540" s="8">
-        <v>0</v>
+        <v>2321369539.86</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
@@ -25100,7 +25100,7 @@
         <v>46262</v>
       </c>
       <c r="D541" s="7">
-        <v>3.579964</v>
+        <v>3.583072</v>
       </c>
       <c r="E541" s="8">
         <v>343914362</v>
@@ -25109,7 +25109,7 @@
         <v>3286</v>
       </c>
       <c r="G541" s="8">
-        <v>1231201073.25</v>
+        <v>1232270061.08</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
@@ -25145,17 +25145,17 @@
       <c r="C543" s="6">
         <v>46262</v>
       </c>
-      <c r="D543" s="8">
-        <v>0</v>
+      <c r="D543" s="7">
+        <v>6.220057</v>
       </c>
       <c r="E543" s="8">
-        <v>0</v>
+        <v>222060386</v>
       </c>
       <c r="F543" s="9">
         <v>2</v>
       </c>
       <c r="G543" s="8">
-        <v>0</v>
+        <v>1381228181.1</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -25214,17 +25214,17 @@
       <c r="C546" s="6">
         <v>46262</v>
       </c>
-      <c r="D546" s="8">
-        <v>0</v>
+      <c r="D546" s="7">
+        <v>61.196888</v>
       </c>
       <c r="E546" s="8">
-        <v>0</v>
+        <v>194715</v>
       </c>
       <c r="F546" s="9">
         <v>1</v>
       </c>
       <c r="G546" s="8">
-        <v>0</v>
+        <v>11915952.05</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
@@ -25237,17 +25237,17 @@
       <c r="C547" s="6">
         <v>46262</v>
       </c>
-      <c r="D547" s="8">
-        <v>0</v>
+      <c r="D547" s="7">
+        <v>62.159669</v>
       </c>
       <c r="E547" s="8">
-        <v>0</v>
+        <v>8101428</v>
       </c>
       <c r="F547" s="9">
         <v>4</v>
       </c>
       <c r="G547" s="8">
-        <v>0</v>
+        <v>503582079.56</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
@@ -25260,17 +25260,17 @@
       <c r="C548" s="6">
         <v>46262</v>
       </c>
-      <c r="D548" s="8">
-        <v>0</v>
+      <c r="D548" s="7">
+        <v>67.069124</v>
       </c>
       <c r="E548" s="8">
-        <v>0</v>
+        <v>23236050</v>
       </c>
       <c r="F548" s="9">
         <v>1</v>
       </c>
       <c r="G548" s="8">
-        <v>0</v>
+        <v>1558421516.6</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
@@ -25283,17 +25283,17 @@
       <c r="C549" s="6">
         <v>46262</v>
       </c>
-      <c r="D549" s="8">
-        <v>0</v>
+      <c r="D549" s="10">
+        <v>76.81281</v>
       </c>
       <c r="E549" s="8">
-        <v>0</v>
+        <v>2099501</v>
       </c>
       <c r="F549" s="9">
         <v>2</v>
       </c>
       <c r="G549" s="8">
-        <v>0</v>
+        <v>161268570.88</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -25329,17 +25329,17 @@
       <c r="C551" s="6">
         <v>46262</v>
       </c>
-      <c r="D551" s="8">
-        <v>0</v>
+      <c r="D551" s="7">
+        <v>61.630848</v>
       </c>
       <c r="E551" s="8">
-        <v>0</v>
+        <v>6634456</v>
       </c>
       <c r="F551" s="9">
         <v>1</v>
       </c>
       <c r="G551" s="8">
-        <v>0</v>
+        <v>408887148.2</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -25375,17 +25375,17 @@
       <c r="C553" s="6">
         <v>46262</v>
       </c>
-      <c r="D553" s="8">
-        <v>0</v>
+      <c r="D553" s="10">
+        <v>70.86184</v>
       </c>
       <c r="E553" s="8">
-        <v>0</v>
+        <v>1555160</v>
       </c>
       <c r="F553" s="9">
         <v>2</v>
       </c>
       <c r="G553" s="8">
-        <v>0</v>
+        <v>110201499.41</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
@@ -25398,17 +25398,17 @@
       <c r="C554" s="6">
         <v>46262</v>
       </c>
-      <c r="D554" s="8">
-        <v>0</v>
+      <c r="D554" s="7">
+        <v>54.172507</v>
       </c>
       <c r="E554" s="8">
-        <v>0</v>
+        <v>30698413</v>
       </c>
       <c r="F554" s="9">
         <v>3</v>
       </c>
       <c r="G554" s="8">
-        <v>0</v>
+        <v>1663009981.76</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
@@ -25421,17 +25421,17 @@
       <c r="C555" s="6">
         <v>46262</v>
       </c>
-      <c r="D555" s="8">
-        <v>0</v>
+      <c r="D555" s="7">
+        <v>11.379148</v>
       </c>
       <c r="E555" s="8">
-        <v>0</v>
+        <v>29486927</v>
       </c>
       <c r="F555" s="9">
         <v>1</v>
       </c>
       <c r="G555" s="8">
-        <v>0</v>
+        <v>335536109.56</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -25444,17 +25444,17 @@
       <c r="C556" s="6">
         <v>46262</v>
       </c>
-      <c r="D556" s="8">
-        <v>0</v>
+      <c r="D556" s="7">
+        <v>80.941463</v>
       </c>
       <c r="E556" s="8">
-        <v>0</v>
+        <v>11573436</v>
       </c>
       <c r="F556" s="9">
         <v>3</v>
       </c>
       <c r="G556" s="8">
-        <v>0</v>
+        <v>936770837.99</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
@@ -25467,17 +25467,17 @@
       <c r="C557" s="6">
         <v>46262</v>
       </c>
-      <c r="D557" s="8">
-        <v>0</v>
+      <c r="D557" s="7">
+        <v>70.889991</v>
       </c>
       <c r="E557" s="8">
-        <v>0</v>
+        <v>5822807</v>
       </c>
       <c r="F557" s="9">
         <v>3</v>
       </c>
       <c r="G557" s="8">
-        <v>0</v>
+        <v>412778733.14</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
@@ -25490,17 +25490,17 @@
       <c r="C558" s="6">
         <v>46262</v>
       </c>
-      <c r="D558" s="8">
-        <v>0</v>
+      <c r="D558" s="7">
+        <v>67.596392</v>
       </c>
       <c r="E558" s="8">
-        <v>0</v>
+        <v>123364230</v>
       </c>
       <c r="F558" s="9">
         <v>3</v>
       </c>
       <c r="G558" s="8">
-        <v>0</v>
+        <v>8338976839.82</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
@@ -25536,17 +25536,17 @@
       <c r="C560" s="6">
         <v>46262</v>
       </c>
-      <c r="D560" s="8">
-        <v>0</v>
+      <c r="D560" s="7">
+        <v>66.274475</v>
       </c>
       <c r="E560" s="8">
-        <v>0</v>
+        <v>90240169</v>
       </c>
       <c r="F560" s="9">
         <v>2</v>
       </c>
       <c r="G560" s="8">
-        <v>0</v>
+        <v>5980619830.22</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
@@ -25628,17 +25628,17 @@
       <c r="C564" s="6">
         <v>46262</v>
       </c>
-      <c r="D564" s="8">
-        <v>0</v>
+      <c r="D564" s="7">
+        <v>10.630442</v>
       </c>
       <c r="E564" s="8">
-        <v>0</v>
+        <v>6927</v>
       </c>
       <c r="F564" s="9">
         <v>1</v>
       </c>
       <c r="G564" s="8">
-        <v>0</v>
+        <v>73637.07</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
@@ -25651,17 +25651,17 @@
       <c r="C565" s="6">
         <v>46262</v>
       </c>
-      <c r="D565" s="8">
-        <v>0</v>
+      <c r="D565" s="7">
+        <v>68.627198</v>
       </c>
       <c r="E565" s="8">
-        <v>0</v>
+        <v>23597904</v>
       </c>
       <c r="F565" s="9">
         <v>3</v>
       </c>
       <c r="G565" s="8">
-        <v>0</v>
+        <v>1619458026.01</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
@@ -25766,17 +25766,17 @@
       <c r="C570" s="6">
         <v>46262</v>
       </c>
-      <c r="D570" s="8">
-        <v>0</v>
+      <c r="D570" s="7">
+        <v>67.112338</v>
       </c>
       <c r="E570" s="8">
-        <v>0</v>
+        <v>14263356</v>
       </c>
       <c r="F570" s="9">
         <v>3</v>
       </c>
       <c r="G570" s="8">
-        <v>0</v>
+        <v>957247172.65</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -25790,7 +25790,7 @@
         <v>46262</v>
       </c>
       <c r="D571" s="10">
-        <v>10.70438</v>
+        <v>10.73461</v>
       </c>
       <c r="E571" s="8">
         <v>7219815</v>
@@ -25799,7 +25799,7 @@
         <v>968</v>
       </c>
       <c r="G571" s="8">
-        <v>77283646.7</v>
+        <v>77501899.91</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
@@ -25812,17 +25812,17 @@
       <c r="C572" s="6">
         <v>46262</v>
       </c>
-      <c r="D572" s="8">
-        <v>0</v>
+      <c r="D572" s="7">
+        <v>64.633454</v>
       </c>
       <c r="E572" s="8">
-        <v>0</v>
+        <v>6334853</v>
       </c>
       <c r="F572" s="9">
         <v>3</v>
       </c>
       <c r="G572" s="8">
-        <v>0</v>
+        <v>409443430.87</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
@@ -25858,17 +25858,17 @@
       <c r="C574" s="6">
         <v>46262</v>
       </c>
-      <c r="D574" s="8">
-        <v>0</v>
+      <c r="D574" s="7">
+        <v>64.656863</v>
       </c>
       <c r="E574" s="8">
-        <v>0</v>
+        <v>3663843</v>
       </c>
       <c r="F574" s="9">
         <v>2</v>
       </c>
       <c r="G574" s="8">
-        <v>0</v>
+        <v>236892595.93</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
@@ -25927,17 +25927,17 @@
       <c r="C577" s="6">
         <v>46262</v>
       </c>
-      <c r="D577" s="8">
-        <v>0</v>
+      <c r="D577" s="7">
+        <v>60.214417</v>
       </c>
       <c r="E577" s="8">
-        <v>0</v>
+        <v>9779449</v>
       </c>
       <c r="F577" s="9">
         <v>1</v>
       </c>
       <c r="G577" s="8">
-        <v>0</v>
+        <v>588863816.38</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
@@ -26042,17 +26042,17 @@
       <c r="C582" s="6">
         <v>46262</v>
       </c>
-      <c r="D582" s="8">
-        <v>0</v>
+      <c r="D582" s="7">
+        <v>66.492493</v>
       </c>
       <c r="E582" s="8">
-        <v>0</v>
+        <v>30617607</v>
       </c>
       <c r="F582" s="9">
         <v>2</v>
       </c>
       <c r="G582" s="8">
-        <v>0</v>
+        <v>2035841026.05</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
@@ -26181,16 +26181,16 @@
         <v>46262</v>
       </c>
       <c r="D588" s="7">
-        <v>4.447053</v>
+        <v>4.436163</v>
       </c>
       <c r="E588" s="8">
-        <v>3870456</v>
+        <v>3873680</v>
       </c>
       <c r="F588" s="9">
         <v>70</v>
       </c>
       <c r="G588" s="8">
-        <v>17212123.76</v>
+        <v>17184276.16</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -26364,17 +26364,17 @@
       <c r="C596" s="6">
         <v>46262</v>
       </c>
-      <c r="D596" s="8">
-        <v>0</v>
+      <c r="D596" s="7">
+        <v>8.262108</v>
       </c>
       <c r="E596" s="8">
-        <v>0</v>
+        <v>533417911</v>
       </c>
       <c r="F596" s="9">
         <v>21229</v>
       </c>
       <c r="G596" s="8">
-        <v>0</v>
+        <v>4407156282.72</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
@@ -26388,7 +26388,7 @@
         <v>46262</v>
       </c>
       <c r="D597" s="7">
-        <v>2.779049</v>
+        <v>2.778974</v>
       </c>
       <c r="E597" s="8">
         <v>5681727</v>
@@ -26397,7 +26397,7 @@
         <v>106</v>
       </c>
       <c r="G597" s="8">
-        <v>15789795.44</v>
+        <v>15789369.97</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
@@ -26732,17 +26732,17 @@
       <c r="C612" s="6">
         <v>46262</v>
       </c>
-      <c r="D612" s="8">
-        <v>0</v>
+      <c r="D612" s="7">
+        <v>1.623019</v>
       </c>
       <c r="E612" s="8">
-        <v>0</v>
+        <v>1222503</v>
       </c>
       <c r="F612" s="9">
         <v>469</v>
       </c>
       <c r="G612" s="8">
-        <v>0</v>
+        <v>1984145.78</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
@@ -26756,7 +26756,7 @@
         <v>46262</v>
       </c>
       <c r="D613" s="7">
-        <v>4.882031</v>
+        <v>4.885247</v>
       </c>
       <c r="E613" s="8">
         <v>16837893</v>
@@ -26765,7 +26765,7 @@
         <v>746</v>
       </c>
       <c r="G613" s="8">
-        <v>82203109.09</v>
+        <v>82257273.23</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
@@ -26788,7 +26788,7 @@
         <v>435</v>
       </c>
       <c r="G614" s="8">
-        <v>25332562.33</v>
+        <v>25332562.28</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
@@ -26802,7 +26802,7 @@
         <v>46262</v>
       </c>
       <c r="D615" s="7">
-        <v>5.028699</v>
+        <v>5.039045</v>
       </c>
       <c r="E615" s="8">
         <v>7518138</v>
@@ -26811,7 +26811,7 @@
         <v>454</v>
       </c>
       <c r="G615" s="8">
-        <v>37806454.67</v>
+        <v>37884236.63</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
@@ -26824,8 +26824,8 @@
       <c r="C616" s="6">
         <v>46262</v>
       </c>
-      <c r="D616" s="7">
-        <v>5.447499</v>
+      <c r="D616" s="10">
+        <v>5.45878</v>
       </c>
       <c r="E616" s="8">
         <v>9193679</v>
@@ -26834,7 +26834,7 @@
         <v>741</v>
       </c>
       <c r="G616" s="8">
-        <v>50082557.95</v>
+        <v>50186270.04</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
@@ -26893,17 +26893,17 @@
       <c r="C619" s="6">
         <v>46262</v>
       </c>
-      <c r="D619" s="8">
-        <v>0</v>
+      <c r="D619" s="7">
+        <v>53.528056</v>
       </c>
       <c r="E619" s="8">
-        <v>0</v>
+        <v>7467832</v>
       </c>
       <c r="F619" s="9">
         <v>323</v>
       </c>
       <c r="G619" s="8">
-        <v>0</v>
+        <v>399738530.89</v>
       </c>
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.25">
@@ -27008,17 +27008,17 @@
       <c r="C624" s="6">
         <v>46262</v>
       </c>
-      <c r="D624" s="8">
-        <v>0</v>
+      <c r="D624" s="7">
+        <v>64.893097</v>
       </c>
       <c r="E624" s="8">
-        <v>0</v>
+        <v>11252091</v>
       </c>
       <c r="F624" s="9">
         <v>466</v>
       </c>
       <c r="G624" s="8">
-        <v>0</v>
+        <v>730183027.23</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
@@ -27054,17 +27054,17 @@
       <c r="C626" s="6">
         <v>46262</v>
       </c>
-      <c r="D626" s="8">
-        <v>0</v>
+      <c r="D626" s="7">
+        <v>12.290466</v>
       </c>
       <c r="E626" s="8">
-        <v>0</v>
+        <v>102325625</v>
       </c>
       <c r="F626" s="9">
         <v>9519</v>
       </c>
       <c r="G626" s="8">
-        <v>0</v>
+        <v>1257629659.92</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
@@ -27077,17 +27077,17 @@
       <c r="C627" s="6">
         <v>46262</v>
       </c>
-      <c r="D627" s="8">
-        <v>0</v>
+      <c r="D627" s="7">
+        <v>72.672562</v>
       </c>
       <c r="E627" s="8">
-        <v>0</v>
+        <v>94459025</v>
       </c>
       <c r="F627" s="9">
         <v>3593</v>
       </c>
       <c r="G627" s="8">
-        <v>0</v>
+        <v>6864579396.49</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
@@ -27146,17 +27146,17 @@
       <c r="C630" s="6">
         <v>46262</v>
       </c>
-      <c r="D630" s="8">
-        <v>0</v>
+      <c r="D630" s="7">
+        <v>45.407545</v>
       </c>
       <c r="E630" s="8">
-        <v>0</v>
+        <v>58637</v>
       </c>
       <c r="F630" s="9">
         <v>1</v>
       </c>
       <c r="G630" s="8">
-        <v>0</v>
+        <v>2662562.22</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -27169,17 +27169,17 @@
       <c r="C631" s="6">
         <v>46262</v>
       </c>
-      <c r="D631" s="8">
-        <v>0</v>
+      <c r="D631" s="7">
+        <v>18.769595</v>
       </c>
       <c r="E631" s="8">
-        <v>0</v>
+        <v>39713878</v>
       </c>
       <c r="F631" s="9">
         <v>2810</v>
       </c>
       <c r="G631" s="8">
-        <v>0</v>
+        <v>745413415.87</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
@@ -27192,17 +27192,17 @@
       <c r="C632" s="6">
         <v>46262</v>
       </c>
-      <c r="D632" s="8">
-        <v>0</v>
+      <c r="D632" s="7">
+        <v>58.392107</v>
       </c>
       <c r="E632" s="8">
-        <v>0</v>
+        <v>14772170</v>
       </c>
       <c r="F632" s="9">
         <v>2</v>
       </c>
       <c r="G632" s="8">
-        <v>0</v>
+        <v>862578126.94</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
@@ -27238,17 +27238,17 @@
       <c r="C634" s="6">
         <v>46262</v>
       </c>
-      <c r="D634" s="8">
-        <v>0</v>
+      <c r="D634" s="7">
+        <v>62.660449</v>
       </c>
       <c r="E634" s="8">
-        <v>0</v>
+        <v>20837078</v>
       </c>
       <c r="F634" s="9">
         <v>2</v>
       </c>
       <c r="G634" s="8">
-        <v>0</v>
+        <v>1305660673.57</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
@@ -27307,17 +27307,17 @@
       <c r="C637" s="6">
         <v>46262</v>
       </c>
-      <c r="D637" s="8">
-        <v>0</v>
+      <c r="D637" s="7">
+        <v>21.533774</v>
       </c>
       <c r="E637" s="8">
-        <v>0</v>
+        <v>16720901</v>
       </c>
       <c r="F637" s="9">
         <v>2458</v>
       </c>
       <c r="G637" s="8">
-        <v>0</v>
+        <v>360064104.82</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.25">
@@ -27377,7 +27377,7 @@
         <v>46262</v>
       </c>
       <c r="D640" s="7">
-        <v>1.843805</v>
+        <v>1.850385</v>
       </c>
       <c r="E640" s="8">
         <v>291887254</v>
@@ -27386,7 +27386,7 @@
         <v>286</v>
       </c>
       <c r="G640" s="8">
-        <v>538183194.32</v>
+        <v>540103669.87</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.25">
@@ -27560,17 +27560,17 @@
       <c r="C648" s="6">
         <v>46262</v>
       </c>
-      <c r="D648" s="8">
-        <v>0</v>
+      <c r="D648" s="7">
+        <v>57.692073</v>
       </c>
       <c r="E648" s="8">
-        <v>0</v>
+        <v>4643160</v>
       </c>
       <c r="F648" s="9">
         <v>2</v>
       </c>
       <c r="G648" s="8">
-        <v>0</v>
+        <v>267873526.84</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
@@ -27675,17 +27675,17 @@
       <c r="C653" s="6">
         <v>46262</v>
       </c>
-      <c r="D653" s="8">
-        <v>0</v>
+      <c r="D653" s="10">
+        <v>7.07187</v>
       </c>
       <c r="E653" s="8">
-        <v>0</v>
+        <v>4029467144</v>
       </c>
       <c r="F653" s="9">
         <v>1</v>
       </c>
       <c r="G653" s="8">
-        <v>0</v>
+        <v>28495869594.85</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
@@ -27767,17 +27767,17 @@
       <c r="C657" s="6">
         <v>46262</v>
       </c>
-      <c r="D657" s="8">
-        <v>0</v>
+      <c r="D657" s="7">
+        <v>6.507256</v>
       </c>
       <c r="E657" s="8">
-        <v>0</v>
+        <v>64452410</v>
       </c>
       <c r="F657" s="9">
         <v>528</v>
       </c>
       <c r="G657" s="8">
-        <v>0</v>
+        <v>419408356.38</v>
       </c>
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.25">
@@ -27790,17 +27790,17 @@
       <c r="C658" s="6">
         <v>46262</v>
       </c>
-      <c r="D658" s="8">
-        <v>0</v>
+      <c r="D658" s="7">
+        <v>12.361581</v>
       </c>
       <c r="E658" s="8">
-        <v>0</v>
+        <v>1068360195</v>
       </c>
       <c r="F658" s="9">
         <v>62478</v>
       </c>
       <c r="G658" s="8">
-        <v>0</v>
+        <v>13206621264.89</v>
       </c>
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.25">
@@ -27813,17 +27813,17 @@
       <c r="C659" s="6">
         <v>46262</v>
       </c>
-      <c r="D659" s="8">
-        <v>0</v>
+      <c r="D659" s="7">
+        <v>6.033389</v>
       </c>
       <c r="E659" s="8">
-        <v>0</v>
+        <v>341860798</v>
       </c>
       <c r="F659" s="9">
         <v>1</v>
       </c>
       <c r="G659" s="8">
-        <v>0</v>
+        <v>2062579110.02</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
@@ -27905,17 +27905,17 @@
       <c r="C663" s="6">
         <v>46262</v>
       </c>
-      <c r="D663" s="8">
-        <v>0</v>
+      <c r="D663" s="7">
+        <v>0.454418</v>
       </c>
       <c r="E663" s="8">
-        <v>0</v>
+        <v>10264183223</v>
       </c>
       <c r="F663" s="9">
         <v>38629</v>
       </c>
       <c r="G663" s="8">
-        <v>0</v>
+        <v>4664228038.79</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -27928,17 +27928,17 @@
       <c r="C664" s="6">
         <v>46262</v>
       </c>
-      <c r="D664" s="8">
-        <v>0</v>
+      <c r="D664" s="7">
+        <v>1.490083</v>
       </c>
       <c r="E664" s="8">
-        <v>0</v>
+        <v>802085254</v>
       </c>
       <c r="F664" s="9">
         <v>2705</v>
       </c>
       <c r="G664" s="8">
-        <v>0</v>
+        <v>1195173832.99</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
@@ -27951,17 +27951,17 @@
       <c r="C665" s="6">
         <v>46262</v>
       </c>
-      <c r="D665" s="8">
-        <v>0</v>
+      <c r="D665" s="7">
+        <v>13.230532</v>
       </c>
       <c r="E665" s="8">
-        <v>0</v>
+        <v>524498731</v>
       </c>
       <c r="F665" s="9">
         <v>52924</v>
       </c>
       <c r="G665" s="8">
-        <v>0</v>
+        <v>6939397338.24</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
@@ -27997,17 +27997,17 @@
       <c r="C667" s="6">
         <v>46262</v>
       </c>
-      <c r="D667" s="8">
-        <v>0</v>
+      <c r="D667" s="7">
+        <v>4.154811</v>
       </c>
       <c r="E667" s="8">
-        <v>0</v>
+        <v>23603643</v>
       </c>
       <c r="F667" s="9">
         <v>3439</v>
       </c>
       <c r="G667" s="8">
-        <v>0</v>
+        <v>98068685.64</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -28020,17 +28020,17 @@
       <c r="C668" s="6">
         <v>46262</v>
       </c>
-      <c r="D668" s="8">
-        <v>0</v>
+      <c r="D668" s="7">
+        <v>68.393811</v>
       </c>
       <c r="E668" s="8">
-        <v>0</v>
+        <v>52499640</v>
       </c>
       <c r="F668" s="9">
         <v>3</v>
       </c>
       <c r="G668" s="8">
-        <v>0</v>
+        <v>3590650448.44</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -28043,17 +28043,17 @@
       <c r="C669" s="6">
         <v>46262</v>
       </c>
-      <c r="D669" s="8">
-        <v>0</v>
+      <c r="D669" s="10">
+        <v>64.76117</v>
       </c>
       <c r="E669" s="8">
-        <v>0</v>
+        <v>4739268</v>
       </c>
       <c r="F669" s="9">
         <v>1</v>
       </c>
       <c r="G669" s="8">
-        <v>0</v>
+        <v>306920541.9</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
@@ -28066,17 +28066,17 @@
       <c r="C670" s="6">
         <v>46262</v>
       </c>
-      <c r="D670" s="8">
-        <v>0</v>
+      <c r="D670" s="7">
+        <v>18.422385</v>
       </c>
       <c r="E670" s="8">
-        <v>0</v>
+        <v>22115</v>
       </c>
       <c r="F670" s="9">
         <v>1</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>407411.04</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -28089,17 +28089,17 @@
       <c r="C671" s="6">
         <v>46262</v>
       </c>
-      <c r="D671" s="8">
-        <v>0</v>
+      <c r="D671" s="7">
+        <v>5.737231</v>
       </c>
       <c r="E671" s="8">
-        <v>0</v>
+        <v>209772430</v>
       </c>
       <c r="F671" s="9">
         <v>4585</v>
       </c>
       <c r="G671" s="8">
-        <v>0</v>
+        <v>1203512970.02</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
@@ -28112,17 +28112,17 @@
       <c r="C672" s="6">
         <v>46262</v>
       </c>
-      <c r="D672" s="8">
-        <v>0</v>
+      <c r="D672" s="10">
+        <v>66.98568</v>
       </c>
       <c r="E672" s="8">
-        <v>0</v>
+        <v>7872114</v>
       </c>
       <c r="F672" s="9">
         <v>3</v>
       </c>
       <c r="G672" s="8">
-        <v>0</v>
+        <v>527318912.98</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
@@ -28135,17 +28135,17 @@
       <c r="C673" s="6">
         <v>46262</v>
       </c>
-      <c r="D673" s="8">
-        <v>0</v>
+      <c r="D673" s="7">
+        <v>73.984884</v>
       </c>
       <c r="E673" s="8">
-        <v>0</v>
+        <v>5533354</v>
       </c>
       <c r="F673" s="9">
         <v>2</v>
       </c>
       <c r="G673" s="8">
-        <v>0</v>
+        <v>409384551.12</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
@@ -28158,17 +28158,17 @@
       <c r="C674" s="6">
         <v>46262</v>
       </c>
-      <c r="D674" s="8">
-        <v>0</v>
+      <c r="D674" s="7">
+        <v>4.112468</v>
       </c>
       <c r="E674" s="8">
-        <v>0</v>
+        <v>5020082762</v>
       </c>
       <c r="F674" s="9">
         <v>1</v>
       </c>
       <c r="G674" s="8">
-        <v>0</v>
+        <v>20644930939.63</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -28181,17 +28181,17 @@
       <c r="C675" s="6">
         <v>46262</v>
       </c>
-      <c r="D675" s="8">
-        <v>0</v>
+      <c r="D675" s="7">
+        <v>72.150864</v>
       </c>
       <c r="E675" s="8">
-        <v>0</v>
+        <v>7036272</v>
       </c>
       <c r="F675" s="9">
         <v>4</v>
       </c>
       <c r="G675" s="8">
-        <v>0</v>
+        <v>507673107.25</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
@@ -28250,17 +28250,17 @@
       <c r="C678" s="6">
         <v>46262</v>
       </c>
-      <c r="D678" s="8">
-        <v>0</v>
+      <c r="D678" s="7">
+        <v>69.221419</v>
       </c>
       <c r="E678" s="8">
-        <v>0</v>
+        <v>20613565</v>
       </c>
       <c r="F678" s="9">
         <v>1</v>
       </c>
       <c r="G678" s="8">
-        <v>0</v>
+        <v>1426900220.99</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
@@ -28273,17 +28273,17 @@
       <c r="C679" s="6">
         <v>46262</v>
       </c>
-      <c r="D679" s="8">
-        <v>0</v>
+      <c r="D679" s="7">
+        <v>63.721518</v>
       </c>
       <c r="E679" s="8">
-        <v>0</v>
+        <v>9307247</v>
       </c>
       <c r="F679" s="9">
         <v>5</v>
       </c>
       <c r="G679" s="8">
-        <v>0</v>
+        <v>593071911.74</v>
       </c>
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.25">
@@ -28342,17 +28342,17 @@
       <c r="C682" s="6">
         <v>46262</v>
       </c>
-      <c r="D682" s="8">
-        <v>0</v>
+      <c r="D682" s="7">
+        <v>7.855449</v>
       </c>
       <c r="E682" s="8">
-        <v>0</v>
+        <v>184623982</v>
       </c>
       <c r="F682" s="9">
         <v>4130</v>
       </c>
       <c r="G682" s="8">
-        <v>0</v>
+        <v>1450304234.66</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
@@ -28365,17 +28365,17 @@
       <c r="C683" s="6">
         <v>46262</v>
       </c>
-      <c r="D683" s="8">
-        <v>0</v>
+      <c r="D683" s="7">
+        <v>7.664767</v>
       </c>
       <c r="E683" s="8">
-        <v>0</v>
+        <v>65188676</v>
       </c>
       <c r="F683" s="9">
         <v>4509</v>
       </c>
       <c r="G683" s="8">
-        <v>0</v>
+        <v>499656018.39</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
@@ -28388,17 +28388,17 @@
       <c r="C684" s="6">
         <v>46262</v>
       </c>
-      <c r="D684" s="8">
-        <v>0</v>
+      <c r="D684" s="7">
+        <v>4.896839</v>
       </c>
       <c r="E684" s="8">
-        <v>0</v>
+        <v>76331097</v>
       </c>
       <c r="F684" s="9">
         <v>5657</v>
       </c>
       <c r="G684" s="8">
-        <v>0</v>
+        <v>373781076.83</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
@@ -28411,17 +28411,17 @@
       <c r="C685" s="6">
         <v>46262</v>
       </c>
-      <c r="D685" s="8">
-        <v>0</v>
+      <c r="D685" s="7">
+        <v>8.851365</v>
       </c>
       <c r="E685" s="8">
-        <v>0</v>
+        <v>198798484</v>
       </c>
       <c r="F685" s="9">
         <v>5199</v>
       </c>
       <c r="G685" s="8">
-        <v>0</v>
+        <v>1759637856.03</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
@@ -28503,17 +28503,17 @@
       <c r="C689" s="6">
         <v>46262</v>
       </c>
-      <c r="D689" s="8">
-        <v>0</v>
+      <c r="D689" s="7">
+        <v>70.433558</v>
       </c>
       <c r="E689" s="8">
-        <v>0</v>
+        <v>1210798</v>
       </c>
       <c r="F689" s="9">
         <v>1</v>
       </c>
       <c r="G689" s="8">
-        <v>0</v>
+        <v>85280811.56</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
@@ -28526,17 +28526,17 @@
       <c r="C690" s="6">
         <v>46262</v>
       </c>
-      <c r="D690" s="8">
-        <v>0</v>
+      <c r="D690" s="7">
+        <v>7.780598</v>
       </c>
       <c r="E690" s="8">
-        <v>0</v>
+        <v>501355736</v>
       </c>
       <c r="F690" s="9">
         <v>10165</v>
       </c>
       <c r="G690" s="8">
-        <v>0</v>
+        <v>3900847642.45</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.25">
@@ -28572,17 +28572,17 @@
       <c r="C692" s="6">
         <v>46262</v>
       </c>
-      <c r="D692" s="8">
-        <v>0</v>
+      <c r="D692" s="7">
+        <v>68.098483</v>
       </c>
       <c r="E692" s="8">
-        <v>0</v>
+        <v>6829649</v>
       </c>
       <c r="F692" s="9">
         <v>2</v>
       </c>
       <c r="G692" s="8">
-        <v>0</v>
+        <v>465088738.16</v>
       </c>
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.25">
@@ -28595,17 +28595,17 @@
       <c r="C693" s="6">
         <v>46262</v>
       </c>
-      <c r="D693" s="8">
-        <v>0</v>
+      <c r="D693" s="7">
+        <v>8.801892</v>
       </c>
       <c r="E693" s="8">
-        <v>0</v>
+        <v>11430566</v>
       </c>
       <c r="F693" s="9">
         <v>1378</v>
       </c>
       <c r="G693" s="8">
-        <v>0</v>
+        <v>100610601.81</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.25">
@@ -28618,17 +28618,17 @@
       <c r="C694" s="6">
         <v>46262</v>
       </c>
-      <c r="D694" s="8">
-        <v>0</v>
+      <c r="D694" s="7">
+        <v>7.868621</v>
       </c>
       <c r="E694" s="8">
-        <v>0</v>
+        <v>8894956</v>
       </c>
       <c r="F694" s="9">
         <v>2319</v>
       </c>
       <c r="G694" s="8">
-        <v>0</v>
+        <v>69991035.79</v>
       </c>
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.25">
@@ -28641,17 +28641,17 @@
       <c r="C695" s="6">
         <v>46262</v>
       </c>
-      <c r="D695" s="8">
-        <v>0</v>
+      <c r="D695" s="7">
+        <v>7.188219</v>
       </c>
       <c r="E695" s="8">
-        <v>0</v>
+        <v>9293350</v>
       </c>
       <c r="F695" s="9">
         <v>1237</v>
       </c>
       <c r="G695" s="8">
-        <v>0</v>
+        <v>66802630.69</v>
       </c>
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.25">
@@ -28894,17 +28894,17 @@
       <c r="C706" s="6">
         <v>46262</v>
       </c>
-      <c r="D706" s="8">
-        <v>0</v>
+      <c r="D706" s="7">
+        <v>4.372327</v>
       </c>
       <c r="E706" s="8">
-        <v>0</v>
+        <v>123304732</v>
       </c>
       <c r="F706" s="9">
         <v>1075</v>
       </c>
       <c r="G706" s="8">
-        <v>0</v>
+        <v>539128563.05</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.25">
@@ -29019,7 +29019,7 @@
         <v>152</v>
       </c>
       <c r="G711" s="8">
-        <v>11267337.3</v>
+        <v>11267337.26</v>
       </c>
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.25">
@@ -29286,7 +29286,7 @@
         <v>46262</v>
       </c>
       <c r="D723" s="7">
-        <v>64.056209</v>
+        <v>64.055641</v>
       </c>
       <c r="E723" s="8">
         <v>137499348</v>
@@ -29295,7 +29295,7 @@
         <v>3253</v>
       </c>
       <c r="G723" s="8">
-        <v>8807687030.15</v>
+        <v>8807608910.96</v>
       </c>
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.25">
@@ -29999,7 +29999,7 @@
         <v>46262</v>
       </c>
       <c r="D754" s="7">
-        <v>54.643085</v>
+        <v>54.642659</v>
       </c>
       <c r="E754" s="8">
         <v>502981694</v>
@@ -30008,7 +30008,7 @@
         <v>8227</v>
       </c>
       <c r="G754" s="8">
-        <v>27484471253.46</v>
+        <v>27484257164.03</v>
       </c>
     </row>
     <row r="755" spans="1:7" x14ac:dyDescent="0.25">
@@ -30206,7 +30206,7 @@
         <v>46262</v>
       </c>
       <c r="D763" s="7">
-        <v>0.368206</v>
+        <v>0.368523</v>
       </c>
       <c r="E763" s="8">
         <v>3700886027</v>
@@ -30215,7 +30215,7 @@
         <v>2534</v>
       </c>
       <c r="G763" s="8">
-        <v>1362686769.79</v>
+        <v>1363861715.14</v>
       </c>
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.25">
@@ -30527,8 +30527,8 @@
       <c r="C777" s="6">
         <v>46262</v>
       </c>
-      <c r="D777" s="7">
-        <v>1658.466034</v>
+      <c r="D777" s="10">
+        <v>1658.41957</v>
       </c>
       <c r="E777" s="8">
         <v>2483925</v>
@@ -30537,7 +30537,7 @@
         <v>2378</v>
       </c>
       <c r="G777" s="8">
-        <v>4119505242.57</v>
+        <v>4119389831.01</v>
       </c>
     </row>
     <row r="778" spans="1:7" x14ac:dyDescent="0.25">
@@ -30666,7 +30666,7 @@
         <v>46262</v>
       </c>
       <c r="D783" s="7">
-        <v>1.054492</v>
+        <v>1.055058</v>
       </c>
       <c r="E783" s="8">
         <v>115902496</v>
@@ -30675,7 +30675,7 @@
         <v>919</v>
       </c>
       <c r="G783" s="8">
-        <v>122218293.26</v>
+        <v>122283881.99</v>
       </c>
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.25">
@@ -30689,7 +30689,7 @@
         <v>46262</v>
       </c>
       <c r="D784" s="7">
-        <v>59.982961</v>
+        <v>59.964587</v>
       </c>
       <c r="E784" s="8">
         <v>80767638</v>
@@ -30698,7 +30698,7 @@
         <v>2612</v>
       </c>
       <c r="G784" s="8">
-        <v>4844682079.34</v>
+        <v>4843198070.93</v>
       </c>
     </row>
     <row r="785" spans="1:7" x14ac:dyDescent="0.25">
@@ -31309,17 +31309,17 @@
       <c r="C811" s="6">
         <v>46262</v>
       </c>
-      <c r="D811" s="8">
-        <v>0</v>
+      <c r="D811" s="7">
+        <v>77.927985</v>
       </c>
       <c r="E811" s="8">
-        <v>0</v>
+        <v>1888090</v>
       </c>
       <c r="F811" s="9">
         <v>22</v>
       </c>
       <c r="G811" s="8">
-        <v>0</v>
+        <v>147135049.68</v>
       </c>
     </row>
     <row r="812" spans="1:7" x14ac:dyDescent="0.25">
@@ -31562,8 +31562,8 @@
       <c r="C822" s="6">
         <v>46262</v>
       </c>
-      <c r="D822" s="7">
-        <v>3.919055</v>
+      <c r="D822" s="10">
+        <v>3.91906</v>
       </c>
       <c r="E822" s="8">
         <v>54294216</v>
@@ -31572,7 +31572,7 @@
         <v>16</v>
       </c>
       <c r="G822" s="8">
-        <v>212782030.25</v>
+        <v>212782291.58</v>
       </c>
     </row>
     <row r="823" spans="1:7" x14ac:dyDescent="0.25">
@@ -32068,8 +32068,8 @@
       <c r="C844" s="6">
         <v>46262</v>
       </c>
-      <c r="D844" s="7">
-        <v>0.238508</v>
+      <c r="D844" s="11">
+        <v>0.2385</v>
       </c>
       <c r="E844" s="8">
         <v>3089100368.13</v>
@@ -32078,7 +32078,7 @@
         <v>2504</v>
       </c>
       <c r="G844" s="8">
-        <v>736773852.83</v>
+        <v>736749295.04</v>
       </c>
     </row>
     <row r="845" spans="1:7" x14ac:dyDescent="0.25">
@@ -32667,7 +32667,7 @@
         <v>46262</v>
       </c>
       <c r="D870" s="7">
-        <v>33.920263</v>
+        <v>33.920027</v>
       </c>
       <c r="E870" s="8">
         <v>53743362</v>
@@ -32676,7 +32676,7 @@
         <v>21560</v>
       </c>
       <c r="G870" s="8">
-        <v>1822988970.87</v>
+        <v>1822976289.28</v>
       </c>
     </row>
     <row r="871" spans="1:7" x14ac:dyDescent="0.25">
@@ -32850,17 +32850,17 @@
       <c r="C878" s="6">
         <v>46262</v>
       </c>
-      <c r="D878" s="8">
-        <v>0</v>
+      <c r="D878" s="7">
+        <v>7.320467</v>
       </c>
       <c r="E878" s="8">
-        <v>0</v>
+        <v>4601558</v>
       </c>
       <c r="F878" s="9">
         <v>395</v>
       </c>
       <c r="G878" s="8">
-        <v>0</v>
+        <v>33685552.11</v>
       </c>
     </row>
     <row r="879" spans="1:7" x14ac:dyDescent="0.25">
@@ -33218,8 +33218,8 @@
       <c r="C894" s="6">
         <v>46262</v>
       </c>
-      <c r="D894" s="10">
-        <v>7.23255</v>
+      <c r="D894" s="7">
+        <v>7.231448</v>
       </c>
       <c r="E894" s="8">
         <v>43526148</v>
@@ -33228,7 +33228,7 @@
         <v>13</v>
       </c>
       <c r="G894" s="8">
-        <v>314805044.73</v>
+        <v>314757086.71</v>
       </c>
     </row>
     <row r="895" spans="1:7" x14ac:dyDescent="0.25">
@@ -33265,7 +33265,7 @@
         <v>46262</v>
       </c>
       <c r="D896" s="7">
-        <v>1.326046</v>
+        <v>1.326072</v>
       </c>
       <c r="E896" s="8">
         <v>1837384432</v>
@@ -33274,7 +33274,7 @@
         <v>4</v>
       </c>
       <c r="G896" s="8">
-        <v>2436456647.03</v>
+        <v>2436504614.79</v>
       </c>
     </row>
     <row r="897" spans="1:7" x14ac:dyDescent="0.25">
@@ -33540,17 +33540,17 @@
       <c r="C908" s="6">
         <v>46262</v>
       </c>
-      <c r="D908" s="8">
-        <v>0</v>
+      <c r="D908" s="7">
+        <v>15.134529</v>
       </c>
       <c r="E908" s="8">
-        <v>0</v>
+        <v>15443652</v>
       </c>
       <c r="F908" s="9">
         <v>375</v>
       </c>
       <c r="G908" s="8">
-        <v>0</v>
+        <v>233732401.98</v>
       </c>
     </row>
     <row r="909" spans="1:7" x14ac:dyDescent="0.25">
@@ -33817,7 +33817,7 @@
         <v>46262</v>
       </c>
       <c r="D920" s="7">
-        <v>57.742661</v>
+        <v>57.747253</v>
       </c>
       <c r="E920" s="8">
         <v>9907429</v>
@@ -33826,7 +33826,7 @@
         <v>1</v>
       </c>
       <c r="G920" s="8">
-        <v>572081309.72</v>
+        <v>572126807.58</v>
       </c>
     </row>
     <row r="921" spans="1:7" x14ac:dyDescent="0.25">
@@ -33932,7 +33932,7 @@
         <v>46262</v>
       </c>
       <c r="D925" s="7">
-        <v>0.124117</v>
+        <v>0.124072</v>
       </c>
       <c r="E925" s="8">
         <v>1105011730</v>
@@ -33941,7 +33941,7 @@
         <v>22</v>
       </c>
       <c r="G925" s="8">
-        <v>137150225.14</v>
+        <v>137101410.31</v>
       </c>
     </row>
     <row r="926" spans="1:7" x14ac:dyDescent="0.25">
@@ -34047,7 +34047,7 @@
         <v>46262</v>
       </c>
       <c r="D930" s="7">
-        <v>0.183017</v>
+        <v>0.183089</v>
       </c>
       <c r="E930" s="8">
         <v>38129844893</v>
@@ -34056,7 +34056,7 @@
         <v>163</v>
       </c>
       <c r="G930" s="8">
-        <v>6978403601.42</v>
+        <v>6981170275.32</v>
       </c>
     </row>
     <row r="931" spans="1:7" x14ac:dyDescent="0.25">
@@ -34185,7 +34185,7 @@
         <v>46262</v>
       </c>
       <c r="D936" s="7">
-        <v>7.519771</v>
+        <v>7.537609</v>
       </c>
       <c r="E936" s="8">
         <v>70973903</v>
@@ -34194,7 +34194,7 @@
         <v>1991</v>
       </c>
       <c r="G936" s="8">
-        <v>533707497.39</v>
+        <v>534973526.5</v>
       </c>
     </row>
     <row r="937" spans="1:7" x14ac:dyDescent="0.25">
@@ -34690,8 +34690,8 @@
       <c r="C958" s="6">
         <v>46262</v>
       </c>
-      <c r="D958" s="10">
-        <v>6.29804</v>
+      <c r="D958" s="7">
+        <v>6.352977</v>
       </c>
       <c r="E958" s="8">
         <v>2000255.66</v>
@@ -34700,7 +34700,7 @@
         <v>716</v>
       </c>
       <c r="G958" s="8">
-        <v>12597690.52</v>
+        <v>12707577.97</v>
       </c>
     </row>
     <row r="959" spans="1:7" x14ac:dyDescent="0.25">
@@ -37244,7 +37244,7 @@
         <v>46262</v>
       </c>
       <c r="D1069" s="7">
-        <v>3.188528</v>
+        <v>3.187506</v>
       </c>
       <c r="E1069" s="8">
         <v>141027787</v>
@@ -37253,7 +37253,7 @@
         <v>678</v>
       </c>
       <c r="G1069" s="8">
-        <v>449671005</v>
+        <v>449526969.3</v>
       </c>
     </row>
     <row r="1070" spans="1:7" x14ac:dyDescent="0.25">
@@ -38440,7 +38440,7 @@
         <v>46262</v>
       </c>
       <c r="D1121" s="7">
-        <v>1.425221</v>
+        <v>1.425113</v>
       </c>
       <c r="E1121" s="8">
         <v>1193853791</v>
@@ -38449,7 +38449,7 @@
         <v>1</v>
       </c>
       <c r="G1121" s="8">
-        <v>1701505082.77</v>
+        <v>1701376763.11</v>
       </c>
     </row>
     <row r="1122" spans="1:7" x14ac:dyDescent="0.25">
@@ -39130,16 +39130,16 @@
         <v>46262</v>
       </c>
       <c r="D1151" s="7">
-        <v>7.858643</v>
+        <v>7.887975</v>
       </c>
       <c r="E1151" s="8">
-        <v>6727248</v>
+        <v>6670578</v>
       </c>
       <c r="F1151" s="9">
         <v>778</v>
       </c>
       <c r="G1151" s="8">
-        <v>52867037.21</v>
+        <v>52617351.28</v>
       </c>
     </row>
     <row r="1152" spans="1:7" x14ac:dyDescent="0.25">
@@ -39176,16 +39176,16 @@
         <v>46262</v>
       </c>
       <c r="D1153" s="7">
-        <v>11.503176</v>
+        <v>11.475599</v>
       </c>
       <c r="E1153" s="8">
-        <v>89876912</v>
+        <v>89103557</v>
       </c>
       <c r="F1153" s="9">
         <v>7528</v>
       </c>
       <c r="G1153" s="8">
-        <v>1033869926.94</v>
+        <v>1022516729.6</v>
       </c>
     </row>
     <row r="1154" spans="1:7" x14ac:dyDescent="0.25">
@@ -39199,16 +39199,16 @@
         <v>46262</v>
       </c>
       <c r="D1154" s="7">
-        <v>4.374991</v>
+        <v>4.410619</v>
       </c>
       <c r="E1154" s="8">
-        <v>6087863</v>
+        <v>6094101</v>
       </c>
       <c r="F1154" s="9">
         <v>32</v>
       </c>
       <c r="G1154" s="8">
-        <v>26634345.82</v>
+        <v>26878755.22</v>
       </c>
     </row>
     <row r="1155" spans="1:7" x14ac:dyDescent="0.25">
@@ -39451,17 +39451,17 @@
       <c r="C1165" s="6">
         <v>46262</v>
       </c>
-      <c r="D1165" s="8">
-        <v>0</v>
+      <c r="D1165" s="7">
+        <v>1.258587</v>
       </c>
       <c r="E1165" s="8">
-        <v>0</v>
+        <v>2651303752</v>
       </c>
       <c r="F1165" s="9">
         <v>13</v>
       </c>
       <c r="G1165" s="8">
-        <v>0</v>
+        <v>3336895874.55</v>
       </c>
     </row>
     <row r="1166" spans="1:7" x14ac:dyDescent="0.25">
@@ -39474,17 +39474,17 @@
       <c r="C1166" s="6">
         <v>46262</v>
       </c>
-      <c r="D1166" s="8">
-        <v>0</v>
+      <c r="D1166" s="7">
+        <v>2.058047</v>
       </c>
       <c r="E1166" s="8">
-        <v>0</v>
+        <v>1833223343</v>
       </c>
       <c r="F1166" s="9">
         <v>15</v>
       </c>
       <c r="G1166" s="8">
-        <v>0</v>
+        <v>3772860641.09</v>
       </c>
     </row>
     <row r="1167" spans="1:7" x14ac:dyDescent="0.25">
@@ -40141,17 +40141,17 @@
       <c r="C1195" s="6">
         <v>46262</v>
       </c>
-      <c r="D1195" s="7">
-        <v>2.792224</v>
+      <c r="D1195" s="11">
+        <v>2.7893</v>
       </c>
       <c r="E1195" s="8">
-        <v>10224480</v>
+        <v>10214586</v>
       </c>
       <c r="F1195" s="9">
         <v>670</v>
       </c>
       <c r="G1195" s="8">
-        <v>28549034.73</v>
+        <v>28491541.63</v>
       </c>
     </row>
     <row r="1196" spans="1:7" x14ac:dyDescent="0.25">
@@ -40164,17 +40164,17 @@
       <c r="C1196" s="6">
         <v>46262</v>
       </c>
-      <c r="D1196" s="8">
-        <v>0</v>
+      <c r="D1196" s="7">
+        <v>0.801389</v>
       </c>
       <c r="E1196" s="8">
-        <v>0</v>
+        <v>1033653600</v>
       </c>
       <c r="F1196" s="9">
         <v>19</v>
       </c>
       <c r="G1196" s="8">
-        <v>0</v>
+        <v>828358549.08</v>
       </c>
     </row>
     <row r="1197" spans="1:7" x14ac:dyDescent="0.25">
@@ -40302,17 +40302,17 @@
       <c r="C1202" s="6">
         <v>46262</v>
       </c>
-      <c r="D1202" s="8">
-        <v>0</v>
+      <c r="D1202" s="7">
+        <v>0.425861</v>
       </c>
       <c r="E1202" s="8">
-        <v>0</v>
+        <v>1199204513</v>
       </c>
       <c r="F1202" s="9">
         <v>12</v>
       </c>
       <c r="G1202" s="8">
-        <v>0</v>
+        <v>510694189.49</v>
       </c>
     </row>
     <row r="1203" spans="1:7" x14ac:dyDescent="0.25">
@@ -40417,17 +40417,17 @@
       <c r="C1207" s="6">
         <v>46262</v>
       </c>
-      <c r="D1207" s="8">
-        <v>0</v>
+      <c r="D1207" s="7">
+        <v>1.526841</v>
       </c>
       <c r="E1207" s="8">
-        <v>0</v>
+        <v>1479131931</v>
       </c>
       <c r="F1207" s="9">
         <v>394</v>
       </c>
       <c r="G1207" s="8">
-        <v>0</v>
+        <v>2258399891.96</v>
       </c>
     </row>
     <row r="1208" spans="1:7" x14ac:dyDescent="0.25">
@@ -40533,7 +40533,7 @@
         <v>46262</v>
       </c>
       <c r="D1212" s="7">
-        <v>1.033154</v>
+        <v>1.036089</v>
       </c>
       <c r="E1212" s="8">
         <v>588672037</v>
@@ -40542,7 +40542,7 @@
         <v>13</v>
       </c>
       <c r="G1212" s="8">
-        <v>608189131.77</v>
+        <v>609916834.82</v>
       </c>
     </row>
     <row r="1213" spans="1:7" x14ac:dyDescent="0.25">
@@ -40578,17 +40578,17 @@
       <c r="C1214" s="6">
         <v>46262</v>
       </c>
-      <c r="D1214" s="8">
-        <v>0</v>
+      <c r="D1214" s="7">
+        <v>1.361817</v>
       </c>
       <c r="E1214" s="8">
-        <v>0</v>
+        <v>1339279649</v>
       </c>
       <c r="F1214" s="9">
         <v>33</v>
       </c>
       <c r="G1214" s="8">
-        <v>0</v>
+        <v>1823853624.72</v>
       </c>
     </row>
     <row r="1215" spans="1:7" x14ac:dyDescent="0.25">
@@ -40647,17 +40647,17 @@
       <c r="C1217" s="6">
         <v>46262</v>
       </c>
-      <c r="D1217" s="8">
-        <v>0</v>
+      <c r="D1217" s="7">
+        <v>5.702395</v>
       </c>
       <c r="E1217" s="8">
-        <v>0</v>
+        <v>2143255</v>
       </c>
       <c r="F1217" s="9">
         <v>153</v>
       </c>
       <c r="G1217" s="8">
-        <v>0</v>
+        <v>12221686.64</v>
       </c>
     </row>
     <row r="1218" spans="1:7" x14ac:dyDescent="0.25">
@@ -41131,7 +41131,7 @@
         <v>46262</v>
       </c>
       <c r="D1238" s="7">
-        <v>51.172558</v>
+        <v>51.171911</v>
       </c>
       <c r="E1238" s="8">
         <v>3559908</v>
@@ -41140,7 +41140,7 @@
         <v>19</v>
       </c>
       <c r="G1238" s="8">
-        <v>182169599.52</v>
+        <v>182167295.42</v>
       </c>
     </row>
     <row r="1239" spans="1:7" x14ac:dyDescent="0.25">
@@ -41475,17 +41475,17 @@
       <c r="C1253" s="6">
         <v>46262</v>
       </c>
-      <c r="D1253" s="8">
-        <v>0</v>
+      <c r="D1253" s="7">
+        <v>1.618522</v>
       </c>
       <c r="E1253" s="8">
-        <v>0</v>
+        <v>592973692</v>
       </c>
       <c r="F1253" s="9">
         <v>1</v>
       </c>
       <c r="G1253" s="8">
-        <v>0</v>
+        <v>959740973.35</v>
       </c>
     </row>
     <row r="1254" spans="1:7" x14ac:dyDescent="0.25">
@@ -41982,7 +41982,7 @@
         <v>46262</v>
       </c>
       <c r="D1275" s="7">
-        <v>3.927428</v>
+        <v>3.927263</v>
       </c>
       <c r="E1275" s="8">
         <v>35850042</v>
@@ -41991,7 +41991,7 @@
         <v>90</v>
       </c>
       <c r="G1275" s="8">
-        <v>140798460.26</v>
+        <v>140792527.98</v>
       </c>
     </row>
     <row r="1276" spans="1:7" x14ac:dyDescent="0.25">
@@ -42396,7 +42396,7 @@
         <v>46262</v>
       </c>
       <c r="D1293" s="7">
-        <v>11.105352</v>
+        <v>11.105176</v>
       </c>
       <c r="E1293" s="8">
         <v>42625905</v>
@@ -42405,7 +42405,7 @@
         <v>30</v>
       </c>
       <c r="G1293" s="8">
-        <v>473375697.78</v>
+        <v>473368181.28</v>
       </c>
     </row>
     <row r="1294" spans="1:7" x14ac:dyDescent="0.25">
@@ -42510,17 +42510,17 @@
       <c r="C1298" s="6">
         <v>46262</v>
       </c>
-      <c r="D1298" s="8">
-        <v>0</v>
+      <c r="D1298" s="7">
+        <v>19.702561</v>
       </c>
       <c r="E1298" s="8">
-        <v>0</v>
+        <v>83344034</v>
       </c>
       <c r="F1298" s="9">
         <v>3828</v>
       </c>
       <c r="G1298" s="8">
-        <v>0</v>
+        <v>1642090941.37</v>
       </c>
     </row>
     <row r="1299" spans="1:7" x14ac:dyDescent="0.25">
@@ -42580,7 +42580,7 @@
         <v>46262</v>
       </c>
       <c r="D1301" s="7">
-        <v>4.100241</v>
+        <v>4.099818</v>
       </c>
       <c r="E1301" s="8">
         <v>38461067</v>
@@ -42589,7 +42589,7 @@
         <v>589</v>
       </c>
       <c r="G1301" s="8">
-        <v>157699644.27</v>
+        <v>157683379.35</v>
       </c>
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
@@ -42648,8 +42648,8 @@
       <c r="C1304" s="6">
         <v>46262</v>
       </c>
-      <c r="D1304" s="10">
-        <v>8.33877</v>
+      <c r="D1304" s="7">
+        <v>8.338482</v>
       </c>
       <c r="E1304" s="8">
         <v>22549777</v>
@@ -42658,7 +42658,7 @@
         <v>434</v>
       </c>
       <c r="G1304" s="8">
-        <v>188037403.5</v>
+        <v>188030915.94</v>
       </c>
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
@@ -42810,7 +42810,7 @@
         <v>46262</v>
       </c>
       <c r="D1311" s="7">
-        <v>4.126281</v>
+        <v>4.108121</v>
       </c>
       <c r="E1311" s="8">
         <v>11372123</v>
@@ -42819,7 +42819,7 @@
         <v>653</v>
       </c>
       <c r="G1311" s="8">
-        <v>46924570.36</v>
+        <v>46718059.61</v>
       </c>
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
@@ -42833,7 +42833,7 @@
         <v>46262</v>
       </c>
       <c r="D1312" s="7">
-        <v>5.156657</v>
+        <v>5.159657</v>
       </c>
       <c r="E1312" s="8">
         <v>3987691</v>
@@ -42842,7 +42842,7 @@
         <v>232</v>
       </c>
       <c r="G1312" s="8">
-        <v>20563155.21</v>
+        <v>20575117.46</v>
       </c>
     </row>
     <row r="1313" spans="1:7" x14ac:dyDescent="0.25">
@@ -42948,7 +42948,7 @@
         <v>46262</v>
       </c>
       <c r="D1317" s="7">
-        <v>13.087795</v>
+        <v>13.094034</v>
       </c>
       <c r="E1317" s="8">
         <v>360194763</v>
@@ -42957,7 +42957,7 @@
         <v>11151</v>
       </c>
       <c r="G1317" s="8">
-        <v>4714155189.7</v>
+        <v>4716402604.51</v>
       </c>
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
@@ -43155,7 +43155,7 @@
         <v>46262</v>
       </c>
       <c r="D1326" s="7">
-        <v>5.104961</v>
+        <v>5.110789</v>
       </c>
       <c r="E1326" s="8">
         <v>63938438</v>
@@ -43164,7 +43164,7 @@
         <v>502</v>
       </c>
       <c r="G1326" s="8">
-        <v>326403254.3</v>
+        <v>326775840.52</v>
       </c>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
@@ -43431,7 +43431,7 @@
         <v>46262</v>
       </c>
       <c r="D1338" s="7">
-        <v>54.425574</v>
+        <v>54.426658</v>
       </c>
       <c r="E1338" s="8">
         <v>2963162882</v>
@@ -43440,7 +43440,7 @@
         <v>23565</v>
       </c>
       <c r="G1338" s="8">
-        <v>161271841532.49</v>
+        <v>161275053801</v>
       </c>
     </row>
     <row r="1339" spans="1:7" x14ac:dyDescent="0.25">
@@ -43509,7 +43509,7 @@
         <v>414</v>
       </c>
       <c r="G1341" s="8">
-        <v>50977497.47</v>
+        <v>50977497.97</v>
       </c>
     </row>
     <row r="1342" spans="1:7" x14ac:dyDescent="0.25">
@@ -43647,7 +43647,7 @@
         <v>495</v>
       </c>
       <c r="G1347" s="8">
-        <v>36288022.64</v>
+        <v>36288022.84</v>
       </c>
     </row>
     <row r="1348" spans="1:7" x14ac:dyDescent="0.25">
@@ -43684,7 +43684,7 @@
         <v>46262</v>
       </c>
       <c r="D1349" s="7">
-        <v>1.573426</v>
+        <v>1.573427</v>
       </c>
       <c r="E1349" s="8">
         <v>807869008</v>
@@ -43693,7 +43693,7 @@
         <v>56</v>
       </c>
       <c r="G1349" s="8">
-        <v>1271122501.83</v>
+        <v>1271122584.9</v>
       </c>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.25">
@@ -43891,7 +43891,7 @@
         <v>46262</v>
       </c>
       <c r="D1358" s="7">
-        <v>7.458346</v>
+        <v>7.457231</v>
       </c>
       <c r="E1358" s="8">
         <v>451026097</v>
@@ -43900,7 +43900,7 @@
         <v>22324</v>
       </c>
       <c r="G1358" s="8">
-        <v>3363908528.15</v>
+        <v>3363405631.56</v>
       </c>
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.25">
@@ -44098,7 +44098,7 @@
         <v>46262</v>
       </c>
       <c r="D1367" s="7">
-        <v>3.485239</v>
+        <v>3.485801</v>
       </c>
       <c r="E1367" s="8">
         <v>216699590</v>
@@ -44107,7 +44107,7 @@
         <v>3075</v>
       </c>
       <c r="G1367" s="8">
-        <v>755249883.54</v>
+        <v>755371733.09</v>
       </c>
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.25">
@@ -44512,7 +44512,7 @@
         <v>46262</v>
       </c>
       <c r="D1385" s="7">
-        <v>2.366659</v>
+        <v>2.376134</v>
       </c>
       <c r="E1385" s="8">
         <v>49877209</v>
@@ -44521,7 +44521,7 @@
         <v>675</v>
       </c>
       <c r="G1385" s="8">
-        <v>118042343.09</v>
+        <v>118514915.71</v>
       </c>
     </row>
     <row r="1386" spans="1:7" x14ac:dyDescent="0.25">
@@ -44949,7 +44949,7 @@
         <v>46262</v>
       </c>
       <c r="D1404" s="7">
-        <v>2.379638</v>
+        <v>2.377968</v>
       </c>
       <c r="E1404" s="8">
         <v>32113804</v>
@@ -44958,7 +44958,7 @@
         <v>285</v>
       </c>
       <c r="G1404" s="8">
-        <v>76419220.14</v>
+        <v>76365610.77</v>
       </c>
     </row>
     <row r="1405" spans="1:7" x14ac:dyDescent="0.25">
@@ -44972,7 +44972,7 @@
         <v>46262</v>
       </c>
       <c r="D1405" s="7">
-        <v>2.988256</v>
+        <v>2.992732</v>
       </c>
       <c r="E1405" s="8">
         <v>5321377</v>
@@ -44981,7 +44981,7 @@
         <v>92</v>
       </c>
       <c r="G1405" s="8">
-        <v>15901637.37</v>
+        <v>15925453.57</v>
       </c>
     </row>
     <row r="1406" spans="1:7" x14ac:dyDescent="0.25">
@@ -45294,7 +45294,7 @@
         <v>46262</v>
       </c>
       <c r="D1419" s="7">
-        <v>4.001796</v>
+        <v>4.005389</v>
       </c>
       <c r="E1419" s="8">
         <v>120991449</v>
@@ -45303,7 +45303,7 @@
         <v>8119</v>
       </c>
       <c r="G1419" s="8">
-        <v>484183098.9</v>
+        <v>484617780.52</v>
       </c>
     </row>
     <row r="1420" spans="1:7" x14ac:dyDescent="0.25">
@@ -45730,17 +45730,17 @@
       <c r="C1438" s="6">
         <v>46262</v>
       </c>
-      <c r="D1438" s="8">
-        <v>0</v>
+      <c r="D1438" s="7">
+        <v>1.285416</v>
       </c>
       <c r="E1438" s="8">
-        <v>0</v>
+        <v>625886</v>
       </c>
       <c r="F1438" s="9">
         <v>115</v>
       </c>
       <c r="G1438" s="8">
-        <v>0</v>
+        <v>804523.94</v>
       </c>
     </row>
     <row r="1439" spans="1:7" x14ac:dyDescent="0.25">
@@ -46696,17 +46696,17 @@
       <c r="C1480" s="6">
         <v>46262</v>
       </c>
-      <c r="D1480" s="8">
-        <v>0</v>
+      <c r="D1480" s="7">
+        <v>3.199518</v>
       </c>
       <c r="E1480" s="8">
-        <v>0</v>
+        <v>35026443373</v>
       </c>
       <c r="F1480" s="9">
         <v>55015</v>
       </c>
       <c r="G1480" s="8">
-        <v>0</v>
+        <v>112067749579.8</v>
       </c>
     </row>
     <row r="1481" spans="1:7" x14ac:dyDescent="0.25">
@@ -47065,7 +47065,7 @@
         <v>46262</v>
       </c>
       <c r="D1496" s="7">
-        <v>1.844781</v>
+        <v>1.844783</v>
       </c>
       <c r="E1496" s="8">
         <v>129825664</v>
@@ -47074,7 +47074,7 @@
         <v>3623</v>
       </c>
       <c r="G1496" s="8">
-        <v>239499888.49</v>
+        <v>239500241.4</v>
       </c>
     </row>
     <row r="1497" spans="1:7" x14ac:dyDescent="0.25">
@@ -47916,7 +47916,7 @@
         <v>46262</v>
       </c>
       <c r="D1533" s="7">
-        <v>62.014695</v>
+        <v>62.014858</v>
       </c>
       <c r="E1533" s="8">
         <v>2685011</v>
@@ -47925,7 +47925,7 @@
         <v>1</v>
       </c>
       <c r="G1533" s="8">
-        <v>166510139.32</v>
+        <v>166510577.17</v>
       </c>
     </row>
     <row r="1534" spans="1:7" x14ac:dyDescent="0.25">
@@ -48077,7 +48077,7 @@
         <v>46262</v>
       </c>
       <c r="D1540" s="7">
-        <v>22.494798</v>
+        <v>22.495194</v>
       </c>
       <c r="E1540" s="8">
         <v>42798417</v>
@@ -48086,7 +48086,7 @@
         <v>11</v>
       </c>
       <c r="G1540" s="8">
-        <v>962741753.65</v>
+        <v>962758711.24</v>
       </c>
     </row>
     <row r="1541" spans="1:7" x14ac:dyDescent="0.25">
@@ -48122,8 +48122,8 @@
       <c r="C1542" s="6">
         <v>46262</v>
       </c>
-      <c r="D1542" s="7">
-        <v>50.558445</v>
+      <c r="D1542" s="10">
+        <v>50.55849</v>
       </c>
       <c r="E1542" s="8">
         <v>13204342</v>
@@ -48132,7 +48132,7 @@
         <v>121</v>
       </c>
       <c r="G1542" s="8">
-        <v>667590997.14</v>
+        <v>667591594.9</v>
       </c>
     </row>
     <row r="1543" spans="1:7" x14ac:dyDescent="0.25">
@@ -48214,8 +48214,8 @@
       <c r="C1546" s="6">
         <v>46262</v>
       </c>
-      <c r="D1546" s="7">
-        <v>1.120689</v>
+      <c r="D1546" s="10">
+        <v>1.12053</v>
       </c>
       <c r="E1546" s="8">
         <v>26022243</v>
@@ -48224,7 +48224,7 @@
         <v>448</v>
       </c>
       <c r="G1546" s="8">
-        <v>29162837.27</v>
+        <v>29158700.24</v>
       </c>
     </row>
     <row r="1547" spans="1:7" x14ac:dyDescent="0.25">
@@ -48606,7 +48606,7 @@
         <v>46262</v>
       </c>
       <c r="D1563" s="7">
-        <v>56.098065</v>
+        <v>56.098097</v>
       </c>
       <c r="E1563" s="8">
         <v>30990843</v>
@@ -48615,7 +48615,7 @@
         <v>615</v>
       </c>
       <c r="G1563" s="8">
-        <v>1738526331.45</v>
+        <v>1738527309.01</v>
       </c>
     </row>
     <row r="1564" spans="1:7" x14ac:dyDescent="0.25">
@@ -48790,7 +48790,7 @@
         <v>46262</v>
       </c>
       <c r="D1571" s="7">
-        <v>64.397577</v>
+        <v>64.398051</v>
       </c>
       <c r="E1571" s="8">
         <v>1790726</v>
@@ -48799,7 +48799,7 @@
         <v>5</v>
       </c>
       <c r="G1571" s="8">
-        <v>115318415.16</v>
+        <v>115319263.57</v>
       </c>
     </row>
     <row r="1572" spans="1:7" x14ac:dyDescent="0.25">
@@ -48928,7 +48928,7 @@
         <v>46262</v>
       </c>
       <c r="D1577" s="7">
-        <v>63.865376</v>
+        <v>63.865845</v>
       </c>
       <c r="E1577" s="8">
         <v>2740768</v>
@@ -48937,7 +48937,7 @@
         <v>97</v>
       </c>
       <c r="G1577" s="8">
-        <v>175040178.07</v>
+        <v>175041464.56</v>
       </c>
     </row>
     <row r="1578" spans="1:7" x14ac:dyDescent="0.25">
@@ -49365,7 +49365,7 @@
         <v>46262</v>
       </c>
       <c r="D1596" s="7">
-        <v>2.561641</v>
+        <v>2.562385</v>
       </c>
       <c r="E1596" s="8">
         <v>76586945</v>
@@ -49374,7 +49374,7 @@
         <v>4727</v>
       </c>
       <c r="G1596" s="8">
-        <v>196188280.93</v>
+        <v>196245223.44</v>
       </c>
     </row>
     <row r="1597" spans="1:7" x14ac:dyDescent="0.25">
@@ -49433,17 +49433,17 @@
       <c r="C1599" s="6">
         <v>46262</v>
       </c>
-      <c r="D1599" s="8">
-        <v>0</v>
+      <c r="D1599" s="7">
+        <v>1.312221</v>
       </c>
       <c r="E1599" s="8">
-        <v>0</v>
+        <v>300626629</v>
       </c>
       <c r="F1599" s="9">
         <v>1</v>
       </c>
       <c r="G1599" s="8">
-        <v>0</v>
+        <v>394488484.29</v>
       </c>
     </row>
     <row r="1600" spans="1:7" x14ac:dyDescent="0.25">
@@ -49526,7 +49526,7 @@
         <v>46262</v>
       </c>
       <c r="D1603" s="7">
-        <v>49.578919</v>
+        <v>49.579203</v>
       </c>
       <c r="E1603" s="8">
         <v>10546456</v>
@@ -49535,7 +49535,7 @@
         <v>58</v>
       </c>
       <c r="G1603" s="8">
-        <v>522881891.75</v>
+        <v>522884888.01</v>
       </c>
     </row>
     <row r="1604" spans="1:7" x14ac:dyDescent="0.25">
@@ -49663,17 +49663,17 @@
       <c r="C1609" s="6">
         <v>46262</v>
       </c>
-      <c r="D1609" s="8">
-        <v>0</v>
+      <c r="D1609" s="7">
+        <v>1.846933</v>
       </c>
       <c r="E1609" s="8">
-        <v>0</v>
+        <v>220295275</v>
       </c>
       <c r="F1609" s="9">
         <v>752</v>
       </c>
       <c r="G1609" s="8">
-        <v>0</v>
+        <v>406870550.41</v>
       </c>
     </row>
     <row r="1610" spans="1:7" x14ac:dyDescent="0.25">
@@ -49778,17 +49778,17 @@
       <c r="C1614" s="6">
         <v>46262</v>
       </c>
-      <c r="D1614" s="8">
-        <v>0</v>
+      <c r="D1614" s="7">
+        <v>1.039576</v>
       </c>
       <c r="E1614" s="8">
-        <v>0</v>
+        <v>44022769</v>
       </c>
       <c r="F1614" s="9">
         <v>205</v>
       </c>
       <c r="G1614" s="8">
-        <v>0</v>
+        <v>45765028.04</v>
       </c>
     </row>
     <row r="1615" spans="1:7" x14ac:dyDescent="0.25">
@@ -49893,8 +49893,8 @@
       <c r="C1619" s="6">
         <v>46262</v>
       </c>
-      <c r="D1619" s="10">
-        <v>1.42492</v>
+      <c r="D1619" s="7">
+        <v>1.426628</v>
       </c>
       <c r="E1619" s="8">
         <v>22275101</v>
@@ -49903,7 +49903,7 @@
         <v>82</v>
       </c>
       <c r="G1619" s="8">
-        <v>31740243.61</v>
+        <v>31778291.31</v>
       </c>
     </row>
     <row r="1620" spans="1:7" x14ac:dyDescent="0.25">
@@ -49939,17 +49939,17 @@
       <c r="C1621" s="6">
         <v>46262</v>
       </c>
-      <c r="D1621" s="8">
-        <v>0</v>
+      <c r="D1621" s="7">
+        <v>2.011242</v>
       </c>
       <c r="E1621" s="8">
-        <v>0</v>
+        <v>101714237</v>
       </c>
       <c r="F1621" s="9">
         <v>2605</v>
       </c>
       <c r="G1621" s="8">
-        <v>0</v>
+        <v>204571962.08</v>
       </c>
     </row>
     <row r="1622" spans="1:7" x14ac:dyDescent="0.25">
@@ -50031,17 +50031,17 @@
       <c r="C1625" s="6">
         <v>46262</v>
       </c>
-      <c r="D1625" s="8">
-        <v>0</v>
+      <c r="D1625" s="7">
+        <v>1.452006</v>
       </c>
       <c r="E1625" s="8">
-        <v>0</v>
+        <v>272029192</v>
       </c>
       <c r="F1625" s="9">
         <v>35</v>
       </c>
       <c r="G1625" s="8">
-        <v>0</v>
+        <v>394987888.74</v>
       </c>
     </row>
     <row r="1626" spans="1:7" x14ac:dyDescent="0.25">
@@ -50054,17 +50054,17 @@
       <c r="C1626" s="6">
         <v>46262</v>
       </c>
-      <c r="D1626" s="8">
-        <v>0</v>
+      <c r="D1626" s="7">
+        <v>0.953335</v>
       </c>
       <c r="E1626" s="8">
-        <v>0</v>
+        <v>924536</v>
       </c>
       <c r="F1626" s="9">
         <v>11</v>
       </c>
       <c r="G1626" s="8">
-        <v>0</v>
+        <v>881392.54</v>
       </c>
     </row>
     <row r="1627" spans="1:7" x14ac:dyDescent="0.25">
@@ -50077,17 +50077,17 @@
       <c r="C1627" s="6">
         <v>46262</v>
       </c>
-      <c r="D1627" s="8">
-        <v>0</v>
+      <c r="D1627" s="7">
+        <v>0.281628</v>
       </c>
       <c r="E1627" s="8">
-        <v>0</v>
+        <v>211943093</v>
       </c>
       <c r="F1627" s="9">
         <v>13</v>
       </c>
       <c r="G1627" s="8">
-        <v>0</v>
+        <v>59689012.3</v>
       </c>
     </row>
     <row r="1628" spans="1:7" x14ac:dyDescent="0.25">
@@ -50376,8 +50376,8 @@
       <c r="C1640" s="6">
         <v>46262</v>
       </c>
-      <c r="D1640" s="10">
-        <v>1.71347</v>
+      <c r="D1640" s="7">
+        <v>1.713326</v>
       </c>
       <c r="E1640" s="8">
         <v>20274911</v>
@@ -50386,7 +50386,7 @@
         <v>475</v>
       </c>
       <c r="G1640" s="8">
-        <v>34740453.38</v>
+        <v>34737525.53</v>
       </c>
     </row>
     <row r="1641" spans="1:7" x14ac:dyDescent="0.25">
@@ -50537,17 +50537,17 @@
       <c r="C1647" s="6">
         <v>46262</v>
       </c>
-      <c r="D1647" s="10">
-        <v>2.21952</v>
+      <c r="D1647" s="7">
+        <v>2.227377</v>
       </c>
       <c r="E1647" s="8">
-        <v>43284835</v>
+        <v>43415172</v>
       </c>
       <c r="F1647" s="9">
         <v>850</v>
       </c>
       <c r="G1647" s="8">
-        <v>96071542.14</v>
+        <v>96701939.97</v>
       </c>
     </row>
     <row r="1648" spans="1:7" x14ac:dyDescent="0.25">
@@ -50860,7 +50860,7 @@
         <v>46262</v>
       </c>
       <c r="D1661" s="7">
-        <v>1.289463</v>
+        <v>1.294176</v>
       </c>
       <c r="E1661" s="8">
         <v>144484931</v>
@@ -50869,7 +50869,7 @@
         <v>69</v>
       </c>
       <c r="G1661" s="8">
-        <v>186308033.72</v>
+        <v>186988941.46</v>
       </c>
     </row>
     <row r="1662" spans="1:7" x14ac:dyDescent="0.25">
@@ -51343,7 +51343,7 @@
         <v>46262</v>
       </c>
       <c r="D1682" s="7">
-        <v>53.573398</v>
+        <v>53.571024</v>
       </c>
       <c r="E1682" s="8">
         <v>757431582</v>
@@ -51352,7 +51352,7 @@
         <v>10698</v>
       </c>
       <c r="G1682" s="8">
-        <v>40578183489.23</v>
+        <v>40576385304.93</v>
       </c>
     </row>
     <row r="1683" spans="1:7" x14ac:dyDescent="0.25">
@@ -51398,7 +51398,7 @@
         <v>2474</v>
       </c>
       <c r="G1684" s="8">
-        <v>443793205.35</v>
+        <v>443793205.43</v>
       </c>
     </row>
     <row r="1685" spans="1:7" x14ac:dyDescent="0.25">
@@ -51526,17 +51526,17 @@
       <c r="C1690" s="6">
         <v>46262</v>
       </c>
-      <c r="D1690" s="8">
-        <v>0</v>
+      <c r="D1690" s="7">
+        <v>4.584385</v>
       </c>
       <c r="E1690" s="8">
-        <v>0</v>
+        <v>707571922</v>
       </c>
       <c r="F1690" s="9">
         <v>2769</v>
       </c>
       <c r="G1690" s="8">
-        <v>0</v>
+        <v>3243781963.48</v>
       </c>
     </row>
     <row r="1691" spans="1:7" x14ac:dyDescent="0.25">
@@ -51665,7 +51665,7 @@
         <v>46262</v>
       </c>
       <c r="D1696" s="7">
-        <v>60.115187</v>
+        <v>60.114531</v>
       </c>
       <c r="E1696" s="8">
         <v>5459727</v>
@@ -51674,7 +51674,7 @@
         <v>44</v>
       </c>
       <c r="G1696" s="8">
-        <v>328212512.01</v>
+        <v>328208929.68</v>
       </c>
     </row>
     <row r="1697" spans="1:7" x14ac:dyDescent="0.25">
@@ -51733,8 +51733,8 @@
       <c r="C1699" s="6">
         <v>46262</v>
       </c>
-      <c r="D1699" s="10">
-        <v>2.79129</v>
+      <c r="D1699" s="7">
+        <v>2.794762</v>
       </c>
       <c r="E1699" s="8">
         <v>266164817</v>
@@ -51743,7 +51743,7 @@
         <v>1331</v>
       </c>
       <c r="G1699" s="8">
-        <v>742943194.3</v>
+        <v>743867242.13</v>
       </c>
     </row>
     <row r="1700" spans="1:7" x14ac:dyDescent="0.25">
@@ -52423,17 +52423,17 @@
       <c r="C1729" s="6">
         <v>46262</v>
       </c>
-      <c r="D1729" s="8">
-        <v>0</v>
+      <c r="D1729" s="10">
+        <v>5.36483</v>
       </c>
       <c r="E1729" s="8">
-        <v>0</v>
+        <v>10092708</v>
       </c>
       <c r="F1729" s="9">
         <v>539</v>
       </c>
       <c r="G1729" s="8">
-        <v>0</v>
+        <v>54145667.51</v>
       </c>
     </row>
     <row r="1730" spans="1:7" x14ac:dyDescent="0.25">
@@ -52446,17 +52446,17 @@
       <c r="C1730" s="6">
         <v>46262</v>
       </c>
-      <c r="D1730" s="8">
-        <v>0</v>
+      <c r="D1730" s="7">
+        <v>6.590084</v>
       </c>
       <c r="E1730" s="8">
-        <v>0</v>
+        <v>91896783</v>
       </c>
       <c r="F1730" s="9">
         <v>907</v>
       </c>
       <c r="G1730" s="8">
-        <v>0</v>
+        <v>605607533.77</v>
       </c>
     </row>
     <row r="1731" spans="1:7" x14ac:dyDescent="0.25">
@@ -52493,7 +52493,7 @@
         <v>46262</v>
       </c>
       <c r="D1732" s="7">
-        <v>68.903235</v>
+        <v>68.903091</v>
       </c>
       <c r="E1732" s="8">
         <v>33093765</v>
@@ -52502,7 +52502,7 @@
         <v>1839</v>
       </c>
       <c r="G1732" s="8">
-        <v>2280267475.86</v>
+        <v>2280262694.93</v>
       </c>
     </row>
     <row r="1733" spans="1:7" x14ac:dyDescent="0.25">
@@ -52769,7 +52769,7 @@
         <v>46262</v>
       </c>
       <c r="D1744" s="7">
-        <v>9140.087998</v>
+        <v>9140.087628</v>
       </c>
       <c r="E1744" s="8">
         <v>29868637</v>
@@ -52778,7 +52778,7 @@
         <v>110917</v>
       </c>
       <c r="G1744" s="8">
-        <v>273001970565.08</v>
+        <v>273001959511.82</v>
       </c>
     </row>
     <row r="1745" spans="1:7" x14ac:dyDescent="0.25">
@@ -52929,17 +52929,17 @@
       <c r="C1751" s="6">
         <v>46262</v>
       </c>
-      <c r="D1751" s="8">
-        <v>0</v>
+      <c r="D1751" s="7">
+        <v>2.167858</v>
       </c>
       <c r="E1751" s="8">
-        <v>0</v>
+        <v>192164604</v>
       </c>
       <c r="F1751" s="9">
         <v>85</v>
       </c>
       <c r="G1751" s="8">
-        <v>0</v>
+        <v>416585650.96</v>
       </c>
     </row>
     <row r="1752" spans="1:7" x14ac:dyDescent="0.25">
@@ -52953,7 +52953,7 @@
         <v>46262</v>
       </c>
       <c r="D1752" s="7">
-        <v>1.436577</v>
+        <v>1.438365</v>
       </c>
       <c r="E1752" s="8">
         <v>41252029</v>
@@ -52962,7 +52962,7 @@
         <v>90</v>
       </c>
       <c r="G1752" s="8">
-        <v>59261726.5</v>
+        <v>59335482.29</v>
       </c>
     </row>
     <row r="1753" spans="1:7" x14ac:dyDescent="0.25">
@@ -52976,7 +52976,7 @@
         <v>46262</v>
       </c>
       <c r="D1753" s="7">
-        <v>10.161825</v>
+        <v>10.161824</v>
       </c>
       <c r="E1753" s="8">
         <v>3990285712</v>
@@ -52985,7 +52985,7 @@
         <v>13449</v>
       </c>
       <c r="G1753" s="8">
-        <v>40548585599.99</v>
+        <v>40548582128.07</v>
       </c>
     </row>
     <row r="1754" spans="1:7" x14ac:dyDescent="0.25">
@@ -53021,8 +53021,8 @@
       <c r="C1755" s="6">
         <v>46262</v>
       </c>
-      <c r="D1755" s="10">
-        <v>50.35515</v>
+      <c r="D1755" s="7">
+        <v>50.354609</v>
       </c>
       <c r="E1755" s="8">
         <v>14127751</v>
@@ -53031,7 +53031,7 @@
         <v>82</v>
       </c>
       <c r="G1755" s="8">
-        <v>711405022.05</v>
+        <v>711397377.32</v>
       </c>
     </row>
     <row r="1756" spans="1:7" x14ac:dyDescent="0.25">
@@ -53113,17 +53113,17 @@
       <c r="C1759" s="6">
         <v>46262</v>
       </c>
-      <c r="D1759" s="8">
-        <v>0</v>
+      <c r="D1759" s="7">
+        <v>11.440705</v>
       </c>
       <c r="E1759" s="8">
-        <v>0</v>
+        <v>687434886</v>
       </c>
       <c r="F1759" s="9">
         <v>2696</v>
       </c>
       <c r="G1759" s="8">
-        <v>0</v>
+        <v>7864739742.91</v>
       </c>
     </row>
     <row r="1760" spans="1:7" x14ac:dyDescent="0.25">
@@ -53206,7 +53206,7 @@
         <v>46262</v>
       </c>
       <c r="D1763" s="7">
-        <v>59.608846</v>
+        <v>59.607039</v>
       </c>
       <c r="E1763" s="8">
         <v>415501632</v>
@@ -53215,7 +53215,7 @@
         <v>6962</v>
       </c>
       <c r="G1763" s="8">
-        <v>24767573001.36</v>
+        <v>24766821816.54</v>
       </c>
     </row>
     <row r="1764" spans="1:7" x14ac:dyDescent="0.25">
@@ -53252,7 +53252,7 @@
         <v>46262</v>
       </c>
       <c r="D1765" s="7">
-        <v>68.355581</v>
+        <v>68.354785</v>
       </c>
       <c r="E1765" s="8">
         <v>5611179</v>
@@ -53261,7 +53261,7 @@
         <v>1</v>
       </c>
       <c r="G1765" s="8">
-        <v>383555402.21</v>
+        <v>383550936.87</v>
       </c>
     </row>
     <row r="1766" spans="1:7" x14ac:dyDescent="0.25">
@@ -53297,17 +53297,17 @@
       <c r="C1767" s="6">
         <v>46262</v>
       </c>
-      <c r="D1767" s="8">
-        <v>0</v>
+      <c r="D1767" s="7">
+        <v>13.606536</v>
       </c>
       <c r="E1767" s="8">
-        <v>0</v>
+        <v>444685422</v>
       </c>
       <c r="F1767" s="9">
         <v>12403</v>
       </c>
       <c r="G1767" s="8">
-        <v>0</v>
+        <v>6050628249.7</v>
       </c>
     </row>
     <row r="1768" spans="1:7" x14ac:dyDescent="0.25">
@@ -53389,17 +53389,17 @@
       <c r="C1771" s="6">
         <v>46262</v>
       </c>
-      <c r="D1771" s="8">
-        <v>0</v>
+      <c r="D1771" s="7">
+        <v>21.314756</v>
       </c>
       <c r="E1771" s="8">
-        <v>0</v>
+        <v>23495459.01</v>
       </c>
       <c r="F1771" s="9">
         <v>1517</v>
       </c>
       <c r="G1771" s="8">
-        <v>0</v>
+        <v>500799973.53</v>
       </c>
     </row>
     <row r="1772" spans="1:7" x14ac:dyDescent="0.25">
@@ -53435,17 +53435,17 @@
       <c r="C1773" s="6">
         <v>46262</v>
       </c>
-      <c r="D1773" s="8">
-        <v>0</v>
+      <c r="D1773" s="7">
+        <v>78.964466</v>
       </c>
       <c r="E1773" s="8">
-        <v>0</v>
+        <v>23934000</v>
       </c>
       <c r="F1773" s="9">
         <v>390</v>
       </c>
       <c r="G1773" s="8">
-        <v>0</v>
+        <v>1889935537.89</v>
       </c>
     </row>
     <row r="1774" spans="1:7" x14ac:dyDescent="0.25">
@@ -53758,7 +53758,7 @@
         <v>46262</v>
       </c>
       <c r="D1787" s="7">
-        <v>51.701251</v>
+        <v>51.701048</v>
       </c>
       <c r="E1787" s="8">
         <v>17213905</v>
@@ -53767,7 +53767,7 @@
         <v>105</v>
       </c>
       <c r="G1787" s="8">
-        <v>889980429.49</v>
+        <v>889976925.02</v>
       </c>
     </row>
     <row r="1788" spans="1:7" x14ac:dyDescent="0.25">
@@ -53849,8 +53849,8 @@
       <c r="C1791" s="6">
         <v>46262</v>
       </c>
-      <c r="D1791" s="7">
-        <v>1.536803</v>
+      <c r="D1791" s="10">
+        <v>1.53686</v>
       </c>
       <c r="E1791" s="8">
         <v>10458780176.21</v>
@@ -53859,7 +53859,7 @@
         <v>31508</v>
       </c>
       <c r="G1791" s="8">
-        <v>16073083618.45</v>
+        <v>16073676881.45</v>
       </c>
     </row>
     <row r="1792" spans="1:7" x14ac:dyDescent="0.25">
@@ -53896,7 +53896,7 @@
         <v>46262</v>
       </c>
       <c r="D1793" s="7">
-        <v>2.954653</v>
+        <v>2.960797</v>
       </c>
       <c r="E1793" s="8">
         <v>3714513</v>
@@ -53905,7 +53905,7 @@
         <v>534</v>
       </c>
       <c r="G1793" s="8">
-        <v>10975098.6</v>
+        <v>10997917.46</v>
       </c>
     </row>
     <row r="1794" spans="1:7" x14ac:dyDescent="0.25">
@@ -54724,7 +54724,7 @@
         <v>46262</v>
       </c>
       <c r="D1829" s="7">
-        <v>9.322835</v>
+        <v>9.318084</v>
       </c>
       <c r="E1829" s="8">
         <v>35253165</v>
@@ -54733,7 +54733,7 @@
         <v>39</v>
       </c>
       <c r="G1829" s="8">
-        <v>328659431.3</v>
+        <v>328491965.6</v>
       </c>
     </row>
     <row r="1830" spans="1:7" x14ac:dyDescent="0.25">
@@ -54770,16 +54770,16 @@
         <v>46262</v>
       </c>
       <c r="D1831" s="7">
-        <v>6.374296</v>
+        <v>6.385621</v>
       </c>
       <c r="E1831" s="8">
-        <v>703086995</v>
+        <v>252840995</v>
       </c>
       <c r="F1831" s="9">
         <v>12</v>
       </c>
       <c r="G1831" s="8">
-        <v>4481684787.87</v>
+        <v>1614546729.5</v>
       </c>
     </row>
     <row r="1832" spans="1:7" x14ac:dyDescent="0.25">
@@ -55275,17 +55275,17 @@
       <c r="C1853" s="6">
         <v>46262</v>
       </c>
-      <c r="D1853" s="8">
-        <v>0</v>
+      <c r="D1853" s="7">
+        <v>14.914224</v>
       </c>
       <c r="E1853" s="8">
-        <v>0</v>
+        <v>370648912</v>
       </c>
       <c r="F1853" s="9">
         <v>9831</v>
       </c>
       <c r="G1853" s="8">
-        <v>0</v>
+        <v>5527940772.63</v>
       </c>
     </row>
     <row r="1854" spans="1:7" x14ac:dyDescent="0.25">
@@ -55344,17 +55344,17 @@
       <c r="C1856" s="6">
         <v>46262</v>
       </c>
-      <c r="D1856" s="8">
-        <v>0</v>
+      <c r="D1856" s="7">
+        <v>14.654924</v>
       </c>
       <c r="E1856" s="8">
-        <v>0</v>
+        <v>127205946</v>
       </c>
       <c r="F1856" s="9">
         <v>3578</v>
       </c>
       <c r="G1856" s="8">
-        <v>0</v>
+        <v>1864193500.99</v>
       </c>
     </row>
     <row r="1857" spans="1:7" x14ac:dyDescent="0.25">
@@ -55597,17 +55597,17 @@
       <c r="C1867" s="6">
         <v>46262</v>
       </c>
-      <c r="D1867" s="8">
-        <v>0</v>
+      <c r="D1867" s="10">
+        <v>2.73061</v>
       </c>
       <c r="E1867" s="8">
-        <v>0</v>
+        <v>39969656</v>
       </c>
       <c r="F1867" s="9">
         <v>114</v>
       </c>
       <c r="G1867" s="8">
-        <v>0</v>
+        <v>109141548.02</v>
       </c>
     </row>
     <row r="1868" spans="1:7" x14ac:dyDescent="0.25">
@@ -55690,7 +55690,7 @@
         <v>46262</v>
       </c>
       <c r="D1871" s="7">
-        <v>4.134225</v>
+        <v>4.139307</v>
       </c>
       <c r="E1871" s="8">
         <v>77561746</v>
@@ -55699,7 +55699,7 @@
         <v>278</v>
       </c>
       <c r="G1871" s="8">
-        <v>320657747.07</v>
+        <v>321051904.86</v>
       </c>
     </row>
     <row r="1872" spans="1:7" x14ac:dyDescent="0.25">
@@ -55804,17 +55804,17 @@
       <c r="C1876" s="6">
         <v>46262</v>
       </c>
-      <c r="D1876" s="8">
-        <v>0</v>
+      <c r="D1876" s="7">
+        <v>1.935597</v>
       </c>
       <c r="E1876" s="8">
-        <v>0</v>
+        <v>678686262</v>
       </c>
       <c r="F1876" s="9">
         <v>2</v>
       </c>
       <c r="G1876" s="8">
-        <v>0</v>
+        <v>1313663194.5</v>
       </c>
     </row>
     <row r="1877" spans="1:7" x14ac:dyDescent="0.25">
@@ -56172,17 +56172,17 @@
       <c r="C1892" s="6">
         <v>46262</v>
       </c>
-      <c r="D1892" s="8">
-        <v>0</v>
+      <c r="D1892" s="7">
+        <v>2.693931</v>
       </c>
       <c r="E1892" s="8">
-        <v>0</v>
+        <v>867263322</v>
       </c>
       <c r="F1892" s="9">
         <v>16722</v>
       </c>
       <c r="G1892" s="8">
-        <v>0</v>
+        <v>2336347132.07</v>
       </c>
     </row>
     <row r="1893" spans="1:7" x14ac:dyDescent="0.25">
@@ -56264,17 +56264,17 @@
       <c r="C1896" s="6">
         <v>46262</v>
       </c>
-      <c r="D1896" s="8">
-        <v>0</v>
+      <c r="D1896" s="7">
+        <v>5.764368</v>
       </c>
       <c r="E1896" s="8">
-        <v>0</v>
+        <v>180446965</v>
       </c>
       <c r="F1896" s="9">
         <v>14121</v>
       </c>
       <c r="G1896" s="8">
-        <v>0</v>
+        <v>1040162681.57</v>
       </c>
     </row>
     <row r="1897" spans="1:7" x14ac:dyDescent="0.25">
@@ -56609,17 +56609,17 @@
       <c r="C1911" s="6">
         <v>46262</v>
       </c>
-      <c r="D1911" s="8">
-        <v>0</v>
+      <c r="D1911" s="7">
+        <v>1.031023</v>
       </c>
       <c r="E1911" s="8">
-        <v>0</v>
+        <v>371036</v>
       </c>
       <c r="F1911" s="9">
         <v>169</v>
       </c>
       <c r="G1911" s="8">
-        <v>0</v>
+        <v>382546.47</v>
       </c>
     </row>
     <row r="1912" spans="1:7" x14ac:dyDescent="0.25">
@@ -57092,17 +57092,17 @@
       <c r="C1932" s="6">
         <v>46262</v>
       </c>
-      <c r="D1932" s="8">
-        <v>0</v>
+      <c r="D1932" s="7">
+        <v>8.048745</v>
       </c>
       <c r="E1932" s="8">
-        <v>0</v>
+        <v>699606102</v>
       </c>
       <c r="F1932" s="9">
         <v>3353</v>
       </c>
       <c r="G1932" s="8">
-        <v>0</v>
+        <v>5630951216.65</v>
       </c>
     </row>
     <row r="1933" spans="1:7" x14ac:dyDescent="0.25">
@@ -57253,17 +57253,17 @@
       <c r="C1939" s="6">
         <v>46262</v>
       </c>
-      <c r="D1939" s="8">
-        <v>0</v>
+      <c r="D1939" s="7">
+        <v>0.967099</v>
       </c>
       <c r="E1939" s="8">
-        <v>0</v>
+        <v>1842783437</v>
       </c>
       <c r="F1939" s="9">
         <v>14899</v>
       </c>
       <c r="G1939" s="8">
-        <v>0</v>
+        <v>1782153351.12</v>
       </c>
     </row>
     <row r="1940" spans="1:7" x14ac:dyDescent="0.25">
@@ -57713,17 +57713,17 @@
       <c r="C1959" s="6">
         <v>46262</v>
       </c>
-      <c r="D1959" s="8">
-        <v>0</v>
+      <c r="D1959" s="7">
+        <v>13.784055</v>
       </c>
       <c r="E1959" s="8">
-        <v>0</v>
+        <v>833210187</v>
       </c>
       <c r="F1959" s="9">
         <v>60891</v>
       </c>
       <c r="G1959" s="8">
-        <v>0</v>
+        <v>11485014768</v>
       </c>
     </row>
     <row r="1960" spans="1:7" x14ac:dyDescent="0.25">
@@ -58266,7 +58266,7 @@
         <v>46262</v>
       </c>
       <c r="D1983" s="7">
-        <v>4.097611</v>
+        <v>4.098266</v>
       </c>
       <c r="E1983" s="8">
         <v>159553100</v>
@@ -58275,7 +58275,7 @@
         <v>6551</v>
       </c>
       <c r="G1983" s="8">
-        <v>653786534.74</v>
+        <v>653891093.03</v>
       </c>
     </row>
     <row r="1984" spans="1:7" x14ac:dyDescent="0.25">
@@ -58817,8 +58817,8 @@
       <c r="C2007" s="6">
         <v>46262</v>
       </c>
-      <c r="D2007" s="7">
-        <v>1.915961</v>
+      <c r="D2007" s="10">
+        <v>1.91617</v>
       </c>
       <c r="E2007" s="8">
         <v>306521428</v>
@@ -58827,7 +58827,7 @@
         <v>11</v>
       </c>
       <c r="G2007" s="8">
-        <v>587283165.87</v>
+        <v>587347126.37</v>
       </c>
     </row>
     <row r="2008" spans="1:7" x14ac:dyDescent="0.25">
@@ -58863,8 +58863,8 @@
       <c r="C2009" s="6">
         <v>46262</v>
       </c>
-      <c r="D2009" s="10">
-        <v>5.83962</v>
+      <c r="D2009" s="7">
+        <v>5.835476</v>
       </c>
       <c r="E2009" s="8">
         <v>106786382</v>
@@ -58873,7 +58873,7 @@
         <v>1</v>
       </c>
       <c r="G2009" s="8">
-        <v>623591924.49</v>
+        <v>623149406.19</v>
       </c>
     </row>
     <row r="2010" spans="1:7" x14ac:dyDescent="0.25">
@@ -59025,7 +59025,7 @@
         <v>46262</v>
       </c>
       <c r="D2016" s="7">
-        <v>19.848696</v>
+        <v>19.849309</v>
       </c>
       <c r="E2016" s="8">
         <v>165041352</v>
@@ -59034,7 +59034,7 @@
         <v>2782</v>
       </c>
       <c r="G2016" s="8">
-        <v>3275855580.61</v>
+        <v>3275956863.63</v>
       </c>
     </row>
     <row r="2017" spans="1:7" x14ac:dyDescent="0.25">
@@ -59301,7 +59301,7 @@
         <v>46262</v>
       </c>
       <c r="D2028" s="7">
-        <v>12.169113</v>
+        <v>12.169782</v>
       </c>
       <c r="E2028" s="8">
         <v>299315692</v>
@@ -59310,7 +59310,7 @@
         <v>24</v>
       </c>
       <c r="G2028" s="8">
-        <v>3642406485.7</v>
+        <v>3642606689.31</v>
       </c>
     </row>
     <row r="2029" spans="1:7" x14ac:dyDescent="0.25">
@@ -59324,7 +59324,7 @@
         <v>46262</v>
       </c>
       <c r="D2029" s="7">
-        <v>53.250508</v>
+        <v>53.309862</v>
       </c>
       <c r="E2029" s="8">
         <v>781339</v>
@@ -59333,7 +59333,7 @@
         <v>1604</v>
       </c>
       <c r="G2029" s="8">
-        <v>41606699.01</v>
+        <v>41653074.57</v>
       </c>
     </row>
     <row r="2030" spans="1:7" x14ac:dyDescent="0.25">
@@ -59347,7 +59347,7 @@
         <v>46262</v>
       </c>
       <c r="D2030" s="7">
-        <v>4.374712</v>
+        <v>4.374535</v>
       </c>
       <c r="E2030" s="8">
         <v>11329800</v>
@@ -59356,7 +59356,7 @@
         <v>916</v>
       </c>
       <c r="G2030" s="8">
-        <v>49564610.79</v>
+        <v>49562601.78</v>
       </c>
     </row>
     <row r="2031" spans="1:7" x14ac:dyDescent="0.25">
@@ -59416,7 +59416,7 @@
         <v>46262</v>
       </c>
       <c r="D2033" s="7">
-        <v>7.632361</v>
+        <v>7.630821</v>
       </c>
       <c r="E2033" s="8">
         <v>274862095</v>
@@ -59425,7 +59425,7 @@
         <v>1</v>
       </c>
       <c r="G2033" s="8">
-        <v>2097846664.31</v>
+        <v>2097423355.67</v>
       </c>
     </row>
     <row r="2034" spans="1:7" x14ac:dyDescent="0.25">
@@ -59439,7 +59439,7 @@
         <v>46262</v>
       </c>
       <c r="D2034" s="7">
-        <v>1.349021</v>
+        <v>1.343968</v>
       </c>
       <c r="E2034" s="8">
         <v>29110294</v>
@@ -59448,7 +59448,7 @@
         <v>1030</v>
       </c>
       <c r="G2034" s="8">
-        <v>39270400.17</v>
+        <v>39123289.16</v>
       </c>
     </row>
     <row r="2035" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>01.09.2026 09:28:43</t>
+    <t>01.09.2026 10:48:31</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -13149,7 +13149,7 @@
         <v>1478</v>
       </c>
       <c r="G21" s="8">
-        <v>349893753.06</v>
+        <v>349893731.11</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -13553,8 +13553,8 @@
       <c r="C39" s="6">
         <v>46266</v>
       </c>
-      <c r="D39" s="7">
-        <v>21.972583</v>
+      <c r="D39" s="10">
+        <v>21.86905</v>
       </c>
       <c r="E39" s="8">
         <v>6111603</v>
@@ -13563,7 +13563,7 @@
         <v>194</v>
       </c>
       <c r="G39" s="8">
-        <v>134287706.95</v>
+        <v>133654951.28</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -13576,8 +13576,8 @@
       <c r="C40" s="6">
         <v>46266</v>
       </c>
-      <c r="D40" s="7">
-        <v>31.616977</v>
+      <c r="D40" s="10">
+        <v>31.65063</v>
       </c>
       <c r="E40" s="8">
         <v>4911820</v>
@@ -13586,7 +13586,7 @@
         <v>14</v>
       </c>
       <c r="G40" s="8">
-        <v>155296899.97</v>
+        <v>155462197.49</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -15394,7 +15394,7 @@
         <v>46266</v>
       </c>
       <c r="D119" s="7">
-        <v>1.829415</v>
+        <v>1.816621</v>
       </c>
       <c r="E119" s="8">
         <v>5607494</v>
@@ -15403,7 +15403,7 @@
         <v>56</v>
       </c>
       <c r="G119" s="8">
-        <v>10258436.19</v>
+        <v>10186693.81</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -15647,7 +15647,7 @@
         <v>46266</v>
       </c>
       <c r="D130" s="7">
-        <v>2.372933</v>
+        <v>2.372942</v>
       </c>
       <c r="E130" s="8">
         <v>1005188803</v>
@@ -15656,7 +15656,7 @@
         <v>443</v>
       </c>
       <c r="G130" s="8">
-        <v>2385245217.26</v>
+        <v>2385254897.37</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -15909,7 +15909,7 @@
         <v>229</v>
       </c>
       <c r="G141" s="8">
-        <v>3600663169.35</v>
+        <v>3600662788.59</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -16152,8 +16152,8 @@
       <c r="C152" s="6">
         <v>46266</v>
       </c>
-      <c r="D152" s="10">
-        <v>1.20533</v>
+      <c r="D152" s="7">
+        <v>1.205341</v>
       </c>
       <c r="E152" s="8">
         <v>49026108</v>
@@ -16162,7 +16162,7 @@
         <v>175</v>
       </c>
       <c r="G152" s="8">
-        <v>59092618.86</v>
+        <v>59093155.38</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -16406,7 +16406,7 @@
         <v>46266</v>
       </c>
       <c r="D163" s="7">
-        <v>1.633774</v>
+        <v>1.621716</v>
       </c>
       <c r="E163" s="8">
         <v>53308229</v>
@@ -16415,7 +16415,7 @@
         <v>1086</v>
       </c>
       <c r="G163" s="8">
-        <v>87093618.47</v>
+        <v>86450801.56</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -16461,7 +16461,7 @@
         <v>15</v>
       </c>
       <c r="G165" s="8">
-        <v>5738999015.39</v>
+        <v>5738999025.54</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -16612,8 +16612,8 @@
       <c r="C172" s="6">
         <v>46266</v>
       </c>
-      <c r="D172" s="10">
-        <v>1.20214</v>
+      <c r="D172" s="7">
+        <v>1.202139</v>
       </c>
       <c r="E172" s="8">
         <v>301031114</v>
@@ -16622,7 +16622,7 @@
         <v>90</v>
       </c>
       <c r="G172" s="8">
-        <v>361881573.69</v>
+        <v>361881270.68</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -16704,8 +16704,8 @@
       <c r="C176" s="6">
         <v>46266</v>
       </c>
-      <c r="D176" s="7">
-        <v>1.793671</v>
+      <c r="D176" s="10">
+        <v>1.79369</v>
       </c>
       <c r="E176" s="8">
         <v>1336351562</v>
@@ -16714,7 +16714,7 @@
         <v>2801</v>
       </c>
       <c r="G176" s="8">
-        <v>2396974591.84</v>
+        <v>2397000689.77</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -18324,7 +18324,7 @@
         <v>742</v>
       </c>
       <c r="G246" s="8">
-        <v>1529703244.8</v>
+        <v>1529703377.47</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -19060,7 +19060,7 @@
         <v>259</v>
       </c>
       <c r="G278" s="8">
-        <v>4036066815.65</v>
+        <v>4036066815.67</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -19120,7 +19120,7 @@
         <v>46266</v>
       </c>
       <c r="D281" s="7">
-        <v>5.367779</v>
+        <v>5.317894</v>
       </c>
       <c r="E281" s="8">
         <v>4813626</v>
@@ -19129,7 +19129,7 @@
         <v>1132</v>
       </c>
       <c r="G281" s="8">
-        <v>25838481.45</v>
+        <v>25598354.08</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -19189,7 +19189,7 @@
         <v>46266</v>
       </c>
       <c r="D284" s="7">
-        <v>1.166295</v>
+        <v>1.166071</v>
       </c>
       <c r="E284" s="8">
         <v>66620064</v>
@@ -19198,7 +19198,7 @@
         <v>774</v>
       </c>
       <c r="G284" s="8">
-        <v>77698671.03</v>
+        <v>77683724.29</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -19672,7 +19672,7 @@
         <v>46266</v>
       </c>
       <c r="D305" s="7">
-        <v>7.050765</v>
+        <v>7.038125</v>
       </c>
       <c r="E305" s="8">
         <v>445431221</v>
@@ -19681,7 +19681,7 @@
         <v>15269</v>
       </c>
       <c r="G305" s="8">
-        <v>3140630973.97</v>
+        <v>3135000498.86</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -19902,7 +19902,7 @@
         <v>46266</v>
       </c>
       <c r="D315" s="7">
-        <v>53.245225</v>
+        <v>53.260129</v>
       </c>
       <c r="E315" s="8">
         <v>27097875</v>
@@ -19911,7 +19911,7 @@
         <v>1076</v>
       </c>
       <c r="G315" s="8">
-        <v>1442832441.79</v>
+        <v>1443236321.85</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -20201,7 +20201,7 @@
         <v>46266</v>
       </c>
       <c r="D328" s="7">
-        <v>75.160979</v>
+        <v>75.182931</v>
       </c>
       <c r="E328" s="8">
         <v>7294243</v>
@@ -20210,7 +20210,7 @@
         <v>3</v>
       </c>
       <c r="G328" s="8">
-        <v>548242444.97</v>
+        <v>548402566.48</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -20477,7 +20477,7 @@
         <v>46266</v>
       </c>
       <c r="D340" s="7">
-        <v>103.157655</v>
+        <v>103.162245</v>
       </c>
       <c r="E340" s="8">
         <v>22490084</v>
@@ -20486,7 +20486,7 @@
         <v>1</v>
       </c>
       <c r="G340" s="8">
-        <v>2320024322.66</v>
+        <v>2320127548.7</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -20753,7 +20753,7 @@
         <v>46266</v>
       </c>
       <c r="D352" s="7">
-        <v>15.062702</v>
+        <v>14.961294</v>
       </c>
       <c r="E352" s="8">
         <v>9842381</v>
@@ -20762,7 +20762,7 @@
         <v>1176</v>
       </c>
       <c r="G352" s="8">
-        <v>148252847.12</v>
+        <v>147254751.87</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -20845,7 +20845,7 @@
         <v>46266</v>
       </c>
       <c r="D356" s="7">
-        <v>1.462639</v>
+        <v>1.462522</v>
       </c>
       <c r="E356" s="8">
         <v>41180899</v>
@@ -20854,7 +20854,7 @@
         <v>2746</v>
       </c>
       <c r="G356" s="8">
-        <v>60232779.87</v>
+        <v>60227961.81</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
@@ -22615,8 +22615,8 @@
       <c r="C433" s="6">
         <v>46266</v>
       </c>
-      <c r="D433" s="7">
-        <v>5.513009</v>
+      <c r="D433" s="12">
+        <v>5.5126</v>
       </c>
       <c r="E433" s="8">
         <v>426605660</v>
@@ -22625,7 +22625,7 @@
         <v>414</v>
       </c>
       <c r="G433" s="8">
-        <v>2351881025.66</v>
+        <v>2351706563.53</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
@@ -22960,8 +22960,8 @@
       <c r="C448" s="6">
         <v>46266</v>
       </c>
-      <c r="D448" s="10">
-        <v>7.91223</v>
+      <c r="D448" s="7">
+        <v>7.825038</v>
       </c>
       <c r="E448" s="8">
         <v>255782022</v>
@@ -22970,7 +22970,7 @@
         <v>2391</v>
       </c>
       <c r="G448" s="8">
-        <v>2023806148.3</v>
+        <v>2001504153.61</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
@@ -23489,8 +23489,8 @@
       <c r="C471" s="6">
         <v>46266</v>
       </c>
-      <c r="D471" s="10">
-        <v>0.20825</v>
+      <c r="D471" s="7">
+        <v>0.207874</v>
       </c>
       <c r="E471" s="8">
         <v>52565477671.04</v>
@@ -23499,7 +23499,7 @@
         <v>6553</v>
       </c>
       <c r="G471" s="8">
-        <v>10946735955.23</v>
+        <v>10927010344.56</v>
       </c>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
@@ -23697,7 +23697,7 @@
         <v>46266</v>
       </c>
       <c r="D480" s="7">
-        <v>69.570993</v>
+        <v>69.639638</v>
       </c>
       <c r="E480" s="8">
         <v>1920992517</v>
@@ -23706,7 +23706,7 @@
         <v>19444</v>
       </c>
       <c r="G480" s="8">
-        <v>133645356086.46</v>
+        <v>133777223196.79</v>
       </c>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
@@ -23996,7 +23996,7 @@
         <v>46266</v>
       </c>
       <c r="D493" s="7">
-        <v>4.861836</v>
+        <v>4.857019</v>
       </c>
       <c r="E493" s="8">
         <v>77399731</v>
@@ -24005,7 +24005,7 @@
         <v>542</v>
       </c>
       <c r="G493" s="8">
-        <v>376304807.3</v>
+        <v>375931980.96</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
@@ -24110,17 +24110,17 @@
       <c r="C498" s="6">
         <v>46266</v>
       </c>
-      <c r="D498" s="8">
-        <v>0</v>
+      <c r="D498" s="7">
+        <v>1.411249</v>
       </c>
       <c r="E498" s="8">
-        <v>0</v>
+        <v>884687150</v>
       </c>
       <c r="F498" s="9">
         <v>5421</v>
       </c>
       <c r="G498" s="8">
-        <v>0</v>
+        <v>1248513953.36</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
@@ -24594,7 +24594,7 @@
         <v>46266</v>
       </c>
       <c r="D519" s="7">
-        <v>5.791912</v>
+        <v>5.743058</v>
       </c>
       <c r="E519" s="8">
         <v>203899642.63</v>
@@ -24603,7 +24603,7 @@
         <v>2118</v>
       </c>
       <c r="G519" s="8">
-        <v>1180968765.95</v>
+        <v>1171007428.74</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
@@ -24754,17 +24754,17 @@
       <c r="C526" s="6">
         <v>46266</v>
       </c>
-      <c r="D526" s="8">
-        <v>0</v>
+      <c r="D526" s="7">
+        <v>12.756526</v>
       </c>
       <c r="E526" s="8">
-        <v>0</v>
+        <v>29091659</v>
       </c>
       <c r="F526" s="9">
         <v>2701</v>
       </c>
       <c r="G526" s="8">
-        <v>0</v>
+        <v>371108506.41</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
@@ -24869,17 +24869,17 @@
       <c r="C531" s="6">
         <v>46266</v>
       </c>
-      <c r="D531" s="8">
-        <v>0</v>
+      <c r="D531" s="7">
+        <v>67.454877</v>
       </c>
       <c r="E531" s="8">
-        <v>0</v>
+        <v>32360328</v>
       </c>
       <c r="F531" s="9">
         <v>5</v>
       </c>
       <c r="G531" s="8">
-        <v>0</v>
+        <v>2182861945.79</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
@@ -24892,17 +24892,17 @@
       <c r="C532" s="6">
         <v>46266</v>
       </c>
-      <c r="D532" s="8">
-        <v>0</v>
+      <c r="D532" s="7">
+        <v>63.141194</v>
       </c>
       <c r="E532" s="8">
-        <v>0</v>
+        <v>3941000</v>
       </c>
       <c r="F532" s="9">
         <v>1</v>
       </c>
       <c r="G532" s="8">
-        <v>0</v>
+        <v>248839447.14</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
@@ -25100,7 +25100,7 @@
         <v>46266</v>
       </c>
       <c r="D541" s="7">
-        <v>3.584631</v>
+        <v>3.583537</v>
       </c>
       <c r="E541" s="8">
         <v>352503539</v>
@@ -25109,7 +25109,7 @@
         <v>3287</v>
       </c>
       <c r="G541" s="8">
-        <v>1263595070.44</v>
+        <v>1263209408.71</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
@@ -25145,17 +25145,17 @@
       <c r="C543" s="6">
         <v>46266</v>
       </c>
-      <c r="D543" s="8">
-        <v>0</v>
+      <c r="D543" s="7">
+        <v>6.131891</v>
       </c>
       <c r="E543" s="8">
-        <v>0</v>
+        <v>222060386</v>
       </c>
       <c r="F543" s="9">
         <v>2</v>
       </c>
       <c r="G543" s="8">
-        <v>0</v>
+        <v>1361649996.85</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -25214,17 +25214,17 @@
       <c r="C546" s="6">
         <v>46266</v>
       </c>
-      <c r="D546" s="8">
-        <v>0</v>
+      <c r="D546" s="7">
+        <v>61.364974</v>
       </c>
       <c r="E546" s="8">
-        <v>0</v>
+        <v>194715</v>
       </c>
       <c r="F546" s="9">
         <v>1</v>
       </c>
       <c r="G546" s="8">
-        <v>0</v>
+        <v>11948680.85</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
@@ -25237,17 +25237,17 @@
       <c r="C547" s="6">
         <v>46266</v>
       </c>
-      <c r="D547" s="8">
-        <v>0</v>
+      <c r="D547" s="7">
+        <v>62.361344</v>
       </c>
       <c r="E547" s="8">
-        <v>0</v>
+        <v>8101428</v>
       </c>
       <c r="F547" s="9">
         <v>4</v>
       </c>
       <c r="G547" s="8">
-        <v>0</v>
+        <v>505215939.11</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
@@ -25260,17 +25260,17 @@
       <c r="C548" s="6">
         <v>46266</v>
       </c>
-      <c r="D548" s="8">
-        <v>0</v>
+      <c r="D548" s="7">
+        <v>67.213574</v>
       </c>
       <c r="E548" s="8">
-        <v>0</v>
+        <v>23236050</v>
       </c>
       <c r="F548" s="9">
         <v>1</v>
       </c>
       <c r="G548" s="8">
-        <v>0</v>
+        <v>1561777965.03</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
@@ -25283,17 +25283,17 @@
       <c r="C549" s="6">
         <v>46266</v>
       </c>
-      <c r="D549" s="8">
-        <v>0</v>
+      <c r="D549" s="7">
+        <v>77.023019</v>
       </c>
       <c r="E549" s="8">
-        <v>0</v>
+        <v>2099501</v>
       </c>
       <c r="F549" s="9">
         <v>2</v>
       </c>
       <c r="G549" s="8">
-        <v>0</v>
+        <v>161709905.05</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -25421,17 +25421,17 @@
       <c r="C555" s="6">
         <v>46266</v>
       </c>
-      <c r="D555" s="8">
-        <v>0</v>
+      <c r="D555" s="7">
+        <v>11.152149</v>
       </c>
       <c r="E555" s="8">
-        <v>0</v>
+        <v>29486927</v>
       </c>
       <c r="F555" s="9">
         <v>1</v>
       </c>
       <c r="G555" s="8">
-        <v>0</v>
+        <v>328842614.19</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -25467,17 +25467,17 @@
       <c r="C557" s="6">
         <v>46266</v>
       </c>
-      <c r="D557" s="8">
-        <v>0</v>
+      <c r="D557" s="7">
+        <v>71.070372</v>
       </c>
       <c r="E557" s="8">
-        <v>0</v>
+        <v>5822807</v>
       </c>
       <c r="F557" s="9">
         <v>3</v>
       </c>
       <c r="G557" s="8">
-        <v>0</v>
+        <v>413829057.42</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
@@ -25490,17 +25490,17 @@
       <c r="C558" s="6">
         <v>46266</v>
       </c>
-      <c r="D558" s="8">
-        <v>0</v>
+      <c r="D558" s="7">
+        <v>67.799881</v>
       </c>
       <c r="E558" s="8">
-        <v>0</v>
+        <v>123364230</v>
       </c>
       <c r="F558" s="9">
         <v>3</v>
       </c>
       <c r="G558" s="8">
-        <v>0</v>
+        <v>8364080092.28</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
@@ -25536,17 +25536,17 @@
       <c r="C560" s="6">
         <v>46266</v>
       </c>
-      <c r="D560" s="8">
-        <v>0</v>
+      <c r="D560" s="7">
+        <v>66.501356</v>
       </c>
       <c r="E560" s="8">
-        <v>0</v>
+        <v>90240169</v>
       </c>
       <c r="F560" s="9">
         <v>2</v>
       </c>
       <c r="G560" s="8">
-        <v>0</v>
+        <v>6001093627.2</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
@@ -25560,7 +25560,7 @@
         <v>46266</v>
       </c>
       <c r="D561" s="7">
-        <v>14.084573</v>
+        <v>14.083266</v>
       </c>
       <c r="E561" s="8">
         <v>181056497</v>
@@ -25569,7 +25569,7 @@
         <v>11937</v>
       </c>
       <c r="G561" s="8">
-        <v>2550103487.16</v>
+        <v>2549866806.99</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
@@ -25582,17 +25582,17 @@
       <c r="C562" s="6">
         <v>46266</v>
       </c>
-      <c r="D562" s="8">
-        <v>0</v>
+      <c r="D562" s="7">
+        <v>8.574626</v>
       </c>
       <c r="E562" s="8">
-        <v>0</v>
+        <v>342290935</v>
       </c>
       <c r="F562" s="9">
         <v>1</v>
       </c>
       <c r="G562" s="8">
-        <v>0</v>
+        <v>2935016741.86</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
@@ -25628,17 +25628,17 @@
       <c r="C564" s="6">
         <v>46266</v>
       </c>
-      <c r="D564" s="8">
-        <v>0</v>
+      <c r="D564" s="7">
+        <v>10.538533</v>
       </c>
       <c r="E564" s="8">
-        <v>0</v>
+        <v>6927</v>
       </c>
       <c r="F564" s="9">
         <v>1</v>
       </c>
       <c r="G564" s="8">
-        <v>0</v>
+        <v>73000.42</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
@@ -25651,17 +25651,17 @@
       <c r="C565" s="6">
         <v>46266</v>
       </c>
-      <c r="D565" s="8">
-        <v>0</v>
+      <c r="D565" s="10">
+        <v>68.82003</v>
       </c>
       <c r="E565" s="8">
-        <v>0</v>
+        <v>23548896</v>
       </c>
       <c r="F565" s="9">
         <v>3</v>
       </c>
       <c r="G565" s="8">
-        <v>0</v>
+        <v>1620635718.83</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
@@ -25697,17 +25697,17 @@
       <c r="C567" s="6">
         <v>46266</v>
       </c>
-      <c r="D567" s="8">
-        <v>0</v>
+      <c r="D567" s="7">
+        <v>1.725772</v>
       </c>
       <c r="E567" s="8">
-        <v>0</v>
+        <v>22996230</v>
       </c>
       <c r="F567" s="9">
         <v>1930</v>
       </c>
       <c r="G567" s="8">
-        <v>0</v>
+        <v>39686241.12</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
@@ -25766,17 +25766,17 @@
       <c r="C570" s="6">
         <v>46266</v>
       </c>
-      <c r="D570" s="8">
-        <v>0</v>
+      <c r="D570" s="10">
+        <v>67.31201</v>
       </c>
       <c r="E570" s="8">
-        <v>0</v>
+        <v>14263356</v>
       </c>
       <c r="F570" s="9">
         <v>3</v>
       </c>
       <c r="G570" s="8">
-        <v>0</v>
+        <v>960095167.23</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -25812,17 +25812,17 @@
       <c r="C572" s="6">
         <v>46266</v>
       </c>
-      <c r="D572" s="8">
-        <v>0</v>
+      <c r="D572" s="7">
+        <v>64.841854</v>
       </c>
       <c r="E572" s="8">
-        <v>0</v>
+        <v>6323702</v>
       </c>
       <c r="F572" s="9">
         <v>3</v>
       </c>
       <c r="G572" s="8">
-        <v>0</v>
+        <v>410040560.03</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
@@ -25835,17 +25835,17 @@
       <c r="C573" s="6">
         <v>46266</v>
       </c>
-      <c r="D573" s="8">
-        <v>0</v>
+      <c r="D573" s="7">
+        <v>64.543175</v>
       </c>
       <c r="E573" s="8">
-        <v>0</v>
+        <v>2316713</v>
       </c>
       <c r="F573" s="9">
         <v>2</v>
       </c>
       <c r="G573" s="8">
-        <v>0</v>
+        <v>149528012.52</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
@@ -25858,17 +25858,17 @@
       <c r="C574" s="6">
         <v>46266</v>
       </c>
-      <c r="D574" s="8">
-        <v>0</v>
+      <c r="D574" s="7">
+        <v>64.793601</v>
       </c>
       <c r="E574" s="8">
-        <v>0</v>
+        <v>3647864</v>
       </c>
       <c r="F574" s="9">
         <v>2</v>
       </c>
       <c r="G574" s="8">
-        <v>0</v>
+        <v>236358245.43</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
@@ -25927,17 +25927,17 @@
       <c r="C577" s="6">
         <v>46266</v>
       </c>
-      <c r="D577" s="8">
-        <v>0</v>
+      <c r="D577" s="7">
+        <v>60.361784</v>
       </c>
       <c r="E577" s="8">
-        <v>0</v>
+        <v>9779449</v>
       </c>
       <c r="F577" s="9">
         <v>1</v>
       </c>
       <c r="G577" s="8">
-        <v>0</v>
+        <v>590304985.94</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
@@ -26042,17 +26042,17 @@
       <c r="C582" s="6">
         <v>46266</v>
       </c>
-      <c r="D582" s="8">
-        <v>0</v>
+      <c r="D582" s="7">
+        <v>66.641858</v>
       </c>
       <c r="E582" s="8">
-        <v>0</v>
+        <v>30617607</v>
       </c>
       <c r="F582" s="9">
         <v>2</v>
       </c>
       <c r="G582" s="8">
-        <v>0</v>
+        <v>2040414217.8</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
@@ -26388,7 +26388,7 @@
         <v>46266</v>
       </c>
       <c r="D597" s="7">
-        <v>2.767007</v>
+        <v>2.767135</v>
       </c>
       <c r="E597" s="8">
         <v>5682086</v>
@@ -26397,7 +26397,7 @@
         <v>107</v>
       </c>
       <c r="G597" s="8">
-        <v>15722372.78</v>
+        <v>15723097.99</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
@@ -26870,17 +26870,17 @@
       <c r="C618" s="6">
         <v>46266</v>
       </c>
-      <c r="D618" s="8">
-        <v>0</v>
+      <c r="D618" s="7">
+        <v>53.350618</v>
       </c>
       <c r="E618" s="8">
-        <v>0</v>
+        <v>7495891</v>
       </c>
       <c r="F618" s="9">
         <v>332</v>
       </c>
       <c r="G618" s="8">
-        <v>0</v>
+        <v>399910415.8</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
@@ -26985,17 +26985,17 @@
       <c r="C623" s="6">
         <v>46266</v>
       </c>
-      <c r="D623" s="8">
-        <v>0</v>
+      <c r="D623" s="7">
+        <v>64.672001</v>
       </c>
       <c r="E623" s="8">
-        <v>0</v>
+        <v>11510132</v>
       </c>
       <c r="F623" s="9">
         <v>473</v>
       </c>
       <c r="G623" s="8">
-        <v>0</v>
+        <v>744383270.04</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
@@ -27031,17 +27031,17 @@
       <c r="C625" s="6">
         <v>46266</v>
       </c>
-      <c r="D625" s="8">
-        <v>0</v>
+      <c r="D625" s="7">
+        <v>12.295089</v>
       </c>
       <c r="E625" s="8">
-        <v>0</v>
+        <v>102497153</v>
       </c>
       <c r="F625" s="9">
         <v>9520</v>
       </c>
       <c r="G625" s="8">
-        <v>0</v>
+        <v>1260211626.93</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.25">
@@ -27054,17 +27054,17 @@
       <c r="C626" s="6">
         <v>46266</v>
       </c>
-      <c r="D626" s="8">
-        <v>0</v>
+      <c r="D626" s="7">
+        <v>72.850688</v>
       </c>
       <c r="E626" s="8">
-        <v>0</v>
+        <v>94134591</v>
       </c>
       <c r="F626" s="9">
         <v>3593</v>
       </c>
       <c r="G626" s="8">
-        <v>0</v>
+        <v>6857769758.75</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
@@ -27123,17 +27123,17 @@
       <c r="C629" s="6">
         <v>46266</v>
       </c>
-      <c r="D629" s="8">
-        <v>0</v>
+      <c r="D629" s="7">
+        <v>45.521191</v>
       </c>
       <c r="E629" s="8">
-        <v>0</v>
+        <v>58637</v>
       </c>
       <c r="F629" s="9">
         <v>1</v>
       </c>
       <c r="G629" s="8">
-        <v>0</v>
+        <v>2669226.06</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.25">
@@ -27146,17 +27146,17 @@
       <c r="C630" s="6">
         <v>46266</v>
       </c>
-      <c r="D630" s="8">
-        <v>0</v>
+      <c r="D630" s="7">
+        <v>18.666199</v>
       </c>
       <c r="E630" s="8">
-        <v>0</v>
+        <v>39753382</v>
       </c>
       <c r="F630" s="9">
         <v>2803</v>
       </c>
       <c r="G630" s="8">
-        <v>0</v>
+        <v>742044520.66</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -27169,17 +27169,17 @@
       <c r="C631" s="6">
         <v>46266</v>
       </c>
-      <c r="D631" s="8">
-        <v>0</v>
+      <c r="D631" s="7">
+        <v>58.581113</v>
       </c>
       <c r="E631" s="8">
-        <v>0</v>
+        <v>14772170</v>
       </c>
       <c r="F631" s="9">
         <v>2</v>
       </c>
       <c r="G631" s="8">
-        <v>0</v>
+        <v>865370164.62</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
@@ -27284,17 +27284,17 @@
       <c r="C636" s="6">
         <v>46266</v>
       </c>
-      <c r="D636" s="8">
-        <v>0</v>
+      <c r="D636" s="7">
+        <v>21.312091</v>
       </c>
       <c r="E636" s="8">
-        <v>0</v>
+        <v>16709535</v>
       </c>
       <c r="F636" s="9">
         <v>2459</v>
       </c>
       <c r="G636" s="8">
-        <v>0</v>
+        <v>356115136.98</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.25">
@@ -27354,7 +27354,7 @@
         <v>46266</v>
       </c>
       <c r="D639" s="7">
-        <v>1.829318</v>
+        <v>1.823595</v>
       </c>
       <c r="E639" s="8">
         <v>292026835</v>
@@ -27363,7 +27363,7 @@
         <v>287</v>
       </c>
       <c r="G639" s="8">
-        <v>534210054.59</v>
+        <v>532538610.65</v>
       </c>
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.25">
@@ -27491,17 +27491,17 @@
       <c r="C645" s="6">
         <v>46266</v>
       </c>
-      <c r="D645" s="8">
-        <v>0</v>
+      <c r="D645" s="7">
+        <v>15.479777</v>
       </c>
       <c r="E645" s="8">
-        <v>0</v>
+        <v>1503321709</v>
       </c>
       <c r="F645" s="9">
         <v>7</v>
       </c>
       <c r="G645" s="8">
-        <v>0</v>
+        <v>23271084857.18</v>
       </c>
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.25">
@@ -27537,17 +27537,17 @@
       <c r="C647" s="6">
         <v>46266</v>
       </c>
-      <c r="D647" s="8">
-        <v>0</v>
+      <c r="D647" s="7">
+        <v>57.868346</v>
       </c>
       <c r="E647" s="8">
-        <v>0</v>
+        <v>4643160</v>
       </c>
       <c r="F647" s="9">
         <v>2</v>
       </c>
       <c r="G647" s="8">
-        <v>0</v>
+        <v>268691989.64</v>
       </c>
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.25">
@@ -27652,17 +27652,17 @@
       <c r="C652" s="6">
         <v>46266</v>
       </c>
-      <c r="D652" s="8">
-        <v>0</v>
+      <c r="D652" s="7">
+        <v>7.090825</v>
       </c>
       <c r="E652" s="8">
-        <v>0</v>
+        <v>4029467144</v>
       </c>
       <c r="F652" s="9">
         <v>1</v>
       </c>
       <c r="G652" s="8">
-        <v>0</v>
+        <v>28572245635.22</v>
       </c>
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.25">
@@ -27744,17 +27744,17 @@
       <c r="C656" s="6">
         <v>46266</v>
       </c>
-      <c r="D656" s="8">
-        <v>0</v>
+      <c r="D656" s="7">
+        <v>6.447034</v>
       </c>
       <c r="E656" s="8">
-        <v>0</v>
+        <v>64470875</v>
       </c>
       <c r="F656" s="9">
         <v>527</v>
       </c>
       <c r="G656" s="8">
-        <v>0</v>
+        <v>415645906.95</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
@@ -27790,17 +27790,17 @@
       <c r="C658" s="6">
         <v>46266</v>
       </c>
-      <c r="D658" s="8">
-        <v>0</v>
+      <c r="D658" s="7">
+        <v>6.042377</v>
       </c>
       <c r="E658" s="8">
-        <v>0</v>
+        <v>341860798</v>
       </c>
       <c r="F658" s="9">
         <v>1</v>
       </c>
       <c r="G658" s="8">
-        <v>0</v>
+        <v>2065651993.54</v>
       </c>
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.25">
@@ -27882,17 +27882,17 @@
       <c r="C662" s="6">
         <v>46266</v>
       </c>
-      <c r="D662" s="8">
-        <v>0</v>
+      <c r="D662" s="7">
+        <v>0.450562</v>
       </c>
       <c r="E662" s="8">
-        <v>0</v>
+        <v>10468623748</v>
       </c>
       <c r="F662" s="9">
         <v>38500</v>
       </c>
       <c r="G662" s="8">
-        <v>0</v>
+        <v>4716765583.87</v>
       </c>
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.25">
@@ -27905,17 +27905,17 @@
       <c r="C663" s="6">
         <v>46266</v>
       </c>
-      <c r="D663" s="8">
-        <v>0</v>
+      <c r="D663" s="7">
+        <v>1.445751</v>
       </c>
       <c r="E663" s="8">
-        <v>0</v>
+        <v>802734043</v>
       </c>
       <c r="F663" s="9">
         <v>2689</v>
       </c>
       <c r="G663" s="8">
-        <v>0</v>
+        <v>1160553294.7</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -27974,17 +27974,17 @@
       <c r="C666" s="6">
         <v>46266</v>
       </c>
-      <c r="D666" s="8">
-        <v>0</v>
+      <c r="D666" s="7">
+        <v>4.120132</v>
       </c>
       <c r="E666" s="8">
-        <v>0</v>
+        <v>23585376</v>
       </c>
       <c r="F666" s="9">
         <v>3425</v>
       </c>
       <c r="G666" s="8">
-        <v>0</v>
+        <v>97174851.7</v>
       </c>
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.25">
@@ -28020,17 +28020,17 @@
       <c r="C668" s="6">
         <v>46266</v>
       </c>
-      <c r="D668" s="8">
-        <v>0</v>
+      <c r="D668" s="7">
+        <v>64.926855</v>
       </c>
       <c r="E668" s="8">
-        <v>0</v>
+        <v>4739268</v>
       </c>
       <c r="F668" s="9">
         <v>1</v>
       </c>
       <c r="G668" s="8">
-        <v>0</v>
+        <v>307705764.44</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -28043,17 +28043,17 @@
       <c r="C669" s="6">
         <v>46266</v>
       </c>
-      <c r="D669" s="8">
-        <v>0</v>
+      <c r="D669" s="7">
+        <v>18.435967</v>
       </c>
       <c r="E669" s="8">
-        <v>0</v>
+        <v>22115</v>
       </c>
       <c r="F669" s="9">
         <v>1</v>
       </c>
       <c r="G669" s="8">
-        <v>0</v>
+        <v>407711.41</v>
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.25">
@@ -28066,17 +28066,17 @@
       <c r="C670" s="6">
         <v>46266</v>
       </c>
-      <c r="D670" s="8">
-        <v>0</v>
+      <c r="D670" s="7">
+        <v>5.656139</v>
       </c>
       <c r="E670" s="8">
-        <v>0</v>
+        <v>209628591</v>
       </c>
       <c r="F670" s="9">
         <v>4581</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>1185688485.53</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -28112,17 +28112,17 @@
       <c r="C672" s="6">
         <v>46266</v>
       </c>
-      <c r="D672" s="8">
-        <v>0</v>
+      <c r="D672" s="7">
+        <v>73.986767</v>
       </c>
       <c r="E672" s="8">
-        <v>0</v>
+        <v>5533354</v>
       </c>
       <c r="F672" s="9">
         <v>2</v>
       </c>
       <c r="G672" s="8">
-        <v>0</v>
+        <v>409394975.16</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
@@ -28135,17 +28135,17 @@
       <c r="C673" s="6">
         <v>46266</v>
       </c>
-      <c r="D673" s="8">
-        <v>0</v>
+      <c r="D673" s="7">
+        <v>4.127432</v>
       </c>
       <c r="E673" s="8">
-        <v>0</v>
+        <v>5020082762</v>
       </c>
       <c r="F673" s="9">
         <v>1</v>
       </c>
       <c r="G673" s="8">
-        <v>0</v>
+        <v>20720048198.68</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
@@ -28158,17 +28158,17 @@
       <c r="C674" s="6">
         <v>46266</v>
       </c>
-      <c r="D674" s="8">
-        <v>0</v>
+      <c r="D674" s="10">
+        <v>72.09824</v>
       </c>
       <c r="E674" s="8">
-        <v>0</v>
+        <v>7036272</v>
       </c>
       <c r="F674" s="9">
         <v>4</v>
       </c>
       <c r="G674" s="8">
-        <v>0</v>
+        <v>507302828.67</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -28227,17 +28227,17 @@
       <c r="C677" s="6">
         <v>46266</v>
       </c>
-      <c r="D677" s="8">
-        <v>0</v>
+      <c r="D677" s="7">
+        <v>69.531134</v>
       </c>
       <c r="E677" s="8">
-        <v>0</v>
+        <v>20613565</v>
       </c>
       <c r="F677" s="9">
         <v>1</v>
       </c>
       <c r="G677" s="8">
-        <v>0</v>
+        <v>1433284551.55</v>
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.25">
@@ -28296,17 +28296,17 @@
       <c r="C680" s="6">
         <v>46266</v>
       </c>
-      <c r="D680" s="8">
-        <v>0</v>
+      <c r="D680" s="7">
+        <v>62.501866</v>
       </c>
       <c r="E680" s="8">
-        <v>0</v>
+        <v>876698</v>
       </c>
       <c r="F680" s="9">
         <v>3</v>
       </c>
       <c r="G680" s="8">
-        <v>0</v>
+        <v>54795261.11</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -28319,17 +28319,17 @@
       <c r="C681" s="6">
         <v>46266</v>
       </c>
-      <c r="D681" s="8">
-        <v>0</v>
+      <c r="D681" s="7">
+        <v>7.956335</v>
       </c>
       <c r="E681" s="8">
-        <v>0</v>
+        <v>184312931</v>
       </c>
       <c r="F681" s="9">
         <v>4111</v>
       </c>
       <c r="G681" s="8">
-        <v>0</v>
+        <v>1466455400.65</v>
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.25">
@@ -28365,17 +28365,17 @@
       <c r="C683" s="6">
         <v>46266</v>
       </c>
-      <c r="D683" s="8">
-        <v>0</v>
+      <c r="D683" s="7">
+        <v>4.784347</v>
       </c>
       <c r="E683" s="8">
-        <v>0</v>
+        <v>76123008</v>
       </c>
       <c r="F683" s="9">
         <v>5609</v>
       </c>
       <c r="G683" s="8">
-        <v>0</v>
+        <v>364198921.25</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
@@ -28388,17 +28388,17 @@
       <c r="C684" s="6">
         <v>46266</v>
       </c>
-      <c r="D684" s="8">
-        <v>0</v>
+      <c r="D684" s="7">
+        <v>8.764663</v>
       </c>
       <c r="E684" s="8">
-        <v>0</v>
+        <v>198707530</v>
       </c>
       <c r="F684" s="9">
         <v>5218</v>
       </c>
       <c r="G684" s="8">
-        <v>0</v>
+        <v>1741604525.76</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
@@ -28411,17 +28411,17 @@
       <c r="C685" s="6">
         <v>46266</v>
       </c>
-      <c r="D685" s="8">
-        <v>0</v>
+      <c r="D685" s="7">
+        <v>5.735217</v>
       </c>
       <c r="E685" s="8">
-        <v>0</v>
+        <v>65919407</v>
       </c>
       <c r="F685" s="9">
         <v>6027</v>
       </c>
       <c r="G685" s="8">
-        <v>0</v>
+        <v>378062100.17</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
@@ -28480,17 +28480,17 @@
       <c r="C688" s="6">
         <v>46266</v>
       </c>
-      <c r="D688" s="8">
-        <v>0</v>
+      <c r="D688" s="7">
+        <v>70.415988</v>
       </c>
       <c r="E688" s="8">
-        <v>0</v>
+        <v>1210798</v>
       </c>
       <c r="F688" s="9">
         <v>1</v>
       </c>
       <c r="G688" s="8">
-        <v>0</v>
+        <v>85259537.46</v>
       </c>
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.25">
@@ -28503,17 +28503,17 @@
       <c r="C689" s="6">
         <v>46266</v>
       </c>
-      <c r="D689" s="8">
-        <v>0</v>
+      <c r="D689" s="7">
+        <v>7.743731</v>
       </c>
       <c r="E689" s="8">
-        <v>0</v>
+        <v>502416906</v>
       </c>
       <c r="F689" s="9">
         <v>10223</v>
       </c>
       <c r="G689" s="8">
-        <v>0</v>
+        <v>3890581222.97</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
@@ -28549,17 +28549,17 @@
       <c r="C691" s="6">
         <v>46266</v>
       </c>
-      <c r="D691" s="8">
-        <v>0</v>
+      <c r="D691" s="7">
+        <v>68.223877</v>
       </c>
       <c r="E691" s="8">
-        <v>0</v>
+        <v>6829649</v>
       </c>
       <c r="F691" s="9">
         <v>2</v>
       </c>
       <c r="G691" s="8">
-        <v>0</v>
+        <v>465945135.82</v>
       </c>
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.25">
@@ -28572,17 +28572,17 @@
       <c r="C692" s="6">
         <v>46266</v>
       </c>
-      <c r="D692" s="8">
-        <v>0</v>
+      <c r="D692" s="7">
+        <v>8.782371</v>
       </c>
       <c r="E692" s="8">
-        <v>0</v>
+        <v>11436943</v>
       </c>
       <c r="F692" s="9">
         <v>1374</v>
       </c>
       <c r="G692" s="8">
-        <v>0</v>
+        <v>100443470.96</v>
       </c>
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.25">
@@ -28595,17 +28595,17 @@
       <c r="C693" s="6">
         <v>46266</v>
       </c>
-      <c r="D693" s="8">
-        <v>0</v>
+      <c r="D693" s="7">
+        <v>7.670968</v>
       </c>
       <c r="E693" s="8">
-        <v>0</v>
+        <v>8876274</v>
       </c>
       <c r="F693" s="9">
         <v>2307</v>
       </c>
       <c r="G693" s="8">
-        <v>0</v>
+        <v>68089617.94</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.25">
@@ -28618,17 +28618,17 @@
       <c r="C694" s="6">
         <v>46266</v>
       </c>
-      <c r="D694" s="8">
-        <v>0</v>
+      <c r="D694" s="12">
+        <v>7.0352</v>
       </c>
       <c r="E694" s="8">
-        <v>0</v>
+        <v>9419239</v>
       </c>
       <c r="F694" s="9">
         <v>1248</v>
       </c>
       <c r="G694" s="8">
-        <v>0</v>
+        <v>66266231.42</v>
       </c>
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.25">
@@ -28826,7 +28826,7 @@
         <v>46266</v>
       </c>
       <c r="D703" s="7">
-        <v>51.826861</v>
+        <v>51.828215</v>
       </c>
       <c r="E703" s="8">
         <v>123199930</v>
@@ -28835,7 +28835,7 @@
         <v>10831</v>
       </c>
       <c r="G703" s="8">
-        <v>6385065700.71</v>
+        <v>6385232486.77</v>
       </c>
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.25">
@@ -28871,17 +28871,17 @@
       <c r="C705" s="6">
         <v>46266</v>
       </c>
-      <c r="D705" s="8">
-        <v>0</v>
+      <c r="D705" s="10">
+        <v>4.34313</v>
       </c>
       <c r="E705" s="8">
-        <v>0</v>
+        <v>122899999</v>
       </c>
       <c r="F705" s="9">
         <v>1066</v>
       </c>
       <c r="G705" s="8">
-        <v>0</v>
+        <v>533770674.99</v>
       </c>
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.25">
@@ -29147,17 +29147,17 @@
       <c r="C717" s="6">
         <v>46266</v>
       </c>
-      <c r="D717" s="8">
-        <v>0</v>
+      <c r="D717" s="7">
+        <v>3.321444</v>
       </c>
       <c r="E717" s="8">
-        <v>0</v>
+        <v>162333227</v>
       </c>
       <c r="F717" s="9">
         <v>1455</v>
       </c>
       <c r="G717" s="8">
-        <v>0</v>
+        <v>539180766.81</v>
       </c>
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.25">
@@ -29469,17 +29469,17 @@
       <c r="C731" s="6">
         <v>46266</v>
       </c>
-      <c r="D731" s="8">
-        <v>0</v>
+      <c r="D731" s="7">
+        <v>4.884278</v>
       </c>
       <c r="E731" s="8">
-        <v>0</v>
+        <v>4802470</v>
       </c>
       <c r="F731" s="9">
         <v>372</v>
       </c>
       <c r="G731" s="8">
-        <v>0</v>
+        <v>23456596.62</v>
       </c>
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.25">
@@ -29818,13 +29818,13 @@
         <v>5.930784</v>
       </c>
       <c r="E746" s="8">
-        <v>30143652</v>
+        <v>30143676</v>
       </c>
       <c r="F746" s="9">
         <v>76</v>
       </c>
       <c r="G746" s="8">
-        <v>178775476.56</v>
+        <v>178775622.66</v>
       </c>
     </row>
     <row r="747" spans="1:7" x14ac:dyDescent="0.25">
@@ -30183,7 +30183,7 @@
         <v>46266</v>
       </c>
       <c r="D762" s="7">
-        <v>0.368474</v>
+        <v>0.368485</v>
       </c>
       <c r="E762" s="8">
         <v>3711762790</v>
@@ -30192,7 +30192,7 @@
         <v>2542</v>
       </c>
       <c r="G762" s="8">
-        <v>1367687320.88</v>
+        <v>1367728194.66</v>
       </c>
     </row>
     <row r="763" spans="1:7" x14ac:dyDescent="0.25">
@@ -30505,7 +30505,7 @@
         <v>46266</v>
       </c>
       <c r="D776" s="7">
-        <v>1640.845745</v>
+        <v>1640.793025</v>
       </c>
       <c r="E776" s="8">
         <v>2485501</v>
@@ -30514,7 +30514,7 @@
         <v>2374</v>
       </c>
       <c r="G776" s="8">
-        <v>4078323740.86</v>
+        <v>4078192705.47</v>
       </c>
     </row>
     <row r="777" spans="1:7" x14ac:dyDescent="0.25">
@@ -30642,8 +30642,8 @@
       <c r="C782" s="6">
         <v>46266</v>
       </c>
-      <c r="D782" s="7">
-        <v>1.037767</v>
+      <c r="D782" s="10">
+        <v>1.03508</v>
       </c>
       <c r="E782" s="8">
         <v>119612169</v>
@@ -30652,7 +30652,7 @@
         <v>903</v>
       </c>
       <c r="G782" s="8">
-        <v>124129550.87</v>
+        <v>123808217.12</v>
       </c>
     </row>
     <row r="783" spans="1:7" x14ac:dyDescent="0.25">
@@ -31195,7 +31195,7 @@
         <v>46266</v>
       </c>
       <c r="D806" s="7">
-        <v>2.162599</v>
+        <v>2.162598</v>
       </c>
       <c r="E806" s="8">
         <v>132761103</v>
@@ -31204,7 +31204,7 @@
         <v>449</v>
       </c>
       <c r="G806" s="8">
-        <v>287109049.96</v>
+        <v>287108943.26</v>
       </c>
     </row>
     <row r="807" spans="1:7" x14ac:dyDescent="0.25">
@@ -31770,7 +31770,7 @@
         <v>46266</v>
       </c>
       <c r="D831" s="7">
-        <v>4.359172</v>
+        <v>4.359175</v>
       </c>
       <c r="E831" s="8">
         <v>90771209</v>
@@ -31779,7 +31779,7 @@
         <v>16</v>
       </c>
       <c r="G831" s="8">
-        <v>395687305.72</v>
+        <v>395687622.45</v>
       </c>
     </row>
     <row r="832" spans="1:7" x14ac:dyDescent="0.25">
@@ -31954,7 +31954,7 @@
         <v>46266</v>
       </c>
       <c r="D839" s="7">
-        <v>6.111011</v>
+        <v>6.111005</v>
       </c>
       <c r="E839" s="8">
         <v>733508048</v>
@@ -31963,7 +31963,7 @@
         <v>3800</v>
       </c>
       <c r="G839" s="8">
-        <v>4482475978.22</v>
+        <v>4482471636.08</v>
       </c>
     </row>
     <row r="840" spans="1:7" x14ac:dyDescent="0.25">
@@ -32092,7 +32092,7 @@
         <v>46266</v>
       </c>
       <c r="D845" s="7">
-        <v>1.252596</v>
+        <v>1.252598</v>
       </c>
       <c r="E845" s="8">
         <v>14425430</v>
@@ -32101,7 +32101,7 @@
         <v>98</v>
       </c>
       <c r="G845" s="8">
-        <v>18069230.68</v>
+        <v>18069260.05</v>
       </c>
     </row>
     <row r="846" spans="1:7" x14ac:dyDescent="0.25">
@@ -32436,8 +32436,8 @@
       <c r="C860" s="6">
         <v>46266</v>
       </c>
-      <c r="D860" s="10">
-        <v>1.80714</v>
+      <c r="D860" s="7">
+        <v>1.807138</v>
       </c>
       <c r="E860" s="8">
         <v>37856733</v>
@@ -32446,7 +32446,7 @@
         <v>276</v>
       </c>
       <c r="G860" s="8">
-        <v>68412418.1</v>
+        <v>68412324.22</v>
       </c>
     </row>
     <row r="861" spans="1:7" x14ac:dyDescent="0.25">
@@ -32689,17 +32689,17 @@
       <c r="C871" s="6">
         <v>46266</v>
       </c>
-      <c r="D871" s="8">
-        <v>0</v>
+      <c r="D871" s="7">
+        <v>43.899139</v>
       </c>
       <c r="E871" s="8">
-        <v>0</v>
+        <v>31939117.25</v>
       </c>
       <c r="F871" s="9">
         <v>146</v>
       </c>
       <c r="G871" s="8">
-        <v>0</v>
+        <v>1402099757.61</v>
       </c>
     </row>
     <row r="872" spans="1:7" x14ac:dyDescent="0.25">
@@ -32975,7 +32975,7 @@
         <v>2820</v>
       </c>
       <c r="G883" s="8">
-        <v>2982557489.48</v>
+        <v>2982557640.64</v>
       </c>
     </row>
     <row r="884" spans="1:7" x14ac:dyDescent="0.25">
@@ -33517,17 +33517,17 @@
       <c r="C907" s="6">
         <v>46266</v>
       </c>
-      <c r="D907" s="8">
-        <v>0</v>
+      <c r="D907" s="7">
+        <v>14.982749</v>
       </c>
       <c r="E907" s="8">
-        <v>0</v>
+        <v>15819486</v>
       </c>
       <c r="F907" s="9">
         <v>379</v>
       </c>
       <c r="G907" s="8">
-        <v>0</v>
+        <v>237019380.73</v>
       </c>
     </row>
     <row r="908" spans="1:7" x14ac:dyDescent="0.25">
@@ -33909,7 +33909,7 @@
         <v>46266</v>
       </c>
       <c r="D924" s="7">
-        <v>0.124076</v>
+        <v>0.124031</v>
       </c>
       <c r="E924" s="8">
         <v>1105011730</v>
@@ -33918,7 +33918,7 @@
         <v>22</v>
       </c>
       <c r="G924" s="8">
-        <v>137105936.35</v>
+        <v>137056213.14</v>
       </c>
     </row>
     <row r="925" spans="1:7" x14ac:dyDescent="0.25">
@@ -34023,8 +34023,8 @@
       <c r="C929" s="6">
         <v>46266</v>
       </c>
-      <c r="D929" s="7">
-        <v>0.183414</v>
+      <c r="D929" s="10">
+        <v>0.18312</v>
       </c>
       <c r="E929" s="8">
         <v>38099877232</v>
@@ -34033,7 +34033,7 @@
         <v>163</v>
       </c>
       <c r="G929" s="8">
-        <v>6988064817.53</v>
+        <v>6976843746.2</v>
       </c>
     </row>
     <row r="930" spans="1:7" x14ac:dyDescent="0.25">
@@ -34185,7 +34185,7 @@
         <v>46266</v>
       </c>
       <c r="D936" s="7">
-        <v>17.980373</v>
+        <v>17.980372</v>
       </c>
       <c r="E936" s="8">
         <v>15147672</v>
@@ -34194,7 +34194,7 @@
         <v>16</v>
       </c>
       <c r="G936" s="8">
-        <v>272360787.83</v>
+        <v>272360770.41</v>
       </c>
     </row>
     <row r="937" spans="1:7" x14ac:dyDescent="0.25">
@@ -34976,7 +34976,7 @@
         <v>2</v>
       </c>
       <c r="G970" s="8">
-        <v>2299389996.47</v>
+        <v>2299389746.1</v>
       </c>
     </row>
     <row r="971" spans="1:7" x14ac:dyDescent="0.25">
@@ -35426,17 +35426,17 @@
       <c r="C990" s="6">
         <v>46266</v>
       </c>
-      <c r="D990" s="8">
-        <v>0</v>
+      <c r="D990" s="7">
+        <v>1.785361</v>
       </c>
       <c r="E990" s="8">
-        <v>0</v>
+        <v>6371480</v>
       </c>
       <c r="F990" s="9">
         <v>173</v>
       </c>
       <c r="G990" s="8">
-        <v>0</v>
+        <v>11375390.64</v>
       </c>
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.25">
@@ -35518,17 +35518,17 @@
       <c r="C994" s="6">
         <v>46266</v>
       </c>
-      <c r="D994" s="8">
-        <v>0</v>
+      <c r="D994" s="7">
+        <v>58.313208</v>
       </c>
       <c r="E994" s="8">
-        <v>0</v>
+        <v>4238148</v>
       </c>
       <c r="F994" s="9">
         <v>12</v>
       </c>
       <c r="G994" s="8">
-        <v>0</v>
+        <v>247140006.65</v>
       </c>
     </row>
     <row r="995" spans="1:7" x14ac:dyDescent="0.25">
@@ -35795,7 +35795,7 @@
         <v>46266</v>
       </c>
       <c r="D1006" s="7">
-        <v>3.037372</v>
+        <v>3.037369</v>
       </c>
       <c r="E1006" s="8">
         <v>1006605100</v>
@@ -35804,7 +35804,7 @@
         <v>30513</v>
       </c>
       <c r="G1006" s="8">
-        <v>3057434431.08</v>
+        <v>3057430921.81</v>
       </c>
     </row>
     <row r="1007" spans="1:7" x14ac:dyDescent="0.25">
@@ -35863,17 +35863,17 @@
       <c r="C1009" s="6">
         <v>46266</v>
       </c>
-      <c r="D1009" s="8">
-        <v>0</v>
+      <c r="D1009" s="7">
+        <v>1.630979</v>
       </c>
       <c r="E1009" s="8">
-        <v>0</v>
+        <v>9435313</v>
       </c>
       <c r="F1009" s="9">
         <v>247</v>
       </c>
       <c r="G1009" s="8">
-        <v>0</v>
+        <v>15388792.77</v>
       </c>
     </row>
     <row r="1010" spans="1:7" x14ac:dyDescent="0.25">
@@ -36116,17 +36116,17 @@
       <c r="C1020" s="6">
         <v>46266</v>
       </c>
-      <c r="D1020" s="8">
-        <v>0</v>
+      <c r="D1020" s="12">
+        <v>1.5541</v>
       </c>
       <c r="E1020" s="8">
-        <v>0</v>
+        <v>38712606</v>
       </c>
       <c r="F1020" s="9">
         <v>27</v>
       </c>
       <c r="G1020" s="8">
-        <v>0</v>
+        <v>60163264.61</v>
       </c>
     </row>
     <row r="1021" spans="1:7" x14ac:dyDescent="0.25">
@@ -36231,17 +36231,17 @@
       <c r="C1025" s="6">
         <v>46266</v>
       </c>
-      <c r="D1025" s="8">
-        <v>0</v>
+      <c r="D1025" s="7">
+        <v>57.973913</v>
       </c>
       <c r="E1025" s="8">
-        <v>0</v>
+        <v>2183293</v>
       </c>
       <c r="F1025" s="9">
         <v>52</v>
       </c>
       <c r="G1025" s="8">
-        <v>0</v>
+        <v>126574038.86</v>
       </c>
     </row>
     <row r="1026" spans="1:7" x14ac:dyDescent="0.25">
@@ -36922,7 +36922,7 @@
         <v>46266</v>
       </c>
       <c r="D1055" s="7">
-        <v>7.772944</v>
+        <v>7.669289</v>
       </c>
       <c r="E1055" s="8">
         <v>2051000</v>
@@ -36931,7 +36931,7 @@
         <v>14</v>
       </c>
       <c r="G1055" s="8">
-        <v>15942308.13</v>
+        <v>15729712.45</v>
       </c>
     </row>
     <row r="1056" spans="1:7" x14ac:dyDescent="0.25">
@@ -36990,17 +36990,17 @@
       <c r="C1058" s="6">
         <v>46266</v>
       </c>
-      <c r="D1058" s="8">
-        <v>0</v>
+      <c r="D1058" s="7">
+        <v>53.491109</v>
       </c>
       <c r="E1058" s="8">
-        <v>0</v>
+        <v>264284</v>
       </c>
       <c r="F1058" s="9">
         <v>10</v>
       </c>
       <c r="G1058" s="8">
-        <v>0</v>
+        <v>14136844.15</v>
       </c>
     </row>
     <row r="1059" spans="1:7" x14ac:dyDescent="0.25">
@@ -37197,17 +37197,17 @@
       <c r="C1067" s="6">
         <v>46266</v>
       </c>
-      <c r="D1067" s="8">
-        <v>0</v>
+      <c r="D1067" s="7">
+        <v>1.040222</v>
       </c>
       <c r="E1067" s="8">
-        <v>0</v>
+        <v>1508400</v>
       </c>
       <c r="F1067" s="9">
         <v>16</v>
       </c>
       <c r="G1067" s="8">
-        <v>0</v>
+        <v>1569070.2</v>
       </c>
     </row>
     <row r="1068" spans="1:7" x14ac:dyDescent="0.25">
@@ -37335,17 +37335,17 @@
       <c r="C1073" s="6">
         <v>46266</v>
       </c>
-      <c r="D1073" s="8">
-        <v>0</v>
+      <c r="D1073" s="7">
+        <v>21.765963</v>
       </c>
       <c r="E1073" s="8">
-        <v>0</v>
+        <v>2064997</v>
       </c>
       <c r="F1073" s="9">
         <v>597</v>
       </c>
       <c r="G1073" s="8">
-        <v>0</v>
+        <v>44946648.62</v>
       </c>
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.25">
@@ -37427,17 +37427,17 @@
       <c r="C1077" s="6">
         <v>46266</v>
       </c>
-      <c r="D1077" s="8">
-        <v>0</v>
+      <c r="D1077" s="7">
+        <v>0.528123</v>
       </c>
       <c r="E1077" s="8">
-        <v>0</v>
+        <v>2837713694</v>
       </c>
       <c r="F1077" s="9">
         <v>1104</v>
       </c>
       <c r="G1077" s="8">
-        <v>0</v>
+        <v>1498660513.25</v>
       </c>
     </row>
     <row r="1078" spans="1:7" x14ac:dyDescent="0.25">
@@ -37450,17 +37450,17 @@
       <c r="C1078" s="6">
         <v>46266</v>
       </c>
-      <c r="D1078" s="8">
-        <v>0</v>
+      <c r="D1078" s="7">
+        <v>75.411445</v>
       </c>
       <c r="E1078" s="8">
-        <v>0</v>
+        <v>10578199</v>
       </c>
       <c r="F1078" s="9">
         <v>168</v>
       </c>
       <c r="G1078" s="8">
-        <v>0</v>
+        <v>797717273.09</v>
       </c>
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.25">
@@ -38002,17 +38002,17 @@
       <c r="C1102" s="6">
         <v>46266</v>
       </c>
-      <c r="D1102" s="8">
-        <v>0</v>
+      <c r="D1102" s="7">
+        <v>0.756487</v>
       </c>
       <c r="E1102" s="8">
-        <v>0</v>
+        <v>808090875</v>
       </c>
       <c r="F1102" s="9">
         <v>3630</v>
       </c>
       <c r="G1102" s="8">
-        <v>0</v>
+        <v>611309951.44</v>
       </c>
     </row>
     <row r="1103" spans="1:7" x14ac:dyDescent="0.25">
@@ -38209,17 +38209,17 @@
       <c r="C1111" s="6">
         <v>46266</v>
       </c>
-      <c r="D1111" s="8">
-        <v>0</v>
+      <c r="D1111" s="7">
+        <v>1.189761</v>
       </c>
       <c r="E1111" s="8">
-        <v>0</v>
+        <v>53410251</v>
       </c>
       <c r="F1111" s="9">
         <v>1535</v>
       </c>
       <c r="G1111" s="8">
-        <v>0</v>
+        <v>63545429.4</v>
       </c>
     </row>
     <row r="1112" spans="1:7" x14ac:dyDescent="0.25">
@@ -38255,17 +38255,17 @@
       <c r="C1113" s="6">
         <v>46266</v>
       </c>
-      <c r="D1113" s="8">
-        <v>0</v>
+      <c r="D1113" s="7">
+        <v>54.314429</v>
       </c>
       <c r="E1113" s="8">
-        <v>0</v>
+        <v>207100</v>
       </c>
       <c r="F1113" s="9">
         <v>18</v>
       </c>
       <c r="G1113" s="8">
-        <v>0</v>
+        <v>11248518.32</v>
       </c>
     </row>
     <row r="1114" spans="1:7" x14ac:dyDescent="0.25">
@@ -38831,7 +38831,7 @@
         <v>46266</v>
       </c>
       <c r="D1138" s="7">
-        <v>1.793235</v>
+        <v>1.793252</v>
       </c>
       <c r="E1138" s="8">
         <v>263511952</v>
@@ -38840,7 +38840,7 @@
         <v>540</v>
       </c>
       <c r="G1138" s="8">
-        <v>472538984.76</v>
+        <v>472543246.19</v>
       </c>
     </row>
     <row r="1139" spans="1:7" x14ac:dyDescent="0.25">
@@ -38945,17 +38945,17 @@
       <c r="C1143" s="6">
         <v>46266</v>
       </c>
-      <c r="D1143" s="8">
-        <v>0</v>
+      <c r="D1143" s="7">
+        <v>5.993966</v>
       </c>
       <c r="E1143" s="8">
-        <v>0</v>
+        <v>124391755</v>
       </c>
       <c r="F1143" s="9">
         <v>6587</v>
       </c>
       <c r="G1143" s="8">
-        <v>0</v>
+        <v>745599910.32</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.25">
@@ -39405,8 +39405,8 @@
       <c r="C1163" s="6">
         <v>46266</v>
       </c>
-      <c r="D1163" s="7">
-        <v>1.289844</v>
+      <c r="D1163" s="10">
+        <v>1.28978</v>
       </c>
       <c r="E1163" s="8">
         <v>263529822</v>
@@ -39415,7 +39415,7 @@
         <v>121</v>
       </c>
       <c r="G1163" s="8">
-        <v>339912440.19</v>
+        <v>339895397.95</v>
       </c>
     </row>
     <row r="1164" spans="1:7" x14ac:dyDescent="0.25">
@@ -39428,17 +39428,17 @@
       <c r="C1164" s="6">
         <v>46266</v>
       </c>
-      <c r="D1164" s="8">
-        <v>0</v>
+      <c r="D1164" s="7">
+        <v>1.314896</v>
       </c>
       <c r="E1164" s="8">
-        <v>0</v>
+        <v>2651303752</v>
       </c>
       <c r="F1164" s="9">
         <v>13</v>
       </c>
       <c r="G1164" s="8">
-        <v>0</v>
+        <v>3486189254.72</v>
       </c>
     </row>
     <row r="1165" spans="1:7" x14ac:dyDescent="0.25">
@@ -39451,17 +39451,17 @@
       <c r="C1165" s="6">
         <v>46266</v>
       </c>
-      <c r="D1165" s="8">
-        <v>0</v>
+      <c r="D1165" s="7">
+        <v>2.133866</v>
       </c>
       <c r="E1165" s="8">
-        <v>0</v>
+        <v>1833223343</v>
       </c>
       <c r="F1165" s="9">
         <v>15</v>
       </c>
       <c r="G1165" s="8">
-        <v>0</v>
+        <v>3911853428.46</v>
       </c>
     </row>
     <row r="1166" spans="1:7" x14ac:dyDescent="0.25">
@@ -40141,17 +40141,17 @@
       <c r="C1195" s="6">
         <v>46266</v>
       </c>
-      <c r="D1195" s="8">
-        <v>0</v>
+      <c r="D1195" s="7">
+        <v>0.791219</v>
       </c>
       <c r="E1195" s="8">
-        <v>0</v>
+        <v>1033653600</v>
       </c>
       <c r="F1195" s="9">
         <v>19</v>
       </c>
       <c r="G1195" s="8">
-        <v>0</v>
+        <v>817845878.46</v>
       </c>
     </row>
     <row r="1196" spans="1:7" x14ac:dyDescent="0.25">
@@ -40326,7 +40326,7 @@
         <v>46266</v>
       </c>
       <c r="D1203" s="7">
-        <v>1.111173</v>
+        <v>1.113722</v>
       </c>
       <c r="E1203" s="8">
         <v>58874427</v>
@@ -40335,7 +40335,7 @@
         <v>15</v>
       </c>
       <c r="G1203" s="8">
-        <v>65419698.99</v>
+        <v>65569735.99</v>
       </c>
     </row>
     <row r="1204" spans="1:7" x14ac:dyDescent="0.25">
@@ -40394,17 +40394,17 @@
       <c r="C1206" s="6">
         <v>46266</v>
       </c>
-      <c r="D1206" s="8">
-        <v>0</v>
+      <c r="D1206" s="7">
+        <v>1.532753</v>
       </c>
       <c r="E1206" s="8">
-        <v>0</v>
+        <v>1475059875</v>
       </c>
       <c r="F1206" s="9">
         <v>392</v>
       </c>
       <c r="G1206" s="8">
-        <v>0</v>
+        <v>2260902037.7</v>
       </c>
     </row>
     <row r="1207" spans="1:7" x14ac:dyDescent="0.25">
@@ -40749,7 +40749,7 @@
         <v>41</v>
       </c>
       <c r="G1221" s="8">
-        <v>1500412701.42</v>
+        <v>1500412455.49</v>
       </c>
     </row>
     <row r="1222" spans="1:7" x14ac:dyDescent="0.25">
@@ -41154,7 +41154,7 @@
         <v>46266</v>
       </c>
       <c r="D1239" s="7">
-        <v>1.640858</v>
+        <v>1.641754</v>
       </c>
       <c r="E1239" s="8">
         <v>229066800</v>
@@ -41163,7 +41163,7 @@
         <v>9579</v>
       </c>
       <c r="G1239" s="8">
-        <v>375866187.22</v>
+        <v>376071363.79</v>
       </c>
     </row>
     <row r="1240" spans="1:7" x14ac:dyDescent="0.25">
@@ -41291,17 +41291,17 @@
       <c r="C1245" s="6">
         <v>46266</v>
       </c>
-      <c r="D1245" s="8">
-        <v>0</v>
+      <c r="D1245" s="7">
+        <v>1.264743</v>
       </c>
       <c r="E1245" s="8">
-        <v>0</v>
+        <v>649087268</v>
       </c>
       <c r="F1245" s="9">
         <v>372</v>
       </c>
       <c r="G1245" s="8">
-        <v>0</v>
+        <v>820928724.3</v>
       </c>
     </row>
     <row r="1246" spans="1:7" x14ac:dyDescent="0.25">
@@ -41452,17 +41452,17 @@
       <c r="C1252" s="6">
         <v>46266</v>
       </c>
-      <c r="D1252" s="8">
-        <v>0</v>
+      <c r="D1252" s="7">
+        <v>1.608672</v>
       </c>
       <c r="E1252" s="8">
-        <v>0</v>
+        <v>592973692</v>
       </c>
       <c r="F1252" s="9">
         <v>1</v>
       </c>
       <c r="G1252" s="8">
-        <v>0</v>
+        <v>953900381.75</v>
       </c>
     </row>
     <row r="1253" spans="1:7" x14ac:dyDescent="0.25">
@@ -41590,17 +41590,17 @@
       <c r="C1258" s="6">
         <v>46266</v>
       </c>
-      <c r="D1258" s="8">
-        <v>0</v>
+      <c r="D1258" s="7">
+        <v>2.220394</v>
       </c>
       <c r="E1258" s="8">
-        <v>0</v>
+        <v>965724797</v>
       </c>
       <c r="F1258" s="9">
         <v>1302</v>
       </c>
       <c r="G1258" s="8">
-        <v>0</v>
+        <v>2144289332.9</v>
       </c>
     </row>
     <row r="1259" spans="1:7" x14ac:dyDescent="0.25">
@@ -42189,7 +42189,7 @@
         <v>46266</v>
       </c>
       <c r="D1284" s="7">
-        <v>1.023701</v>
+        <v>1.023579</v>
       </c>
       <c r="E1284" s="8">
         <v>825016483</v>
@@ -42198,7 +42198,7 @@
         <v>370</v>
       </c>
       <c r="G1284" s="8">
-        <v>844569898.24</v>
+        <v>844469685.77</v>
       </c>
     </row>
     <row r="1285" spans="1:7" x14ac:dyDescent="0.25">
@@ -42418,8 +42418,8 @@
       <c r="C1294" s="6">
         <v>46266</v>
       </c>
-      <c r="D1294" s="7">
-        <v>58.566258</v>
+      <c r="D1294" s="10">
+        <v>58.56567</v>
       </c>
       <c r="E1294" s="8">
         <v>667763977</v>
@@ -42428,7 +42428,7 @@
         <v>4977</v>
       </c>
       <c r="G1294" s="8">
-        <v>39108437558.37</v>
+        <v>39108044833.91</v>
       </c>
     </row>
     <row r="1295" spans="1:7" x14ac:dyDescent="0.25">
@@ -42557,7 +42557,7 @@
         <v>46266</v>
       </c>
       <c r="D1300" s="7">
-        <v>4.091707</v>
+        <v>4.091683</v>
       </c>
       <c r="E1300" s="8">
         <v>38446328</v>
@@ -42566,7 +42566,7 @@
         <v>584</v>
       </c>
       <c r="G1300" s="8">
-        <v>157311122.62</v>
+        <v>157310179.48</v>
       </c>
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.25">
@@ -42626,7 +42626,7 @@
         <v>46266</v>
       </c>
       <c r="D1303" s="7">
-        <v>8.315189</v>
+        <v>8.315228</v>
       </c>
       <c r="E1303" s="8">
         <v>22549204</v>
@@ -42635,7 +42635,7 @@
         <v>433</v>
       </c>
       <c r="G1303" s="8">
-        <v>187500884.74</v>
+        <v>187501764.12</v>
       </c>
     </row>
     <row r="1304" spans="1:7" x14ac:dyDescent="0.25">
@@ -42911,7 +42911,7 @@
         <v>27774</v>
       </c>
       <c r="G1315" s="8">
-        <v>47623986407.7</v>
+        <v>47623986165.4</v>
       </c>
     </row>
     <row r="1316" spans="1:7" x14ac:dyDescent="0.25">
@@ -42925,7 +42925,7 @@
         <v>46266</v>
       </c>
       <c r="D1316" s="7">
-        <v>12.990225</v>
+        <v>12.979013</v>
       </c>
       <c r="E1316" s="8">
         <v>361063500</v>
@@ -42934,7 +42934,7 @@
         <v>11172</v>
       </c>
       <c r="G1316" s="8">
-        <v>4690296256.31</v>
+        <v>4686247853.08</v>
       </c>
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
@@ -43385,7 +43385,7 @@
         <v>46266</v>
       </c>
       <c r="D1336" s="7">
-        <v>6.545775</v>
+        <v>6.545769</v>
       </c>
       <c r="E1336" s="8">
         <v>224500822</v>
@@ -43394,7 +43394,7 @@
         <v>586</v>
       </c>
       <c r="G1336" s="8">
-        <v>1469531842.47</v>
+        <v>1469530617.76</v>
       </c>
     </row>
     <row r="1337" spans="1:7" x14ac:dyDescent="0.25">
@@ -43661,7 +43661,7 @@
         <v>46266</v>
       </c>
       <c r="D1348" s="7">
-        <v>1.531909</v>
+        <v>1.531483</v>
       </c>
       <c r="E1348" s="8">
         <v>934875713</v>
@@ -43670,7 +43670,7 @@
         <v>56</v>
       </c>
       <c r="G1348" s="8">
-        <v>1432144271.84</v>
+        <v>1431746294.74</v>
       </c>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.25">
@@ -43868,7 +43868,7 @@
         <v>46266</v>
       </c>
       <c r="D1357" s="7">
-        <v>7.319139</v>
+        <v>7.300961</v>
       </c>
       <c r="E1357" s="8">
         <v>448850509</v>
@@ -43877,7 +43877,7 @@
         <v>22218</v>
       </c>
       <c r="G1357" s="8">
-        <v>3285199485.39</v>
+        <v>3277039949.28</v>
       </c>
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.25">
@@ -44235,17 +44235,17 @@
       <c r="C1373" s="6">
         <v>46266</v>
       </c>
-      <c r="D1373" s="8">
-        <v>0</v>
+      <c r="D1373" s="12">
+        <v>1.1124</v>
       </c>
       <c r="E1373" s="8">
-        <v>0</v>
+        <v>42020747</v>
       </c>
       <c r="F1373" s="9">
         <v>533</v>
       </c>
       <c r="G1373" s="8">
-        <v>0</v>
+        <v>46743880.18</v>
       </c>
     </row>
     <row r="1374" spans="1:7" x14ac:dyDescent="0.25">
@@ -44351,7 +44351,7 @@
         <v>46266</v>
       </c>
       <c r="D1378" s="7">
-        <v>57.511081</v>
+        <v>57.511112</v>
       </c>
       <c r="E1378" s="8">
         <v>2644372358</v>
@@ -44360,7 +44360,7 @@
         <v>31262</v>
       </c>
       <c r="G1378" s="8">
-        <v>152080711775.1</v>
+        <v>152080794026.12</v>
       </c>
     </row>
     <row r="1379" spans="1:7" x14ac:dyDescent="0.25">
@@ -44926,7 +44926,7 @@
         <v>46266</v>
       </c>
       <c r="D1403" s="7">
-        <v>2.389415</v>
+        <v>2.379669</v>
       </c>
       <c r="E1403" s="8">
         <v>32114158</v>
@@ -44935,7 +44935,7 @@
         <v>286</v>
       </c>
       <c r="G1403" s="8">
-        <v>76734065.35</v>
+        <v>76421063.05</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.25">
@@ -45271,7 +45271,7 @@
         <v>46266</v>
       </c>
       <c r="D1418" s="7">
-        <v>3.950982</v>
+        <v>3.934491</v>
       </c>
       <c r="E1418" s="8">
         <v>118469672</v>
@@ -45280,7 +45280,7 @@
         <v>8095</v>
       </c>
       <c r="G1418" s="8">
-        <v>468071592.14</v>
+        <v>466117801.52</v>
       </c>
     </row>
     <row r="1419" spans="1:7" x14ac:dyDescent="0.25">
@@ -45500,17 +45500,17 @@
       <c r="C1428" s="6">
         <v>46266</v>
       </c>
-      <c r="D1428" s="8">
-        <v>0</v>
+      <c r="D1428" s="10">
+        <v>2.52128</v>
       </c>
       <c r="E1428" s="8">
-        <v>0</v>
+        <v>605506954</v>
       </c>
       <c r="F1428" s="9">
         <v>12</v>
       </c>
       <c r="G1428" s="8">
-        <v>0</v>
+        <v>1526652870.11</v>
       </c>
     </row>
     <row r="1429" spans="1:7" x14ac:dyDescent="0.25">
@@ -45707,17 +45707,17 @@
       <c r="C1437" s="6">
         <v>46266</v>
       </c>
-      <c r="D1437" s="8">
-        <v>0</v>
+      <c r="D1437" s="7">
+        <v>1.291258</v>
       </c>
       <c r="E1437" s="8">
-        <v>0</v>
+        <v>548515</v>
       </c>
       <c r="F1437" s="9">
         <v>116</v>
       </c>
       <c r="G1437" s="8">
-        <v>0</v>
+        <v>708274.4</v>
       </c>
     </row>
     <row r="1438" spans="1:7" x14ac:dyDescent="0.25">
@@ -45845,17 +45845,17 @@
       <c r="C1443" s="6">
         <v>46266</v>
       </c>
-      <c r="D1443" s="8">
-        <v>0</v>
+      <c r="D1443" s="7">
+        <v>1.253905</v>
       </c>
       <c r="E1443" s="8">
-        <v>0</v>
+        <v>30367679180</v>
       </c>
       <c r="F1443" s="9">
         <v>25455</v>
       </c>
       <c r="G1443" s="8">
-        <v>0</v>
+        <v>38078177494.68</v>
       </c>
     </row>
     <row r="1444" spans="1:7" x14ac:dyDescent="0.25">
@@ -47754,8 +47754,8 @@
       <c r="C1526" s="6">
         <v>46266</v>
       </c>
-      <c r="D1526" s="7">
-        <v>1.855581</v>
+      <c r="D1526" s="10">
+        <v>1.85574</v>
       </c>
       <c r="E1526" s="8">
         <v>173521197</v>
@@ -47764,7 +47764,7 @@
         <v>819</v>
       </c>
       <c r="G1526" s="8">
-        <v>321982706.7</v>
+        <v>322010240.43</v>
       </c>
     </row>
     <row r="1527" spans="1:7" x14ac:dyDescent="0.25">
@@ -48192,7 +48192,7 @@
         <v>46266</v>
       </c>
       <c r="D1545" s="7">
-        <v>1.109952</v>
+        <v>1.109636</v>
       </c>
       <c r="E1545" s="8">
         <v>25507460</v>
@@ -48201,7 +48201,7 @@
         <v>461</v>
       </c>
       <c r="G1545" s="8">
-        <v>28312060.39</v>
+        <v>28303987.07</v>
       </c>
     </row>
     <row r="1546" spans="1:7" x14ac:dyDescent="0.25">
@@ -48881,17 +48881,17 @@
       <c r="C1575" s="6">
         <v>46266</v>
       </c>
-      <c r="D1575" s="8">
-        <v>0</v>
+      <c r="D1575" s="7">
+        <v>5.020432</v>
       </c>
       <c r="E1575" s="8">
-        <v>0</v>
+        <v>1319468950</v>
       </c>
       <c r="F1575" s="9">
         <v>7584</v>
       </c>
       <c r="G1575" s="8">
-        <v>0</v>
+        <v>6624304138.15</v>
       </c>
     </row>
     <row r="1576" spans="1:7" x14ac:dyDescent="0.25">
@@ -49410,17 +49410,17 @@
       <c r="C1598" s="6">
         <v>46266</v>
       </c>
-      <c r="D1598" s="8">
-        <v>0</v>
+      <c r="D1598" s="10">
+        <v>1.24333</v>
       </c>
       <c r="E1598" s="8">
-        <v>0</v>
+        <v>300626629</v>
       </c>
       <c r="F1598" s="9">
         <v>1</v>
       </c>
       <c r="G1598" s="8">
-        <v>0</v>
+        <v>373778196.56</v>
       </c>
     </row>
     <row r="1599" spans="1:7" x14ac:dyDescent="0.25">
@@ -49640,17 +49640,17 @@
       <c r="C1608" s="6">
         <v>46266</v>
       </c>
-      <c r="D1608" s="8">
-        <v>0</v>
+      <c r="D1608" s="7">
+        <v>1.736096</v>
       </c>
       <c r="E1608" s="8">
-        <v>0</v>
+        <v>210515596</v>
       </c>
       <c r="F1608" s="9">
         <v>735</v>
       </c>
       <c r="G1608" s="8">
-        <v>0</v>
+        <v>365475358.93</v>
       </c>
     </row>
     <row r="1609" spans="1:7" x14ac:dyDescent="0.25">
@@ -49755,17 +49755,17 @@
       <c r="C1613" s="6">
         <v>46266</v>
       </c>
-      <c r="D1613" s="8">
-        <v>0</v>
+      <c r="D1613" s="7">
+        <v>1.018842</v>
       </c>
       <c r="E1613" s="8">
-        <v>0</v>
+        <v>46921705</v>
       </c>
       <c r="F1613" s="9">
         <v>202</v>
       </c>
       <c r="G1613" s="8">
-        <v>0</v>
+        <v>47805807.21</v>
       </c>
     </row>
     <row r="1614" spans="1:7" x14ac:dyDescent="0.25">
@@ -49871,7 +49871,7 @@
         <v>46266</v>
       </c>
       <c r="D1618" s="7">
-        <v>1.431782</v>
+        <v>1.418438</v>
       </c>
       <c r="E1618" s="8">
         <v>22276079</v>
@@ -49880,7 +49880,7 @@
         <v>82</v>
       </c>
       <c r="G1618" s="8">
-        <v>31894492.02</v>
+        <v>31597231.47</v>
       </c>
     </row>
     <row r="1619" spans="1:7" x14ac:dyDescent="0.25">
@@ -49916,17 +49916,17 @@
       <c r="C1620" s="6">
         <v>46266</v>
       </c>
-      <c r="D1620" s="8">
-        <v>0</v>
+      <c r="D1620" s="7">
+        <v>1.991059</v>
       </c>
       <c r="E1620" s="8">
-        <v>0</v>
+        <v>101958620</v>
       </c>
       <c r="F1620" s="9">
         <v>2626</v>
       </c>
       <c r="G1620" s="8">
-        <v>0</v>
+        <v>203005588.77</v>
       </c>
     </row>
     <row r="1621" spans="1:7" x14ac:dyDescent="0.25">
@@ -50008,17 +50008,17 @@
       <c r="C1624" s="6">
         <v>46266</v>
       </c>
-      <c r="D1624" s="8">
-        <v>0</v>
+      <c r="D1624" s="7">
+        <v>1.451943</v>
       </c>
       <c r="E1624" s="8">
-        <v>0</v>
+        <v>304160226</v>
       </c>
       <c r="F1624" s="9">
         <v>37</v>
       </c>
       <c r="G1624" s="8">
-        <v>0</v>
+        <v>441623392.39</v>
       </c>
     </row>
     <row r="1625" spans="1:7" x14ac:dyDescent="0.25">
@@ -50031,17 +50031,17 @@
       <c r="C1625" s="6">
         <v>46266</v>
       </c>
-      <c r="D1625" s="8">
-        <v>0</v>
+      <c r="D1625" s="7">
+        <v>0.877204</v>
       </c>
       <c r="E1625" s="8">
-        <v>0</v>
+        <v>1072723</v>
       </c>
       <c r="F1625" s="9">
         <v>11</v>
       </c>
       <c r="G1625" s="8">
-        <v>0</v>
+        <v>940996.88</v>
       </c>
     </row>
     <row r="1626" spans="1:7" x14ac:dyDescent="0.25">
@@ -50054,17 +50054,17 @@
       <c r="C1626" s="6">
         <v>46266</v>
       </c>
-      <c r="D1626" s="8">
-        <v>0</v>
+      <c r="D1626" s="7">
+        <v>0.254252</v>
       </c>
       <c r="E1626" s="8">
-        <v>0</v>
+        <v>211943093</v>
       </c>
       <c r="F1626" s="9">
         <v>13</v>
       </c>
       <c r="G1626" s="8">
-        <v>0</v>
+        <v>53887050.44</v>
       </c>
     </row>
     <row r="1627" spans="1:7" x14ac:dyDescent="0.25">
@@ -50354,7 +50354,7 @@
         <v>46266</v>
       </c>
       <c r="D1639" s="7">
-        <v>1.690673</v>
+        <v>1.690667</v>
       </c>
       <c r="E1639" s="8">
         <v>22950480</v>
@@ -50363,7 +50363,7 @@
         <v>533</v>
       </c>
       <c r="G1639" s="8">
-        <v>38801747.11</v>
+        <v>38801626.59</v>
       </c>
     </row>
     <row r="1640" spans="1:7" x14ac:dyDescent="0.25">
@@ -50698,8 +50698,8 @@
       <c r="C1654" s="6">
         <v>46266</v>
       </c>
-      <c r="D1654" s="10">
-        <v>1.76477</v>
+      <c r="D1654" s="7">
+        <v>1.764648</v>
       </c>
       <c r="E1654" s="8">
         <v>28562196</v>
@@ -50708,7 +50708,7 @@
         <v>593</v>
       </c>
       <c r="G1654" s="8">
-        <v>50405707.69</v>
+        <v>50402233.16</v>
       </c>
     </row>
     <row r="1655" spans="1:7" x14ac:dyDescent="0.25">
@@ -50836,8 +50836,8 @@
       <c r="C1660" s="6">
         <v>46266</v>
       </c>
-      <c r="D1660" s="7">
-        <v>1.290888</v>
+      <c r="D1660" s="10">
+        <v>1.28955</v>
       </c>
       <c r="E1660" s="8">
         <v>144552329</v>
@@ -50846,7 +50846,7 @@
         <v>74</v>
       </c>
       <c r="G1660" s="8">
-        <v>186600931.18</v>
+        <v>186407440.16</v>
       </c>
     </row>
     <row r="1661" spans="1:7" x14ac:dyDescent="0.25">
@@ -51044,7 +51044,7 @@
         <v>46266</v>
       </c>
       <c r="D1669" s="7">
-        <v>2.723993</v>
+        <v>2.724013</v>
       </c>
       <c r="E1669" s="8">
         <v>414228781</v>
@@ -51053,7 +51053,7 @@
         <v>1</v>
       </c>
       <c r="G1669" s="8">
-        <v>1128356484.56</v>
+        <v>1128364548.27</v>
       </c>
     </row>
     <row r="1670" spans="1:7" x14ac:dyDescent="0.25">
@@ -51205,7 +51205,7 @@
         <v>46266</v>
       </c>
       <c r="D1676" s="7">
-        <v>2.653747</v>
+        <v>2.798728</v>
       </c>
       <c r="E1676" s="8">
         <v>12681669</v>
@@ -51214,7 +51214,7 @@
         <v>755</v>
       </c>
       <c r="G1676" s="8">
-        <v>33653937.56</v>
+        <v>35492546.09</v>
       </c>
     </row>
     <row r="1677" spans="1:7" x14ac:dyDescent="0.25">
@@ -51687,17 +51687,17 @@
       <c r="C1697" s="6">
         <v>46266</v>
       </c>
-      <c r="D1697" s="8">
-        <v>0</v>
+      <c r="D1697" s="7">
+        <v>6.632262</v>
       </c>
       <c r="E1697" s="8">
-        <v>0</v>
+        <v>275888407</v>
       </c>
       <c r="F1697" s="9">
         <v>1444</v>
       </c>
       <c r="G1697" s="8">
-        <v>0</v>
+        <v>1829764169.39</v>
       </c>
     </row>
     <row r="1698" spans="1:7" x14ac:dyDescent="0.25">
@@ -51711,7 +51711,7 @@
         <v>46266</v>
       </c>
       <c r="D1698" s="7">
-        <v>2.771115</v>
+        <v>2.766351</v>
       </c>
       <c r="E1698" s="8">
         <v>263782035</v>
@@ -51720,7 +51720,7 @@
         <v>1322</v>
       </c>
       <c r="G1698" s="8">
-        <v>730970333.09</v>
+        <v>729713672.5</v>
       </c>
     </row>
     <row r="1699" spans="1:7" x14ac:dyDescent="0.25">
@@ -52332,16 +52332,16 @@
         <v>46266</v>
       </c>
       <c r="D1725" s="7">
-        <v>50.295742</v>
+        <v>50.302296</v>
       </c>
       <c r="E1725" s="8">
-        <v>16293472</v>
+        <v>17693616</v>
       </c>
       <c r="F1725" s="9">
         <v>77</v>
       </c>
       <c r="G1725" s="8">
-        <v>819492264.61</v>
+        <v>890029505.63</v>
       </c>
     </row>
     <row r="1726" spans="1:7" x14ac:dyDescent="0.25">
@@ -52584,17 +52584,17 @@
       <c r="C1736" s="6">
         <v>46266</v>
       </c>
-      <c r="D1736" s="8">
-        <v>0</v>
+      <c r="D1736" s="7">
+        <v>1.066846</v>
       </c>
       <c r="E1736" s="8">
-        <v>0</v>
+        <v>411131729</v>
       </c>
       <c r="F1736" s="9">
         <v>310</v>
       </c>
       <c r="G1736" s="8">
-        <v>0</v>
+        <v>438614104.91</v>
       </c>
     </row>
     <row r="1737" spans="1:7" x14ac:dyDescent="0.25">
@@ -52745,17 +52745,17 @@
       <c r="C1743" s="6">
         <v>46266</v>
       </c>
-      <c r="D1743" s="8">
-        <v>0</v>
+      <c r="D1743" s="7">
+        <v>9200.361325</v>
       </c>
       <c r="E1743" s="8">
-        <v>0</v>
+        <v>29214243</v>
       </c>
       <c r="F1743" s="9">
         <v>111462</v>
       </c>
       <c r="G1743" s="8">
-        <v>0</v>
+        <v>268781591425.07</v>
       </c>
     </row>
     <row r="1744" spans="1:7" x14ac:dyDescent="0.25">
@@ -52916,7 +52916,7 @@
         <v>85</v>
       </c>
       <c r="G1750" s="8">
-        <v>405006548.1</v>
+        <v>405006548.09</v>
       </c>
     </row>
     <row r="1751" spans="1:7" x14ac:dyDescent="0.25">
@@ -52930,7 +52930,7 @@
         <v>46266</v>
       </c>
       <c r="D1751" s="7">
-        <v>1.443176</v>
+        <v>1.439715</v>
       </c>
       <c r="E1751" s="8">
         <v>41286219</v>
@@ -52939,7 +52939,7 @@
         <v>91</v>
       </c>
       <c r="G1751" s="8">
-        <v>59583280.49</v>
+        <v>59440386.57</v>
       </c>
     </row>
     <row r="1752" spans="1:7" x14ac:dyDescent="0.25">
@@ -53090,17 +53090,17 @@
       <c r="C1758" s="6">
         <v>46266</v>
       </c>
-      <c r="D1758" s="8">
-        <v>0</v>
+      <c r="D1758" s="7">
+        <v>11.487512</v>
       </c>
       <c r="E1758" s="8">
-        <v>0</v>
+        <v>697132441</v>
       </c>
       <c r="F1758" s="9">
         <v>2770</v>
       </c>
       <c r="G1758" s="8">
-        <v>0</v>
+        <v>8008317223.33</v>
       </c>
     </row>
     <row r="1759" spans="1:7" x14ac:dyDescent="0.25">
@@ -53366,17 +53366,17 @@
       <c r="C1770" s="6">
         <v>46266</v>
       </c>
-      <c r="D1770" s="8">
-        <v>0</v>
+      <c r="D1770" s="7">
+        <v>21.357115</v>
       </c>
       <c r="E1770" s="8">
-        <v>0</v>
+        <v>23597470.01</v>
       </c>
       <c r="F1770" s="9">
         <v>1519</v>
       </c>
       <c r="G1770" s="8">
-        <v>0</v>
+        <v>503973887.88</v>
       </c>
     </row>
     <row r="1771" spans="1:7" x14ac:dyDescent="0.25">
@@ -53412,17 +53412,17 @@
       <c r="C1772" s="6">
         <v>46266</v>
       </c>
-      <c r="D1772" s="8">
-        <v>0</v>
+      <c r="D1772" s="7">
+        <v>78.102177</v>
       </c>
       <c r="E1772" s="8">
-        <v>0</v>
+        <v>24001000</v>
       </c>
       <c r="F1772" s="9">
         <v>395</v>
       </c>
       <c r="G1772" s="8">
-        <v>0</v>
+        <v>1874530361.22</v>
       </c>
     </row>
     <row r="1773" spans="1:7" x14ac:dyDescent="0.25">
@@ -53826,8 +53826,8 @@
       <c r="C1790" s="6">
         <v>46266</v>
       </c>
-      <c r="D1790" s="10">
-        <v>1.48979</v>
+      <c r="D1790" s="7">
+        <v>1.489814</v>
       </c>
       <c r="E1790" s="8">
         <v>10381318222.21</v>
@@ -53836,7 +53836,7 @@
         <v>31452</v>
       </c>
       <c r="G1790" s="8">
-        <v>15465988077.63</v>
+        <v>15466237185.81</v>
       </c>
     </row>
     <row r="1791" spans="1:7" x14ac:dyDescent="0.25">
@@ -53873,7 +53873,7 @@
         <v>46266</v>
       </c>
       <c r="D1792" s="7">
-        <v>2.994975</v>
+        <v>2.977298</v>
       </c>
       <c r="E1792" s="8">
         <v>3094370</v>
@@ -53882,7 +53882,7 @@
         <v>525</v>
       </c>
       <c r="G1792" s="8">
-        <v>9267561.78</v>
+        <v>9212860.76</v>
       </c>
     </row>
     <row r="1793" spans="1:7" x14ac:dyDescent="0.25">
@@ -54447,17 +54447,17 @@
       <c r="C1817" s="6">
         <v>46266</v>
       </c>
-      <c r="D1817" s="8">
-        <v>0</v>
+      <c r="D1817" s="7">
+        <v>1.952039</v>
       </c>
       <c r="E1817" s="8">
-        <v>0</v>
+        <v>346377325</v>
       </c>
       <c r="F1817" s="9">
         <v>9244</v>
       </c>
       <c r="G1817" s="8">
-        <v>0</v>
+        <v>676142150.3</v>
       </c>
     </row>
     <row r="1818" spans="1:7" x14ac:dyDescent="0.25">
@@ -55275,17 +55275,17 @@
       <c r="C1853" s="6">
         <v>46266</v>
       </c>
-      <c r="D1853" s="8">
-        <v>0</v>
+      <c r="D1853" s="10">
+        <v>14.80796</v>
       </c>
       <c r="E1853" s="8">
-        <v>0</v>
+        <v>370599277</v>
       </c>
       <c r="F1853" s="9">
         <v>9826</v>
       </c>
       <c r="G1853" s="8">
-        <v>0</v>
+        <v>5487819381.5</v>
       </c>
     </row>
     <row r="1854" spans="1:7" x14ac:dyDescent="0.25">
@@ -55344,17 +55344,17 @@
       <c r="C1856" s="6">
         <v>46266</v>
       </c>
-      <c r="D1856" s="8">
-        <v>0</v>
+      <c r="D1856" s="7">
+        <v>14.689645</v>
       </c>
       <c r="E1856" s="8">
-        <v>0</v>
+        <v>127168179</v>
       </c>
       <c r="F1856" s="9">
         <v>3583</v>
       </c>
       <c r="G1856" s="8">
-        <v>0</v>
+        <v>1868055352.22</v>
       </c>
     </row>
     <row r="1857" spans="1:7" x14ac:dyDescent="0.25">
@@ -55597,17 +55597,17 @@
       <c r="C1867" s="6">
         <v>46266</v>
       </c>
-      <c r="D1867" s="8">
-        <v>0</v>
+      <c r="D1867" s="7">
+        <v>2.723435</v>
       </c>
       <c r="E1867" s="8">
-        <v>0</v>
+        <v>39652266</v>
       </c>
       <c r="F1867" s="9">
         <v>114</v>
       </c>
       <c r="G1867" s="8">
-        <v>0</v>
+        <v>107990350.77</v>
       </c>
     </row>
     <row r="1868" spans="1:7" x14ac:dyDescent="0.25">
@@ -56172,17 +56172,17 @@
       <c r="C1892" s="6">
         <v>46266</v>
       </c>
-      <c r="D1892" s="8">
-        <v>0</v>
+      <c r="D1892" s="7">
+        <v>2.616048</v>
       </c>
       <c r="E1892" s="8">
-        <v>0</v>
+        <v>865562461</v>
       </c>
       <c r="F1892" s="9">
         <v>16454</v>
       </c>
       <c r="G1892" s="8">
-        <v>0</v>
+        <v>2264352988.74</v>
       </c>
     </row>
     <row r="1893" spans="1:7" x14ac:dyDescent="0.25">
@@ -56264,17 +56264,17 @@
       <c r="C1896" s="6">
         <v>46266</v>
       </c>
-      <c r="D1896" s="8">
-        <v>0</v>
+      <c r="D1896" s="7">
+        <v>5.713071</v>
       </c>
       <c r="E1896" s="8">
-        <v>0</v>
+        <v>179905794</v>
       </c>
       <c r="F1896" s="9">
         <v>14107</v>
       </c>
       <c r="G1896" s="8">
-        <v>0</v>
+        <v>1027814586.43</v>
       </c>
     </row>
     <row r="1897" spans="1:7" x14ac:dyDescent="0.25">
@@ -57092,17 +57092,17 @@
       <c r="C1932" s="6">
         <v>46266</v>
       </c>
-      <c r="D1932" s="8">
-        <v>0</v>
+      <c r="D1932" s="7">
+        <v>7.966284</v>
       </c>
       <c r="E1932" s="8">
-        <v>0</v>
+        <v>699481451</v>
       </c>
       <c r="F1932" s="9">
         <v>3350</v>
       </c>
       <c r="G1932" s="8">
-        <v>0</v>
+        <v>5572268195.96</v>
       </c>
     </row>
     <row r="1933" spans="1:7" x14ac:dyDescent="0.25">
@@ -57253,17 +57253,17 @@
       <c r="C1939" s="6">
         <v>46266</v>
       </c>
-      <c r="D1939" s="8">
-        <v>0</v>
+      <c r="D1939" s="7">
+        <v>0.956629</v>
       </c>
       <c r="E1939" s="8">
-        <v>0</v>
+        <v>1841796390</v>
       </c>
       <c r="F1939" s="9">
         <v>14914</v>
       </c>
       <c r="G1939" s="8">
-        <v>0</v>
+        <v>1761916077.95</v>
       </c>
     </row>
     <row r="1940" spans="1:7" x14ac:dyDescent="0.25">
@@ -57713,17 +57713,17 @@
       <c r="C1959" s="6">
         <v>46266</v>
       </c>
-      <c r="D1959" s="8">
-        <v>0</v>
+      <c r="D1959" s="7">
+        <v>13.490173</v>
       </c>
       <c r="E1959" s="8">
-        <v>0</v>
+        <v>830967202</v>
       </c>
       <c r="F1959" s="9">
         <v>60813</v>
       </c>
       <c r="G1959" s="8">
-        <v>0</v>
+        <v>11209891611.55</v>
       </c>
     </row>
     <row r="1960" spans="1:7" x14ac:dyDescent="0.25">
@@ -58266,7 +58266,7 @@
         <v>46266</v>
       </c>
       <c r="D1983" s="7">
-        <v>4.097012</v>
+        <v>4.082127</v>
       </c>
       <c r="E1983" s="8">
         <v>152153200</v>
@@ -58275,7 +58275,7 @@
         <v>6532</v>
       </c>
       <c r="G1983" s="8">
-        <v>623373556.87</v>
+        <v>621108687.97</v>
       </c>
     </row>
     <row r="1984" spans="1:7" x14ac:dyDescent="0.25">
@@ -58818,7 +58818,7 @@
         <v>46266</v>
       </c>
       <c r="D2007" s="7">
-        <v>1.907324</v>
+        <v>1.911851</v>
       </c>
       <c r="E2007" s="8">
         <v>306521428</v>
@@ -58827,7 +58827,7 @@
         <v>11</v>
       </c>
       <c r="G2007" s="8">
-        <v>584635627.65</v>
+        <v>586023430.92</v>
       </c>
     </row>
     <row r="2008" spans="1:7" x14ac:dyDescent="0.25">
@@ -58864,7 +58864,7 @@
         <v>46266</v>
       </c>
       <c r="D2009" s="7">
-        <v>5.847087</v>
+        <v>5.847091</v>
       </c>
       <c r="E2009" s="8">
         <v>106786382</v>
@@ -58873,7 +58873,7 @@
         <v>1</v>
       </c>
       <c r="G2009" s="8">
-        <v>624389304.7</v>
+        <v>624389725.25</v>
       </c>
     </row>
     <row r="2010" spans="1:7" x14ac:dyDescent="0.25">
@@ -59025,7 +59025,7 @@
         <v>46266</v>
       </c>
       <c r="D2016" s="7">
-        <v>19.600985</v>
+        <v>19.598951</v>
       </c>
       <c r="E2016" s="8">
         <v>165036973</v>
@@ -59034,7 +59034,7 @@
         <v>2788</v>
       </c>
       <c r="G2016" s="8">
-        <v>3234887178.03</v>
+        <v>3234551489.09</v>
       </c>
     </row>
     <row r="2017" spans="1:7" x14ac:dyDescent="0.25">
@@ -59301,7 +59301,7 @@
         <v>46266</v>
       </c>
       <c r="D2028" s="7">
-        <v>12.249761</v>
+        <v>12.260817</v>
       </c>
       <c r="E2028" s="8">
         <v>299315692</v>
@@ -59310,7 +59310,7 @@
         <v>24</v>
       </c>
       <c r="G2028" s="8">
-        <v>3666545652.03</v>
+        <v>3669854905.28</v>
       </c>
     </row>
     <row r="2029" spans="1:7" x14ac:dyDescent="0.25">
@@ -59347,7 +59347,7 @@
         <v>46266</v>
       </c>
       <c r="D2030" s="7">
-        <v>4.362751</v>
+        <v>4.344927</v>
       </c>
       <c r="E2030" s="8">
         <v>11440100</v>
@@ -59356,7 +59356,7 @@
         <v>917</v>
       </c>
       <c r="G2030" s="8">
-        <v>49910310.41</v>
+        <v>49706396.96</v>
       </c>
     </row>
     <row r="2031" spans="1:7" x14ac:dyDescent="0.25">
@@ -59416,7 +59416,7 @@
         <v>46266</v>
       </c>
       <c r="D2033" s="7">
-        <v>7.644873</v>
+        <v>7.653267</v>
       </c>
       <c r="E2033" s="8">
         <v>274862095</v>
@@ -59425,7 +59425,7 @@
         <v>1</v>
       </c>
       <c r="G2033" s="8">
-        <v>2101285760.93</v>
+        <v>2103593081.83</v>
       </c>
     </row>
     <row r="2034" spans="1:7" x14ac:dyDescent="0.25">
@@ -59439,7 +59439,7 @@
         <v>46266</v>
       </c>
       <c r="D2034" s="7">
-        <v>1.361266</v>
+        <v>1.361665</v>
       </c>
       <c r="E2034" s="8">
         <v>29444118</v>
@@ -59448,7 +59448,7 @@
         <v>1041</v>
       </c>
       <c r="G2034" s="8">
-        <v>40081284.75</v>
+        <v>40093012.65</v>
       </c>
     </row>
     <row r="2035" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>04.09.2026 09:32:35</t>
+    <t>04.09.2026 10:15:04</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -16719,7 +16719,7 @@
         <v>46269</v>
       </c>
       <c r="D176" s="7">
-        <v>1.796764</v>
+        <v>1.796757</v>
       </c>
       <c r="E176" s="8">
         <v>1229782874</v>
@@ -16728,7 +16728,7 @@
         <v>2794</v>
       </c>
       <c r="G176" s="8">
-        <v>2209630112.08</v>
+        <v>2209621312.78</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -18352,7 +18352,7 @@
         <v>46269</v>
       </c>
       <c r="D247" s="7">
-        <v>55.683386</v>
+        <v>55.665396</v>
       </c>
       <c r="E247" s="8">
         <v>2094162565.31</v>
@@ -18361,7 +18361,7 @@
         <v>25300</v>
       </c>
       <c r="G247" s="8">
-        <v>116610062733.92</v>
+        <v>116572388767.52</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -18490,7 +18490,7 @@
         <v>46269</v>
       </c>
       <c r="D253" s="7">
-        <v>0.115618</v>
+        <v>0.115619</v>
       </c>
       <c r="E253" s="8">
         <v>2673144838.85</v>
@@ -18499,7 +18499,7 @@
         <v>2030</v>
       </c>
       <c r="G253" s="8">
-        <v>309063400.88</v>
+        <v>309065080.78</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -19915,8 +19915,8 @@
       <c r="C315" s="6">
         <v>46269</v>
       </c>
-      <c r="D315" s="11">
-        <v>52.89528</v>
+      <c r="D315" s="7">
+        <v>53.258688</v>
       </c>
       <c r="E315" s="8">
         <v>26735461</v>
@@ -19925,7 +19925,7 @@
         <v>1066</v>
       </c>
       <c r="G315" s="8">
-        <v>1414179693.95</v>
+        <v>1423895572.45</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
@@ -20215,7 +20215,7 @@
         <v>46269</v>
       </c>
       <c r="D328" s="7">
-        <v>75.276468</v>
+        <v>75.143663</v>
       </c>
       <c r="E328" s="8">
         <v>7294243</v>
@@ -20224,7 +20224,7 @@
         <v>3</v>
       </c>
       <c r="G328" s="8">
-        <v>549084848.09</v>
+        <v>548116138.63</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -20491,7 +20491,7 @@
         <v>46269</v>
       </c>
       <c r="D340" s="7">
-        <v>103.462908</v>
+        <v>103.378584</v>
       </c>
       <c r="E340" s="8">
         <v>22490084</v>
@@ -20500,7 +20500,7 @@
         <v>1</v>
       </c>
       <c r="G340" s="8">
-        <v>2326889490.37</v>
+        <v>2324993045.82</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -20606,7 +20606,7 @@
         <v>46269</v>
       </c>
       <c r="D345" s="7">
-        <v>1.228882</v>
+        <v>1.232494</v>
       </c>
       <c r="E345" s="8">
         <v>34074242</v>
@@ -20615,7 +20615,7 @@
         <v>46</v>
       </c>
       <c r="G345" s="8">
-        <v>41873234.1</v>
+        <v>41996296.67</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
@@ -20721,7 +20721,7 @@
         <v>46269</v>
       </c>
       <c r="D350" s="7">
-        <v>72.690087</v>
+        <v>72.690026</v>
       </c>
       <c r="E350" s="8">
         <v>53664035</v>
@@ -20730,7 +20730,7 @@
         <v>1420</v>
       </c>
       <c r="G350" s="8">
-        <v>3900843368.54</v>
+        <v>3900840102.97</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
@@ -21365,7 +21365,7 @@
         <v>46269</v>
       </c>
       <c r="D378" s="7">
-        <v>1.370719</v>
+        <v>1.370715</v>
       </c>
       <c r="E378" s="8">
         <v>9211693295</v>
@@ -21374,7 +21374,7 @@
         <v>2</v>
       </c>
       <c r="G378" s="8">
-        <v>12626639224.49</v>
+        <v>12626608384.71</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
@@ -22928,8 +22928,8 @@
       <c r="C446" s="6">
         <v>46269</v>
       </c>
-      <c r="D446" s="11">
-        <v>8.76657</v>
+      <c r="D446" s="7">
+        <v>8.766535</v>
       </c>
       <c r="E446" s="8">
         <v>192445468</v>
@@ -22938,7 +22938,7 @@
         <v>2166</v>
       </c>
       <c r="G446" s="8">
-        <v>1687086675.91</v>
+        <v>1687080012.71</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
@@ -23504,7 +23504,7 @@
         <v>46269</v>
       </c>
       <c r="D471" s="7">
-        <v>0.206061</v>
+        <v>0.206724</v>
       </c>
       <c r="E471" s="8">
         <v>52368724685.04</v>
@@ -23513,7 +23513,7 @@
         <v>6542</v>
       </c>
       <c r="G471" s="8">
-        <v>10791174355.25</v>
+        <v>10825886816.75</v>
       </c>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
@@ -24240,7 +24240,7 @@
         <v>46269</v>
       </c>
       <c r="D503" s="7">
-        <v>0.761381</v>
+        <v>0.761382</v>
       </c>
       <c r="E503" s="8">
         <v>1224185375</v>
@@ -24249,7 +24249,7 @@
         <v>2162</v>
       </c>
       <c r="G503" s="8">
-        <v>932071085.36</v>
+        <v>932072738.68</v>
       </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
@@ -24676,17 +24676,17 @@
       <c r="C522" s="6">
         <v>46269</v>
       </c>
-      <c r="D522" s="8">
-        <v>0</v>
+      <c r="D522" s="7">
+        <v>77.973088</v>
       </c>
       <c r="E522" s="8">
-        <v>0</v>
+        <v>5527677</v>
       </c>
       <c r="F522" s="9">
         <v>1</v>
       </c>
       <c r="G522" s="8">
-        <v>0</v>
+        <v>431010045.92</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.25">
@@ -24768,17 +24768,17 @@
       <c r="C526" s="6">
         <v>46269</v>
       </c>
-      <c r="D526" s="8">
-        <v>0</v>
+      <c r="D526" s="7">
+        <v>12.742183</v>
       </c>
       <c r="E526" s="8">
-        <v>0</v>
+        <v>29021709</v>
       </c>
       <c r="F526" s="9">
         <v>2708</v>
       </c>
       <c r="G526" s="8">
-        <v>0</v>
+        <v>369799939.38</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
@@ -24791,17 +24791,17 @@
       <c r="C527" s="6">
         <v>46269</v>
       </c>
-      <c r="D527" s="8">
-        <v>0</v>
+      <c r="D527" s="7">
+        <v>63.987502</v>
       </c>
       <c r="E527" s="8">
-        <v>0</v>
+        <v>7935068</v>
       </c>
       <c r="F527" s="9">
         <v>1</v>
       </c>
       <c r="G527" s="8">
-        <v>0</v>
+        <v>507745182.86</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.25">
@@ -24883,17 +24883,17 @@
       <c r="C531" s="6">
         <v>46269</v>
       </c>
-      <c r="D531" s="8">
-        <v>0</v>
+      <c r="D531" s="7">
+        <v>67.487327</v>
       </c>
       <c r="E531" s="8">
-        <v>0</v>
+        <v>32360328</v>
       </c>
       <c r="F531" s="9">
         <v>5</v>
       </c>
       <c r="G531" s="8">
-        <v>0</v>
+        <v>2183912036.54</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
@@ -24906,17 +24906,17 @@
       <c r="C532" s="6">
         <v>46269</v>
       </c>
-      <c r="D532" s="8">
-        <v>0</v>
+      <c r="D532" s="7">
+        <v>63.065794</v>
       </c>
       <c r="E532" s="8">
-        <v>0</v>
+        <v>3941000</v>
       </c>
       <c r="F532" s="9">
         <v>1</v>
       </c>
       <c r="G532" s="8">
-        <v>0</v>
+        <v>248542293.37</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
@@ -25090,17 +25090,17 @@
       <c r="C540" s="6">
         <v>46269</v>
       </c>
-      <c r="D540" s="8">
-        <v>0</v>
+      <c r="D540" s="7">
+        <v>13.066661</v>
       </c>
       <c r="E540" s="8">
-        <v>0</v>
+        <v>167562559</v>
       </c>
       <c r="F540" s="9">
         <v>22109</v>
       </c>
       <c r="G540" s="8">
-        <v>0</v>
+        <v>2189483127.44</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
@@ -25136,17 +25136,17 @@
       <c r="C542" s="6">
         <v>46269</v>
       </c>
-      <c r="D542" s="8">
-        <v>0</v>
+      <c r="D542" s="11">
+        <v>71.93224</v>
       </c>
       <c r="E542" s="8">
-        <v>0</v>
+        <v>11517383</v>
       </c>
       <c r="F542" s="9">
         <v>2</v>
       </c>
       <c r="G542" s="8">
-        <v>0</v>
+        <v>828471163.67</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
@@ -25160,16 +25160,16 @@
         <v>46269</v>
       </c>
       <c r="D543" s="8">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="E543" s="8">
-        <v>0</v>
+        <v>222060386</v>
       </c>
       <c r="F543" s="9">
         <v>2</v>
       </c>
       <c r="G543" s="8">
-        <v>0</v>
+        <v>1330141818.04</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -25205,17 +25205,17 @@
       <c r="C545" s="6">
         <v>46269</v>
       </c>
-      <c r="D545" s="8">
-        <v>0</v>
+      <c r="D545" s="7">
+        <v>65.117708</v>
       </c>
       <c r="E545" s="8">
-        <v>0</v>
+        <v>3425896</v>
       </c>
       <c r="F545" s="9">
         <v>3</v>
       </c>
       <c r="G545" s="8">
-        <v>0</v>
+        <v>223086494.03</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -25228,17 +25228,17 @@
       <c r="C546" s="6">
         <v>46269</v>
       </c>
-      <c r="D546" s="8">
-        <v>0</v>
+      <c r="D546" s="7">
+        <v>61.431466</v>
       </c>
       <c r="E546" s="8">
-        <v>0</v>
+        <v>194715</v>
       </c>
       <c r="F546" s="9">
         <v>1</v>
       </c>
       <c r="G546" s="8">
-        <v>0</v>
+        <v>11961627.96</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
@@ -25297,17 +25297,17 @@
       <c r="C549" s="6">
         <v>46269</v>
       </c>
-      <c r="D549" s="8">
-        <v>0</v>
+      <c r="D549" s="7">
+        <v>77.006239</v>
       </c>
       <c r="E549" s="8">
-        <v>0</v>
+        <v>2099501</v>
       </c>
       <c r="F549" s="9">
         <v>2</v>
       </c>
       <c r="G549" s="8">
-        <v>0</v>
+        <v>161674676.75</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
@@ -25366,17 +25366,17 @@
       <c r="C552" s="6">
         <v>46269</v>
       </c>
-      <c r="D552" s="8">
-        <v>0</v>
+      <c r="D552" s="7">
+        <v>70.951967</v>
       </c>
       <c r="E552" s="8">
-        <v>0</v>
+        <v>5961167</v>
       </c>
       <c r="F552" s="9">
         <v>4</v>
       </c>
       <c r="G552" s="8">
-        <v>0</v>
+        <v>422956522.8</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
@@ -25412,17 +25412,17 @@
       <c r="C554" s="6">
         <v>46269</v>
       </c>
-      <c r="D554" s="8">
-        <v>0</v>
+      <c r="D554" s="10">
+        <v>54.3018</v>
       </c>
       <c r="E554" s="8">
-        <v>0</v>
+        <v>30698413</v>
       </c>
       <c r="F554" s="9">
         <v>3</v>
       </c>
       <c r="G554" s="8">
-        <v>0</v>
+        <v>1666979092.02</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
@@ -25435,17 +25435,17 @@
       <c r="C555" s="6">
         <v>46269</v>
       </c>
-      <c r="D555" s="8">
-        <v>0</v>
+      <c r="D555" s="7">
+        <v>10.874827</v>
       </c>
       <c r="E555" s="8">
-        <v>0</v>
+        <v>29486927</v>
       </c>
       <c r="F555" s="9">
         <v>1</v>
       </c>
       <c r="G555" s="8">
-        <v>0</v>
+        <v>320665240.05</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -25481,17 +25481,17 @@
       <c r="C557" s="6">
         <v>46269</v>
       </c>
-      <c r="D557" s="8">
-        <v>0</v>
+      <c r="D557" s="7">
+        <v>71.054709</v>
       </c>
       <c r="E557" s="8">
-        <v>0</v>
+        <v>5822807</v>
       </c>
       <c r="F557" s="9">
         <v>3</v>
       </c>
       <c r="G557" s="8">
-        <v>0</v>
+        <v>413737856.62</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
@@ -25504,17 +25504,17 @@
       <c r="C558" s="6">
         <v>46269</v>
       </c>
-      <c r="D558" s="8">
-        <v>0</v>
+      <c r="D558" s="7">
+        <v>67.824505</v>
       </c>
       <c r="E558" s="8">
-        <v>0</v>
+        <v>123364230</v>
       </c>
       <c r="F558" s="9">
         <v>3</v>
       </c>
       <c r="G558" s="8">
-        <v>0</v>
+        <v>8367117779.9</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
@@ -25550,17 +25550,17 @@
       <c r="C560" s="6">
         <v>46269</v>
       </c>
-      <c r="D560" s="8">
-        <v>0</v>
+      <c r="D560" s="11">
+        <v>66.52926</v>
       </c>
       <c r="E560" s="8">
-        <v>0</v>
+        <v>90240169</v>
       </c>
       <c r="F560" s="9">
         <v>2</v>
       </c>
       <c r="G560" s="8">
-        <v>0</v>
+        <v>6003611710.54</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
@@ -25596,17 +25596,17 @@
       <c r="C562" s="6">
         <v>46269</v>
       </c>
-      <c r="D562" s="8">
-        <v>0</v>
+      <c r="D562" s="7">
+        <v>8.600367</v>
       </c>
       <c r="E562" s="8">
-        <v>0</v>
+        <v>342290935</v>
       </c>
       <c r="F562" s="9">
         <v>1</v>
       </c>
       <c r="G562" s="8">
-        <v>0</v>
+        <v>2943827493.39</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
@@ -25619,17 +25619,17 @@
       <c r="C563" s="6">
         <v>46269</v>
       </c>
-      <c r="D563" s="8">
-        <v>0</v>
+      <c r="D563" s="7">
+        <v>70.114526</v>
       </c>
       <c r="E563" s="8">
-        <v>0</v>
+        <v>6963426</v>
       </c>
       <c r="F563" s="9">
         <v>4</v>
       </c>
       <c r="G563" s="8">
-        <v>0</v>
+        <v>488237314.35</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.25">
@@ -25665,17 +25665,17 @@
       <c r="C565" s="6">
         <v>46269</v>
       </c>
-      <c r="D565" s="8">
-        <v>0</v>
+      <c r="D565" s="11">
+        <v>68.86198</v>
       </c>
       <c r="E565" s="8">
-        <v>0</v>
+        <v>23548896</v>
       </c>
       <c r="F565" s="9">
         <v>3</v>
       </c>
       <c r="G565" s="8">
-        <v>0</v>
+        <v>1621623617.01</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
@@ -25711,17 +25711,17 @@
       <c r="C567" s="6">
         <v>46269</v>
       </c>
-      <c r="D567" s="8">
-        <v>0</v>
+      <c r="D567" s="7">
+        <v>1.635522</v>
       </c>
       <c r="E567" s="8">
-        <v>0</v>
+        <v>23091775</v>
       </c>
       <c r="F567" s="9">
         <v>1931</v>
       </c>
       <c r="G567" s="8">
-        <v>0</v>
+        <v>37767096.5</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
@@ -25780,17 +25780,17 @@
       <c r="C570" s="6">
         <v>46269</v>
       </c>
-      <c r="D570" s="8">
-        <v>0</v>
+      <c r="D570" s="7">
+        <v>67.287859</v>
       </c>
       <c r="E570" s="8">
-        <v>0</v>
+        <v>14263356</v>
       </c>
       <c r="F570" s="9">
         <v>3</v>
       </c>
       <c r="G570" s="8">
-        <v>0</v>
+        <v>959750688.83</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -25849,17 +25849,17 @@
       <c r="C573" s="6">
         <v>46269</v>
       </c>
-      <c r="D573" s="8">
-        <v>0</v>
+      <c r="D573" s="7">
+        <v>64.491692</v>
       </c>
       <c r="E573" s="8">
-        <v>0</v>
+        <v>2316713</v>
       </c>
       <c r="F573" s="9">
         <v>2</v>
       </c>
       <c r="G573" s="8">
-        <v>0</v>
+        <v>149408740.99</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
@@ -25872,17 +25872,17 @@
       <c r="C574" s="6">
         <v>46269</v>
       </c>
-      <c r="D574" s="8">
-        <v>0</v>
+      <c r="D574" s="11">
+        <v>64.73195</v>
       </c>
       <c r="E574" s="8">
-        <v>0</v>
+        <v>3647864</v>
       </c>
       <c r="F574" s="9">
         <v>2</v>
       </c>
       <c r="G574" s="8">
-        <v>0</v>
+        <v>236133350.07</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
@@ -26286,17 +26286,17 @@
       <c r="C592" s="6">
         <v>46269</v>
       </c>
-      <c r="D592" s="8">
-        <v>0</v>
+      <c r="D592" s="7">
+        <v>69.317331</v>
       </c>
       <c r="E592" s="8">
-        <v>0</v>
+        <v>8202021</v>
       </c>
       <c r="F592" s="9">
         <v>4</v>
       </c>
       <c r="G592" s="8">
-        <v>0</v>
+        <v>568542205.68</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
@@ -26402,7 +26402,7 @@
         <v>46269</v>
       </c>
       <c r="D597" s="7">
-        <v>2.754956</v>
+        <v>2.754975</v>
       </c>
       <c r="E597" s="8">
         <v>5682086</v>
@@ -26411,7 +26411,7 @@
         <v>107</v>
       </c>
       <c r="G597" s="8">
-        <v>15653894.26</v>
+        <v>15654005.77</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
@@ -26677,17 +26677,17 @@
       <c r="C609" s="6">
         <v>46269</v>
       </c>
-      <c r="D609" s="8">
-        <v>0</v>
+      <c r="D609" s="7">
+        <v>61.849471</v>
       </c>
       <c r="E609" s="8">
-        <v>0</v>
+        <v>28454944</v>
       </c>
       <c r="F609" s="9">
         <v>3</v>
       </c>
       <c r="G609" s="8">
-        <v>0</v>
+        <v>1759923224.52</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
@@ -27022,17 +27022,17 @@
       <c r="C624" s="6">
         <v>46269</v>
       </c>
-      <c r="D624" s="8">
-        <v>0</v>
+      <c r="D624" s="7">
+        <v>64.676049</v>
       </c>
       <c r="E624" s="8">
-        <v>0</v>
+        <v>11533890</v>
       </c>
       <c r="F624" s="9">
         <v>478</v>
       </c>
       <c r="G624" s="8">
-        <v>0</v>
+        <v>745966432.73</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
@@ -27068,17 +27068,17 @@
       <c r="C626" s="6">
         <v>46269</v>
       </c>
-      <c r="D626" s="8">
-        <v>0</v>
+      <c r="D626" s="7">
+        <v>12.307638</v>
       </c>
       <c r="E626" s="8">
-        <v>0</v>
+        <v>102363032</v>
       </c>
       <c r="F626" s="9">
         <v>9551</v>
       </c>
       <c r="G626" s="8">
-        <v>0</v>
+        <v>1259847111.88</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
@@ -27160,17 +27160,17 @@
       <c r="C630" s="6">
         <v>46269</v>
       </c>
-      <c r="D630" s="8">
-        <v>0</v>
+      <c r="D630" s="7">
+        <v>45.561999</v>
       </c>
       <c r="E630" s="8">
-        <v>0</v>
+        <v>58637</v>
       </c>
       <c r="F630" s="9">
         <v>1</v>
       </c>
       <c r="G630" s="8">
-        <v>0</v>
+        <v>2671618.93</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -27183,17 +27183,17 @@
       <c r="C631" s="6">
         <v>46269</v>
       </c>
-      <c r="D631" s="8">
-        <v>0</v>
+      <c r="D631" s="7">
+        <v>18.649735</v>
       </c>
       <c r="E631" s="8">
-        <v>0</v>
+        <v>39580572</v>
       </c>
       <c r="F631" s="9">
         <v>2801</v>
       </c>
       <c r="G631" s="8">
-        <v>0</v>
+        <v>738167161.85</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
@@ -27321,17 +27321,17 @@
       <c r="C637" s="6">
         <v>46269</v>
       </c>
-      <c r="D637" s="8">
-        <v>0</v>
+      <c r="D637" s="7">
+        <v>21.237072</v>
       </c>
       <c r="E637" s="8">
-        <v>0</v>
+        <v>16792116</v>
       </c>
       <c r="F637" s="9">
         <v>2475</v>
       </c>
       <c r="G637" s="8">
-        <v>0</v>
+        <v>356615374.71</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.25">
@@ -27391,7 +27391,7 @@
         <v>46269</v>
       </c>
       <c r="D640" s="7">
-        <v>1.787122</v>
+        <v>1.801599</v>
       </c>
       <c r="E640" s="8">
         <v>210773659</v>
@@ -27400,7 +27400,7 @@
         <v>284</v>
       </c>
       <c r="G640" s="8">
-        <v>376678237.27</v>
+        <v>379729605.83</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.25">
@@ -27528,17 +27528,17 @@
       <c r="C646" s="6">
         <v>46269</v>
       </c>
-      <c r="D646" s="8">
-        <v>0</v>
+      <c r="D646" s="7">
+        <v>15.526094</v>
       </c>
       <c r="E646" s="8">
-        <v>0</v>
+        <v>1794022098</v>
       </c>
       <c r="F646" s="9">
         <v>8</v>
       </c>
       <c r="G646" s="8">
-        <v>0</v>
+        <v>27854155235.2</v>
       </c>
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.25">
@@ -27689,17 +27689,17 @@
       <c r="C653" s="6">
         <v>46269</v>
       </c>
-      <c r="D653" s="8">
-        <v>0</v>
+      <c r="D653" s="7">
+        <v>7.111956</v>
       </c>
       <c r="E653" s="8">
-        <v>0</v>
+        <v>4029467144</v>
       </c>
       <c r="F653" s="9">
         <v>1</v>
       </c>
       <c r="G653" s="8">
-        <v>0</v>
+        <v>28657391632.46</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
@@ -27758,17 +27758,17 @@
       <c r="C656" s="6">
         <v>46269</v>
       </c>
-      <c r="D656" s="8">
-        <v>0</v>
+      <c r="D656" s="7">
+        <v>52.819555</v>
       </c>
       <c r="E656" s="8">
-        <v>0</v>
+        <v>28012535</v>
       </c>
       <c r="F656" s="9">
         <v>2</v>
       </c>
       <c r="G656" s="8">
-        <v>0</v>
+        <v>1479609637.58</v>
       </c>
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.25">
@@ -27827,17 +27827,17 @@
       <c r="C659" s="6">
         <v>46269</v>
       </c>
-      <c r="D659" s="8">
-        <v>0</v>
+      <c r="D659" s="7">
+        <v>6.052877</v>
       </c>
       <c r="E659" s="8">
-        <v>0</v>
+        <v>341860798</v>
       </c>
       <c r="F659" s="9">
         <v>1</v>
       </c>
       <c r="G659" s="8">
-        <v>0</v>
+        <v>2069241508.44</v>
       </c>
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.25">
@@ -27919,17 +27919,17 @@
       <c r="C663" s="6">
         <v>46269</v>
       </c>
-      <c r="D663" s="8">
-        <v>0</v>
+      <c r="D663" s="7">
+        <v>0.441943</v>
       </c>
       <c r="E663" s="8">
-        <v>0</v>
+        <v>10413284512</v>
       </c>
       <c r="F663" s="9">
         <v>38569</v>
       </c>
       <c r="G663" s="8">
-        <v>0</v>
+        <v>4602079026.6</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -28011,17 +28011,17 @@
       <c r="C667" s="6">
         <v>46269</v>
       </c>
-      <c r="D667" s="8">
-        <v>0</v>
+      <c r="D667" s="11">
+        <v>4.03899</v>
       </c>
       <c r="E667" s="8">
-        <v>0</v>
+        <v>23511685</v>
       </c>
       <c r="F667" s="9">
         <v>3413</v>
       </c>
       <c r="G667" s="8">
-        <v>0</v>
+        <v>94963456.6</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -28034,17 +28034,17 @@
       <c r="C668" s="6">
         <v>46269</v>
       </c>
-      <c r="D668" s="8">
-        <v>0</v>
+      <c r="D668" s="10">
+        <v>68.5377</v>
       </c>
       <c r="E668" s="8">
-        <v>0</v>
+        <v>52499640</v>
       </c>
       <c r="F668" s="9">
         <v>3</v>
       </c>
       <c r="G668" s="8">
-        <v>0</v>
+        <v>3598204601.99</v>
       </c>
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.25">
@@ -28080,17 +28080,17 @@
       <c r="C670" s="6">
         <v>46269</v>
       </c>
-      <c r="D670" s="8">
-        <v>0</v>
+      <c r="D670" s="7">
+        <v>18.426891</v>
       </c>
       <c r="E670" s="8">
-        <v>0</v>
+        <v>22115</v>
       </c>
       <c r="F670" s="9">
         <v>1</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>407510.7</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -28103,17 +28103,17 @@
       <c r="C671" s="6">
         <v>46269</v>
       </c>
-      <c r="D671" s="8">
-        <v>0</v>
+      <c r="D671" s="7">
+        <v>5.615114</v>
       </c>
       <c r="E671" s="8">
-        <v>0</v>
+        <v>210068131</v>
       </c>
       <c r="F671" s="9">
         <v>4617</v>
       </c>
       <c r="G671" s="8">
-        <v>0</v>
+        <v>1179556492.64</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
@@ -28126,17 +28126,17 @@
       <c r="C672" s="6">
         <v>46269</v>
       </c>
-      <c r="D672" s="8">
-        <v>0</v>
+      <c r="D672" s="7">
+        <v>67.261005</v>
       </c>
       <c r="E672" s="8">
-        <v>0</v>
+        <v>7872114</v>
       </c>
       <c r="F672" s="9">
         <v>3</v>
       </c>
       <c r="G672" s="8">
-        <v>0</v>
+        <v>529486295.38</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
@@ -28172,17 +28172,17 @@
       <c r="C674" s="6">
         <v>46269</v>
       </c>
-      <c r="D674" s="8">
-        <v>0</v>
+      <c r="D674" s="11">
+        <v>4.13886</v>
       </c>
       <c r="E674" s="8">
-        <v>0</v>
+        <v>5020082762</v>
       </c>
       <c r="F674" s="9">
         <v>1</v>
       </c>
       <c r="G674" s="8">
-        <v>0</v>
+        <v>20777419729.56</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -28195,17 +28195,17 @@
       <c r="C675" s="6">
         <v>46269</v>
       </c>
-      <c r="D675" s="8">
-        <v>0</v>
+      <c r="D675" s="7">
+        <v>72.050283</v>
       </c>
       <c r="E675" s="8">
-        <v>0</v>
+        <v>7036272</v>
       </c>
       <c r="F675" s="9">
         <v>4</v>
       </c>
       <c r="G675" s="8">
-        <v>0</v>
+        <v>506965391.89</v>
       </c>
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.25">
@@ -28264,17 +28264,17 @@
       <c r="C678" s="6">
         <v>46269</v>
       </c>
-      <c r="D678" s="8">
-        <v>0</v>
+      <c r="D678" s="7">
+        <v>69.532174</v>
       </c>
       <c r="E678" s="8">
-        <v>0</v>
+        <v>20613565</v>
       </c>
       <c r="F678" s="9">
         <v>1</v>
       </c>
       <c r="G678" s="8">
-        <v>0</v>
+        <v>1433305989.21</v>
       </c>
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.25">
@@ -28310,17 +28310,17 @@
       <c r="C680" s="6">
         <v>46269</v>
       </c>
-      <c r="D680" s="8">
-        <v>0</v>
+      <c r="D680" s="7">
+        <v>7.606117</v>
       </c>
       <c r="E680" s="8">
-        <v>0</v>
+        <v>190000000</v>
       </c>
       <c r="F680" s="9">
         <v>1</v>
       </c>
       <c r="G680" s="8">
-        <v>0</v>
+        <v>1445162230.63</v>
       </c>
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.25">
@@ -28379,17 +28379,17 @@
       <c r="C683" s="6">
         <v>46269</v>
       </c>
-      <c r="D683" s="8">
-        <v>0</v>
+      <c r="D683" s="7">
+        <v>7.605744</v>
       </c>
       <c r="E683" s="8">
-        <v>0</v>
+        <v>56170102</v>
       </c>
       <c r="F683" s="9">
         <v>4566</v>
       </c>
       <c r="G683" s="8">
-        <v>0</v>
+        <v>427215416.77</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
@@ -28402,17 +28402,17 @@
       <c r="C684" s="6">
         <v>46269</v>
       </c>
-      <c r="D684" s="8">
-        <v>0</v>
+      <c r="D684" s="7">
+        <v>4.749433</v>
       </c>
       <c r="E684" s="8">
-        <v>0</v>
+        <v>75405419</v>
       </c>
       <c r="F684" s="9">
         <v>5544</v>
       </c>
       <c r="G684" s="8">
-        <v>0</v>
+        <v>358132974.24</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
@@ -28448,17 +28448,17 @@
       <c r="C686" s="6">
         <v>46269</v>
       </c>
-      <c r="D686" s="8">
-        <v>0</v>
+      <c r="D686" s="7">
+        <v>5.878619</v>
       </c>
       <c r="E686" s="8">
-        <v>0</v>
+        <v>65475448</v>
       </c>
       <c r="F686" s="9">
         <v>6029</v>
       </c>
       <c r="G686" s="8">
-        <v>0</v>
+        <v>384905242.65</v>
       </c>
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.25">
@@ -28517,17 +28517,17 @@
       <c r="C689" s="6">
         <v>46269</v>
       </c>
-      <c r="D689" s="8">
-        <v>0</v>
+      <c r="D689" s="7">
+        <v>70.255927</v>
       </c>
       <c r="E689" s="8">
-        <v>0</v>
+        <v>1210798</v>
       </c>
       <c r="F689" s="9">
         <v>1</v>
       </c>
       <c r="G689" s="8">
-        <v>0</v>
+        <v>85065735.48</v>
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.25">
@@ -28540,17 +28540,17 @@
       <c r="C690" s="6">
         <v>46269</v>
       </c>
-      <c r="D690" s="8">
-        <v>0</v>
+      <c r="D690" s="7">
+        <v>7.731475</v>
       </c>
       <c r="E690" s="8">
-        <v>0</v>
+        <v>502710529</v>
       </c>
       <c r="F690" s="9">
         <v>10356</v>
       </c>
       <c r="G690" s="8">
-        <v>0</v>
+        <v>3886694005.88</v>
       </c>
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.25">
@@ -28586,17 +28586,17 @@
       <c r="C692" s="6">
         <v>46269</v>
       </c>
-      <c r="D692" s="8">
-        <v>0</v>
+      <c r="D692" s="7">
+        <v>68.203416</v>
       </c>
       <c r="E692" s="8">
-        <v>0</v>
+        <v>6829649</v>
       </c>
       <c r="F692" s="9">
         <v>2</v>
       </c>
       <c r="G692" s="8">
-        <v>0</v>
+        <v>465805392.48</v>
       </c>
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.25">
@@ -28609,17 +28609,17 @@
       <c r="C693" s="6">
         <v>46269</v>
       </c>
-      <c r="D693" s="8">
-        <v>0</v>
+      <c r="D693" s="7">
+        <v>8.713517</v>
       </c>
       <c r="E693" s="8">
-        <v>0</v>
+        <v>11467130</v>
       </c>
       <c r="F693" s="9">
         <v>1387</v>
       </c>
       <c r="G693" s="8">
-        <v>0</v>
+        <v>99919037.39</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.25">
@@ -28771,7 +28771,7 @@
         <v>46269</v>
       </c>
       <c r="D700" s="7">
-        <v>1.065998</v>
+        <v>1.063859</v>
       </c>
       <c r="E700" s="8">
         <v>89892956</v>
@@ -28780,7 +28780,7 @@
         <v>69</v>
       </c>
       <c r="G700" s="8">
-        <v>95825712.94</v>
+        <v>95633385.9</v>
       </c>
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.25">
@@ -28908,17 +28908,17 @@
       <c r="C706" s="6">
         <v>46269</v>
       </c>
-      <c r="D706" s="8">
-        <v>0</v>
+      <c r="D706" s="7">
+        <v>4.329646</v>
       </c>
       <c r="E706" s="8">
-        <v>0</v>
+        <v>122644702</v>
       </c>
       <c r="F706" s="9">
         <v>1062</v>
       </c>
       <c r="G706" s="8">
-        <v>0</v>
+        <v>531008128.35</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.25">
@@ -29852,16 +29852,16 @@
         <v>46269</v>
       </c>
       <c r="D747" s="7">
-        <v>5.703564</v>
+        <v>5.702263</v>
       </c>
       <c r="E747" s="8">
-        <v>26579952</v>
+        <v>26218012</v>
       </c>
       <c r="F747" s="9">
         <v>70</v>
       </c>
       <c r="G747" s="8">
-        <v>151600461.1</v>
+        <v>149502010.26</v>
       </c>
     </row>
     <row r="748" spans="1:7" x14ac:dyDescent="0.25">
@@ -29921,16 +29921,16 @@
         <v>46269</v>
       </c>
       <c r="D750" s="7">
-        <v>1.845826</v>
+        <v>1.826412</v>
       </c>
       <c r="E750" s="8">
-        <v>22179665</v>
+        <v>16392863</v>
       </c>
       <c r="F750" s="9">
         <v>10</v>
       </c>
       <c r="G750" s="8">
-        <v>40939798.52</v>
+        <v>29940116.15</v>
       </c>
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.25">
@@ -30220,7 +30220,7 @@
         <v>46269</v>
       </c>
       <c r="D763" s="7">
-        <v>0.366551</v>
+        <v>0.366818</v>
       </c>
       <c r="E763" s="8">
         <v>3710271769</v>
@@ -30229,7 +30229,7 @@
         <v>2539</v>
       </c>
       <c r="G763" s="8">
-        <v>1360005327.53</v>
+        <v>1360996274.05</v>
       </c>
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.25">
@@ -33554,17 +33554,17 @@
       <c r="C908" s="6">
         <v>46269</v>
       </c>
-      <c r="D908" s="8">
-        <v>0</v>
+      <c r="D908" s="7">
+        <v>14.940139</v>
       </c>
       <c r="E908" s="8">
-        <v>0</v>
+        <v>15843143</v>
       </c>
       <c r="F908" s="9">
         <v>383</v>
       </c>
       <c r="G908" s="8">
-        <v>0</v>
+        <v>236698751.06</v>
       </c>
     </row>
     <row r="909" spans="1:7" x14ac:dyDescent="0.25">
@@ -35463,17 +35463,17 @@
       <c r="C991" s="6">
         <v>46269</v>
       </c>
-      <c r="D991" s="8">
-        <v>0</v>
+      <c r="D991" s="7">
+        <v>1.763691</v>
       </c>
       <c r="E991" s="8">
-        <v>0</v>
+        <v>6356630</v>
       </c>
       <c r="F991" s="9">
         <v>174</v>
       </c>
       <c r="G991" s="8">
-        <v>0</v>
+        <v>11211131.74</v>
       </c>
     </row>
     <row r="992" spans="1:7" x14ac:dyDescent="0.25">
@@ -35555,17 +35555,17 @@
       <c r="C995" s="6">
         <v>46269</v>
       </c>
-      <c r="D995" s="8">
-        <v>0</v>
+      <c r="D995" s="7">
+        <v>58.551247</v>
       </c>
       <c r="E995" s="8">
-        <v>0</v>
+        <v>4238148</v>
       </c>
       <c r="F995" s="9">
         <v>12</v>
       </c>
       <c r="G995" s="8">
-        <v>0</v>
+        <v>248148850.29</v>
       </c>
     </row>
     <row r="996" spans="1:7" x14ac:dyDescent="0.25">
@@ -35900,17 +35900,17 @@
       <c r="C1010" s="6">
         <v>46269</v>
       </c>
-      <c r="D1010" s="8">
-        <v>0</v>
+      <c r="D1010" s="7">
+        <v>1.571619</v>
       </c>
       <c r="E1010" s="8">
-        <v>0</v>
+        <v>9428546</v>
       </c>
       <c r="F1010" s="9">
         <v>242</v>
       </c>
       <c r="G1010" s="8">
-        <v>0</v>
+        <v>14818085.05</v>
       </c>
     </row>
     <row r="1011" spans="1:7" x14ac:dyDescent="0.25">
@@ -36153,17 +36153,17 @@
       <c r="C1021" s="6">
         <v>46269</v>
       </c>
-      <c r="D1021" s="8">
-        <v>0</v>
+      <c r="D1021" s="7">
+        <v>1.558166</v>
       </c>
       <c r="E1021" s="8">
-        <v>0</v>
+        <v>38712606</v>
       </c>
       <c r="F1021" s="9">
         <v>27</v>
       </c>
       <c r="G1021" s="8">
-        <v>0</v>
+        <v>60320674.51</v>
       </c>
     </row>
     <row r="1022" spans="1:7" x14ac:dyDescent="0.25">
@@ -36268,17 +36268,17 @@
       <c r="C1026" s="6">
         <v>46269</v>
       </c>
-      <c r="D1026" s="8">
-        <v>0</v>
+      <c r="D1026" s="7">
+        <v>58.084717</v>
       </c>
       <c r="E1026" s="8">
-        <v>0</v>
+        <v>2373618</v>
       </c>
       <c r="F1026" s="9">
         <v>52</v>
       </c>
       <c r="G1026" s="8">
-        <v>0</v>
+        <v>137870928.92</v>
       </c>
     </row>
     <row r="1027" spans="1:7" x14ac:dyDescent="0.25">
@@ -37027,17 +37027,17 @@
       <c r="C1059" s="6">
         <v>46269</v>
       </c>
-      <c r="D1059" s="8">
-        <v>0</v>
+      <c r="D1059" s="11">
+        <v>53.59194</v>
       </c>
       <c r="E1059" s="8">
-        <v>0</v>
+        <v>264284</v>
       </c>
       <c r="F1059" s="9">
         <v>10</v>
       </c>
       <c r="G1059" s="8">
-        <v>0</v>
+        <v>14163492.28</v>
       </c>
     </row>
     <row r="1060" spans="1:7" x14ac:dyDescent="0.25">
@@ -37234,17 +37234,17 @@
       <c r="C1068" s="6">
         <v>46269</v>
       </c>
-      <c r="D1068" s="8">
-        <v>0</v>
+      <c r="D1068" s="11">
+        <v>1.02279</v>
       </c>
       <c r="E1068" s="8">
-        <v>0</v>
+        <v>1508400</v>
       </c>
       <c r="F1068" s="9">
         <v>16</v>
       </c>
       <c r="G1068" s="8">
-        <v>0</v>
+        <v>1542776.39</v>
       </c>
     </row>
     <row r="1069" spans="1:7" x14ac:dyDescent="0.25">
@@ -37257,17 +37257,17 @@
       <c r="C1069" s="6">
         <v>46269</v>
       </c>
-      <c r="D1069" s="8">
-        <v>0</v>
+      <c r="D1069" s="7">
+        <v>3.208905</v>
       </c>
       <c r="E1069" s="8">
-        <v>0</v>
+        <v>137506504</v>
       </c>
       <c r="F1069" s="9">
         <v>673</v>
       </c>
       <c r="G1069" s="8">
-        <v>0</v>
+        <v>441245242.91</v>
       </c>
     </row>
     <row r="1070" spans="1:7" x14ac:dyDescent="0.25">
@@ -37349,17 +37349,17 @@
       <c r="C1073" s="6">
         <v>46269</v>
       </c>
-      <c r="D1073" s="8">
-        <v>0</v>
+      <c r="D1073" s="7">
+        <v>0.148369</v>
       </c>
       <c r="E1073" s="8">
-        <v>0</v>
+        <v>204469320</v>
       </c>
       <c r="F1073" s="9">
         <v>150</v>
       </c>
       <c r="G1073" s="8">
-        <v>0</v>
+        <v>30336914.77</v>
       </c>
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.25">
@@ -37372,17 +37372,17 @@
       <c r="C1074" s="6">
         <v>46269</v>
       </c>
-      <c r="D1074" s="8">
-        <v>0</v>
+      <c r="D1074" s="7">
+        <v>21.704622</v>
       </c>
       <c r="E1074" s="8">
-        <v>0</v>
+        <v>2059607</v>
       </c>
       <c r="F1074" s="9">
         <v>592</v>
       </c>
       <c r="G1074" s="8">
-        <v>0</v>
+        <v>44702991.07</v>
       </c>
     </row>
     <row r="1075" spans="1:7" x14ac:dyDescent="0.25">
@@ -37464,17 +37464,17 @@
       <c r="C1078" s="6">
         <v>46269</v>
       </c>
-      <c r="D1078" s="8">
-        <v>0</v>
+      <c r="D1078" s="7">
+        <v>0.529027</v>
       </c>
       <c r="E1078" s="8">
-        <v>0</v>
+        <v>2779365471</v>
       </c>
       <c r="F1078" s="9">
         <v>1098</v>
       </c>
       <c r="G1078" s="8">
-        <v>0</v>
+        <v>1470358408.72</v>
       </c>
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.25">
@@ -37487,17 +37487,17 @@
       <c r="C1079" s="6">
         <v>46269</v>
       </c>
-      <c r="D1079" s="8">
-        <v>0</v>
+      <c r="D1079" s="7">
+        <v>75.475045</v>
       </c>
       <c r="E1079" s="8">
-        <v>0</v>
+        <v>10578262</v>
       </c>
       <c r="F1079" s="9">
         <v>168</v>
       </c>
       <c r="G1079" s="8">
-        <v>0</v>
+        <v>798394801.76</v>
       </c>
     </row>
     <row r="1080" spans="1:7" x14ac:dyDescent="0.25">
@@ -38039,17 +38039,17 @@
       <c r="C1103" s="6">
         <v>46269</v>
       </c>
-      <c r="D1103" s="8">
-        <v>0</v>
+      <c r="D1103" s="7">
+        <v>0.758878</v>
       </c>
       <c r="E1103" s="8">
-        <v>0</v>
+        <v>805679526</v>
       </c>
       <c r="F1103" s="9">
         <v>3606</v>
       </c>
       <c r="G1103" s="8">
-        <v>0</v>
+        <v>611412748.47</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.25">
@@ -38086,7 +38086,7 @@
         <v>46269</v>
       </c>
       <c r="D1105" s="7">
-        <v>49.456033</v>
+        <v>49.456931</v>
       </c>
       <c r="E1105" s="8">
         <v>41310587</v>
@@ -38095,7 +38095,7 @@
         <v>128</v>
       </c>
       <c r="G1105" s="8">
-        <v>2043057745.83</v>
+        <v>2043094860.71</v>
       </c>
     </row>
     <row r="1106" spans="1:7" x14ac:dyDescent="0.25">
@@ -38246,17 +38246,17 @@
       <c r="C1112" s="6">
         <v>46269</v>
       </c>
-      <c r="D1112" s="8">
-        <v>0</v>
+      <c r="D1112" s="7">
+        <v>1.174674</v>
       </c>
       <c r="E1112" s="8">
-        <v>0</v>
+        <v>53432551</v>
       </c>
       <c r="F1112" s="9">
         <v>1526</v>
       </c>
       <c r="G1112" s="8">
-        <v>0</v>
+        <v>62765822.4</v>
       </c>
     </row>
     <row r="1113" spans="1:7" x14ac:dyDescent="0.25">
@@ -38292,17 +38292,17 @@
       <c r="C1114" s="6">
         <v>46269</v>
       </c>
-      <c r="D1114" s="8">
-        <v>0</v>
+      <c r="D1114" s="7">
+        <v>54.143888</v>
       </c>
       <c r="E1114" s="8">
-        <v>0</v>
+        <v>207100</v>
       </c>
       <c r="F1114" s="9">
         <v>18</v>
       </c>
       <c r="G1114" s="8">
-        <v>0</v>
+        <v>11213199.19</v>
       </c>
     </row>
     <row r="1115" spans="1:7" x14ac:dyDescent="0.25">
@@ -41444,7 +41444,7 @@
         <v>46269</v>
       </c>
       <c r="D1251" s="7">
-        <v>5.277185</v>
+        <v>5.342181</v>
       </c>
       <c r="E1251" s="8">
         <v>282263191</v>
@@ -41453,7 +41453,7 @@
         <v>148</v>
       </c>
       <c r="G1251" s="8">
-        <v>1489554984.44</v>
+        <v>1507901075.03</v>
       </c>
     </row>
     <row r="1252" spans="1:7" x14ac:dyDescent="0.25">
@@ -41844,7 +41844,7 @@
         <v>1518</v>
       </c>
       <c r="G1268" s="8">
-        <v>270650376.61</v>
+        <v>270650385.26</v>
       </c>
     </row>
     <row r="1269" spans="1:7" x14ac:dyDescent="0.25">
@@ -42594,7 +42594,7 @@
         <v>46269</v>
       </c>
       <c r="D1301" s="7">
-        <v>4.105494</v>
+        <v>4.105513</v>
       </c>
       <c r="E1301" s="8">
         <v>38452056</v>
@@ -42603,7 +42603,7 @@
         <v>583</v>
       </c>
       <c r="G1301" s="8">
-        <v>157864695.4</v>
+        <v>157865402.5</v>
       </c>
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
@@ -42663,7 +42663,7 @@
         <v>46269</v>
       </c>
       <c r="D1304" s="7">
-        <v>8.340602</v>
+        <v>8.340674</v>
       </c>
       <c r="E1304" s="8">
         <v>22522088</v>
@@ -42672,7 +42672,7 @@
         <v>433</v>
       </c>
       <c r="G1304" s="8">
-        <v>187847770.63</v>
+        <v>187849386.16</v>
       </c>
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
@@ -42948,7 +42948,7 @@
         <v>27656</v>
       </c>
       <c r="G1316" s="8">
-        <v>47269928202.14</v>
+        <v>47269928210.34</v>
       </c>
     </row>
     <row r="1317" spans="1:7" x14ac:dyDescent="0.25">
@@ -42962,7 +42962,7 @@
         <v>46269</v>
       </c>
       <c r="D1317" s="7">
-        <v>12.817684</v>
+        <v>12.807096</v>
       </c>
       <c r="E1317" s="8">
         <v>358771756</v>
@@ -42971,7 +42971,7 @@
         <v>11155</v>
       </c>
       <c r="G1317" s="8">
-        <v>4598622904.64</v>
+        <v>4594824399.91</v>
       </c>
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
@@ -43905,7 +43905,7 @@
         <v>46269</v>
       </c>
       <c r="D1358" s="7">
-        <v>7.369495</v>
+        <v>7.373717</v>
       </c>
       <c r="E1358" s="8">
         <v>443686856</v>
@@ -43914,7 +43914,7 @@
         <v>21948</v>
       </c>
       <c r="G1358" s="8">
-        <v>3269748134.94</v>
+        <v>3271621252.13</v>
       </c>
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.25">
@@ -45744,17 +45744,17 @@
       <c r="C1438" s="6">
         <v>46269</v>
       </c>
-      <c r="D1438" s="8">
-        <v>0</v>
+      <c r="D1438" s="7">
+        <v>1.295145</v>
       </c>
       <c r="E1438" s="8">
-        <v>0</v>
+        <v>502197</v>
       </c>
       <c r="F1438" s="9">
         <v>117</v>
       </c>
       <c r="G1438" s="8">
-        <v>0</v>
+        <v>650417.77</v>
       </c>
     </row>
     <row r="1439" spans="1:7" x14ac:dyDescent="0.25">
@@ -46987,7 +46987,7 @@
         <v>46269</v>
       </c>
       <c r="D1492" s="7">
-        <v>1.458478</v>
+        <v>1.458354</v>
       </c>
       <c r="E1492" s="8">
         <v>569680575</v>
@@ -46996,7 +46996,7 @@
         <v>289</v>
       </c>
       <c r="G1492" s="8">
-        <v>830866750.57</v>
+        <v>830795685.52</v>
       </c>
     </row>
     <row r="1493" spans="1:7" x14ac:dyDescent="0.25">
@@ -49447,17 +49447,17 @@
       <c r="C1599" s="6">
         <v>46269</v>
       </c>
-      <c r="D1599" s="8">
-        <v>0</v>
+      <c r="D1599" s="7">
+        <v>1.207211</v>
       </c>
       <c r="E1599" s="8">
-        <v>0</v>
+        <v>300626629</v>
       </c>
       <c r="F1599" s="9">
         <v>1</v>
       </c>
       <c r="G1599" s="8">
-        <v>0</v>
+        <v>362919867.56</v>
       </c>
     </row>
     <row r="1600" spans="1:7" x14ac:dyDescent="0.25">
@@ -49677,17 +49677,17 @@
       <c r="C1609" s="6">
         <v>46269</v>
       </c>
-      <c r="D1609" s="8">
-        <v>0</v>
+      <c r="D1609" s="7">
+        <v>1.703904</v>
       </c>
       <c r="E1609" s="8">
-        <v>0</v>
+        <v>196192399</v>
       </c>
       <c r="F1609" s="9">
         <v>663</v>
       </c>
       <c r="G1609" s="8">
-        <v>0</v>
+        <v>334293061.09</v>
       </c>
     </row>
     <row r="1610" spans="1:7" x14ac:dyDescent="0.25">
@@ -49792,17 +49792,17 @@
       <c r="C1614" s="6">
         <v>46269</v>
       </c>
-      <c r="D1614" s="8">
-        <v>0</v>
+      <c r="D1614" s="7">
+        <v>1.016539</v>
       </c>
       <c r="E1614" s="8">
-        <v>0</v>
+        <v>45839190</v>
       </c>
       <c r="F1614" s="9">
         <v>191</v>
       </c>
       <c r="G1614" s="8">
-        <v>0</v>
+        <v>46597311.94</v>
       </c>
     </row>
     <row r="1615" spans="1:7" x14ac:dyDescent="0.25">
@@ -49953,17 +49953,17 @@
       <c r="C1621" s="6">
         <v>46269</v>
       </c>
-      <c r="D1621" s="8">
-        <v>0</v>
+      <c r="D1621" s="7">
+        <v>1.910678</v>
       </c>
       <c r="E1621" s="8">
-        <v>0</v>
+        <v>96961191</v>
       </c>
       <c r="F1621" s="9">
         <v>2732</v>
       </c>
       <c r="G1621" s="8">
-        <v>0</v>
+        <v>185261662.8</v>
       </c>
     </row>
     <row r="1622" spans="1:7" x14ac:dyDescent="0.25">
@@ -50045,17 +50045,17 @@
       <c r="C1625" s="6">
         <v>46269</v>
       </c>
-      <c r="D1625" s="8">
-        <v>0</v>
+      <c r="D1625" s="7">
+        <v>1.447315</v>
       </c>
       <c r="E1625" s="8">
-        <v>0</v>
+        <v>292835556</v>
       </c>
       <c r="F1625" s="9">
         <v>35</v>
       </c>
       <c r="G1625" s="8">
-        <v>0</v>
+        <v>423825366.48</v>
       </c>
     </row>
     <row r="1626" spans="1:7" x14ac:dyDescent="0.25">
@@ -50068,17 +50068,17 @@
       <c r="C1626" s="6">
         <v>46269</v>
       </c>
-      <c r="D1626" s="8">
-        <v>0</v>
+      <c r="D1626" s="7">
+        <v>0.880773</v>
       </c>
       <c r="E1626" s="8">
-        <v>0</v>
+        <v>1072723</v>
       </c>
       <c r="F1626" s="9">
         <v>5</v>
       </c>
       <c r="G1626" s="8">
-        <v>0</v>
+        <v>944824.95</v>
       </c>
     </row>
     <row r="1627" spans="1:7" x14ac:dyDescent="0.25">
@@ -50091,17 +50091,17 @@
       <c r="C1627" s="6">
         <v>46269</v>
       </c>
-      <c r="D1627" s="8">
-        <v>0</v>
+      <c r="D1627" s="7">
+        <v>0.255124</v>
       </c>
       <c r="E1627" s="8">
-        <v>0</v>
+        <v>238798338</v>
       </c>
       <c r="F1627" s="9">
         <v>14</v>
       </c>
       <c r="G1627" s="8">
-        <v>0</v>
+        <v>60923158.73</v>
       </c>
     </row>
     <row r="1628" spans="1:7" x14ac:dyDescent="0.25">
@@ -51219,7 +51219,7 @@
         <v>46269</v>
       </c>
       <c r="D1676" s="7">
-        <v>0.131743</v>
+        <v>0.131771</v>
       </c>
       <c r="E1676" s="8">
         <v>110242481860</v>
@@ -51228,7 +51228,7 @@
         <v>18</v>
       </c>
       <c r="G1676" s="8">
-        <v>14523708615.82</v>
+        <v>14526718858.31</v>
       </c>
     </row>
     <row r="1677" spans="1:7" x14ac:dyDescent="0.25">
@@ -55358,17 +55358,17 @@
       <c r="C1856" s="6">
         <v>46269</v>
       </c>
-      <c r="D1856" s="8">
-        <v>0</v>
+      <c r="D1856" s="7">
+        <v>14.716526</v>
       </c>
       <c r="E1856" s="8">
-        <v>0</v>
+        <v>368811941</v>
       </c>
       <c r="F1856" s="9">
         <v>9823</v>
       </c>
       <c r="G1856" s="8">
-        <v>0</v>
+        <v>5427630356.31</v>
       </c>
     </row>
     <row r="1857" spans="1:7" x14ac:dyDescent="0.25">
@@ -55427,17 +55427,17 @@
       <c r="C1859" s="6">
         <v>46269</v>
       </c>
-      <c r="D1859" s="8">
-        <v>0</v>
+      <c r="D1859" s="7">
+        <v>14.712065</v>
       </c>
       <c r="E1859" s="8">
-        <v>0</v>
+        <v>127045443</v>
       </c>
       <c r="F1859" s="9">
         <v>3596</v>
       </c>
       <c r="G1859" s="8">
-        <v>0</v>
+        <v>1869100772.29</v>
       </c>
     </row>
     <row r="1860" spans="1:7" x14ac:dyDescent="0.25">
@@ -55680,17 +55680,17 @@
       <c r="C1870" s="6">
         <v>46269</v>
       </c>
-      <c r="D1870" s="8">
-        <v>0</v>
+      <c r="D1870" s="7">
+        <v>2.713216</v>
       </c>
       <c r="E1870" s="8">
-        <v>0</v>
+        <v>39652266</v>
       </c>
       <c r="F1870" s="9">
         <v>113</v>
       </c>
       <c r="G1870" s="8">
-        <v>0</v>
+        <v>107585146.13</v>
       </c>
     </row>
     <row r="1871" spans="1:7" x14ac:dyDescent="0.25">
@@ -56255,17 +56255,17 @@
       <c r="C1895" s="6">
         <v>46269</v>
       </c>
-      <c r="D1895" s="8">
-        <v>0</v>
+      <c r="D1895" s="7">
+        <v>2.527265</v>
       </c>
       <c r="E1895" s="8">
-        <v>0</v>
+        <v>826302216</v>
       </c>
       <c r="F1895" s="9">
         <v>16340</v>
       </c>
       <c r="G1895" s="8">
-        <v>0</v>
+        <v>2088284535.7</v>
       </c>
     </row>
     <row r="1896" spans="1:7" x14ac:dyDescent="0.25">
@@ -56347,17 +56347,17 @@
       <c r="C1899" s="6">
         <v>46269</v>
       </c>
-      <c r="D1899" s="8">
-        <v>0</v>
+      <c r="D1899" s="7">
+        <v>5.577649</v>
       </c>
       <c r="E1899" s="8">
-        <v>0</v>
+        <v>179077968</v>
       </c>
       <c r="F1899" s="9">
         <v>14110</v>
       </c>
       <c r="G1899" s="8">
-        <v>0</v>
+        <v>998834125.78</v>
       </c>
     </row>
     <row r="1900" spans="1:7" x14ac:dyDescent="0.25">
@@ -57175,17 +57175,17 @@
       <c r="C1935" s="6">
         <v>46269</v>
       </c>
-      <c r="D1935" s="8">
-        <v>0</v>
+      <c r="D1935" s="7">
+        <v>7.886196</v>
       </c>
       <c r="E1935" s="8">
-        <v>0</v>
+        <v>691866401</v>
       </c>
       <c r="F1935" s="9">
         <v>3335</v>
       </c>
       <c r="G1935" s="8">
-        <v>0</v>
+        <v>5456193705.49</v>
       </c>
     </row>
     <row r="1936" spans="1:7" x14ac:dyDescent="0.25">
@@ -57336,17 +57336,17 @@
       <c r="C1942" s="6">
         <v>46269</v>
       </c>
-      <c r="D1942" s="8">
-        <v>0</v>
+      <c r="D1942" s="11">
+        <v>0.94251</v>
       </c>
       <c r="E1942" s="8">
-        <v>0</v>
+        <v>1843603334</v>
       </c>
       <c r="F1942" s="9">
         <v>14968</v>
       </c>
       <c r="G1942" s="8">
-        <v>0</v>
+        <v>1737615167.15</v>
       </c>
     </row>
     <row r="1943" spans="1:7" x14ac:dyDescent="0.25">
@@ -57796,17 +57796,17 @@
       <c r="C1962" s="6">
         <v>46269</v>
       </c>
-      <c r="D1962" s="8">
-        <v>0</v>
+      <c r="D1962" s="11">
+        <v>13.43937</v>
       </c>
       <c r="E1962" s="8">
-        <v>0</v>
+        <v>822928188</v>
       </c>
       <c r="F1962" s="9">
         <v>60387</v>
       </c>
       <c r="G1962" s="8">
-        <v>0</v>
+        <v>11059636334.58</v>
       </c>
     </row>
     <row r="1963" spans="1:7" x14ac:dyDescent="0.25">
@@ -58349,7 +58349,7 @@
         <v>46269</v>
       </c>
       <c r="D1986" s="7">
-        <v>4.114228</v>
+        <v>4.121672</v>
       </c>
       <c r="E1986" s="8">
         <v>153790800</v>
@@ -58358,7 +58358,7 @@
         <v>6521</v>
       </c>
       <c r="G1986" s="8">
-        <v>632730458.43</v>
+        <v>633875310.19</v>
       </c>
     </row>
     <row r="1987" spans="1:7" x14ac:dyDescent="0.25">
@@ -58900,8 +58900,8 @@
       <c r="C2010" s="6">
         <v>46269</v>
       </c>
-      <c r="D2010" s="11">
-        <v>1.88895</v>
+      <c r="D2010" s="7">
+        <v>1.889676</v>
       </c>
       <c r="E2010" s="8">
         <v>306521428</v>
@@ -58910,7 +58910,7 @@
         <v>11</v>
       </c>
       <c r="G2010" s="8">
-        <v>579003547.23</v>
+        <v>579226229.37</v>
       </c>
     </row>
     <row r="2011" spans="1:7" x14ac:dyDescent="0.25">
@@ -58946,8 +58946,8 @@
       <c r="C2012" s="6">
         <v>46269</v>
       </c>
-      <c r="D2012" s="11">
-        <v>5.86396</v>
+      <c r="D2012" s="7">
+        <v>5.864604</v>
       </c>
       <c r="E2012" s="8">
         <v>106786382</v>
@@ -58956,7 +58956,7 @@
         <v>1</v>
       </c>
       <c r="G2012" s="8">
-        <v>626191101.32</v>
+        <v>626259879.06</v>
       </c>
     </row>
     <row r="2013" spans="1:7" x14ac:dyDescent="0.25">
@@ -59108,7 +59108,7 @@
         <v>46269</v>
       </c>
       <c r="D2019" s="7">
-        <v>19.504259</v>
+        <v>19.504025</v>
       </c>
       <c r="E2019" s="8">
         <v>164976754</v>
@@ -59117,7 +59117,7 @@
         <v>2790</v>
       </c>
       <c r="G2019" s="8">
-        <v>3217749401.75</v>
+        <v>3217710662.66</v>
       </c>
     </row>
     <row r="2020" spans="1:7" x14ac:dyDescent="0.25">
@@ -59384,7 +59384,7 @@
         <v>46269</v>
       </c>
       <c r="D2031" s="7">
-        <v>12.339693</v>
+        <v>12.339025</v>
       </c>
       <c r="E2031" s="8">
         <v>216588410</v>
@@ -59393,7 +59393,7 @@
         <v>25</v>
       </c>
       <c r="G2031" s="8">
-        <v>2672634551.79</v>
+        <v>2672489845.03</v>
       </c>
     </row>
     <row r="2032" spans="1:7" x14ac:dyDescent="0.25">
@@ -59429,8 +59429,8 @@
       <c r="C2033" s="6">
         <v>46269</v>
       </c>
-      <c r="D2033" s="7">
-        <v>4.331376</v>
+      <c r="D2033" s="11">
+        <v>4.33016</v>
       </c>
       <c r="E2033" s="8">
         <v>11573900</v>
@@ -59439,7 +59439,7 @@
         <v>914</v>
       </c>
       <c r="G2033" s="8">
-        <v>50130914.3</v>
+        <v>50116840.97</v>
       </c>
     </row>
     <row r="2034" spans="1:7" x14ac:dyDescent="0.25">
@@ -59499,7 +59499,7 @@
         <v>46269</v>
       </c>
       <c r="D2036" s="7">
-        <v>7.676399</v>
+        <v>7.675901</v>
       </c>
       <c r="E2036" s="8">
         <v>274862095</v>
@@ -59508,7 +59508,7 @@
         <v>1</v>
       </c>
       <c r="G2036" s="8">
-        <v>2109951088.3</v>
+        <v>2109814339.67</v>
       </c>
     </row>
     <row r="2037" spans="1:7" x14ac:dyDescent="0.25">
@@ -59522,7 +59522,7 @@
         <v>46269</v>
       </c>
       <c r="D2037" s="7">
-        <v>1.368759</v>
+        <v>1.369674</v>
       </c>
       <c r="E2037" s="8">
         <v>34828789</v>
@@ -59531,7 +59531,7 @@
         <v>1079</v>
       </c>
       <c r="G2037" s="8">
-        <v>47672207.83</v>
+        <v>47704097.98</v>
       </c>
     </row>
     <row r="2038" spans="1:7" x14ac:dyDescent="0.25">

--- a/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/menkul-kiymet-yatirim-fonlari/data/menkul-kiymet-yatirim-fonlari-tarihsel.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>10.09.2026 09:19:54</t>
+    <t>10.09.2026 12:48:19</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -12854,7 +12854,7 @@
         <v>46275</v>
       </c>
       <c r="D7" s="7">
-        <v>12.899615</v>
+        <v>12.899632</v>
       </c>
       <c r="E7" s="8">
         <v>1400703</v>
@@ -12863,7 +12863,7 @@
         <v>155</v>
       </c>
       <c r="G7" s="8">
-        <v>18068528.73</v>
+        <v>18068553.35</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -13313,17 +13313,17 @@
       <c r="C27" s="6">
         <v>46275</v>
       </c>
-      <c r="D27" s="8">
-        <v>0</v>
+      <c r="D27" s="11">
+        <v>0.19955</v>
       </c>
       <c r="E27" s="8">
-        <v>0</v>
+        <v>7425620529</v>
       </c>
       <c r="F27" s="9">
         <v>35759</v>
       </c>
       <c r="G27" s="8">
-        <v>0</v>
+        <v>1481782304.75</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -13590,7 +13590,7 @@
         <v>46275</v>
       </c>
       <c r="D39" s="7">
-        <v>22.121509</v>
+        <v>22.173296</v>
       </c>
       <c r="E39" s="8">
         <v>6216640</v>
@@ -13599,7 +13599,7 @@
         <v>204</v>
       </c>
       <c r="G39" s="8">
-        <v>137521455.13</v>
+        <v>137843397.05</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -13612,8 +13612,8 @@
       <c r="C40" s="6">
         <v>46275</v>
       </c>
-      <c r="D40" s="11">
-        <v>32.08665</v>
+      <c r="D40" s="7">
+        <v>32.151804</v>
       </c>
       <c r="E40" s="8">
         <v>3162820</v>
@@ -13622,7 +13622,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="8">
-        <v>101484297.21</v>
+        <v>101690367.56</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -14165,16 +14165,16 @@
         <v>46275</v>
       </c>
       <c r="D64" s="7">
-        <v>22.003192</v>
+        <v>22.003193</v>
       </c>
       <c r="E64" s="8">
-        <v>11834133</v>
+        <v>11834553</v>
       </c>
       <c r="F64" s="9">
         <v>157</v>
       </c>
       <c r="G64" s="8">
-        <v>260388702.81</v>
+        <v>260397948.47</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -14348,17 +14348,17 @@
       <c r="C72" s="6">
         <v>46275</v>
       </c>
-      <c r="D72" s="8">
-        <v>0</v>
+      <c r="D72" s="7">
+        <v>7.009887</v>
       </c>
       <c r="E72" s="8">
-        <v>0</v>
+        <v>11966739</v>
       </c>
       <c r="F72" s="9">
         <v>2881</v>
       </c>
       <c r="G72" s="8">
-        <v>0</v>
+        <v>83885489.76</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -14463,17 +14463,17 @@
       <c r="C77" s="6">
         <v>46275</v>
       </c>
-      <c r="D77" s="8">
-        <v>0</v>
+      <c r="D77" s="7">
+        <v>16.276416</v>
       </c>
       <c r="E77" s="8">
-        <v>0</v>
+        <v>247313034</v>
       </c>
       <c r="F77" s="9">
         <v>7336</v>
       </c>
       <c r="G77" s="8">
-        <v>0</v>
+        <v>4025369818.23</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -14486,17 +14486,17 @@
       <c r="C78" s="6">
         <v>46275</v>
       </c>
-      <c r="D78" s="8">
-        <v>0</v>
+      <c r="D78" s="7">
+        <v>18.700775</v>
       </c>
       <c r="E78" s="8">
-        <v>0</v>
+        <v>163664872</v>
       </c>
       <c r="F78" s="9">
         <v>5021</v>
       </c>
       <c r="G78" s="8">
-        <v>0</v>
+        <v>3060659967.28</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -14588,7 +14588,7 @@
         <v>745</v>
       </c>
       <c r="G82" s="8">
-        <v>62297900.35</v>
+        <v>62297902.36</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -14670,17 +14670,17 @@
       <c r="C86" s="6">
         <v>46275</v>
       </c>
-      <c r="D86" s="8">
-        <v>0</v>
+      <c r="D86" s="7">
+        <v>129.818566</v>
       </c>
       <c r="E86" s="8">
-        <v>0</v>
+        <v>2028702</v>
       </c>
       <c r="F86" s="9">
         <v>12</v>
       </c>
       <c r="G86" s="8">
-        <v>0</v>
+        <v>263363185.02</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -15157,7 +15157,7 @@
         <v>0.024407</v>
       </c>
       <c r="E107" s="8">
-        <v>343025633</v>
+        <v>3252400</v>
       </c>
       <c r="F107" s="9">
         <v>8</v>
@@ -15430,7 +15430,7 @@
         <v>46275</v>
       </c>
       <c r="D119" s="7">
-        <v>1.849883</v>
+        <v>1.851322</v>
       </c>
       <c r="E119" s="8">
         <v>5601605</v>
@@ -15439,7 +15439,7 @@
         <v>56</v>
       </c>
       <c r="G119" s="8">
-        <v>10362312.41</v>
+        <v>10370375.86</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -16419,7 +16419,7 @@
         <v>46275</v>
       </c>
       <c r="D162" s="7">
-        <v>1.360195</v>
+        <v>1.368564</v>
       </c>
       <c r="E162" s="8">
         <v>86896483</v>
@@ -16428,7 +16428,7 @@
         <v>38</v>
       </c>
       <c r="G162" s="8">
-        <v>118196121.11</v>
+        <v>118923441.39</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -16442,7 +16442,7 @@
         <v>46275</v>
       </c>
       <c r="D163" s="11">
-        <v>1.66192</v>
+        <v>1.66307</v>
       </c>
       <c r="E163" s="8">
         <v>53541731</v>
@@ -16451,7 +16451,7 @@
         <v>1152</v>
       </c>
       <c r="G163" s="8">
-        <v>88982089.8</v>
+        <v>89043622.11</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -16741,7 +16741,7 @@
         <v>46275</v>
       </c>
       <c r="D176" s="7">
-        <v>1.820299</v>
+        <v>1.820293</v>
       </c>
       <c r="E176" s="8">
         <v>1368978024</v>
@@ -16750,7 +16750,7 @@
         <v>2768</v>
       </c>
       <c r="G176" s="8">
-        <v>2491948693.36</v>
+        <v>2491940693.99</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -16948,7 +16948,7 @@
         <v>46275</v>
       </c>
       <c r="D185" s="7">
-        <v>1.323668</v>
+        <v>1.327129</v>
       </c>
       <c r="E185" s="8">
         <v>72891857</v>
@@ -16957,7 +16957,7 @@
         <v>2413</v>
       </c>
       <c r="G185" s="8">
-        <v>96484629.53</v>
+        <v>96736866.99</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -17684,7 +17684,7 @@
         <v>46275</v>
       </c>
       <c r="D217" s="7">
-        <v>2.048821</v>
+        <v>2.187295</v>
       </c>
       <c r="E217" s="8">
         <v>327679259</v>
@@ -17693,7 +17693,7 @@
         <v>2925</v>
       </c>
       <c r="G217" s="8">
-        <v>671356272.34</v>
+        <v>716731166.97</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -17776,7 +17776,7 @@
         <v>46275</v>
       </c>
       <c r="D221" s="7">
-        <v>3.878405</v>
+        <v>3.878384</v>
       </c>
       <c r="E221" s="8">
         <v>244627558</v>
@@ -17785,7 +17785,7 @@
         <v>14066</v>
       </c>
       <c r="G221" s="8">
-        <v>948764722.27</v>
+        <v>948759596.54</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -19155,8 +19155,8 @@
       <c r="C281" s="6">
         <v>46275</v>
       </c>
-      <c r="D281" s="7">
-        <v>5.431054</v>
+      <c r="D281" s="11">
+        <v>5.43084</v>
       </c>
       <c r="E281" s="8">
         <v>4778989</v>
@@ -19165,7 +19165,7 @@
         <v>1125</v>
       </c>
       <c r="G281" s="8">
-        <v>25954946.49</v>
+        <v>25953925.76</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -19225,7 +19225,7 @@
         <v>46275</v>
       </c>
       <c r="D284" s="7">
-        <v>1.151731</v>
+        <v>1.151617</v>
       </c>
       <c r="E284" s="8">
         <v>63251563</v>
@@ -19234,7 +19234,7 @@
         <v>773</v>
       </c>
       <c r="G284" s="8">
-        <v>72848809.51</v>
+        <v>72841572.88</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -19271,7 +19271,7 @@
         <v>46275</v>
       </c>
       <c r="D286" s="7">
-        <v>1.495644</v>
+        <v>1.494959</v>
       </c>
       <c r="E286" s="8">
         <v>18863957</v>
@@ -19280,7 +19280,7 @@
         <v>157</v>
       </c>
       <c r="G286" s="8">
-        <v>28213766.54</v>
+        <v>28200841.12</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -19708,7 +19708,7 @@
         <v>46275</v>
       </c>
       <c r="D305" s="7">
-        <v>7.107033</v>
+        <v>7.113512</v>
       </c>
       <c r="E305" s="8">
         <v>438683746</v>
@@ -19717,7 +19717,7 @@
         <v>15288</v>
       </c>
       <c r="G305" s="8">
-        <v>3117739936.4</v>
+        <v>3120581980.54</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -19846,7 +19846,7 @@
         <v>46275</v>
       </c>
       <c r="D311" s="7">
-        <v>1.382108</v>
+        <v>1.383603</v>
       </c>
       <c r="E311" s="8">
         <v>187438768</v>
@@ -19855,7 +19855,7 @@
         <v>190</v>
       </c>
       <c r="G311" s="8">
-        <v>259060575.99</v>
+        <v>259340765.68</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -20236,8 +20236,8 @@
       <c r="C328" s="6">
         <v>46275</v>
       </c>
-      <c r="D328" s="11">
-        <v>75.68477</v>
+      <c r="D328" s="7">
+        <v>75.683774</v>
       </c>
       <c r="E328" s="8">
         <v>7294243</v>
@@ -20246,7 +20246,7 @@
         <v>3</v>
       </c>
       <c r="G328" s="8">
-        <v>552063106.08</v>
+        <v>552055841.29</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
@@ -20513,7 +20513,7 @@
         <v>46275</v>
       </c>
       <c r="D340" s="7">
-        <v>103.852887</v>
+        <v>103.854813</v>
       </c>
       <c r="E340" s="8">
         <v>22490084</v>
@@ -20522,7 +20522,7 @@
         <v>1</v>
       </c>
       <c r="G340" s="8">
-        <v>2335660151.7</v>
+        <v>2335703479.25</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
@@ -20788,8 +20788,8 @@
       <c r="C352" s="6">
         <v>46275</v>
       </c>
-      <c r="D352" s="11">
-        <v>15.06396</v>
+      <c r="D352" s="7">
+        <v>15.067598</v>
       </c>
       <c r="E352" s="8">
         <v>9835012</v>
@@ -20798,7 +20798,7 @@
         <v>1224</v>
       </c>
       <c r="G352" s="8">
-        <v>148154231.27</v>
+        <v>148190005.22</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
@@ -21226,7 +21226,7 @@
         <v>46275</v>
       </c>
       <c r="D371" s="7">
-        <v>10.013589</v>
+        <v>10.013215</v>
       </c>
       <c r="E371" s="8">
         <v>90365248</v>
@@ -21235,7 +21235,7 @@
         <v>11049</v>
       </c>
       <c r="G371" s="8">
-        <v>904880479</v>
+        <v>904846679.4</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
@@ -21824,7 +21824,7 @@
         <v>46275</v>
       </c>
       <c r="D397" s="7">
-        <v>1.058911</v>
+        <v>1.058205</v>
       </c>
       <c r="E397" s="8">
         <v>262335376</v>
@@ -21833,7 +21833,7 @@
         <v>122</v>
       </c>
       <c r="G397" s="8">
-        <v>277789812.08</v>
+        <v>277604621.02</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
@@ -21938,17 +21938,17 @@
       <c r="C402" s="6">
         <v>46275</v>
       </c>
-      <c r="D402" s="8">
-        <v>0</v>
+      <c r="D402" s="7">
+        <v>9.804966</v>
       </c>
       <c r="E402" s="8">
-        <v>0</v>
+        <v>68419205</v>
       </c>
       <c r="F402" s="9">
         <v>1</v>
       </c>
       <c r="G402" s="8">
-        <v>0</v>
+        <v>670847988.76</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
@@ -22109,7 +22109,7 @@
         <v>666</v>
       </c>
       <c r="G409" s="8">
-        <v>68376822.52</v>
+        <v>68376822.72</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
@@ -22123,7 +22123,7 @@
         <v>46275</v>
       </c>
       <c r="D410" s="7">
-        <v>49.082506</v>
+        <v>49.082611</v>
       </c>
       <c r="E410" s="8">
         <v>1565638</v>
@@ -22132,7 +22132,7 @@
         <v>119</v>
       </c>
       <c r="G410" s="8">
-        <v>76845437.12</v>
+        <v>76845600.68</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
@@ -22238,7 +22238,7 @@
         <v>46275</v>
       </c>
       <c r="D415" s="7">
-        <v>1.137919</v>
+        <v>1.136498</v>
       </c>
       <c r="E415" s="8">
         <v>252644514</v>
@@ -22247,7 +22247,7 @@
         <v>338</v>
       </c>
       <c r="G415" s="8">
-        <v>287488979.44</v>
+        <v>287129970.9</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
@@ -22261,7 +22261,7 @@
         <v>46275</v>
       </c>
       <c r="D416" s="7">
-        <v>1.382524</v>
+        <v>1.393756</v>
       </c>
       <c r="E416" s="8">
         <v>171740263</v>
@@ -22270,7 +22270,7 @@
         <v>1504</v>
       </c>
       <c r="G416" s="8">
-        <v>237434962.01</v>
+        <v>239364029.12</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
@@ -22491,7 +22491,7 @@
         <v>46275</v>
       </c>
       <c r="D426" s="7">
-        <v>1.198671</v>
+        <v>1.198316</v>
       </c>
       <c r="E426" s="8">
         <v>47109379</v>
@@ -22500,7 +22500,7 @@
         <v>649</v>
       </c>
       <c r="G426" s="8">
-        <v>56468646.26</v>
+        <v>56451944.16</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
@@ -22514,16 +22514,16 @@
         <v>46275</v>
       </c>
       <c r="D427" s="7">
-        <v>3.079774</v>
+        <v>3.087774</v>
       </c>
       <c r="E427" s="8">
-        <v>13741636</v>
+        <v>13693070</v>
       </c>
       <c r="F427" s="9">
         <v>484</v>
       </c>
       <c r="G427" s="8">
-        <v>42321130.57</v>
+        <v>42281101.02</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
@@ -22652,7 +22652,7 @@
         <v>46275</v>
       </c>
       <c r="D433" s="7">
-        <v>5.571901</v>
+        <v>5.571844</v>
       </c>
       <c r="E433" s="8">
         <v>426605660</v>
@@ -22661,7 +22661,7 @@
         <v>417</v>
       </c>
       <c r="G433" s="8">
-        <v>2377004371.63</v>
+        <v>2376980315.35</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
@@ -22698,7 +22698,7 @@
         <v>46275</v>
       </c>
       <c r="D435" s="7">
-        <v>4.771053</v>
+        <v>4.771055</v>
       </c>
       <c r="E435" s="8">
         <v>62584006</v>
@@ -22707,7 +22707,7 @@
         <v>398</v>
       </c>
       <c r="G435" s="8">
-        <v>298591625.1</v>
+        <v>298591744.39</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
@@ -22997,7 +22997,7 @@
         <v>46275</v>
       </c>
       <c r="D448" s="7">
-        <v>7.880549</v>
+        <v>7.897267</v>
       </c>
       <c r="E448" s="8">
         <v>255555682</v>
@@ -23006,7 +23006,7 @@
         <v>2393</v>
       </c>
       <c r="G448" s="8">
-        <v>2013919201.14</v>
+        <v>2018191326.87</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
@@ -23226,8 +23226,8 @@
       <c r="C458" s="6">
         <v>46275</v>
       </c>
-      <c r="D458" s="7">
-        <v>7.377801</v>
+      <c r="D458" s="11">
+        <v>7.37734</v>
       </c>
       <c r="E458" s="8">
         <v>54154743</v>
@@ -23236,7 +23236,7 @@
         <v>729</v>
       </c>
       <c r="G458" s="8">
-        <v>399542897.33</v>
+        <v>399517972.87</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.25">
@@ -23732,8 +23732,8 @@
       <c r="C480" s="6">
         <v>46275</v>
       </c>
-      <c r="D480" s="11">
-        <v>70.01305</v>
+      <c r="D480" s="7">
+        <v>70.013049</v>
       </c>
       <c r="E480" s="8">
         <v>1936730338</v>
@@ -23742,7 +23742,7 @@
         <v>19506</v>
       </c>
       <c r="G480" s="8">
-        <v>135596397083.53</v>
+        <v>135596395631.88</v>
       </c>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
@@ -23940,7 +23940,7 @@
         <v>46275</v>
       </c>
       <c r="D489" s="7">
-        <v>2.393241</v>
+        <v>2.392863</v>
       </c>
       <c r="E489" s="8">
         <v>23868196</v>
@@ -23949,7 +23949,7 @@
         <v>62</v>
       </c>
       <c r="G489" s="8">
-        <v>57122355.92</v>
+        <v>57113333.3</v>
       </c>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
@@ -24031,8 +24031,8 @@
       <c r="C493" s="6">
         <v>46275</v>
       </c>
-      <c r="D493" s="11">
-        <v>4.87261</v>
+      <c r="D493" s="7">
+        <v>4.872713</v>
       </c>
       <c r="E493" s="8">
         <v>76997961</v>
@@ -24041,7 +24041,7 @@
         <v>527</v>
       </c>
       <c r="G493" s="8">
-        <v>375181047.77</v>
+        <v>375188956.59</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
@@ -24146,17 +24146,17 @@
       <c r="C498" s="6">
         <v>46275</v>
       </c>
-      <c r="D498" s="8">
-        <v>0</v>
+      <c r="D498" s="7">
+        <v>1.494935</v>
       </c>
       <c r="E498" s="8">
-        <v>0</v>
+        <v>1147646364</v>
       </c>
       <c r="F498" s="9">
         <v>7815</v>
       </c>
       <c r="G498" s="8">
-        <v>0</v>
+        <v>1715656240.86</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
@@ -24377,7 +24377,7 @@
         <v>46275</v>
       </c>
       <c r="D508" s="7">
-        <v>0.055087</v>
+        <v>0.055086</v>
       </c>
       <c r="E508" s="8">
         <v>28027125480.69</v>
@@ -24386,7 +24386,7 @@
         <v>143</v>
       </c>
       <c r="G508" s="8">
-        <v>1543917544.98</v>
+        <v>1543913383.21</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
@@ -24630,7 +24630,7 @@
         <v>46275</v>
       </c>
       <c r="D519" s="7">
-        <v>5.783749</v>
+        <v>5.796738</v>
       </c>
       <c r="E519" s="8">
         <v>202733301.63</v>
@@ -24639,7 +24639,7 @@
         <v>2117</v>
       </c>
       <c r="G519" s="8">
-        <v>1172558453.64</v>
+        <v>1175191798.61</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
@@ -24790,17 +24790,17 @@
       <c r="C526" s="6">
         <v>46275</v>
       </c>
-      <c r="D526" s="8">
-        <v>0</v>
+      <c r="D526" s="7">
+        <v>12.884075</v>
       </c>
       <c r="E526" s="8">
-        <v>0</v>
+        <v>27976880</v>
       </c>
       <c r="F526" s="9">
         <v>2705</v>
       </c>
       <c r="G526" s="8">
-        <v>0</v>
+        <v>360456220.47</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
@@ -24928,17 +24928,17 @@
       <c r="C532" s="6">
         <v>46275</v>
       </c>
-      <c r="D532" s="8">
-        <v>0</v>
+      <c r="D532" s="7">
+        <v>63.125898</v>
       </c>
       <c r="E532" s="8">
-        <v>0</v>
+        <v>3941000</v>
       </c>
       <c r="F532" s="9">
         <v>1</v>
       </c>
       <c r="G532" s="8">
-        <v>0</v>
+        <v>248779165.05</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
@@ -25089,17 +25089,17 @@
       <c r="C539" s="6">
         <v>46275</v>
       </c>
-      <c r="D539" s="8">
-        <v>0</v>
+      <c r="D539" s="7">
+        <v>71.801283</v>
       </c>
       <c r="E539" s="8">
-        <v>0</v>
+        <v>53983981</v>
       </c>
       <c r="F539" s="9">
         <v>2</v>
       </c>
       <c r="G539" s="8">
-        <v>0</v>
+        <v>3876119093.13</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
@@ -25112,17 +25112,17 @@
       <c r="C540" s="6">
         <v>46275</v>
       </c>
-      <c r="D540" s="8">
-        <v>0</v>
+      <c r="D540" s="7">
+        <v>13.677329</v>
       </c>
       <c r="E540" s="8">
-        <v>0</v>
+        <v>165346771</v>
       </c>
       <c r="F540" s="9">
         <v>21915</v>
       </c>
       <c r="G540" s="8">
-        <v>0</v>
+        <v>2261502171.65</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
@@ -25136,7 +25136,7 @@
         <v>46275</v>
       </c>
       <c r="D541" s="7">
-        <v>3.673545</v>
+        <v>3.673127</v>
       </c>
       <c r="E541" s="8">
         <v>335083928</v>
@@ -25145,7 +25145,7 @@
         <v>3238</v>
       </c>
       <c r="G541" s="8">
-        <v>1230946012.5</v>
+        <v>1230805908.04</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
@@ -25181,17 +25181,17 @@
       <c r="C543" s="6">
         <v>46275</v>
       </c>
-      <c r="D543" s="8">
-        <v>0</v>
+      <c r="D543" s="7">
+        <v>6.029414</v>
       </c>
       <c r="E543" s="8">
-        <v>0</v>
+        <v>222060386</v>
       </c>
       <c r="F543" s="9">
         <v>2</v>
       </c>
       <c r="G543" s="8">
-        <v>0</v>
+        <v>1338894016.51</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
@@ -25250,17 +25250,17 @@
       <c r="C546" s="6">
         <v>46275</v>
       </c>
-      <c r="D546" s="8">
-        <v>0</v>
+      <c r="D546" s="7">
+        <v>61.651206</v>
       </c>
       <c r="E546" s="8">
-        <v>0</v>
+        <v>194715</v>
       </c>
       <c r="F546" s="9">
         <v>1</v>
       </c>
       <c r="G546" s="8">
-        <v>0</v>
+        <v>12004414.57</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
@@ -25273,17 +25273,17 @@
       <c r="C547" s="6">
         <v>46275</v>
       </c>
-      <c r="D547" s="8">
-        <v>0</v>
+      <c r="D547" s="7">
+        <v>62.694795</v>
       </c>
       <c r="E547" s="8">
-        <v>0</v>
+        <v>8101428</v>
       </c>
       <c r="F547" s="9">
         <v>4</v>
       </c>
       <c r="G547" s="8">
-        <v>0</v>
+        <v>507917369.01</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
@@ -25457,17 +25457,17 @@
       <c r="C555" s="6">
         <v>46275</v>
       </c>
-      <c r="D555" s="8">
-        <v>0</v>
+      <c r="D555" s="7">
+        <v>11.656889</v>
       </c>
       <c r="E555" s="8">
-        <v>0</v>
+        <v>29486927</v>
       </c>
       <c r="F555" s="9">
         <v>1</v>
       </c>
       <c r="G555" s="8">
-        <v>0</v>
+        <v>343725823.54</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
@@ -25503,17 +25503,17 @@
       <c r="C557" s="6">
         <v>46275</v>
       </c>
-      <c r="D557" s="8">
-        <v>0</v>
+      <c r="D557" s="7">
+        <v>71.208756</v>
       </c>
       <c r="E557" s="8">
-        <v>0</v>
+        <v>5822807</v>
       </c>
       <c r="F557" s="9">
         <v>3</v>
       </c>
       <c r="G557" s="8">
-        <v>0</v>
+        <v>414634843.91</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
@@ -25664,17 +25664,17 @@
       <c r="C564" s="6">
         <v>46275</v>
       </c>
-      <c r="D564" s="8">
-        <v>0</v>
+      <c r="D564" s="7">
+        <v>10.313121</v>
       </c>
       <c r="E564" s="8">
-        <v>0</v>
+        <v>6927</v>
       </c>
       <c r="F564" s="9">
         <v>1</v>
       </c>
       <c r="G564" s="8">
-        <v>0</v>
+        <v>71438.99</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
@@ -25687,17 +25687,17 @@
       <c r="C565" s="6">
         <v>46275</v>
       </c>
-      <c r="D565" s="8">
-        <v>0</v>
+      <c r="D565" s="7">
+        <v>69.088339</v>
       </c>
       <c r="E565" s="8">
-        <v>0</v>
+        <v>23548896</v>
       </c>
       <c r="F565" s="9">
         <v>3</v>
       </c>
       <c r="G565" s="8">
-        <v>0</v>
+        <v>1626954104.59</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
@@ -25802,17 +25802,17 @@
       <c r="C570" s="6">
         <v>46275</v>
       </c>
-      <c r="D570" s="8">
-        <v>0</v>
+      <c r="D570" s="7">
+        <v>67.503534</v>
       </c>
       <c r="E570" s="8">
-        <v>0</v>
+        <v>14263356</v>
       </c>
       <c r="F570" s="9">
         <v>3</v>
       </c>
       <c r="G570" s="8">
-        <v>0</v>
+        <v>962826938.36</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
@@ -25826,7 +25826,7 @@
         <v>46275</v>
       </c>
       <c r="D571" s="7">
-        <v>10.680499</v>
+        <v>10.676802</v>
       </c>
       <c r="E571" s="8">
         <v>6991639</v>
@@ -25835,7 +25835,7 @@
         <v>949</v>
       </c>
       <c r="G571" s="8">
-        <v>74674196.09</v>
+        <v>74648344.28</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
@@ -25894,17 +25894,17 @@
       <c r="C574" s="6">
         <v>46275</v>
       </c>
-      <c r="D574" s="8">
-        <v>0</v>
+      <c r="D574" s="7">
+        <v>64.842566</v>
       </c>
       <c r="E574" s="8">
-        <v>0</v>
+        <v>3647864</v>
       </c>
       <c r="F574" s="9">
         <v>2</v>
       </c>
       <c r="G574" s="8">
-        <v>0</v>
+        <v>236536863.7</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
@@ -25963,17 +25963,17 @@
       <c r="C577" s="6">
         <v>46275</v>
       </c>
-      <c r="D577" s="8">
-        <v>0</v>
+      <c r="D577" s="7">
+        <v>60.539628</v>
       </c>
       <c r="E577" s="8">
-        <v>0</v>
+        <v>9779449</v>
       </c>
       <c r="F577" s="9">
         <v>1</v>
       </c>
       <c r="G577" s="8">
-        <v>0</v>
+        <v>592044200.39</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
@@ -26216,8 +26216,8 @@
       <c r="C588" s="6">
         <v>46275</v>
       </c>
-      <c r="D588" s="7">
-        <v>4.420713</v>
+      <c r="D588" s="11">
+        <v>4.42669</v>
       </c>
       <c r="E588" s="8">
         <v>3875881</v>
@@ -26226,7 +26226,7 @@
         <v>71</v>
       </c>
       <c r="G588" s="8">
-        <v>17134156.49</v>
+        <v>17157322.75</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
@@ -26400,17 +26400,17 @@
       <c r="C596" s="6">
         <v>46275</v>
       </c>
-      <c r="D596" s="8">
-        <v>0</v>
+      <c r="D596" s="7">
+        <v>8.173861</v>
       </c>
       <c r="E596" s="8">
-        <v>0</v>
+        <v>506649811</v>
       </c>
       <c r="F596" s="9">
         <v>20791</v>
       </c>
       <c r="G596" s="8">
-        <v>0</v>
+        <v>4141284935.45</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
@@ -26424,7 +26424,7 @@
         <v>46275</v>
       </c>
       <c r="D597" s="7">
-        <v>2.797751</v>
+        <v>2.797839</v>
       </c>
       <c r="E597" s="8">
         <v>5674704</v>
@@ -26433,7 +26433,7 @@
         <v>108</v>
       </c>
       <c r="G597" s="8">
-        <v>15876408.93</v>
+        <v>15876907.81</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
@@ -26768,17 +26768,17 @@
       <c r="C612" s="6">
         <v>46275</v>
       </c>
-      <c r="D612" s="8">
-        <v>0</v>
+      <c r="D612" s="7">
+        <v>1.620639</v>
       </c>
       <c r="E612" s="8">
-        <v>0</v>
+        <v>1257615</v>
       </c>
       <c r="F612" s="9">
         <v>465</v>
       </c>
       <c r="G612" s="8">
-        <v>0</v>
+        <v>2038140.01</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
@@ -26792,7 +26792,7 @@
         <v>46275</v>
       </c>
       <c r="D613" s="7">
-        <v>4.884475</v>
+        <v>4.886767</v>
       </c>
       <c r="E613" s="8">
         <v>16684283</v>
@@ -26801,7 +26801,7 @@
         <v>736</v>
       </c>
       <c r="G613" s="8">
-        <v>81493970.26</v>
+        <v>81532200.09</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
@@ -26815,7 +26815,7 @@
         <v>46275</v>
       </c>
       <c r="D614" s="11">
-        <v>5.01472</v>
+        <v>5.01015</v>
       </c>
       <c r="E614" s="8">
         <v>7462619</v>
@@ -26824,7 +26824,7 @@
         <v>449</v>
       </c>
       <c r="G614" s="8">
-        <v>37422947.07</v>
+        <v>37388839.01</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
@@ -26838,7 +26838,7 @@
         <v>46275</v>
       </c>
       <c r="D615" s="7">
-        <v>5.428706</v>
+        <v>5.421489</v>
       </c>
       <c r="E615" s="8">
         <v>9167689</v>
@@ -26847,7 +26847,7 @@
         <v>733</v>
       </c>
       <c r="G615" s="8">
-        <v>49768685.57</v>
+        <v>49702522.55</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
@@ -26870,7 +26870,7 @@
         <v>3976</v>
       </c>
       <c r="G616" s="8">
-        <v>4792467377.19</v>
+        <v>4792467376.85</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
@@ -27182,17 +27182,17 @@
       <c r="C630" s="6">
         <v>46275</v>
       </c>
-      <c r="D630" s="8">
-        <v>0</v>
+      <c r="D630" s="7">
+        <v>45.708917</v>
       </c>
       <c r="E630" s="8">
-        <v>0</v>
+        <v>58637</v>
       </c>
       <c r="F630" s="9">
         <v>1</v>
       </c>
       <c r="G630" s="8">
-        <v>0</v>
+        <v>2680233.77</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
@@ -27205,17 +27205,17 @@
       <c r="C631" s="6">
         <v>46275</v>
       </c>
-      <c r="D631" s="8">
-        <v>0</v>
+      <c r="D631" s="7">
+        <v>18.850259</v>
       </c>
       <c r="E631" s="8">
-        <v>0</v>
+        <v>39493140</v>
       </c>
       <c r="F631" s="9">
         <v>2801</v>
       </c>
       <c r="G631" s="8">
-        <v>0</v>
+        <v>744455932.95</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
@@ -27596,17 +27596,17 @@
       <c r="C648" s="6">
         <v>46275</v>
       </c>
-      <c r="D648" s="8">
-        <v>0</v>
+      <c r="D648" s="7">
+        <v>58.067356</v>
       </c>
       <c r="E648" s="8">
-        <v>0</v>
+        <v>4643160</v>
       </c>
       <c r="F648" s="9">
         <v>2</v>
       </c>
       <c r="G648" s="8">
-        <v>0</v>
+        <v>269616024.69</v>
       </c>
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.25">
@@ -27711,17 +27711,17 @@
       <c r="C653" s="6">
         <v>46275</v>
       </c>
-      <c r="D653" s="8">
-        <v>0</v>
+      <c r="D653" s="7">
+        <v>7.147771</v>
       </c>
       <c r="E653" s="8">
-        <v>0</v>
+        <v>4029467144</v>
       </c>
       <c r="F653" s="9">
         <v>1</v>
       </c>
       <c r="G653" s="8">
-        <v>0</v>
+        <v>28801706942.43</v>
       </c>
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.25">
@@ -27941,17 +27941,17 @@
       <c r="C663" s="6">
         <v>46275</v>
       </c>
-      <c r="D663" s="8">
-        <v>0</v>
+      <c r="D663" s="7">
+        <v>0.468145</v>
       </c>
       <c r="E663" s="8">
-        <v>0</v>
+        <v>10727274084</v>
       </c>
       <c r="F663" s="9">
         <v>38501</v>
       </c>
       <c r="G663" s="8">
-        <v>0</v>
+        <v>5021920432.46</v>
       </c>
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.25">
@@ -27964,17 +27964,17 @@
       <c r="C664" s="6">
         <v>46275</v>
       </c>
-      <c r="D664" s="8">
-        <v>0</v>
+      <c r="D664" s="7">
+        <v>1.469832</v>
       </c>
       <c r="E664" s="8">
-        <v>0</v>
+        <v>791739035</v>
       </c>
       <c r="F664" s="9">
         <v>2606</v>
       </c>
       <c r="G664" s="8">
-        <v>0</v>
+        <v>1163723692.88</v>
       </c>
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.25">
@@ -27987,17 +27987,17 @@
       <c r="C665" s="6">
         <v>46275</v>
       </c>
-      <c r="D665" s="8">
-        <v>0</v>
+      <c r="D665" s="7">
+        <v>13.185291</v>
       </c>
       <c r="E665" s="8">
-        <v>0</v>
+        <v>518919341</v>
       </c>
       <c r="F665" s="9">
         <v>52678</v>
       </c>
       <c r="G665" s="8">
-        <v>0</v>
+        <v>6842102278.88</v>
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.25">
@@ -28033,17 +28033,17 @@
       <c r="C667" s="6">
         <v>46275</v>
       </c>
-      <c r="D667" s="8">
-        <v>0</v>
+      <c r="D667" s="7">
+        <v>4.184537</v>
       </c>
       <c r="E667" s="8">
-        <v>0</v>
+        <v>22930456</v>
       </c>
       <c r="F667" s="9">
         <v>3390</v>
       </c>
       <c r="G667" s="8">
-        <v>0</v>
+        <v>95953337.07</v>
       </c>
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.25">
@@ -28102,17 +28102,17 @@
       <c r="C670" s="6">
         <v>46275</v>
       </c>
-      <c r="D670" s="8">
-        <v>0</v>
+      <c r="D670" s="7">
+        <v>18.436944</v>
       </c>
       <c r="E670" s="8">
-        <v>0</v>
+        <v>22115</v>
       </c>
       <c r="F670" s="9">
         <v>1</v>
       </c>
       <c r="G670" s="8">
-        <v>0</v>
+        <v>407733.01</v>
       </c>
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.25">
@@ -28125,17 +28125,17 @@
       <c r="C671" s="6">
         <v>46275</v>
       </c>
-      <c r="D671" s="8">
-        <v>0</v>
+      <c r="D671" s="7">
+        <v>5.726017</v>
       </c>
       <c r="E671" s="8">
-        <v>0</v>
+        <v>205419161</v>
       </c>
       <c r="F671" s="9">
         <v>4573</v>
       </c>
       <c r="G671" s="8">
-        <v>0</v>
+        <v>1176233579.51</v>
       </c>
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.25">
@@ -28148,17 +28148,17 @@
       <c r="C672" s="6">
         <v>46275</v>
       </c>
-      <c r="D672" s="8">
-        <v>0</v>
+      <c r="D672" s="7">
+        <v>67.491595</v>
       </c>
       <c r="E672" s="8">
-        <v>0</v>
+        <v>7872114</v>
       </c>
       <c r="F672" s="9">
         <v>3</v>
       </c>
       <c r="G672" s="8">
-        <v>0</v>
+        <v>531301531.94</v>
       </c>
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.25">
@@ -28194,17 +28194,17 @@
       <c r="C674" s="6">
         <v>46275</v>
       </c>
-      <c r="D674" s="8">
-        <v>0</v>
+      <c r="D674" s="7">
+        <v>4.161339</v>
       </c>
       <c r="E674" s="8">
-        <v>0</v>
+        <v>5020082762</v>
       </c>
       <c r="F674" s="9">
         <v>1</v>
       </c>
       <c r="G674" s="8">
-        <v>0</v>
+        <v>20890267961.13</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
@@ -28378,17 +28378,17 @@
       <c r="C682" s="6">
         <v>46275</v>
       </c>
-      <c r="D682" s="8">
-        <v>0</v>
+      <c r="D682" s="7">
+        <v>8.151625</v>
       </c>
       <c r="E682" s="8">
-        <v>0</v>
+        <v>180930928</v>
       </c>
       <c r="F682" s="9">
         <v>4094</v>
       </c>
       <c r="G682" s="8">
-        <v>0</v>
+        <v>1474881065.71</v>
       </c>
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.25">
@@ -28401,17 +28401,17 @@
       <c r="C683" s="6">
         <v>46275</v>
       </c>
-      <c r="D683" s="8">
-        <v>0</v>
+      <c r="D683" s="7">
+        <v>7.463833</v>
       </c>
       <c r="E683" s="8">
-        <v>0</v>
+        <v>57427871</v>
       </c>
       <c r="F683" s="9">
         <v>4605</v>
       </c>
       <c r="G683" s="8">
-        <v>0</v>
+        <v>428632028.02</v>
       </c>
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.25">
@@ -28424,17 +28424,17 @@
       <c r="C684" s="6">
         <v>46275</v>
       </c>
-      <c r="D684" s="8">
-        <v>0</v>
+      <c r="D684" s="7">
+        <v>4.929951</v>
       </c>
       <c r="E684" s="8">
-        <v>0</v>
+        <v>74597090</v>
       </c>
       <c r="F684" s="9">
         <v>5499</v>
       </c>
       <c r="G684" s="8">
-        <v>0</v>
+        <v>367760035.58</v>
       </c>
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.25">
@@ -28447,17 +28447,17 @@
       <c r="C685" s="6">
         <v>46275</v>
       </c>
-      <c r="D685" s="8">
-        <v>0</v>
+      <c r="D685" s="7">
+        <v>8.847364</v>
       </c>
       <c r="E685" s="8">
-        <v>0</v>
+        <v>198036673</v>
       </c>
       <c r="F685" s="9">
         <v>5232</v>
       </c>
       <c r="G685" s="8">
-        <v>0</v>
+        <v>1752102507.5</v>
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.25">
@@ -28631,17 +28631,17 @@
       <c r="C693" s="6">
         <v>46275</v>
       </c>
-      <c r="D693" s="8">
-        <v>0</v>
+      <c r="D693" s="7">
+        <v>8.800625</v>
       </c>
       <c r="E693" s="8">
-        <v>0</v>
+        <v>11469860</v>
       </c>
       <c r="F693" s="9">
         <v>1379</v>
       </c>
       <c r="G693" s="8">
-        <v>0</v>
+        <v>100941935.64</v>
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.25">
@@ -28654,17 +28654,17 @@
       <c r="C694" s="6">
         <v>46275</v>
       </c>
-      <c r="D694" s="8">
-        <v>0</v>
+      <c r="D694" s="11">
+        <v>7.48794</v>
       </c>
       <c r="E694" s="8">
-        <v>0</v>
+        <v>8580684</v>
       </c>
       <c r="F694" s="9">
         <v>2257</v>
       </c>
       <c r="G694" s="8">
-        <v>0</v>
+        <v>64251642.77</v>
       </c>
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.25">
@@ -28677,17 +28677,17 @@
       <c r="C695" s="6">
         <v>46275</v>
       </c>
-      <c r="D695" s="8">
-        <v>0</v>
+      <c r="D695" s="7">
+        <v>7.097757</v>
       </c>
       <c r="E695" s="8">
-        <v>0</v>
+        <v>9188890</v>
       </c>
       <c r="F695" s="9">
         <v>1238</v>
       </c>
       <c r="G695" s="8">
-        <v>0</v>
+        <v>65220510.11</v>
       </c>
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.25">
@@ -28931,7 +28931,7 @@
         <v>46275</v>
       </c>
       <c r="D706" s="7">
-        <v>4.373019</v>
+        <v>4.378507</v>
       </c>
       <c r="E706" s="8">
         <v>122391336</v>
@@ -28940,7 +28940,7 @@
         <v>1066</v>
       </c>
       <c r="G706" s="8">
-        <v>535219641.95</v>
+        <v>535891322</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.25">
@@ -29206,17 +29206,17 @@
       <c r="C718" s="6">
         <v>46275</v>
       </c>
-      <c r="D718" s="8">
-        <v>0</v>
+      <c r="D718" s="7">
+        <v>3.339942</v>
       </c>
       <c r="E718" s="8">
-        <v>0</v>
+        <v>118829651</v>
       </c>
       <c r="F718" s="9">
         <v>1421</v>
       </c>
       <c r="G718" s="8">
-        <v>0</v>
+        <v>396884172.64</v>
       </c>
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.25">
@@ -30242,7 +30242,7 @@
         <v>46275</v>
       </c>
       <c r="D763" s="7">
-        <v>0.369976</v>
+        <v>0.369922</v>
       </c>
       <c r="E763" s="8">
         <v>3714397959</v>
@@ -30251,7 +30251,7 @@
         <v>2544</v>
       </c>
       <c r="G763" s="8">
-        <v>1374237790.74</v>
+        <v>1374039215.71</v>
       </c>
     </row>
     <row r="764" spans="1:7" x14ac:dyDescent="0.25">
@@ -30550,7 +30550,7 @@
         <v>5615</v>
       </c>
       <c r="G776" s="8">
-        <v>228164484.88</v>
+        <v>228164487.48</v>
       </c>
     </row>
     <row r="777" spans="1:7" x14ac:dyDescent="0.25">
@@ -30702,7 +30702,7 @@
         <v>46275</v>
       </c>
       <c r="D783" s="7">
-        <v>1.015461</v>
+        <v>1.014994</v>
       </c>
       <c r="E783" s="8">
         <v>110950432</v>
@@ -30711,7 +30711,7 @@
         <v>851</v>
       </c>
       <c r="G783" s="8">
-        <v>112665826.25</v>
+        <v>112613999.35</v>
       </c>
     </row>
     <row r="784" spans="1:7" x14ac:dyDescent="0.25">
@@ -31506,8 +31506,8 @@
       <c r="C818" s="6">
         <v>46275</v>
       </c>
-      <c r="D818" s="7">
-        <v>16.048175</v>
+      <c r="D818" s="11">
+        <v>16.04814</v>
       </c>
       <c r="E818" s="8">
         <v>33125727</v>
@@ -31516,7 +31516,7 @@
         <v>12</v>
       </c>
       <c r="G818" s="8">
-        <v>531607458.57</v>
+        <v>531606309.67</v>
       </c>
     </row>
     <row r="819" spans="1:7" x14ac:dyDescent="0.25">
@@ -31990,7 +31990,7 @@
         <v>46275</v>
       </c>
       <c r="D839" s="7">
-        <v>1.797211</v>
+        <v>1.795212</v>
       </c>
       <c r="E839" s="8">
         <v>38191392</v>
@@ -31999,7 +31999,7 @@
         <v>1121</v>
       </c>
       <c r="G839" s="8">
-        <v>68637973.15</v>
+        <v>68561631.62</v>
       </c>
     </row>
     <row r="840" spans="1:7" x14ac:dyDescent="0.25">
@@ -32679,17 +32679,17 @@
       <c r="C869" s="6">
         <v>46275</v>
       </c>
-      <c r="D869" s="8">
-        <v>0</v>
+      <c r="D869" s="7">
+        <v>1.598326</v>
       </c>
       <c r="E869" s="8">
-        <v>0</v>
+        <v>764576106</v>
       </c>
       <c r="F869" s="9">
         <v>14</v>
       </c>
       <c r="G869" s="8">
-        <v>0</v>
+        <v>1222041633.74</v>
       </c>
     </row>
     <row r="870" spans="1:7" x14ac:dyDescent="0.25">
@@ -32703,7 +32703,7 @@
         <v>46275</v>
       </c>
       <c r="D870" s="7">
-        <v>34.168922</v>
+        <v>34.168782</v>
       </c>
       <c r="E870" s="8">
         <v>52567064</v>
@@ -32712,7 +32712,7 @@
         <v>21296</v>
       </c>
       <c r="G870" s="8">
-        <v>1796159896.6</v>
+        <v>1796152536.83</v>
       </c>
     </row>
     <row r="871" spans="1:7" x14ac:dyDescent="0.25">
@@ -32749,7 +32749,7 @@
         <v>46275</v>
       </c>
       <c r="D872" s="7">
-        <v>36.849947</v>
+        <v>36.849199</v>
       </c>
       <c r="E872" s="8">
         <v>31363464.25</v>
@@ -32758,7 +32758,7 @@
         <v>134</v>
       </c>
       <c r="G872" s="8">
-        <v>1155741985.05</v>
+        <v>1155718530.2</v>
       </c>
     </row>
     <row r="873" spans="1:7" x14ac:dyDescent="0.25">
@@ -32864,7 +32864,7 @@
         <v>46275</v>
       </c>
       <c r="D877" s="7">
-        <v>9.762225</v>
+        <v>9.762298</v>
       </c>
       <c r="E877" s="8">
         <v>91781736</v>
@@ -32873,7 +32873,7 @@
         <v>2</v>
       </c>
       <c r="G877" s="8">
-        <v>895993919.7</v>
+        <v>896000702.81</v>
       </c>
     </row>
     <row r="878" spans="1:7" x14ac:dyDescent="0.25">
@@ -32886,17 +32886,17 @@
       <c r="C878" s="6">
         <v>46275</v>
       </c>
-      <c r="D878" s="8">
-        <v>0</v>
+      <c r="D878" s="7">
+        <v>7.394583</v>
       </c>
       <c r="E878" s="8">
-        <v>0</v>
+        <v>4408151</v>
       </c>
       <c r="F878" s="9">
         <v>387</v>
       </c>
       <c r="G878" s="8">
-        <v>0</v>
+        <v>32596438.53</v>
       </c>
     </row>
     <row r="879" spans="1:7" x14ac:dyDescent="0.25">
@@ -33576,17 +33576,17 @@
       <c r="C908" s="6">
         <v>46275</v>
       </c>
-      <c r="D908" s="8">
-        <v>0</v>
+      <c r="D908" s="11">
+        <v>15.14615</v>
       </c>
       <c r="E908" s="8">
-        <v>0</v>
+        <v>15081842</v>
       </c>
       <c r="F908" s="9">
         <v>381</v>
       </c>
       <c r="G908" s="8">
-        <v>0</v>
+        <v>228431843.3</v>
       </c>
     </row>
     <row r="909" spans="1:7" x14ac:dyDescent="0.25">
@@ -33967,8 +33967,8 @@
       <c r="C925" s="6">
         <v>46275</v>
       </c>
-      <c r="D925" s="7">
-        <v>0.124571</v>
+      <c r="D925" s="11">
+        <v>0.12461</v>
       </c>
       <c r="E925" s="8">
         <v>1105011730</v>
@@ -33977,7 +33977,7 @@
         <v>22</v>
       </c>
       <c r="G925" s="8">
-        <v>137652544.53</v>
+        <v>137695598.43</v>
       </c>
     </row>
     <row r="926" spans="1:7" x14ac:dyDescent="0.25">
@@ -34083,7 +34083,7 @@
         <v>46275</v>
       </c>
       <c r="D930" s="7">
-        <v>0.183965</v>
+        <v>0.184149</v>
       </c>
       <c r="E930" s="8">
         <v>38173757220</v>
@@ -34092,7 +34092,7 @@
         <v>162</v>
       </c>
       <c r="G930" s="8">
-        <v>7022641774.24</v>
+        <v>7029660140.16</v>
       </c>
     </row>
     <row r="931" spans="1:7" x14ac:dyDescent="0.25">
@@ -34175,7 +34175,7 @@
         <v>46275</v>
       </c>
       <c r="D934" s="7">
-        <v>1.339788</v>
+        <v>1.339782</v>
       </c>
       <c r="E934" s="8">
         <v>985476408</v>
@@ -34184,7 +34184,7 @@
         <v>750</v>
       </c>
       <c r="G934" s="8">
-        <v>1320329231.59</v>
+        <v>1320323292.59</v>
       </c>
     </row>
     <row r="935" spans="1:7" x14ac:dyDescent="0.25">
@@ -34220,17 +34220,17 @@
       <c r="C936" s="6">
         <v>46275</v>
       </c>
-      <c r="D936" s="8">
-        <v>0</v>
+      <c r="D936" s="7">
+        <v>7.584907</v>
       </c>
       <c r="E936" s="8">
-        <v>0</v>
+        <v>69560173</v>
       </c>
       <c r="F936" s="9">
         <v>1961</v>
       </c>
       <c r="G936" s="8">
-        <v>0</v>
+        <v>527607408.71</v>
       </c>
     </row>
     <row r="937" spans="1:7" x14ac:dyDescent="0.25">
@@ -34244,7 +34244,7 @@
         <v>46275</v>
       </c>
       <c r="D937" s="7">
-        <v>18.497145</v>
+        <v>18.497143</v>
       </c>
       <c r="E937" s="8">
         <v>15147672</v>
@@ -34253,7 +34253,7 @@
         <v>16</v>
       </c>
       <c r="G937" s="8">
-        <v>280188690.73</v>
+        <v>280188656.93</v>
       </c>
     </row>
     <row r="938" spans="1:7" x14ac:dyDescent="0.25">
@@ -34727,7 +34727,7 @@
         <v>46275</v>
       </c>
       <c r="D958" s="7">
-        <v>6.389166</v>
+        <v>6.383634</v>
       </c>
       <c r="E958" s="8">
         <v>1927715.66</v>
@@ -34736,7 +34736,7 @@
         <v>713</v>
       </c>
       <c r="G958" s="8">
-        <v>12316494.98</v>
+        <v>12305831.9</v>
       </c>
     </row>
     <row r="959" spans="1:7" x14ac:dyDescent="0.25">
@@ -35279,7 +35279,7 @@
         <v>46275</v>
       </c>
       <c r="D982" s="7">
-        <v>2.293816</v>
+        <v>2.293861</v>
       </c>
       <c r="E982" s="8">
         <v>214799255</v>
@@ -35288,7 +35288,7 @@
         <v>16843</v>
       </c>
       <c r="G982" s="8">
-        <v>492709946.42</v>
+        <v>492719670.05</v>
       </c>
     </row>
     <row r="983" spans="1:7" x14ac:dyDescent="0.25">
@@ -35577,17 +35577,17 @@
       <c r="C995" s="6">
         <v>46275</v>
       </c>
-      <c r="D995" s="8">
-        <v>0</v>
+      <c r="D995" s="7">
+        <v>58.611779</v>
       </c>
       <c r="E995" s="8">
-        <v>0</v>
+        <v>4238148</v>
       </c>
       <c r="F995" s="9">
         <v>12</v>
       </c>
       <c r="G995" s="8">
-        <v>0</v>
+        <v>248405395.01</v>
       </c>
     </row>
     <row r="996" spans="1:7" x14ac:dyDescent="0.25">
@@ -37256,17 +37256,17 @@
       <c r="C1068" s="6">
         <v>46275</v>
       </c>
-      <c r="D1068" s="8">
-        <v>0</v>
+      <c r="D1068" s="7">
+        <v>1.049535</v>
       </c>
       <c r="E1068" s="8">
-        <v>0</v>
+        <v>1508400</v>
       </c>
       <c r="F1068" s="9">
         <v>16</v>
       </c>
       <c r="G1068" s="8">
-        <v>0</v>
+        <v>1583118.2</v>
       </c>
     </row>
     <row r="1069" spans="1:7" x14ac:dyDescent="0.25">
@@ -37325,17 +37325,17 @@
       <c r="C1071" s="6">
         <v>46275</v>
       </c>
-      <c r="D1071" s="8">
-        <v>0</v>
+      <c r="D1071" s="7">
+        <v>48.546007</v>
       </c>
       <c r="E1071" s="8">
-        <v>0</v>
+        <v>485020000</v>
       </c>
       <c r="F1071" s="9">
         <v>3270</v>
       </c>
       <c r="G1071" s="8">
-        <v>0</v>
+        <v>23545784519.07</v>
       </c>
     </row>
     <row r="1072" spans="1:7" x14ac:dyDescent="0.25">
@@ -38061,17 +38061,17 @@
       <c r="C1103" s="6">
         <v>46275</v>
       </c>
-      <c r="D1103" s="8">
-        <v>0</v>
+      <c r="D1103" s="7">
+        <v>0.761859</v>
       </c>
       <c r="E1103" s="8">
-        <v>0</v>
+        <v>802540735</v>
       </c>
       <c r="F1103" s="9">
         <v>3583</v>
       </c>
       <c r="G1103" s="8">
-        <v>0</v>
+        <v>611423095.97</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.25">
@@ -38660,7 +38660,7 @@
         <v>46275</v>
       </c>
       <c r="D1129" s="7">
-        <v>3.743209</v>
+        <v>3.742757</v>
       </c>
       <c r="E1129" s="8">
         <v>245457201</v>
@@ -38669,7 +38669,7 @@
         <v>12</v>
       </c>
       <c r="G1129" s="8">
-        <v>918797527.68</v>
+        <v>918686700.77</v>
       </c>
     </row>
     <row r="1130" spans="1:7" x14ac:dyDescent="0.25">
@@ -38982,7 +38982,7 @@
         <v>46275</v>
       </c>
       <c r="D1143" s="7">
-        <v>1.374992</v>
+        <v>1.376543</v>
       </c>
       <c r="E1143" s="8">
         <v>388423829</v>
@@ -38991,7 +38991,7 @@
         <v>928</v>
       </c>
       <c r="G1143" s="8">
-        <v>534079797.17</v>
+        <v>534682295.05</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.25">
@@ -39166,16 +39166,16 @@
         <v>46275</v>
       </c>
       <c r="D1151" s="11">
-        <v>7.90091</v>
+        <v>7.90416</v>
       </c>
       <c r="E1151" s="8">
-        <v>6800110</v>
+        <v>6681115</v>
       </c>
       <c r="F1151" s="9">
         <v>804</v>
       </c>
       <c r="G1151" s="8">
-        <v>53727058.14</v>
+        <v>52808603.58</v>
       </c>
     </row>
     <row r="1152" spans="1:7" x14ac:dyDescent="0.25">
@@ -39212,16 +39212,16 @@
         <v>46275</v>
       </c>
       <c r="D1153" s="7">
-        <v>11.198677</v>
+        <v>11.371547</v>
       </c>
       <c r="E1153" s="8">
-        <v>88238490</v>
+        <v>88001508</v>
       </c>
       <c r="F1153" s="9">
         <v>7396</v>
       </c>
       <c r="G1153" s="8">
-        <v>988154357.13</v>
+        <v>1000713303.3</v>
       </c>
     </row>
     <row r="1154" spans="1:7" x14ac:dyDescent="0.25">
@@ -39235,7 +39235,7 @@
         <v>46275</v>
       </c>
       <c r="D1154" s="7">
-        <v>4.544395</v>
+        <v>4.503952</v>
       </c>
       <c r="E1154" s="8">
         <v>6093544</v>
@@ -39244,7 +39244,7 @@
         <v>34</v>
       </c>
       <c r="G1154" s="8">
-        <v>27691471.4</v>
+        <v>27445027.71</v>
       </c>
     </row>
     <row r="1155" spans="1:7" x14ac:dyDescent="0.25">
@@ -39428,7 +39428,7 @@
         <v>1426</v>
       </c>
       <c r="G1162" s="8">
-        <v>193714316.97</v>
+        <v>193714326.17</v>
       </c>
     </row>
     <row r="1163" spans="1:7" x14ac:dyDescent="0.25">
@@ -39465,7 +39465,7 @@
         <v>46275</v>
       </c>
       <c r="D1164" s="7">
-        <v>1.307642</v>
+        <v>1.305629</v>
       </c>
       <c r="E1164" s="8">
         <v>263455085</v>
@@ -39474,7 +39474,7 @@
         <v>117</v>
       </c>
       <c r="G1164" s="8">
-        <v>344504898.55</v>
+        <v>343974530.74</v>
       </c>
     </row>
     <row r="1165" spans="1:7" x14ac:dyDescent="0.25">
@@ -39487,17 +39487,17 @@
       <c r="C1165" s="6">
         <v>46275</v>
       </c>
-      <c r="D1165" s="8">
-        <v>0</v>
+      <c r="D1165" s="11">
+        <v>1.52798</v>
       </c>
       <c r="E1165" s="8">
-        <v>0</v>
+        <v>2651303752</v>
       </c>
       <c r="F1165" s="9">
         <v>13</v>
       </c>
       <c r="G1165" s="8">
-        <v>0</v>
+        <v>4051138306.29</v>
       </c>
     </row>
     <row r="1166" spans="1:7" x14ac:dyDescent="0.25">
@@ -39510,17 +39510,17 @@
       <c r="C1166" s="6">
         <v>46275</v>
       </c>
-      <c r="D1166" s="8">
-        <v>0</v>
+      <c r="D1166" s="7">
+        <v>2.148988</v>
       </c>
       <c r="E1166" s="8">
-        <v>0</v>
+        <v>1833168551</v>
       </c>
       <c r="F1166" s="9">
         <v>15</v>
       </c>
       <c r="G1166" s="8">
-        <v>0</v>
+        <v>3939457561.95</v>
       </c>
     </row>
     <row r="1167" spans="1:7" x14ac:dyDescent="0.25">
@@ -40178,16 +40178,16 @@
         <v>46275</v>
       </c>
       <c r="D1195" s="7">
-        <v>2.879408</v>
+        <v>2.882325</v>
       </c>
       <c r="E1195" s="8">
-        <v>10198598</v>
+        <v>10165589</v>
       </c>
       <c r="F1195" s="9">
         <v>679</v>
       </c>
       <c r="G1195" s="8">
-        <v>29365922.04</v>
+        <v>29300527.29</v>
       </c>
     </row>
     <row r="1196" spans="1:7" x14ac:dyDescent="0.25">
@@ -40200,17 +40200,17 @@
       <c r="C1196" s="6">
         <v>46275</v>
       </c>
-      <c r="D1196" s="8">
-        <v>0</v>
+      <c r="D1196" s="7">
+        <v>0.798543</v>
       </c>
       <c r="E1196" s="8">
-        <v>0</v>
+        <v>1033594769</v>
       </c>
       <c r="F1196" s="9">
         <v>19</v>
       </c>
       <c r="G1196" s="8">
-        <v>0</v>
+        <v>825370164.73</v>
       </c>
     </row>
     <row r="1197" spans="1:7" x14ac:dyDescent="0.25">
@@ -40453,17 +40453,17 @@
       <c r="C1207" s="6">
         <v>46275</v>
       </c>
-      <c r="D1207" s="8">
-        <v>0</v>
+      <c r="D1207" s="7">
+        <v>1.545872</v>
       </c>
       <c r="E1207" s="8">
-        <v>0</v>
+        <v>1504138569</v>
       </c>
       <c r="F1207" s="9">
         <v>395</v>
       </c>
       <c r="G1207" s="8">
-        <v>0</v>
+        <v>2325205281.15</v>
       </c>
     </row>
     <row r="1208" spans="1:7" x14ac:dyDescent="0.25">
@@ -40614,17 +40614,17 @@
       <c r="C1214" s="6">
         <v>46275</v>
       </c>
-      <c r="D1214" s="8">
-        <v>0</v>
+      <c r="D1214" s="7">
+        <v>1.375535</v>
       </c>
       <c r="E1214" s="8">
-        <v>0</v>
+        <v>1338955611</v>
       </c>
       <c r="F1214" s="9">
         <v>32</v>
       </c>
       <c r="G1214" s="8">
-        <v>0</v>
+        <v>1841780032.74</v>
       </c>
     </row>
     <row r="1215" spans="1:7" x14ac:dyDescent="0.25">
@@ -40683,17 +40683,17 @@
       <c r="C1217" s="6">
         <v>46275</v>
       </c>
-      <c r="D1217" s="8">
-        <v>0</v>
+      <c r="D1217" s="7">
+        <v>5.725108</v>
       </c>
       <c r="E1217" s="8">
-        <v>0</v>
+        <v>2093148</v>
       </c>
       <c r="F1217" s="9">
         <v>150</v>
       </c>
       <c r="G1217" s="8">
-        <v>0</v>
+        <v>11983499.09</v>
       </c>
     </row>
     <row r="1218" spans="1:7" x14ac:dyDescent="0.25">
@@ -41511,17 +41511,17 @@
       <c r="C1253" s="6">
         <v>46275</v>
       </c>
-      <c r="D1253" s="8">
-        <v>0</v>
+      <c r="D1253" s="7">
+        <v>1.621558</v>
       </c>
       <c r="E1253" s="8">
-        <v>0</v>
+        <v>592961232</v>
       </c>
       <c r="F1253" s="9">
         <v>1</v>
       </c>
       <c r="G1253" s="8">
-        <v>0</v>
+        <v>961521130.97</v>
       </c>
     </row>
     <row r="1254" spans="1:7" x14ac:dyDescent="0.25">
@@ -41580,17 +41580,17 @@
       <c r="C1256" s="6">
         <v>46275</v>
       </c>
-      <c r="D1256" s="8">
-        <v>0</v>
+      <c r="D1256" s="7">
+        <v>161.237289</v>
       </c>
       <c r="E1256" s="8">
-        <v>0</v>
+        <v>2588867</v>
       </c>
       <c r="F1256" s="9">
         <v>11</v>
       </c>
       <c r="G1256" s="8">
-        <v>0</v>
+        <v>417421896.18</v>
       </c>
     </row>
     <row r="1257" spans="1:7" x14ac:dyDescent="0.25">
@@ -41719,7 +41719,7 @@
         <v>46275</v>
       </c>
       <c r="D1262" s="7">
-        <v>66.063691</v>
+        <v>65.851962</v>
       </c>
       <c r="E1262" s="8">
         <v>16965870</v>
@@ -41728,7 +41728,7 @@
         <v>1</v>
       </c>
       <c r="G1262" s="8">
-        <v>1120827994.66</v>
+        <v>1117235822.85</v>
       </c>
     </row>
     <row r="1263" spans="1:7" x14ac:dyDescent="0.25">
@@ -42464,7 +42464,7 @@
         <v>39</v>
       </c>
       <c r="G1294" s="8">
-        <v>66943499.41</v>
+        <v>66943499.39</v>
       </c>
     </row>
     <row r="1295" spans="1:7" x14ac:dyDescent="0.25">
@@ -42501,7 +42501,7 @@
         <v>46275</v>
       </c>
       <c r="D1296" s="7">
-        <v>7.341385</v>
+        <v>7.341782</v>
       </c>
       <c r="E1296" s="8">
         <v>42019951</v>
@@ -42510,7 +42510,7 @@
         <v>142</v>
       </c>
       <c r="G1296" s="8">
-        <v>308484620.59</v>
+        <v>308501322.72</v>
       </c>
     </row>
     <row r="1297" spans="1:7" x14ac:dyDescent="0.25">
@@ -42546,17 +42546,17 @@
       <c r="C1298" s="6">
         <v>46275</v>
       </c>
-      <c r="D1298" s="8">
-        <v>0</v>
+      <c r="D1298" s="7">
+        <v>19.770727</v>
       </c>
       <c r="E1298" s="8">
-        <v>0</v>
+        <v>80775339</v>
       </c>
       <c r="F1298" s="9">
         <v>3797</v>
       </c>
       <c r="G1298" s="8">
-        <v>0</v>
+        <v>1596987177.86</v>
       </c>
     </row>
     <row r="1299" spans="1:7" x14ac:dyDescent="0.25">
@@ -42615,8 +42615,8 @@
       <c r="C1301" s="6">
         <v>46275</v>
       </c>
-      <c r="D1301" s="11">
-        <v>4.15132</v>
+      <c r="D1301" s="7">
+        <v>4.151321</v>
       </c>
       <c r="E1301" s="8">
         <v>38489912</v>
@@ -42625,7 +42625,7 @@
         <v>580</v>
       </c>
       <c r="G1301" s="8">
-        <v>159783923.76</v>
+        <v>159783983.07</v>
       </c>
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.25">
@@ -42685,7 +42685,7 @@
         <v>46275</v>
       </c>
       <c r="D1304" s="7">
-        <v>8.459952</v>
+        <v>8.459993</v>
       </c>
       <c r="E1304" s="8">
         <v>22427778</v>
@@ -42694,7 +42694,7 @@
         <v>428</v>
       </c>
       <c r="G1304" s="8">
-        <v>189737925.59</v>
+        <v>189738854.29</v>
       </c>
     </row>
     <row r="1305" spans="1:7" x14ac:dyDescent="0.25">
@@ -42845,8 +42845,8 @@
       <c r="C1311" s="6">
         <v>46275</v>
       </c>
-      <c r="D1311" s="7">
-        <v>3.953883</v>
+      <c r="D1311" s="11">
+        <v>3.95957</v>
       </c>
       <c r="E1311" s="8">
         <v>11368129</v>
@@ -42855,7 +42855,7 @@
         <v>666</v>
       </c>
       <c r="G1311" s="8">
-        <v>44948254.81</v>
+        <v>45012907.85</v>
       </c>
     </row>
     <row r="1312" spans="1:7" x14ac:dyDescent="0.25">
@@ -42868,8 +42868,8 @@
       <c r="C1312" s="6">
         <v>46275</v>
       </c>
-      <c r="D1312" s="7">
-        <v>5.166419</v>
+      <c r="D1312" s="11">
+        <v>5.17901</v>
       </c>
       <c r="E1312" s="8">
         <v>3813000</v>
@@ -42878,7 +42878,7 @@
         <v>228</v>
       </c>
       <c r="G1312" s="8">
-        <v>19699553.86</v>
+        <v>19747564.77</v>
       </c>
     </row>
     <row r="1313" spans="1:7" x14ac:dyDescent="0.25">
@@ -42984,7 +42984,7 @@
         <v>46275</v>
       </c>
       <c r="D1317" s="7">
-        <v>13.132947</v>
+        <v>13.128453</v>
       </c>
       <c r="E1317" s="8">
         <v>357107319</v>
@@ -42993,7 +42993,7 @@
         <v>11125</v>
       </c>
       <c r="G1317" s="8">
-        <v>4689871617.24</v>
+        <v>4688266679.14</v>
       </c>
     </row>
     <row r="1318" spans="1:7" x14ac:dyDescent="0.25">
@@ -43168,7 +43168,7 @@
         <v>46275</v>
       </c>
       <c r="D1325" s="7">
-        <v>3.159351</v>
+        <v>3.158617</v>
       </c>
       <c r="E1325" s="8">
         <v>43512614</v>
@@ -43177,7 +43177,7 @@
         <v>5480</v>
       </c>
       <c r="G1325" s="8">
-        <v>137471614.48</v>
+        <v>137439699.88</v>
       </c>
     </row>
     <row r="1326" spans="1:7" x14ac:dyDescent="0.25">
@@ -43191,7 +43191,7 @@
         <v>46275</v>
       </c>
       <c r="D1326" s="7">
-        <v>5.173609</v>
+        <v>5.179219</v>
       </c>
       <c r="E1326" s="8">
         <v>69782465</v>
@@ -43200,7 +43200,7 @@
         <v>488</v>
       </c>
       <c r="G1326" s="8">
-        <v>361027160.64</v>
+        <v>361418639.27</v>
       </c>
     </row>
     <row r="1327" spans="1:7" x14ac:dyDescent="0.25">
@@ -43384,7 +43384,7 @@
         <v>682</v>
       </c>
       <c r="G1334" s="8">
-        <v>32213020.7</v>
+        <v>32213024.8</v>
       </c>
     </row>
     <row r="1335" spans="1:7" x14ac:dyDescent="0.25">
@@ -43581,17 +43581,17 @@
       <c r="C1343" s="6">
         <v>46275</v>
       </c>
-      <c r="D1343" s="8">
-        <v>0</v>
+      <c r="D1343" s="7">
+        <v>3.308039</v>
       </c>
       <c r="E1343" s="8">
-        <v>0</v>
+        <v>135124827</v>
       </c>
       <c r="F1343" s="9">
         <v>1020</v>
       </c>
       <c r="G1343" s="8">
-        <v>0</v>
+        <v>446998203.81</v>
       </c>
     </row>
     <row r="1344" spans="1:7" x14ac:dyDescent="0.25">
@@ -43811,17 +43811,17 @@
       <c r="C1353" s="6">
         <v>46275</v>
       </c>
-      <c r="D1353" s="8">
-        <v>0</v>
+      <c r="D1353" s="11">
+        <v>113.42047</v>
       </c>
       <c r="E1353" s="8">
-        <v>0</v>
+        <v>41339249</v>
       </c>
       <c r="F1353" s="9">
         <v>17</v>
       </c>
       <c r="G1353" s="8">
-        <v>0</v>
+        <v>4688717069.78</v>
       </c>
     </row>
     <row r="1354" spans="1:7" x14ac:dyDescent="0.25">
@@ -43950,7 +43950,7 @@
         <v>46275</v>
       </c>
       <c r="D1359" s="7">
-        <v>7.466566</v>
+        <v>7.467626</v>
       </c>
       <c r="E1359" s="8">
         <v>440412704</v>
@@ -43959,7 +43959,7 @@
         <v>21682</v>
       </c>
       <c r="G1359" s="8">
-        <v>3288370314.15</v>
+        <v>3288837446.05</v>
       </c>
     </row>
     <row r="1360" spans="1:7" x14ac:dyDescent="0.25">
@@ -44157,7 +44157,7 @@
         <v>46275</v>
       </c>
       <c r="D1368" s="7">
-        <v>3.600568</v>
+        <v>3.601637</v>
       </c>
       <c r="E1368" s="8">
         <v>237188038</v>
@@ -44166,7 +44166,7 @@
         <v>3191</v>
       </c>
       <c r="G1368" s="8">
-        <v>854011557.86</v>
+        <v>854265160.9</v>
       </c>
     </row>
     <row r="1369" spans="1:7" x14ac:dyDescent="0.25">
@@ -44571,7 +44571,7 @@
         <v>46275</v>
       </c>
       <c r="D1386" s="7">
-        <v>2.377832</v>
+        <v>2.386756</v>
       </c>
       <c r="E1386" s="8">
         <v>46614504</v>
@@ -44580,7 +44580,7 @@
         <v>680</v>
       </c>
       <c r="G1386" s="8">
-        <v>110841451.98</v>
+        <v>111257454.85</v>
       </c>
     </row>
     <row r="1387" spans="1:7" x14ac:dyDescent="0.25">
@@ -45008,7 +45008,7 @@
         <v>46275</v>
       </c>
       <c r="D1405" s="7">
-        <v>2.411658</v>
+        <v>2.419028</v>
       </c>
       <c r="E1405" s="8">
         <v>32490415</v>
@@ -45017,7 +45017,7 @@
         <v>286</v>
       </c>
       <c r="G1405" s="8">
-        <v>78355775.77</v>
+        <v>78595229.58</v>
       </c>
     </row>
     <row r="1406" spans="1:7" x14ac:dyDescent="0.25">
@@ -45031,7 +45031,7 @@
         <v>46275</v>
       </c>
       <c r="D1406" s="7">
-        <v>2.891989</v>
+        <v>2.895845</v>
       </c>
       <c r="E1406" s="8">
         <v>5293492</v>
@@ -45040,7 +45040,7 @@
         <v>89</v>
       </c>
       <c r="G1406" s="8">
-        <v>15308721.7</v>
+        <v>15329133.62</v>
       </c>
     </row>
     <row r="1407" spans="1:7" x14ac:dyDescent="0.25">
@@ -45168,17 +45168,17 @@
       <c r="C1412" s="6">
         <v>46275</v>
       </c>
-      <c r="D1412" s="8">
-        <v>0</v>
+      <c r="D1412" s="7">
+        <v>1.049772</v>
       </c>
       <c r="E1412" s="8">
-        <v>0</v>
+        <v>1899265544</v>
       </c>
       <c r="F1412" s="9">
         <v>59098</v>
       </c>
       <c r="G1412" s="8">
-        <v>0</v>
+        <v>1993795290.76</v>
       </c>
     </row>
     <row r="1413" spans="1:7" x14ac:dyDescent="0.25">
@@ -45353,7 +45353,7 @@
         <v>46275</v>
       </c>
       <c r="D1420" s="7">
-        <v>3.982998</v>
+        <v>3.986959</v>
       </c>
       <c r="E1420" s="8">
         <v>109912488</v>
@@ -45362,7 +45362,7 @@
         <v>7879</v>
       </c>
       <c r="G1420" s="8">
-        <v>437781222.69</v>
+        <v>438216627.31</v>
       </c>
     </row>
     <row r="1421" spans="1:7" x14ac:dyDescent="0.25">
@@ -45789,17 +45789,17 @@
       <c r="C1439" s="6">
         <v>46275</v>
       </c>
-      <c r="D1439" s="8">
-        <v>0</v>
+      <c r="D1439" s="7">
+        <v>1.301939</v>
       </c>
       <c r="E1439" s="8">
-        <v>0</v>
+        <v>544354</v>
       </c>
       <c r="F1439" s="9">
         <v>123</v>
       </c>
       <c r="G1439" s="8">
-        <v>0</v>
+        <v>708715.84</v>
       </c>
     </row>
     <row r="1440" spans="1:7" x14ac:dyDescent="0.25">
@@ -45927,17 +45927,17 @@
       <c r="C1445" s="6">
         <v>46275</v>
       </c>
-      <c r="D1445" s="8">
-        <v>0</v>
+      <c r="D1445" s="7">
+        <v>1.271161</v>
       </c>
       <c r="E1445" s="8">
-        <v>0</v>
+        <v>15030977087</v>
       </c>
       <c r="F1445" s="9">
         <v>20814</v>
       </c>
       <c r="G1445" s="8">
-        <v>0</v>
+        <v>19106793297.37</v>
       </c>
     </row>
     <row r="1446" spans="1:7" x14ac:dyDescent="0.25">
@@ -46755,17 +46755,17 @@
       <c r="C1481" s="6">
         <v>46275</v>
       </c>
-      <c r="D1481" s="8">
-        <v>0</v>
+      <c r="D1481" s="7">
+        <v>3.258552</v>
       </c>
       <c r="E1481" s="8">
-        <v>0</v>
+        <v>15042977167</v>
       </c>
       <c r="F1481" s="9">
         <v>41145</v>
       </c>
       <c r="G1481" s="8">
-        <v>0</v>
+        <v>49018328570.19</v>
       </c>
     </row>
     <row r="1482" spans="1:7" x14ac:dyDescent="0.25">
@@ -47837,7 +47837,7 @@
         <v>46275</v>
       </c>
       <c r="D1528" s="7">
-        <v>1.908177</v>
+        <v>1.908022</v>
       </c>
       <c r="E1528" s="8">
         <v>127132822</v>
@@ -47846,7 +47846,7 @@
         <v>814</v>
       </c>
       <c r="G1528" s="8">
-        <v>242591896.43</v>
+        <v>242572217.52</v>
       </c>
     </row>
     <row r="1529" spans="1:7" x14ac:dyDescent="0.25">
@@ -47929,7 +47929,7 @@
         <v>46275</v>
       </c>
       <c r="D1532" s="7">
-        <v>5.472299</v>
+        <v>6.717069</v>
       </c>
       <c r="E1532" s="8">
         <v>204957706</v>
@@ -47938,7 +47938,7 @@
         <v>2911</v>
       </c>
       <c r="G1532" s="8">
-        <v>1121589947.81</v>
+        <v>1376715056.24</v>
       </c>
     </row>
     <row r="1533" spans="1:7" x14ac:dyDescent="0.25">
@@ -48274,7 +48274,7 @@
         <v>46275</v>
       </c>
       <c r="D1547" s="7">
-        <v>1.165723</v>
+        <v>1.166447</v>
       </c>
       <c r="E1547" s="8">
         <v>33113989</v>
@@ -48283,7 +48283,7 @@
         <v>533</v>
       </c>
       <c r="G1547" s="8">
-        <v>38601737.98</v>
+        <v>38625703.62</v>
       </c>
     </row>
     <row r="1548" spans="1:7" x14ac:dyDescent="0.25">
@@ -48297,7 +48297,7 @@
         <v>46275</v>
       </c>
       <c r="D1548" s="7">
-        <v>1.166864</v>
+        <v>1.163286</v>
       </c>
       <c r="E1548" s="8">
         <v>23086875</v>
@@ -48306,7 +48306,7 @@
         <v>127</v>
       </c>
       <c r="G1548" s="8">
-        <v>26939236.02</v>
+        <v>26856644.28</v>
       </c>
     </row>
     <row r="1549" spans="1:7" x14ac:dyDescent="0.25">
@@ -48319,8 +48319,8 @@
       <c r="C1549" s="6">
         <v>46275</v>
       </c>
-      <c r="D1549" s="11">
-        <v>1.15089</v>
+      <c r="D1549" s="7">
+        <v>1.157228</v>
       </c>
       <c r="E1549" s="8">
         <v>31804605</v>
@@ -48329,7 +48329,7 @@
         <v>25</v>
       </c>
       <c r="G1549" s="8">
-        <v>36603587.21</v>
+        <v>36805170.64</v>
       </c>
     </row>
     <row r="1550" spans="1:7" x14ac:dyDescent="0.25">
@@ -48388,8 +48388,8 @@
       <c r="C1552" s="6">
         <v>46275</v>
       </c>
-      <c r="D1552" s="7">
-        <v>7.464518</v>
+      <c r="D1552" s="11">
+        <v>7.46447</v>
       </c>
       <c r="E1552" s="8">
         <v>105884613</v>
@@ -48398,7 +48398,7 @@
         <v>1460</v>
       </c>
       <c r="G1552" s="8">
-        <v>790377645.53</v>
+        <v>790372519.8</v>
       </c>
     </row>
     <row r="1553" spans="1:7" x14ac:dyDescent="0.25">
@@ -48458,7 +48458,7 @@
         <v>46275</v>
       </c>
       <c r="D1555" s="7">
-        <v>5.584871</v>
+        <v>5.581656</v>
       </c>
       <c r="E1555" s="8">
         <v>98154521</v>
@@ -48467,7 +48467,7 @@
         <v>3530</v>
       </c>
       <c r="G1555" s="8">
-        <v>548180308.24</v>
+        <v>547864728.37</v>
       </c>
     </row>
     <row r="1556" spans="1:7" x14ac:dyDescent="0.25">
@@ -48757,7 +48757,7 @@
         <v>46275</v>
       </c>
       <c r="D1568" s="7">
-        <v>14.754977</v>
+        <v>14.754966</v>
       </c>
       <c r="E1568" s="8">
         <v>17518229</v>
@@ -48766,7 +48766,7 @@
         <v>1801</v>
       </c>
       <c r="G1568" s="8">
-        <v>258481057.62</v>
+        <v>258480881.62</v>
       </c>
     </row>
     <row r="1569" spans="1:7" x14ac:dyDescent="0.25">
@@ -48872,7 +48872,7 @@
         <v>46275</v>
       </c>
       <c r="D1573" s="7">
-        <v>1.759531</v>
+        <v>1.766557</v>
       </c>
       <c r="E1573" s="8">
         <v>70047587</v>
@@ -48881,7 +48881,7 @@
         <v>15</v>
       </c>
       <c r="G1573" s="8">
-        <v>123250867.3</v>
+        <v>123743066.84</v>
       </c>
     </row>
     <row r="1574" spans="1:7" x14ac:dyDescent="0.25">
@@ -49010,7 +49010,7 @@
         <v>46275</v>
       </c>
       <c r="D1579" s="7">
-        <v>5.254117</v>
+        <v>5.254093</v>
       </c>
       <c r="E1579" s="8">
         <v>235881734</v>
@@ -49019,7 +49019,7 @@
         <v>173</v>
       </c>
       <c r="G1579" s="8">
-        <v>1239350164.18</v>
+        <v>1239344525.62</v>
       </c>
     </row>
     <row r="1580" spans="1:7" x14ac:dyDescent="0.25">
@@ -49079,7 +49079,7 @@
         <v>46275</v>
       </c>
       <c r="D1582" s="7">
-        <v>1.532778</v>
+        <v>1.532775</v>
       </c>
       <c r="E1582" s="8">
         <v>815639647</v>
@@ -49088,7 +49088,7 @@
         <v>179</v>
       </c>
       <c r="G1582" s="8">
-        <v>1250194731.1</v>
+        <v>1250192168.07</v>
       </c>
     </row>
     <row r="1583" spans="1:7" x14ac:dyDescent="0.25">
@@ -49309,7 +49309,7 @@
         <v>46275</v>
       </c>
       <c r="D1592" s="7">
-        <v>5.891758</v>
+        <v>5.892009</v>
       </c>
       <c r="E1592" s="8">
         <v>43044104</v>
@@ -49318,7 +49318,7 @@
         <v>4765</v>
       </c>
       <c r="G1592" s="8">
-        <v>253605425</v>
+        <v>253616228.8</v>
       </c>
     </row>
     <row r="1593" spans="1:7" x14ac:dyDescent="0.25">
@@ -49492,17 +49492,17 @@
       <c r="C1600" s="6">
         <v>46275</v>
       </c>
-      <c r="D1600" s="8">
-        <v>0</v>
+      <c r="D1600" s="7">
+        <v>1.249372</v>
       </c>
       <c r="E1600" s="8">
-        <v>0</v>
+        <v>300623899</v>
       </c>
       <c r="F1600" s="9">
         <v>1</v>
       </c>
       <c r="G1600" s="8">
-        <v>0</v>
+        <v>375590953.31</v>
       </c>
     </row>
     <row r="1601" spans="1:7" x14ac:dyDescent="0.25">
@@ -49722,17 +49722,17 @@
       <c r="C1610" s="6">
         <v>46275</v>
       </c>
-      <c r="D1610" s="8">
-        <v>0</v>
+      <c r="D1610" s="7">
+        <v>1.835093</v>
       </c>
       <c r="E1610" s="8">
-        <v>0</v>
+        <v>192062359</v>
       </c>
       <c r="F1610" s="9">
         <v>612</v>
       </c>
       <c r="G1610" s="8">
-        <v>0</v>
+        <v>352452322.82</v>
       </c>
     </row>
     <row r="1611" spans="1:7" x14ac:dyDescent="0.25">
@@ -49837,17 +49837,17 @@
       <c r="C1615" s="6">
         <v>46275</v>
       </c>
-      <c r="D1615" s="8">
-        <v>0</v>
+      <c r="D1615" s="7">
+        <v>1.036007</v>
       </c>
       <c r="E1615" s="8">
-        <v>0</v>
+        <v>48309234</v>
       </c>
       <c r="F1615" s="9">
         <v>181</v>
       </c>
       <c r="G1615" s="8">
-        <v>0</v>
+        <v>50048717.03</v>
       </c>
     </row>
     <row r="1616" spans="1:7" x14ac:dyDescent="0.25">
@@ -49953,7 +49953,7 @@
         <v>46275</v>
       </c>
       <c r="D1620" s="7">
-        <v>1.433636</v>
+        <v>1.436513</v>
       </c>
       <c r="E1620" s="8">
         <v>22294908</v>
@@ -49962,7 +49962,7 @@
         <v>82</v>
       </c>
       <c r="G1620" s="8">
-        <v>31962789.57</v>
+        <v>32026933.58</v>
       </c>
     </row>
     <row r="1621" spans="1:7" x14ac:dyDescent="0.25">
@@ -49976,7 +49976,7 @@
         <v>46275</v>
       </c>
       <c r="D1621" s="7">
-        <v>0.988464</v>
+        <v>0.979078</v>
       </c>
       <c r="E1621" s="8">
         <v>200496272</v>
@@ -49985,7 +49985,7 @@
         <v>79</v>
       </c>
       <c r="G1621" s="8">
-        <v>198183382.47</v>
+        <v>196301559.24</v>
       </c>
     </row>
     <row r="1622" spans="1:7" x14ac:dyDescent="0.25">
@@ -49998,17 +49998,17 @@
       <c r="C1622" s="6">
         <v>46275</v>
       </c>
-      <c r="D1622" s="8">
-        <v>0</v>
+      <c r="D1622" s="7">
+        <v>1.968875</v>
       </c>
       <c r="E1622" s="8">
-        <v>0</v>
+        <v>96250289</v>
       </c>
       <c r="F1622" s="9">
         <v>2718</v>
       </c>
       <c r="G1622" s="8">
-        <v>0</v>
+        <v>189504762.74</v>
       </c>
     </row>
     <row r="1623" spans="1:7" x14ac:dyDescent="0.25">
@@ -50090,17 +50090,17 @@
       <c r="C1626" s="6">
         <v>46275</v>
       </c>
-      <c r="D1626" s="8">
-        <v>0</v>
+      <c r="D1626" s="7">
+        <v>1.435929</v>
       </c>
       <c r="E1626" s="8">
-        <v>0</v>
+        <v>201555876</v>
       </c>
       <c r="F1626" s="9">
         <v>27</v>
       </c>
       <c r="G1626" s="8">
-        <v>0</v>
+        <v>289420007.33</v>
       </c>
     </row>
     <row r="1627" spans="1:7" x14ac:dyDescent="0.25">
@@ -50113,17 +50113,17 @@
       <c r="C1627" s="6">
         <v>46275</v>
       </c>
-      <c r="D1627" s="8">
-        <v>0</v>
+      <c r="D1627" s="10">
+        <v>0.9312</v>
       </c>
       <c r="E1627" s="8">
-        <v>0</v>
+        <v>1072723</v>
       </c>
       <c r="F1627" s="9">
         <v>5</v>
       </c>
       <c r="G1627" s="8">
-        <v>0</v>
+        <v>998919.83</v>
       </c>
     </row>
     <row r="1628" spans="1:7" x14ac:dyDescent="0.25">
@@ -50136,17 +50136,17 @@
       <c r="C1628" s="6">
         <v>46275</v>
       </c>
-      <c r="D1628" s="8">
-        <v>0</v>
+      <c r="D1628" s="7">
+        <v>0.282108</v>
       </c>
       <c r="E1628" s="8">
-        <v>0</v>
+        <v>238794293</v>
       </c>
       <c r="F1628" s="9">
         <v>14</v>
       </c>
       <c r="G1628" s="8">
-        <v>0</v>
+        <v>67365752.99</v>
       </c>
     </row>
     <row r="1629" spans="1:7" x14ac:dyDescent="0.25">
@@ -50596,17 +50596,17 @@
       <c r="C1648" s="6">
         <v>46275</v>
       </c>
-      <c r="D1648" s="7">
-        <v>2.218581</v>
+      <c r="D1648" s="11">
+        <v>2.22965</v>
       </c>
       <c r="E1648" s="8">
-        <v>44405806</v>
+        <v>44413612</v>
       </c>
       <c r="F1648" s="9">
         <v>902</v>
       </c>
       <c r="G1648" s="8">
-        <v>98517886.43</v>
+        <v>99026789.92</v>
       </c>
     </row>
     <row r="1649" spans="1:7" x14ac:dyDescent="0.25">
@@ -50781,7 +50781,7 @@
         <v>46275</v>
       </c>
       <c r="D1656" s="7">
-        <v>1.758116</v>
+        <v>1.757825</v>
       </c>
       <c r="E1656" s="8">
         <v>27675341</v>
@@ -50790,7 +50790,7 @@
         <v>586</v>
       </c>
       <c r="G1656" s="8">
-        <v>48656448.27</v>
+        <v>48648418.37</v>
       </c>
     </row>
     <row r="1657" spans="1:7" x14ac:dyDescent="0.25">
@@ -51333,7 +51333,7 @@
         <v>46275</v>
       </c>
       <c r="D1680" s="7">
-        <v>2.600115</v>
+        <v>2.600646</v>
       </c>
       <c r="E1680" s="8">
         <v>53501390</v>
@@ -51342,7 +51342,7 @@
         <v>6734</v>
       </c>
       <c r="G1680" s="8">
-        <v>139109754.38</v>
+        <v>139138192.82</v>
       </c>
     </row>
     <row r="1681" spans="1:7" x14ac:dyDescent="0.25">
@@ -51562,17 +51562,17 @@
       <c r="C1690" s="6">
         <v>46275</v>
       </c>
-      <c r="D1690" s="8">
-        <v>0</v>
+      <c r="D1690" s="7">
+        <v>49.490517</v>
       </c>
       <c r="E1690" s="8">
-        <v>0</v>
+        <v>29546752</v>
       </c>
       <c r="F1690" s="9">
         <v>11629</v>
       </c>
       <c r="G1690" s="8">
-        <v>0</v>
+        <v>1462284035.93</v>
       </c>
     </row>
     <row r="1691" spans="1:7" x14ac:dyDescent="0.25">
@@ -51585,17 +51585,17 @@
       <c r="C1691" s="6">
         <v>46275</v>
       </c>
-      <c r="D1691" s="8">
-        <v>0</v>
+      <c r="D1691" s="7">
+        <v>4.642423</v>
       </c>
       <c r="E1691" s="8">
-        <v>0</v>
+        <v>691429409</v>
       </c>
       <c r="F1691" s="9">
         <v>2775</v>
       </c>
       <c r="G1691" s="8">
-        <v>0</v>
+        <v>3209907921.03</v>
       </c>
     </row>
     <row r="1692" spans="1:7" x14ac:dyDescent="0.25">
@@ -51792,8 +51792,8 @@
       <c r="C1700" s="6">
         <v>46275</v>
       </c>
-      <c r="D1700" s="7">
-        <v>2.795472</v>
+      <c r="D1700" s="11">
+        <v>2.79629</v>
       </c>
       <c r="E1700" s="8">
         <v>262616535</v>
@@ -51802,7 +51802,7 @@
         <v>1313</v>
       </c>
       <c r="G1700" s="8">
-        <v>734137139.64</v>
+        <v>734351995.49</v>
       </c>
     </row>
     <row r="1701" spans="1:7" x14ac:dyDescent="0.25">
@@ -51839,7 +51839,7 @@
         <v>46275</v>
       </c>
       <c r="D1702" s="7">
-        <v>44.049337</v>
+        <v>44.049203</v>
       </c>
       <c r="E1702" s="8">
         <v>30625518</v>
@@ -51848,7 +51848,7 @@
         <v>9007</v>
       </c>
       <c r="G1702" s="8">
-        <v>1349033768.21</v>
+        <v>1349029665.31</v>
       </c>
     </row>
     <row r="1703" spans="1:7" x14ac:dyDescent="0.25">
@@ -52078,7 +52078,7 @@
         <v>172380</v>
       </c>
       <c r="G1712" s="8">
-        <v>120844028800.75</v>
+        <v>120844028801.08</v>
       </c>
     </row>
     <row r="1713" spans="1:7" x14ac:dyDescent="0.25">
@@ -52206,17 +52206,17 @@
       <c r="C1718" s="6">
         <v>46275</v>
       </c>
-      <c r="D1718" s="8">
-        <v>0</v>
+      <c r="D1718" s="7">
+        <v>48.318239</v>
       </c>
       <c r="E1718" s="8">
-        <v>0</v>
+        <v>45111410</v>
       </c>
       <c r="F1718" s="9">
         <v>16</v>
       </c>
       <c r="G1718" s="8">
-        <v>0</v>
+        <v>2179703908.31</v>
       </c>
     </row>
     <row r="1719" spans="1:7" x14ac:dyDescent="0.25">
@@ -52482,17 +52482,17 @@
       <c r="C1730" s="6">
         <v>46275</v>
       </c>
-      <c r="D1730" s="8">
-        <v>0</v>
+      <c r="D1730" s="7">
+        <v>5.424055</v>
       </c>
       <c r="E1730" s="8">
-        <v>0</v>
+        <v>10092337</v>
       </c>
       <c r="F1730" s="9">
         <v>540</v>
       </c>
       <c r="G1730" s="8">
-        <v>0</v>
+        <v>54741387.24</v>
       </c>
     </row>
     <row r="1731" spans="1:7" x14ac:dyDescent="0.25">
@@ -52505,17 +52505,17 @@
       <c r="C1731" s="6">
         <v>46275</v>
       </c>
-      <c r="D1731" s="8">
-        <v>0</v>
+      <c r="D1731" s="11">
+        <v>6.63821</v>
       </c>
       <c r="E1731" s="8">
-        <v>0</v>
+        <v>77062027</v>
       </c>
       <c r="F1731" s="9">
         <v>898</v>
       </c>
       <c r="G1731" s="8">
-        <v>0</v>
+        <v>511553946.11</v>
       </c>
     </row>
     <row r="1732" spans="1:7" x14ac:dyDescent="0.25">
@@ -53011,8 +53011,8 @@
       <c r="C1753" s="6">
         <v>46275</v>
       </c>
-      <c r="D1753" s="7">
-        <v>1.454288</v>
+      <c r="D1753" s="11">
+        <v>1.45633</v>
       </c>
       <c r="E1753" s="8">
         <v>38869838</v>
@@ -53021,7 +53021,7 @@
         <v>94</v>
       </c>
       <c r="G1753" s="8">
-        <v>56527930.89</v>
+        <v>56607325.22</v>
       </c>
     </row>
     <row r="1754" spans="1:7" x14ac:dyDescent="0.25">
@@ -53034,17 +53034,17 @@
       <c r="C1754" s="6">
         <v>46275</v>
       </c>
-      <c r="D1754" s="8">
-        <v>0</v>
+      <c r="D1754" s="7">
+        <v>11.051013</v>
       </c>
       <c r="E1754" s="8">
-        <v>0</v>
+        <v>4007313208</v>
       </c>
       <c r="F1754" s="9">
         <v>15449</v>
       </c>
       <c r="G1754" s="8">
-        <v>0</v>
+        <v>44284871642.92</v>
       </c>
     </row>
     <row r="1755" spans="1:7" x14ac:dyDescent="0.25">
@@ -53265,16 +53265,16 @@
         <v>46275</v>
       </c>
       <c r="D1764" s="7">
-        <v>60.010702</v>
+        <v>60.011313</v>
       </c>
       <c r="E1764" s="8">
-        <v>405031727</v>
+        <v>405030727</v>
       </c>
       <c r="F1764" s="9">
         <v>6919</v>
       </c>
       <c r="G1764" s="8">
-        <v>24306238104.98</v>
+        <v>24306425909.4</v>
       </c>
     </row>
     <row r="1765" spans="1:7" x14ac:dyDescent="0.25">
@@ -53356,17 +53356,17 @@
       <c r="C1768" s="6">
         <v>46275</v>
       </c>
-      <c r="D1768" s="8">
-        <v>0</v>
+      <c r="D1768" s="7">
+        <v>13.704056</v>
       </c>
       <c r="E1768" s="8">
-        <v>0</v>
+        <v>437648671</v>
       </c>
       <c r="F1768" s="9">
         <v>12065</v>
       </c>
       <c r="G1768" s="8">
-        <v>0</v>
+        <v>5997561836.6</v>
       </c>
     </row>
     <row r="1769" spans="1:7" x14ac:dyDescent="0.25">
@@ -53504,7 +53504,7 @@
         <v>387</v>
       </c>
       <c r="G1774" s="8">
-        <v>1908446218.06</v>
+        <v>1908446217.88</v>
       </c>
     </row>
     <row r="1775" spans="1:7" x14ac:dyDescent="0.25">
@@ -53793,8 +53793,8 @@
       <c r="C1787" s="6">
         <v>46275</v>
       </c>
-      <c r="D1787" s="7">
-        <v>39.583528</v>
+      <c r="D1787" s="11">
+        <v>39.60631</v>
       </c>
       <c r="E1787" s="8">
         <v>7861238</v>
@@ -53803,7 +53803,7 @@
         <v>344</v>
       </c>
       <c r="G1787" s="8">
-        <v>311175536.09</v>
+        <v>311354627.33</v>
       </c>
     </row>
     <row r="1788" spans="1:7" x14ac:dyDescent="0.25">
@@ -53932,7 +53932,7 @@
         <v>46275</v>
       </c>
       <c r="D1793" s="7">
-        <v>1.150671</v>
+        <v>1.148481</v>
       </c>
       <c r="E1793" s="8">
         <v>199059645</v>
@@ -53941,7 +53941,7 @@
         <v>356</v>
       </c>
       <c r="G1793" s="8">
-        <v>229052235.74</v>
+        <v>228616127.57</v>
       </c>
     </row>
     <row r="1794" spans="1:7" x14ac:dyDescent="0.25">
@@ -53954,8 +53954,8 @@
       <c r="C1794" s="6">
         <v>46275</v>
       </c>
-      <c r="D1794" s="7">
-        <v>3.034345</v>
+      <c r="D1794" s="11">
+        <v>3.04258</v>
       </c>
       <c r="E1794" s="8">
         <v>3238429</v>
@@ -53964,7 +53964,7 @@
         <v>527</v>
       </c>
       <c r="G1794" s="8">
-        <v>9826509.38</v>
+        <v>9853179.49</v>
       </c>
     </row>
     <row r="1795" spans="1:7" x14ac:dyDescent="0.25">
@@ -54529,8 +54529,8 @@
       <c r="C1819" s="6">
         <v>46275</v>
       </c>
-      <c r="D1819" s="11">
-        <v>2.00262</v>
+      <c r="D1819" s="7">
+        <v>2.002841</v>
       </c>
       <c r="E1819" s="8">
         <v>332724286</v>
@@ -54539,7 +54539,7 @@
         <v>9004</v>
       </c>
       <c r="G1819" s="8">
-        <v>666320439.73</v>
+        <v>666393699.43</v>
       </c>
     </row>
     <row r="1820" spans="1:7" x14ac:dyDescent="0.25">
@@ -54783,7 +54783,7 @@
         <v>46275</v>
       </c>
       <c r="D1830" s="7">
-        <v>9.411413</v>
+        <v>9.410514</v>
       </c>
       <c r="E1830" s="8">
         <v>35392468</v>
@@ -54792,7 +54792,7 @@
         <v>43</v>
       </c>
       <c r="G1830" s="8">
-        <v>333093148.17</v>
+        <v>333061329.14</v>
       </c>
     </row>
     <row r="1831" spans="1:7" x14ac:dyDescent="0.25">
@@ -54920,17 +54920,17 @@
       <c r="C1836" s="6">
         <v>46275</v>
       </c>
-      <c r="D1836" s="8">
-        <v>0</v>
+      <c r="D1836" s="7">
+        <v>1.018667</v>
       </c>
       <c r="E1836" s="8">
-        <v>0</v>
+        <v>403155180</v>
       </c>
       <c r="F1836" s="9">
         <v>8484</v>
       </c>
       <c r="G1836" s="8">
-        <v>0</v>
+        <v>410680678.01</v>
       </c>
     </row>
     <row r="1837" spans="1:7" x14ac:dyDescent="0.25">
@@ -54966,17 +54966,17 @@
       <c r="C1838" s="6">
         <v>46275</v>
       </c>
-      <c r="D1838" s="8">
-        <v>0</v>
+      <c r="D1838" s="7">
+        <v>1.023221</v>
       </c>
       <c r="E1838" s="8">
-        <v>0</v>
+        <v>14960632</v>
       </c>
       <c r="F1838" s="9">
         <v>542</v>
       </c>
       <c r="G1838" s="8">
-        <v>0</v>
+        <v>15308038.9</v>
       </c>
     </row>
     <row r="1839" spans="1:7" x14ac:dyDescent="0.25">
@@ -55242,17 +55242,17 @@
       <c r="C1850" s="6">
         <v>46275</v>
       </c>
-      <c r="D1850" s="8">
-        <v>0</v>
+      <c r="D1850" s="11">
+        <v>1.00293</v>
       </c>
       <c r="E1850" s="8">
-        <v>0</v>
+        <v>6899169</v>
       </c>
       <c r="F1850" s="9">
         <v>70</v>
       </c>
       <c r="G1850" s="8">
-        <v>0</v>
+        <v>6919382.46</v>
       </c>
     </row>
     <row r="1851" spans="1:7" x14ac:dyDescent="0.25">
@@ -55265,17 +55265,17 @@
       <c r="C1851" s="6">
         <v>46275</v>
       </c>
-      <c r="D1851" s="8">
-        <v>0</v>
+      <c r="D1851" s="7">
+        <v>1.002695</v>
       </c>
       <c r="E1851" s="8">
-        <v>0</v>
+        <v>6775849</v>
       </c>
       <c r="F1851" s="9">
         <v>50</v>
       </c>
       <c r="G1851" s="8">
-        <v>0</v>
+        <v>6794109.07</v>
       </c>
     </row>
     <row r="1852" spans="1:7" x14ac:dyDescent="0.25">
@@ -55288,17 +55288,17 @@
       <c r="C1852" s="6">
         <v>46275</v>
       </c>
-      <c r="D1852" s="8">
-        <v>0</v>
+      <c r="D1852" s="7">
+        <v>1.037954</v>
       </c>
       <c r="E1852" s="8">
-        <v>0</v>
+        <v>27920218</v>
       </c>
       <c r="F1852" s="9">
         <v>513</v>
       </c>
       <c r="G1852" s="8">
-        <v>0</v>
+        <v>28979897.68</v>
       </c>
     </row>
     <row r="1853" spans="1:7" x14ac:dyDescent="0.25">
@@ -55449,17 +55449,17 @@
       <c r="C1859" s="6">
         <v>46275</v>
       </c>
-      <c r="D1859" s="8">
-        <v>0</v>
+      <c r="D1859" s="7">
+        <v>15.019087</v>
       </c>
       <c r="E1859" s="8">
-        <v>0</v>
+        <v>367497148</v>
       </c>
       <c r="F1859" s="9">
         <v>9787</v>
       </c>
       <c r="G1859" s="8">
-        <v>0</v>
+        <v>5519471547.59</v>
       </c>
     </row>
     <row r="1860" spans="1:7" x14ac:dyDescent="0.25">
@@ -55518,17 +55518,17 @@
       <c r="C1862" s="6">
         <v>46275</v>
       </c>
-      <c r="D1862" s="8">
-        <v>0</v>
+      <c r="D1862" s="11">
+        <v>14.84166</v>
       </c>
       <c r="E1862" s="8">
-        <v>0</v>
+        <v>126848963</v>
       </c>
       <c r="F1862" s="9">
         <v>3597</v>
       </c>
       <c r="G1862" s="8">
-        <v>0</v>
+        <v>1882649201.71</v>
       </c>
     </row>
     <row r="1863" spans="1:7" x14ac:dyDescent="0.25">
@@ -55771,17 +55771,17 @@
       <c r="C1873" s="6">
         <v>46275</v>
       </c>
-      <c r="D1873" s="8">
-        <v>0</v>
+      <c r="D1873" s="11">
+        <v>2.74688</v>
       </c>
       <c r="E1873" s="8">
-        <v>0</v>
+        <v>39643052</v>
       </c>
       <c r="F1873" s="9">
         <v>113</v>
       </c>
       <c r="G1873" s="8">
-        <v>0</v>
+        <v>108894721.28</v>
       </c>
     </row>
     <row r="1874" spans="1:7" x14ac:dyDescent="0.25">
@@ -55863,17 +55863,17 @@
       <c r="C1877" s="6">
         <v>46275</v>
       </c>
-      <c r="D1877" s="8">
-        <v>0</v>
+      <c r="D1877" s="7">
+        <v>4.172583</v>
       </c>
       <c r="E1877" s="8">
-        <v>0</v>
+        <v>90817863</v>
       </c>
       <c r="F1877" s="9">
         <v>276</v>
       </c>
       <c r="G1877" s="8">
-        <v>0</v>
+        <v>378945025.96</v>
       </c>
     </row>
     <row r="1878" spans="1:7" x14ac:dyDescent="0.25">
@@ -56438,17 +56438,17 @@
       <c r="C1902" s="6">
         <v>46275</v>
       </c>
-      <c r="D1902" s="8">
-        <v>0</v>
+      <c r="D1902" s="7">
+        <v>5.784088</v>
       </c>
       <c r="E1902" s="8">
-        <v>0</v>
+        <v>178530455</v>
       </c>
       <c r="F1902" s="9">
         <v>14100</v>
       </c>
       <c r="G1902" s="8">
-        <v>0</v>
+        <v>1032635784.4</v>
       </c>
     </row>
     <row r="1903" spans="1:7" x14ac:dyDescent="0.25">
@@ -56783,17 +56783,17 @@
       <c r="C1917" s="6">
         <v>46275</v>
       </c>
-      <c r="D1917" s="8">
-        <v>0</v>
+      <c r="D1917" s="11">
+        <v>1.04571</v>
       </c>
       <c r="E1917" s="8">
-        <v>0</v>
+        <v>955120</v>
       </c>
       <c r="F1917" s="9">
         <v>281</v>
       </c>
       <c r="G1917" s="8">
-        <v>0</v>
+        <v>998778.39</v>
       </c>
     </row>
     <row r="1918" spans="1:7" x14ac:dyDescent="0.25">
@@ -57266,17 +57266,17 @@
       <c r="C1938" s="6">
         <v>46275</v>
       </c>
-      <c r="D1938" s="8">
-        <v>0</v>
+      <c r="D1938" s="7">
+        <v>8.112434</v>
       </c>
       <c r="E1938" s="8">
-        <v>0</v>
+        <v>690045545</v>
       </c>
       <c r="F1938" s="9">
         <v>3329</v>
       </c>
       <c r="G1938" s="8">
-        <v>0</v>
+        <v>5597948860.78</v>
       </c>
     </row>
     <row r="1939" spans="1:7" x14ac:dyDescent="0.25">
@@ -57427,17 +57427,17 @@
       <c r="C1945" s="6">
         <v>46275</v>
       </c>
-      <c r="D1945" s="8">
-        <v>0</v>
+      <c r="D1945" s="7">
+        <v>0.990851</v>
       </c>
       <c r="E1945" s="8">
-        <v>0</v>
+        <v>1848182611</v>
       </c>
       <c r="F1945" s="9">
         <v>15007</v>
       </c>
       <c r="G1945" s="8">
-        <v>0</v>
+        <v>1831273185.61</v>
       </c>
     </row>
     <row r="1946" spans="1:7" x14ac:dyDescent="0.25">
@@ -57887,17 +57887,17 @@
       <c r="C1965" s="6">
         <v>46275</v>
       </c>
-      <c r="D1965" s="8">
-        <v>0</v>
+      <c r="D1965" s="7">
+        <v>13.641141</v>
       </c>
       <c r="E1965" s="8">
-        <v>0</v>
+        <v>816811035</v>
       </c>
       <c r="F1965" s="9">
         <v>60092</v>
       </c>
       <c r="G1965" s="8">
-        <v>0</v>
+        <v>11142234571.67</v>
       </c>
     </row>
     <row r="1966" spans="1:7" x14ac:dyDescent="0.25">
@@ -58439,8 +58439,8 @@
       <c r="C1989" s="6">
         <v>46275</v>
       </c>
-      <c r="D1989" s="11">
-        <v>4.18259</v>
+      <c r="D1989" s="7">
+        <v>4.183111</v>
       </c>
       <c r="E1989" s="8">
         <v>148782300</v>
@@ -58449,7 +58449,7 @@
         <v>6489</v>
       </c>
       <c r="G1989" s="8">
-        <v>622295401.96</v>
+        <v>622372912.65</v>
       </c>
     </row>
     <row r="1990" spans="1:7" x14ac:dyDescent="0.25">
@@ -58992,7 +58992,7 @@
         <v>46275</v>
       </c>
       <c r="D2013" s="7">
-        <v>1.909933</v>
+        <v>1.902482</v>
       </c>
       <c r="E2013" s="8">
         <v>306521428</v>
@@ -59001,7 +59001,7 @@
         <v>11</v>
       </c>
       <c r="G2013" s="8">
-        <v>585435353.99</v>
+        <v>583151499.83</v>
       </c>
     </row>
     <row r="2014" spans="1:7" x14ac:dyDescent="0.25">
@@ -59037,17 +59037,17 @@
       <c r="C2015" s="6">
         <v>46275</v>
       </c>
-      <c r="D2015" s="8">
-        <v>0</v>
+      <c r="D2015" s="7">
+        <v>5.945138</v>
       </c>
       <c r="E2015" s="8">
-        <v>0</v>
+        <v>106786382</v>
       </c>
       <c r="F2015" s="9">
         <v>1</v>
       </c>
       <c r="G2015" s="8">
-        <v>0</v>
+        <v>634859824.35</v>
       </c>
     </row>
     <row r="2016" spans="1:7" x14ac:dyDescent="0.25">
@@ -59199,7 +59199,7 @@
         <v>46275</v>
       </c>
       <c r="D2022" s="7">
-        <v>20.132342</v>
+        <v>20.133013</v>
       </c>
       <c r="E2022" s="8">
         <v>164932070</v>
@@ -59208,7 +59208,7 @@
         <v>2790</v>
       </c>
       <c r="G2022" s="8">
-        <v>3320468822.11</v>
+        <v>3320579498.95</v>
       </c>
     </row>
     <row r="2023" spans="1:7" x14ac:dyDescent="0.25">
@@ -59475,7 +59475,7 @@
         <v>46275</v>
       </c>
       <c r="D2034" s="7">
-        <v>12.499101</v>
+        <v>12.497879</v>
       </c>
       <c r="E2034" s="8">
         <v>216588410</v>
@@ -59484,7 +59484,7 @@
         <v>25</v>
       </c>
       <c r="G2034" s="8">
-        <v>2707160506.25</v>
+        <v>2706895734.48</v>
       </c>
     </row>
     <row r="2035" spans="1:7" x14ac:dyDescent="0.25">
@@ -59521,7 +59521,7 @@
         <v>46275</v>
       </c>
       <c r="D2036" s="7">
-        <v>4.457076</v>
+        <v>4.460085</v>
       </c>
       <c r="E2036" s="8">
         <v>11571700</v>
@@ -59530,7 +59530,7 @@
         <v>912</v>
       </c>
       <c r="G2036" s="8">
-        <v>51575947.14</v>
+        <v>51610766.33</v>
       </c>
     </row>
     <row r="2037" spans="1:7" x14ac:dyDescent="0.25">
@@ -59589,8 +59589,8 @@
       <c r="C2039" s="6">
         <v>46275</v>
       </c>
-      <c r="D2039" s="7">
-        <v>7.725263</v>
+      <c r="D2039" s="11">
+        <v>7.71736</v>
       </c>
       <c r="E2039" s="8">
         <v>274862095</v>
@@ -59599,7 +59599,7 @@
         <v>1</v>
       </c>
       <c r="G2039" s="8">
-        <v>2123382046.43</v>
+        <v>2121209643.42</v>
       </c>
     </row>
     <row r="2040" spans="1:7" x14ac:dyDescent="0.25">
@@ -59612,8 +59612,8 @@
       <c r="C2040" s="6">
         <v>46275</v>
       </c>
-      <c r="D2040" s="7">
-        <v>1.377458</v>
+      <c r="D2040" s="11">
+        <v>1.37665</v>
       </c>
       <c r="E2040" s="8">
         <v>33640296</v>
@@ -59622,7 +59622,7 @@
         <v>1131</v>
       </c>
       <c r="G2040" s="8">
-        <v>46338085.78</v>
+        <v>46310916.02</v>
       </c>
     </row>
     <row r="2041" spans="1:7" x14ac:dyDescent="0.25">
